--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7928" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7930" uniqueCount="381">
   <si>
     <t>CodCliente</t>
   </si>
@@ -30410,6 +30410,9 @@
       <c r="O434">
         <v>18273589</v>
       </c>
+      <c r="P434" t="s">
+        <v>205</v>
+      </c>
       <c r="Q434" t="s">
         <v>223</v>
       </c>
@@ -30424,6 +30427,9 @@
       </c>
       <c r="AF434" t="s">
         <v>372</v>
+      </c>
+      <c r="AG434" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="435" spans="1:33">

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8411" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8415" uniqueCount="420">
   <si>
     <t>CodCliente</t>
   </si>
@@ -40873,6 +40873,9 @@
       <c r="O589">
         <v>18274360</v>
       </c>
+      <c r="P589" t="s">
+        <v>234</v>
+      </c>
       <c r="Q589" t="s">
         <v>242</v>
       </c>
@@ -40926,6 +40929,9 @@
       <c r="O590">
         <v>18274348</v>
       </c>
+      <c r="P590" t="s">
+        <v>234</v>
+      </c>
       <c r="Q590" t="s">
         <v>242</v>
       </c>
@@ -41351,6 +41357,9 @@
       <c r="O597">
         <v>18274368</v>
       </c>
+      <c r="P597" t="s">
+        <v>235</v>
+      </c>
       <c r="Q597" t="s">
         <v>242</v>
       </c>
@@ -41403,6 +41412,9 @@
       </c>
       <c r="O598">
         <v>18274352</v>
+      </c>
+      <c r="P598" t="s">
+        <v>235</v>
       </c>
       <c r="Q598" t="s">
         <v>242</v>

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -1114,10 +1114,6 @@
     <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 15/09/2026 - Data Comentário: 15/09/2026 09:24</t>
   </si>
   <si>
-    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 16/09/2026 
-Em processamento. - Data Comentário: 15/09/2026 09:24</t>
-  </si>
-  <si>
     <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 18/09/2026 - Data Comentário: 15/09/2026 15:19</t>
   </si>
   <si>
@@ -1207,6 +1203,9 @@
   </si>
   <si>
     <t>Imposto enviado via SCI Report - Data Comentário: 14/09/2026 13:54</t>
+  </si>
+  <si>
+    <t>Imposto enviado via SCI Report - Data Comentário: 16/09/2026 08:55</t>
   </si>
   <si>
     <t>Imposto enviado via SCI Report - Data Comentário: 15/09/2026 10:07</t>
@@ -26505,16 +26504,16 @@
     </row>
     <row r="360" spans="1:34">
       <c r="A360">
-        <v>6779</v>
+        <v>5417</v>
       </c>
       <c r="B360" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C360" t="s">
         <v>61</v>
       </c>
       <c r="D360" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E360" t="s">
         <v>65</v>
@@ -26523,46 +26522,37 @@
         <v>67</v>
       </c>
       <c r="G360">
-        <v>7012</v>
+        <v>5836</v>
       </c>
       <c r="H360">
-        <v>0</v>
+        <v>5784</v>
       </c>
       <c r="I360" t="s">
         <v>72</v>
       </c>
       <c r="J360" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L360" s="1">
-        <v>46281</v>
-      </c>
-      <c r="M360" t="s">
-        <v>211</v>
+        <v>46286</v>
       </c>
       <c r="N360" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O360">
-        <v>18255012</v>
+        <v>17399027</v>
       </c>
       <c r="P360" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="Q360" t="s">
         <v>250</v>
       </c>
       <c r="S360">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="T360" t="s">
-        <v>258</v>
-      </c>
-      <c r="V360" t="s">
-        <v>268</v>
-      </c>
-      <c r="W360" t="s">
-        <v>358</v>
+        <v>257</v>
       </c>
       <c r="AA360">
         <v>0</v>
@@ -26570,16 +26560,13 @@
       <c r="AG360" t="s">
         <v>429</v>
       </c>
-      <c r="AH360" t="s">
-        <v>422</v>
-      </c>
     </row>
     <row r="361" spans="1:34">
       <c r="A361">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B361" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C361" t="s">
         <v>61</v>
@@ -26608,14 +26595,17 @@
       <c r="L361" s="1">
         <v>46286</v>
       </c>
+      <c r="M361" t="s">
+        <v>212</v>
+      </c>
       <c r="N361" t="s">
         <v>217</v>
       </c>
       <c r="O361">
-        <v>17399027</v>
+        <v>16976037</v>
       </c>
       <c r="P361" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="Q361" t="s">
         <v>250</v>
@@ -26624,7 +26614,13 @@
         <v>-5</v>
       </c>
       <c r="T361" t="s">
-        <v>257</v>
+        <v>259</v>
+      </c>
+      <c r="V361" t="s">
+        <v>268</v>
+      </c>
+      <c r="W361" t="s">
+        <v>358</v>
       </c>
       <c r="AA361">
         <v>0</v>
@@ -26632,13 +26628,16 @@
       <c r="AG361" t="s">
         <v>429</v>
       </c>
+      <c r="AH361" t="s">
+        <v>436</v>
+      </c>
     </row>
     <row r="362" spans="1:34">
       <c r="A362">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B362" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C362" t="s">
         <v>61</v>
@@ -26674,10 +26673,10 @@
         <v>217</v>
       </c>
       <c r="O362">
-        <v>16976037</v>
+        <v>17222579</v>
       </c>
       <c r="P362" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q362" t="s">
         <v>250</v>
@@ -26686,7 +26685,7 @@
         <v>-5</v>
       </c>
       <c r="T362" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="V362" t="s">
         <v>268</v>
@@ -26706,10 +26705,10 @@
     </row>
     <row r="363" spans="1:34">
       <c r="A363">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B363" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C363" t="s">
         <v>61</v>
@@ -26718,7 +26717,7 @@
         <v>62</v>
       </c>
       <c r="E363" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F363" t="s">
         <v>67</v>
@@ -26745,10 +26744,10 @@
         <v>217</v>
       </c>
       <c r="O363">
-        <v>17222579</v>
+        <v>18068500</v>
       </c>
       <c r="P363" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="Q363" t="s">
         <v>250</v>
@@ -26757,13 +26756,13 @@
         <v>-5</v>
       </c>
       <c r="T363" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="V363" t="s">
         <v>268</v>
       </c>
       <c r="W363" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="AA363">
         <v>0</v>
@@ -26777,16 +26776,16 @@
     </row>
     <row r="364" spans="1:34">
       <c r="A364">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B364" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C364" t="s">
         <v>61</v>
       </c>
       <c r="D364" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E364" t="s">
         <v>66</v>
@@ -26816,7 +26815,7 @@
         <v>217</v>
       </c>
       <c r="O364">
-        <v>18068500</v>
+        <v>18052419</v>
       </c>
       <c r="P364" t="s">
         <v>227</v>
@@ -26834,7 +26833,7 @@
         <v>268</v>
       </c>
       <c r="W364" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AA364">
         <v>0</v>
@@ -26848,19 +26847,19 @@
     </row>
     <row r="365" spans="1:34">
       <c r="A365">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B365" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C365" t="s">
         <v>61</v>
       </c>
       <c r="D365" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E365" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F365" t="s">
         <v>67</v>
@@ -26887,10 +26886,10 @@
         <v>217</v>
       </c>
       <c r="O365">
-        <v>18052419</v>
+        <v>18077082</v>
       </c>
       <c r="P365" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="Q365" t="s">
         <v>250</v>
@@ -26899,13 +26898,10 @@
         <v>-5</v>
       </c>
       <c r="T365" t="s">
-        <v>253</v>
-      </c>
-      <c r="V365" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="W365" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AA365">
         <v>0</v>
@@ -26919,16 +26915,16 @@
     </row>
     <row r="366" spans="1:34">
       <c r="A366">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B366" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C366" t="s">
         <v>61</v>
       </c>
       <c r="D366" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E366" t="s">
         <v>65</v>
@@ -26952,16 +26948,16 @@
         <v>46286</v>
       </c>
       <c r="M366" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N366" t="s">
         <v>217</v>
       </c>
       <c r="O366">
-        <v>18077082</v>
+        <v>18090149</v>
       </c>
       <c r="P366" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q366" t="s">
         <v>250</v>
@@ -26970,7 +26966,10 @@
         <v>-5</v>
       </c>
       <c r="T366" t="s">
-        <v>260</v>
+        <v>258</v>
+      </c>
+      <c r="V366" t="s">
+        <v>268</v>
       </c>
       <c r="W366" t="s">
         <v>361</v>
@@ -26982,15 +26981,15 @@
         <v>429</v>
       </c>
       <c r="AH366" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
     </row>
     <row r="367" spans="1:34">
       <c r="A367">
-        <v>6779</v>
+        <v>6945</v>
       </c>
       <c r="B367" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C367" t="s">
         <v>61</v>
@@ -27002,7 +27001,7 @@
         <v>65</v>
       </c>
       <c r="F367" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G367">
         <v>5836</v>
@@ -27019,17 +27018,14 @@
       <c r="L367" s="1">
         <v>46286</v>
       </c>
-      <c r="M367" t="s">
-        <v>214</v>
-      </c>
       <c r="N367" t="s">
         <v>217</v>
       </c>
       <c r="O367">
-        <v>18090149</v>
+        <v>18179083</v>
       </c>
       <c r="P367" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="Q367" t="s">
         <v>250</v>
@@ -27038,13 +27034,7 @@
         <v>-5</v>
       </c>
       <c r="T367" t="s">
-        <v>258</v>
-      </c>
-      <c r="V367" t="s">
-        <v>268</v>
-      </c>
-      <c r="W367" t="s">
-        <v>362</v>
+        <v>254</v>
       </c>
       <c r="AA367">
         <v>0</v>
@@ -27053,30 +27043,30 @@
         <v>429</v>
       </c>
       <c r="AH367" t="s">
-        <v>422</v>
+        <v>437</v>
       </c>
     </row>
     <row r="368" spans="1:34">
       <c r="A368">
-        <v>6945</v>
+        <v>6548</v>
       </c>
       <c r="B368" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C368" t="s">
         <v>61</v>
       </c>
       <c r="D368" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E368" t="s">
         <v>65</v>
       </c>
       <c r="F368" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G368">
-        <v>5836</v>
+        <v>5905</v>
       </c>
       <c r="H368">
         <v>5784</v>
@@ -27085,51 +27075,54 @@
         <v>72</v>
       </c>
       <c r="J368" t="s">
-        <v>144</v>
+        <v>83</v>
       </c>
       <c r="L368" s="1">
-        <v>46286</v>
+        <v>46295</v>
       </c>
       <c r="N368" t="s">
         <v>217</v>
       </c>
       <c r="O368">
-        <v>18179083</v>
+        <v>17222671</v>
       </c>
       <c r="P368" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q368" t="s">
         <v>250</v>
       </c>
       <c r="S368">
-        <v>-5</v>
+        <v>-14</v>
       </c>
       <c r="T368" t="s">
-        <v>254</v>
+        <v>252</v>
+      </c>
+      <c r="V368" t="s">
+        <v>268</v>
       </c>
       <c r="AA368">
         <v>0</v>
       </c>
       <c r="AG368" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AH368" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="369" spans="1:34">
       <c r="A369">
-        <v>6548</v>
+        <v>6404</v>
       </c>
       <c r="B369" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="C369" t="s">
         <v>61</v>
       </c>
       <c r="D369" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E369" t="s">
         <v>65</v>
@@ -27138,49 +27131,52 @@
         <v>67</v>
       </c>
       <c r="G369">
-        <v>5905</v>
+        <v>5903</v>
       </c>
       <c r="H369">
-        <v>5784</v>
+        <v>5830</v>
       </c>
       <c r="I369" t="s">
         <v>72</v>
       </c>
       <c r="J369" t="s">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="L369" s="1">
-        <v>46295</v>
+        <v>46286</v>
+      </c>
+      <c r="M369" t="s">
+        <v>213</v>
       </c>
       <c r="N369" t="s">
         <v>217</v>
       </c>
       <c r="O369">
-        <v>17222671</v>
+        <v>16962221</v>
       </c>
       <c r="P369" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q369" t="s">
         <v>250</v>
       </c>
       <c r="S369">
-        <v>-14</v>
+        <v>-5</v>
       </c>
       <c r="T369" t="s">
-        <v>252</v>
-      </c>
-      <c r="V369" t="s">
-        <v>268</v>
+        <v>261</v>
+      </c>
+      <c r="W369" t="s">
+        <v>362</v>
       </c>
       <c r="AA369">
         <v>0</v>
       </c>
       <c r="AG369" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="AH369" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
     </row>
     <row r="370" spans="1:34">
@@ -27203,28 +27199,25 @@
         <v>67</v>
       </c>
       <c r="G370">
-        <v>5903</v>
+        <v>5830</v>
       </c>
       <c r="H370">
-        <v>5830</v>
+        <v>5784</v>
       </c>
       <c r="I370" t="s">
         <v>72</v>
       </c>
       <c r="J370" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L370" s="1">
         <v>46286</v>
       </c>
-      <c r="M370" t="s">
-        <v>213</v>
-      </c>
       <c r="N370" t="s">
         <v>217</v>
       </c>
       <c r="O370">
-        <v>16962221</v>
+        <v>16962211</v>
       </c>
       <c r="P370" t="s">
         <v>233</v>
@@ -27238,9 +27231,6 @@
       <c r="T370" t="s">
         <v>261</v>
       </c>
-      <c r="W370" t="s">
-        <v>363</v>
-      </c>
       <c r="AA370">
         <v>0</v>
       </c>
@@ -27253,16 +27243,16 @@
     </row>
     <row r="371" spans="1:34">
       <c r="A371">
-        <v>6404</v>
+        <v>6548</v>
       </c>
       <c r="B371" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C371" t="s">
         <v>61</v>
       </c>
       <c r="D371" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E371" t="s">
         <v>65</v>
@@ -27271,7 +27261,7 @@
         <v>67</v>
       </c>
       <c r="G371">
-        <v>5830</v>
+        <v>5853</v>
       </c>
       <c r="H371">
         <v>5784</v>
@@ -27280,28 +27270,31 @@
         <v>72</v>
       </c>
       <c r="J371" t="s">
-        <v>146</v>
+        <v>84</v>
       </c>
       <c r="L371" s="1">
-        <v>46286</v>
+        <v>46295</v>
       </c>
       <c r="N371" t="s">
         <v>217</v>
       </c>
       <c r="O371">
-        <v>16962211</v>
+        <v>17222589</v>
       </c>
       <c r="P371" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="Q371" t="s">
         <v>250</v>
       </c>
       <c r="S371">
-        <v>-5</v>
+        <v>-14</v>
       </c>
       <c r="T371" t="s">
-        <v>261</v>
+        <v>252</v>
+      </c>
+      <c r="V371" t="s">
+        <v>268</v>
       </c>
       <c r="AA371">
         <v>0</v>
@@ -27310,15 +27303,15 @@
         <v>429</v>
       </c>
       <c r="AH371" t="s">
-        <v>422</v>
+        <v>436</v>
       </c>
     </row>
     <row r="372" spans="1:34">
       <c r="A372">
-        <v>6548</v>
+        <v>5417</v>
       </c>
       <c r="B372" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C372" t="s">
         <v>61</v>
@@ -27333,7 +27326,7 @@
         <v>67</v>
       </c>
       <c r="G372">
-        <v>5853</v>
+        <v>5847</v>
       </c>
       <c r="H372">
         <v>5784</v>
@@ -27342,31 +27335,28 @@
         <v>72</v>
       </c>
       <c r="J372" t="s">
-        <v>84</v>
+        <v>147</v>
       </c>
       <c r="L372" s="1">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="N372" t="s">
         <v>217</v>
       </c>
       <c r="O372">
-        <v>17222589</v>
+        <v>18158417</v>
       </c>
       <c r="P372" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q372" t="s">
         <v>250</v>
       </c>
       <c r="S372">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="T372" t="s">
-        <v>252</v>
-      </c>
-      <c r="V372" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="AA372">
         <v>0</v>
@@ -27374,22 +27364,19 @@
       <c r="AG372" t="s">
         <v>429</v>
       </c>
-      <c r="AH372" t="s">
-        <v>436</v>
-      </c>
     </row>
     <row r="373" spans="1:34">
       <c r="A373">
-        <v>5417</v>
+        <v>6779</v>
       </c>
       <c r="B373" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C373" t="s">
         <v>61</v>
       </c>
       <c r="D373" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E373" t="s">
         <v>65</v>
@@ -27416,10 +27403,10 @@
         <v>217</v>
       </c>
       <c r="O373">
-        <v>18158417</v>
+        <v>18158764</v>
       </c>
       <c r="P373" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q373" t="s">
         <v>250</v>
@@ -27428,7 +27415,10 @@
         <v>-12</v>
       </c>
       <c r="T373" t="s">
-        <v>257</v>
+        <v>258</v>
+      </c>
+      <c r="V373" t="s">
+        <v>268</v>
       </c>
       <c r="AA373">
         <v>0</v>
@@ -27436,19 +27426,22 @@
       <c r="AG373" t="s">
         <v>429</v>
       </c>
+      <c r="AH373" t="s">
+        <v>422</v>
+      </c>
     </row>
     <row r="374" spans="1:34">
       <c r="A374">
-        <v>6779</v>
+        <v>6548</v>
       </c>
       <c r="B374" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C374" t="s">
         <v>61</v>
       </c>
       <c r="D374" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E374" t="s">
         <v>65</v>
@@ -27457,7 +27450,7 @@
         <v>67</v>
       </c>
       <c r="G374">
-        <v>5847</v>
+        <v>5906</v>
       </c>
       <c r="H374">
         <v>5784</v>
@@ -27466,28 +27459,28 @@
         <v>72</v>
       </c>
       <c r="J374" t="s">
-        <v>147</v>
+        <v>90</v>
       </c>
       <c r="L374" s="1">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="N374" t="s">
         <v>217</v>
       </c>
       <c r="O374">
-        <v>18158764</v>
+        <v>17222688</v>
       </c>
       <c r="P374" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="Q374" t="s">
         <v>250</v>
       </c>
       <c r="S374">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="T374" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="V374" t="s">
         <v>268</v>
@@ -27496,10 +27489,10 @@
         <v>0</v>
       </c>
       <c r="AG374" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AH374" t="s">
-        <v>422</v>
+        <v>436</v>
       </c>
     </row>
     <row r="375" spans="1:34">
@@ -27522,7 +27515,7 @@
         <v>67</v>
       </c>
       <c r="G375">
-        <v>5906</v>
+        <v>5907</v>
       </c>
       <c r="H375">
         <v>5784</v>
@@ -27531,7 +27524,7 @@
         <v>72</v>
       </c>
       <c r="J375" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="L375" s="1">
         <v>46295</v>
@@ -27540,7 +27533,7 @@
         <v>217</v>
       </c>
       <c r="O375">
-        <v>17222688</v>
+        <v>17222699</v>
       </c>
       <c r="P375" t="s">
         <v>231</v>
@@ -27561,7 +27554,7 @@
         <v>0</v>
       </c>
       <c r="AG375" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="AH375" t="s">
         <v>436</v>
@@ -27569,10 +27562,10 @@
     </row>
     <row r="376" spans="1:34">
       <c r="A376">
-        <v>6548</v>
+        <v>5417</v>
       </c>
       <c r="B376" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C376" t="s">
         <v>61</v>
@@ -27587,57 +27580,57 @@
         <v>67</v>
       </c>
       <c r="G376">
-        <v>5907</v>
+        <v>6348</v>
       </c>
       <c r="H376">
-        <v>5784</v>
+        <v>0</v>
       </c>
       <c r="I376" t="s">
         <v>72</v>
       </c>
       <c r="J376" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L376" s="1">
-        <v>46295</v>
+        <v>46288</v>
+      </c>
+      <c r="M376" t="s">
+        <v>215</v>
       </c>
       <c r="N376" t="s">
         <v>217</v>
       </c>
       <c r="O376">
-        <v>17222699</v>
+        <v>18274307</v>
       </c>
       <c r="P376" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q376" t="s">
         <v>250</v>
       </c>
       <c r="S376">
-        <v>-14</v>
+        <v>-7</v>
       </c>
       <c r="T376" t="s">
-        <v>252</v>
-      </c>
-      <c r="V376" t="s">
-        <v>268</v>
+        <v>257</v>
+      </c>
+      <c r="W376" t="s">
+        <v>363</v>
       </c>
       <c r="AA376">
         <v>0</v>
       </c>
       <c r="AG376" t="s">
-        <v>429</v>
-      </c>
-      <c r="AH376" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
     </row>
     <row r="377" spans="1:34">
       <c r="A377">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B377" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C377" t="s">
         <v>61</v>
@@ -27664,28 +27657,31 @@
         <v>93</v>
       </c>
       <c r="L377" s="1">
-        <v>46288</v>
+        <v>46282</v>
       </c>
       <c r="M377" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="N377" t="s">
         <v>217</v>
       </c>
       <c r="O377">
-        <v>18274307</v>
+        <v>18271101</v>
       </c>
       <c r="P377" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="Q377" t="s">
         <v>250</v>
       </c>
       <c r="S377">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="T377" t="s">
-        <v>257</v>
+        <v>259</v>
+      </c>
+      <c r="V377" t="s">
+        <v>268</v>
       </c>
       <c r="W377" t="s">
         <v>364</v>
@@ -27696,13 +27692,16 @@
       <c r="AG377" t="s">
         <v>430</v>
       </c>
+      <c r="AH377" t="s">
+        <v>436</v>
+      </c>
     </row>
     <row r="378" spans="1:34">
       <c r="A378">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B378" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C378" t="s">
         <v>61</v>
@@ -27717,63 +27716,57 @@
         <v>67</v>
       </c>
       <c r="G378">
-        <v>6348</v>
+        <v>1913</v>
       </c>
       <c r="H378">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="I378" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J378" t="s">
-        <v>93</v>
+        <v>148</v>
       </c>
       <c r="L378" s="1">
-        <v>46282</v>
-      </c>
-      <c r="M378" t="s">
-        <v>211</v>
+        <v>46286</v>
       </c>
       <c r="N378" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="O378">
-        <v>18271101</v>
+        <v>17988579</v>
       </c>
       <c r="P378" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="Q378" t="s">
         <v>250</v>
       </c>
       <c r="S378">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="T378" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="V378" t="s">
         <v>268</v>
       </c>
-      <c r="W378" t="s">
-        <v>365</v>
-      </c>
       <c r="AA378">
         <v>0</v>
       </c>
       <c r="AG378" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AH378" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
     </row>
     <row r="379" spans="1:34">
       <c r="A379">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B379" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C379" t="s">
         <v>61</v>
@@ -27782,7 +27775,7 @@
         <v>62</v>
       </c>
       <c r="E379" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F379" t="s">
         <v>67</v>
@@ -27806,10 +27799,10 @@
         <v>216</v>
       </c>
       <c r="O379">
-        <v>17988579</v>
+        <v>18048433</v>
       </c>
       <c r="P379" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q379" t="s">
         <v>250</v>
@@ -27818,7 +27811,7 @@
         <v>-5</v>
       </c>
       <c r="T379" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="V379" t="s">
         <v>268</v>
@@ -27829,16 +27822,13 @@
       <c r="AG379" t="s">
         <v>429</v>
       </c>
-      <c r="AH379" t="s">
-        <v>423</v>
-      </c>
     </row>
     <row r="380" spans="1:34">
       <c r="A380">
-        <v>6627</v>
+        <v>6949</v>
       </c>
       <c r="B380" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C380" t="s">
         <v>61</v>
@@ -27847,10 +27837,10 @@
         <v>62</v>
       </c>
       <c r="E380" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F380" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G380">
         <v>1913</v>
@@ -27871,10 +27861,10 @@
         <v>216</v>
       </c>
       <c r="O380">
-        <v>18048433</v>
+        <v>18214877</v>
       </c>
       <c r="P380" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q380" t="s">
         <v>250</v>
@@ -27883,10 +27873,7 @@
         <v>-5</v>
       </c>
       <c r="T380" t="s">
-        <v>253</v>
-      </c>
-      <c r="V380" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="AA380">
         <v>0</v>
@@ -27894,19 +27881,22 @@
       <c r="AG380" t="s">
         <v>429</v>
       </c>
+      <c r="AH380" t="s">
+        <v>423</v>
+      </c>
     </row>
     <row r="381" spans="1:34">
       <c r="A381">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B381" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C381" t="s">
         <v>61</v>
       </c>
       <c r="D381" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E381" t="s">
         <v>65</v>
@@ -27915,37 +27905,43 @@
         <v>68</v>
       </c>
       <c r="G381">
-        <v>1913</v>
+        <v>11617</v>
       </c>
       <c r="H381">
-        <v>1862</v>
+        <v>0</v>
       </c>
       <c r="I381" t="s">
         <v>73</v>
       </c>
       <c r="J381" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L381" s="1">
-        <v>46286</v>
+        <v>46283</v>
+      </c>
+      <c r="M381" t="s">
+        <v>212</v>
       </c>
       <c r="N381" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O381">
-        <v>18214877</v>
+        <v>18186565</v>
       </c>
       <c r="P381" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="Q381" t="s">
         <v>250</v>
       </c>
       <c r="S381">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="T381" t="s">
-        <v>255</v>
+        <v>256</v>
+      </c>
+      <c r="W381" t="s">
+        <v>365</v>
       </c>
       <c r="AA381">
         <v>0</v>
@@ -27959,10 +27955,10 @@
     </row>
     <row r="382" spans="1:34">
       <c r="A382">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B382" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C382" t="s">
         <v>61</v>
@@ -27998,7 +27994,7 @@
         <v>218</v>
       </c>
       <c r="O382">
-        <v>18186565</v>
+        <v>18186566</v>
       </c>
       <c r="P382" t="s">
         <v>245</v>
@@ -28013,7 +28009,7 @@
         <v>256</v>
       </c>
       <c r="W382" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AA382">
         <v>0</v>
@@ -28027,16 +28023,16 @@
     </row>
     <row r="383" spans="1:34">
       <c r="A383">
-        <v>6963</v>
+        <v>6945</v>
       </c>
       <c r="B383" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C383" t="s">
         <v>61</v>
       </c>
       <c r="D383" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E383" t="s">
         <v>65</v>
@@ -28045,7 +28041,7 @@
         <v>68</v>
       </c>
       <c r="G383">
-        <v>11617</v>
+        <v>5764</v>
       </c>
       <c r="H383">
         <v>0</v>
@@ -28054,66 +28050,57 @@
         <v>73</v>
       </c>
       <c r="J383" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L383" s="1">
-        <v>46283</v>
-      </c>
-      <c r="M383" t="s">
-        <v>212</v>
+        <v>46290</v>
       </c>
       <c r="N383" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="O383">
-        <v>18186566</v>
+        <v>18220203</v>
       </c>
       <c r="P383" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="Q383" t="s">
         <v>250</v>
       </c>
       <c r="S383">
-        <v>-2</v>
+        <v>-9</v>
       </c>
       <c r="T383" t="s">
-        <v>256</v>
-      </c>
-      <c r="W383" t="s">
-        <v>366</v>
+        <v>254</v>
       </c>
       <c r="AA383">
         <v>0</v>
       </c>
       <c r="AG383" t="s">
-        <v>429</v>
-      </c>
-      <c r="AH383" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
     </row>
     <row r="384" spans="1:34">
       <c r="A384">
-        <v>6945</v>
+        <v>6548</v>
       </c>
       <c r="B384" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C384" t="s">
         <v>61</v>
       </c>
       <c r="D384" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E384" t="s">
         <v>65</v>
       </c>
       <c r="F384" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G384">
-        <v>5764</v>
+        <v>1876</v>
       </c>
       <c r="H384">
         <v>0</v>
@@ -28122,42 +28109,54 @@
         <v>73</v>
       </c>
       <c r="J384" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L384" s="1">
-        <v>46290</v>
+        <v>46283</v>
+      </c>
+      <c r="M384" t="s">
+        <v>212</v>
       </c>
       <c r="N384" t="s">
         <v>216</v>
       </c>
       <c r="O384">
-        <v>18220203</v>
+        <v>17988555</v>
       </c>
       <c r="P384" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q384" t="s">
         <v>250</v>
       </c>
       <c r="S384">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="T384" t="s">
-        <v>254</v>
+        <v>252</v>
+      </c>
+      <c r="V384" t="s">
+        <v>268</v>
+      </c>
+      <c r="W384" t="s">
+        <v>366</v>
       </c>
       <c r="AA384">
         <v>0</v>
       </c>
       <c r="AG384" t="s">
-        <v>431</v>
+        <v>430</v>
+      </c>
+      <c r="AH384" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="385" spans="1:34">
       <c r="A385">
-        <v>6548</v>
+        <v>6949</v>
       </c>
       <c r="B385" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C385" t="s">
         <v>61</v>
@@ -28169,7 +28168,7 @@
         <v>65</v>
       </c>
       <c r="F385" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G385">
         <v>1876</v>
@@ -28193,10 +28192,10 @@
         <v>216</v>
       </c>
       <c r="O385">
-        <v>17988555</v>
+        <v>18214865</v>
       </c>
       <c r="P385" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q385" t="s">
         <v>250</v>
@@ -28205,13 +28204,10 @@
         <v>-2</v>
       </c>
       <c r="T385" t="s">
-        <v>252</v>
-      </c>
-      <c r="V385" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="W385" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AA385">
         <v>0</v>
@@ -28225,10 +28221,10 @@
     </row>
     <row r="386" spans="1:34">
       <c r="A386">
-        <v>6949</v>
+        <v>6627</v>
       </c>
       <c r="B386" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C386" t="s">
         <v>61</v>
@@ -28237,13 +28233,13 @@
         <v>62</v>
       </c>
       <c r="E386" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F386" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G386">
-        <v>1876</v>
+        <v>11411</v>
       </c>
       <c r="H386">
         <v>0</v>
@@ -28252,7 +28248,7 @@
         <v>73</v>
       </c>
       <c r="J386" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L386" s="1">
         <v>46283</v>
@@ -28264,10 +28260,10 @@
         <v>216</v>
       </c>
       <c r="O386">
-        <v>18214865</v>
+        <v>18048483</v>
       </c>
       <c r="P386" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="Q386" t="s">
         <v>250</v>
@@ -28276,10 +28272,13 @@
         <v>-2</v>
       </c>
       <c r="T386" t="s">
-        <v>255</v>
+        <v>253</v>
+      </c>
+      <c r="V386" t="s">
+        <v>268</v>
       </c>
       <c r="W386" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AA386">
         <v>0</v>
@@ -28287,16 +28286,13 @@
       <c r="AG386" t="s">
         <v>430</v>
       </c>
-      <c r="AH386" t="s">
-        <v>423</v>
-      </c>
     </row>
     <row r="387" spans="1:34">
       <c r="A387">
-        <v>6627</v>
+        <v>6949</v>
       </c>
       <c r="B387" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C387" t="s">
         <v>61</v>
@@ -28305,10 +28301,10 @@
         <v>62</v>
       </c>
       <c r="E387" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F387" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G387">
         <v>11411</v>
@@ -28332,10 +28328,10 @@
         <v>216</v>
       </c>
       <c r="O387">
-        <v>18048483</v>
+        <v>18214925</v>
       </c>
       <c r="P387" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q387" t="s">
         <v>250</v>
@@ -28344,13 +28340,10 @@
         <v>-2</v>
       </c>
       <c r="T387" t="s">
-        <v>253</v>
-      </c>
-      <c r="V387" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="W387" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AA387">
         <v>0</v>
@@ -28358,19 +28351,22 @@
       <c r="AG387" t="s">
         <v>430</v>
       </c>
+      <c r="AH387" t="s">
+        <v>423</v>
+      </c>
     </row>
     <row r="388" spans="1:34">
       <c r="A388">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B388" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C388" t="s">
         <v>61</v>
       </c>
       <c r="D388" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E388" t="s">
         <v>65</v>
@@ -28379,7 +28375,7 @@
         <v>68</v>
       </c>
       <c r="G388">
-        <v>11411</v>
+        <v>1877</v>
       </c>
       <c r="H388">
         <v>0</v>
@@ -28388,34 +28384,28 @@
         <v>73</v>
       </c>
       <c r="J388" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L388" s="1">
-        <v>46283</v>
-      </c>
-      <c r="M388" t="s">
-        <v>212</v>
+        <v>46293</v>
       </c>
       <c r="N388" t="s">
         <v>216</v>
       </c>
       <c r="O388">
-        <v>18214925</v>
+        <v>18220188</v>
       </c>
       <c r="P388" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="Q388" t="s">
         <v>250</v>
       </c>
       <c r="S388">
-        <v>-2</v>
+        <v>-12</v>
       </c>
       <c r="T388" t="s">
-        <v>255</v>
-      </c>
-      <c r="W388" t="s">
-        <v>367</v>
+        <v>254</v>
       </c>
       <c r="AA388">
         <v>0</v>
@@ -28423,16 +28413,13 @@
       <c r="AG388" t="s">
         <v>430</v>
       </c>
-      <c r="AH388" t="s">
-        <v>423</v>
-      </c>
     </row>
     <row r="389" spans="1:34">
       <c r="A389">
-        <v>6945</v>
+        <v>6628</v>
       </c>
       <c r="B389" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C389" t="s">
         <v>61</v>
@@ -28441,13 +28428,13 @@
         <v>63</v>
       </c>
       <c r="E389" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F389" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G389">
-        <v>1877</v>
+        <v>1879</v>
       </c>
       <c r="H389">
         <v>0</v>
@@ -28456,28 +28443,37 @@
         <v>73</v>
       </c>
       <c r="J389" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L389" s="1">
-        <v>46293</v>
+        <v>46283</v>
+      </c>
+      <c r="M389" t="s">
+        <v>212</v>
       </c>
       <c r="N389" t="s">
         <v>216</v>
       </c>
       <c r="O389">
-        <v>18220188</v>
+        <v>17988684</v>
       </c>
       <c r="P389" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q389" t="s">
         <v>250</v>
       </c>
       <c r="S389">
-        <v>-12</v>
+        <v>-2</v>
       </c>
       <c r="T389" t="s">
-        <v>254</v>
+        <v>253</v>
+      </c>
+      <c r="V389" t="s">
+        <v>268</v>
+      </c>
+      <c r="W389" t="s">
+        <v>366</v>
       </c>
       <c r="AA389">
         <v>0</v>
@@ -28485,13 +28481,16 @@
       <c r="AG389" t="s">
         <v>430</v>
       </c>
+      <c r="AH389" t="s">
+        <v>423</v>
+      </c>
     </row>
     <row r="390" spans="1:34">
       <c r="A390">
-        <v>6628</v>
+        <v>6945</v>
       </c>
       <c r="B390" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C390" t="s">
         <v>61</v>
@@ -28500,10 +28499,10 @@
         <v>63</v>
       </c>
       <c r="E390" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F390" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G390">
         <v>1879</v>
@@ -28527,10 +28526,10 @@
         <v>216</v>
       </c>
       <c r="O390">
-        <v>17988684</v>
+        <v>18220194</v>
       </c>
       <c r="P390" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Q390" t="s">
         <v>250</v>
@@ -28539,13 +28538,10 @@
         <v>-2</v>
       </c>
       <c r="T390" t="s">
-        <v>253</v>
-      </c>
-      <c r="V390" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="W390" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AA390">
         <v>0</v>
@@ -28553,22 +28549,19 @@
       <c r="AG390" t="s">
         <v>430</v>
       </c>
-      <c r="AH390" t="s">
-        <v>423</v>
-      </c>
     </row>
     <row r="391" spans="1:34">
       <c r="A391">
-        <v>6945</v>
+        <v>6962</v>
       </c>
       <c r="B391" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C391" t="s">
         <v>61</v>
       </c>
       <c r="D391" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E391" t="s">
         <v>65</v>
@@ -28577,7 +28570,7 @@
         <v>68</v>
       </c>
       <c r="G391">
-        <v>1879</v>
+        <v>1881</v>
       </c>
       <c r="H391">
         <v>0</v>
@@ -28586,34 +28579,28 @@
         <v>73</v>
       </c>
       <c r="J391" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L391" s="1">
-        <v>46283</v>
-      </c>
-      <c r="M391" t="s">
-        <v>212</v>
+        <v>46287</v>
       </c>
       <c r="N391" t="s">
         <v>216</v>
       </c>
       <c r="O391">
-        <v>18220194</v>
+        <v>18260044</v>
       </c>
       <c r="P391" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q391" t="s">
         <v>250</v>
       </c>
       <c r="S391">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="T391" t="s">
-        <v>254</v>
-      </c>
-      <c r="W391" t="s">
-        <v>367</v>
+        <v>256</v>
       </c>
       <c r="AA391">
         <v>0</v>
@@ -28621,13 +28608,16 @@
       <c r="AG391" t="s">
         <v>430</v>
       </c>
+      <c r="AH391" t="s">
+        <v>423</v>
+      </c>
     </row>
     <row r="392" spans="1:34">
       <c r="A392">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B392" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C392" t="s">
         <v>61</v>
@@ -28660,7 +28650,7 @@
         <v>216</v>
       </c>
       <c r="O392">
-        <v>18260044</v>
+        <v>18260177</v>
       </c>
       <c r="P392" t="s">
         <v>239</v>
@@ -28686,25 +28676,25 @@
     </row>
     <row r="393" spans="1:34">
       <c r="A393">
-        <v>6963</v>
+        <v>6548</v>
       </c>
       <c r="B393" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C393" t="s">
         <v>61</v>
       </c>
       <c r="D393" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E393" t="s">
         <v>65</v>
       </c>
       <c r="F393" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G393">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="H393">
         <v>0</v>
@@ -28713,7 +28703,7 @@
         <v>73</v>
       </c>
       <c r="J393" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L393" s="1">
         <v>46287</v>
@@ -28722,10 +28712,10 @@
         <v>216</v>
       </c>
       <c r="O393">
-        <v>18260177</v>
+        <v>17988567</v>
       </c>
       <c r="P393" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="Q393" t="s">
         <v>250</v>
@@ -28734,7 +28724,10 @@
         <v>-6</v>
       </c>
       <c r="T393" t="s">
-        <v>256</v>
+        <v>252</v>
+      </c>
+      <c r="V393" t="s">
+        <v>268</v>
       </c>
       <c r="AA393">
         <v>0</v>
@@ -28748,10 +28741,10 @@
     </row>
     <row r="394" spans="1:34">
       <c r="A394">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B394" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C394" t="s">
         <v>61</v>
@@ -28760,7 +28753,7 @@
         <v>62</v>
       </c>
       <c r="E394" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F394" t="s">
         <v>67</v>
@@ -28784,10 +28777,10 @@
         <v>216</v>
       </c>
       <c r="O394">
-        <v>17988567</v>
+        <v>17968390</v>
       </c>
       <c r="P394" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q394" t="s">
         <v>250</v>
@@ -28796,7 +28789,7 @@
         <v>-6</v>
       </c>
       <c r="T394" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="V394" t="s">
         <v>268</v>
@@ -28807,16 +28800,13 @@
       <c r="AG394" t="s">
         <v>430</v>
       </c>
-      <c r="AH394" t="s">
-        <v>423</v>
-      </c>
     </row>
     <row r="395" spans="1:34">
       <c r="A395">
-        <v>6627</v>
+        <v>6949</v>
       </c>
       <c r="B395" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C395" t="s">
         <v>61</v>
@@ -28825,10 +28815,10 @@
         <v>62</v>
       </c>
       <c r="E395" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F395" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G395">
         <v>1882</v>
@@ -28849,10 +28839,10 @@
         <v>216</v>
       </c>
       <c r="O395">
-        <v>17968390</v>
+        <v>18214871</v>
       </c>
       <c r="P395" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q395" t="s">
         <v>250</v>
@@ -28861,10 +28851,7 @@
         <v>-6</v>
       </c>
       <c r="T395" t="s">
-        <v>253</v>
-      </c>
-      <c r="V395" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="AA395">
         <v>0</v>
@@ -28872,13 +28859,16 @@
       <c r="AG395" t="s">
         <v>430</v>
       </c>
+      <c r="AH395" t="s">
+        <v>423</v>
+      </c>
     </row>
     <row r="396" spans="1:34">
       <c r="A396">
-        <v>6949</v>
+        <v>6548</v>
       </c>
       <c r="B396" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C396" t="s">
         <v>61</v>
@@ -28890,10 +28880,10 @@
         <v>65</v>
       </c>
       <c r="F396" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G396">
-        <v>1882</v>
+        <v>7026</v>
       </c>
       <c r="H396">
         <v>0</v>
@@ -28902,34 +28892,37 @@
         <v>73</v>
       </c>
       <c r="J396" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L396" s="1">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="N396" t="s">
         <v>216</v>
       </c>
       <c r="O396">
-        <v>18214871</v>
+        <v>18094899</v>
       </c>
       <c r="P396" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="Q396" t="s">
         <v>250</v>
       </c>
       <c r="S396">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="T396" t="s">
-        <v>255</v>
+        <v>252</v>
+      </c>
+      <c r="V396" t="s">
+        <v>268</v>
       </c>
       <c r="AA396">
         <v>0</v>
       </c>
       <c r="AG396" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AH396" t="s">
         <v>423</v>
@@ -28937,10 +28930,10 @@
     </row>
     <row r="397" spans="1:34">
       <c r="A397">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B397" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C397" t="s">
         <v>61</v>
@@ -28949,7 +28942,7 @@
         <v>62</v>
       </c>
       <c r="E397" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F397" t="s">
         <v>67</v>
@@ -28973,10 +28966,10 @@
         <v>216</v>
       </c>
       <c r="O397">
-        <v>18094899</v>
+        <v>18048473</v>
       </c>
       <c r="P397" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q397" t="s">
         <v>250</v>
@@ -28985,7 +28978,7 @@
         <v>-7</v>
       </c>
       <c r="T397" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="V397" t="s">
         <v>268</v>
@@ -28996,16 +28989,13 @@
       <c r="AG397" t="s">
         <v>429</v>
       </c>
-      <c r="AH397" t="s">
-        <v>423</v>
-      </c>
     </row>
     <row r="398" spans="1:34">
       <c r="A398">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B398" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C398" t="s">
         <v>61</v>
@@ -29014,43 +29004,43 @@
         <v>62</v>
       </c>
       <c r="E398" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F398" t="s">
         <v>67</v>
       </c>
       <c r="G398">
-        <v>7026</v>
+        <v>1914</v>
       </c>
       <c r="H398">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="I398" t="s">
         <v>73</v>
       </c>
       <c r="J398" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L398" s="1">
-        <v>46288</v>
+        <v>46286</v>
       </c>
       <c r="N398" t="s">
         <v>216</v>
       </c>
       <c r="O398">
-        <v>18048473</v>
+        <v>17988591</v>
       </c>
       <c r="P398" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q398" t="s">
         <v>250</v>
       </c>
       <c r="S398">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="T398" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="V398" t="s">
         <v>268</v>
@@ -29061,13 +29051,16 @@
       <c r="AG398" t="s">
         <v>429</v>
       </c>
+      <c r="AH398" t="s">
+        <v>423</v>
+      </c>
     </row>
     <row r="399" spans="1:34">
       <c r="A399">
-        <v>6548</v>
+        <v>6949</v>
       </c>
       <c r="B399" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C399" t="s">
         <v>61</v>
@@ -29079,7 +29072,7 @@
         <v>65</v>
       </c>
       <c r="F399" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G399">
         <v>1914</v>
@@ -29100,10 +29093,10 @@
         <v>216</v>
       </c>
       <c r="O399">
-        <v>17988591</v>
+        <v>18214883</v>
       </c>
       <c r="P399" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q399" t="s">
         <v>250</v>
@@ -29112,10 +29105,7 @@
         <v>-5</v>
       </c>
       <c r="T399" t="s">
-        <v>252</v>
-      </c>
-      <c r="V399" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="AA399">
         <v>0</v>
@@ -29129,10 +29119,10 @@
     </row>
     <row r="400" spans="1:34">
       <c r="A400">
-        <v>6949</v>
+        <v>5417</v>
       </c>
       <c r="B400" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C400" t="s">
         <v>61</v>
@@ -29144,40 +29134,40 @@
         <v>65</v>
       </c>
       <c r="F400" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G400">
-        <v>1914</v>
+        <v>6759</v>
       </c>
       <c r="H400">
-        <v>1862</v>
+        <v>1788</v>
       </c>
       <c r="I400" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J400" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L400" s="1">
-        <v>46286</v>
+        <v>46289</v>
       </c>
       <c r="N400" t="s">
         <v>216</v>
       </c>
       <c r="O400">
-        <v>18214883</v>
+        <v>17399190</v>
       </c>
       <c r="P400" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q400" t="s">
         <v>250</v>
       </c>
       <c r="S400">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="T400" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AA400">
         <v>0</v>
@@ -29186,15 +29176,15 @@
         <v>429</v>
       </c>
       <c r="AH400" t="s">
-        <v>423</v>
+        <v>438</v>
       </c>
     </row>
     <row r="401" spans="1:34">
       <c r="A401">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B401" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C401" t="s">
         <v>61</v>
@@ -29227,7 +29217,7 @@
         <v>216</v>
       </c>
       <c r="O401">
-        <v>17399190</v>
+        <v>16976177</v>
       </c>
       <c r="P401" t="s">
         <v>240</v>
@@ -29239,7 +29229,10 @@
         <v>-8</v>
       </c>
       <c r="T401" t="s">
-        <v>257</v>
+        <v>259</v>
+      </c>
+      <c r="V401" t="s">
+        <v>268</v>
       </c>
       <c r="AA401">
         <v>0</v>
@@ -29253,16 +29246,16 @@
     </row>
     <row r="402" spans="1:34">
       <c r="A402">
-        <v>6486</v>
+        <v>6705</v>
       </c>
       <c r="B402" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C402" t="s">
         <v>61</v>
       </c>
       <c r="D402" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E402" t="s">
         <v>65</v>
@@ -29289,7 +29282,7 @@
         <v>216</v>
       </c>
       <c r="O402">
-        <v>16976177</v>
+        <v>17949019</v>
       </c>
       <c r="P402" t="s">
         <v>240</v>
@@ -29301,10 +29294,7 @@
         <v>-8</v>
       </c>
       <c r="T402" t="s">
-        <v>259</v>
-      </c>
-      <c r="V402" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="AA402">
         <v>0</v>
@@ -29318,16 +29308,16 @@
     </row>
     <row r="403" spans="1:34">
       <c r="A403">
-        <v>6705</v>
+        <v>5417</v>
       </c>
       <c r="B403" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C403" t="s">
         <v>61</v>
       </c>
       <c r="D403" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E403" t="s">
         <v>65</v>
@@ -29336,25 +29326,28 @@
         <v>67</v>
       </c>
       <c r="G403">
-        <v>6759</v>
+        <v>11678</v>
       </c>
       <c r="H403">
-        <v>1788</v>
+        <v>0</v>
       </c>
       <c r="I403" t="s">
         <v>74</v>
       </c>
       <c r="J403" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L403" s="1">
-        <v>46289</v>
+        <v>46281</v>
+      </c>
+      <c r="M403" t="s">
+        <v>211</v>
       </c>
       <c r="N403" t="s">
         <v>216</v>
       </c>
       <c r="O403">
-        <v>17949019</v>
+        <v>16948688</v>
       </c>
       <c r="P403" t="s">
         <v>240</v>
@@ -29363,10 +29356,13 @@
         <v>250</v>
       </c>
       <c r="S403">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="T403" t="s">
-        <v>258</v>
+        <v>257</v>
+      </c>
+      <c r="W403" t="s">
+        <v>367</v>
       </c>
       <c r="AA403">
         <v>0</v>
@@ -29380,16 +29376,16 @@
     </row>
     <row r="404" spans="1:34">
       <c r="A404">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B404" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C404" t="s">
         <v>61</v>
       </c>
       <c r="D404" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E404" t="s">
         <v>65</v>
@@ -29419,7 +29415,7 @@
         <v>216</v>
       </c>
       <c r="O404">
-        <v>16948688</v>
+        <v>16962484</v>
       </c>
       <c r="P404" t="s">
         <v>240</v>
@@ -29431,10 +29427,10 @@
         <v>0</v>
       </c>
       <c r="T404" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="W404" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AA404">
         <v>0</v>
@@ -29448,16 +29444,16 @@
     </row>
     <row r="405" spans="1:34">
       <c r="A405">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B405" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C405" t="s">
         <v>61</v>
       </c>
       <c r="D405" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E405" t="s">
         <v>65</v>
@@ -29487,7 +29483,7 @@
         <v>216</v>
       </c>
       <c r="O405">
-        <v>16962484</v>
+        <v>16976381</v>
       </c>
       <c r="P405" t="s">
         <v>240</v>
@@ -29499,10 +29495,13 @@
         <v>0</v>
       </c>
       <c r="T405" t="s">
-        <v>261</v>
+        <v>259</v>
+      </c>
+      <c r="V405" t="s">
+        <v>268</v>
       </c>
       <c r="W405" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AA405">
         <v>0</v>
@@ -29516,10 +29515,10 @@
     </row>
     <row r="406" spans="1:34">
       <c r="A406">
-        <v>6486</v>
+        <v>6704</v>
       </c>
       <c r="B406" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C406" t="s">
         <v>61</v>
@@ -29534,7 +29533,7 @@
         <v>67</v>
       </c>
       <c r="G406">
-        <v>11678</v>
+        <v>11874</v>
       </c>
       <c r="H406">
         <v>0</v>
@@ -29543,7 +29542,7 @@
         <v>74</v>
       </c>
       <c r="J406" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="L406" s="1">
         <v>46281</v>
@@ -29555,7 +29554,7 @@
         <v>216</v>
       </c>
       <c r="O406">
-        <v>16976381</v>
+        <v>18273589</v>
       </c>
       <c r="P406" t="s">
         <v>240</v>
@@ -29567,19 +29566,19 @@
         <v>0</v>
       </c>
       <c r="T406" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="V406" t="s">
         <v>268</v>
       </c>
       <c r="W406" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AA406">
         <v>0</v>
       </c>
       <c r="AG406" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AH406" t="s">
         <v>438</v>
@@ -29587,16 +29586,16 @@
     </row>
     <row r="407" spans="1:34">
       <c r="A407">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B407" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C407" t="s">
         <v>61</v>
       </c>
       <c r="D407" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E407" t="s">
         <v>65</v>
@@ -29626,7 +29625,7 @@
         <v>216</v>
       </c>
       <c r="O407">
-        <v>18273589</v>
+        <v>18239293</v>
       </c>
       <c r="P407" t="s">
         <v>240</v>
@@ -29640,11 +29639,8 @@
       <c r="T407" t="s">
         <v>258</v>
       </c>
-      <c r="V407" t="s">
-        <v>268</v>
-      </c>
       <c r="W407" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AA407">
         <v>0</v>
@@ -29658,16 +29654,16 @@
     </row>
     <row r="408" spans="1:34">
       <c r="A408">
-        <v>6705</v>
+        <v>6703</v>
       </c>
       <c r="B408" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C408" t="s">
         <v>61</v>
       </c>
       <c r="D408" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E408" t="s">
         <v>65</v>
@@ -29676,7 +29672,7 @@
         <v>67</v>
       </c>
       <c r="G408">
-        <v>11874</v>
+        <v>1802</v>
       </c>
       <c r="H408">
         <v>0</v>
@@ -29685,19 +29681,19 @@
         <v>74</v>
       </c>
       <c r="J408" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="L408" s="1">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="M408" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N408" t="s">
         <v>216</v>
       </c>
       <c r="O408">
-        <v>18239293</v>
+        <v>17948796</v>
       </c>
       <c r="P408" t="s">
         <v>240</v>
@@ -29706,10 +29702,10 @@
         <v>250</v>
       </c>
       <c r="S408">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="T408" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="W408" t="s">
         <v>368</v>
@@ -29726,16 +29722,16 @@
     </row>
     <row r="409" spans="1:34">
       <c r="A409">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B409" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C409" t="s">
         <v>61</v>
       </c>
       <c r="D409" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E409" t="s">
         <v>65</v>
@@ -29765,7 +29761,7 @@
         <v>216</v>
       </c>
       <c r="O409">
-        <v>17948796</v>
+        <v>18085198</v>
       </c>
       <c r="P409" t="s">
         <v>240</v>
@@ -29777,10 +29773,13 @@
         <v>-2</v>
       </c>
       <c r="T409" t="s">
-        <v>260</v>
+        <v>258</v>
+      </c>
+      <c r="V409" t="s">
+        <v>268</v>
       </c>
       <c r="W409" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AA409">
         <v>0</v>
@@ -29794,10 +29793,10 @@
     </row>
     <row r="410" spans="1:34">
       <c r="A410">
-        <v>6704</v>
+        <v>5417</v>
       </c>
       <c r="B410" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C410" t="s">
         <v>61</v>
@@ -29812,7 +29811,7 @@
         <v>67</v>
       </c>
       <c r="G410">
-        <v>1802</v>
+        <v>11286</v>
       </c>
       <c r="H410">
         <v>0</v>
@@ -29821,7 +29820,7 @@
         <v>74</v>
       </c>
       <c r="J410" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L410" s="1">
         <v>46283</v>
@@ -29833,7 +29832,7 @@
         <v>216</v>
       </c>
       <c r="O410">
-        <v>18085198</v>
+        <v>17399434</v>
       </c>
       <c r="P410" t="s">
         <v>240</v>
@@ -29845,13 +29844,10 @@
         <v>-2</v>
       </c>
       <c r="T410" t="s">
-        <v>258</v>
-      </c>
-      <c r="V410" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="W410" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AA410">
         <v>0</v>
@@ -29865,16 +29861,16 @@
     </row>
     <row r="411" spans="1:34">
       <c r="A411">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B411" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C411" t="s">
         <v>61</v>
       </c>
       <c r="D411" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E411" t="s">
         <v>65</v>
@@ -29904,7 +29900,7 @@
         <v>216</v>
       </c>
       <c r="O411">
-        <v>17399434</v>
+        <v>16962464</v>
       </c>
       <c r="P411" t="s">
         <v>240</v>
@@ -29916,10 +29912,10 @@
         <v>-2</v>
       </c>
       <c r="T411" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="W411" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AA411">
         <v>0</v>
@@ -29933,16 +29929,16 @@
     </row>
     <row r="412" spans="1:34">
       <c r="A412">
-        <v>6404</v>
+        <v>6705</v>
       </c>
       <c r="B412" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C412" t="s">
         <v>61</v>
       </c>
       <c r="D412" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E412" t="s">
         <v>65</v>
@@ -29951,7 +29947,7 @@
         <v>67</v>
       </c>
       <c r="G412">
-        <v>11286</v>
+        <v>1803</v>
       </c>
       <c r="H412">
         <v>0</v>
@@ -29960,19 +29956,16 @@
         <v>74</v>
       </c>
       <c r="J412" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L412" s="1">
-        <v>46283</v>
-      </c>
-      <c r="M412" t="s">
-        <v>212</v>
+        <v>46293</v>
       </c>
       <c r="N412" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="O412">
-        <v>16962464</v>
+        <v>17948937</v>
       </c>
       <c r="P412" t="s">
         <v>240</v>
@@ -29981,13 +29974,10 @@
         <v>250</v>
       </c>
       <c r="S412">
-        <v>-2</v>
+        <v>-12</v>
       </c>
       <c r="T412" t="s">
-        <v>261</v>
-      </c>
-      <c r="W412" t="s">
-        <v>369</v>
+        <v>258</v>
       </c>
       <c r="AA412">
         <v>0</v>
@@ -30019,7 +30009,7 @@
         <v>67</v>
       </c>
       <c r="G413">
-        <v>1803</v>
+        <v>1805</v>
       </c>
       <c r="H413">
         <v>0</v>
@@ -30028,16 +30018,19 @@
         <v>74</v>
       </c>
       <c r="J413" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L413" s="1">
-        <v>46293</v>
+        <v>46283</v>
+      </c>
+      <c r="M413" t="s">
+        <v>212</v>
       </c>
       <c r="N413" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="O413">
-        <v>17948937</v>
+        <v>17948948</v>
       </c>
       <c r="P413" t="s">
         <v>240</v>
@@ -30046,11 +30039,14 @@
         <v>250</v>
       </c>
       <c r="S413">
-        <v>-12</v>
+        <v>-2</v>
       </c>
       <c r="T413" t="s">
         <v>258</v>
       </c>
+      <c r="W413" t="s">
+        <v>368</v>
+      </c>
       <c r="AA413">
         <v>0</v>
       </c>
@@ -30063,10 +30059,10 @@
     </row>
     <row r="414" spans="1:34">
       <c r="A414">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B414" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C414" t="s">
         <v>61</v>
@@ -30102,7 +30098,7 @@
         <v>216</v>
       </c>
       <c r="O414">
-        <v>17948948</v>
+        <v>18084966</v>
       </c>
       <c r="P414" t="s">
         <v>240</v>
@@ -30116,8 +30112,11 @@
       <c r="T414" t="s">
         <v>258</v>
       </c>
+      <c r="V414" t="s">
+        <v>268</v>
+      </c>
       <c r="W414" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AA414">
         <v>0</v>
@@ -30131,16 +30130,16 @@
     </row>
     <row r="415" spans="1:34">
       <c r="A415">
-        <v>6779</v>
+        <v>6703</v>
       </c>
       <c r="B415" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C415" t="s">
         <v>61</v>
       </c>
       <c r="D415" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E415" t="s">
         <v>65</v>
@@ -30149,7 +30148,7 @@
         <v>67</v>
       </c>
       <c r="G415">
-        <v>1805</v>
+        <v>1811</v>
       </c>
       <c r="H415">
         <v>0</v>
@@ -30158,19 +30157,16 @@
         <v>74</v>
       </c>
       <c r="J415" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="L415" s="1">
-        <v>46283</v>
-      </c>
-      <c r="M415" t="s">
-        <v>212</v>
+        <v>46290</v>
       </c>
       <c r="N415" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O415">
-        <v>18084966</v>
+        <v>17948816</v>
       </c>
       <c r="P415" t="s">
         <v>240</v>
@@ -30179,16 +30175,10 @@
         <v>250</v>
       </c>
       <c r="S415">
-        <v>-2</v>
+        <v>-9</v>
       </c>
       <c r="T415" t="s">
-        <v>258</v>
-      </c>
-      <c r="V415" t="s">
-        <v>268</v>
-      </c>
-      <c r="W415" t="s">
-        <v>369</v>
+        <v>260</v>
       </c>
       <c r="AA415">
         <v>0</v>
@@ -30202,10 +30192,10 @@
     </row>
     <row r="416" spans="1:34">
       <c r="A416">
-        <v>6703</v>
+        <v>6404</v>
       </c>
       <c r="B416" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C416" t="s">
         <v>61</v>
@@ -30220,7 +30210,7 @@
         <v>67</v>
       </c>
       <c r="G416">
-        <v>1811</v>
+        <v>1807</v>
       </c>
       <c r="H416">
         <v>0</v>
@@ -30229,16 +30219,16 @@
         <v>74</v>
       </c>
       <c r="J416" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="L416" s="1">
-        <v>46290</v>
+        <v>46287</v>
       </c>
       <c r="N416" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="O416">
-        <v>17948816</v>
+        <v>16962171</v>
       </c>
       <c r="P416" t="s">
         <v>240</v>
@@ -30247,10 +30237,10 @@
         <v>250</v>
       </c>
       <c r="S416">
-        <v>-9</v>
+        <v>-6</v>
       </c>
       <c r="T416" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AA416">
         <v>0</v>
@@ -30264,10 +30254,10 @@
     </row>
     <row r="417" spans="1:34">
       <c r="A417">
-        <v>6404</v>
+        <v>6703</v>
       </c>
       <c r="B417" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C417" t="s">
         <v>61</v>
@@ -30300,7 +30290,7 @@
         <v>216</v>
       </c>
       <c r="O417">
-        <v>16962171</v>
+        <v>17948806</v>
       </c>
       <c r="P417" t="s">
         <v>240</v>
@@ -30312,7 +30302,7 @@
         <v>-6</v>
       </c>
       <c r="T417" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AA417">
         <v>0</v>
@@ -30326,16 +30316,16 @@
     </row>
     <row r="418" spans="1:34">
       <c r="A418">
-        <v>6703</v>
+        <v>5417</v>
       </c>
       <c r="B418" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C418" t="s">
         <v>61</v>
       </c>
       <c r="D418" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E418" t="s">
         <v>65</v>
@@ -30344,7 +30334,7 @@
         <v>67</v>
       </c>
       <c r="G418">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="H418">
         <v>0</v>
@@ -30353,7 +30343,7 @@
         <v>74</v>
       </c>
       <c r="J418" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L418" s="1">
         <v>46287</v>
@@ -30362,7 +30352,7 @@
         <v>216</v>
       </c>
       <c r="O418">
-        <v>17948806</v>
+        <v>17398965</v>
       </c>
       <c r="P418" t="s">
         <v>240</v>
@@ -30374,7 +30364,7 @@
         <v>-6</v>
       </c>
       <c r="T418" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="AA418">
         <v>0</v>
@@ -30388,10 +30378,10 @@
     </row>
     <row r="419" spans="1:34">
       <c r="A419">
-        <v>5417</v>
+        <v>6704</v>
       </c>
       <c r="B419" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C419" t="s">
         <v>61</v>
@@ -30424,7 +30414,7 @@
         <v>216</v>
       </c>
       <c r="O419">
-        <v>17398965</v>
+        <v>18085209</v>
       </c>
       <c r="P419" t="s">
         <v>240</v>
@@ -30436,7 +30426,10 @@
         <v>-6</v>
       </c>
       <c r="T419" t="s">
-        <v>257</v>
+        <v>258</v>
+      </c>
+      <c r="V419" t="s">
+        <v>268</v>
       </c>
       <c r="AA419">
         <v>0</v>
@@ -30450,10 +30443,10 @@
     </row>
     <row r="420" spans="1:34">
       <c r="A420">
-        <v>6704</v>
+        <v>5417</v>
       </c>
       <c r="B420" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C420" t="s">
         <v>61</v>
@@ -30468,7 +30461,7 @@
         <v>67</v>
       </c>
       <c r="G420">
-        <v>1808</v>
+        <v>7025</v>
       </c>
       <c r="H420">
         <v>0</v>
@@ -30477,16 +30470,16 @@
         <v>74</v>
       </c>
       <c r="J420" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L420" s="1">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="N420" t="s">
         <v>216</v>
       </c>
       <c r="O420">
-        <v>18085209</v>
+        <v>17399280</v>
       </c>
       <c r="P420" t="s">
         <v>240</v>
@@ -30495,19 +30488,19 @@
         <v>250</v>
       </c>
       <c r="S420">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="T420" t="s">
-        <v>258</v>
-      </c>
-      <c r="V420" t="s">
-        <v>268</v>
+        <v>257</v>
+      </c>
+      <c r="W420" t="s">
+        <v>369</v>
       </c>
       <c r="AA420">
         <v>0</v>
       </c>
       <c r="AG420" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AH420" t="s">
         <v>438</v>
@@ -30515,16 +30508,16 @@
     </row>
     <row r="421" spans="1:34">
       <c r="A421">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B421" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C421" t="s">
         <v>61</v>
       </c>
       <c r="D421" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E421" t="s">
         <v>65</v>
@@ -30551,7 +30544,7 @@
         <v>216</v>
       </c>
       <c r="O421">
-        <v>17399280</v>
+        <v>16962338</v>
       </c>
       <c r="P421" t="s">
         <v>240</v>
@@ -30563,10 +30556,7 @@
         <v>-7</v>
       </c>
       <c r="T421" t="s">
-        <v>257</v>
-      </c>
-      <c r="W421" t="s">
-        <v>370</v>
+        <v>261</v>
       </c>
       <c r="AA421">
         <v>0</v>
@@ -30580,84 +30570,90 @@
     </row>
     <row r="422" spans="1:34">
       <c r="A422">
-        <v>6404</v>
+        <v>6627</v>
       </c>
       <c r="B422" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C422" t="s">
         <v>61</v>
       </c>
       <c r="D422" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E422" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F422" t="s">
         <v>67</v>
       </c>
       <c r="G422">
-        <v>7025</v>
+        <v>946</v>
       </c>
       <c r="H422">
         <v>0</v>
       </c>
       <c r="I422" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J422" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="L422" s="1">
-        <v>46288</v>
+        <v>46283</v>
+      </c>
+      <c r="M422" t="s">
+        <v>212</v>
       </c>
       <c r="N422" t="s">
         <v>216</v>
       </c>
       <c r="O422">
-        <v>16962338</v>
+        <v>17042272</v>
       </c>
       <c r="P422" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q422" t="s">
         <v>250</v>
       </c>
       <c r="S422">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="T422" t="s">
-        <v>261</v>
+        <v>253</v>
+      </c>
+      <c r="V422" t="s">
+        <v>268</v>
+      </c>
+      <c r="W422" t="s">
+        <v>368</v>
       </c>
       <c r="AA422">
         <v>0</v>
       </c>
       <c r="AG422" t="s">
-        <v>429</v>
-      </c>
-      <c r="AH422" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
     </row>
     <row r="423" spans="1:34">
       <c r="A423">
-        <v>6627</v>
+        <v>6945</v>
       </c>
       <c r="B423" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C423" t="s">
         <v>61</v>
       </c>
       <c r="D423" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E423" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F423" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G423">
         <v>946</v>
@@ -30681,7 +30677,7 @@
         <v>216</v>
       </c>
       <c r="O423">
-        <v>17042272</v>
+        <v>18164494</v>
       </c>
       <c r="P423" t="s">
         <v>241</v>
@@ -30693,13 +30689,10 @@
         <v>-2</v>
       </c>
       <c r="T423" t="s">
-        <v>253</v>
-      </c>
-      <c r="V423" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="W423" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AA423">
         <v>0</v>
@@ -30710,10 +30703,10 @@
     </row>
     <row r="424" spans="1:34">
       <c r="A424">
-        <v>6945</v>
+        <v>6705</v>
       </c>
       <c r="B424" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C424" t="s">
         <v>61</v>
@@ -30725,10 +30718,10 @@
         <v>65</v>
       </c>
       <c r="F424" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G424">
-        <v>946</v>
+        <v>7022</v>
       </c>
       <c r="H424">
         <v>0</v>
@@ -30737,7 +30730,7 @@
         <v>75</v>
       </c>
       <c r="J424" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L424" s="1">
         <v>46283</v>
@@ -30749,7 +30742,7 @@
         <v>216</v>
       </c>
       <c r="O424">
-        <v>18164494</v>
+        <v>17952601</v>
       </c>
       <c r="P424" t="s">
         <v>241</v>
@@ -30761,10 +30754,10 @@
         <v>-2</v>
       </c>
       <c r="T424" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="W424" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AA424">
         <v>0</v>
@@ -30775,16 +30768,16 @@
     </row>
     <row r="425" spans="1:34">
       <c r="A425">
-        <v>6705</v>
+        <v>5417</v>
       </c>
       <c r="B425" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C425" t="s">
         <v>61</v>
       </c>
       <c r="D425" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E425" t="s">
         <v>65</v>
@@ -30793,7 +30786,7 @@
         <v>67</v>
       </c>
       <c r="G425">
-        <v>7022</v>
+        <v>9086</v>
       </c>
       <c r="H425">
         <v>0</v>
@@ -30802,19 +30795,19 @@
         <v>75</v>
       </c>
       <c r="J425" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L425" s="1">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="M425" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N425" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O425">
-        <v>17952601</v>
+        <v>17399363</v>
       </c>
       <c r="P425" t="s">
         <v>241</v>
@@ -30823,33 +30816,33 @@
         <v>250</v>
       </c>
       <c r="S425">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T425" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="W425" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AA425">
         <v>0</v>
       </c>
       <c r="AG425" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="426" spans="1:34">
       <c r="A426">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B426" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C426" t="s">
         <v>61</v>
       </c>
       <c r="D426" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E426" t="s">
         <v>65</v>
@@ -30879,7 +30872,7 @@
         <v>217</v>
       </c>
       <c r="O426">
-        <v>17399363</v>
+        <v>16962380</v>
       </c>
       <c r="P426" t="s">
         <v>241</v>
@@ -30891,10 +30884,10 @@
         <v>-1</v>
       </c>
       <c r="T426" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="W426" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AA426">
         <v>0</v>
@@ -30905,16 +30898,16 @@
     </row>
     <row r="427" spans="1:34">
       <c r="A427">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B427" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C427" t="s">
         <v>61</v>
       </c>
       <c r="D427" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E427" t="s">
         <v>65</v>
@@ -30944,7 +30937,7 @@
         <v>217</v>
       </c>
       <c r="O427">
-        <v>16962380</v>
+        <v>16976270</v>
       </c>
       <c r="P427" t="s">
         <v>241</v>
@@ -30956,10 +30949,13 @@
         <v>-1</v>
       </c>
       <c r="T427" t="s">
-        <v>261</v>
+        <v>259</v>
+      </c>
+      <c r="V427" t="s">
+        <v>268</v>
       </c>
       <c r="W427" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AA427">
         <v>0</v>
@@ -30970,10 +30966,10 @@
     </row>
     <row r="428" spans="1:34">
       <c r="A428">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B428" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C428" t="s">
         <v>61</v>
@@ -31009,7 +31005,7 @@
         <v>217</v>
       </c>
       <c r="O428">
-        <v>16976270</v>
+        <v>17222865</v>
       </c>
       <c r="P428" t="s">
         <v>241</v>
@@ -31021,13 +31017,13 @@
         <v>-1</v>
       </c>
       <c r="T428" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="V428" t="s">
         <v>268</v>
       </c>
       <c r="W428" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AA428">
         <v>0</v>
@@ -31038,10 +31034,10 @@
     </row>
     <row r="429" spans="1:34">
       <c r="A429">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B429" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C429" t="s">
         <v>61</v>
@@ -31050,7 +31046,7 @@
         <v>62</v>
       </c>
       <c r="E429" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F429" t="s">
         <v>67</v>
@@ -31077,7 +31073,7 @@
         <v>217</v>
       </c>
       <c r="O429">
-        <v>17222865</v>
+        <v>17042587</v>
       </c>
       <c r="P429" t="s">
         <v>241</v>
@@ -31089,13 +31085,13 @@
         <v>-1</v>
       </c>
       <c r="T429" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="V429" t="s">
         <v>268</v>
       </c>
       <c r="W429" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AA429">
         <v>0</v>
@@ -31106,16 +31102,16 @@
     </row>
     <row r="430" spans="1:34">
       <c r="A430">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B430" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C430" t="s">
         <v>61</v>
       </c>
       <c r="D430" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E430" t="s">
         <v>66</v>
@@ -31145,7 +31141,7 @@
         <v>217</v>
       </c>
       <c r="O430">
-        <v>17042587</v>
+        <v>16960074</v>
       </c>
       <c r="P430" t="s">
         <v>241</v>
@@ -31163,7 +31159,7 @@
         <v>268</v>
       </c>
       <c r="W430" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AA430">
         <v>0</v>
@@ -31174,19 +31170,19 @@
     </row>
     <row r="431" spans="1:34">
       <c r="A431">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B431" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C431" t="s">
         <v>61</v>
       </c>
       <c r="D431" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E431" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F431" t="s">
         <v>67</v>
@@ -31213,7 +31209,7 @@
         <v>217</v>
       </c>
       <c r="O431">
-        <v>16960074</v>
+        <v>17941217</v>
       </c>
       <c r="P431" t="s">
         <v>241</v>
@@ -31225,13 +31221,10 @@
         <v>-1</v>
       </c>
       <c r="T431" t="s">
-        <v>253</v>
-      </c>
-      <c r="V431" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="W431" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AA431">
         <v>0</v>
@@ -31242,16 +31235,16 @@
     </row>
     <row r="432" spans="1:34">
       <c r="A432">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B432" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C432" t="s">
         <v>61</v>
       </c>
       <c r="D432" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E432" t="s">
         <v>65</v>
@@ -31281,7 +31274,7 @@
         <v>217</v>
       </c>
       <c r="O432">
-        <v>17941217</v>
+        <v>17952444</v>
       </c>
       <c r="P432" t="s">
         <v>241</v>
@@ -31293,10 +31286,13 @@
         <v>-1</v>
       </c>
       <c r="T432" t="s">
-        <v>260</v>
+        <v>258</v>
+      </c>
+      <c r="V432" t="s">
+        <v>268</v>
       </c>
       <c r="W432" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AA432">
         <v>0</v>
@@ -31307,16 +31303,16 @@
     </row>
     <row r="433" spans="1:33">
       <c r="A433">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B433" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C433" t="s">
         <v>61</v>
       </c>
       <c r="D433" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E433" t="s">
         <v>65</v>
@@ -31346,7 +31342,7 @@
         <v>217</v>
       </c>
       <c r="O433">
-        <v>17952444</v>
+        <v>17952624</v>
       </c>
       <c r="P433" t="s">
         <v>241</v>
@@ -31360,11 +31356,8 @@
       <c r="T433" t="s">
         <v>258</v>
       </c>
-      <c r="V433" t="s">
-        <v>268</v>
-      </c>
       <c r="W433" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AA433">
         <v>0</v>
@@ -31375,10 +31368,10 @@
     </row>
     <row r="434" spans="1:33">
       <c r="A434">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B434" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C434" t="s">
         <v>61</v>
@@ -31414,7 +31407,7 @@
         <v>217</v>
       </c>
       <c r="O434">
-        <v>17952624</v>
+        <v>18056801</v>
       </c>
       <c r="P434" t="s">
         <v>241</v>
@@ -31428,8 +31421,11 @@
       <c r="T434" t="s">
         <v>258</v>
       </c>
+      <c r="V434" t="s">
+        <v>268</v>
+      </c>
       <c r="W434" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AA434">
         <v>0</v>
@@ -31440,10 +31436,10 @@
     </row>
     <row r="435" spans="1:33">
       <c r="A435">
-        <v>6779</v>
+        <v>6945</v>
       </c>
       <c r="B435" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C435" t="s">
         <v>61</v>
@@ -31455,7 +31451,7 @@
         <v>65</v>
       </c>
       <c r="F435" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G435">
         <v>9086</v>
@@ -31479,7 +31475,7 @@
         <v>217</v>
       </c>
       <c r="O435">
-        <v>18056801</v>
+        <v>18164551</v>
       </c>
       <c r="P435" t="s">
         <v>241</v>
@@ -31491,13 +31487,10 @@
         <v>-1</v>
       </c>
       <c r="T435" t="s">
-        <v>258</v>
-      </c>
-      <c r="V435" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="W435" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AA435">
         <v>0</v>
@@ -31508,16 +31501,16 @@
     </row>
     <row r="436" spans="1:33">
       <c r="A436">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B436" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C436" t="s">
         <v>61</v>
       </c>
       <c r="D436" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E436" t="s">
         <v>65</v>
@@ -31547,7 +31540,7 @@
         <v>217</v>
       </c>
       <c r="O436">
-        <v>18164551</v>
+        <v>18178187</v>
       </c>
       <c r="P436" t="s">
         <v>241</v>
@@ -31559,7 +31552,7 @@
         <v>-1</v>
       </c>
       <c r="T436" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="W436" t="s">
         <v>371</v>
@@ -31573,16 +31566,16 @@
     </row>
     <row r="437" spans="1:33">
       <c r="A437">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B437" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C437" t="s">
         <v>61</v>
       </c>
       <c r="D437" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E437" t="s">
         <v>65</v>
@@ -31612,7 +31605,7 @@
         <v>217</v>
       </c>
       <c r="O437">
-        <v>18178187</v>
+        <v>18188774</v>
       </c>
       <c r="P437" t="s">
         <v>241</v>
@@ -31624,10 +31617,10 @@
         <v>-1</v>
       </c>
       <c r="T437" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="W437" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="AA437">
         <v>0</v>
@@ -31638,10 +31631,10 @@
     </row>
     <row r="438" spans="1:33">
       <c r="A438">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B438" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C438" t="s">
         <v>61</v>
@@ -31677,7 +31670,7 @@
         <v>217</v>
       </c>
       <c r="O438">
-        <v>18188774</v>
+        <v>18188680</v>
       </c>
       <c r="P438" t="s">
         <v>241</v>
@@ -31692,7 +31685,7 @@
         <v>256</v>
       </c>
       <c r="W438" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AA438">
         <v>0</v>
@@ -31703,25 +31696,25 @@
     </row>
     <row r="439" spans="1:33">
       <c r="A439">
-        <v>6963</v>
+        <v>5417</v>
       </c>
       <c r="B439" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C439" t="s">
         <v>61</v>
       </c>
       <c r="D439" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E439" t="s">
         <v>65</v>
       </c>
       <c r="F439" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G439">
-        <v>9086</v>
+        <v>940</v>
       </c>
       <c r="H439">
         <v>0</v>
@@ -31730,19 +31723,19 @@
         <v>75</v>
       </c>
       <c r="J439" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L439" s="1">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="M439" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="N439" t="s">
         <v>217</v>
       </c>
       <c r="O439">
-        <v>18188680</v>
+        <v>17398840</v>
       </c>
       <c r="P439" t="s">
         <v>241</v>
@@ -31751,13 +31744,13 @@
         <v>250</v>
       </c>
       <c r="S439">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="T439" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="W439" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AA439">
         <v>0</v>
@@ -31768,16 +31761,16 @@
     </row>
     <row r="440" spans="1:33">
       <c r="A440">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B440" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C440" t="s">
         <v>61</v>
       </c>
       <c r="D440" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E440" t="s">
         <v>65</v>
@@ -31807,7 +31800,7 @@
         <v>217</v>
       </c>
       <c r="O440">
-        <v>17398840</v>
+        <v>16962074</v>
       </c>
       <c r="P440" t="s">
         <v>241</v>
@@ -31819,10 +31812,10 @@
         <v>-2</v>
       </c>
       <c r="T440" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="W440" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AA440">
         <v>0</v>
@@ -31833,16 +31826,16 @@
     </row>
     <row r="441" spans="1:33">
       <c r="A441">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B441" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C441" t="s">
         <v>61</v>
       </c>
       <c r="D441" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E441" t="s">
         <v>65</v>
@@ -31872,7 +31865,7 @@
         <v>217</v>
       </c>
       <c r="O441">
-        <v>16962074</v>
+        <v>16975871</v>
       </c>
       <c r="P441" t="s">
         <v>241</v>
@@ -31884,10 +31877,13 @@
         <v>-2</v>
       </c>
       <c r="T441" t="s">
-        <v>261</v>
+        <v>259</v>
+      </c>
+      <c r="V441" t="s">
+        <v>268</v>
       </c>
       <c r="W441" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AA441">
         <v>0</v>
@@ -31898,10 +31894,10 @@
     </row>
     <row r="442" spans="1:33">
       <c r="A442">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B442" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C442" t="s">
         <v>61</v>
@@ -31937,7 +31933,7 @@
         <v>217</v>
       </c>
       <c r="O442">
-        <v>16975871</v>
+        <v>17222366</v>
       </c>
       <c r="P442" t="s">
         <v>241</v>
@@ -31949,13 +31945,13 @@
         <v>-2</v>
       </c>
       <c r="T442" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="V442" t="s">
         <v>268</v>
       </c>
       <c r="W442" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AA442">
         <v>0</v>
@@ -31966,10 +31962,10 @@
     </row>
     <row r="443" spans="1:33">
       <c r="A443">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B443" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C443" t="s">
         <v>61</v>
@@ -31978,7 +31974,7 @@
         <v>62</v>
       </c>
       <c r="E443" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F443" t="s">
         <v>67</v>
@@ -32005,7 +32001,7 @@
         <v>217</v>
       </c>
       <c r="O443">
-        <v>17222366</v>
+        <v>17042221</v>
       </c>
       <c r="P443" t="s">
         <v>241</v>
@@ -32017,13 +32013,13 @@
         <v>-2</v>
       </c>
       <c r="T443" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="V443" t="s">
         <v>268</v>
       </c>
       <c r="W443" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AA443">
         <v>0</v>
@@ -32034,16 +32030,16 @@
     </row>
     <row r="444" spans="1:33">
       <c r="A444">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B444" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C444" t="s">
         <v>61</v>
       </c>
       <c r="D444" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E444" t="s">
         <v>66</v>
@@ -32073,7 +32069,7 @@
         <v>217</v>
       </c>
       <c r="O444">
-        <v>17042221</v>
+        <v>16959926</v>
       </c>
       <c r="P444" t="s">
         <v>241</v>
@@ -32091,7 +32087,7 @@
         <v>268</v>
       </c>
       <c r="W444" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AA444">
         <v>0</v>
@@ -32102,19 +32098,19 @@
     </row>
     <row r="445" spans="1:33">
       <c r="A445">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B445" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C445" t="s">
         <v>61</v>
       </c>
       <c r="D445" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E445" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F445" t="s">
         <v>67</v>
@@ -32141,7 +32137,7 @@
         <v>217</v>
       </c>
       <c r="O445">
-        <v>16959926</v>
+        <v>17941112</v>
       </c>
       <c r="P445" t="s">
         <v>241</v>
@@ -32153,13 +32149,10 @@
         <v>-2</v>
       </c>
       <c r="T445" t="s">
-        <v>253</v>
-      </c>
-      <c r="V445" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="W445" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AA445">
         <v>0</v>
@@ -32170,16 +32163,16 @@
     </row>
     <row r="446" spans="1:33">
       <c r="A446">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B446" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C446" t="s">
         <v>61</v>
       </c>
       <c r="D446" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E446" t="s">
         <v>65</v>
@@ -32209,7 +32202,7 @@
         <v>217</v>
       </c>
       <c r="O446">
-        <v>17941112</v>
+        <v>17952292</v>
       </c>
       <c r="P446" t="s">
         <v>241</v>
@@ -32221,10 +32214,13 @@
         <v>-2</v>
       </c>
       <c r="T446" t="s">
-        <v>260</v>
+        <v>258</v>
+      </c>
+      <c r="V446" t="s">
+        <v>268</v>
       </c>
       <c r="W446" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AA446">
         <v>0</v>
@@ -32235,16 +32231,16 @@
     </row>
     <row r="447" spans="1:33">
       <c r="A447">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B447" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C447" t="s">
         <v>61</v>
       </c>
       <c r="D447" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E447" t="s">
         <v>65</v>
@@ -32274,7 +32270,7 @@
         <v>217</v>
       </c>
       <c r="O447">
-        <v>17952292</v>
+        <v>17952491</v>
       </c>
       <c r="P447" t="s">
         <v>241</v>
@@ -32288,11 +32284,8 @@
       <c r="T447" t="s">
         <v>258</v>
       </c>
-      <c r="V447" t="s">
-        <v>268</v>
-      </c>
       <c r="W447" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AA447">
         <v>0</v>
@@ -32303,10 +32296,10 @@
     </row>
     <row r="448" spans="1:33">
       <c r="A448">
-        <v>6705</v>
+        <v>6945</v>
       </c>
       <c r="B448" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C448" t="s">
         <v>61</v>
@@ -32318,7 +32311,7 @@
         <v>65</v>
       </c>
       <c r="F448" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G448">
         <v>940</v>
@@ -32342,7 +32335,7 @@
         <v>217</v>
       </c>
       <c r="O448">
-        <v>17952491</v>
+        <v>18164473</v>
       </c>
       <c r="P448" t="s">
         <v>241</v>
@@ -32354,7 +32347,7 @@
         <v>-2</v>
       </c>
       <c r="T448" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="W448" t="s">
         <v>373</v>
@@ -32368,16 +32361,16 @@
     </row>
     <row r="449" spans="1:33">
       <c r="A449">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B449" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C449" t="s">
         <v>61</v>
       </c>
       <c r="D449" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E449" t="s">
         <v>65</v>
@@ -32407,7 +32400,7 @@
         <v>217</v>
       </c>
       <c r="O449">
-        <v>18164473</v>
+        <v>18178120</v>
       </c>
       <c r="P449" t="s">
         <v>241</v>
@@ -32419,10 +32412,10 @@
         <v>-2</v>
       </c>
       <c r="T449" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="W449" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA449">
         <v>0</v>
@@ -32433,10 +32426,10 @@
     </row>
     <row r="450" spans="1:33">
       <c r="A450">
-        <v>6949</v>
+        <v>5417</v>
       </c>
       <c r="B450" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C450" t="s">
         <v>61</v>
@@ -32448,10 +32441,10 @@
         <v>65</v>
       </c>
       <c r="F450" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G450">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="H450">
         <v>0</v>
@@ -32460,19 +32453,16 @@
         <v>75</v>
       </c>
       <c r="J450" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L450" s="1">
-        <v>46283</v>
-      </c>
-      <c r="M450" t="s">
-        <v>212</v>
+        <v>46295</v>
       </c>
       <c r="N450" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="O450">
-        <v>18178120</v>
+        <v>17398859</v>
       </c>
       <c r="P450" t="s">
         <v>241</v>
@@ -32481,27 +32471,24 @@
         <v>250</v>
       </c>
       <c r="S450">
-        <v>-2</v>
+        <v>-14</v>
       </c>
       <c r="T450" t="s">
-        <v>255</v>
-      </c>
-      <c r="W450" t="s">
-        <v>374</v>
+        <v>257</v>
       </c>
       <c r="AA450">
         <v>0</v>
       </c>
       <c r="AG450" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="451" spans="1:33">
       <c r="A451">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B451" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C451" t="s">
         <v>61</v>
@@ -32534,7 +32521,7 @@
         <v>216</v>
       </c>
       <c r="O451">
-        <v>17398859</v>
+        <v>16975890</v>
       </c>
       <c r="P451" t="s">
         <v>241</v>
@@ -32546,7 +32533,10 @@
         <v>-14</v>
       </c>
       <c r="T451" t="s">
-        <v>257</v>
+        <v>259</v>
+      </c>
+      <c r="V451" t="s">
+        <v>268</v>
       </c>
       <c r="AA451">
         <v>0</v>
@@ -32557,16 +32547,16 @@
     </row>
     <row r="452" spans="1:33">
       <c r="A452">
-        <v>6486</v>
+        <v>6703</v>
       </c>
       <c r="B452" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C452" t="s">
         <v>61</v>
       </c>
       <c r="D452" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E452" t="s">
         <v>65</v>
@@ -32593,7 +32583,7 @@
         <v>216</v>
       </c>
       <c r="O452">
-        <v>16975890</v>
+        <v>17941122</v>
       </c>
       <c r="P452" t="s">
         <v>241</v>
@@ -32605,10 +32595,7 @@
         <v>-14</v>
       </c>
       <c r="T452" t="s">
-        <v>259</v>
-      </c>
-      <c r="V452" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="AA452">
         <v>0</v>
@@ -32619,16 +32606,16 @@
     </row>
     <row r="453" spans="1:33">
       <c r="A453">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B453" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C453" t="s">
         <v>61</v>
       </c>
       <c r="D453" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E453" t="s">
         <v>65</v>
@@ -32655,7 +32642,7 @@
         <v>216</v>
       </c>
       <c r="O453">
-        <v>17941122</v>
+        <v>17952314</v>
       </c>
       <c r="P453" t="s">
         <v>241</v>
@@ -32667,7 +32654,10 @@
         <v>-14</v>
       </c>
       <c r="T453" t="s">
-        <v>260</v>
+        <v>258</v>
+      </c>
+      <c r="V453" t="s">
+        <v>268</v>
       </c>
       <c r="AA453">
         <v>0</v>
@@ -32678,16 +32668,16 @@
     </row>
     <row r="454" spans="1:33">
       <c r="A454">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B454" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C454" t="s">
         <v>61</v>
       </c>
       <c r="D454" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E454" t="s">
         <v>65</v>
@@ -32714,7 +32704,7 @@
         <v>216</v>
       </c>
       <c r="O454">
-        <v>17952314</v>
+        <v>17952513</v>
       </c>
       <c r="P454" t="s">
         <v>241</v>
@@ -32728,9 +32718,6 @@
       <c r="T454" t="s">
         <v>258</v>
       </c>
-      <c r="V454" t="s">
-        <v>268</v>
-      </c>
       <c r="AA454">
         <v>0</v>
       </c>
@@ -32740,22 +32727,22 @@
     </row>
     <row r="455" spans="1:33">
       <c r="A455">
-        <v>6705</v>
+        <v>6949</v>
       </c>
       <c r="B455" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C455" t="s">
         <v>61</v>
       </c>
       <c r="D455" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E455" t="s">
         <v>65</v>
       </c>
       <c r="F455" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G455">
         <v>943</v>
@@ -32776,7 +32763,7 @@
         <v>216</v>
       </c>
       <c r="O455">
-        <v>17952513</v>
+        <v>18178126</v>
       </c>
       <c r="P455" t="s">
         <v>241</v>
@@ -32788,7 +32775,7 @@
         <v>-14</v>
       </c>
       <c r="T455" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="AA455">
         <v>0</v>
@@ -32799,16 +32786,16 @@
     </row>
     <row r="456" spans="1:33">
       <c r="A456">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B456" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C456" t="s">
         <v>61</v>
       </c>
       <c r="D456" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E456" t="s">
         <v>65</v>
@@ -32835,7 +32822,7 @@
         <v>216</v>
       </c>
       <c r="O456">
-        <v>18178126</v>
+        <v>18188710</v>
       </c>
       <c r="P456" t="s">
         <v>241</v>
@@ -32847,7 +32834,7 @@
         <v>-14</v>
       </c>
       <c r="T456" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AA456">
         <v>0</v>
@@ -32858,10 +32845,10 @@
     </row>
     <row r="457" spans="1:33">
       <c r="A457">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B457" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C457" t="s">
         <v>61</v>
@@ -32894,7 +32881,7 @@
         <v>216</v>
       </c>
       <c r="O457">
-        <v>18188710</v>
+        <v>18188616</v>
       </c>
       <c r="P457" t="s">
         <v>241</v>
@@ -32917,75 +32904,81 @@
     </row>
     <row r="458" spans="1:33">
       <c r="A458">
-        <v>6963</v>
+        <v>5417</v>
       </c>
       <c r="B458" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C458" t="s">
         <v>61</v>
       </c>
       <c r="D458" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E458" t="s">
         <v>65</v>
       </c>
       <c r="F458" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G458">
-        <v>943</v>
+        <v>9088</v>
       </c>
       <c r="H458">
         <v>0</v>
       </c>
       <c r="I458" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J458" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L458" s="1">
-        <v>46295</v>
+        <v>46283</v>
+      </c>
+      <c r="M458" t="s">
+        <v>212</v>
       </c>
       <c r="N458" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O458">
-        <v>18188616</v>
+        <v>17399383</v>
       </c>
       <c r="P458" t="s">
-        <v>241</v>
+        <v>65</v>
       </c>
       <c r="Q458" t="s">
         <v>250</v>
       </c>
       <c r="S458">
-        <v>-14</v>
+        <v>-2</v>
       </c>
       <c r="T458" t="s">
-        <v>256</v>
+        <v>257</v>
+      </c>
+      <c r="W458" t="s">
+        <v>373</v>
       </c>
       <c r="AA458">
         <v>0</v>
       </c>
       <c r="AG458" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="459" spans="1:33">
       <c r="A459">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B459" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C459" t="s">
         <v>61</v>
       </c>
       <c r="D459" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E459" t="s">
         <v>65</v>
@@ -33015,7 +33008,7 @@
         <v>217</v>
       </c>
       <c r="O459">
-        <v>17399383</v>
+        <v>16962400</v>
       </c>
       <c r="P459" t="s">
         <v>65</v>
@@ -33027,10 +33020,10 @@
         <v>-2</v>
       </c>
       <c r="T459" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="W459" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA459">
         <v>0</v>
@@ -33041,16 +33034,16 @@
     </row>
     <row r="460" spans="1:33">
       <c r="A460">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B460" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C460" t="s">
         <v>61</v>
       </c>
       <c r="D460" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E460" t="s">
         <v>65</v>
@@ -33080,7 +33073,7 @@
         <v>217</v>
       </c>
       <c r="O460">
-        <v>16962400</v>
+        <v>16976290</v>
       </c>
       <c r="P460" t="s">
         <v>65</v>
@@ -33092,10 +33085,13 @@
         <v>-2</v>
       </c>
       <c r="T460" t="s">
-        <v>261</v>
+        <v>259</v>
+      </c>
+      <c r="V460" t="s">
+        <v>268</v>
       </c>
       <c r="W460" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA460">
         <v>0</v>
@@ -33106,10 +33102,10 @@
     </row>
     <row r="461" spans="1:33">
       <c r="A461">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B461" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C461" t="s">
         <v>61</v>
@@ -33145,7 +33141,7 @@
         <v>217</v>
       </c>
       <c r="O461">
-        <v>16976290</v>
+        <v>17222899</v>
       </c>
       <c r="P461" t="s">
         <v>65</v>
@@ -33157,13 +33153,13 @@
         <v>-2</v>
       </c>
       <c r="T461" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="V461" t="s">
         <v>268</v>
       </c>
       <c r="W461" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA461">
         <v>0</v>
@@ -33174,10 +33170,10 @@
     </row>
     <row r="462" spans="1:33">
       <c r="A462">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B462" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C462" t="s">
         <v>61</v>
@@ -33186,7 +33182,7 @@
         <v>62</v>
       </c>
       <c r="E462" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F462" t="s">
         <v>67</v>
@@ -33213,10 +33209,10 @@
         <v>217</v>
       </c>
       <c r="O462">
-        <v>17222899</v>
+        <v>17042627</v>
       </c>
       <c r="P462" t="s">
-        <v>65</v>
+        <v>242</v>
       </c>
       <c r="Q462" t="s">
         <v>250</v>
@@ -33225,13 +33221,13 @@
         <v>-2</v>
       </c>
       <c r="T462" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="V462" t="s">
         <v>268</v>
       </c>
       <c r="W462" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA462">
         <v>0</v>
@@ -33242,16 +33238,16 @@
     </row>
     <row r="463" spans="1:33">
       <c r="A463">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B463" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C463" t="s">
         <v>61</v>
       </c>
       <c r="D463" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E463" t="s">
         <v>66</v>
@@ -33281,10 +33277,10 @@
         <v>217</v>
       </c>
       <c r="O463">
-        <v>17042627</v>
+        <v>16960098</v>
       </c>
       <c r="P463" t="s">
-        <v>242</v>
+        <v>66</v>
       </c>
       <c r="Q463" t="s">
         <v>250</v>
@@ -33299,7 +33295,7 @@
         <v>268</v>
       </c>
       <c r="W463" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA463">
         <v>0</v>
@@ -33310,19 +33306,19 @@
     </row>
     <row r="464" spans="1:33">
       <c r="A464">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B464" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C464" t="s">
         <v>61</v>
       </c>
       <c r="D464" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E464" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F464" t="s">
         <v>67</v>
@@ -33349,10 +33345,10 @@
         <v>217</v>
       </c>
       <c r="O464">
-        <v>16960098</v>
+        <v>17941237</v>
       </c>
       <c r="P464" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Q464" t="s">
         <v>250</v>
@@ -33361,13 +33357,10 @@
         <v>-2</v>
       </c>
       <c r="T464" t="s">
-        <v>253</v>
-      </c>
-      <c r="V464" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="W464" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA464">
         <v>0</v>
@@ -33378,16 +33371,16 @@
     </row>
     <row r="465" spans="1:33">
       <c r="A465">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B465" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C465" t="s">
         <v>61</v>
       </c>
       <c r="D465" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E465" t="s">
         <v>65</v>
@@ -33417,7 +33410,7 @@
         <v>217</v>
       </c>
       <c r="O465">
-        <v>17941237</v>
+        <v>17952466</v>
       </c>
       <c r="P465" t="s">
         <v>65</v>
@@ -33429,10 +33422,13 @@
         <v>-2</v>
       </c>
       <c r="T465" t="s">
-        <v>260</v>
+        <v>258</v>
+      </c>
+      <c r="V465" t="s">
+        <v>268</v>
       </c>
       <c r="W465" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA465">
         <v>0</v>
@@ -33443,16 +33439,16 @@
     </row>
     <row r="466" spans="1:33">
       <c r="A466">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B466" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C466" t="s">
         <v>61</v>
       </c>
       <c r="D466" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E466" t="s">
         <v>65</v>
@@ -33482,7 +33478,7 @@
         <v>217</v>
       </c>
       <c r="O466">
-        <v>17952466</v>
+        <v>17952646</v>
       </c>
       <c r="P466" t="s">
         <v>65</v>
@@ -33496,11 +33492,8 @@
       <c r="T466" t="s">
         <v>258</v>
       </c>
-      <c r="V466" t="s">
-        <v>268</v>
-      </c>
       <c r="W466" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA466">
         <v>0</v>
@@ -33511,10 +33504,10 @@
     </row>
     <row r="467" spans="1:33">
       <c r="A467">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B467" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C467" t="s">
         <v>61</v>
@@ -33550,10 +33543,10 @@
         <v>217</v>
       </c>
       <c r="O467">
-        <v>17952646</v>
+        <v>18056821</v>
       </c>
       <c r="P467" t="s">
-        <v>65</v>
+        <v>242</v>
       </c>
       <c r="Q467" t="s">
         <v>250</v>
@@ -33564,8 +33557,11 @@
       <c r="T467" t="s">
         <v>258</v>
       </c>
+      <c r="V467" t="s">
+        <v>268</v>
+      </c>
       <c r="W467" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA467">
         <v>0</v>
@@ -33576,10 +33572,10 @@
     </row>
     <row r="468" spans="1:33">
       <c r="A468">
-        <v>6779</v>
+        <v>6945</v>
       </c>
       <c r="B468" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C468" t="s">
         <v>61</v>
@@ -33591,7 +33587,7 @@
         <v>65</v>
       </c>
       <c r="F468" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G468">
         <v>9088</v>
@@ -33615,10 +33611,10 @@
         <v>217</v>
       </c>
       <c r="O468">
-        <v>18056821</v>
+        <v>18164565</v>
       </c>
       <c r="P468" t="s">
-        <v>242</v>
+        <v>65</v>
       </c>
       <c r="Q468" t="s">
         <v>250</v>
@@ -33627,13 +33623,10 @@
         <v>-2</v>
       </c>
       <c r="T468" t="s">
-        <v>258</v>
-      </c>
-      <c r="V468" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="W468" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA468">
         <v>0</v>
@@ -33644,16 +33637,16 @@
     </row>
     <row r="469" spans="1:33">
       <c r="A469">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B469" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C469" t="s">
         <v>61</v>
       </c>
       <c r="D469" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E469" t="s">
         <v>65</v>
@@ -33683,10 +33676,10 @@
         <v>217</v>
       </c>
       <c r="O469">
-        <v>18164565</v>
+        <v>18178199</v>
       </c>
       <c r="P469" t="s">
-        <v>65</v>
+        <v>242</v>
       </c>
       <c r="Q469" t="s">
         <v>250</v>
@@ -33695,7 +33688,7 @@
         <v>-2</v>
       </c>
       <c r="T469" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="W469" t="s">
         <v>374</v>
@@ -33709,16 +33702,16 @@
     </row>
     <row r="470" spans="1:33">
       <c r="A470">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B470" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C470" t="s">
         <v>61</v>
       </c>
       <c r="D470" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E470" t="s">
         <v>65</v>
@@ -33748,10 +33741,10 @@
         <v>217</v>
       </c>
       <c r="O470">
-        <v>18178199</v>
+        <v>18188788</v>
       </c>
       <c r="P470" t="s">
-        <v>242</v>
+        <v>65</v>
       </c>
       <c r="Q470" t="s">
         <v>250</v>
@@ -33760,10 +33753,10 @@
         <v>-2</v>
       </c>
       <c r="T470" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="W470" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="AA470">
         <v>0</v>
@@ -33774,10 +33767,10 @@
     </row>
     <row r="471" spans="1:33">
       <c r="A471">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B471" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C471" t="s">
         <v>61</v>
@@ -33813,7 +33806,7 @@
         <v>217</v>
       </c>
       <c r="O471">
-        <v>18188788</v>
+        <v>18188694</v>
       </c>
       <c r="P471" t="s">
         <v>65</v>
@@ -33828,7 +33821,7 @@
         <v>256</v>
       </c>
       <c r="W471" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA471">
         <v>0</v>
@@ -33839,25 +33832,25 @@
     </row>
     <row r="472" spans="1:33">
       <c r="A472">
-        <v>6963</v>
+        <v>5417</v>
       </c>
       <c r="B472" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C472" t="s">
         <v>61</v>
       </c>
       <c r="D472" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E472" t="s">
         <v>65</v>
       </c>
       <c r="F472" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G472">
-        <v>9088</v>
+        <v>6813</v>
       </c>
       <c r="H472">
         <v>0</v>
@@ -33866,7 +33859,7 @@
         <v>76</v>
       </c>
       <c r="J472" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L472" s="1">
         <v>46283</v>
@@ -33878,7 +33871,7 @@
         <v>217</v>
       </c>
       <c r="O472">
-        <v>18188694</v>
+        <v>17399241</v>
       </c>
       <c r="P472" t="s">
         <v>65</v>
@@ -33890,10 +33883,10 @@
         <v>-2</v>
       </c>
       <c r="T472" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="W472" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA472">
         <v>0</v>
@@ -33904,16 +33897,16 @@
     </row>
     <row r="473" spans="1:33">
       <c r="A473">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B473" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C473" t="s">
         <v>61</v>
       </c>
       <c r="D473" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E473" t="s">
         <v>65</v>
@@ -33943,7 +33936,7 @@
         <v>217</v>
       </c>
       <c r="O473">
-        <v>17399241</v>
+        <v>16962319</v>
       </c>
       <c r="P473" t="s">
         <v>65</v>
@@ -33955,10 +33948,10 @@
         <v>-2</v>
       </c>
       <c r="T473" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="W473" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA473">
         <v>0</v>
@@ -33969,16 +33962,16 @@
     </row>
     <row r="474" spans="1:33">
       <c r="A474">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B474" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C474" t="s">
         <v>61</v>
       </c>
       <c r="D474" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E474" t="s">
         <v>65</v>
@@ -34008,7 +34001,7 @@
         <v>217</v>
       </c>
       <c r="O474">
-        <v>16962319</v>
+        <v>16976198</v>
       </c>
       <c r="P474" t="s">
         <v>65</v>
@@ -34020,10 +34013,13 @@
         <v>-2</v>
       </c>
       <c r="T474" t="s">
-        <v>261</v>
+        <v>259</v>
+      </c>
+      <c r="V474" t="s">
+        <v>268</v>
       </c>
       <c r="W474" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA474">
         <v>0</v>
@@ -34034,10 +34030,10 @@
     </row>
     <row r="475" spans="1:33">
       <c r="A475">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B475" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C475" t="s">
         <v>61</v>
@@ -34073,7 +34069,7 @@
         <v>217</v>
       </c>
       <c r="O475">
-        <v>16976198</v>
+        <v>17222763</v>
       </c>
       <c r="P475" t="s">
         <v>65</v>
@@ -34085,13 +34081,13 @@
         <v>-2</v>
       </c>
       <c r="T475" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="V475" t="s">
         <v>268</v>
       </c>
       <c r="W475" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA475">
         <v>0</v>
@@ -34102,10 +34098,10 @@
     </row>
     <row r="476" spans="1:33">
       <c r="A476">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B476" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C476" t="s">
         <v>61</v>
@@ -34114,7 +34110,7 @@
         <v>62</v>
       </c>
       <c r="E476" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F476" t="s">
         <v>67</v>
@@ -34141,10 +34137,10 @@
         <v>217</v>
       </c>
       <c r="O476">
-        <v>17222763</v>
+        <v>17042469</v>
       </c>
       <c r="P476" t="s">
-        <v>65</v>
+        <v>242</v>
       </c>
       <c r="Q476" t="s">
         <v>250</v>
@@ -34153,13 +34149,13 @@
         <v>-2</v>
       </c>
       <c r="T476" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="V476" t="s">
         <v>268</v>
       </c>
       <c r="W476" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA476">
         <v>0</v>
@@ -34170,16 +34166,16 @@
     </row>
     <row r="477" spans="1:33">
       <c r="A477">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B477" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C477" t="s">
         <v>61</v>
       </c>
       <c r="D477" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E477" t="s">
         <v>66</v>
@@ -34209,10 +34205,10 @@
         <v>217</v>
       </c>
       <c r="O477">
-        <v>17042469</v>
+        <v>16960013</v>
       </c>
       <c r="P477" t="s">
-        <v>242</v>
+        <v>66</v>
       </c>
       <c r="Q477" t="s">
         <v>250</v>
@@ -34227,7 +34223,7 @@
         <v>268</v>
       </c>
       <c r="W477" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA477">
         <v>0</v>
@@ -34238,19 +34234,19 @@
     </row>
     <row r="478" spans="1:33">
       <c r="A478">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B478" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C478" t="s">
         <v>61</v>
       </c>
       <c r="D478" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E478" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F478" t="s">
         <v>67</v>
@@ -34277,10 +34273,10 @@
         <v>217</v>
       </c>
       <c r="O478">
-        <v>16960013</v>
+        <v>17941197</v>
       </c>
       <c r="P478" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Q478" t="s">
         <v>250</v>
@@ -34289,13 +34285,10 @@
         <v>-2</v>
       </c>
       <c r="T478" t="s">
-        <v>253</v>
-      </c>
-      <c r="V478" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="W478" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA478">
         <v>0</v>
@@ -34306,16 +34299,16 @@
     </row>
     <row r="479" spans="1:33">
       <c r="A479">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B479" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C479" t="s">
         <v>61</v>
       </c>
       <c r="D479" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E479" t="s">
         <v>65</v>
@@ -34345,7 +34338,7 @@
         <v>217</v>
       </c>
       <c r="O479">
-        <v>17941197</v>
+        <v>17952411</v>
       </c>
       <c r="P479" t="s">
         <v>65</v>
@@ -34357,10 +34350,13 @@
         <v>-2</v>
       </c>
       <c r="T479" t="s">
-        <v>260</v>
+        <v>258</v>
+      </c>
+      <c r="V479" t="s">
+        <v>268</v>
       </c>
       <c r="W479" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA479">
         <v>0</v>
@@ -34371,16 +34367,16 @@
     </row>
     <row r="480" spans="1:33">
       <c r="A480">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B480" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C480" t="s">
         <v>61</v>
       </c>
       <c r="D480" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E480" t="s">
         <v>65</v>
@@ -34410,7 +34406,7 @@
         <v>217</v>
       </c>
       <c r="O480">
-        <v>17952411</v>
+        <v>17952591</v>
       </c>
       <c r="P480" t="s">
         <v>65</v>
@@ -34424,11 +34420,8 @@
       <c r="T480" t="s">
         <v>258</v>
       </c>
-      <c r="V480" t="s">
-        <v>268</v>
-      </c>
       <c r="W480" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA480">
         <v>0</v>
@@ -34439,10 +34432,10 @@
     </row>
     <row r="481" spans="1:34">
       <c r="A481">
-        <v>6705</v>
+        <v>6945</v>
       </c>
       <c r="B481" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C481" t="s">
         <v>61</v>
@@ -34454,7 +34447,7 @@
         <v>65</v>
       </c>
       <c r="F481" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G481">
         <v>6813</v>
@@ -34478,7 +34471,7 @@
         <v>217</v>
       </c>
       <c r="O481">
-        <v>17952591</v>
+        <v>18164530</v>
       </c>
       <c r="P481" t="s">
         <v>65</v>
@@ -34490,7 +34483,7 @@
         <v>-2</v>
       </c>
       <c r="T481" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="W481" t="s">
         <v>374</v>
@@ -34504,16 +34497,16 @@
     </row>
     <row r="482" spans="1:34">
       <c r="A482">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B482" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C482" t="s">
         <v>61</v>
       </c>
       <c r="D482" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E482" t="s">
         <v>65</v>
@@ -34543,10 +34536,10 @@
         <v>217</v>
       </c>
       <c r="O482">
-        <v>18164530</v>
+        <v>18178169</v>
       </c>
       <c r="P482" t="s">
-        <v>65</v>
+        <v>242</v>
       </c>
       <c r="Q482" t="s">
         <v>250</v>
@@ -34555,10 +34548,10 @@
         <v>-2</v>
       </c>
       <c r="T482" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="W482" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AA482">
         <v>0</v>
@@ -34569,16 +34562,16 @@
     </row>
     <row r="483" spans="1:34">
       <c r="A483">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B483" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C483" t="s">
         <v>61</v>
       </c>
       <c r="D483" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E483" t="s">
         <v>65</v>
@@ -34587,40 +34580,37 @@
         <v>68</v>
       </c>
       <c r="G483">
-        <v>6813</v>
+        <v>11056</v>
       </c>
       <c r="H483">
         <v>0</v>
       </c>
       <c r="I483" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J483" t="s">
-        <v>168</v>
+        <v>132</v>
       </c>
       <c r="L483" s="1">
-        <v>46283</v>
-      </c>
-      <c r="M483" t="s">
-        <v>212</v>
+        <v>46287</v>
       </c>
       <c r="N483" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="O483">
-        <v>18178169</v>
+        <v>18274091</v>
       </c>
       <c r="P483" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q483" t="s">
         <v>250</v>
       </c>
       <c r="S483">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="T483" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="W483" t="s">
         <v>375</v>
@@ -34629,77 +34619,86 @@
         <v>0</v>
       </c>
       <c r="AG483" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="484" spans="1:34">
       <c r="A484">
-        <v>6962</v>
+        <v>6628</v>
       </c>
       <c r="B484" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C484" t="s">
         <v>61</v>
       </c>
       <c r="D484" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E484" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F484" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G484">
-        <v>11056</v>
+        <v>1650</v>
       </c>
       <c r="H484">
         <v>0</v>
       </c>
       <c r="I484" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="J484" t="s">
-        <v>132</v>
+        <v>169</v>
       </c>
       <c r="L484" s="1">
-        <v>46287</v>
+        <v>46293</v>
       </c>
       <c r="N484" t="s">
         <v>216</v>
       </c>
       <c r="O484">
-        <v>18274091</v>
+        <v>16959974</v>
       </c>
       <c r="P484" t="s">
-        <v>246</v>
+        <v>222</v>
       </c>
       <c r="Q484" t="s">
-        <v>250</v>
+        <v>249</v>
+      </c>
+      <c r="R484" s="1">
+        <v>46265.00248284722</v>
       </c>
       <c r="S484">
-        <v>-6</v>
+        <v>-12</v>
       </c>
       <c r="T484" t="s">
-        <v>256</v>
-      </c>
-      <c r="W484" t="s">
-        <v>376</v>
+        <v>253</v>
+      </c>
+      <c r="V484" t="s">
+        <v>268</v>
       </c>
       <c r="AA484">
         <v>0</v>
+      </c>
+      <c r="AB484" t="s">
+        <v>424</v>
       </c>
       <c r="AG484" t="s">
         <v>429</v>
       </c>
+      <c r="AH484" t="s">
+        <v>433</v>
+      </c>
     </row>
     <row r="485" spans="1:34">
       <c r="A485">
-        <v>6628</v>
+        <v>6945</v>
       </c>
       <c r="B485" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C485" t="s">
         <v>61</v>
@@ -34708,10 +34707,10 @@
         <v>63</v>
       </c>
       <c r="E485" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F485" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G485">
         <v>1650</v>
@@ -34732,25 +34731,22 @@
         <v>216</v>
       </c>
       <c r="O485">
-        <v>16959974</v>
+        <v>18163667</v>
       </c>
       <c r="P485" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q485" t="s">
         <v>249</v>
       </c>
       <c r="R485" s="1">
-        <v>46265.00248284722</v>
+        <v>46265.00255472222</v>
       </c>
       <c r="S485">
         <v>-12</v>
       </c>
       <c r="T485" t="s">
-        <v>253</v>
-      </c>
-      <c r="V485" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="AA485">
         <v>0</v>
@@ -34767,25 +34763,25 @@
     </row>
     <row r="486" spans="1:34">
       <c r="A486">
-        <v>6945</v>
+        <v>6548</v>
       </c>
       <c r="B486" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C486" t="s">
         <v>61</v>
       </c>
       <c r="D486" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E486" t="s">
         <v>65</v>
       </c>
       <c r="F486" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G486">
-        <v>1650</v>
+        <v>1652</v>
       </c>
       <c r="H486">
         <v>0</v>
@@ -34794,31 +34790,37 @@
         <v>70</v>
       </c>
       <c r="J486" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L486" s="1">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="N486" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O486">
-        <v>18163667</v>
+        <v>17967989</v>
       </c>
       <c r="P486" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="Q486" t="s">
         <v>249</v>
       </c>
       <c r="R486" s="1">
-        <v>46265.00255472222</v>
+        <v>46234.66180127315</v>
       </c>
       <c r="S486">
-        <v>-12</v>
+        <v>-9</v>
       </c>
       <c r="T486" t="s">
-        <v>254</v>
+        <v>252</v>
+      </c>
+      <c r="V486" t="s">
+        <v>268</v>
+      </c>
+      <c r="W486" t="s">
+        <v>376</v>
       </c>
       <c r="AA486">
         <v>0</v>
@@ -34827,18 +34829,18 @@
         <v>424</v>
       </c>
       <c r="AG486" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AH486" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="487" spans="1:34">
       <c r="A487">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B487" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C487" t="s">
         <v>61</v>
@@ -34847,7 +34849,7 @@
         <v>62</v>
       </c>
       <c r="E487" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F487" t="s">
         <v>67</v>
@@ -34871,22 +34873,22 @@
         <v>218</v>
       </c>
       <c r="O487">
-        <v>17967989</v>
+        <v>17042389</v>
       </c>
       <c r="P487" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q487" t="s">
         <v>249</v>
       </c>
       <c r="R487" s="1">
-        <v>46234.66180127315</v>
+        <v>46245.76585582176</v>
       </c>
       <c r="S487">
         <v>-9</v>
       </c>
       <c r="T487" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="V487" t="s">
         <v>268</v>
@@ -34904,15 +34906,15 @@
         <v>430</v>
       </c>
       <c r="AH487" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="488" spans="1:34">
       <c r="A488">
-        <v>6627</v>
+        <v>6704</v>
       </c>
       <c r="B488" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C488" t="s">
         <v>61</v>
@@ -34921,72 +34923,69 @@
         <v>62</v>
       </c>
       <c r="E488" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F488" t="s">
         <v>67</v>
       </c>
       <c r="G488">
-        <v>1652</v>
+        <v>7868</v>
       </c>
       <c r="H488">
         <v>0</v>
       </c>
       <c r="I488" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J488" t="s">
-        <v>170</v>
+        <v>133</v>
       </c>
       <c r="L488" s="1">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="N488" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="O488">
-        <v>17042389</v>
+        <v>17955421</v>
       </c>
       <c r="P488" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Q488" t="s">
         <v>249</v>
       </c>
       <c r="R488" s="1">
-        <v>46245.76585582176</v>
+        <v>46267.47365627315</v>
       </c>
       <c r="S488">
-        <v>-9</v>
+        <v>-12</v>
       </c>
       <c r="T488" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="V488" t="s">
         <v>268</v>
       </c>
-      <c r="W488" t="s">
-        <v>378</v>
-      </c>
       <c r="AA488">
         <v>0</v>
       </c>
       <c r="AB488" t="s">
-        <v>424</v>
+        <v>226</v>
       </c>
       <c r="AG488" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AH488" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="489" spans="1:34">
       <c r="A489">
-        <v>6704</v>
+        <v>5417</v>
       </c>
       <c r="B489" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C489" t="s">
         <v>61</v>
@@ -35001,7 +35000,7 @@
         <v>67</v>
       </c>
       <c r="G489">
-        <v>7868</v>
+        <v>11276</v>
       </c>
       <c r="H489">
         <v>0</v>
@@ -35010,54 +35009,51 @@
         <v>71</v>
       </c>
       <c r="J489" t="s">
-        <v>133</v>
+        <v>171</v>
       </c>
       <c r="L489" s="1">
-        <v>46293</v>
+        <v>46283</v>
       </c>
       <c r="N489" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="O489">
-        <v>17955421</v>
+        <v>17399423</v>
       </c>
       <c r="P489" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Q489" t="s">
         <v>249</v>
       </c>
       <c r="R489" s="1">
-        <v>46267.47365627315</v>
+        <v>46266.47620831019</v>
       </c>
       <c r="S489">
-        <v>-12</v>
+        <v>-2</v>
       </c>
       <c r="T489" t="s">
-        <v>258</v>
-      </c>
-      <c r="V489" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="AA489">
         <v>0</v>
       </c>
       <c r="AB489" t="s">
-        <v>226</v>
+        <v>426</v>
       </c>
       <c r="AG489" t="s">
         <v>429</v>
       </c>
       <c r="AH489" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="490" spans="1:34">
       <c r="A490">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B490" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C490" t="s">
         <v>61</v>
@@ -35090,28 +35086,31 @@
         <v>219</v>
       </c>
       <c r="O490">
-        <v>17399423</v>
+        <v>18152557</v>
       </c>
       <c r="P490" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="Q490" t="s">
         <v>249</v>
       </c>
       <c r="R490" s="1">
-        <v>46266.47620831019</v>
+        <v>46267.57586420139</v>
       </c>
       <c r="S490">
         <v>-2</v>
       </c>
       <c r="T490" t="s">
-        <v>257</v>
+        <v>259</v>
+      </c>
+      <c r="V490" t="s">
+        <v>268</v>
       </c>
       <c r="AA490">
         <v>0</v>
       </c>
       <c r="AB490" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG490" t="s">
         <v>429</v>
@@ -35122,10 +35121,10 @@
     </row>
     <row r="491" spans="1:34">
       <c r="A491">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B491" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C491" t="s">
         <v>61</v>
@@ -35140,7 +35139,7 @@
         <v>67</v>
       </c>
       <c r="G491">
-        <v>11276</v>
+        <v>1583</v>
       </c>
       <c r="H491">
         <v>0</v>
@@ -35149,43 +35148,40 @@
         <v>71</v>
       </c>
       <c r="J491" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L491" s="1">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="N491" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O491">
-        <v>18152557</v>
+        <v>17398917</v>
       </c>
       <c r="P491" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="Q491" t="s">
         <v>249</v>
       </c>
       <c r="R491" s="1">
-        <v>46267.57586420139</v>
+        <v>46233.72355880787</v>
       </c>
       <c r="S491">
-        <v>-2</v>
+        <v>-9</v>
       </c>
       <c r="T491" t="s">
-        <v>259</v>
-      </c>
-      <c r="V491" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="AA491">
         <v>0</v>
       </c>
       <c r="AB491" t="s">
-        <v>427</v>
+        <v>225</v>
       </c>
       <c r="AG491" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AH491" t="s">
         <v>434</v>
@@ -35193,10 +35189,10 @@
     </row>
     <row r="492" spans="1:34">
       <c r="A492">
-        <v>5417</v>
+        <v>5617</v>
       </c>
       <c r="B492" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C492" t="s">
         <v>61</v>
@@ -35229,42 +35225,36 @@
         <v>218</v>
       </c>
       <c r="O492">
-        <v>17398917</v>
-      </c>
-      <c r="P492" t="s">
-        <v>225</v>
+        <v>17407553</v>
       </c>
       <c r="Q492" t="s">
         <v>249</v>
       </c>
       <c r="R492" s="1">
-        <v>46233.72355880787</v>
+        <v>46261.36669849537</v>
       </c>
       <c r="S492">
         <v>-9</v>
       </c>
       <c r="T492" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="AA492">
         <v>0</v>
       </c>
       <c r="AB492" t="s">
-        <v>225</v>
+        <v>421</v>
       </c>
       <c r="AG492" t="s">
         <v>430</v>
       </c>
-      <c r="AH492" t="s">
-        <v>434</v>
-      </c>
     </row>
     <row r="493" spans="1:34">
       <c r="A493">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B493" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C493" t="s">
         <v>61</v>
@@ -35276,7 +35266,7 @@
         <v>65</v>
       </c>
       <c r="F493" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G493">
         <v>1583</v>
@@ -35297,13 +35287,13 @@
         <v>218</v>
       </c>
       <c r="O493">
-        <v>17407553</v>
+        <v>17688645</v>
       </c>
       <c r="Q493" t="s">
         <v>249</v>
       </c>
       <c r="R493" s="1">
-        <v>46261.36669849537</v>
+        <v>46266.44156952546</v>
       </c>
       <c r="S493">
         <v>-9</v>
@@ -35311,11 +35301,14 @@
       <c r="T493" t="s">
         <v>262</v>
       </c>
+      <c r="V493" t="s">
+        <v>268</v>
+      </c>
       <c r="AA493">
         <v>0</v>
       </c>
       <c r="AB493" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="AG493" t="s">
         <v>430</v>
@@ -35323,10 +35316,10 @@
     </row>
     <row r="494" spans="1:34">
       <c r="A494">
-        <v>6224</v>
+        <v>6278</v>
       </c>
       <c r="B494" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C494" t="s">
         <v>61</v>
@@ -35338,7 +35331,7 @@
         <v>65</v>
       </c>
       <c r="F494" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G494">
         <v>1583</v>
@@ -35359,28 +35352,31 @@
         <v>218</v>
       </c>
       <c r="O494">
-        <v>17688645</v>
+        <v>18166312</v>
       </c>
       <c r="Q494" t="s">
         <v>249</v>
       </c>
       <c r="R494" s="1">
-        <v>46266.44156952546</v>
+        <v>46233.50562820602</v>
       </c>
       <c r="S494">
         <v>-9</v>
       </c>
       <c r="T494" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="V494" t="s">
         <v>268</v>
       </c>
+      <c r="W494" t="s">
+        <v>378</v>
+      </c>
       <c r="AA494">
         <v>0</v>
       </c>
       <c r="AB494" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="AG494" t="s">
         <v>430</v>
@@ -35388,10 +35384,10 @@
     </row>
     <row r="495" spans="1:34">
       <c r="A495">
-        <v>6278</v>
+        <v>6486</v>
       </c>
       <c r="B495" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C495" t="s">
         <v>61</v>
@@ -35424,42 +35420,45 @@
         <v>218</v>
       </c>
       <c r="O495">
-        <v>18166312</v>
+        <v>18114208</v>
+      </c>
+      <c r="P495" t="s">
+        <v>243</v>
       </c>
       <c r="Q495" t="s">
         <v>249</v>
       </c>
       <c r="R495" s="1">
-        <v>46233.50562820602</v>
+        <v>46233.80164280093</v>
       </c>
       <c r="S495">
         <v>-9</v>
       </c>
       <c r="T495" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="V495" t="s">
         <v>268</v>
       </c>
-      <c r="W495" t="s">
-        <v>379</v>
-      </c>
       <c r="AA495">
         <v>0</v>
       </c>
       <c r="AB495" t="s">
-        <v>424</v>
+        <v>243</v>
       </c>
       <c r="AG495" t="s">
         <v>430</v>
       </c>
+      <c r="AH495" t="s">
+        <v>434</v>
+      </c>
     </row>
     <row r="496" spans="1:34">
       <c r="A496">
-        <v>6486</v>
+        <v>6704</v>
       </c>
       <c r="B496" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C496" t="s">
         <v>61</v>
@@ -35492,22 +35491,22 @@
         <v>218</v>
       </c>
       <c r="O496">
-        <v>18114208</v>
+        <v>17955373</v>
       </c>
       <c r="P496" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="Q496" t="s">
         <v>249</v>
       </c>
       <c r="R496" s="1">
-        <v>46233.80164280093</v>
+        <v>46232.72913953703</v>
       </c>
       <c r="S496">
         <v>-9</v>
       </c>
       <c r="T496" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="V496" t="s">
         <v>268</v>
@@ -35516,21 +35515,21 @@
         <v>0</v>
       </c>
       <c r="AB496" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="AG496" t="s">
         <v>430</v>
       </c>
       <c r="AH496" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="497" spans="1:34">
       <c r="A497">
-        <v>6704</v>
+        <v>5417</v>
       </c>
       <c r="B497" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C497" t="s">
         <v>61</v>
@@ -35545,69 +35544,66 @@
         <v>67</v>
       </c>
       <c r="G497">
-        <v>1583</v>
+        <v>1628</v>
       </c>
       <c r="H497">
-        <v>0</v>
+        <v>1581</v>
       </c>
       <c r="I497" t="s">
         <v>71</v>
       </c>
       <c r="J497" t="s">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="L497" s="1">
-        <v>46290</v>
+        <v>46286</v>
       </c>
       <c r="N497" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="O497">
-        <v>17955373</v>
+        <v>17398925</v>
       </c>
       <c r="P497" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Q497" t="s">
         <v>249</v>
       </c>
       <c r="R497" s="1">
-        <v>46232.72913953703</v>
+        <v>46280.37528408565</v>
       </c>
       <c r="S497">
-        <v>-9</v>
+        <v>-5</v>
       </c>
       <c r="T497" t="s">
-        <v>258</v>
-      </c>
-      <c r="V497" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="AA497">
         <v>0</v>
       </c>
       <c r="AB497" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AG497" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AH497" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="498" spans="1:34">
       <c r="A498">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B498" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C498" t="s">
         <v>61</v>
       </c>
       <c r="D498" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E498" t="s">
         <v>65</v>
@@ -35634,48 +35630,48 @@
         <v>216</v>
       </c>
       <c r="O498">
-        <v>17398925</v>
+        <v>16962141</v>
       </c>
       <c r="P498" t="s">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="Q498" t="s">
         <v>249</v>
       </c>
       <c r="R498" s="1">
-        <v>46280.37528408565</v>
+        <v>46266.37634084491</v>
       </c>
       <c r="S498">
         <v>-5</v>
       </c>
       <c r="T498" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="AA498">
         <v>0</v>
       </c>
       <c r="AB498" t="s">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="AG498" t="s">
         <v>429</v>
       </c>
       <c r="AH498" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="499" spans="1:34">
       <c r="A499">
-        <v>6404</v>
+        <v>6704</v>
       </c>
       <c r="B499" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C499" t="s">
         <v>61</v>
       </c>
       <c r="D499" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E499" t="s">
         <v>65</v>
@@ -35702,28 +35698,31 @@
         <v>216</v>
       </c>
       <c r="O499">
-        <v>16962141</v>
+        <v>17955384</v>
       </c>
       <c r="P499" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="Q499" t="s">
         <v>249</v>
       </c>
       <c r="R499" s="1">
-        <v>46266.37634084491</v>
+        <v>46267.47452163194</v>
       </c>
       <c r="S499">
         <v>-5</v>
       </c>
       <c r="T499" t="s">
-        <v>261</v>
+        <v>258</v>
+      </c>
+      <c r="V499" t="s">
+        <v>268</v>
       </c>
       <c r="AA499">
         <v>0</v>
       </c>
       <c r="AB499" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="AG499" t="s">
         <v>429</v>
@@ -35734,16 +35733,16 @@
     </row>
     <row r="500" spans="1:34">
       <c r="A500">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B500" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C500" t="s">
         <v>61</v>
       </c>
       <c r="D500" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E500" t="s">
         <v>65</v>
@@ -35770,7 +35769,7 @@
         <v>216</v>
       </c>
       <c r="O500">
-        <v>17955384</v>
+        <v>17955238</v>
       </c>
       <c r="P500" t="s">
         <v>226</v>
@@ -35779,7 +35778,7 @@
         <v>249</v>
       </c>
       <c r="R500" s="1">
-        <v>46267.47452163194</v>
+        <v>46267.4745221412</v>
       </c>
       <c r="S500">
         <v>-5</v>
@@ -35787,9 +35786,6 @@
       <c r="T500" t="s">
         <v>258</v>
       </c>
-      <c r="V500" t="s">
-        <v>268</v>
-      </c>
       <c r="AA500">
         <v>0</v>
       </c>
@@ -35805,10 +35801,10 @@
     </row>
     <row r="501" spans="1:34">
       <c r="A501">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B501" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C501" t="s">
         <v>61</v>
@@ -35841,7 +35837,7 @@
         <v>216</v>
       </c>
       <c r="O501">
-        <v>17955238</v>
+        <v>18056729</v>
       </c>
       <c r="P501" t="s">
         <v>226</v>
@@ -35850,7 +35846,7 @@
         <v>249</v>
       </c>
       <c r="R501" s="1">
-        <v>46267.4745221412</v>
+        <v>46267.47452299768</v>
       </c>
       <c r="S501">
         <v>-5</v>
@@ -35858,6 +35854,9 @@
       <c r="T501" t="s">
         <v>258</v>
       </c>
+      <c r="V501" t="s">
+        <v>268</v>
+      </c>
       <c r="AA501">
         <v>0</v>
       </c>
@@ -35873,16 +35872,16 @@
     </row>
     <row r="502" spans="1:34">
       <c r="A502">
-        <v>6779</v>
+        <v>6703</v>
       </c>
       <c r="B502" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C502" t="s">
         <v>61</v>
       </c>
       <c r="D502" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E502" t="s">
         <v>65</v>
@@ -35891,69 +35890,66 @@
         <v>67</v>
       </c>
       <c r="G502">
-        <v>1628</v>
+        <v>6395</v>
       </c>
       <c r="H502">
-        <v>1581</v>
+        <v>5792</v>
       </c>
       <c r="I502" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J502" t="s">
-        <v>139</v>
+        <v>172</v>
       </c>
       <c r="L502" s="1">
-        <v>46286</v>
+        <v>46283</v>
       </c>
       <c r="N502" t="s">
         <v>216</v>
       </c>
       <c r="O502">
-        <v>18056729</v>
+        <v>18105120</v>
       </c>
       <c r="P502" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="Q502" t="s">
         <v>249</v>
       </c>
       <c r="R502" s="1">
-        <v>46267.47452299768</v>
+        <v>46268.58940019676</v>
       </c>
       <c r="S502">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="T502" t="s">
-        <v>258</v>
-      </c>
-      <c r="V502" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="AA502">
         <v>0</v>
       </c>
       <c r="AB502" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="AG502" t="s">
         <v>429</v>
       </c>
       <c r="AH502" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="503" spans="1:34">
       <c r="A503">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B503" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C503" t="s">
         <v>61</v>
       </c>
       <c r="D503" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E503" t="s">
         <v>65</v>
@@ -35962,7 +35958,7 @@
         <v>67</v>
       </c>
       <c r="G503">
-        <v>6395</v>
+        <v>5882</v>
       </c>
       <c r="H503">
         <v>5792</v>
@@ -35971,57 +35967,66 @@
         <v>72</v>
       </c>
       <c r="J503" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L503" s="1">
         <v>46283</v>
       </c>
+      <c r="M503" t="s">
+        <v>212</v>
+      </c>
       <c r="N503" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O503">
-        <v>18105120</v>
+        <v>18195621</v>
       </c>
       <c r="P503" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q503" t="s">
         <v>249</v>
       </c>
       <c r="R503" s="1">
-        <v>46268.58940019676</v>
+        <v>46279.66710767361</v>
       </c>
       <c r="S503">
         <v>-2</v>
       </c>
       <c r="T503" t="s">
-        <v>260</v>
+        <v>258</v>
+      </c>
+      <c r="V503" t="s">
+        <v>268</v>
+      </c>
+      <c r="W503" t="s">
+        <v>379</v>
       </c>
       <c r="AA503">
         <v>0</v>
       </c>
       <c r="AB503" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AG503" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AH503" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
     </row>
     <row r="504" spans="1:34">
       <c r="A504">
-        <v>6779</v>
+        <v>6548</v>
       </c>
       <c r="B504" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C504" t="s">
         <v>61</v>
       </c>
       <c r="D504" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E504" t="s">
         <v>65</v>
@@ -36030,7 +36035,7 @@
         <v>67</v>
       </c>
       <c r="G504">
-        <v>5882</v>
+        <v>5883</v>
       </c>
       <c r="H504">
         <v>5792</v>
@@ -36039,34 +36044,34 @@
         <v>72</v>
       </c>
       <c r="J504" t="s">
-        <v>173</v>
+        <v>141</v>
       </c>
       <c r="L504" s="1">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="M504" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N504" t="s">
         <v>217</v>
       </c>
       <c r="O504">
-        <v>18195621</v>
+        <v>17222629</v>
       </c>
       <c r="P504" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="Q504" t="s">
         <v>249</v>
       </c>
       <c r="R504" s="1">
-        <v>46279.66710767361</v>
+        <v>46280.57958537037</v>
       </c>
       <c r="S504">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="T504" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="V504" t="s">
         <v>268</v>
@@ -36078,27 +36083,27 @@
         <v>0</v>
       </c>
       <c r="AB504" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="AG504" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AH504" t="s">
-        <v>422</v>
+        <v>436</v>
       </c>
     </row>
     <row r="505" spans="1:34">
       <c r="A505">
-        <v>6548</v>
+        <v>6703</v>
       </c>
       <c r="B505" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C505" t="s">
         <v>61</v>
       </c>
       <c r="D505" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E505" t="s">
         <v>65</v>
@@ -36121,41 +36126,32 @@
       <c r="L505" s="1">
         <v>46286</v>
       </c>
-      <c r="M505" t="s">
-        <v>209</v>
-      </c>
       <c r="N505" t="s">
         <v>217</v>
       </c>
       <c r="O505">
-        <v>17222629</v>
+        <v>18077112</v>
       </c>
       <c r="P505" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q505" t="s">
         <v>249</v>
       </c>
       <c r="R505" s="1">
-        <v>46280.57958537037</v>
+        <v>46279.62681744213</v>
       </c>
       <c r="S505">
         <v>-5</v>
       </c>
       <c r="T505" t="s">
-        <v>252</v>
-      </c>
-      <c r="V505" t="s">
-        <v>268</v>
-      </c>
-      <c r="W505" t="s">
-        <v>381</v>
+        <v>260</v>
       </c>
       <c r="AA505">
         <v>0</v>
       </c>
       <c r="AB505" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG505" t="s">
         <v>429</v>
@@ -36166,16 +36162,16 @@
     </row>
     <row r="506" spans="1:34">
       <c r="A506">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B506" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C506" t="s">
         <v>61</v>
       </c>
       <c r="D506" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E506" t="s">
         <v>65</v>
@@ -36202,48 +36198,51 @@
         <v>217</v>
       </c>
       <c r="O506">
-        <v>18077112</v>
+        <v>18090189</v>
       </c>
       <c r="P506" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q506" t="s">
         <v>249</v>
       </c>
       <c r="R506" s="1">
-        <v>46279.62681744213</v>
+        <v>46279.66707821759</v>
       </c>
       <c r="S506">
         <v>-5</v>
       </c>
       <c r="T506" t="s">
-        <v>260</v>
+        <v>258</v>
+      </c>
+      <c r="V506" t="s">
+        <v>268</v>
       </c>
       <c r="AA506">
         <v>0</v>
       </c>
       <c r="AB506" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AG506" t="s">
         <v>429</v>
       </c>
       <c r="AH506" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
     </row>
     <row r="507" spans="1:34">
       <c r="A507">
-        <v>6779</v>
+        <v>6548</v>
       </c>
       <c r="B507" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C507" t="s">
         <v>61</v>
       </c>
       <c r="D507" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E507" t="s">
         <v>65</v>
@@ -36252,7 +36251,7 @@
         <v>67</v>
       </c>
       <c r="G507">
-        <v>5883</v>
+        <v>5884</v>
       </c>
       <c r="H507">
         <v>5792</v>
@@ -36261,60 +36260,66 @@
         <v>72</v>
       </c>
       <c r="J507" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L507" s="1">
         <v>46286</v>
       </c>
+      <c r="M507" t="s">
+        <v>209</v>
+      </c>
       <c r="N507" t="s">
         <v>217</v>
       </c>
       <c r="O507">
-        <v>18090189</v>
+        <v>17222647</v>
       </c>
       <c r="P507" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="Q507" t="s">
         <v>249</v>
       </c>
       <c r="R507" s="1">
-        <v>46279.66707821759</v>
+        <v>46280.57972293982</v>
       </c>
       <c r="S507">
         <v>-5</v>
       </c>
       <c r="T507" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="V507" t="s">
         <v>268</v>
       </c>
+      <c r="W507" t="s">
+        <v>381</v>
+      </c>
       <c r="AA507">
         <v>0</v>
       </c>
       <c r="AB507" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="AG507" t="s">
         <v>429</v>
       </c>
       <c r="AH507" t="s">
-        <v>422</v>
+        <v>436</v>
       </c>
     </row>
     <row r="508" spans="1:34">
       <c r="A508">
-        <v>6548</v>
+        <v>6703</v>
       </c>
       <c r="B508" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C508" t="s">
         <v>61</v>
       </c>
       <c r="D508" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E508" t="s">
         <v>65</v>
@@ -36337,41 +36342,32 @@
       <c r="L508" s="1">
         <v>46286</v>
       </c>
-      <c r="M508" t="s">
-        <v>209</v>
-      </c>
       <c r="N508" t="s">
         <v>217</v>
       </c>
       <c r="O508">
-        <v>17222647</v>
+        <v>18077122</v>
       </c>
       <c r="P508" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q508" t="s">
         <v>249</v>
       </c>
       <c r="R508" s="1">
-        <v>46280.57972293982</v>
+        <v>46279.6268503125</v>
       </c>
       <c r="S508">
         <v>-5</v>
       </c>
       <c r="T508" t="s">
-        <v>252</v>
-      </c>
-      <c r="V508" t="s">
-        <v>268</v>
-      </c>
-      <c r="W508" t="s">
-        <v>382</v>
+        <v>260</v>
       </c>
       <c r="AA508">
         <v>0</v>
       </c>
       <c r="AB508" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG508" t="s">
         <v>429</v>
@@ -36382,16 +36378,16 @@
     </row>
     <row r="509" spans="1:34">
       <c r="A509">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B509" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C509" t="s">
         <v>61</v>
       </c>
       <c r="D509" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E509" t="s">
         <v>65</v>
@@ -36418,48 +36414,51 @@
         <v>217</v>
       </c>
       <c r="O509">
-        <v>18077122</v>
+        <v>18090199</v>
       </c>
       <c r="P509" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q509" t="s">
         <v>249</v>
       </c>
       <c r="R509" s="1">
-        <v>46279.6268503125</v>
+        <v>46279.66698128472</v>
       </c>
       <c r="S509">
         <v>-5</v>
       </c>
       <c r="T509" t="s">
-        <v>260</v>
+        <v>258</v>
+      </c>
+      <c r="V509" t="s">
+        <v>268</v>
       </c>
       <c r="AA509">
         <v>0</v>
       </c>
       <c r="AB509" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AG509" t="s">
         <v>429</v>
       </c>
       <c r="AH509" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
     </row>
     <row r="510" spans="1:34">
       <c r="A510">
-        <v>6779</v>
+        <v>5417</v>
       </c>
       <c r="B510" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C510" t="s">
         <v>61</v>
       </c>
       <c r="D510" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E510" t="s">
         <v>65</v>
@@ -36468,69 +36467,66 @@
         <v>67</v>
       </c>
       <c r="G510">
-        <v>5884</v>
+        <v>7012</v>
       </c>
       <c r="H510">
-        <v>5792</v>
+        <v>0</v>
       </c>
       <c r="I510" t="s">
         <v>72</v>
       </c>
       <c r="J510" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L510" s="1">
-        <v>46286</v>
+        <v>46281</v>
       </c>
       <c r="N510" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="O510">
-        <v>18090199</v>
+        <v>18257773</v>
       </c>
       <c r="P510" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="Q510" t="s">
         <v>249</v>
       </c>
       <c r="R510" s="1">
-        <v>46279.66698128472</v>
+        <v>46279.66929922454</v>
       </c>
       <c r="S510">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="T510" t="s">
-        <v>258</v>
-      </c>
-      <c r="V510" t="s">
-        <v>268</v>
+        <v>257</v>
+      </c>
+      <c r="W510" t="s">
+        <v>382</v>
       </c>
       <c r="AA510">
         <v>0</v>
       </c>
       <c r="AB510" t="s">
-        <v>234</v>
+        <v>419</v>
       </c>
       <c r="AG510" t="s">
         <v>429</v>
       </c>
-      <c r="AH510" t="s">
-        <v>422</v>
-      </c>
     </row>
     <row r="511" spans="1:34">
       <c r="A511">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B511" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C511" t="s">
         <v>61</v>
       </c>
       <c r="D511" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E511" t="s">
         <v>65</v>
@@ -36557,22 +36553,22 @@
         <v>216</v>
       </c>
       <c r="O511">
-        <v>18257773</v>
+        <v>18258536</v>
       </c>
       <c r="P511" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q511" t="s">
         <v>249</v>
       </c>
       <c r="R511" s="1">
-        <v>46279.66929922454</v>
+        <v>46280.61353684028</v>
       </c>
       <c r="S511">
         <v>0</v>
       </c>
       <c r="T511" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="W511" t="s">
         <v>383</v>
@@ -36586,19 +36582,22 @@
       <c r="AG511" t="s">
         <v>429</v>
       </c>
+      <c r="AH511" t="s">
+        <v>422</v>
+      </c>
     </row>
     <row r="512" spans="1:34">
       <c r="A512">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B512" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C512" t="s">
         <v>61</v>
       </c>
       <c r="D512" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E512" t="s">
         <v>65</v>
@@ -36625,22 +36624,25 @@
         <v>216</v>
       </c>
       <c r="O512">
-        <v>18258536</v>
+        <v>18254964</v>
       </c>
       <c r="P512" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="Q512" t="s">
         <v>249</v>
       </c>
       <c r="R512" s="1">
-        <v>46280.61353684028</v>
+        <v>46280.61353920139</v>
       </c>
       <c r="S512">
         <v>0</v>
       </c>
       <c r="T512" t="s">
-        <v>261</v>
+        <v>259</v>
+      </c>
+      <c r="V512" t="s">
+        <v>268</v>
       </c>
       <c r="W512" t="s">
         <v>384</v>
@@ -36655,15 +36657,15 @@
         <v>429</v>
       </c>
       <c r="AH512" t="s">
-        <v>422</v>
+        <v>436</v>
       </c>
     </row>
     <row r="513" spans="1:34">
       <c r="A513">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B513" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C513" t="s">
         <v>61</v>
@@ -36696,22 +36698,22 @@
         <v>216</v>
       </c>
       <c r="O513">
-        <v>18254964</v>
+        <v>18255116</v>
       </c>
       <c r="P513" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q513" t="s">
         <v>249</v>
       </c>
       <c r="R513" s="1">
-        <v>46280.61353920139</v>
+        <v>46279.63250563657</v>
       </c>
       <c r="S513">
         <v>0</v>
       </c>
       <c r="T513" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="V513" t="s">
         <v>268</v>
@@ -36734,10 +36736,10 @@
     </row>
     <row r="514" spans="1:34">
       <c r="A514">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B514" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C514" t="s">
         <v>61</v>
@@ -36746,7 +36748,7 @@
         <v>62</v>
       </c>
       <c r="E514" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F514" t="s">
         <v>67</v>
@@ -36770,28 +36772,28 @@
         <v>216</v>
       </c>
       <c r="O514">
-        <v>18255116</v>
+        <v>18257668</v>
       </c>
       <c r="P514" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="Q514" t="s">
         <v>249</v>
       </c>
       <c r="R514" s="1">
-        <v>46279.63250563657</v>
+        <v>46280.61354019676</v>
       </c>
       <c r="S514">
         <v>0</v>
       </c>
       <c r="T514" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="V514" t="s">
         <v>268</v>
       </c>
       <c r="W514" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="AA514">
         <v>0</v>
@@ -36808,16 +36810,16 @@
     </row>
     <row r="515" spans="1:34">
       <c r="A515">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B515" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C515" t="s">
         <v>61</v>
       </c>
       <c r="D515" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E515" t="s">
         <v>66</v>
@@ -36844,7 +36846,7 @@
         <v>216</v>
       </c>
       <c r="O515">
-        <v>18257668</v>
+        <v>18256366</v>
       </c>
       <c r="P515" t="s">
         <v>227</v>
@@ -36853,7 +36855,7 @@
         <v>249</v>
       </c>
       <c r="R515" s="1">
-        <v>46280.61354019676</v>
+        <v>46280.6135403125</v>
       </c>
       <c r="S515">
         <v>0</v>
@@ -36865,7 +36867,7 @@
         <v>268</v>
       </c>
       <c r="W515" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AA515">
         <v>0</v>
@@ -36882,10 +36884,10 @@
     </row>
     <row r="516" spans="1:34">
       <c r="A516">
-        <v>6628</v>
+        <v>6779</v>
       </c>
       <c r="B516" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C516" t="s">
         <v>61</v>
@@ -36894,7 +36896,7 @@
         <v>63</v>
       </c>
       <c r="E516" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F516" t="s">
         <v>67</v>
@@ -36918,28 +36920,28 @@
         <v>216</v>
       </c>
       <c r="O516">
-        <v>18256366</v>
+        <v>18255012</v>
       </c>
       <c r="P516" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="Q516" t="s">
         <v>249</v>
       </c>
       <c r="R516" s="1">
-        <v>46280.6135403125</v>
+        <v>46281.41576883102</v>
       </c>
       <c r="S516">
         <v>0</v>
       </c>
       <c r="T516" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="V516" t="s">
         <v>268</v>
       </c>
       <c r="W516" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AA516">
         <v>0</v>
@@ -36951,7 +36953,7 @@
         <v>429</v>
       </c>
       <c r="AH516" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
     </row>
     <row r="517" spans="1:34">
@@ -37992,7 +37994,7 @@
         <v>268</v>
       </c>
       <c r="W531" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AA531">
         <v>0</v>
@@ -38844,7 +38846,7 @@
         <v>257</v>
       </c>
       <c r="W543" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AA543">
         <v>0</v>

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8667" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8668" uniqueCount="435">
   <si>
     <t>CodCliente</t>
   </si>
@@ -24119,10 +24119,10 @@
     </row>
     <row r="323" spans="1:34">
       <c r="A323">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B323" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C323" t="s">
         <v>58</v>
@@ -24131,7 +24131,7 @@
         <v>59</v>
       </c>
       <c r="E323" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F323" t="s">
         <v>64</v>
@@ -24155,10 +24155,10 @@
         <v>213</v>
       </c>
       <c r="O323">
-        <v>17968001</v>
+        <v>17042403</v>
       </c>
       <c r="P323" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q323" t="s">
         <v>247</v>
@@ -24167,7 +24167,7 @@
         <v>-4</v>
       </c>
       <c r="T323" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="V323" t="s">
         <v>263</v>
@@ -24179,15 +24179,15 @@
         <v>425</v>
       </c>
       <c r="AH323" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="324" spans="1:34">
       <c r="A324">
-        <v>6627</v>
+        <v>6949</v>
       </c>
       <c r="B324" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C324" t="s">
         <v>58</v>
@@ -24196,10 +24196,10 @@
         <v>59</v>
       </c>
       <c r="E324" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F324" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G324">
         <v>1697</v>
@@ -24220,10 +24220,10 @@
         <v>213</v>
       </c>
       <c r="O324">
-        <v>17042403</v>
+        <v>18178280</v>
       </c>
       <c r="P324" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q324" t="s">
         <v>247</v>
@@ -24232,10 +24232,7 @@
         <v>-4</v>
       </c>
       <c r="T324" t="s">
-        <v>249</v>
-      </c>
-      <c r="V324" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="AA324">
         <v>0</v>
@@ -24244,15 +24241,15 @@
         <v>425</v>
       </c>
       <c r="AH324" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="325" spans="1:34">
       <c r="A325">
-        <v>6949</v>
+        <v>5417</v>
       </c>
       <c r="B325" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C325" t="s">
         <v>58</v>
@@ -24264,40 +24261,40 @@
         <v>62</v>
       </c>
       <c r="F325" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G325">
-        <v>1697</v>
+        <v>7868</v>
       </c>
       <c r="H325">
-        <v>1650</v>
+        <v>0</v>
       </c>
       <c r="I325" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J325" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="L325" s="1">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="N325" t="s">
         <v>213</v>
       </c>
       <c r="O325">
-        <v>18178280</v>
+        <v>17399310</v>
       </c>
       <c r="P325" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Q325" t="s">
         <v>247</v>
       </c>
       <c r="S325">
-        <v>-4</v>
+        <v>-11</v>
       </c>
       <c r="T325" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AA325">
         <v>0</v>
@@ -24306,15 +24303,15 @@
         <v>425</v>
       </c>
       <c r="AH325" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="326" spans="1:34">
       <c r="A326">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B326" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C326" t="s">
         <v>58</v>
@@ -24347,10 +24344,10 @@
         <v>213</v>
       </c>
       <c r="O326">
-        <v>17399310</v>
+        <v>18114218</v>
       </c>
       <c r="P326" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="Q326" t="s">
         <v>247</v>
@@ -24359,7 +24356,10 @@
         <v>-11</v>
       </c>
       <c r="T326" t="s">
-        <v>253</v>
+        <v>255</v>
+      </c>
+      <c r="V326" t="s">
+        <v>263</v>
       </c>
       <c r="AA326">
         <v>0</v>
@@ -24373,10 +24373,10 @@
     </row>
     <row r="327" spans="1:34">
       <c r="A327">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B327" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C327" t="s">
         <v>58</v>
@@ -24391,7 +24391,7 @@
         <v>64</v>
       </c>
       <c r="G327">
-        <v>7868</v>
+        <v>6890</v>
       </c>
       <c r="H327">
         <v>0</v>
@@ -24400,37 +24400,34 @@
         <v>68</v>
       </c>
       <c r="J327" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L327" s="1">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="N327" t="s">
         <v>213</v>
       </c>
       <c r="O327">
-        <v>18114218</v>
+        <v>17399260</v>
       </c>
       <c r="P327" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="Q327" t="s">
         <v>247</v>
       </c>
       <c r="S327">
-        <v>-11</v>
+        <v>-8</v>
       </c>
       <c r="T327" t="s">
-        <v>255</v>
-      </c>
-      <c r="V327" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="AA327">
         <v>0</v>
       </c>
       <c r="AG327" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AH327" t="s">
         <v>430</v>
@@ -24438,16 +24435,16 @@
     </row>
     <row r="328" spans="1:34">
       <c r="A328">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B328" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C328" t="s">
         <v>58</v>
       </c>
       <c r="D328" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E328" t="s">
         <v>62</v>
@@ -24474,10 +24471,10 @@
         <v>213</v>
       </c>
       <c r="O328">
-        <v>17399260</v>
+        <v>16962328</v>
       </c>
       <c r="P328" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="Q328" t="s">
         <v>247</v>
@@ -24486,7 +24483,7 @@
         <v>-8</v>
       </c>
       <c r="T328" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="AA328">
         <v>0</v>
@@ -24495,21 +24492,21 @@
         <v>427</v>
       </c>
       <c r="AH328" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="329" spans="1:34">
       <c r="A329">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B329" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C329" t="s">
         <v>58</v>
       </c>
       <c r="D329" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E329" t="s">
         <v>62</v>
@@ -24536,10 +24533,10 @@
         <v>213</v>
       </c>
       <c r="O329">
-        <v>16962328</v>
+        <v>18152538</v>
       </c>
       <c r="P329" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q329" t="s">
         <v>247</v>
@@ -24548,7 +24545,10 @@
         <v>-8</v>
       </c>
       <c r="T329" t="s">
-        <v>257</v>
+        <v>255</v>
+      </c>
+      <c r="V329" t="s">
+        <v>263</v>
       </c>
       <c r="AA329">
         <v>0</v>
@@ -24557,21 +24557,21 @@
         <v>427</v>
       </c>
       <c r="AH329" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="330" spans="1:34">
       <c r="A330">
-        <v>6486</v>
+        <v>6703</v>
       </c>
       <c r="B330" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C330" t="s">
         <v>58</v>
       </c>
       <c r="D330" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E330" t="s">
         <v>62</v>
@@ -24598,7 +24598,7 @@
         <v>213</v>
       </c>
       <c r="O330">
-        <v>18152538</v>
+        <v>17955186</v>
       </c>
       <c r="P330" t="s">
         <v>240</v>
@@ -24610,10 +24610,7 @@
         <v>-8</v>
       </c>
       <c r="T330" t="s">
-        <v>255</v>
-      </c>
-      <c r="V330" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="AA330">
         <v>0</v>
@@ -24627,16 +24624,16 @@
     </row>
     <row r="331" spans="1:34">
       <c r="A331">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B331" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C331" t="s">
         <v>58</v>
       </c>
       <c r="D331" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E331" t="s">
         <v>62</v>
@@ -24663,10 +24660,10 @@
         <v>213</v>
       </c>
       <c r="O331">
-        <v>17955186</v>
+        <v>17955399</v>
       </c>
       <c r="P331" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="Q331" t="s">
         <v>247</v>
@@ -24675,7 +24672,10 @@
         <v>-8</v>
       </c>
       <c r="T331" t="s">
-        <v>256</v>
+        <v>254</v>
+      </c>
+      <c r="V331" t="s">
+        <v>263</v>
       </c>
       <c r="AA331">
         <v>0</v>
@@ -24684,21 +24684,21 @@
         <v>427</v>
       </c>
       <c r="AH331" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="332" spans="1:34">
       <c r="A332">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B332" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C332" t="s">
         <v>58</v>
       </c>
       <c r="D332" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E332" t="s">
         <v>62</v>
@@ -24725,7 +24725,7 @@
         <v>213</v>
       </c>
       <c r="O332">
-        <v>17955399</v>
+        <v>17955249</v>
       </c>
       <c r="P332" t="s">
         <v>223</v>
@@ -24739,9 +24739,6 @@
       <c r="T332" t="s">
         <v>254</v>
       </c>
-      <c r="V332" t="s">
-        <v>263</v>
-      </c>
       <c r="AA332">
         <v>0</v>
       </c>
@@ -24754,10 +24751,10 @@
     </row>
     <row r="333" spans="1:34">
       <c r="A333">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B333" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C333" t="s">
         <v>58</v>
@@ -24790,7 +24787,7 @@
         <v>213</v>
       </c>
       <c r="O333">
-        <v>17955249</v>
+        <v>18056769</v>
       </c>
       <c r="P333" t="s">
         <v>223</v>
@@ -24804,6 +24801,9 @@
       <c r="T333" t="s">
         <v>254</v>
       </c>
+      <c r="V333" t="s">
+        <v>263</v>
+      </c>
       <c r="AA333">
         <v>0</v>
       </c>
@@ -24816,16 +24816,16 @@
     </row>
     <row r="334" spans="1:34">
       <c r="A334">
-        <v>6779</v>
+        <v>5417</v>
       </c>
       <c r="B334" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C334" t="s">
         <v>58</v>
       </c>
       <c r="D334" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E334" t="s">
         <v>62</v>
@@ -24834,7 +24834,7 @@
         <v>64</v>
       </c>
       <c r="G334">
-        <v>6890</v>
+        <v>11514</v>
       </c>
       <c r="H334">
         <v>0</v>
@@ -24843,7 +24843,7 @@
         <v>68</v>
       </c>
       <c r="J334" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L334" s="1">
         <v>46290</v>
@@ -24852,10 +24852,10 @@
         <v>213</v>
       </c>
       <c r="O334">
-        <v>18056769</v>
+        <v>17399465</v>
       </c>
       <c r="P334" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q334" t="s">
         <v>247</v>
@@ -24864,10 +24864,7 @@
         <v>-8</v>
       </c>
       <c r="T334" t="s">
-        <v>254</v>
-      </c>
-      <c r="V334" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="AA334">
         <v>0</v>
@@ -24876,21 +24873,21 @@
         <v>427</v>
       </c>
       <c r="AH334" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="335" spans="1:34">
       <c r="A335">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B335" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C335" t="s">
         <v>58</v>
       </c>
       <c r="D335" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E335" t="s">
         <v>62</v>
@@ -24917,10 +24914,10 @@
         <v>213</v>
       </c>
       <c r="O335">
-        <v>17399465</v>
+        <v>16962474</v>
       </c>
       <c r="P335" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="Q335" t="s">
         <v>247</v>
@@ -24929,7 +24926,7 @@
         <v>-8</v>
       </c>
       <c r="T335" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="AA335">
         <v>0</v>
@@ -24938,21 +24935,21 @@
         <v>427</v>
       </c>
       <c r="AH335" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="336" spans="1:34">
       <c r="A336">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B336" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C336" t="s">
         <v>58</v>
       </c>
       <c r="D336" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E336" t="s">
         <v>62</v>
@@ -24979,10 +24976,10 @@
         <v>213</v>
       </c>
       <c r="O336">
-        <v>16962474</v>
+        <v>18114227</v>
       </c>
       <c r="P336" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q336" t="s">
         <v>247</v>
@@ -24991,7 +24988,10 @@
         <v>-8</v>
       </c>
       <c r="T336" t="s">
-        <v>257</v>
+        <v>255</v>
+      </c>
+      <c r="V336" t="s">
+        <v>263</v>
       </c>
       <c r="AA336">
         <v>0</v>
@@ -25000,21 +25000,21 @@
         <v>427</v>
       </c>
       <c r="AH336" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="337" spans="1:34">
       <c r="A337">
-        <v>6486</v>
+        <v>6703</v>
       </c>
       <c r="B337" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C337" t="s">
         <v>58</v>
       </c>
       <c r="D337" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E337" t="s">
         <v>62</v>
@@ -25041,7 +25041,7 @@
         <v>213</v>
       </c>
       <c r="O337">
-        <v>18114227</v>
+        <v>17955212</v>
       </c>
       <c r="P337" t="s">
         <v>240</v>
@@ -25053,10 +25053,7 @@
         <v>-8</v>
       </c>
       <c r="T337" t="s">
-        <v>255</v>
-      </c>
-      <c r="V337" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="AA337">
         <v>0</v>
@@ -25070,16 +25067,16 @@
     </row>
     <row r="338" spans="1:34">
       <c r="A338">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B338" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C338" t="s">
         <v>58</v>
       </c>
       <c r="D338" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E338" t="s">
         <v>62</v>
@@ -25106,10 +25103,10 @@
         <v>213</v>
       </c>
       <c r="O338">
-        <v>17955212</v>
+        <v>17955445</v>
       </c>
       <c r="P338" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="Q338" t="s">
         <v>247</v>
@@ -25118,7 +25115,10 @@
         <v>-8</v>
       </c>
       <c r="T338" t="s">
-        <v>256</v>
+        <v>254</v>
+      </c>
+      <c r="V338" t="s">
+        <v>263</v>
       </c>
       <c r="AA338">
         <v>0</v>
@@ -25127,21 +25127,21 @@
         <v>427</v>
       </c>
       <c r="AH338" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="339" spans="1:34">
       <c r="A339">
-        <v>6704</v>
+        <v>6404</v>
       </c>
       <c r="B339" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C339" t="s">
         <v>58</v>
       </c>
       <c r="D339" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E339" t="s">
         <v>62</v>
@@ -25150,7 +25150,7 @@
         <v>64</v>
       </c>
       <c r="G339">
-        <v>11514</v>
+        <v>10988</v>
       </c>
       <c r="H339">
         <v>0</v>
@@ -25159,37 +25159,34 @@
         <v>68</v>
       </c>
       <c r="J339" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L339" s="1">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="N339" t="s">
         <v>213</v>
       </c>
       <c r="O339">
-        <v>17955445</v>
+        <v>16962444</v>
       </c>
       <c r="P339" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="Q339" t="s">
         <v>247</v>
       </c>
       <c r="S339">
-        <v>-8</v>
+        <v>-13</v>
       </c>
       <c r="T339" t="s">
-        <v>254</v>
-      </c>
-      <c r="V339" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="AA339">
         <v>0</v>
       </c>
       <c r="AG339" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="AH339" t="s">
         <v>431</v>
@@ -25197,10 +25194,10 @@
     </row>
     <row r="340" spans="1:34">
       <c r="A340">
-        <v>6404</v>
+        <v>6703</v>
       </c>
       <c r="B340" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C340" t="s">
         <v>58</v>
@@ -25233,10 +25230,10 @@
         <v>213</v>
       </c>
       <c r="O340">
-        <v>16962444</v>
+        <v>18112918</v>
       </c>
       <c r="P340" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q340" t="s">
         <v>247</v>
@@ -25245,7 +25242,7 @@
         <v>-13</v>
       </c>
       <c r="T340" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AA340">
         <v>0</v>
@@ -25254,21 +25251,21 @@
         <v>425</v>
       </c>
       <c r="AH340" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="341" spans="1:34">
       <c r="A341">
-        <v>6703</v>
+        <v>5417</v>
       </c>
       <c r="B341" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C341" t="s">
         <v>58</v>
       </c>
       <c r="D341" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E341" t="s">
         <v>62</v>
@@ -25277,7 +25274,7 @@
         <v>64</v>
       </c>
       <c r="G341">
-        <v>10988</v>
+        <v>7874</v>
       </c>
       <c r="H341">
         <v>0</v>
@@ -25286,7 +25283,7 @@
         <v>68</v>
       </c>
       <c r="J341" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L341" s="1">
         <v>46295</v>
@@ -25295,10 +25292,10 @@
         <v>213</v>
       </c>
       <c r="O341">
-        <v>18112918</v>
+        <v>17399320</v>
       </c>
       <c r="P341" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="Q341" t="s">
         <v>247</v>
@@ -25307,7 +25304,7 @@
         <v>-13</v>
       </c>
       <c r="T341" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="AA341">
         <v>0</v>
@@ -25321,10 +25318,10 @@
     </row>
     <row r="342" spans="1:34">
       <c r="A342">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B342" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C342" t="s">
         <v>58</v>
@@ -25357,10 +25354,10 @@
         <v>213</v>
       </c>
       <c r="O342">
-        <v>17399320</v>
+        <v>18130463</v>
       </c>
       <c r="P342" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="Q342" t="s">
         <v>247</v>
@@ -25369,7 +25366,10 @@
         <v>-13</v>
       </c>
       <c r="T342" t="s">
-        <v>253</v>
+        <v>255</v>
+      </c>
+      <c r="V342" t="s">
+        <v>263</v>
       </c>
       <c r="AA342">
         <v>0</v>
@@ -25383,10 +25383,10 @@
     </row>
     <row r="343" spans="1:34">
       <c r="A343">
-        <v>6486</v>
+        <v>6704</v>
       </c>
       <c r="B343" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C343" t="s">
         <v>58</v>
@@ -25419,10 +25419,10 @@
         <v>213</v>
       </c>
       <c r="O343">
-        <v>18130463</v>
+        <v>18096767</v>
       </c>
       <c r="P343" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="Q343" t="s">
         <v>247</v>
@@ -25431,7 +25431,7 @@
         <v>-13</v>
       </c>
       <c r="T343" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="V343" t="s">
         <v>263</v>
@@ -25443,21 +25443,21 @@
         <v>425</v>
       </c>
       <c r="AH343" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="344" spans="1:34">
       <c r="A344">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B344" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C344" t="s">
         <v>58</v>
       </c>
       <c r="D344" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E344" t="s">
         <v>62</v>
@@ -25466,7 +25466,7 @@
         <v>64</v>
       </c>
       <c r="G344">
-        <v>7874</v>
+        <v>9762</v>
       </c>
       <c r="H344">
         <v>0</v>
@@ -25475,7 +25475,7 @@
         <v>68</v>
       </c>
       <c r="J344" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L344" s="1">
         <v>46295</v>
@@ -25484,7 +25484,7 @@
         <v>213</v>
       </c>
       <c r="O344">
-        <v>18096767</v>
+        <v>18096939</v>
       </c>
       <c r="P344" t="s">
         <v>223</v>
@@ -25498,9 +25498,6 @@
       <c r="T344" t="s">
         <v>254</v>
       </c>
-      <c r="V344" t="s">
-        <v>263</v>
-      </c>
       <c r="AA344">
         <v>0</v>
       </c>
@@ -25513,10 +25510,10 @@
     </row>
     <row r="345" spans="1:34">
       <c r="A345">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B345" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C345" t="s">
         <v>58</v>
@@ -25549,7 +25546,7 @@
         <v>213</v>
       </c>
       <c r="O345">
-        <v>18096939</v>
+        <v>18130484</v>
       </c>
       <c r="P345" t="s">
         <v>223</v>
@@ -25563,6 +25560,9 @@
       <c r="T345" t="s">
         <v>254</v>
       </c>
+      <c r="V345" t="s">
+        <v>263</v>
+      </c>
       <c r="AA345">
         <v>0</v>
       </c>
@@ -25575,16 +25575,16 @@
     </row>
     <row r="346" spans="1:34">
       <c r="A346">
-        <v>6779</v>
+        <v>6548</v>
       </c>
       <c r="B346" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C346" t="s">
         <v>58</v>
       </c>
       <c r="D346" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E346" t="s">
         <v>62</v>
@@ -25593,28 +25593,28 @@
         <v>64</v>
       </c>
       <c r="G346">
-        <v>9762</v>
+        <v>5859</v>
       </c>
       <c r="H346">
-        <v>0</v>
+        <v>5786</v>
       </c>
       <c r="I346" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J346" t="s">
-        <v>137</v>
+        <v>76</v>
       </c>
       <c r="L346" s="1">
         <v>46295</v>
       </c>
       <c r="N346" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O346">
-        <v>18130484</v>
+        <v>17222602</v>
       </c>
       <c r="P346" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="Q346" t="s">
         <v>247</v>
@@ -25623,7 +25623,7 @@
         <v>-13</v>
       </c>
       <c r="T346" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="V346" t="s">
         <v>263</v>
@@ -25632,89 +25632,86 @@
         <v>0</v>
       </c>
       <c r="AG346" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AH346" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="347" spans="1:34">
       <c r="A347">
-        <v>6548</v>
+        <v>6945</v>
       </c>
       <c r="B347" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C347" t="s">
         <v>58</v>
       </c>
       <c r="D347" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E347" t="s">
         <v>62</v>
       </c>
       <c r="F347" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G347">
-        <v>5859</v>
+        <v>5883</v>
       </c>
       <c r="H347">
-        <v>5786</v>
+        <v>5792</v>
       </c>
       <c r="I347" t="s">
         <v>69</v>
       </c>
       <c r="J347" t="s">
-        <v>76</v>
+        <v>139</v>
       </c>
       <c r="L347" s="1">
-        <v>46295</v>
+        <v>46286</v>
       </c>
       <c r="N347" t="s">
         <v>214</v>
       </c>
       <c r="O347">
-        <v>17222602</v>
+        <v>18179111</v>
       </c>
       <c r="P347" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="Q347" t="s">
         <v>247</v>
       </c>
       <c r="S347">
-        <v>-13</v>
+        <v>-4</v>
       </c>
       <c r="T347" t="s">
-        <v>248</v>
-      </c>
-      <c r="V347" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="AA347">
         <v>0</v>
       </c>
       <c r="AG347" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AH347" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="348" spans="1:34">
       <c r="A348">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B348" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C348" t="s">
         <v>58</v>
       </c>
       <c r="D348" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E348" t="s">
         <v>62</v>
@@ -25741,10 +25738,10 @@
         <v>214</v>
       </c>
       <c r="O348">
-        <v>18179111</v>
+        <v>18190420</v>
       </c>
       <c r="P348" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q348" t="s">
         <v>247</v>
@@ -25753,7 +25750,7 @@
         <v>-4</v>
       </c>
       <c r="T348" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AA348">
         <v>0</v>
@@ -25767,16 +25764,16 @@
     </row>
     <row r="349" spans="1:34">
       <c r="A349">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B349" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C349" t="s">
         <v>58</v>
       </c>
       <c r="D349" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E349" t="s">
         <v>62</v>
@@ -25785,7 +25782,7 @@
         <v>65</v>
       </c>
       <c r="G349">
-        <v>5883</v>
+        <v>5884</v>
       </c>
       <c r="H349">
         <v>5792</v>
@@ -25794,7 +25791,7 @@
         <v>69</v>
       </c>
       <c r="J349" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L349" s="1">
         <v>46286</v>
@@ -25803,10 +25800,10 @@
         <v>214</v>
       </c>
       <c r="O349">
-        <v>18190420</v>
+        <v>18179118</v>
       </c>
       <c r="P349" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Q349" t="s">
         <v>247</v>
@@ -25815,7 +25812,7 @@
         <v>-4</v>
       </c>
       <c r="T349" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AA349">
         <v>0</v>
@@ -25829,16 +25826,16 @@
     </row>
     <row r="350" spans="1:34">
       <c r="A350">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B350" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C350" t="s">
         <v>58</v>
       </c>
       <c r="D350" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E350" t="s">
         <v>62</v>
@@ -25865,10 +25862,10 @@
         <v>214</v>
       </c>
       <c r="O350">
-        <v>18179118</v>
+        <v>18190426</v>
       </c>
       <c r="P350" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q350" t="s">
         <v>247</v>
@@ -25877,7 +25874,7 @@
         <v>-4</v>
       </c>
       <c r="T350" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AA350">
         <v>0</v>
@@ -25891,10 +25888,10 @@
     </row>
     <row r="351" spans="1:34">
       <c r="A351">
-        <v>6949</v>
+        <v>5417</v>
       </c>
       <c r="B351" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C351" t="s">
         <v>58</v>
@@ -25906,19 +25903,19 @@
         <v>62</v>
       </c>
       <c r="F351" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G351">
-        <v>5884</v>
+        <v>5836</v>
       </c>
       <c r="H351">
-        <v>5792</v>
+        <v>5784</v>
       </c>
       <c r="I351" t="s">
         <v>69</v>
       </c>
       <c r="J351" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L351" s="1">
         <v>46286</v>
@@ -25927,10 +25924,10 @@
         <v>214</v>
       </c>
       <c r="O351">
-        <v>18190426</v>
+        <v>17399027</v>
       </c>
       <c r="P351" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q351" t="s">
         <v>247</v>
@@ -25939,7 +25936,7 @@
         <v>-4</v>
       </c>
       <c r="T351" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AA351">
         <v>0</v>
@@ -25947,16 +25944,13 @@
       <c r="AG351" t="s">
         <v>425</v>
       </c>
-      <c r="AH351" t="s">
-        <v>433</v>
-      </c>
     </row>
     <row r="352" spans="1:34">
       <c r="A352">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B352" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C352" t="s">
         <v>58</v>
@@ -25985,14 +25979,17 @@
       <c r="L352" s="1">
         <v>46286</v>
       </c>
+      <c r="M352" t="s">
+        <v>209</v>
+      </c>
       <c r="N352" t="s">
         <v>214</v>
       </c>
       <c r="O352">
-        <v>17399027</v>
+        <v>16976037</v>
       </c>
       <c r="P352" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="Q352" t="s">
         <v>247</v>
@@ -26001,7 +25998,13 @@
         <v>-4</v>
       </c>
       <c r="T352" t="s">
-        <v>253</v>
+        <v>255</v>
+      </c>
+      <c r="V352" t="s">
+        <v>263</v>
+      </c>
+      <c r="W352" t="s">
+        <v>351</v>
       </c>
       <c r="AA352">
         <v>0</v>
@@ -26009,13 +26012,16 @@
       <c r="AG352" t="s">
         <v>425</v>
       </c>
+      <c r="AH352" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="353" spans="1:34">
       <c r="A353">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B353" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C353" t="s">
         <v>58</v>
@@ -26051,10 +26057,10 @@
         <v>214</v>
       </c>
       <c r="O353">
-        <v>16976037</v>
+        <v>17222579</v>
       </c>
       <c r="P353" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q353" t="s">
         <v>247</v>
@@ -26063,13 +26069,13 @@
         <v>-4</v>
       </c>
       <c r="T353" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="V353" t="s">
         <v>263</v>
       </c>
       <c r="W353" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AA353">
         <v>0</v>
@@ -26083,10 +26089,10 @@
     </row>
     <row r="354" spans="1:34">
       <c r="A354">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B354" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C354" t="s">
         <v>58</v>
@@ -26095,7 +26101,7 @@
         <v>59</v>
       </c>
       <c r="E354" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F354" t="s">
         <v>64</v>
@@ -26122,10 +26128,10 @@
         <v>214</v>
       </c>
       <c r="O354">
-        <v>17222579</v>
+        <v>18068500</v>
       </c>
       <c r="P354" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="Q354" t="s">
         <v>247</v>
@@ -26134,13 +26140,13 @@
         <v>-4</v>
       </c>
       <c r="T354" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="V354" t="s">
         <v>263</v>
       </c>
       <c r="W354" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AA354">
         <v>0</v>
@@ -26154,16 +26160,16 @@
     </row>
     <row r="355" spans="1:34">
       <c r="A355">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B355" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C355" t="s">
         <v>58</v>
       </c>
       <c r="D355" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E355" t="s">
         <v>63</v>
@@ -26193,7 +26199,7 @@
         <v>214</v>
       </c>
       <c r="O355">
-        <v>18068500</v>
+        <v>18052419</v>
       </c>
       <c r="P355" t="s">
         <v>224</v>
@@ -26225,19 +26231,19 @@
     </row>
     <row r="356" spans="1:34">
       <c r="A356">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B356" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C356" t="s">
         <v>58</v>
       </c>
       <c r="D356" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E356" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F356" t="s">
         <v>64</v>
@@ -26264,10 +26270,10 @@
         <v>214</v>
       </c>
       <c r="O356">
-        <v>18052419</v>
+        <v>18077082</v>
       </c>
       <c r="P356" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="Q356" t="s">
         <v>247</v>
@@ -26276,13 +26282,10 @@
         <v>-4</v>
       </c>
       <c r="T356" t="s">
-        <v>249</v>
-      </c>
-      <c r="V356" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="W356" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AA356">
         <v>0</v>
@@ -26296,16 +26299,16 @@
     </row>
     <row r="357" spans="1:34">
       <c r="A357">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B357" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C357" t="s">
         <v>58</v>
       </c>
       <c r="D357" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E357" t="s">
         <v>62</v>
@@ -26329,16 +26332,16 @@
         <v>46286</v>
       </c>
       <c r="M357" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="N357" t="s">
         <v>214</v>
       </c>
       <c r="O357">
-        <v>18077082</v>
+        <v>18090149</v>
       </c>
       <c r="P357" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q357" t="s">
         <v>247</v>
@@ -26347,10 +26350,13 @@
         <v>-4</v>
       </c>
       <c r="T357" t="s">
-        <v>256</v>
+        <v>254</v>
+      </c>
+      <c r="V357" t="s">
+        <v>263</v>
       </c>
       <c r="W357" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AA357">
         <v>0</v>
@@ -26359,15 +26365,15 @@
         <v>425</v>
       </c>
       <c r="AH357" t="s">
-        <v>432</v>
+        <v>418</v>
       </c>
     </row>
     <row r="358" spans="1:34">
       <c r="A358">
-        <v>6779</v>
+        <v>6945</v>
       </c>
       <c r="B358" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C358" t="s">
         <v>58</v>
@@ -26379,7 +26385,7 @@
         <v>62</v>
       </c>
       <c r="F358" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G358">
         <v>5836</v>
@@ -26396,17 +26402,14 @@
       <c r="L358" s="1">
         <v>46286</v>
       </c>
-      <c r="M358" t="s">
-        <v>206</v>
-      </c>
       <c r="N358" t="s">
         <v>214</v>
       </c>
       <c r="O358">
-        <v>18090149</v>
+        <v>18179083</v>
       </c>
       <c r="P358" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="Q358" t="s">
         <v>247</v>
@@ -26415,13 +26418,7 @@
         <v>-4</v>
       </c>
       <c r="T358" t="s">
-        <v>254</v>
-      </c>
-      <c r="V358" t="s">
-        <v>263</v>
-      </c>
-      <c r="W358" t="s">
-        <v>354</v>
+        <v>250</v>
       </c>
       <c r="AA358">
         <v>0</v>
@@ -26430,30 +26427,30 @@
         <v>425</v>
       </c>
       <c r="AH358" t="s">
-        <v>418</v>
+        <v>433</v>
       </c>
     </row>
     <row r="359" spans="1:34">
       <c r="A359">
-        <v>6945</v>
+        <v>6548</v>
       </c>
       <c r="B359" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C359" t="s">
         <v>58</v>
       </c>
       <c r="D359" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E359" t="s">
         <v>62</v>
       </c>
       <c r="F359" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G359">
-        <v>5836</v>
+        <v>5905</v>
       </c>
       <c r="H359">
         <v>5784</v>
@@ -26462,37 +26459,40 @@
         <v>69</v>
       </c>
       <c r="J359" t="s">
-        <v>141</v>
+        <v>80</v>
       </c>
       <c r="L359" s="1">
-        <v>46286</v>
+        <v>46295</v>
       </c>
       <c r="N359" t="s">
         <v>214</v>
       </c>
       <c r="O359">
-        <v>18179083</v>
+        <v>17222671</v>
       </c>
       <c r="P359" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q359" t="s">
         <v>247</v>
       </c>
       <c r="S359">
-        <v>-4</v>
+        <v>-13</v>
       </c>
       <c r="T359" t="s">
-        <v>250</v>
+        <v>248</v>
+      </c>
+      <c r="V359" t="s">
+        <v>263</v>
       </c>
       <c r="AA359">
         <v>0</v>
       </c>
       <c r="AG359" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AH359" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="360" spans="1:34">
@@ -26515,7 +26515,7 @@
         <v>64</v>
       </c>
       <c r="G360">
-        <v>5905</v>
+        <v>5853</v>
       </c>
       <c r="H360">
         <v>5784</v>
@@ -26524,7 +26524,7 @@
         <v>69</v>
       </c>
       <c r="J360" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L360" s="1">
         <v>46295</v>
@@ -26533,7 +26533,7 @@
         <v>214</v>
       </c>
       <c r="O360">
-        <v>17222671</v>
+        <v>17222589</v>
       </c>
       <c r="P360" t="s">
         <v>228</v>
@@ -26554,7 +26554,7 @@
         <v>0</v>
       </c>
       <c r="AG360" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="AH360" t="s">
         <v>432</v>
@@ -26562,10 +26562,10 @@
     </row>
     <row r="361" spans="1:34">
       <c r="A361">
-        <v>6548</v>
+        <v>5417</v>
       </c>
       <c r="B361" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C361" t="s">
         <v>58</v>
@@ -26580,7 +26580,7 @@
         <v>64</v>
       </c>
       <c r="G361">
-        <v>5853</v>
+        <v>5847</v>
       </c>
       <c r="H361">
         <v>5784</v>
@@ -26589,31 +26589,28 @@
         <v>69</v>
       </c>
       <c r="J361" t="s">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="L361" s="1">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="N361" t="s">
         <v>214</v>
       </c>
       <c r="O361">
-        <v>17222589</v>
+        <v>18158417</v>
       </c>
       <c r="P361" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q361" t="s">
         <v>247</v>
       </c>
       <c r="S361">
-        <v>-13</v>
+        <v>-11</v>
       </c>
       <c r="T361" t="s">
-        <v>248</v>
-      </c>
-      <c r="V361" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="AA361">
         <v>0</v>
@@ -26621,22 +26618,19 @@
       <c r="AG361" t="s">
         <v>425</v>
       </c>
-      <c r="AH361" t="s">
-        <v>432</v>
-      </c>
     </row>
     <row r="362" spans="1:34">
       <c r="A362">
-        <v>5417</v>
+        <v>6779</v>
       </c>
       <c r="B362" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C362" t="s">
         <v>58</v>
       </c>
       <c r="D362" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E362" t="s">
         <v>62</v>
@@ -26663,10 +26657,10 @@
         <v>214</v>
       </c>
       <c r="O362">
-        <v>18158417</v>
+        <v>18158764</v>
       </c>
       <c r="P362" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q362" t="s">
         <v>247</v>
@@ -26675,7 +26669,10 @@
         <v>-11</v>
       </c>
       <c r="T362" t="s">
-        <v>253</v>
+        <v>254</v>
+      </c>
+      <c r="V362" t="s">
+        <v>263</v>
       </c>
       <c r="AA362">
         <v>0</v>
@@ -26683,19 +26680,22 @@
       <c r="AG362" t="s">
         <v>425</v>
       </c>
+      <c r="AH362" t="s">
+        <v>418</v>
+      </c>
     </row>
     <row r="363" spans="1:34">
       <c r="A363">
-        <v>6779</v>
+        <v>6548</v>
       </c>
       <c r="B363" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C363" t="s">
         <v>58</v>
       </c>
       <c r="D363" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E363" t="s">
         <v>62</v>
@@ -26704,7 +26704,7 @@
         <v>64</v>
       </c>
       <c r="G363">
-        <v>5847</v>
+        <v>5906</v>
       </c>
       <c r="H363">
         <v>5784</v>
@@ -26713,28 +26713,28 @@
         <v>69</v>
       </c>
       <c r="J363" t="s">
-        <v>142</v>
+        <v>87</v>
       </c>
       <c r="L363" s="1">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="N363" t="s">
         <v>214</v>
       </c>
       <c r="O363">
-        <v>18158764</v>
+        <v>17222688</v>
       </c>
       <c r="P363" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="Q363" t="s">
         <v>247</v>
       </c>
       <c r="S363">
-        <v>-11</v>
+        <v>-13</v>
       </c>
       <c r="T363" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="V363" t="s">
         <v>263</v>
@@ -26743,10 +26743,10 @@
         <v>0</v>
       </c>
       <c r="AG363" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AH363" t="s">
-        <v>418</v>
+        <v>432</v>
       </c>
     </row>
     <row r="364" spans="1:34">
@@ -26769,7 +26769,7 @@
         <v>64</v>
       </c>
       <c r="G364">
-        <v>5906</v>
+        <v>5907</v>
       </c>
       <c r="H364">
         <v>5784</v>
@@ -26778,7 +26778,7 @@
         <v>69</v>
       </c>
       <c r="J364" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L364" s="1">
         <v>46295</v>
@@ -26787,7 +26787,7 @@
         <v>214</v>
       </c>
       <c r="O364">
-        <v>17222688</v>
+        <v>17222699</v>
       </c>
       <c r="P364" t="s">
         <v>228</v>
@@ -26808,7 +26808,7 @@
         <v>0</v>
       </c>
       <c r="AG364" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="AH364" t="s">
         <v>432</v>
@@ -26816,10 +26816,10 @@
     </row>
     <row r="365" spans="1:34">
       <c r="A365">
-        <v>6548</v>
+        <v>5417</v>
       </c>
       <c r="B365" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C365" t="s">
         <v>58</v>
@@ -26834,57 +26834,57 @@
         <v>64</v>
       </c>
       <c r="G365">
-        <v>5907</v>
+        <v>6348</v>
       </c>
       <c r="H365">
-        <v>5784</v>
+        <v>0</v>
       </c>
       <c r="I365" t="s">
         <v>69</v>
       </c>
       <c r="J365" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L365" s="1">
-        <v>46295</v>
+        <v>46288</v>
+      </c>
+      <c r="M365" t="s">
+        <v>210</v>
       </c>
       <c r="N365" t="s">
         <v>214</v>
       </c>
       <c r="O365">
-        <v>17222699</v>
+        <v>18274307</v>
       </c>
       <c r="P365" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q365" t="s">
         <v>247</v>
       </c>
       <c r="S365">
-        <v>-13</v>
+        <v>-6</v>
       </c>
       <c r="T365" t="s">
-        <v>248</v>
-      </c>
-      <c r="V365" t="s">
-        <v>263</v>
+        <v>253</v>
+      </c>
+      <c r="W365" t="s">
+        <v>355</v>
       </c>
       <c r="AA365">
         <v>0</v>
       </c>
       <c r="AG365" t="s">
-        <v>425</v>
-      </c>
-      <c r="AH365" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
     </row>
     <row r="366" spans="1:34">
       <c r="A366">
-        <v>5417</v>
+        <v>6949</v>
       </c>
       <c r="B366" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C366" t="s">
         <v>58</v>
@@ -26896,7 +26896,7 @@
         <v>62</v>
       </c>
       <c r="F366" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G366">
         <v>6348</v>
@@ -26914,16 +26914,16 @@
         <v>46288</v>
       </c>
       <c r="M366" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N366" t="s">
         <v>214</v>
       </c>
       <c r="O366">
-        <v>18274307</v>
+        <v>18275979</v>
       </c>
       <c r="P366" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q366" t="s">
         <v>247</v>
@@ -26932,10 +26932,10 @@
         <v>-6</v>
       </c>
       <c r="T366" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="W366" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AA366">
         <v>0</v>
@@ -26943,13 +26943,16 @@
       <c r="AG366" t="s">
         <v>426</v>
       </c>
+      <c r="AH366" t="s">
+        <v>433</v>
+      </c>
     </row>
     <row r="367" spans="1:34">
       <c r="A367">
-        <v>6949</v>
+        <v>6548</v>
       </c>
       <c r="B367" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C367" t="s">
         <v>58</v>
@@ -26961,63 +26964,60 @@
         <v>62</v>
       </c>
       <c r="F367" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G367">
-        <v>6348</v>
+        <v>1913</v>
       </c>
       <c r="H367">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="I367" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J367" t="s">
-        <v>90</v>
+        <v>143</v>
       </c>
       <c r="L367" s="1">
-        <v>46288</v>
-      </c>
-      <c r="M367" t="s">
-        <v>211</v>
+        <v>46286</v>
       </c>
       <c r="N367" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O367">
-        <v>18275979</v>
+        <v>17988579</v>
       </c>
       <c r="P367" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="Q367" t="s">
         <v>247</v>
       </c>
       <c r="S367">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="T367" t="s">
-        <v>251</v>
-      </c>
-      <c r="W367" t="s">
-        <v>356</v>
+        <v>248</v>
+      </c>
+      <c r="V367" t="s">
+        <v>263</v>
       </c>
       <c r="AA367">
         <v>0</v>
       </c>
       <c r="AG367" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AH367" t="s">
-        <v>433</v>
+        <v>419</v>
       </c>
     </row>
     <row r="368" spans="1:34">
       <c r="A368">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B368" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C368" t="s">
         <v>58</v>
@@ -27026,7 +27026,7 @@
         <v>59</v>
       </c>
       <c r="E368" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F368" t="s">
         <v>64</v>
@@ -27050,10 +27050,10 @@
         <v>213</v>
       </c>
       <c r="O368">
-        <v>17988579</v>
+        <v>18048433</v>
       </c>
       <c r="P368" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q368" t="s">
         <v>247</v>
@@ -27062,7 +27062,7 @@
         <v>-4</v>
       </c>
       <c r="T368" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="V368" t="s">
         <v>263</v>
@@ -27073,16 +27073,13 @@
       <c r="AG368" t="s">
         <v>425</v>
       </c>
-      <c r="AH368" t="s">
-        <v>419</v>
-      </c>
     </row>
     <row r="369" spans="1:34">
       <c r="A369">
-        <v>6627</v>
+        <v>6949</v>
       </c>
       <c r="B369" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C369" t="s">
         <v>58</v>
@@ -27091,10 +27088,10 @@
         <v>59</v>
       </c>
       <c r="E369" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F369" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G369">
         <v>1913</v>
@@ -27115,10 +27112,10 @@
         <v>213</v>
       </c>
       <c r="O369">
-        <v>18048433</v>
+        <v>18214877</v>
       </c>
       <c r="P369" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q369" t="s">
         <v>247</v>
@@ -27127,10 +27124,7 @@
         <v>-4</v>
       </c>
       <c r="T369" t="s">
-        <v>249</v>
-      </c>
-      <c r="V369" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="AA369">
         <v>0</v>
@@ -27138,19 +27132,22 @@
       <c r="AG369" t="s">
         <v>425</v>
       </c>
+      <c r="AH369" t="s">
+        <v>419</v>
+      </c>
     </row>
     <row r="370" spans="1:34">
       <c r="A370">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B370" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C370" t="s">
         <v>58</v>
       </c>
       <c r="D370" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E370" t="s">
         <v>62</v>
@@ -27159,37 +27156,43 @@
         <v>65</v>
       </c>
       <c r="G370">
-        <v>1913</v>
+        <v>11617</v>
       </c>
       <c r="H370">
-        <v>1862</v>
+        <v>0</v>
       </c>
       <c r="I370" t="s">
         <v>70</v>
       </c>
       <c r="J370" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L370" s="1">
-        <v>46286</v>
+        <v>46283</v>
+      </c>
+      <c r="M370" t="s">
+        <v>209</v>
       </c>
       <c r="N370" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="O370">
-        <v>18214877</v>
+        <v>18186565</v>
       </c>
       <c r="P370" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="Q370" t="s">
         <v>247</v>
       </c>
       <c r="S370">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="T370" t="s">
-        <v>251</v>
+        <v>252</v>
+      </c>
+      <c r="W370" t="s">
+        <v>357</v>
       </c>
       <c r="AA370">
         <v>0</v>
@@ -27203,10 +27206,10 @@
     </row>
     <row r="371" spans="1:34">
       <c r="A371">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B371" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C371" t="s">
         <v>58</v>
@@ -27242,7 +27245,7 @@
         <v>215</v>
       </c>
       <c r="O371">
-        <v>18186565</v>
+        <v>18186566</v>
       </c>
       <c r="P371" t="s">
         <v>242</v>
@@ -27271,16 +27274,16 @@
     </row>
     <row r="372" spans="1:34">
       <c r="A372">
-        <v>6963</v>
+        <v>6945</v>
       </c>
       <c r="B372" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C372" t="s">
         <v>58</v>
       </c>
       <c r="D372" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E372" t="s">
         <v>62</v>
@@ -27289,7 +27292,7 @@
         <v>65</v>
       </c>
       <c r="G372">
-        <v>11617</v>
+        <v>5764</v>
       </c>
       <c r="H372">
         <v>0</v>
@@ -27298,66 +27301,57 @@
         <v>70</v>
       </c>
       <c r="J372" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L372" s="1">
-        <v>46283</v>
-      </c>
-      <c r="M372" t="s">
-        <v>209</v>
+        <v>46290</v>
       </c>
       <c r="N372" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="O372">
-        <v>18186566</v>
+        <v>18220203</v>
       </c>
       <c r="P372" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="Q372" t="s">
         <v>247</v>
       </c>
       <c r="S372">
-        <v>-1</v>
+        <v>-8</v>
       </c>
       <c r="T372" t="s">
-        <v>252</v>
-      </c>
-      <c r="W372" t="s">
-        <v>357</v>
+        <v>250</v>
       </c>
       <c r="AA372">
         <v>0</v>
       </c>
       <c r="AG372" t="s">
-        <v>425</v>
-      </c>
-      <c r="AH372" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
     </row>
     <row r="373" spans="1:34">
       <c r="A373">
-        <v>6945</v>
+        <v>6548</v>
       </c>
       <c r="B373" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C373" t="s">
         <v>58</v>
       </c>
       <c r="D373" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E373" t="s">
         <v>62</v>
       </c>
       <c r="F373" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G373">
-        <v>5764</v>
+        <v>1876</v>
       </c>
       <c r="H373">
         <v>0</v>
@@ -27366,42 +27360,54 @@
         <v>70</v>
       </c>
       <c r="J373" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L373" s="1">
-        <v>46290</v>
+        <v>46283</v>
+      </c>
+      <c r="M373" t="s">
+        <v>209</v>
       </c>
       <c r="N373" t="s">
         <v>213</v>
       </c>
       <c r="O373">
-        <v>18220203</v>
+        <v>17988555</v>
       </c>
       <c r="P373" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q373" t="s">
         <v>247</v>
       </c>
       <c r="S373">
-        <v>-8</v>
+        <v>-1</v>
       </c>
       <c r="T373" t="s">
-        <v>250</v>
+        <v>248</v>
+      </c>
+      <c r="V373" t="s">
+        <v>263</v>
+      </c>
+      <c r="W373" t="s">
+        <v>358</v>
       </c>
       <c r="AA373">
         <v>0</v>
       </c>
       <c r="AG373" t="s">
-        <v>427</v>
+        <v>426</v>
+      </c>
+      <c r="AH373" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="374" spans="1:34">
       <c r="A374">
-        <v>6548</v>
+        <v>6949</v>
       </c>
       <c r="B374" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C374" t="s">
         <v>58</v>
@@ -27413,7 +27419,7 @@
         <v>62</v>
       </c>
       <c r="F374" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G374">
         <v>1876</v>
@@ -27437,10 +27443,10 @@
         <v>213</v>
       </c>
       <c r="O374">
-        <v>17988555</v>
+        <v>18214865</v>
       </c>
       <c r="P374" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q374" t="s">
         <v>247</v>
@@ -27449,10 +27455,7 @@
         <v>-1</v>
       </c>
       <c r="T374" t="s">
-        <v>248</v>
-      </c>
-      <c r="V374" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="W374" t="s">
         <v>358</v>
@@ -27469,10 +27472,10 @@
     </row>
     <row r="375" spans="1:34">
       <c r="A375">
-        <v>6949</v>
+        <v>6627</v>
       </c>
       <c r="B375" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C375" t="s">
         <v>58</v>
@@ -27481,13 +27484,13 @@
         <v>59</v>
       </c>
       <c r="E375" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F375" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G375">
-        <v>1876</v>
+        <v>11411</v>
       </c>
       <c r="H375">
         <v>0</v>
@@ -27496,7 +27499,7 @@
         <v>70</v>
       </c>
       <c r="J375" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L375" s="1">
         <v>46283</v>
@@ -27508,10 +27511,10 @@
         <v>213</v>
       </c>
       <c r="O375">
-        <v>18214865</v>
+        <v>18048483</v>
       </c>
       <c r="P375" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="Q375" t="s">
         <v>247</v>
@@ -27520,7 +27523,10 @@
         <v>-1</v>
       </c>
       <c r="T375" t="s">
-        <v>251</v>
+        <v>249</v>
+      </c>
+      <c r="V375" t="s">
+        <v>263</v>
       </c>
       <c r="W375" t="s">
         <v>358</v>
@@ -27531,16 +27537,13 @@
       <c r="AG375" t="s">
         <v>426</v>
       </c>
-      <c r="AH375" t="s">
-        <v>419</v>
-      </c>
     </row>
     <row r="376" spans="1:34">
       <c r="A376">
-        <v>6627</v>
+        <v>6949</v>
       </c>
       <c r="B376" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C376" t="s">
         <v>58</v>
@@ -27549,10 +27552,10 @@
         <v>59</v>
       </c>
       <c r="E376" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F376" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G376">
         <v>11411</v>
@@ -27576,10 +27579,10 @@
         <v>213</v>
       </c>
       <c r="O376">
-        <v>18048483</v>
+        <v>18214925</v>
       </c>
       <c r="P376" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q376" t="s">
         <v>247</v>
@@ -27588,10 +27591,7 @@
         <v>-1</v>
       </c>
       <c r="T376" t="s">
-        <v>249</v>
-      </c>
-      <c r="V376" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="W376" t="s">
         <v>358</v>
@@ -27602,19 +27602,22 @@
       <c r="AG376" t="s">
         <v>426</v>
       </c>
+      <c r="AH376" t="s">
+        <v>419</v>
+      </c>
     </row>
     <row r="377" spans="1:34">
       <c r="A377">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B377" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C377" t="s">
         <v>58</v>
       </c>
       <c r="D377" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E377" t="s">
         <v>62</v>
@@ -27623,7 +27626,7 @@
         <v>65</v>
       </c>
       <c r="G377">
-        <v>11411</v>
+        <v>1877</v>
       </c>
       <c r="H377">
         <v>0</v>
@@ -27632,34 +27635,28 @@
         <v>70</v>
       </c>
       <c r="J377" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L377" s="1">
-        <v>46283</v>
-      </c>
-      <c r="M377" t="s">
-        <v>209</v>
+        <v>46293</v>
       </c>
       <c r="N377" t="s">
         <v>213</v>
       </c>
       <c r="O377">
-        <v>18214925</v>
+        <v>18220188</v>
       </c>
       <c r="P377" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="Q377" t="s">
         <v>247</v>
       </c>
       <c r="S377">
-        <v>-1</v>
+        <v>-11</v>
       </c>
       <c r="T377" t="s">
-        <v>251</v>
-      </c>
-      <c r="W377" t="s">
-        <v>358</v>
+        <v>250</v>
       </c>
       <c r="AA377">
         <v>0</v>
@@ -27667,16 +27664,13 @@
       <c r="AG377" t="s">
         <v>426</v>
       </c>
-      <c r="AH377" t="s">
-        <v>419</v>
-      </c>
     </row>
     <row r="378" spans="1:34">
       <c r="A378">
-        <v>6945</v>
+        <v>6628</v>
       </c>
       <c r="B378" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C378" t="s">
         <v>58</v>
@@ -27685,13 +27679,13 @@
         <v>60</v>
       </c>
       <c r="E378" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F378" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G378">
-        <v>1877</v>
+        <v>1879</v>
       </c>
       <c r="H378">
         <v>0</v>
@@ -27700,28 +27694,37 @@
         <v>70</v>
       </c>
       <c r="J378" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L378" s="1">
-        <v>46293</v>
+        <v>46283</v>
+      </c>
+      <c r="M378" t="s">
+        <v>209</v>
       </c>
       <c r="N378" t="s">
         <v>213</v>
       </c>
       <c r="O378">
-        <v>18220188</v>
+        <v>17988684</v>
       </c>
       <c r="P378" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q378" t="s">
         <v>247</v>
       </c>
       <c r="S378">
-        <v>-11</v>
+        <v>-1</v>
       </c>
       <c r="T378" t="s">
-        <v>250</v>
+        <v>249</v>
+      </c>
+      <c r="V378" t="s">
+        <v>263</v>
+      </c>
+      <c r="W378" t="s">
+        <v>358</v>
       </c>
       <c r="AA378">
         <v>0</v>
@@ -27729,13 +27732,16 @@
       <c r="AG378" t="s">
         <v>426</v>
       </c>
+      <c r="AH378" t="s">
+        <v>419</v>
+      </c>
     </row>
     <row r="379" spans="1:34">
       <c r="A379">
-        <v>6628</v>
+        <v>6945</v>
       </c>
       <c r="B379" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C379" t="s">
         <v>58</v>
@@ -27744,10 +27750,10 @@
         <v>60</v>
       </c>
       <c r="E379" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F379" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G379">
         <v>1879</v>
@@ -27771,10 +27777,10 @@
         <v>213</v>
       </c>
       <c r="O379">
-        <v>17988684</v>
+        <v>18220194</v>
       </c>
       <c r="P379" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="Q379" t="s">
         <v>247</v>
@@ -27783,10 +27789,7 @@
         <v>-1</v>
       </c>
       <c r="T379" t="s">
-        <v>249</v>
-      </c>
-      <c r="V379" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="W379" t="s">
         <v>358</v>
@@ -27797,22 +27800,19 @@
       <c r="AG379" t="s">
         <v>426</v>
       </c>
-      <c r="AH379" t="s">
-        <v>419</v>
-      </c>
     </row>
     <row r="380" spans="1:34">
       <c r="A380">
-        <v>6945</v>
+        <v>6962</v>
       </c>
       <c r="B380" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C380" t="s">
         <v>58</v>
       </c>
       <c r="D380" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E380" t="s">
         <v>62</v>
@@ -27821,7 +27821,7 @@
         <v>65</v>
       </c>
       <c r="G380">
-        <v>1879</v>
+        <v>1881</v>
       </c>
       <c r="H380">
         <v>0</v>
@@ -27830,34 +27830,28 @@
         <v>70</v>
       </c>
       <c r="J380" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L380" s="1">
-        <v>46283</v>
-      </c>
-      <c r="M380" t="s">
-        <v>209</v>
+        <v>46287</v>
       </c>
       <c r="N380" t="s">
         <v>213</v>
       </c>
       <c r="O380">
-        <v>18220194</v>
+        <v>18260044</v>
       </c>
       <c r="P380" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q380" t="s">
         <v>247</v>
       </c>
       <c r="S380">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="T380" t="s">
-        <v>250</v>
-      </c>
-      <c r="W380" t="s">
-        <v>358</v>
+        <v>252</v>
       </c>
       <c r="AA380">
         <v>0</v>
@@ -27865,13 +27859,16 @@
       <c r="AG380" t="s">
         <v>426</v>
       </c>
+      <c r="AH380" t="s">
+        <v>419</v>
+      </c>
     </row>
     <row r="381" spans="1:34">
       <c r="A381">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B381" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C381" t="s">
         <v>58</v>
@@ -27904,7 +27901,7 @@
         <v>213</v>
       </c>
       <c r="O381">
-        <v>18260044</v>
+        <v>18260177</v>
       </c>
       <c r="P381" t="s">
         <v>236</v>
@@ -27930,25 +27927,25 @@
     </row>
     <row r="382" spans="1:34">
       <c r="A382">
-        <v>6963</v>
+        <v>6548</v>
       </c>
       <c r="B382" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C382" t="s">
         <v>58</v>
       </c>
       <c r="D382" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E382" t="s">
         <v>62</v>
       </c>
       <c r="F382" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G382">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="H382">
         <v>0</v>
@@ -27957,7 +27954,7 @@
         <v>70</v>
       </c>
       <c r="J382" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L382" s="1">
         <v>46287</v>
@@ -27966,10 +27963,10 @@
         <v>213</v>
       </c>
       <c r="O382">
-        <v>18260177</v>
+        <v>17988567</v>
       </c>
       <c r="P382" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="Q382" t="s">
         <v>247</v>
@@ -27978,7 +27975,10 @@
         <v>-5</v>
       </c>
       <c r="T382" t="s">
-        <v>252</v>
+        <v>248</v>
+      </c>
+      <c r="V382" t="s">
+        <v>263</v>
       </c>
       <c r="AA382">
         <v>0</v>
@@ -27992,10 +27992,10 @@
     </row>
     <row r="383" spans="1:34">
       <c r="A383">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B383" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C383" t="s">
         <v>58</v>
@@ -28004,7 +28004,7 @@
         <v>59</v>
       </c>
       <c r="E383" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F383" t="s">
         <v>64</v>
@@ -28028,10 +28028,10 @@
         <v>213</v>
       </c>
       <c r="O383">
-        <v>17988567</v>
+        <v>17968390</v>
       </c>
       <c r="P383" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q383" t="s">
         <v>247</v>
@@ -28040,7 +28040,7 @@
         <v>-5</v>
       </c>
       <c r="T383" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="V383" t="s">
         <v>263</v>
@@ -28051,16 +28051,13 @@
       <c r="AG383" t="s">
         <v>426</v>
       </c>
-      <c r="AH383" t="s">
-        <v>419</v>
-      </c>
     </row>
     <row r="384" spans="1:34">
       <c r="A384">
-        <v>6627</v>
+        <v>6949</v>
       </c>
       <c r="B384" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C384" t="s">
         <v>58</v>
@@ -28069,10 +28066,10 @@
         <v>59</v>
       </c>
       <c r="E384" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F384" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G384">
         <v>1882</v>
@@ -28093,10 +28090,10 @@
         <v>213</v>
       </c>
       <c r="O384">
-        <v>17968390</v>
+        <v>18214871</v>
       </c>
       <c r="P384" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q384" t="s">
         <v>247</v>
@@ -28105,10 +28102,7 @@
         <v>-5</v>
       </c>
       <c r="T384" t="s">
-        <v>249</v>
-      </c>
-      <c r="V384" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="AA384">
         <v>0</v>
@@ -28116,13 +28110,16 @@
       <c r="AG384" t="s">
         <v>426</v>
       </c>
+      <c r="AH384" t="s">
+        <v>419</v>
+      </c>
     </row>
     <row r="385" spans="1:34">
       <c r="A385">
-        <v>6949</v>
+        <v>6548</v>
       </c>
       <c r="B385" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C385" t="s">
         <v>58</v>
@@ -28134,10 +28131,10 @@
         <v>62</v>
       </c>
       <c r="F385" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G385">
-        <v>1882</v>
+        <v>7026</v>
       </c>
       <c r="H385">
         <v>0</v>
@@ -28146,34 +28143,37 @@
         <v>70</v>
       </c>
       <c r="J385" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L385" s="1">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="N385" t="s">
         <v>213</v>
       </c>
       <c r="O385">
-        <v>18214871</v>
+        <v>18094899</v>
       </c>
       <c r="P385" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="Q385" t="s">
         <v>247</v>
       </c>
       <c r="S385">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="T385" t="s">
-        <v>251</v>
+        <v>248</v>
+      </c>
+      <c r="V385" t="s">
+        <v>263</v>
       </c>
       <c r="AA385">
         <v>0</v>
       </c>
       <c r="AG385" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AH385" t="s">
         <v>419</v>
@@ -28181,10 +28181,10 @@
     </row>
     <row r="386" spans="1:34">
       <c r="A386">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B386" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C386" t="s">
         <v>58</v>
@@ -28193,7 +28193,7 @@
         <v>59</v>
       </c>
       <c r="E386" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F386" t="s">
         <v>64</v>
@@ -28217,10 +28217,10 @@
         <v>213</v>
       </c>
       <c r="O386">
-        <v>18094899</v>
+        <v>18048473</v>
       </c>
       <c r="P386" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q386" t="s">
         <v>247</v>
@@ -28229,7 +28229,7 @@
         <v>-6</v>
       </c>
       <c r="T386" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="V386" t="s">
         <v>263</v>
@@ -28240,16 +28240,13 @@
       <c r="AG386" t="s">
         <v>425</v>
       </c>
-      <c r="AH386" t="s">
-        <v>419</v>
-      </c>
     </row>
     <row r="387" spans="1:34">
       <c r="A387">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B387" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C387" t="s">
         <v>58</v>
@@ -28258,43 +28255,43 @@
         <v>59</v>
       </c>
       <c r="E387" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F387" t="s">
         <v>64</v>
       </c>
       <c r="G387">
-        <v>7026</v>
+        <v>1914</v>
       </c>
       <c r="H387">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="I387" t="s">
         <v>70</v>
       </c>
       <c r="J387" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L387" s="1">
-        <v>46288</v>
+        <v>46286</v>
       </c>
       <c r="N387" t="s">
         <v>213</v>
       </c>
       <c r="O387">
-        <v>18048473</v>
+        <v>17988591</v>
       </c>
       <c r="P387" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q387" t="s">
         <v>247</v>
       </c>
       <c r="S387">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="T387" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="V387" t="s">
         <v>263</v>
@@ -28305,13 +28302,16 @@
       <c r="AG387" t="s">
         <v>425</v>
       </c>
+      <c r="AH387" t="s">
+        <v>419</v>
+      </c>
     </row>
     <row r="388" spans="1:34">
       <c r="A388">
-        <v>6548</v>
+        <v>6949</v>
       </c>
       <c r="B388" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C388" t="s">
         <v>58</v>
@@ -28323,7 +28323,7 @@
         <v>62</v>
       </c>
       <c r="F388" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G388">
         <v>1914</v>
@@ -28344,10 +28344,10 @@
         <v>213</v>
       </c>
       <c r="O388">
-        <v>17988591</v>
+        <v>18214883</v>
       </c>
       <c r="P388" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q388" t="s">
         <v>247</v>
@@ -28356,10 +28356,7 @@
         <v>-4</v>
       </c>
       <c r="T388" t="s">
-        <v>248</v>
-      </c>
-      <c r="V388" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="AA388">
         <v>0</v>
@@ -28373,10 +28370,10 @@
     </row>
     <row r="389" spans="1:34">
       <c r="A389">
-        <v>6949</v>
+        <v>5417</v>
       </c>
       <c r="B389" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C389" t="s">
         <v>58</v>
@@ -28388,40 +28385,40 @@
         <v>62</v>
       </c>
       <c r="F389" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G389">
-        <v>1914</v>
+        <v>6759</v>
       </c>
       <c r="H389">
-        <v>1862</v>
+        <v>1788</v>
       </c>
       <c r="I389" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J389" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L389" s="1">
-        <v>46286</v>
+        <v>46289</v>
       </c>
       <c r="N389" t="s">
         <v>213</v>
       </c>
       <c r="O389">
-        <v>18214883</v>
+        <v>17399190</v>
       </c>
       <c r="P389" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q389" t="s">
         <v>247</v>
       </c>
       <c r="S389">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="T389" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AA389">
         <v>0</v>
@@ -28430,15 +28427,15 @@
         <v>425</v>
       </c>
       <c r="AH389" t="s">
-        <v>419</v>
+        <v>434</v>
       </c>
     </row>
     <row r="390" spans="1:34">
       <c r="A390">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B390" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C390" t="s">
         <v>58</v>
@@ -28471,7 +28468,7 @@
         <v>213</v>
       </c>
       <c r="O390">
-        <v>17399190</v>
+        <v>16976177</v>
       </c>
       <c r="P390" t="s">
         <v>237</v>
@@ -28483,7 +28480,10 @@
         <v>-7</v>
       </c>
       <c r="T390" t="s">
-        <v>253</v>
+        <v>255</v>
+      </c>
+      <c r="V390" t="s">
+        <v>263</v>
       </c>
       <c r="AA390">
         <v>0</v>
@@ -28497,16 +28497,16 @@
     </row>
     <row r="391" spans="1:34">
       <c r="A391">
-        <v>6486</v>
+        <v>6705</v>
       </c>
       <c r="B391" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C391" t="s">
         <v>58</v>
       </c>
       <c r="D391" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E391" t="s">
         <v>62</v>
@@ -28533,7 +28533,7 @@
         <v>213</v>
       </c>
       <c r="O391">
-        <v>16976177</v>
+        <v>17949019</v>
       </c>
       <c r="P391" t="s">
         <v>237</v>
@@ -28545,10 +28545,7 @@
         <v>-7</v>
       </c>
       <c r="T391" t="s">
-        <v>255</v>
-      </c>
-      <c r="V391" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="AA391">
         <v>0</v>
@@ -28562,16 +28559,16 @@
     </row>
     <row r="392" spans="1:34">
       <c r="A392">
-        <v>6705</v>
+        <v>6703</v>
       </c>
       <c r="B392" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C392" t="s">
         <v>58</v>
       </c>
       <c r="D392" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E392" t="s">
         <v>62</v>
@@ -28580,25 +28577,28 @@
         <v>64</v>
       </c>
       <c r="G392">
-        <v>6759</v>
+        <v>1802</v>
       </c>
       <c r="H392">
-        <v>1788</v>
+        <v>0</v>
       </c>
       <c r="I392" t="s">
         <v>71</v>
       </c>
       <c r="J392" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="L392" s="1">
-        <v>46289</v>
+        <v>46283</v>
+      </c>
+      <c r="M392" t="s">
+        <v>209</v>
       </c>
       <c r="N392" t="s">
         <v>213</v>
       </c>
       <c r="O392">
-        <v>17949019</v>
+        <v>17948796</v>
       </c>
       <c r="P392" t="s">
         <v>237</v>
@@ -28607,16 +28607,19 @@
         <v>247</v>
       </c>
       <c r="S392">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="T392" t="s">
-        <v>254</v>
+        <v>256</v>
+      </c>
+      <c r="W392" t="s">
+        <v>359</v>
       </c>
       <c r="AA392">
         <v>0</v>
       </c>
       <c r="AG392" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AH392" t="s">
         <v>434</v>
@@ -28624,16 +28627,16 @@
     </row>
     <row r="393" spans="1:34">
       <c r="A393">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B393" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C393" t="s">
         <v>58</v>
       </c>
       <c r="D393" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E393" t="s">
         <v>62</v>
@@ -28663,7 +28666,7 @@
         <v>213</v>
       </c>
       <c r="O393">
-        <v>17948796</v>
+        <v>18085198</v>
       </c>
       <c r="P393" t="s">
         <v>237</v>
@@ -28675,7 +28678,10 @@
         <v>-1</v>
       </c>
       <c r="T393" t="s">
-        <v>256</v>
+        <v>254</v>
+      </c>
+      <c r="V393" t="s">
+        <v>263</v>
       </c>
       <c r="W393" t="s">
         <v>359</v>
@@ -28692,10 +28698,10 @@
     </row>
     <row r="394" spans="1:34">
       <c r="A394">
-        <v>6704</v>
+        <v>5417</v>
       </c>
       <c r="B394" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C394" t="s">
         <v>58</v>
@@ -28710,7 +28716,7 @@
         <v>64</v>
       </c>
       <c r="G394">
-        <v>1802</v>
+        <v>11286</v>
       </c>
       <c r="H394">
         <v>0</v>
@@ -28719,7 +28725,7 @@
         <v>71</v>
       </c>
       <c r="J394" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L394" s="1">
         <v>46283</v>
@@ -28731,7 +28737,7 @@
         <v>213</v>
       </c>
       <c r="O394">
-        <v>18085198</v>
+        <v>17399434</v>
       </c>
       <c r="P394" t="s">
         <v>237</v>
@@ -28743,10 +28749,7 @@
         <v>-1</v>
       </c>
       <c r="T394" t="s">
-        <v>254</v>
-      </c>
-      <c r="V394" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="W394" t="s">
         <v>359</v>
@@ -28763,16 +28766,16 @@
     </row>
     <row r="395" spans="1:34">
       <c r="A395">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B395" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C395" t="s">
         <v>58</v>
       </c>
       <c r="D395" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E395" t="s">
         <v>62</v>
@@ -28802,7 +28805,7 @@
         <v>213</v>
       </c>
       <c r="O395">
-        <v>17399434</v>
+        <v>16962464</v>
       </c>
       <c r="P395" t="s">
         <v>237</v>
@@ -28814,7 +28817,7 @@
         <v>-1</v>
       </c>
       <c r="T395" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="W395" t="s">
         <v>359</v>
@@ -28831,16 +28834,16 @@
     </row>
     <row r="396" spans="1:34">
       <c r="A396">
-        <v>6404</v>
+        <v>6705</v>
       </c>
       <c r="B396" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C396" t="s">
         <v>58</v>
       </c>
       <c r="D396" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E396" t="s">
         <v>62</v>
@@ -28849,7 +28852,7 @@
         <v>64</v>
       </c>
       <c r="G396">
-        <v>11286</v>
+        <v>1803</v>
       </c>
       <c r="H396">
         <v>0</v>
@@ -28858,19 +28861,16 @@
         <v>71</v>
       </c>
       <c r="J396" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L396" s="1">
-        <v>46283</v>
-      </c>
-      <c r="M396" t="s">
-        <v>209</v>
+        <v>46293</v>
       </c>
       <c r="N396" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="O396">
-        <v>16962464</v>
+        <v>17948937</v>
       </c>
       <c r="P396" t="s">
         <v>237</v>
@@ -28879,13 +28879,10 @@
         <v>247</v>
       </c>
       <c r="S396">
-        <v>-1</v>
+        <v>-11</v>
       </c>
       <c r="T396" t="s">
-        <v>257</v>
-      </c>
-      <c r="W396" t="s">
-        <v>359</v>
+        <v>254</v>
       </c>
       <c r="AA396">
         <v>0</v>
@@ -28917,7 +28914,7 @@
         <v>64</v>
       </c>
       <c r="G397">
-        <v>1803</v>
+        <v>1805</v>
       </c>
       <c r="H397">
         <v>0</v>
@@ -28926,16 +28923,19 @@
         <v>71</v>
       </c>
       <c r="J397" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L397" s="1">
-        <v>46293</v>
+        <v>46283</v>
+      </c>
+      <c r="M397" t="s">
+        <v>209</v>
       </c>
       <c r="N397" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="O397">
-        <v>17948937</v>
+        <v>17948948</v>
       </c>
       <c r="P397" t="s">
         <v>237</v>
@@ -28944,11 +28944,14 @@
         <v>247</v>
       </c>
       <c r="S397">
-        <v>-11</v>
+        <v>-1</v>
       </c>
       <c r="T397" t="s">
         <v>254</v>
       </c>
+      <c r="W397" t="s">
+        <v>359</v>
+      </c>
       <c r="AA397">
         <v>0</v>
       </c>
@@ -28961,10 +28964,10 @@
     </row>
     <row r="398" spans="1:34">
       <c r="A398">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B398" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C398" t="s">
         <v>58</v>
@@ -29000,7 +29003,7 @@
         <v>213</v>
       </c>
       <c r="O398">
-        <v>17948948</v>
+        <v>18084966</v>
       </c>
       <c r="P398" t="s">
         <v>237</v>
@@ -29014,6 +29017,9 @@
       <c r="T398" t="s">
         <v>254</v>
       </c>
+      <c r="V398" t="s">
+        <v>263</v>
+      </c>
       <c r="W398" t="s">
         <v>359</v>
       </c>
@@ -29029,16 +29035,16 @@
     </row>
     <row r="399" spans="1:34">
       <c r="A399">
-        <v>6779</v>
+        <v>6703</v>
       </c>
       <c r="B399" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C399" t="s">
         <v>58</v>
       </c>
       <c r="D399" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E399" t="s">
         <v>62</v>
@@ -29047,7 +29053,7 @@
         <v>64</v>
       </c>
       <c r="G399">
-        <v>1805</v>
+        <v>1811</v>
       </c>
       <c r="H399">
         <v>0</v>
@@ -29056,19 +29062,16 @@
         <v>71</v>
       </c>
       <c r="J399" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="L399" s="1">
-        <v>46283</v>
-      </c>
-      <c r="M399" t="s">
-        <v>209</v>
+        <v>46290</v>
       </c>
       <c r="N399" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="O399">
-        <v>18084966</v>
+        <v>17948816</v>
       </c>
       <c r="P399" t="s">
         <v>237</v>
@@ -29077,16 +29080,10 @@
         <v>247</v>
       </c>
       <c r="S399">
-        <v>-1</v>
+        <v>-8</v>
       </c>
       <c r="T399" t="s">
-        <v>254</v>
-      </c>
-      <c r="V399" t="s">
-        <v>263</v>
-      </c>
-      <c r="W399" t="s">
-        <v>359</v>
+        <v>256</v>
       </c>
       <c r="AA399">
         <v>0</v>
@@ -29100,10 +29097,10 @@
     </row>
     <row r="400" spans="1:34">
       <c r="A400">
-        <v>6703</v>
+        <v>6404</v>
       </c>
       <c r="B400" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C400" t="s">
         <v>58</v>
@@ -29118,7 +29115,7 @@
         <v>64</v>
       </c>
       <c r="G400">
-        <v>1811</v>
+        <v>1807</v>
       </c>
       <c r="H400">
         <v>0</v>
@@ -29127,16 +29124,16 @@
         <v>71</v>
       </c>
       <c r="J400" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="L400" s="1">
-        <v>46290</v>
+        <v>46287</v>
       </c>
       <c r="N400" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="O400">
-        <v>17948816</v>
+        <v>16962171</v>
       </c>
       <c r="P400" t="s">
         <v>237</v>
@@ -29145,10 +29142,10 @@
         <v>247</v>
       </c>
       <c r="S400">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="T400" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AA400">
         <v>0</v>
@@ -29162,10 +29159,10 @@
     </row>
     <row r="401" spans="1:34">
       <c r="A401">
-        <v>6404</v>
+        <v>6703</v>
       </c>
       <c r="B401" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C401" t="s">
         <v>58</v>
@@ -29198,7 +29195,7 @@
         <v>213</v>
       </c>
       <c r="O401">
-        <v>16962171</v>
+        <v>17948806</v>
       </c>
       <c r="P401" t="s">
         <v>237</v>
@@ -29210,7 +29207,7 @@
         <v>-5</v>
       </c>
       <c r="T401" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AA401">
         <v>0</v>
@@ -29224,16 +29221,16 @@
     </row>
     <row r="402" spans="1:34">
       <c r="A402">
-        <v>6703</v>
+        <v>5417</v>
       </c>
       <c r="B402" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C402" t="s">
         <v>58</v>
       </c>
       <c r="D402" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E402" t="s">
         <v>62</v>
@@ -29242,7 +29239,7 @@
         <v>64</v>
       </c>
       <c r="G402">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="H402">
         <v>0</v>
@@ -29251,7 +29248,7 @@
         <v>71</v>
       </c>
       <c r="J402" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L402" s="1">
         <v>46287</v>
@@ -29260,7 +29257,7 @@
         <v>213</v>
       </c>
       <c r="O402">
-        <v>17948806</v>
+        <v>17398965</v>
       </c>
       <c r="P402" t="s">
         <v>237</v>
@@ -29272,7 +29269,7 @@
         <v>-5</v>
       </c>
       <c r="T402" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="AA402">
         <v>0</v>
@@ -29286,10 +29283,10 @@
     </row>
     <row r="403" spans="1:34">
       <c r="A403">
-        <v>5417</v>
+        <v>6704</v>
       </c>
       <c r="B403" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C403" t="s">
         <v>58</v>
@@ -29322,7 +29319,7 @@
         <v>213</v>
       </c>
       <c r="O403">
-        <v>17398965</v>
+        <v>18085209</v>
       </c>
       <c r="P403" t="s">
         <v>237</v>
@@ -29334,7 +29331,10 @@
         <v>-5</v>
       </c>
       <c r="T403" t="s">
-        <v>253</v>
+        <v>254</v>
+      </c>
+      <c r="V403" t="s">
+        <v>263</v>
       </c>
       <c r="AA403">
         <v>0</v>
@@ -29348,10 +29348,10 @@
     </row>
     <row r="404" spans="1:34">
       <c r="A404">
-        <v>6704</v>
+        <v>5417</v>
       </c>
       <c r="B404" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C404" t="s">
         <v>58</v>
@@ -29366,7 +29366,7 @@
         <v>64</v>
       </c>
       <c r="G404">
-        <v>1808</v>
+        <v>7025</v>
       </c>
       <c r="H404">
         <v>0</v>
@@ -29375,16 +29375,16 @@
         <v>71</v>
       </c>
       <c r="J404" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L404" s="1">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="N404" t="s">
         <v>213</v>
       </c>
       <c r="O404">
-        <v>18085209</v>
+        <v>17399280</v>
       </c>
       <c r="P404" t="s">
         <v>237</v>
@@ -29393,19 +29393,19 @@
         <v>247</v>
       </c>
       <c r="S404">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="T404" t="s">
-        <v>254</v>
-      </c>
-      <c r="V404" t="s">
-        <v>263</v>
+        <v>253</v>
+      </c>
+      <c r="W404" t="s">
+        <v>360</v>
       </c>
       <c r="AA404">
         <v>0</v>
       </c>
       <c r="AG404" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AH404" t="s">
         <v>434</v>
@@ -29413,10 +29413,10 @@
     </row>
     <row r="405" spans="1:34">
       <c r="A405">
-        <v>5417</v>
+        <v>6627</v>
       </c>
       <c r="B405" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C405" t="s">
         <v>58</v>
@@ -29425,75 +29425,78 @@
         <v>59</v>
       </c>
       <c r="E405" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F405" t="s">
         <v>64</v>
       </c>
       <c r="G405">
-        <v>7025</v>
+        <v>946</v>
       </c>
       <c r="H405">
         <v>0</v>
       </c>
       <c r="I405" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J405" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="L405" s="1">
-        <v>46288</v>
+        <v>46283</v>
+      </c>
+      <c r="M405" t="s">
+        <v>209</v>
       </c>
       <c r="N405" t="s">
         <v>213</v>
       </c>
       <c r="O405">
-        <v>17399280</v>
+        <v>17042272</v>
       </c>
       <c r="P405" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q405" t="s">
         <v>247</v>
       </c>
       <c r="S405">
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="T405" t="s">
-        <v>253</v>
+        <v>249</v>
+      </c>
+      <c r="V405" t="s">
+        <v>263</v>
       </c>
       <c r="W405" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AA405">
         <v>0</v>
       </c>
       <c r="AG405" t="s">
-        <v>425</v>
-      </c>
-      <c r="AH405" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
     </row>
     <row r="406" spans="1:34">
       <c r="A406">
-        <v>6627</v>
+        <v>6945</v>
       </c>
       <c r="B406" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C406" t="s">
         <v>58</v>
       </c>
       <c r="D406" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E406" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F406" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G406">
         <v>946</v>
@@ -29517,7 +29520,7 @@
         <v>213</v>
       </c>
       <c r="O406">
-        <v>17042272</v>
+        <v>18164494</v>
       </c>
       <c r="P406" t="s">
         <v>238</v>
@@ -29529,10 +29532,7 @@
         <v>-1</v>
       </c>
       <c r="T406" t="s">
-        <v>249</v>
-      </c>
-      <c r="V406" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="W406" t="s">
         <v>359</v>
@@ -29546,10 +29546,10 @@
     </row>
     <row r="407" spans="1:34">
       <c r="A407">
-        <v>6945</v>
+        <v>6705</v>
       </c>
       <c r="B407" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C407" t="s">
         <v>58</v>
@@ -29561,10 +29561,10 @@
         <v>62</v>
       </c>
       <c r="F407" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G407">
-        <v>946</v>
+        <v>7022</v>
       </c>
       <c r="H407">
         <v>0</v>
@@ -29573,7 +29573,7 @@
         <v>72</v>
       </c>
       <c r="J407" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L407" s="1">
         <v>46283</v>
@@ -29585,7 +29585,7 @@
         <v>213</v>
       </c>
       <c r="O407">
-        <v>18164494</v>
+        <v>17952601</v>
       </c>
       <c r="P407" t="s">
         <v>238</v>
@@ -29597,7 +29597,7 @@
         <v>-1</v>
       </c>
       <c r="T407" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="W407" t="s">
         <v>359</v>
@@ -29611,16 +29611,16 @@
     </row>
     <row r="408" spans="1:34">
       <c r="A408">
-        <v>6705</v>
+        <v>5417</v>
       </c>
       <c r="B408" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C408" t="s">
         <v>58</v>
       </c>
       <c r="D408" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E408" t="s">
         <v>62</v>
@@ -29629,7 +29629,7 @@
         <v>64</v>
       </c>
       <c r="G408">
-        <v>7022</v>
+        <v>940</v>
       </c>
       <c r="H408">
         <v>0</v>
@@ -29638,7 +29638,7 @@
         <v>72</v>
       </c>
       <c r="J408" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L408" s="1">
         <v>46283</v>
@@ -29647,10 +29647,10 @@
         <v>209</v>
       </c>
       <c r="N408" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O408">
-        <v>17952601</v>
+        <v>17398840</v>
       </c>
       <c r="P408" t="s">
         <v>238</v>
@@ -29662,30 +29662,30 @@
         <v>-1</v>
       </c>
       <c r="T408" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="W408" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AA408">
         <v>0</v>
       </c>
       <c r="AG408" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="409" spans="1:34">
       <c r="A409">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B409" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C409" t="s">
         <v>58</v>
       </c>
       <c r="D409" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E409" t="s">
         <v>62</v>
@@ -29715,7 +29715,7 @@
         <v>214</v>
       </c>
       <c r="O409">
-        <v>17398840</v>
+        <v>16962074</v>
       </c>
       <c r="P409" t="s">
         <v>238</v>
@@ -29727,7 +29727,7 @@
         <v>-1</v>
       </c>
       <c r="T409" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="W409" t="s">
         <v>361</v>
@@ -29741,16 +29741,16 @@
     </row>
     <row r="410" spans="1:34">
       <c r="A410">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B410" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C410" t="s">
         <v>58</v>
       </c>
       <c r="D410" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E410" t="s">
         <v>62</v>
@@ -29780,7 +29780,7 @@
         <v>214</v>
       </c>
       <c r="O410">
-        <v>16962074</v>
+        <v>16975871</v>
       </c>
       <c r="P410" t="s">
         <v>238</v>
@@ -29792,7 +29792,10 @@
         <v>-1</v>
       </c>
       <c r="T410" t="s">
-        <v>257</v>
+        <v>255</v>
+      </c>
+      <c r="V410" t="s">
+        <v>263</v>
       </c>
       <c r="W410" t="s">
         <v>361</v>
@@ -29806,10 +29809,10 @@
     </row>
     <row r="411" spans="1:34">
       <c r="A411">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B411" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C411" t="s">
         <v>58</v>
@@ -29845,7 +29848,7 @@
         <v>214</v>
       </c>
       <c r="O411">
-        <v>16975871</v>
+        <v>17222366</v>
       </c>
       <c r="P411" t="s">
         <v>238</v>
@@ -29857,7 +29860,7 @@
         <v>-1</v>
       </c>
       <c r="T411" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="V411" t="s">
         <v>263</v>
@@ -29874,10 +29877,10 @@
     </row>
     <row r="412" spans="1:34">
       <c r="A412">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B412" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C412" t="s">
         <v>58</v>
@@ -29886,7 +29889,7 @@
         <v>59</v>
       </c>
       <c r="E412" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F412" t="s">
         <v>64</v>
@@ -29913,7 +29916,7 @@
         <v>214</v>
       </c>
       <c r="O412">
-        <v>17222366</v>
+        <v>17042221</v>
       </c>
       <c r="P412" t="s">
         <v>238</v>
@@ -29925,7 +29928,7 @@
         <v>-1</v>
       </c>
       <c r="T412" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="V412" t="s">
         <v>263</v>
@@ -29942,16 +29945,16 @@
     </row>
     <row r="413" spans="1:34">
       <c r="A413">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B413" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C413" t="s">
         <v>58</v>
       </c>
       <c r="D413" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E413" t="s">
         <v>63</v>
@@ -29981,7 +29984,7 @@
         <v>214</v>
       </c>
       <c r="O413">
-        <v>17042221</v>
+        <v>16959926</v>
       </c>
       <c r="P413" t="s">
         <v>238</v>
@@ -30010,19 +30013,19 @@
     </row>
     <row r="414" spans="1:34">
       <c r="A414">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B414" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C414" t="s">
         <v>58</v>
       </c>
       <c r="D414" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E414" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F414" t="s">
         <v>64</v>
@@ -30049,7 +30052,7 @@
         <v>214</v>
       </c>
       <c r="O414">
-        <v>16959926</v>
+        <v>17941112</v>
       </c>
       <c r="P414" t="s">
         <v>238</v>
@@ -30061,10 +30064,7 @@
         <v>-1</v>
       </c>
       <c r="T414" t="s">
-        <v>249</v>
-      </c>
-      <c r="V414" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="W414" t="s">
         <v>361</v>
@@ -30078,16 +30078,16 @@
     </row>
     <row r="415" spans="1:34">
       <c r="A415">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B415" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C415" t="s">
         <v>58</v>
       </c>
       <c r="D415" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E415" t="s">
         <v>62</v>
@@ -30117,7 +30117,7 @@
         <v>214</v>
       </c>
       <c r="O415">
-        <v>17941112</v>
+        <v>17952292</v>
       </c>
       <c r="P415" t="s">
         <v>238</v>
@@ -30129,7 +30129,10 @@
         <v>-1</v>
       </c>
       <c r="T415" t="s">
-        <v>256</v>
+        <v>254</v>
+      </c>
+      <c r="V415" t="s">
+        <v>263</v>
       </c>
       <c r="W415" t="s">
         <v>361</v>
@@ -30143,16 +30146,16 @@
     </row>
     <row r="416" spans="1:34">
       <c r="A416">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B416" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C416" t="s">
         <v>58</v>
       </c>
       <c r="D416" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E416" t="s">
         <v>62</v>
@@ -30182,7 +30185,7 @@
         <v>214</v>
       </c>
       <c r="O416">
-        <v>17952292</v>
+        <v>17952491</v>
       </c>
       <c r="P416" t="s">
         <v>238</v>
@@ -30196,9 +30199,6 @@
       <c r="T416" t="s">
         <v>254</v>
       </c>
-      <c r="V416" t="s">
-        <v>263</v>
-      </c>
       <c r="W416" t="s">
         <v>361</v>
       </c>
@@ -30211,10 +30211,10 @@
     </row>
     <row r="417" spans="1:33">
       <c r="A417">
-        <v>6705</v>
+        <v>6945</v>
       </c>
       <c r="B417" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C417" t="s">
         <v>58</v>
@@ -30226,7 +30226,7 @@
         <v>62</v>
       </c>
       <c r="F417" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G417">
         <v>940</v>
@@ -30250,7 +30250,7 @@
         <v>214</v>
       </c>
       <c r="O417">
-        <v>17952491</v>
+        <v>18164473</v>
       </c>
       <c r="P417" t="s">
         <v>238</v>
@@ -30262,10 +30262,10 @@
         <v>-1</v>
       </c>
       <c r="T417" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="W417" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AA417">
         <v>0</v>
@@ -30276,16 +30276,16 @@
     </row>
     <row r="418" spans="1:33">
       <c r="A418">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B418" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C418" t="s">
         <v>58</v>
       </c>
       <c r="D418" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E418" t="s">
         <v>62</v>
@@ -30315,7 +30315,7 @@
         <v>214</v>
       </c>
       <c r="O418">
-        <v>18164473</v>
+        <v>18178120</v>
       </c>
       <c r="P418" t="s">
         <v>238</v>
@@ -30327,7 +30327,7 @@
         <v>-1</v>
       </c>
       <c r="T418" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="W418" t="s">
         <v>362</v>
@@ -30341,10 +30341,10 @@
     </row>
     <row r="419" spans="1:33">
       <c r="A419">
-        <v>6949</v>
+        <v>5417</v>
       </c>
       <c r="B419" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C419" t="s">
         <v>58</v>
@@ -30356,10 +30356,10 @@
         <v>62</v>
       </c>
       <c r="F419" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G419">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="H419">
         <v>0</v>
@@ -30368,19 +30368,16 @@
         <v>72</v>
       </c>
       <c r="J419" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L419" s="1">
-        <v>46283</v>
-      </c>
-      <c r="M419" t="s">
-        <v>209</v>
+        <v>46295</v>
       </c>
       <c r="N419" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O419">
-        <v>18178120</v>
+        <v>17398859</v>
       </c>
       <c r="P419" t="s">
         <v>238</v>
@@ -30389,27 +30386,24 @@
         <v>247</v>
       </c>
       <c r="S419">
-        <v>-1</v>
+        <v>-13</v>
       </c>
       <c r="T419" t="s">
-        <v>251</v>
-      </c>
-      <c r="W419" t="s">
-        <v>362</v>
+        <v>253</v>
       </c>
       <c r="AA419">
         <v>0</v>
       </c>
       <c r="AG419" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="420" spans="1:33">
       <c r="A420">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B420" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C420" t="s">
         <v>58</v>
@@ -30442,7 +30436,7 @@
         <v>213</v>
       </c>
       <c r="O420">
-        <v>17398859</v>
+        <v>16975890</v>
       </c>
       <c r="P420" t="s">
         <v>238</v>
@@ -30454,7 +30448,10 @@
         <v>-13</v>
       </c>
       <c r="T420" t="s">
-        <v>253</v>
+        <v>255</v>
+      </c>
+      <c r="V420" t="s">
+        <v>263</v>
       </c>
       <c r="AA420">
         <v>0</v>
@@ -30465,16 +30462,16 @@
     </row>
     <row r="421" spans="1:33">
       <c r="A421">
-        <v>6486</v>
+        <v>6703</v>
       </c>
       <c r="B421" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C421" t="s">
         <v>58</v>
       </c>
       <c r="D421" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E421" t="s">
         <v>62</v>
@@ -30501,7 +30498,7 @@
         <v>213</v>
       </c>
       <c r="O421">
-        <v>16975890</v>
+        <v>17941122</v>
       </c>
       <c r="P421" t="s">
         <v>238</v>
@@ -30513,10 +30510,7 @@
         <v>-13</v>
       </c>
       <c r="T421" t="s">
-        <v>255</v>
-      </c>
-      <c r="V421" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="AA421">
         <v>0</v>
@@ -30527,16 +30521,16 @@
     </row>
     <row r="422" spans="1:33">
       <c r="A422">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B422" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C422" t="s">
         <v>58</v>
       </c>
       <c r="D422" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E422" t="s">
         <v>62</v>
@@ -30563,7 +30557,7 @@
         <v>213</v>
       </c>
       <c r="O422">
-        <v>17941122</v>
+        <v>17952314</v>
       </c>
       <c r="P422" t="s">
         <v>238</v>
@@ -30575,7 +30569,10 @@
         <v>-13</v>
       </c>
       <c r="T422" t="s">
-        <v>256</v>
+        <v>254</v>
+      </c>
+      <c r="V422" t="s">
+        <v>263</v>
       </c>
       <c r="AA422">
         <v>0</v>
@@ -30586,16 +30583,16 @@
     </row>
     <row r="423" spans="1:33">
       <c r="A423">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B423" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C423" t="s">
         <v>58</v>
       </c>
       <c r="D423" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E423" t="s">
         <v>62</v>
@@ -30622,7 +30619,7 @@
         <v>213</v>
       </c>
       <c r="O423">
-        <v>17952314</v>
+        <v>17952513</v>
       </c>
       <c r="P423" t="s">
         <v>238</v>
@@ -30636,9 +30633,6 @@
       <c r="T423" t="s">
         <v>254</v>
       </c>
-      <c r="V423" t="s">
-        <v>263</v>
-      </c>
       <c r="AA423">
         <v>0</v>
       </c>
@@ -30648,22 +30642,22 @@
     </row>
     <row r="424" spans="1:33">
       <c r="A424">
-        <v>6705</v>
+        <v>6949</v>
       </c>
       <c r="B424" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C424" t="s">
         <v>58</v>
       </c>
       <c r="D424" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E424" t="s">
         <v>62</v>
       </c>
       <c r="F424" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G424">
         <v>943</v>
@@ -30684,7 +30678,7 @@
         <v>213</v>
       </c>
       <c r="O424">
-        <v>17952513</v>
+        <v>18178126</v>
       </c>
       <c r="P424" t="s">
         <v>238</v>
@@ -30696,7 +30690,7 @@
         <v>-13</v>
       </c>
       <c r="T424" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="AA424">
         <v>0</v>
@@ -30707,16 +30701,16 @@
     </row>
     <row r="425" spans="1:33">
       <c r="A425">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B425" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C425" t="s">
         <v>58</v>
       </c>
       <c r="D425" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E425" t="s">
         <v>62</v>
@@ -30743,7 +30737,7 @@
         <v>213</v>
       </c>
       <c r="O425">
-        <v>18178126</v>
+        <v>18188710</v>
       </c>
       <c r="P425" t="s">
         <v>238</v>
@@ -30755,7 +30749,7 @@
         <v>-13</v>
       </c>
       <c r="T425" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AA425">
         <v>0</v>
@@ -30766,10 +30760,10 @@
     </row>
     <row r="426" spans="1:33">
       <c r="A426">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B426" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C426" t="s">
         <v>58</v>
@@ -30802,7 +30796,7 @@
         <v>213</v>
       </c>
       <c r="O426">
-        <v>18188710</v>
+        <v>18188616</v>
       </c>
       <c r="P426" t="s">
         <v>238</v>
@@ -30825,75 +30819,81 @@
     </row>
     <row r="427" spans="1:33">
       <c r="A427">
-        <v>6963</v>
+        <v>5417</v>
       </c>
       <c r="B427" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C427" t="s">
         <v>58</v>
       </c>
       <c r="D427" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E427" t="s">
         <v>62</v>
       </c>
       <c r="F427" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G427">
-        <v>943</v>
+        <v>6813</v>
       </c>
       <c r="H427">
         <v>0</v>
       </c>
       <c r="I427" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J427" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L427" s="1">
-        <v>46295</v>
+        <v>46283</v>
+      </c>
+      <c r="M427" t="s">
+        <v>209</v>
       </c>
       <c r="N427" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O427">
-        <v>18188616</v>
+        <v>17399241</v>
       </c>
       <c r="P427" t="s">
-        <v>238</v>
+        <v>62</v>
       </c>
       <c r="Q427" t="s">
         <v>247</v>
       </c>
       <c r="S427">
-        <v>-13</v>
+        <v>-1</v>
       </c>
       <c r="T427" t="s">
-        <v>252</v>
+        <v>253</v>
+      </c>
+      <c r="W427" t="s">
+        <v>362</v>
       </c>
       <c r="AA427">
         <v>0</v>
       </c>
       <c r="AG427" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="428" spans="1:33">
       <c r="A428">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B428" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C428" t="s">
         <v>58</v>
       </c>
       <c r="D428" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E428" t="s">
         <v>62</v>
@@ -30923,7 +30923,7 @@
         <v>214</v>
       </c>
       <c r="O428">
-        <v>17399241</v>
+        <v>16962319</v>
       </c>
       <c r="P428" t="s">
         <v>62</v>
@@ -30935,7 +30935,7 @@
         <v>-1</v>
       </c>
       <c r="T428" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="W428" t="s">
         <v>362</v>
@@ -30949,16 +30949,16 @@
     </row>
     <row r="429" spans="1:33">
       <c r="A429">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B429" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C429" t="s">
         <v>58</v>
       </c>
       <c r="D429" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E429" t="s">
         <v>62</v>
@@ -30988,7 +30988,7 @@
         <v>214</v>
       </c>
       <c r="O429">
-        <v>16962319</v>
+        <v>16976198</v>
       </c>
       <c r="P429" t="s">
         <v>62</v>
@@ -31000,7 +31000,10 @@
         <v>-1</v>
       </c>
       <c r="T429" t="s">
-        <v>257</v>
+        <v>255</v>
+      </c>
+      <c r="V429" t="s">
+        <v>263</v>
       </c>
       <c r="W429" t="s">
         <v>362</v>
@@ -31014,10 +31017,10 @@
     </row>
     <row r="430" spans="1:33">
       <c r="A430">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B430" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C430" t="s">
         <v>58</v>
@@ -31053,7 +31056,7 @@
         <v>214</v>
       </c>
       <c r="O430">
-        <v>16976198</v>
+        <v>17222763</v>
       </c>
       <c r="P430" t="s">
         <v>62</v>
@@ -31065,7 +31068,7 @@
         <v>-1</v>
       </c>
       <c r="T430" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="V430" t="s">
         <v>263</v>
@@ -31082,10 +31085,10 @@
     </row>
     <row r="431" spans="1:33">
       <c r="A431">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B431" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C431" t="s">
         <v>58</v>
@@ -31094,7 +31097,7 @@
         <v>59</v>
       </c>
       <c r="E431" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F431" t="s">
         <v>64</v>
@@ -31121,10 +31124,10 @@
         <v>214</v>
       </c>
       <c r="O431">
-        <v>17222763</v>
+        <v>17042469</v>
       </c>
       <c r="P431" t="s">
-        <v>62</v>
+        <v>239</v>
       </c>
       <c r="Q431" t="s">
         <v>247</v>
@@ -31133,7 +31136,7 @@
         <v>-1</v>
       </c>
       <c r="T431" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="V431" t="s">
         <v>263</v>
@@ -31150,16 +31153,16 @@
     </row>
     <row r="432" spans="1:33">
       <c r="A432">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B432" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C432" t="s">
         <v>58</v>
       </c>
       <c r="D432" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E432" t="s">
         <v>63</v>
@@ -31189,10 +31192,10 @@
         <v>214</v>
       </c>
       <c r="O432">
-        <v>17042469</v>
+        <v>16960013</v>
       </c>
       <c r="P432" t="s">
-        <v>239</v>
+        <v>63</v>
       </c>
       <c r="Q432" t="s">
         <v>247</v>
@@ -31218,19 +31221,19 @@
     </row>
     <row r="433" spans="1:34">
       <c r="A433">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B433" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C433" t="s">
         <v>58</v>
       </c>
       <c r="D433" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E433" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F433" t="s">
         <v>64</v>
@@ -31257,10 +31260,10 @@
         <v>214</v>
       </c>
       <c r="O433">
-        <v>16960013</v>
+        <v>17941197</v>
       </c>
       <c r="P433" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q433" t="s">
         <v>247</v>
@@ -31269,10 +31272,7 @@
         <v>-1</v>
       </c>
       <c r="T433" t="s">
-        <v>249</v>
-      </c>
-      <c r="V433" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="W433" t="s">
         <v>362</v>
@@ -31286,16 +31286,16 @@
     </row>
     <row r="434" spans="1:34">
       <c r="A434">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B434" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C434" t="s">
         <v>58</v>
       </c>
       <c r="D434" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E434" t="s">
         <v>62</v>
@@ -31325,7 +31325,7 @@
         <v>214</v>
       </c>
       <c r="O434">
-        <v>17941197</v>
+        <v>17952411</v>
       </c>
       <c r="P434" t="s">
         <v>62</v>
@@ -31337,7 +31337,10 @@
         <v>-1</v>
       </c>
       <c r="T434" t="s">
-        <v>256</v>
+        <v>254</v>
+      </c>
+      <c r="V434" t="s">
+        <v>263</v>
       </c>
       <c r="W434" t="s">
         <v>362</v>
@@ -31351,16 +31354,16 @@
     </row>
     <row r="435" spans="1:34">
       <c r="A435">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B435" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C435" t="s">
         <v>58</v>
       </c>
       <c r="D435" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E435" t="s">
         <v>62</v>
@@ -31390,7 +31393,7 @@
         <v>214</v>
       </c>
       <c r="O435">
-        <v>17952411</v>
+        <v>17952591</v>
       </c>
       <c r="P435" t="s">
         <v>62</v>
@@ -31404,9 +31407,6 @@
       <c r="T435" t="s">
         <v>254</v>
       </c>
-      <c r="V435" t="s">
-        <v>263</v>
-      </c>
       <c r="W435" t="s">
         <v>362</v>
       </c>
@@ -31419,10 +31419,10 @@
     </row>
     <row r="436" spans="1:34">
       <c r="A436">
-        <v>6705</v>
+        <v>6945</v>
       </c>
       <c r="B436" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C436" t="s">
         <v>58</v>
@@ -31434,7 +31434,7 @@
         <v>62</v>
       </c>
       <c r="F436" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G436">
         <v>6813</v>
@@ -31458,7 +31458,7 @@
         <v>214</v>
       </c>
       <c r="O436">
-        <v>17952591</v>
+        <v>18164530</v>
       </c>
       <c r="P436" t="s">
         <v>62</v>
@@ -31470,10 +31470,10 @@
         <v>-1</v>
       </c>
       <c r="T436" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="W436" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AA436">
         <v>0</v>
@@ -31484,16 +31484,16 @@
     </row>
     <row r="437" spans="1:34">
       <c r="A437">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B437" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C437" t="s">
         <v>58</v>
       </c>
       <c r="D437" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E437" t="s">
         <v>62</v>
@@ -31523,10 +31523,10 @@
         <v>214</v>
       </c>
       <c r="O437">
-        <v>18164530</v>
+        <v>18178169</v>
       </c>
       <c r="P437" t="s">
-        <v>62</v>
+        <v>239</v>
       </c>
       <c r="Q437" t="s">
         <v>247</v>
@@ -31535,7 +31535,7 @@
         <v>-1</v>
       </c>
       <c r="T437" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="W437" t="s">
         <v>363</v>
@@ -31549,25 +31549,25 @@
     </row>
     <row r="438" spans="1:34">
       <c r="A438">
-        <v>6949</v>
+        <v>6404</v>
       </c>
       <c r="B438" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C438" t="s">
         <v>58</v>
       </c>
       <c r="D438" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E438" t="s">
         <v>62</v>
       </c>
       <c r="F438" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G438">
-        <v>6813</v>
+        <v>7027</v>
       </c>
       <c r="H438">
         <v>0</v>
@@ -31576,54 +31576,51 @@
         <v>73</v>
       </c>
       <c r="J438" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="L438" s="1">
-        <v>46283</v>
-      </c>
-      <c r="M438" t="s">
-        <v>209</v>
+        <v>46289</v>
       </c>
       <c r="N438" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O438">
-        <v>18178169</v>
+        <v>16962348</v>
       </c>
       <c r="P438" t="s">
-        <v>239</v>
+        <v>62</v>
       </c>
       <c r="Q438" t="s">
         <v>247</v>
       </c>
       <c r="S438">
-        <v>-1</v>
+        <v>-7</v>
       </c>
       <c r="T438" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="W438" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AA438">
         <v>0</v>
       </c>
       <c r="AG438" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="439" spans="1:34">
       <c r="A439">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B439" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C439" t="s">
         <v>58</v>
       </c>
       <c r="D439" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E439" t="s">
         <v>62</v>
@@ -31632,40 +31629,40 @@
         <v>64</v>
       </c>
       <c r="G439">
-        <v>7027</v>
+        <v>11056</v>
       </c>
       <c r="H439">
         <v>0</v>
       </c>
       <c r="I439" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J439" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="L439" s="1">
-        <v>46289</v>
+        <v>46287</v>
       </c>
       <c r="N439" t="s">
         <v>213</v>
       </c>
       <c r="O439">
-        <v>16962348</v>
+        <v>18275526</v>
       </c>
       <c r="P439" t="s">
-        <v>62</v>
+        <v>243</v>
       </c>
       <c r="Q439" t="s">
         <v>247</v>
       </c>
       <c r="S439">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="T439" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="W439" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AA439">
         <v>0</v>
@@ -31676,22 +31673,22 @@
     </row>
     <row r="440" spans="1:34">
       <c r="A440">
-        <v>5417</v>
+        <v>6962</v>
       </c>
       <c r="B440" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C440" t="s">
         <v>58</v>
       </c>
       <c r="D440" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E440" t="s">
         <v>62</v>
       </c>
       <c r="F440" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G440">
         <v>11056</v>
@@ -31712,7 +31709,7 @@
         <v>213</v>
       </c>
       <c r="O440">
-        <v>18275526</v>
+        <v>18274091</v>
       </c>
       <c r="P440" t="s">
         <v>243</v>
@@ -31724,10 +31721,10 @@
         <v>-5</v>
       </c>
       <c r="T440" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="W440" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AA440">
         <v>0</v>
@@ -31738,72 +31735,81 @@
     </row>
     <row r="441" spans="1:34">
       <c r="A441">
-        <v>6962</v>
+        <v>6628</v>
       </c>
       <c r="B441" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C441" t="s">
         <v>58</v>
       </c>
       <c r="D441" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E441" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F441" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G441">
-        <v>11056</v>
+        <v>1650</v>
       </c>
       <c r="H441">
         <v>0</v>
       </c>
       <c r="I441" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="J441" t="s">
-        <v>129</v>
+        <v>161</v>
       </c>
       <c r="L441" s="1">
-        <v>46287</v>
+        <v>46293</v>
       </c>
       <c r="N441" t="s">
         <v>213</v>
       </c>
       <c r="O441">
-        <v>18274091</v>
+        <v>16959974</v>
       </c>
       <c r="P441" t="s">
-        <v>243</v>
+        <v>219</v>
       </c>
       <c r="Q441" t="s">
-        <v>247</v>
+        <v>245</v>
+      </c>
+      <c r="R441" s="1">
+        <v>46265.00248284722</v>
       </c>
       <c r="S441">
-        <v>-5</v>
+        <v>-11</v>
       </c>
       <c r="T441" t="s">
-        <v>252</v>
-      </c>
-      <c r="W441" t="s">
-        <v>366</v>
+        <v>249</v>
+      </c>
+      <c r="V441" t="s">
+        <v>263</v>
       </c>
       <c r="AA441">
         <v>0</v>
+      </c>
+      <c r="AB441" t="s">
+        <v>420</v>
       </c>
       <c r="AG441" t="s">
         <v>425</v>
       </c>
+      <c r="AH441" t="s">
+        <v>429</v>
+      </c>
     </row>
     <row r="442" spans="1:34">
       <c r="A442">
-        <v>6628</v>
+        <v>6945</v>
       </c>
       <c r="B442" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C442" t="s">
         <v>58</v>
@@ -31812,10 +31818,10 @@
         <v>60</v>
       </c>
       <c r="E442" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F442" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G442">
         <v>1650</v>
@@ -31836,25 +31842,22 @@
         <v>213</v>
       </c>
       <c r="O442">
-        <v>16959974</v>
+        <v>18163667</v>
       </c>
       <c r="P442" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q442" t="s">
         <v>245</v>
       </c>
       <c r="R442" s="1">
-        <v>46265.00248284722</v>
+        <v>46265.00255472222</v>
       </c>
       <c r="S442">
         <v>-11</v>
       </c>
       <c r="T442" t="s">
-        <v>249</v>
-      </c>
-      <c r="V442" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="AA442">
         <v>0</v>
@@ -31871,25 +31874,25 @@
     </row>
     <row r="443" spans="1:34">
       <c r="A443">
-        <v>6945</v>
+        <v>6548</v>
       </c>
       <c r="B443" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C443" t="s">
         <v>58</v>
       </c>
       <c r="D443" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E443" t="s">
         <v>62</v>
       </c>
       <c r="F443" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G443">
-        <v>1650</v>
+        <v>1652</v>
       </c>
       <c r="H443">
         <v>0</v>
@@ -31898,31 +31901,37 @@
         <v>67</v>
       </c>
       <c r="J443" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L443" s="1">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="N443" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="O443">
-        <v>18163667</v>
+        <v>17967989</v>
       </c>
       <c r="P443" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="Q443" t="s">
         <v>245</v>
       </c>
       <c r="R443" s="1">
-        <v>46265.00255472222</v>
+        <v>46234.66180127315</v>
       </c>
       <c r="S443">
-        <v>-11</v>
+        <v>-8</v>
       </c>
       <c r="T443" t="s">
-        <v>250</v>
+        <v>248</v>
+      </c>
+      <c r="V443" t="s">
+        <v>263</v>
+      </c>
+      <c r="W443" t="s">
+        <v>367</v>
       </c>
       <c r="AA443">
         <v>0</v>
@@ -31931,18 +31940,18 @@
         <v>420</v>
       </c>
       <c r="AG443" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AH443" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="444" spans="1:34">
       <c r="A444">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B444" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C444" t="s">
         <v>58</v>
@@ -31951,7 +31960,7 @@
         <v>59</v>
       </c>
       <c r="E444" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F444" t="s">
         <v>64</v>
@@ -31975,28 +31984,28 @@
         <v>215</v>
       </c>
       <c r="O444">
-        <v>17967989</v>
+        <v>17042389</v>
       </c>
       <c r="P444" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q444" t="s">
         <v>245</v>
       </c>
       <c r="R444" s="1">
-        <v>46234.66180127315</v>
+        <v>46245.76585582176</v>
       </c>
       <c r="S444">
         <v>-8</v>
       </c>
       <c r="T444" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="V444" t="s">
         <v>263</v>
       </c>
       <c r="W444" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AA444">
         <v>0</v>
@@ -32008,15 +32017,15 @@
         <v>426</v>
       </c>
       <c r="AH444" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="445" spans="1:34">
       <c r="A445">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B445" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C445" t="s">
         <v>58</v>
@@ -32025,64 +32034,61 @@
         <v>59</v>
       </c>
       <c r="E445" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F445" t="s">
         <v>64</v>
       </c>
       <c r="G445">
-        <v>1652</v>
+        <v>1697</v>
       </c>
       <c r="H445">
-        <v>0</v>
+        <v>1650</v>
       </c>
       <c r="I445" t="s">
         <v>67</v>
       </c>
       <c r="J445" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="L445" s="1">
-        <v>46290</v>
+        <v>46286</v>
       </c>
       <c r="N445" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="O445">
-        <v>17042389</v>
+        <v>17968001</v>
       </c>
       <c r="P445" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q445" t="s">
         <v>245</v>
       </c>
       <c r="R445" s="1">
-        <v>46245.76585582176</v>
+        <v>46282.62254486111</v>
       </c>
       <c r="S445">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="T445" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="V445" t="s">
         <v>263</v>
       </c>
-      <c r="W445" t="s">
-        <v>368</v>
-      </c>
       <c r="AA445">
         <v>0</v>
       </c>
       <c r="AB445" t="s">
-        <v>420</v>
+        <v>218</v>
       </c>
       <c r="AG445" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AH445" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="446" spans="1:34">

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8668" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8669" uniqueCount="435">
   <si>
     <t>CodCliente</t>
   </si>
@@ -1135,9 +1135,6 @@
     <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 18/09/2026 - Em andamento - Data Comentário: 15/09/2026 09:29</t>
   </si>
   <si>
-    <t>Reaberto via API integração MGC x Sistema de Analise Fiscal em 17/09/2026 12:58:09. - Data Comentário: 17/09/2026 12:53</t>
-  </si>
-  <si>
     <t>PREPARAR MATERIAL - Data Comentário: 16/09/2026 17:01</t>
   </si>
   <si>
@@ -1280,6 +1277,9 @@
     <t>Integração com Sistema de Análise 
 ICMS liberado, aguardo a validação do SPED Contribuições. 
 Data Simulação: 14/09/2026 17:01:47 - Data Comentário: 14/09/2026 17:05</t>
+  </si>
+  <si>
+    <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 17/09/2026 15:25:25. - Data Comentário: 17/09/2026 15:20</t>
   </si>
   <si>
     <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 17/09/2026 
@@ -31549,16 +31549,16 @@
     </row>
     <row r="438" spans="1:34">
       <c r="A438">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B438" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C438" t="s">
         <v>58</v>
       </c>
       <c r="D438" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E438" t="s">
         <v>62</v>
@@ -31567,37 +31567,37 @@
         <v>64</v>
       </c>
       <c r="G438">
-        <v>7027</v>
+        <v>11056</v>
       </c>
       <c r="H438">
         <v>0</v>
       </c>
       <c r="I438" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J438" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="L438" s="1">
-        <v>46289</v>
+        <v>46287</v>
       </c>
       <c r="N438" t="s">
         <v>213</v>
       </c>
       <c r="O438">
-        <v>16962348</v>
+        <v>18275526</v>
       </c>
       <c r="P438" t="s">
-        <v>62</v>
+        <v>243</v>
       </c>
       <c r="Q438" t="s">
         <v>247</v>
       </c>
       <c r="S438">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="T438" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="W438" t="s">
         <v>364</v>
@@ -31611,22 +31611,22 @@
     </row>
     <row r="439" spans="1:34">
       <c r="A439">
-        <v>5417</v>
+        <v>6962</v>
       </c>
       <c r="B439" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C439" t="s">
         <v>58</v>
       </c>
       <c r="D439" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E439" t="s">
         <v>62</v>
       </c>
       <c r="F439" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G439">
         <v>11056</v>
@@ -31647,7 +31647,7 @@
         <v>213</v>
       </c>
       <c r="O439">
-        <v>18275526</v>
+        <v>18274091</v>
       </c>
       <c r="P439" t="s">
         <v>243</v>
@@ -31659,7 +31659,7 @@
         <v>-5</v>
       </c>
       <c r="T439" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="W439" t="s">
         <v>365</v>
@@ -31673,72 +31673,81 @@
     </row>
     <row r="440" spans="1:34">
       <c r="A440">
-        <v>6962</v>
+        <v>6628</v>
       </c>
       <c r="B440" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C440" t="s">
         <v>58</v>
       </c>
       <c r="D440" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E440" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F440" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G440">
-        <v>11056</v>
+        <v>1650</v>
       </c>
       <c r="H440">
         <v>0</v>
       </c>
       <c r="I440" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="J440" t="s">
-        <v>129</v>
+        <v>161</v>
       </c>
       <c r="L440" s="1">
-        <v>46287</v>
+        <v>46293</v>
       </c>
       <c r="N440" t="s">
         <v>213</v>
       </c>
       <c r="O440">
-        <v>18274091</v>
+        <v>16959974</v>
       </c>
       <c r="P440" t="s">
-        <v>243</v>
+        <v>219</v>
       </c>
       <c r="Q440" t="s">
-        <v>247</v>
+        <v>245</v>
+      </c>
+      <c r="R440" s="1">
+        <v>46265.00248284722</v>
       </c>
       <c r="S440">
-        <v>-5</v>
+        <v>-11</v>
       </c>
       <c r="T440" t="s">
-        <v>252</v>
-      </c>
-      <c r="W440" t="s">
-        <v>366</v>
+        <v>249</v>
+      </c>
+      <c r="V440" t="s">
+        <v>263</v>
       </c>
       <c r="AA440">
         <v>0</v>
+      </c>
+      <c r="AB440" t="s">
+        <v>420</v>
       </c>
       <c r="AG440" t="s">
         <v>425</v>
       </c>
+      <c r="AH440" t="s">
+        <v>429</v>
+      </c>
     </row>
     <row r="441" spans="1:34">
       <c r="A441">
-        <v>6628</v>
+        <v>6945</v>
       </c>
       <c r="B441" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C441" t="s">
         <v>58</v>
@@ -31747,10 +31756,10 @@
         <v>60</v>
       </c>
       <c r="E441" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F441" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G441">
         <v>1650</v>
@@ -31771,25 +31780,22 @@
         <v>213</v>
       </c>
       <c r="O441">
-        <v>16959974</v>
+        <v>18163667</v>
       </c>
       <c r="P441" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q441" t="s">
         <v>245</v>
       </c>
       <c r="R441" s="1">
-        <v>46265.00248284722</v>
+        <v>46265.00255472222</v>
       </c>
       <c r="S441">
         <v>-11</v>
       </c>
       <c r="T441" t="s">
-        <v>249</v>
-      </c>
-      <c r="V441" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="AA441">
         <v>0</v>
@@ -31806,25 +31812,25 @@
     </row>
     <row r="442" spans="1:34">
       <c r="A442">
-        <v>6945</v>
+        <v>6548</v>
       </c>
       <c r="B442" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C442" t="s">
         <v>58</v>
       </c>
       <c r="D442" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E442" t="s">
         <v>62</v>
       </c>
       <c r="F442" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G442">
-        <v>1650</v>
+        <v>1652</v>
       </c>
       <c r="H442">
         <v>0</v>
@@ -31833,31 +31839,37 @@
         <v>67</v>
       </c>
       <c r="J442" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L442" s="1">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="N442" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="O442">
-        <v>18163667</v>
+        <v>17967989</v>
       </c>
       <c r="P442" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="Q442" t="s">
         <v>245</v>
       </c>
       <c r="R442" s="1">
-        <v>46265.00255472222</v>
+        <v>46234.66180127315</v>
       </c>
       <c r="S442">
-        <v>-11</v>
+        <v>-8</v>
       </c>
       <c r="T442" t="s">
-        <v>250</v>
+        <v>248</v>
+      </c>
+      <c r="V442" t="s">
+        <v>263</v>
+      </c>
+      <c r="W442" t="s">
+        <v>366</v>
       </c>
       <c r="AA442">
         <v>0</v>
@@ -31866,18 +31878,18 @@
         <v>420</v>
       </c>
       <c r="AG442" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AH442" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="443" spans="1:34">
       <c r="A443">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B443" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C443" t="s">
         <v>58</v>
@@ -31886,7 +31898,7 @@
         <v>59</v>
       </c>
       <c r="E443" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F443" t="s">
         <v>64</v>
@@ -31910,22 +31922,22 @@
         <v>215</v>
       </c>
       <c r="O443">
-        <v>17967989</v>
+        <v>17042389</v>
       </c>
       <c r="P443" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q443" t="s">
         <v>245</v>
       </c>
       <c r="R443" s="1">
-        <v>46234.66180127315</v>
+        <v>46245.76585582176</v>
       </c>
       <c r="S443">
         <v>-8</v>
       </c>
       <c r="T443" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="V443" t="s">
         <v>263</v>
@@ -31943,15 +31955,15 @@
         <v>426</v>
       </c>
       <c r="AH443" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="444" spans="1:34">
       <c r="A444">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B444" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C444" t="s">
         <v>58</v>
@@ -31960,72 +31972,69 @@
         <v>59</v>
       </c>
       <c r="E444" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F444" t="s">
         <v>64</v>
       </c>
       <c r="G444">
-        <v>1652</v>
+        <v>1697</v>
       </c>
       <c r="H444">
-        <v>0</v>
+        <v>1650</v>
       </c>
       <c r="I444" t="s">
         <v>67</v>
       </c>
       <c r="J444" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="L444" s="1">
-        <v>46290</v>
+        <v>46286</v>
       </c>
       <c r="N444" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="O444">
-        <v>17042389</v>
+        <v>17968001</v>
       </c>
       <c r="P444" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q444" t="s">
         <v>245</v>
       </c>
       <c r="R444" s="1">
-        <v>46245.76585582176</v>
+        <v>46282.62254486111</v>
       </c>
       <c r="S444">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="T444" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="V444" t="s">
         <v>263</v>
       </c>
-      <c r="W444" t="s">
-        <v>368</v>
-      </c>
       <c r="AA444">
         <v>0</v>
       </c>
       <c r="AB444" t="s">
-        <v>420</v>
+        <v>218</v>
       </c>
       <c r="AG444" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AH444" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="445" spans="1:34">
       <c r="A445">
-        <v>6548</v>
+        <v>6704</v>
       </c>
       <c r="B445" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C445" t="s">
         <v>58</v>
@@ -32040,40 +32049,40 @@
         <v>64</v>
       </c>
       <c r="G445">
-        <v>1697</v>
+        <v>7868</v>
       </c>
       <c r="H445">
-        <v>1650</v>
+        <v>0</v>
       </c>
       <c r="I445" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J445" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="L445" s="1">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="N445" t="s">
         <v>213</v>
       </c>
       <c r="O445">
-        <v>17968001</v>
+        <v>17955421</v>
       </c>
       <c r="P445" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="Q445" t="s">
         <v>245</v>
       </c>
       <c r="R445" s="1">
-        <v>46282.62254486111</v>
+        <v>46267.47365627315</v>
       </c>
       <c r="S445">
-        <v>-4</v>
+        <v>-11</v>
       </c>
       <c r="T445" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="V445" t="s">
         <v>263</v>
@@ -32082,21 +32091,21 @@
         <v>0</v>
       </c>
       <c r="AB445" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="AG445" t="s">
         <v>425</v>
       </c>
       <c r="AH445" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="446" spans="1:34">
       <c r="A446">
-        <v>6704</v>
+        <v>5417</v>
       </c>
       <c r="B446" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C446" t="s">
         <v>58</v>
@@ -32111,7 +32120,7 @@
         <v>64</v>
       </c>
       <c r="G446">
-        <v>7868</v>
+        <v>11276</v>
       </c>
       <c r="H446">
         <v>0</v>
@@ -32120,54 +32129,51 @@
         <v>68</v>
       </c>
       <c r="J446" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="L446" s="1">
-        <v>46293</v>
+        <v>46283</v>
       </c>
       <c r="N446" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="O446">
-        <v>17955421</v>
+        <v>17399423</v>
       </c>
       <c r="P446" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q446" t="s">
         <v>245</v>
       </c>
       <c r="R446" s="1">
-        <v>46267.47365627315</v>
+        <v>46266.47620831019</v>
       </c>
       <c r="S446">
-        <v>-11</v>
+        <v>-1</v>
       </c>
       <c r="T446" t="s">
-        <v>254</v>
-      </c>
-      <c r="V446" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="AA446">
         <v>0</v>
       </c>
       <c r="AB446" t="s">
-        <v>223</v>
+        <v>422</v>
       </c>
       <c r="AG446" t="s">
         <v>425</v>
       </c>
       <c r="AH446" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="447" spans="1:34">
       <c r="A447">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B447" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C447" t="s">
         <v>58</v>
@@ -32200,28 +32206,31 @@
         <v>216</v>
       </c>
       <c r="O447">
-        <v>17399423</v>
+        <v>18152557</v>
       </c>
       <c r="P447" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="Q447" t="s">
         <v>245</v>
       </c>
       <c r="R447" s="1">
-        <v>46266.47620831019</v>
+        <v>46267.57586420139</v>
       </c>
       <c r="S447">
         <v>-1</v>
       </c>
       <c r="T447" t="s">
-        <v>253</v>
+        <v>255</v>
+      </c>
+      <c r="V447" t="s">
+        <v>263</v>
       </c>
       <c r="AA447">
         <v>0</v>
       </c>
       <c r="AB447" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG447" t="s">
         <v>425</v>
@@ -32232,10 +32241,10 @@
     </row>
     <row r="448" spans="1:34">
       <c r="A448">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B448" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C448" t="s">
         <v>58</v>
@@ -32250,7 +32259,7 @@
         <v>64</v>
       </c>
       <c r="G448">
-        <v>11276</v>
+        <v>1583</v>
       </c>
       <c r="H448">
         <v>0</v>
@@ -32259,43 +32268,40 @@
         <v>68</v>
       </c>
       <c r="J448" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L448" s="1">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="N448" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="O448">
-        <v>18152557</v>
+        <v>17398917</v>
       </c>
       <c r="P448" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="Q448" t="s">
         <v>245</v>
       </c>
       <c r="R448" s="1">
-        <v>46267.57586420139</v>
+        <v>46233.72355880787</v>
       </c>
       <c r="S448">
-        <v>-1</v>
+        <v>-8</v>
       </c>
       <c r="T448" t="s">
-        <v>255</v>
-      </c>
-      <c r="V448" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="AA448">
         <v>0</v>
       </c>
       <c r="AB448" t="s">
-        <v>423</v>
+        <v>222</v>
       </c>
       <c r="AG448" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AH448" t="s">
         <v>430</v>
@@ -32303,10 +32309,10 @@
     </row>
     <row r="449" spans="1:34">
       <c r="A449">
-        <v>5417</v>
+        <v>5617</v>
       </c>
       <c r="B449" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C449" t="s">
         <v>58</v>
@@ -32339,42 +32345,36 @@
         <v>215</v>
       </c>
       <c r="O449">
-        <v>17398917</v>
-      </c>
-      <c r="P449" t="s">
-        <v>222</v>
+        <v>17407553</v>
       </c>
       <c r="Q449" t="s">
         <v>245</v>
       </c>
       <c r="R449" s="1">
-        <v>46233.72355880787</v>
+        <v>46261.36669849537</v>
       </c>
       <c r="S449">
         <v>-8</v>
       </c>
       <c r="T449" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="AA449">
         <v>0</v>
       </c>
       <c r="AB449" t="s">
-        <v>222</v>
+        <v>417</v>
       </c>
       <c r="AG449" t="s">
         <v>426</v>
       </c>
-      <c r="AH449" t="s">
-        <v>430</v>
-      </c>
     </row>
     <row r="450" spans="1:34">
       <c r="A450">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B450" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C450" t="s">
         <v>58</v>
@@ -32386,7 +32386,7 @@
         <v>62</v>
       </c>
       <c r="F450" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G450">
         <v>1583</v>
@@ -32407,13 +32407,13 @@
         <v>215</v>
       </c>
       <c r="O450">
-        <v>17407553</v>
+        <v>17688645</v>
       </c>
       <c r="Q450" t="s">
         <v>245</v>
       </c>
       <c r="R450" s="1">
-        <v>46261.36669849537</v>
+        <v>46266.44156952546</v>
       </c>
       <c r="S450">
         <v>-8</v>
@@ -32421,11 +32421,14 @@
       <c r="T450" t="s">
         <v>258</v>
       </c>
+      <c r="V450" t="s">
+        <v>263</v>
+      </c>
       <c r="AA450">
         <v>0</v>
       </c>
       <c r="AB450" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="AG450" t="s">
         <v>426</v>
@@ -32433,10 +32436,10 @@
     </row>
     <row r="451" spans="1:34">
       <c r="A451">
-        <v>6224</v>
+        <v>6278</v>
       </c>
       <c r="B451" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C451" t="s">
         <v>58</v>
@@ -32448,7 +32451,7 @@
         <v>62</v>
       </c>
       <c r="F451" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G451">
         <v>1583</v>
@@ -32469,28 +32472,31 @@
         <v>215</v>
       </c>
       <c r="O451">
-        <v>17688645</v>
+        <v>18166312</v>
       </c>
       <c r="Q451" t="s">
         <v>245</v>
       </c>
       <c r="R451" s="1">
-        <v>46266.44156952546</v>
+        <v>46233.50562820602</v>
       </c>
       <c r="S451">
         <v>-8</v>
       </c>
       <c r="T451" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="V451" t="s">
         <v>263</v>
       </c>
+      <c r="W451" t="s">
+        <v>368</v>
+      </c>
       <c r="AA451">
         <v>0</v>
       </c>
       <c r="AB451" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="AG451" t="s">
         <v>426</v>
@@ -32498,10 +32504,10 @@
     </row>
     <row r="452" spans="1:34">
       <c r="A452">
-        <v>6278</v>
+        <v>6486</v>
       </c>
       <c r="B452" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C452" t="s">
         <v>58</v>
@@ -32534,42 +32540,45 @@
         <v>215</v>
       </c>
       <c r="O452">
-        <v>18166312</v>
+        <v>18114208</v>
+      </c>
+      <c r="P452" t="s">
+        <v>240</v>
       </c>
       <c r="Q452" t="s">
         <v>245</v>
       </c>
       <c r="R452" s="1">
-        <v>46233.50562820602</v>
+        <v>46233.80164280093</v>
       </c>
       <c r="S452">
         <v>-8</v>
       </c>
       <c r="T452" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="V452" t="s">
         <v>263</v>
       </c>
-      <c r="W452" t="s">
-        <v>369</v>
-      </c>
       <c r="AA452">
         <v>0</v>
       </c>
       <c r="AB452" t="s">
-        <v>420</v>
+        <v>240</v>
       </c>
       <c r="AG452" t="s">
         <v>426</v>
       </c>
+      <c r="AH452" t="s">
+        <v>430</v>
+      </c>
     </row>
     <row r="453" spans="1:34">
       <c r="A453">
-        <v>6486</v>
+        <v>6704</v>
       </c>
       <c r="B453" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C453" t="s">
         <v>58</v>
@@ -32602,22 +32611,22 @@
         <v>215</v>
       </c>
       <c r="O453">
-        <v>18114208</v>
+        <v>17955373</v>
       </c>
       <c r="P453" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="Q453" t="s">
         <v>245</v>
       </c>
       <c r="R453" s="1">
-        <v>46233.80164280093</v>
+        <v>46232.72913953703</v>
       </c>
       <c r="S453">
         <v>-8</v>
       </c>
       <c r="T453" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="V453" t="s">
         <v>263</v>
@@ -32626,21 +32635,21 @@
         <v>0</v>
       </c>
       <c r="AB453" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="AG453" t="s">
         <v>426</v>
       </c>
       <c r="AH453" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="454" spans="1:34">
       <c r="A454">
-        <v>6704</v>
+        <v>5417</v>
       </c>
       <c r="B454" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C454" t="s">
         <v>58</v>
@@ -32655,69 +32664,66 @@
         <v>64</v>
       </c>
       <c r="G454">
-        <v>1583</v>
+        <v>1628</v>
       </c>
       <c r="H454">
-        <v>0</v>
+        <v>1581</v>
       </c>
       <c r="I454" t="s">
         <v>68</v>
       </c>
       <c r="J454" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="L454" s="1">
-        <v>46290</v>
+        <v>46286</v>
       </c>
       <c r="N454" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="O454">
-        <v>17955373</v>
+        <v>17398925</v>
       </c>
       <c r="P454" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q454" t="s">
         <v>245</v>
       </c>
       <c r="R454" s="1">
-        <v>46232.72913953703</v>
+        <v>46280.37528408565</v>
       </c>
       <c r="S454">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="T454" t="s">
-        <v>254</v>
-      </c>
-      <c r="V454" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="AA454">
         <v>0</v>
       </c>
       <c r="AB454" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AG454" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AH454" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="455" spans="1:34">
       <c r="A455">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B455" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C455" t="s">
         <v>58</v>
       </c>
       <c r="D455" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E455" t="s">
         <v>62</v>
@@ -32744,42 +32750,42 @@
         <v>213</v>
       </c>
       <c r="O455">
-        <v>17398925</v>
+        <v>16962141</v>
       </c>
       <c r="P455" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="Q455" t="s">
         <v>245</v>
       </c>
       <c r="R455" s="1">
-        <v>46280.37528408565</v>
+        <v>46266.37634084491</v>
       </c>
       <c r="S455">
         <v>-4</v>
       </c>
       <c r="T455" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="AA455">
         <v>0</v>
       </c>
       <c r="AB455" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="AG455" t="s">
         <v>425</v>
       </c>
       <c r="AH455" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="456" spans="1:34">
       <c r="A456">
-        <v>6404</v>
+        <v>6703</v>
       </c>
       <c r="B456" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C456" t="s">
         <v>58</v>
@@ -32812,48 +32818,48 @@
         <v>213</v>
       </c>
       <c r="O456">
-        <v>16962141</v>
+        <v>17955176</v>
       </c>
       <c r="P456" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q456" t="s">
         <v>245</v>
       </c>
       <c r="R456" s="1">
-        <v>46266.37634084491</v>
+        <v>46282.42251184028</v>
       </c>
       <c r="S456">
         <v>-4</v>
       </c>
       <c r="T456" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AA456">
         <v>0</v>
       </c>
       <c r="AB456" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AG456" t="s">
         <v>425</v>
       </c>
       <c r="AH456" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="457" spans="1:34">
       <c r="A457">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B457" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C457" t="s">
         <v>58</v>
       </c>
       <c r="D457" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E457" t="s">
         <v>62</v>
@@ -32880,48 +32886,51 @@
         <v>213</v>
       </c>
       <c r="O457">
-        <v>17955176</v>
+        <v>17955384</v>
       </c>
       <c r="P457" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="Q457" t="s">
         <v>245</v>
       </c>
       <c r="R457" s="1">
-        <v>46282.42251184028</v>
+        <v>46267.47452163194</v>
       </c>
       <c r="S457">
         <v>-4</v>
       </c>
       <c r="T457" t="s">
-        <v>256</v>
+        <v>254</v>
+      </c>
+      <c r="V457" t="s">
+        <v>263</v>
       </c>
       <c r="AA457">
         <v>0</v>
       </c>
       <c r="AB457" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="AG457" t="s">
         <v>425</v>
       </c>
       <c r="AH457" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="458" spans="1:34">
       <c r="A458">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B458" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C458" t="s">
         <v>58</v>
       </c>
       <c r="D458" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E458" t="s">
         <v>62</v>
@@ -32948,7 +32957,7 @@
         <v>213</v>
       </c>
       <c r="O458">
-        <v>17955384</v>
+        <v>17955238</v>
       </c>
       <c r="P458" t="s">
         <v>223</v>
@@ -32957,7 +32966,7 @@
         <v>245</v>
       </c>
       <c r="R458" s="1">
-        <v>46267.47452163194</v>
+        <v>46267.4745221412</v>
       </c>
       <c r="S458">
         <v>-4</v>
@@ -32965,9 +32974,6 @@
       <c r="T458" t="s">
         <v>254</v>
       </c>
-      <c r="V458" t="s">
-        <v>263</v>
-      </c>
       <c r="AA458">
         <v>0</v>
       </c>
@@ -32983,10 +32989,10 @@
     </row>
     <row r="459" spans="1:34">
       <c r="A459">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B459" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C459" t="s">
         <v>58</v>
@@ -33019,7 +33025,7 @@
         <v>213</v>
       </c>
       <c r="O459">
-        <v>17955238</v>
+        <v>18056729</v>
       </c>
       <c r="P459" t="s">
         <v>223</v>
@@ -33028,7 +33034,7 @@
         <v>245</v>
       </c>
       <c r="R459" s="1">
-        <v>46267.4745221412</v>
+        <v>46267.47452299768</v>
       </c>
       <c r="S459">
         <v>-4</v>
@@ -33036,6 +33042,9 @@
       <c r="T459" t="s">
         <v>254</v>
       </c>
+      <c r="V459" t="s">
+        <v>263</v>
+      </c>
       <c r="AA459">
         <v>0</v>
       </c>
@@ -33051,87 +33060,93 @@
     </row>
     <row r="460" spans="1:34">
       <c r="A460">
-        <v>6779</v>
+        <v>6627</v>
       </c>
       <c r="B460" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="C460" t="s">
         <v>58</v>
       </c>
       <c r="D460" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E460" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F460" t="s">
         <v>64</v>
       </c>
       <c r="G460">
-        <v>1628</v>
+        <v>5885</v>
       </c>
       <c r="H460">
-        <v>1581</v>
+        <v>5784</v>
       </c>
       <c r="I460" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J460" t="s">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="L460" s="1">
-        <v>46286</v>
+        <v>46283</v>
+      </c>
+      <c r="M460" t="s">
+        <v>212</v>
       </c>
       <c r="N460" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O460">
-        <v>18056729</v>
+        <v>18068566</v>
       </c>
       <c r="P460" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q460" t="s">
         <v>245</v>
       </c>
       <c r="R460" s="1">
-        <v>46267.47452299768</v>
+        <v>46281.63558861111</v>
       </c>
       <c r="S460">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="T460" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="V460" t="s">
         <v>263</v>
       </c>
+      <c r="W460" t="s">
+        <v>369</v>
+      </c>
       <c r="AA460">
         <v>0</v>
       </c>
       <c r="AB460" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG460" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AH460" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="461" spans="1:34">
       <c r="A461">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B461" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C461" t="s">
         <v>58</v>
       </c>
       <c r="D461" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E461" t="s">
         <v>63</v>
@@ -33161,7 +33176,7 @@
         <v>214</v>
       </c>
       <c r="O461">
-        <v>18068566</v>
+        <v>18052485</v>
       </c>
       <c r="P461" t="s">
         <v>224</v>
@@ -33170,7 +33185,7 @@
         <v>245</v>
       </c>
       <c r="R461" s="1">
-        <v>46281.63558861111</v>
+        <v>46281.6358927662</v>
       </c>
       <c r="S461">
         <v>-1</v>
@@ -33182,7 +33197,7 @@
         <v>263</v>
       </c>
       <c r="W461" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AA461">
         <v>0</v>
@@ -33199,10 +33214,10 @@
     </row>
     <row r="462" spans="1:34">
       <c r="A462">
-        <v>6628</v>
+        <v>6945</v>
       </c>
       <c r="B462" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C462" t="s">
         <v>58</v>
@@ -33211,10 +33226,10 @@
         <v>60</v>
       </c>
       <c r="E462" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F462" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G462">
         <v>5885</v>
@@ -33232,31 +33247,28 @@
         <v>46283</v>
       </c>
       <c r="M462" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N462" t="s">
         <v>214</v>
       </c>
       <c r="O462">
-        <v>18052485</v>
+        <v>18206577</v>
       </c>
       <c r="P462" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q462" t="s">
         <v>245</v>
       </c>
       <c r="R462" s="1">
-        <v>46281.6358927662</v>
+        <v>46281.47564895833</v>
       </c>
       <c r="S462">
         <v>-1</v>
       </c>
       <c r="T462" t="s">
-        <v>249</v>
-      </c>
-      <c r="V462" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="W462" t="s">
         <v>370</v>
@@ -33265,101 +33277,95 @@
         <v>0</v>
       </c>
       <c r="AB462" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG462" t="s">
         <v>426</v>
       </c>
       <c r="AH462" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="463" spans="1:34">
       <c r="A463">
-        <v>6945</v>
+        <v>6703</v>
       </c>
       <c r="B463" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C463" t="s">
         <v>58</v>
       </c>
       <c r="D463" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E463" t="s">
         <v>62</v>
       </c>
       <c r="F463" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G463">
-        <v>5885</v>
+        <v>6395</v>
       </c>
       <c r="H463">
-        <v>5784</v>
+        <v>5792</v>
       </c>
       <c r="I463" t="s">
         <v>69</v>
       </c>
       <c r="J463" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L463" s="1">
         <v>46283</v>
       </c>
-      <c r="M463" t="s">
-        <v>209</v>
-      </c>
       <c r="N463" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O463">
-        <v>18206577</v>
+        <v>18105120</v>
       </c>
       <c r="P463" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q463" t="s">
         <v>245</v>
       </c>
       <c r="R463" s="1">
-        <v>46281.47564895833</v>
+        <v>46268.58940019676</v>
       </c>
       <c r="S463">
         <v>-1</v>
       </c>
       <c r="T463" t="s">
-        <v>250</v>
-      </c>
-      <c r="W463" t="s">
-        <v>371</v>
+        <v>256</v>
       </c>
       <c r="AA463">
         <v>0</v>
       </c>
       <c r="AB463" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="AG463" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AH463" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="464" spans="1:34">
       <c r="A464">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B464" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C464" t="s">
         <v>58</v>
       </c>
       <c r="D464" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E464" t="s">
         <v>62</v>
@@ -33368,7 +33374,7 @@
         <v>64</v>
       </c>
       <c r="G464">
-        <v>6395</v>
+        <v>5882</v>
       </c>
       <c r="H464">
         <v>5792</v>
@@ -33377,57 +33383,66 @@
         <v>69</v>
       </c>
       <c r="J464" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L464" s="1">
         <v>46283</v>
       </c>
+      <c r="M464" t="s">
+        <v>209</v>
+      </c>
       <c r="N464" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O464">
-        <v>18105120</v>
+        <v>18195621</v>
       </c>
       <c r="P464" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q464" t="s">
         <v>245</v>
       </c>
       <c r="R464" s="1">
-        <v>46268.58940019676</v>
+        <v>46279.66710767361</v>
       </c>
       <c r="S464">
         <v>-1</v>
       </c>
       <c r="T464" t="s">
-        <v>256</v>
+        <v>254</v>
+      </c>
+      <c r="V464" t="s">
+        <v>263</v>
+      </c>
+      <c r="W464" t="s">
+        <v>371</v>
       </c>
       <c r="AA464">
         <v>0</v>
       </c>
       <c r="AB464" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AG464" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AH464" t="s">
-        <v>432</v>
+        <v>418</v>
       </c>
     </row>
     <row r="465" spans="1:34">
       <c r="A465">
-        <v>6779</v>
+        <v>5417</v>
       </c>
       <c r="B465" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C465" t="s">
         <v>58</v>
       </c>
       <c r="D465" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E465" t="s">
         <v>62</v>
@@ -33436,7 +33451,7 @@
         <v>64</v>
       </c>
       <c r="G465">
-        <v>5882</v>
+        <v>5883</v>
       </c>
       <c r="H465">
         <v>5792</v>
@@ -33445,60 +33460,48 @@
         <v>69</v>
       </c>
       <c r="J465" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="L465" s="1">
-        <v>46283</v>
-      </c>
-      <c r="M465" t="s">
-        <v>209</v>
+        <v>46286</v>
       </c>
       <c r="N465" t="s">
         <v>214</v>
       </c>
       <c r="O465">
-        <v>18195621</v>
+        <v>17399067</v>
       </c>
       <c r="P465" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="Q465" t="s">
         <v>245</v>
       </c>
       <c r="R465" s="1">
-        <v>46279.66710767361</v>
+        <v>46282.47420876157</v>
       </c>
       <c r="S465">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="T465" t="s">
-        <v>254</v>
-      </c>
-      <c r="V465" t="s">
-        <v>263</v>
-      </c>
-      <c r="W465" t="s">
-        <v>372</v>
+        <v>253</v>
       </c>
       <c r="AA465">
         <v>0</v>
       </c>
       <c r="AB465" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="AG465" t="s">
-        <v>426</v>
-      </c>
-      <c r="AH465" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
     </row>
     <row r="466" spans="1:34">
       <c r="A466">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B466" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C466" t="s">
         <v>58</v>
@@ -33527,43 +33530,55 @@
       <c r="L466" s="1">
         <v>46286</v>
       </c>
+      <c r="M466" t="s">
+        <v>207</v>
+      </c>
       <c r="N466" t="s">
         <v>214</v>
       </c>
       <c r="O466">
-        <v>17399067</v>
+        <v>16976067</v>
       </c>
       <c r="P466" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="Q466" t="s">
         <v>245</v>
       </c>
       <c r="R466" s="1">
-        <v>46282.47420876157</v>
+        <v>46281.68877074074</v>
       </c>
       <c r="S466">
         <v>-4</v>
       </c>
       <c r="T466" t="s">
-        <v>253</v>
+        <v>255</v>
+      </c>
+      <c r="V466" t="s">
+        <v>263</v>
+      </c>
+      <c r="W466" t="s">
+        <v>372</v>
       </c>
       <c r="AA466">
         <v>0</v>
       </c>
       <c r="AB466" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AG466" t="s">
         <v>425</v>
       </c>
+      <c r="AH466" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="467" spans="1:34">
       <c r="A467">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B467" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C467" t="s">
         <v>58</v>
@@ -33593,28 +33608,28 @@
         <v>46286</v>
       </c>
       <c r="M467" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="N467" t="s">
         <v>214</v>
       </c>
       <c r="O467">
-        <v>16976067</v>
+        <v>17222629</v>
       </c>
       <c r="P467" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q467" t="s">
         <v>245</v>
       </c>
       <c r="R467" s="1">
-        <v>46281.68877074074</v>
+        <v>46280.57958537037</v>
       </c>
       <c r="S467">
         <v>-4</v>
       </c>
       <c r="T467" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="V467" t="s">
         <v>263</v>
@@ -33626,7 +33641,7 @@
         <v>0</v>
       </c>
       <c r="AB467" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="AG467" t="s">
         <v>425</v>
@@ -33637,10 +33652,10 @@
     </row>
     <row r="468" spans="1:34">
       <c r="A468">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B468" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C468" t="s">
         <v>58</v>
@@ -33649,7 +33664,7 @@
         <v>59</v>
       </c>
       <c r="E468" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F468" t="s">
         <v>64</v>
@@ -33670,40 +33685,40 @@
         <v>46286</v>
       </c>
       <c r="M468" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N468" t="s">
         <v>214</v>
       </c>
       <c r="O468">
-        <v>17222629</v>
+        <v>18068544</v>
       </c>
       <c r="P468" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="Q468" t="s">
         <v>245</v>
       </c>
       <c r="R468" s="1">
-        <v>46280.57958537037</v>
+        <v>46281.63570936343</v>
       </c>
       <c r="S468">
         <v>-4</v>
       </c>
       <c r="T468" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="V468" t="s">
         <v>263</v>
       </c>
       <c r="W468" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AA468">
         <v>0</v>
       </c>
       <c r="AB468" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="AG468" t="s">
         <v>425</v>
@@ -33714,16 +33729,16 @@
     </row>
     <row r="469" spans="1:34">
       <c r="A469">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B469" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C469" t="s">
         <v>58</v>
       </c>
       <c r="D469" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E469" t="s">
         <v>63</v>
@@ -33753,7 +33768,7 @@
         <v>214</v>
       </c>
       <c r="O469">
-        <v>18068544</v>
+        <v>18052463</v>
       </c>
       <c r="P469" t="s">
         <v>224</v>
@@ -33762,7 +33777,7 @@
         <v>245</v>
       </c>
       <c r="R469" s="1">
-        <v>46281.63570936343</v>
+        <v>46281.63595871528</v>
       </c>
       <c r="S469">
         <v>-4</v>
@@ -33774,7 +33789,7 @@
         <v>263</v>
       </c>
       <c r="W469" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AA469">
         <v>0</v>
@@ -33791,19 +33806,19 @@
     </row>
     <row r="470" spans="1:34">
       <c r="A470">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B470" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C470" t="s">
         <v>58</v>
       </c>
       <c r="D470" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E470" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F470" t="s">
         <v>64</v>
@@ -33823,41 +33838,32 @@
       <c r="L470" s="1">
         <v>46286</v>
       </c>
-      <c r="M470" t="s">
-        <v>207</v>
-      </c>
       <c r="N470" t="s">
         <v>214</v>
       </c>
       <c r="O470">
-        <v>18052463</v>
+        <v>18077112</v>
       </c>
       <c r="P470" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="Q470" t="s">
         <v>245</v>
       </c>
       <c r="R470" s="1">
-        <v>46281.63595871528</v>
+        <v>46279.62681744213</v>
       </c>
       <c r="S470">
         <v>-4</v>
       </c>
       <c r="T470" t="s">
-        <v>249</v>
-      </c>
-      <c r="V470" t="s">
-        <v>263</v>
-      </c>
-      <c r="W470" t="s">
-        <v>373</v>
+        <v>256</v>
       </c>
       <c r="AA470">
         <v>0</v>
       </c>
       <c r="AB470" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="AG470" t="s">
         <v>425</v>
@@ -33868,16 +33874,16 @@
     </row>
     <row r="471" spans="1:34">
       <c r="A471">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B471" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C471" t="s">
         <v>58</v>
       </c>
       <c r="D471" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E471" t="s">
         <v>62</v>
@@ -33904,48 +33910,51 @@
         <v>214</v>
       </c>
       <c r="O471">
-        <v>18077112</v>
+        <v>18090189</v>
       </c>
       <c r="P471" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q471" t="s">
         <v>245</v>
       </c>
       <c r="R471" s="1">
-        <v>46279.62681744213</v>
+        <v>46279.66707821759</v>
       </c>
       <c r="S471">
         <v>-4</v>
       </c>
       <c r="T471" t="s">
-        <v>256</v>
+        <v>254</v>
+      </c>
+      <c r="V471" t="s">
+        <v>263</v>
       </c>
       <c r="AA471">
         <v>0</v>
       </c>
       <c r="AB471" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AG471" t="s">
         <v>425</v>
       </c>
       <c r="AH471" t="s">
-        <v>432</v>
+        <v>418</v>
       </c>
     </row>
     <row r="472" spans="1:34">
       <c r="A472">
-        <v>6779</v>
+        <v>5417</v>
       </c>
       <c r="B472" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C472" t="s">
         <v>58</v>
       </c>
       <c r="D472" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E472" t="s">
         <v>62</v>
@@ -33954,7 +33963,7 @@
         <v>64</v>
       </c>
       <c r="G472">
-        <v>5883</v>
+        <v>5884</v>
       </c>
       <c r="H472">
         <v>5792</v>
@@ -33963,7 +33972,7 @@
         <v>69</v>
       </c>
       <c r="J472" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L472" s="1">
         <v>46286</v>
@@ -33972,45 +33981,39 @@
         <v>214</v>
       </c>
       <c r="O472">
-        <v>18090189</v>
+        <v>17399077</v>
       </c>
       <c r="P472" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="Q472" t="s">
         <v>245</v>
       </c>
       <c r="R472" s="1">
-        <v>46279.66707821759</v>
+        <v>46282.47437324074</v>
       </c>
       <c r="S472">
         <v>-4</v>
       </c>
       <c r="T472" t="s">
-        <v>254</v>
-      </c>
-      <c r="V472" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="AA472">
         <v>0</v>
       </c>
       <c r="AB472" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="AG472" t="s">
         <v>425</v>
       </c>
-      <c r="AH472" t="s">
-        <v>418</v>
-      </c>
     </row>
     <row r="473" spans="1:34">
       <c r="A473">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B473" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C473" t="s">
         <v>58</v>
@@ -34039,43 +34042,55 @@
       <c r="L473" s="1">
         <v>46286</v>
       </c>
+      <c r="M473" t="s">
+        <v>207</v>
+      </c>
       <c r="N473" t="s">
         <v>214</v>
       </c>
       <c r="O473">
-        <v>17399077</v>
+        <v>16976077</v>
       </c>
       <c r="P473" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="Q473" t="s">
         <v>245</v>
       </c>
       <c r="R473" s="1">
-        <v>46282.47437324074</v>
+        <v>46281.68880230324</v>
       </c>
       <c r="S473">
         <v>-4</v>
       </c>
       <c r="T473" t="s">
-        <v>253</v>
+        <v>255</v>
+      </c>
+      <c r="V473" t="s">
+        <v>263</v>
+      </c>
+      <c r="W473" t="s">
+        <v>372</v>
       </c>
       <c r="AA473">
         <v>0</v>
       </c>
       <c r="AB473" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AG473" t="s">
         <v>425</v>
       </c>
+      <c r="AH473" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="474" spans="1:34">
       <c r="A474">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B474" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C474" t="s">
         <v>58</v>
@@ -34105,40 +34120,40 @@
         <v>46286</v>
       </c>
       <c r="M474" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="N474" t="s">
         <v>214</v>
       </c>
       <c r="O474">
-        <v>16976077</v>
+        <v>17222647</v>
       </c>
       <c r="P474" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q474" t="s">
         <v>245</v>
       </c>
       <c r="R474" s="1">
-        <v>46281.68880230324</v>
+        <v>46280.57972293982</v>
       </c>
       <c r="S474">
         <v>-4</v>
       </c>
       <c r="T474" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="V474" t="s">
         <v>263</v>
       </c>
       <c r="W474" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AA474">
         <v>0</v>
       </c>
       <c r="AB474" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="AG474" t="s">
         <v>425</v>
@@ -34149,10 +34164,10 @@
     </row>
     <row r="475" spans="1:34">
       <c r="A475">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B475" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C475" t="s">
         <v>58</v>
@@ -34161,7 +34176,7 @@
         <v>59</v>
       </c>
       <c r="E475" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F475" t="s">
         <v>64</v>
@@ -34182,40 +34197,40 @@
         <v>46286</v>
       </c>
       <c r="M475" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N475" t="s">
         <v>214</v>
       </c>
       <c r="O475">
-        <v>17222647</v>
+        <v>18068555</v>
       </c>
       <c r="P475" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="Q475" t="s">
         <v>245</v>
       </c>
       <c r="R475" s="1">
-        <v>46280.57972293982</v>
+        <v>46281.63575075231</v>
       </c>
       <c r="S475">
         <v>-4</v>
       </c>
       <c r="T475" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="V475" t="s">
         <v>263</v>
       </c>
       <c r="W475" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="AA475">
         <v>0</v>
       </c>
       <c r="AB475" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="AG475" t="s">
         <v>425</v>
@@ -34226,16 +34241,16 @@
     </row>
     <row r="476" spans="1:34">
       <c r="A476">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B476" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C476" t="s">
         <v>58</v>
       </c>
       <c r="D476" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E476" t="s">
         <v>63</v>
@@ -34265,7 +34280,7 @@
         <v>214</v>
       </c>
       <c r="O476">
-        <v>18068555</v>
+        <v>18052474</v>
       </c>
       <c r="P476" t="s">
         <v>224</v>
@@ -34274,7 +34289,7 @@
         <v>245</v>
       </c>
       <c r="R476" s="1">
-        <v>46281.63575075231</v>
+        <v>46281.63599785879</v>
       </c>
       <c r="S476">
         <v>-4</v>
@@ -34286,7 +34301,7 @@
         <v>263</v>
       </c>
       <c r="W476" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AA476">
         <v>0</v>
@@ -34303,19 +34318,19 @@
     </row>
     <row r="477" spans="1:34">
       <c r="A477">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B477" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C477" t="s">
         <v>58</v>
       </c>
       <c r="D477" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E477" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F477" t="s">
         <v>64</v>
@@ -34335,41 +34350,32 @@
       <c r="L477" s="1">
         <v>46286</v>
       </c>
-      <c r="M477" t="s">
-        <v>207</v>
-      </c>
       <c r="N477" t="s">
         <v>214</v>
       </c>
       <c r="O477">
-        <v>18052474</v>
+        <v>18077122</v>
       </c>
       <c r="P477" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="Q477" t="s">
         <v>245</v>
       </c>
       <c r="R477" s="1">
-        <v>46281.63599785879</v>
+        <v>46279.6268503125</v>
       </c>
       <c r="S477">
         <v>-4</v>
       </c>
       <c r="T477" t="s">
-        <v>249</v>
-      </c>
-      <c r="V477" t="s">
-        <v>263</v>
-      </c>
-      <c r="W477" t="s">
-        <v>373</v>
+        <v>256</v>
       </c>
       <c r="AA477">
         <v>0</v>
       </c>
       <c r="AB477" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="AG477" t="s">
         <v>425</v>
@@ -34380,16 +34386,16 @@
     </row>
     <row r="478" spans="1:34">
       <c r="A478">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B478" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C478" t="s">
         <v>58</v>
       </c>
       <c r="D478" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E478" t="s">
         <v>62</v>
@@ -34416,48 +34422,51 @@
         <v>214</v>
       </c>
       <c r="O478">
-        <v>18077122</v>
+        <v>18090199</v>
       </c>
       <c r="P478" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q478" t="s">
         <v>245</v>
       </c>
       <c r="R478" s="1">
-        <v>46279.6268503125</v>
+        <v>46279.66698128472</v>
       </c>
       <c r="S478">
         <v>-4</v>
       </c>
       <c r="T478" t="s">
-        <v>256</v>
+        <v>254</v>
+      </c>
+      <c r="V478" t="s">
+        <v>263</v>
       </c>
       <c r="AA478">
         <v>0</v>
       </c>
       <c r="AB478" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AG478" t="s">
         <v>425</v>
       </c>
       <c r="AH478" t="s">
-        <v>432</v>
+        <v>418</v>
       </c>
     </row>
     <row r="479" spans="1:34">
       <c r="A479">
-        <v>6779</v>
+        <v>5417</v>
       </c>
       <c r="B479" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C479" t="s">
         <v>58</v>
       </c>
       <c r="D479" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E479" t="s">
         <v>62</v>
@@ -34466,69 +34475,66 @@
         <v>64</v>
       </c>
       <c r="G479">
-        <v>5884</v>
+        <v>7012</v>
       </c>
       <c r="H479">
-        <v>5792</v>
+        <v>0</v>
       </c>
       <c r="I479" t="s">
         <v>69</v>
       </c>
       <c r="J479" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="L479" s="1">
-        <v>46286</v>
+        <v>46281</v>
       </c>
       <c r="N479" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O479">
-        <v>18090199</v>
+        <v>18257773</v>
       </c>
       <c r="P479" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="Q479" t="s">
         <v>245</v>
       </c>
       <c r="R479" s="1">
-        <v>46279.66698128472</v>
+        <v>46279.66929922454</v>
       </c>
       <c r="S479">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="T479" t="s">
-        <v>254</v>
-      </c>
-      <c r="V479" t="s">
-        <v>263</v>
+        <v>253</v>
+      </c>
+      <c r="W479" t="s">
+        <v>375</v>
       </c>
       <c r="AA479">
         <v>0</v>
       </c>
       <c r="AB479" t="s">
-        <v>231</v>
+        <v>415</v>
       </c>
       <c r="AG479" t="s">
         <v>425</v>
       </c>
-      <c r="AH479" t="s">
-        <v>418</v>
-      </c>
     </row>
     <row r="480" spans="1:34">
       <c r="A480">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B480" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C480" t="s">
         <v>58</v>
       </c>
       <c r="D480" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E480" t="s">
         <v>62</v>
@@ -34555,22 +34561,22 @@
         <v>213</v>
       </c>
       <c r="O480">
-        <v>18257773</v>
+        <v>18258536</v>
       </c>
       <c r="P480" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q480" t="s">
         <v>245</v>
       </c>
       <c r="R480" s="1">
-        <v>46279.66929922454</v>
+        <v>46280.61353684028</v>
       </c>
       <c r="S480">
         <v>1</v>
       </c>
       <c r="T480" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="W480" t="s">
         <v>376</v>
@@ -34584,19 +34590,22 @@
       <c r="AG480" t="s">
         <v>425</v>
       </c>
+      <c r="AH480" t="s">
+        <v>418</v>
+      </c>
     </row>
     <row r="481" spans="1:34">
       <c r="A481">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B481" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C481" t="s">
         <v>58</v>
       </c>
       <c r="D481" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E481" t="s">
         <v>62</v>
@@ -34623,22 +34632,25 @@
         <v>213</v>
       </c>
       <c r="O481">
-        <v>18258536</v>
+        <v>18254964</v>
       </c>
       <c r="P481" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="Q481" t="s">
         <v>245</v>
       </c>
       <c r="R481" s="1">
-        <v>46280.61353684028</v>
+        <v>46280.61353920139</v>
       </c>
       <c r="S481">
         <v>1</v>
       </c>
       <c r="T481" t="s">
-        <v>257</v>
+        <v>255</v>
+      </c>
+      <c r="V481" t="s">
+        <v>263</v>
       </c>
       <c r="W481" t="s">
         <v>377</v>
@@ -34653,15 +34665,15 @@
         <v>425</v>
       </c>
       <c r="AH481" t="s">
-        <v>418</v>
+        <v>432</v>
       </c>
     </row>
     <row r="482" spans="1:34">
       <c r="A482">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B482" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C482" t="s">
         <v>58</v>
@@ -34694,22 +34706,22 @@
         <v>213</v>
       </c>
       <c r="O482">
-        <v>18254964</v>
+        <v>18255116</v>
       </c>
       <c r="P482" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q482" t="s">
         <v>245</v>
       </c>
       <c r="R482" s="1">
-        <v>46280.61353920139</v>
+        <v>46279.63250563657</v>
       </c>
       <c r="S482">
         <v>1</v>
       </c>
       <c r="T482" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="V482" t="s">
         <v>263</v>
@@ -34732,10 +34744,10 @@
     </row>
     <row r="483" spans="1:34">
       <c r="A483">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B483" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C483" t="s">
         <v>58</v>
@@ -34744,7 +34756,7 @@
         <v>59</v>
       </c>
       <c r="E483" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F483" t="s">
         <v>64</v>
@@ -34768,28 +34780,28 @@
         <v>213</v>
       </c>
       <c r="O483">
-        <v>18255116</v>
+        <v>18257668</v>
       </c>
       <c r="P483" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="Q483" t="s">
         <v>245</v>
       </c>
       <c r="R483" s="1">
-        <v>46279.63250563657</v>
+        <v>46280.61354019676</v>
       </c>
       <c r="S483">
         <v>1</v>
       </c>
       <c r="T483" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="V483" t="s">
         <v>263</v>
       </c>
       <c r="W483" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AA483">
         <v>0</v>
@@ -34806,16 +34818,16 @@
     </row>
     <row r="484" spans="1:34">
       <c r="A484">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B484" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C484" t="s">
         <v>58</v>
       </c>
       <c r="D484" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E484" t="s">
         <v>63</v>
@@ -34842,7 +34854,7 @@
         <v>213</v>
       </c>
       <c r="O484">
-        <v>18257668</v>
+        <v>18256366</v>
       </c>
       <c r="P484" t="s">
         <v>224</v>
@@ -34851,7 +34863,7 @@
         <v>245</v>
       </c>
       <c r="R484" s="1">
-        <v>46280.61354019676</v>
+        <v>46280.6135403125</v>
       </c>
       <c r="S484">
         <v>1</v>
@@ -34863,7 +34875,7 @@
         <v>263</v>
       </c>
       <c r="W484" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AA484">
         <v>0</v>
@@ -34880,19 +34892,19 @@
     </row>
     <row r="485" spans="1:34">
       <c r="A485">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B485" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C485" t="s">
         <v>58</v>
       </c>
       <c r="D485" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E485" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F485" t="s">
         <v>64</v>
@@ -34912,38 +34924,38 @@
       <c r="L485" s="1">
         <v>46281</v>
       </c>
+      <c r="M485" t="s">
+        <v>212</v>
+      </c>
       <c r="N485" t="s">
         <v>213</v>
       </c>
       <c r="O485">
-        <v>18256366</v>
+        <v>18256433</v>
       </c>
       <c r="P485" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="Q485" t="s">
         <v>245</v>
       </c>
       <c r="R485" s="1">
-        <v>46280.6135403125</v>
+        <v>46281.71218414352</v>
       </c>
       <c r="S485">
         <v>1</v>
       </c>
       <c r="T485" t="s">
-        <v>249</v>
-      </c>
-      <c r="V485" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="W485" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AA485">
         <v>0</v>
       </c>
       <c r="AB485" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="AG485" t="s">
         <v>425</v>
@@ -34954,16 +34966,16 @@
     </row>
     <row r="486" spans="1:34">
       <c r="A486">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B486" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C486" t="s">
         <v>58</v>
       </c>
       <c r="D486" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E486" t="s">
         <v>62</v>
@@ -34986,29 +34998,29 @@
       <c r="L486" s="1">
         <v>46281</v>
       </c>
-      <c r="M486" t="s">
-        <v>212</v>
-      </c>
       <c r="N486" t="s">
         <v>213</v>
       </c>
       <c r="O486">
-        <v>18256433</v>
+        <v>18255012</v>
       </c>
       <c r="P486" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q486" t="s">
         <v>245</v>
       </c>
       <c r="R486" s="1">
-        <v>46281.71218414352</v>
+        <v>46281.41576883102</v>
       </c>
       <c r="S486">
         <v>1</v>
       </c>
       <c r="T486" t="s">
-        <v>256</v>
+        <v>254</v>
+      </c>
+      <c r="V486" t="s">
+        <v>263</v>
       </c>
       <c r="W486" t="s">
         <v>380</v>
@@ -35017,21 +35029,21 @@
         <v>0</v>
       </c>
       <c r="AB486" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="AG486" t="s">
         <v>425</v>
       </c>
       <c r="AH486" t="s">
-        <v>432</v>
+        <v>418</v>
       </c>
     </row>
     <row r="487" spans="1:34">
       <c r="A487">
-        <v>6779</v>
+        <v>6945</v>
       </c>
       <c r="B487" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C487" t="s">
         <v>58</v>
@@ -35043,7 +35055,7 @@
         <v>62</v>
       </c>
       <c r="F487" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G487">
         <v>7012</v>
@@ -35064,25 +35076,22 @@
         <v>213</v>
       </c>
       <c r="O487">
-        <v>18255012</v>
+        <v>18254903</v>
       </c>
       <c r="P487" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="Q487" t="s">
         <v>245</v>
       </c>
       <c r="R487" s="1">
-        <v>46281.41576883102</v>
+        <v>46280.43132989584</v>
       </c>
       <c r="S487">
         <v>1</v>
       </c>
       <c r="T487" t="s">
-        <v>254</v>
-      </c>
-      <c r="V487" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="W487" t="s">
         <v>381</v>
@@ -35097,21 +35106,21 @@
         <v>425</v>
       </c>
       <c r="AH487" t="s">
-        <v>418</v>
+        <v>433</v>
       </c>
     </row>
     <row r="488" spans="1:34">
       <c r="A488">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B488" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C488" t="s">
         <v>58</v>
       </c>
       <c r="D488" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E488" t="s">
         <v>62</v>
@@ -35138,22 +35147,22 @@
         <v>213</v>
       </c>
       <c r="O488">
-        <v>18254903</v>
+        <v>18258489</v>
       </c>
       <c r="P488" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q488" t="s">
         <v>245</v>
       </c>
       <c r="R488" s="1">
-        <v>46280.43132989584</v>
+        <v>46280.61367623843</v>
       </c>
       <c r="S488">
         <v>1</v>
       </c>
       <c r="T488" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="W488" t="s">
         <v>382</v>
@@ -35173,58 +35182,61 @@
     </row>
     <row r="489" spans="1:34">
       <c r="A489">
-        <v>6949</v>
+        <v>6404</v>
       </c>
       <c r="B489" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C489" t="s">
         <v>58</v>
       </c>
       <c r="D489" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E489" t="s">
         <v>62</v>
       </c>
       <c r="F489" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G489">
-        <v>7012</v>
+        <v>5903</v>
       </c>
       <c r="H489">
-        <v>0</v>
+        <v>5830</v>
       </c>
       <c r="I489" t="s">
         <v>69</v>
       </c>
       <c r="J489" t="s">
-        <v>131</v>
+        <v>167</v>
       </c>
       <c r="L489" s="1">
-        <v>46281</v>
+        <v>46286</v>
+      </c>
+      <c r="M489" t="s">
+        <v>209</v>
       </c>
       <c r="N489" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O489">
-        <v>18258489</v>
+        <v>16962221</v>
       </c>
       <c r="P489" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q489" t="s">
         <v>245</v>
       </c>
       <c r="R489" s="1">
-        <v>46280.61367623843</v>
+        <v>46282.42048836806</v>
       </c>
       <c r="S489">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="T489" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="W489" t="s">
         <v>383</v>
@@ -35233,13 +35245,13 @@
         <v>0</v>
       </c>
       <c r="AB489" t="s">
-        <v>415</v>
+        <v>230</v>
       </c>
       <c r="AG489" t="s">
         <v>425</v>
       </c>
       <c r="AH489" t="s">
-        <v>433</v>
+        <v>418</v>
       </c>
     </row>
     <row r="490" spans="1:34">
@@ -35262,28 +35274,25 @@
         <v>64</v>
       </c>
       <c r="G490">
-        <v>5903</v>
+        <v>5830</v>
       </c>
       <c r="H490">
-        <v>5830</v>
+        <v>5784</v>
       </c>
       <c r="I490" t="s">
         <v>69</v>
       </c>
       <c r="J490" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L490" s="1">
         <v>46286</v>
       </c>
-      <c r="M490" t="s">
-        <v>209</v>
-      </c>
       <c r="N490" t="s">
         <v>214</v>
       </c>
       <c r="O490">
-        <v>16962221</v>
+        <v>16962211</v>
       </c>
       <c r="P490" t="s">
         <v>230</v>
@@ -35292,7 +35301,7 @@
         <v>245</v>
       </c>
       <c r="R490" s="1">
-        <v>46282.42048836806</v>
+        <v>46282.42138976852</v>
       </c>
       <c r="S490">
         <v>-4</v>
@@ -35300,9 +35309,6 @@
       <c r="T490" t="s">
         <v>257</v>
       </c>
-      <c r="W490" t="s">
-        <v>384</v>
-      </c>
       <c r="AA490">
         <v>0</v>
       </c>
@@ -35318,16 +35324,16 @@
     </row>
     <row r="491" spans="1:34">
       <c r="A491">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B491" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C491" t="s">
         <v>58</v>
       </c>
       <c r="D491" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E491" t="s">
         <v>62</v>
@@ -35336,66 +35342,63 @@
         <v>64</v>
       </c>
       <c r="G491">
-        <v>5830</v>
+        <v>5786</v>
       </c>
       <c r="H491">
-        <v>5784</v>
+        <v>0</v>
       </c>
       <c r="I491" t="s">
         <v>69</v>
       </c>
       <c r="J491" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L491" s="1">
-        <v>46286</v>
+        <v>46283</v>
       </c>
       <c r="N491" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O491">
-        <v>16962211</v>
+        <v>17398997</v>
       </c>
       <c r="P491" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="Q491" t="s">
         <v>245</v>
       </c>
       <c r="R491" s="1">
-        <v>46282.42138976852</v>
+        <v>46279.66936339121</v>
       </c>
       <c r="S491">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="T491" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="AA491">
         <v>0</v>
       </c>
       <c r="AB491" t="s">
-        <v>230</v>
+        <v>415</v>
       </c>
       <c r="AG491" t="s">
-        <v>425</v>
-      </c>
-      <c r="AH491" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
     </row>
     <row r="492" spans="1:34">
       <c r="A492">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B492" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C492" t="s">
         <v>58</v>
       </c>
       <c r="D492" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E492" t="s">
         <v>62</v>
@@ -35422,45 +35425,48 @@
         <v>213</v>
       </c>
       <c r="O492">
-        <v>17398997</v>
+        <v>16962199</v>
       </c>
       <c r="P492" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q492" t="s">
         <v>245</v>
       </c>
       <c r="R492" s="1">
-        <v>46279.66936339121</v>
+        <v>46264.0028866088</v>
       </c>
       <c r="S492">
         <v>-1</v>
       </c>
       <c r="T492" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="AA492">
         <v>0</v>
       </c>
       <c r="AB492" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="AG492" t="s">
         <v>426</v>
       </c>
+      <c r="AH492" t="s">
+        <v>418</v>
+      </c>
     </row>
     <row r="493" spans="1:34">
       <c r="A493">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B493" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C493" t="s">
         <v>58</v>
       </c>
       <c r="D493" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E493" t="s">
         <v>62</v>
@@ -35487,42 +35493,45 @@
         <v>213</v>
       </c>
       <c r="O493">
-        <v>16962199</v>
+        <v>16976005</v>
       </c>
       <c r="P493" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="Q493" t="s">
         <v>245</v>
       </c>
       <c r="R493" s="1">
-        <v>46264.0028866088</v>
+        <v>46279.62931917824</v>
       </c>
       <c r="S493">
         <v>-1</v>
       </c>
       <c r="T493" t="s">
-        <v>257</v>
+        <v>255</v>
+      </c>
+      <c r="V493" t="s">
+        <v>263</v>
       </c>
       <c r="AA493">
         <v>0</v>
       </c>
       <c r="AB493" t="s">
-        <v>420</v>
+        <v>224</v>
       </c>
       <c r="AG493" t="s">
         <v>426</v>
       </c>
       <c r="AH493" t="s">
-        <v>418</v>
+        <v>432</v>
       </c>
     </row>
     <row r="494" spans="1:34">
       <c r="A494">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B494" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C494" t="s">
         <v>58</v>
@@ -35555,22 +35564,22 @@
         <v>213</v>
       </c>
       <c r="O494">
-        <v>16976005</v>
+        <v>17222531</v>
       </c>
       <c r="P494" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q494" t="s">
         <v>245</v>
       </c>
       <c r="R494" s="1">
-        <v>46279.62931917824</v>
+        <v>46279.40189447917</v>
       </c>
       <c r="S494">
         <v>-1</v>
       </c>
       <c r="T494" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="V494" t="s">
         <v>263</v>
@@ -35579,7 +35588,7 @@
         <v>0</v>
       </c>
       <c r="AB494" t="s">
-        <v>224</v>
+        <v>415</v>
       </c>
       <c r="AG494" t="s">
         <v>426</v>
@@ -35590,10 +35599,10 @@
     </row>
     <row r="495" spans="1:34">
       <c r="A495">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B495" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C495" t="s">
         <v>58</v>
@@ -35602,7 +35611,7 @@
         <v>59</v>
       </c>
       <c r="E495" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F495" t="s">
         <v>64</v>
@@ -35626,22 +35635,22 @@
         <v>213</v>
       </c>
       <c r="O495">
-        <v>17222531</v>
+        <v>18068463</v>
       </c>
       <c r="P495" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="Q495" t="s">
         <v>245</v>
       </c>
       <c r="R495" s="1">
-        <v>46279.40189447917</v>
+        <v>46279.62936614583</v>
       </c>
       <c r="S495">
         <v>-1</v>
       </c>
       <c r="T495" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="V495" t="s">
         <v>263</v>
@@ -35650,7 +35659,7 @@
         <v>0</v>
       </c>
       <c r="AB495" t="s">
-        <v>415</v>
+        <v>224</v>
       </c>
       <c r="AG495" t="s">
         <v>426</v>
@@ -35661,16 +35670,16 @@
     </row>
     <row r="496" spans="1:34">
       <c r="A496">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B496" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C496" t="s">
         <v>58</v>
       </c>
       <c r="D496" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E496" t="s">
         <v>63</v>
@@ -35697,7 +35706,7 @@
         <v>213</v>
       </c>
       <c r="O496">
-        <v>18068463</v>
+        <v>18052384</v>
       </c>
       <c r="P496" t="s">
         <v>224</v>
@@ -35706,7 +35715,7 @@
         <v>245</v>
       </c>
       <c r="R496" s="1">
-        <v>46279.62936614583</v>
+        <v>46279.62936509259</v>
       </c>
       <c r="S496">
         <v>-1</v>
@@ -35732,10 +35741,10 @@
     </row>
     <row r="497" spans="1:34">
       <c r="A497">
-        <v>6628</v>
+        <v>6779</v>
       </c>
       <c r="B497" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C497" t="s">
         <v>58</v>
@@ -35744,7 +35753,7 @@
         <v>60</v>
       </c>
       <c r="E497" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F497" t="s">
         <v>64</v>
@@ -35768,22 +35777,22 @@
         <v>213</v>
       </c>
       <c r="O497">
-        <v>18052384</v>
+        <v>18090113</v>
       </c>
       <c r="P497" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="Q497" t="s">
         <v>245</v>
       </c>
       <c r="R497" s="1">
-        <v>46279.62936509259</v>
+        <v>46276.63187607639</v>
       </c>
       <c r="S497">
         <v>-1</v>
       </c>
       <c r="T497" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="V497" t="s">
         <v>263</v>
@@ -35792,21 +35801,21 @@
         <v>0</v>
       </c>
       <c r="AB497" t="s">
-        <v>224</v>
+        <v>415</v>
       </c>
       <c r="AG497" t="s">
         <v>426</v>
       </c>
       <c r="AH497" t="s">
-        <v>432</v>
+        <v>418</v>
       </c>
     </row>
     <row r="498" spans="1:34">
       <c r="A498">
-        <v>6779</v>
+        <v>6945</v>
       </c>
       <c r="B498" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C498" t="s">
         <v>58</v>
@@ -35818,7 +35827,7 @@
         <v>62</v>
       </c>
       <c r="F498" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G498">
         <v>5786</v>
@@ -35839,25 +35848,22 @@
         <v>213</v>
       </c>
       <c r="O498">
-        <v>18090113</v>
+        <v>18179053</v>
       </c>
       <c r="P498" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="Q498" t="s">
         <v>245</v>
       </c>
       <c r="R498" s="1">
-        <v>46276.63187607639</v>
+        <v>46279.62658503472</v>
       </c>
       <c r="S498">
         <v>-1</v>
       </c>
       <c r="T498" t="s">
-        <v>254</v>
-      </c>
-      <c r="V498" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="AA498">
         <v>0</v>
@@ -35869,21 +35875,21 @@
         <v>426</v>
       </c>
       <c r="AH498" t="s">
-        <v>418</v>
+        <v>433</v>
       </c>
     </row>
     <row r="499" spans="1:34">
       <c r="A499">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B499" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C499" t="s">
         <v>58</v>
       </c>
       <c r="D499" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E499" t="s">
         <v>62</v>
@@ -35910,22 +35916,22 @@
         <v>213</v>
       </c>
       <c r="O499">
-        <v>18179053</v>
+        <v>18190370</v>
       </c>
       <c r="P499" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q499" t="s">
         <v>245</v>
       </c>
       <c r="R499" s="1">
-        <v>46279.62658503472</v>
+        <v>46279.63255474537</v>
       </c>
       <c r="S499">
         <v>-1</v>
       </c>
       <c r="T499" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AA499">
         <v>0</v>
@@ -35942,10 +35948,10 @@
     </row>
     <row r="500" spans="1:34">
       <c r="A500">
-        <v>6949</v>
+        <v>6486</v>
       </c>
       <c r="B500" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C500" t="s">
         <v>58</v>
@@ -35957,10 +35963,10 @@
         <v>62</v>
       </c>
       <c r="F500" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G500">
-        <v>5786</v>
+        <v>5787</v>
       </c>
       <c r="H500">
         <v>0</v>
@@ -35969,57 +35975,60 @@
         <v>69</v>
       </c>
       <c r="J500" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L500" s="1">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="N500" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="O500">
-        <v>18190370</v>
+        <v>16976010</v>
       </c>
       <c r="P500" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="Q500" t="s">
         <v>245</v>
       </c>
       <c r="R500" s="1">
-        <v>46279.63255474537</v>
+        <v>46256.00536641204</v>
       </c>
       <c r="S500">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="T500" t="s">
-        <v>251</v>
+        <v>255</v>
+      </c>
+      <c r="V500" t="s">
+        <v>263</v>
       </c>
       <c r="AA500">
         <v>0</v>
       </c>
       <c r="AB500" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="AG500" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AH500" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="501" spans="1:34">
       <c r="A501">
-        <v>6486</v>
+        <v>6779</v>
       </c>
       <c r="B501" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C501" t="s">
         <v>58</v>
       </c>
       <c r="D501" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E501" t="s">
         <v>62</v>
@@ -36046,22 +36055,22 @@
         <v>217</v>
       </c>
       <c r="O501">
-        <v>16976010</v>
+        <v>18090118</v>
       </c>
       <c r="P501" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="Q501" t="s">
         <v>245</v>
       </c>
       <c r="R501" s="1">
-        <v>46256.00536641204</v>
+        <v>46256.00539434027</v>
       </c>
       <c r="S501">
         <v>-4</v>
       </c>
       <c r="T501" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="V501" t="s">
         <v>263</v>
@@ -36076,15 +36085,15 @@
         <v>425</v>
       </c>
       <c r="AH501" t="s">
-        <v>432</v>
+        <v>418</v>
       </c>
     </row>
     <row r="502" spans="1:34">
       <c r="A502">
-        <v>6779</v>
+        <v>6945</v>
       </c>
       <c r="B502" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C502" t="s">
         <v>58</v>
@@ -36096,7 +36105,7 @@
         <v>62</v>
       </c>
       <c r="F502" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G502">
         <v>5787</v>
@@ -36117,25 +36126,22 @@
         <v>217</v>
       </c>
       <c r="O502">
-        <v>18090118</v>
+        <v>18179058</v>
       </c>
       <c r="P502" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="Q502" t="s">
         <v>245</v>
       </c>
       <c r="R502" s="1">
-        <v>46256.00539434027</v>
+        <v>46256.00540109954</v>
       </c>
       <c r="S502">
         <v>-4</v>
       </c>
       <c r="T502" t="s">
-        <v>254</v>
-      </c>
-      <c r="V502" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="AA502">
         <v>0</v>
@@ -36147,15 +36153,15 @@
         <v>425</v>
       </c>
       <c r="AH502" t="s">
-        <v>418</v>
+        <v>433</v>
       </c>
     </row>
     <row r="503" spans="1:34">
       <c r="A503">
-        <v>6945</v>
+        <v>6779</v>
       </c>
       <c r="B503" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C503" t="s">
         <v>58</v>
@@ -36167,69 +36173,78 @@
         <v>62</v>
       </c>
       <c r="F503" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G503">
-        <v>5787</v>
+        <v>5837</v>
       </c>
       <c r="H503">
-        <v>0</v>
+        <v>5784</v>
       </c>
       <c r="I503" t="s">
         <v>69</v>
       </c>
       <c r="J503" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L503" s="1">
-        <v>46286</v>
+        <v>46283</v>
+      </c>
+      <c r="M503" t="s">
+        <v>209</v>
       </c>
       <c r="N503" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="O503">
-        <v>18179058</v>
+        <v>18195614</v>
       </c>
       <c r="P503" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="Q503" t="s">
         <v>245</v>
       </c>
       <c r="R503" s="1">
-        <v>46256.00540109954</v>
+        <v>46279.66713805556</v>
       </c>
       <c r="S503">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="T503" t="s">
-        <v>250</v>
+        <v>254</v>
+      </c>
+      <c r="V503" t="s">
+        <v>263</v>
+      </c>
+      <c r="W503" t="s">
+        <v>371</v>
       </c>
       <c r="AA503">
         <v>0</v>
       </c>
       <c r="AB503" t="s">
-        <v>420</v>
+        <v>231</v>
       </c>
       <c r="AG503" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AH503" t="s">
-        <v>433</v>
+        <v>418</v>
       </c>
     </row>
     <row r="504" spans="1:34">
       <c r="A504">
-        <v>6779</v>
+        <v>6486</v>
       </c>
       <c r="B504" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C504" t="s">
         <v>58</v>
       </c>
       <c r="D504" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E504" t="s">
         <v>62</v>
@@ -36238,69 +36253,63 @@
         <v>64</v>
       </c>
       <c r="G504">
-        <v>5837</v>
+        <v>6348</v>
       </c>
       <c r="H504">
-        <v>5784</v>
+        <v>0</v>
       </c>
       <c r="I504" t="s">
         <v>69</v>
       </c>
       <c r="J504" t="s">
-        <v>171</v>
+        <v>90</v>
       </c>
       <c r="L504" s="1">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="M504" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="N504" t="s">
         <v>214</v>
       </c>
       <c r="O504">
-        <v>18195614</v>
-      </c>
-      <c r="P504" t="s">
-        <v>231</v>
+        <v>18271101</v>
       </c>
       <c r="Q504" t="s">
         <v>245</v>
       </c>
       <c r="R504" s="1">
-        <v>46279.66713805556</v>
+        <v>46281.63317659722</v>
       </c>
       <c r="S504">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T504" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="V504" t="s">
         <v>263</v>
       </c>
       <c r="W504" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="AA504">
         <v>0</v>
       </c>
       <c r="AB504" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="AG504" t="s">
         <v>426</v>
       </c>
-      <c r="AH504" t="s">
-        <v>418</v>
-      </c>
     </row>
     <row r="505" spans="1:34">
       <c r="A505">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B505" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C505" t="s">
         <v>58</v>
@@ -36315,63 +36324,63 @@
         <v>64</v>
       </c>
       <c r="G505">
-        <v>6348</v>
+        <v>11550</v>
       </c>
       <c r="H505">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="I505" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J505" t="s">
-        <v>90</v>
+        <v>172</v>
       </c>
       <c r="L505" s="1">
-        <v>46282</v>
-      </c>
-      <c r="M505" t="s">
-        <v>212</v>
+        <v>46286</v>
       </c>
       <c r="N505" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O505">
-        <v>18271101</v>
+        <v>17988603</v>
+      </c>
+      <c r="P505" t="s">
+        <v>232</v>
       </c>
       <c r="Q505" t="s">
         <v>245</v>
       </c>
       <c r="R505" s="1">
-        <v>46281.63317659722</v>
+        <v>46267.72055925926</v>
       </c>
       <c r="S505">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="T505" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="V505" t="s">
         <v>263</v>
       </c>
-      <c r="W505" t="s">
-        <v>385</v>
-      </c>
       <c r="AA505">
         <v>0</v>
       </c>
       <c r="AB505" t="s">
-        <v>224</v>
+        <v>419</v>
       </c>
       <c r="AG505" t="s">
-        <v>426</v>
+        <v>425</v>
+      </c>
+      <c r="AH505" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="506" spans="1:34">
       <c r="A506">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B506" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C506" t="s">
         <v>58</v>
@@ -36380,7 +36389,7 @@
         <v>59</v>
       </c>
       <c r="E506" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F506" t="s">
         <v>64</v>
@@ -36404,22 +36413,22 @@
         <v>213</v>
       </c>
       <c r="O506">
-        <v>17988603</v>
+        <v>18048493</v>
       </c>
       <c r="P506" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q506" t="s">
         <v>245</v>
       </c>
       <c r="R506" s="1">
-        <v>46267.72055925926</v>
+        <v>46267.79441380787</v>
       </c>
       <c r="S506">
         <v>-4</v>
       </c>
       <c r="T506" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="V506" t="s">
         <v>263</v>
@@ -36433,16 +36442,13 @@
       <c r="AG506" t="s">
         <v>425</v>
       </c>
-      <c r="AH506" t="s">
-        <v>419</v>
-      </c>
     </row>
     <row r="507" spans="1:34">
       <c r="A507">
-        <v>6627</v>
+        <v>6949</v>
       </c>
       <c r="B507" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C507" t="s">
         <v>58</v>
@@ -36451,10 +36457,10 @@
         <v>59</v>
       </c>
       <c r="E507" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F507" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G507">
         <v>11550</v>
@@ -36475,48 +36481,48 @@
         <v>213</v>
       </c>
       <c r="O507">
-        <v>18048493</v>
+        <v>18214931</v>
       </c>
       <c r="P507" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q507" t="s">
         <v>245</v>
       </c>
       <c r="R507" s="1">
-        <v>46267.79441380787</v>
+        <v>46267.79441215278</v>
       </c>
       <c r="S507">
         <v>-4</v>
       </c>
       <c r="T507" t="s">
-        <v>249</v>
-      </c>
-      <c r="V507" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="AA507">
         <v>0</v>
       </c>
       <c r="AB507" t="s">
-        <v>419</v>
+        <v>235</v>
       </c>
       <c r="AG507" t="s">
         <v>425</v>
       </c>
+      <c r="AH507" t="s">
+        <v>419</v>
+      </c>
     </row>
     <row r="508" spans="1:34">
       <c r="A508">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B508" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C508" t="s">
         <v>58</v>
       </c>
       <c r="D508" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E508" t="s">
         <v>62</v>
@@ -36525,49 +36531,55 @@
         <v>65</v>
       </c>
       <c r="G508">
-        <v>11550</v>
+        <v>11873</v>
       </c>
       <c r="H508">
-        <v>1862</v>
+        <v>0</v>
       </c>
       <c r="I508" t="s">
         <v>70</v>
       </c>
       <c r="J508" t="s">
-        <v>172</v>
+        <v>131</v>
       </c>
       <c r="L508" s="1">
-        <v>46286</v>
+        <v>46281</v>
+      </c>
+      <c r="M508" t="s">
+        <v>212</v>
       </c>
       <c r="N508" t="s">
         <v>213</v>
       </c>
       <c r="O508">
-        <v>18214931</v>
+        <v>18223029</v>
       </c>
       <c r="P508" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q508" t="s">
         <v>245</v>
       </c>
       <c r="R508" s="1">
-        <v>46267.79441215278</v>
+        <v>46280.62789608796</v>
       </c>
       <c r="S508">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="T508" t="s">
-        <v>251</v>
+        <v>252</v>
+      </c>
+      <c r="W508" t="s">
+        <v>385</v>
       </c>
       <c r="AA508">
         <v>0</v>
       </c>
       <c r="AB508" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG508" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AH508" t="s">
         <v>419</v>
@@ -36575,10 +36587,10 @@
     </row>
     <row r="509" spans="1:34">
       <c r="A509">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B509" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C509" t="s">
         <v>58</v>
@@ -36614,7 +36626,7 @@
         <v>213</v>
       </c>
       <c r="O509">
-        <v>18223029</v>
+        <v>18222688</v>
       </c>
       <c r="P509" t="s">
         <v>236</v>
@@ -36623,7 +36635,7 @@
         <v>245</v>
       </c>
       <c r="R509" s="1">
-        <v>46280.62789608796</v>
+        <v>46280.63189497685</v>
       </c>
       <c r="S509">
         <v>1</v>
@@ -36632,7 +36644,7 @@
         <v>252</v>
       </c>
       <c r="W509" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AA509">
         <v>0</v>
@@ -36649,25 +36661,25 @@
     </row>
     <row r="510" spans="1:34">
       <c r="A510">
-        <v>6963</v>
+        <v>6628</v>
       </c>
       <c r="B510" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C510" t="s">
         <v>58</v>
       </c>
       <c r="D510" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E510" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F510" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G510">
-        <v>11873</v>
+        <v>1862</v>
       </c>
       <c r="H510">
         <v>0</v>
@@ -36676,46 +36688,43 @@
         <v>70</v>
       </c>
       <c r="J510" t="s">
-        <v>131</v>
+        <v>161</v>
       </c>
       <c r="L510" s="1">
         <v>46281</v>
       </c>
-      <c r="M510" t="s">
-        <v>212</v>
-      </c>
       <c r="N510" t="s">
         <v>213</v>
       </c>
       <c r="O510">
-        <v>18222688</v>
+        <v>18047772</v>
       </c>
       <c r="P510" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="Q510" t="s">
         <v>245</v>
       </c>
       <c r="R510" s="1">
-        <v>46280.63189497685</v>
+        <v>46265.00319547454</v>
       </c>
       <c r="S510">
         <v>1</v>
       </c>
       <c r="T510" t="s">
-        <v>252</v>
-      </c>
-      <c r="W510" t="s">
-        <v>386</v>
+        <v>249</v>
+      </c>
+      <c r="V510" t="s">
+        <v>263</v>
       </c>
       <c r="AA510">
         <v>0</v>
       </c>
       <c r="AB510" t="s">
-        <v>236</v>
+        <v>420</v>
       </c>
       <c r="AG510" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AH510" t="s">
         <v>419</v>
@@ -36723,10 +36732,10 @@
     </row>
     <row r="511" spans="1:34">
       <c r="A511">
-        <v>6628</v>
+        <v>6945</v>
       </c>
       <c r="B511" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C511" t="s">
         <v>58</v>
@@ -36735,10 +36744,10 @@
         <v>60</v>
       </c>
       <c r="E511" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F511" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G511">
         <v>1862</v>
@@ -36759,45 +36768,39 @@
         <v>213</v>
       </c>
       <c r="O511">
-        <v>18047772</v>
+        <v>18220176</v>
       </c>
       <c r="P511" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="Q511" t="s">
         <v>245</v>
       </c>
       <c r="R511" s="1">
-        <v>46265.00319547454</v>
+        <v>46276.37795540509</v>
       </c>
       <c r="S511">
         <v>1</v>
       </c>
       <c r="T511" t="s">
-        <v>249</v>
-      </c>
-      <c r="V511" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="AA511">
         <v>0</v>
       </c>
       <c r="AB511" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG511" t="s">
         <v>425</v>
       </c>
-      <c r="AH511" t="s">
-        <v>419</v>
-      </c>
     </row>
     <row r="512" spans="1:34">
       <c r="A512">
-        <v>6945</v>
+        <v>6628</v>
       </c>
       <c r="B512" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C512" t="s">
         <v>58</v>
@@ -36806,13 +36809,13 @@
         <v>60</v>
       </c>
       <c r="E512" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F512" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G512">
-        <v>1862</v>
+        <v>7026</v>
       </c>
       <c r="H512">
         <v>0</v>
@@ -36821,96 +36824,105 @@
         <v>70</v>
       </c>
       <c r="J512" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="L512" s="1">
-        <v>46281</v>
+        <v>46288</v>
       </c>
       <c r="N512" t="s">
         <v>213</v>
       </c>
       <c r="O512">
-        <v>18220176</v>
+        <v>18094910</v>
       </c>
       <c r="P512" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q512" t="s">
         <v>245</v>
       </c>
       <c r="R512" s="1">
-        <v>46276.37795540509</v>
+        <v>46280.66345891204</v>
       </c>
       <c r="S512">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="T512" t="s">
-        <v>250</v>
+        <v>249</v>
+      </c>
+      <c r="V512" t="s">
+        <v>263</v>
+      </c>
+      <c r="W512" t="s">
+        <v>386</v>
       </c>
       <c r="AA512">
         <v>0</v>
       </c>
       <c r="AB512" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AG512" t="s">
         <v>425</v>
       </c>
+      <c r="AH512" t="s">
+        <v>419</v>
+      </c>
     </row>
     <row r="513" spans="1:34">
       <c r="A513">
-        <v>6628</v>
+        <v>6486</v>
       </c>
       <c r="B513" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C513" t="s">
         <v>58</v>
       </c>
       <c r="D513" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E513" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F513" t="s">
         <v>64</v>
       </c>
       <c r="G513">
-        <v>7026</v>
+        <v>11286</v>
       </c>
       <c r="H513">
         <v>0</v>
       </c>
       <c r="I513" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J513" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="L513" s="1">
-        <v>46288</v>
+        <v>46283</v>
       </c>
       <c r="N513" t="s">
         <v>213</v>
       </c>
       <c r="O513">
-        <v>18094910</v>
+        <v>18155336</v>
       </c>
       <c r="P513" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q513" t="s">
         <v>245</v>
       </c>
       <c r="R513" s="1">
-        <v>46280.66345891204</v>
+        <v>46280.59788275463</v>
       </c>
       <c r="S513">
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="T513" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="V513" t="s">
         <v>263</v>
@@ -36925,18 +36937,18 @@
         <v>420</v>
       </c>
       <c r="AG513" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AH513" t="s">
-        <v>419</v>
+        <v>434</v>
       </c>
     </row>
     <row r="514" spans="1:34">
       <c r="A514">
-        <v>6486</v>
+        <v>6704</v>
       </c>
       <c r="B514" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C514" t="s">
         <v>58</v>
@@ -36951,7 +36963,7 @@
         <v>64</v>
       </c>
       <c r="G514">
-        <v>11286</v>
+        <v>1788</v>
       </c>
       <c r="H514">
         <v>0</v>
@@ -36960,16 +36972,16 @@
         <v>71</v>
       </c>
       <c r="J514" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="L514" s="1">
-        <v>46283</v>
+        <v>46281</v>
       </c>
       <c r="N514" t="s">
         <v>213</v>
       </c>
       <c r="O514">
-        <v>18155336</v>
+        <v>18085132</v>
       </c>
       <c r="P514" t="s">
         <v>237</v>
@@ -36978,28 +36990,25 @@
         <v>245</v>
       </c>
       <c r="R514" s="1">
-        <v>46280.59788275463</v>
+        <v>46266.45957931713</v>
       </c>
       <c r="S514">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="T514" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="V514" t="s">
         <v>263</v>
       </c>
-      <c r="W514" t="s">
-        <v>388</v>
-      </c>
       <c r="AA514">
         <v>0</v>
       </c>
       <c r="AB514" t="s">
-        <v>420</v>
+        <v>237</v>
       </c>
       <c r="AG514" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AH514" t="s">
         <v>434</v>
@@ -37007,16 +37016,16 @@
     </row>
     <row r="515" spans="1:34">
       <c r="A515">
-        <v>6704</v>
+        <v>6404</v>
       </c>
       <c r="B515" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C515" t="s">
         <v>58</v>
       </c>
       <c r="D515" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E515" t="s">
         <v>62</v>
@@ -37025,7 +37034,7 @@
         <v>64</v>
       </c>
       <c r="G515">
-        <v>1788</v>
+        <v>1811</v>
       </c>
       <c r="H515">
         <v>0</v>
@@ -37034,16 +37043,16 @@
         <v>71</v>
       </c>
       <c r="J515" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="L515" s="1">
-        <v>46281</v>
+        <v>46290</v>
       </c>
       <c r="N515" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="O515">
-        <v>18085132</v>
+        <v>16962181</v>
       </c>
       <c r="P515" t="s">
         <v>237</v>
@@ -37052,25 +37061,22 @@
         <v>245</v>
       </c>
       <c r="R515" s="1">
-        <v>46266.45957931713</v>
+        <v>46240.6829959838</v>
       </c>
       <c r="S515">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="T515" t="s">
-        <v>254</v>
-      </c>
-      <c r="V515" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="AA515">
         <v>0</v>
       </c>
       <c r="AB515" t="s">
-        <v>237</v>
+        <v>417</v>
       </c>
       <c r="AG515" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AH515" t="s">
         <v>434</v>
@@ -37096,7 +37102,7 @@
         <v>64</v>
       </c>
       <c r="G516">
-        <v>1811</v>
+        <v>7025</v>
       </c>
       <c r="H516">
         <v>0</v>
@@ -37105,16 +37111,16 @@
         <v>71</v>
       </c>
       <c r="J516" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="L516" s="1">
-        <v>46290</v>
+        <v>46288</v>
       </c>
       <c r="N516" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="O516">
-        <v>16962181</v>
+        <v>16962338</v>
       </c>
       <c r="P516" t="s">
         <v>237</v>
@@ -37123,22 +37129,25 @@
         <v>245</v>
       </c>
       <c r="R516" s="1">
-        <v>46240.6829959838</v>
+        <v>46282.54038741898</v>
       </c>
       <c r="S516">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="T516" t="s">
         <v>257</v>
       </c>
+      <c r="W516" t="s">
+        <v>388</v>
+      </c>
       <c r="AA516">
         <v>0</v>
       </c>
       <c r="AB516" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="AG516" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AH516" t="s">
         <v>434</v>
@@ -37146,16 +37155,16 @@
     </row>
     <row r="517" spans="1:34">
       <c r="A517">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B517" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C517" t="s">
         <v>58</v>
       </c>
       <c r="D517" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E517" t="s">
         <v>62</v>
@@ -37164,7 +37173,7 @@
         <v>64</v>
       </c>
       <c r="G517">
-        <v>7025</v>
+        <v>1793</v>
       </c>
       <c r="H517">
         <v>0</v>
@@ -37173,16 +37182,19 @@
         <v>71</v>
       </c>
       <c r="J517" t="s">
-        <v>152</v>
+        <v>105</v>
       </c>
       <c r="L517" s="1">
-        <v>46288</v>
+        <v>46283</v>
+      </c>
+      <c r="M517" t="s">
+        <v>209</v>
       </c>
       <c r="N517" t="s">
         <v>213</v>
       </c>
       <c r="O517">
-        <v>16962338</v>
+        <v>17398945</v>
       </c>
       <c r="P517" t="s">
         <v>237</v>
@@ -37191,25 +37203,25 @@
         <v>245</v>
       </c>
       <c r="R517" s="1">
-        <v>46282.54038741898</v>
+        <v>46280.74859975695</v>
       </c>
       <c r="S517">
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="T517" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="W517" t="s">
-        <v>389</v>
+        <v>359</v>
       </c>
       <c r="AA517">
         <v>0</v>
       </c>
       <c r="AB517" t="s">
-        <v>420</v>
+        <v>237</v>
       </c>
       <c r="AG517" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AH517" t="s">
         <v>434</v>
@@ -37217,84 +37229,81 @@
     </row>
     <row r="518" spans="1:34">
       <c r="A518">
-        <v>5417</v>
+        <v>6628</v>
       </c>
       <c r="B518" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C518" t="s">
         <v>58</v>
       </c>
       <c r="D518" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E518" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F518" t="s">
         <v>64</v>
       </c>
       <c r="G518">
-        <v>1793</v>
+        <v>945</v>
       </c>
       <c r="H518">
         <v>0</v>
       </c>
       <c r="I518" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J518" t="s">
-        <v>105</v>
+        <v>174</v>
       </c>
       <c r="L518" s="1">
         <v>46283</v>
       </c>
-      <c r="M518" t="s">
-        <v>209</v>
-      </c>
       <c r="N518" t="s">
         <v>213</v>
       </c>
       <c r="O518">
-        <v>17398945</v>
+        <v>16959938</v>
       </c>
       <c r="P518" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q518" t="s">
         <v>245</v>
       </c>
       <c r="R518" s="1">
-        <v>46280.74859975695</v>
+        <v>46266.04180934028</v>
       </c>
       <c r="S518">
         <v>-1</v>
       </c>
       <c r="T518" t="s">
-        <v>253</v>
+        <v>249</v>
+      </c>
+      <c r="V518" t="s">
+        <v>263</v>
       </c>
       <c r="W518" t="s">
-        <v>359</v>
+        <v>389</v>
       </c>
       <c r="AA518">
         <v>0</v>
       </c>
       <c r="AB518" t="s">
-        <v>237</v>
+        <v>420</v>
       </c>
       <c r="AG518" t="s">
         <v>426</v>
       </c>
-      <c r="AH518" t="s">
-        <v>434</v>
-      </c>
     </row>
     <row r="519" spans="1:34">
       <c r="A519">
-        <v>6628</v>
+        <v>6705</v>
       </c>
       <c r="B519" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C519" t="s">
         <v>58</v>
@@ -37303,7 +37312,7 @@
         <v>60</v>
       </c>
       <c r="E519" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F519" t="s">
         <v>64</v>
@@ -37327,7 +37336,7 @@
         <v>213</v>
       </c>
       <c r="O519">
-        <v>16959938</v>
+        <v>17952524</v>
       </c>
       <c r="P519" t="s">
         <v>238</v>
@@ -37336,19 +37345,13 @@
         <v>245</v>
       </c>
       <c r="R519" s="1">
-        <v>46266.04180934028</v>
+        <v>46057.40119546296</v>
       </c>
       <c r="S519">
         <v>-1</v>
       </c>
       <c r="T519" t="s">
-        <v>249</v>
-      </c>
-      <c r="V519" t="s">
-        <v>263</v>
-      </c>
-      <c r="W519" t="s">
-        <v>390</v>
+        <v>254</v>
       </c>
       <c r="AA519">
         <v>0</v>
@@ -37362,10 +37365,10 @@
     </row>
     <row r="520" spans="1:34">
       <c r="A520">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B520" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C520" t="s">
         <v>58</v>
@@ -37398,7 +37401,7 @@
         <v>213</v>
       </c>
       <c r="O520">
-        <v>17952524</v>
+        <v>18056695</v>
       </c>
       <c r="P520" t="s">
         <v>238</v>
@@ -37407,7 +37410,7 @@
         <v>245</v>
       </c>
       <c r="R520" s="1">
-        <v>46057.40119546296</v>
+        <v>46266.08343295139</v>
       </c>
       <c r="S520">
         <v>-1</v>
@@ -37415,6 +37418,12 @@
       <c r="T520" t="s">
         <v>254</v>
       </c>
+      <c r="V520" t="s">
+        <v>263</v>
+      </c>
+      <c r="W520" t="s">
+        <v>390</v>
+      </c>
       <c r="AA520">
         <v>0</v>
       </c>
@@ -37427,10 +37436,10 @@
     </row>
     <row r="521" spans="1:34">
       <c r="A521">
-        <v>6779</v>
+        <v>6945</v>
       </c>
       <c r="B521" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C521" t="s">
         <v>58</v>
@@ -37442,7 +37451,7 @@
         <v>62</v>
       </c>
       <c r="F521" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G521">
         <v>945</v>
@@ -37463,7 +37472,7 @@
         <v>213</v>
       </c>
       <c r="O521">
-        <v>18056695</v>
+        <v>18164487</v>
       </c>
       <c r="P521" t="s">
         <v>238</v>
@@ -37472,16 +37481,13 @@
         <v>245</v>
       </c>
       <c r="R521" s="1">
-        <v>46266.08343295139</v>
+        <v>46266.08344398148</v>
       </c>
       <c r="S521">
         <v>-1</v>
       </c>
       <c r="T521" t="s">
-        <v>254</v>
-      </c>
-      <c r="V521" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="W521" t="s">
         <v>391</v>
@@ -37498,25 +37504,25 @@
     </row>
     <row r="522" spans="1:34">
       <c r="A522">
-        <v>6945</v>
+        <v>5417</v>
       </c>
       <c r="B522" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C522" t="s">
         <v>58</v>
       </c>
       <c r="D522" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E522" t="s">
         <v>62</v>
       </c>
       <c r="F522" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G522">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H522">
         <v>0</v>
@@ -37525,7 +37531,7 @@
         <v>72</v>
       </c>
       <c r="J522" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="L522" s="1">
         <v>46283</v>
@@ -37534,7 +37540,7 @@
         <v>213</v>
       </c>
       <c r="O522">
-        <v>18164487</v>
+        <v>17398869</v>
       </c>
       <c r="P522" t="s">
         <v>238</v>
@@ -37543,13 +37549,13 @@
         <v>245</v>
       </c>
       <c r="R522" s="1">
-        <v>46266.08344398148</v>
+        <v>46266.25077376157</v>
       </c>
       <c r="S522">
         <v>-1</v>
       </c>
       <c r="T522" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="W522" t="s">
         <v>392</v>
@@ -37566,10 +37572,10 @@
     </row>
     <row r="523" spans="1:34">
       <c r="A523">
-        <v>5417</v>
+        <v>6278</v>
       </c>
       <c r="B523" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C523" t="s">
         <v>58</v>
@@ -37602,25 +37608,22 @@
         <v>213</v>
       </c>
       <c r="O523">
-        <v>17398869</v>
-      </c>
-      <c r="P523" t="s">
-        <v>238</v>
+        <v>17539710</v>
       </c>
       <c r="Q523" t="s">
         <v>245</v>
       </c>
       <c r="R523" s="1">
-        <v>46266.25077376157</v>
+        <v>46023.15052320602</v>
       </c>
       <c r="S523">
         <v>-1</v>
       </c>
       <c r="T523" t="s">
-        <v>253</v>
-      </c>
-      <c r="W523" t="s">
-        <v>393</v>
+        <v>259</v>
+      </c>
+      <c r="V523" t="s">
+        <v>263</v>
       </c>
       <c r="AA523">
         <v>0</v>
@@ -37634,16 +37637,16 @@
     </row>
     <row r="524" spans="1:34">
       <c r="A524">
-        <v>6278</v>
+        <v>6404</v>
       </c>
       <c r="B524" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C524" t="s">
         <v>58</v>
       </c>
       <c r="D524" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E524" t="s">
         <v>62</v>
@@ -37670,22 +37673,25 @@
         <v>213</v>
       </c>
       <c r="O524">
-        <v>17539710</v>
+        <v>16962093</v>
+      </c>
+      <c r="P524" t="s">
+        <v>238</v>
       </c>
       <c r="Q524" t="s">
         <v>245</v>
       </c>
       <c r="R524" s="1">
-        <v>46023.15052320602</v>
+        <v>46266.25004302083</v>
       </c>
       <c r="S524">
         <v>-1</v>
       </c>
       <c r="T524" t="s">
-        <v>259</v>
-      </c>
-      <c r="V524" t="s">
-        <v>263</v>
+        <v>257</v>
+      </c>
+      <c r="W524" t="s">
+        <v>393</v>
       </c>
       <c r="AA524">
         <v>0</v>
@@ -37699,10 +37705,10 @@
     </row>
     <row r="525" spans="1:34">
       <c r="A525">
-        <v>6404</v>
+        <v>6703</v>
       </c>
       <c r="B525" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C525" t="s">
         <v>58</v>
@@ -37735,7 +37741,7 @@
         <v>213</v>
       </c>
       <c r="O525">
-        <v>16962093</v>
+        <v>17941132</v>
       </c>
       <c r="P525" t="s">
         <v>238</v>
@@ -37744,13 +37750,13 @@
         <v>245</v>
       </c>
       <c r="R525" s="1">
-        <v>46266.25004302083</v>
+        <v>46266.25135543982</v>
       </c>
       <c r="S525">
         <v>-1</v>
       </c>
       <c r="T525" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="W525" t="s">
         <v>394</v>
@@ -37767,16 +37773,16 @@
     </row>
     <row r="526" spans="1:34">
       <c r="A526">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B526" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C526" t="s">
         <v>58</v>
       </c>
       <c r="D526" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E526" t="s">
         <v>62</v>
@@ -37803,7 +37809,7 @@
         <v>213</v>
       </c>
       <c r="O526">
-        <v>17941132</v>
+        <v>17952325</v>
       </c>
       <c r="P526" t="s">
         <v>238</v>
@@ -37812,16 +37818,16 @@
         <v>245</v>
       </c>
       <c r="R526" s="1">
-        <v>46266.25135543982</v>
+        <v>46057.39078453703</v>
       </c>
       <c r="S526">
         <v>-1</v>
       </c>
       <c r="T526" t="s">
-        <v>256</v>
-      </c>
-      <c r="W526" t="s">
-        <v>395</v>
+        <v>254</v>
+      </c>
+      <c r="V526" t="s">
+        <v>263</v>
       </c>
       <c r="AA526">
         <v>0</v>
@@ -37835,10 +37841,10 @@
     </row>
     <row r="527" spans="1:34">
       <c r="A527">
-        <v>6704</v>
+        <v>5417</v>
       </c>
       <c r="B527" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C527" t="s">
         <v>58</v>
@@ -37853,7 +37859,7 @@
         <v>64</v>
       </c>
       <c r="G527">
-        <v>946</v>
+        <v>953</v>
       </c>
       <c r="H527">
         <v>0</v>
@@ -37862,16 +37868,16 @@
         <v>72</v>
       </c>
       <c r="J527" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="L527" s="1">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="N527" t="s">
         <v>213</v>
       </c>
       <c r="O527">
-        <v>17952325</v>
+        <v>17398883</v>
       </c>
       <c r="P527" t="s">
         <v>238</v>
@@ -37880,16 +37886,16 @@
         <v>245</v>
       </c>
       <c r="R527" s="1">
-        <v>46057.39078453703</v>
+        <v>46266.25305</v>
       </c>
       <c r="S527">
-        <v>-1</v>
+        <v>-8</v>
       </c>
       <c r="T527" t="s">
-        <v>254</v>
-      </c>
-      <c r="V527" t="s">
-        <v>263</v>
+        <v>253</v>
+      </c>
+      <c r="W527" t="s">
+        <v>395</v>
       </c>
       <c r="AA527">
         <v>0</v>
@@ -37903,10 +37909,10 @@
     </row>
     <row r="528" spans="1:34">
       <c r="A528">
-        <v>5417</v>
+        <v>6278</v>
       </c>
       <c r="B528" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C528" t="s">
         <v>58</v>
@@ -37939,25 +37945,22 @@
         <v>213</v>
       </c>
       <c r="O528">
-        <v>17398883</v>
-      </c>
-      <c r="P528" t="s">
-        <v>238</v>
+        <v>17539724</v>
       </c>
       <c r="Q528" t="s">
         <v>245</v>
       </c>
       <c r="R528" s="1">
-        <v>46266.25305</v>
+        <v>46023.15053086806</v>
       </c>
       <c r="S528">
         <v>-8</v>
       </c>
       <c r="T528" t="s">
-        <v>253</v>
-      </c>
-      <c r="W528" t="s">
-        <v>396</v>
+        <v>259</v>
+      </c>
+      <c r="V528" t="s">
+        <v>263</v>
       </c>
       <c r="AA528">
         <v>0</v>
@@ -37971,16 +37974,16 @@
     </row>
     <row r="529" spans="1:33">
       <c r="A529">
-        <v>6278</v>
+        <v>6404</v>
       </c>
       <c r="B529" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C529" t="s">
         <v>58</v>
       </c>
       <c r="D529" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E529" t="s">
         <v>62</v>
@@ -38007,22 +38010,25 @@
         <v>213</v>
       </c>
       <c r="O529">
-        <v>17539724</v>
+        <v>16962107</v>
+      </c>
+      <c r="P529" t="s">
+        <v>238</v>
       </c>
       <c r="Q529" t="s">
         <v>245</v>
       </c>
       <c r="R529" s="1">
-        <v>46023.15053086806</v>
+        <v>46266.25270034722</v>
       </c>
       <c r="S529">
         <v>-8</v>
       </c>
       <c r="T529" t="s">
-        <v>259</v>
-      </c>
-      <c r="V529" t="s">
-        <v>263</v>
+        <v>257</v>
+      </c>
+      <c r="W529" t="s">
+        <v>396</v>
       </c>
       <c r="AA529">
         <v>0</v>
@@ -38036,19 +38042,19 @@
     </row>
     <row r="530" spans="1:33">
       <c r="A530">
-        <v>6404</v>
+        <v>6627</v>
       </c>
       <c r="B530" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C530" t="s">
         <v>58</v>
       </c>
       <c r="D530" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E530" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F530" t="s">
         <v>64</v>
@@ -38072,7 +38078,7 @@
         <v>213</v>
       </c>
       <c r="O530">
-        <v>16962107</v>
+        <v>17042317</v>
       </c>
       <c r="P530" t="s">
         <v>238</v>
@@ -38081,13 +38087,16 @@
         <v>245</v>
       </c>
       <c r="R530" s="1">
-        <v>46266.25270034722</v>
+        <v>46266.25274991898</v>
       </c>
       <c r="S530">
         <v>-8</v>
       </c>
       <c r="T530" t="s">
-        <v>257</v>
+        <v>249</v>
+      </c>
+      <c r="V530" t="s">
+        <v>263</v>
       </c>
       <c r="W530" t="s">
         <v>397</v>
@@ -38104,19 +38113,19 @@
     </row>
     <row r="531" spans="1:33">
       <c r="A531">
-        <v>6627</v>
+        <v>6703</v>
       </c>
       <c r="B531" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C531" t="s">
         <v>58</v>
       </c>
       <c r="D531" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E531" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F531" t="s">
         <v>64</v>
@@ -38140,7 +38149,7 @@
         <v>213</v>
       </c>
       <c r="O531">
-        <v>17042317</v>
+        <v>17941166</v>
       </c>
       <c r="P531" t="s">
         <v>238</v>
@@ -38149,16 +38158,13 @@
         <v>245</v>
       </c>
       <c r="R531" s="1">
-        <v>46266.25274991898</v>
+        <v>46266.25364633102</v>
       </c>
       <c r="S531">
         <v>-8</v>
       </c>
       <c r="T531" t="s">
-        <v>249</v>
-      </c>
-      <c r="V531" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="W531" t="s">
         <v>398</v>
@@ -38175,16 +38181,16 @@
     </row>
     <row r="532" spans="1:33">
       <c r="A532">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B532" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C532" t="s">
         <v>58</v>
       </c>
       <c r="D532" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E532" t="s">
         <v>62</v>
@@ -38211,7 +38217,7 @@
         <v>213</v>
       </c>
       <c r="O532">
-        <v>17941166</v>
+        <v>17952362</v>
       </c>
       <c r="P532" t="s">
         <v>238</v>
@@ -38220,16 +38226,16 @@
         <v>245</v>
       </c>
       <c r="R532" s="1">
-        <v>46266.25364633102</v>
+        <v>46057.39080065972</v>
       </c>
       <c r="S532">
         <v>-8</v>
       </c>
       <c r="T532" t="s">
-        <v>256</v>
-      </c>
-      <c r="W532" t="s">
-        <v>399</v>
+        <v>254</v>
+      </c>
+      <c r="V532" t="s">
+        <v>263</v>
       </c>
       <c r="AA532">
         <v>0</v>
@@ -38243,10 +38249,10 @@
     </row>
     <row r="533" spans="1:33">
       <c r="A533">
-        <v>6704</v>
+        <v>6949</v>
       </c>
       <c r="B533" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C533" t="s">
         <v>58</v>
@@ -38258,7 +38264,7 @@
         <v>62</v>
       </c>
       <c r="F533" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G533">
         <v>953</v>
@@ -38279,7 +38285,7 @@
         <v>213</v>
       </c>
       <c r="O533">
-        <v>17952362</v>
+        <v>18178144</v>
       </c>
       <c r="P533" t="s">
         <v>238</v>
@@ -38288,16 +38294,16 @@
         <v>245</v>
       </c>
       <c r="R533" s="1">
-        <v>46057.39080065972</v>
+        <v>46266.25369826389</v>
       </c>
       <c r="S533">
         <v>-8</v>
       </c>
       <c r="T533" t="s">
-        <v>254</v>
-      </c>
-      <c r="V533" t="s">
-        <v>263</v>
+        <v>251</v>
+      </c>
+      <c r="W533" t="s">
+        <v>399</v>
       </c>
       <c r="AA533">
         <v>0</v>
@@ -38311,16 +38317,16 @@
     </row>
     <row r="534" spans="1:33">
       <c r="A534">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B534" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C534" t="s">
         <v>58</v>
       </c>
       <c r="D534" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E534" t="s">
         <v>62</v>
@@ -38347,7 +38353,7 @@
         <v>213</v>
       </c>
       <c r="O534">
-        <v>18178144</v>
+        <v>18188731</v>
       </c>
       <c r="P534" t="s">
         <v>238</v>
@@ -38356,16 +38362,13 @@
         <v>245</v>
       </c>
       <c r="R534" s="1">
-        <v>46266.25369826389</v>
+        <v>46192.5668585301</v>
       </c>
       <c r="S534">
         <v>-8</v>
       </c>
       <c r="T534" t="s">
-        <v>251</v>
-      </c>
-      <c r="W534" t="s">
-        <v>400</v>
+        <v>252</v>
       </c>
       <c r="AA534">
         <v>0</v>
@@ -38379,10 +38382,10 @@
     </row>
     <row r="535" spans="1:33">
       <c r="A535">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B535" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C535" t="s">
         <v>58</v>
@@ -38415,7 +38418,7 @@
         <v>213</v>
       </c>
       <c r="O535">
-        <v>18188731</v>
+        <v>18188637</v>
       </c>
       <c r="P535" t="s">
         <v>238</v>
@@ -38424,7 +38427,7 @@
         <v>245</v>
       </c>
       <c r="R535" s="1">
-        <v>46192.5668585301</v>
+        <v>46192.56339922453</v>
       </c>
       <c r="S535">
         <v>-8</v>
@@ -38444,25 +38447,25 @@
     </row>
     <row r="536" spans="1:33">
       <c r="A536">
-        <v>6963</v>
+        <v>5417</v>
       </c>
       <c r="B536" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C536" t="s">
         <v>58</v>
       </c>
       <c r="D536" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E536" t="s">
         <v>62</v>
       </c>
       <c r="F536" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G536">
-        <v>953</v>
+        <v>7022</v>
       </c>
       <c r="H536">
         <v>0</v>
@@ -38471,16 +38474,16 @@
         <v>72</v>
       </c>
       <c r="J536" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="L536" s="1">
-        <v>46290</v>
+        <v>46283</v>
       </c>
       <c r="N536" t="s">
         <v>213</v>
       </c>
       <c r="O536">
-        <v>18188637</v>
+        <v>17399270</v>
       </c>
       <c r="P536" t="s">
         <v>238</v>
@@ -38489,13 +38492,16 @@
         <v>245</v>
       </c>
       <c r="R536" s="1">
-        <v>46192.56339922453</v>
+        <v>46266.25305112269</v>
       </c>
       <c r="S536">
-        <v>-8</v>
+        <v>-1</v>
       </c>
       <c r="T536" t="s">
-        <v>252</v>
+        <v>253</v>
+      </c>
+      <c r="W536" t="s">
+        <v>400</v>
       </c>
       <c r="AA536">
         <v>0</v>
@@ -38509,10 +38515,10 @@
     </row>
     <row r="537" spans="1:33">
       <c r="A537">
-        <v>5417</v>
+        <v>6627</v>
       </c>
       <c r="B537" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C537" t="s">
         <v>58</v>
@@ -38521,7 +38527,7 @@
         <v>59</v>
       </c>
       <c r="E537" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F537" t="s">
         <v>64</v>
@@ -38545,7 +38551,7 @@
         <v>213</v>
       </c>
       <c r="O537">
-        <v>17399270</v>
+        <v>17042505</v>
       </c>
       <c r="P537" t="s">
         <v>238</v>
@@ -38554,13 +38560,16 @@
         <v>245</v>
       </c>
       <c r="R537" s="1">
-        <v>46266.25305112269</v>
+        <v>46266.25275173611</v>
       </c>
       <c r="S537">
         <v>-1</v>
       </c>
       <c r="T537" t="s">
-        <v>253</v>
+        <v>249</v>
+      </c>
+      <c r="V537" t="s">
+        <v>263</v>
       </c>
       <c r="W537" t="s">
         <v>401</v>
@@ -38577,10 +38586,10 @@
     </row>
     <row r="538" spans="1:33">
       <c r="A538">
-        <v>6627</v>
+        <v>6704</v>
       </c>
       <c r="B538" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C538" t="s">
         <v>58</v>
@@ -38589,7 +38598,7 @@
         <v>59</v>
       </c>
       <c r="E538" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F538" t="s">
         <v>64</v>
@@ -38613,7 +38622,7 @@
         <v>213</v>
       </c>
       <c r="O538">
-        <v>17042505</v>
+        <v>17952421</v>
       </c>
       <c r="P538" t="s">
         <v>238</v>
@@ -38622,13 +38631,13 @@
         <v>245</v>
       </c>
       <c r="R538" s="1">
-        <v>46266.25275173611</v>
+        <v>46266.25364869213</v>
       </c>
       <c r="S538">
         <v>-1</v>
       </c>
       <c r="T538" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="V538" t="s">
         <v>263</v>
@@ -38648,22 +38657,22 @@
     </row>
     <row r="539" spans="1:33">
       <c r="A539">
-        <v>6704</v>
+        <v>6945</v>
       </c>
       <c r="B539" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C539" t="s">
         <v>58</v>
       </c>
       <c r="D539" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E539" t="s">
         <v>62</v>
       </c>
       <c r="F539" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G539">
         <v>7022</v>
@@ -38684,7 +38693,7 @@
         <v>213</v>
       </c>
       <c r="O539">
-        <v>17952421</v>
+        <v>18164536</v>
       </c>
       <c r="P539" t="s">
         <v>238</v>
@@ -38693,19 +38702,13 @@
         <v>245</v>
       </c>
       <c r="R539" s="1">
-        <v>46266.25364869213</v>
+        <v>46168.72822087963</v>
       </c>
       <c r="S539">
         <v>-1</v>
       </c>
       <c r="T539" t="s">
-        <v>254</v>
-      </c>
-      <c r="V539" t="s">
-        <v>263</v>
-      </c>
-      <c r="W539" t="s">
-        <v>403</v>
+        <v>250</v>
       </c>
       <c r="AA539">
         <v>0</v>
@@ -38719,16 +38722,16 @@
     </row>
     <row r="540" spans="1:33">
       <c r="A540">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B540" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C540" t="s">
         <v>58</v>
       </c>
       <c r="D540" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E540" t="s">
         <v>62</v>
@@ -38755,7 +38758,7 @@
         <v>213</v>
       </c>
       <c r="O540">
-        <v>18164536</v>
+        <v>18178174</v>
       </c>
       <c r="P540" t="s">
         <v>238</v>
@@ -38764,13 +38767,16 @@
         <v>245</v>
       </c>
       <c r="R540" s="1">
-        <v>46168.72822087963</v>
+        <v>46266.25369988426</v>
       </c>
       <c r="S540">
         <v>-1</v>
       </c>
       <c r="T540" t="s">
-        <v>250</v>
+        <v>251</v>
+      </c>
+      <c r="W540" t="s">
+        <v>403</v>
       </c>
       <c r="AA540">
         <v>0</v>
@@ -38784,16 +38790,16 @@
     </row>
     <row r="541" spans="1:33">
       <c r="A541">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B541" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C541" t="s">
         <v>58</v>
       </c>
       <c r="D541" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E541" t="s">
         <v>62</v>
@@ -38820,7 +38826,7 @@
         <v>213</v>
       </c>
       <c r="O541">
-        <v>18178174</v>
+        <v>18188759</v>
       </c>
       <c r="P541" t="s">
         <v>238</v>
@@ -38829,16 +38835,13 @@
         <v>245</v>
       </c>
       <c r="R541" s="1">
-        <v>46266.25369988426</v>
+        <v>46192.56687822917</v>
       </c>
       <c r="S541">
         <v>-1</v>
       </c>
       <c r="T541" t="s">
-        <v>251</v>
-      </c>
-      <c r="W541" t="s">
-        <v>404</v>
+        <v>252</v>
       </c>
       <c r="AA541">
         <v>0</v>
@@ -38852,10 +38855,10 @@
     </row>
     <row r="542" spans="1:33">
       <c r="A542">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B542" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C542" t="s">
         <v>58</v>
@@ -38888,7 +38891,7 @@
         <v>213</v>
       </c>
       <c r="O542">
-        <v>18188759</v>
+        <v>18188665</v>
       </c>
       <c r="P542" t="s">
         <v>238</v>
@@ -38897,7 +38900,7 @@
         <v>245</v>
       </c>
       <c r="R542" s="1">
-        <v>46192.56687822917</v>
+        <v>46192.56342662037</v>
       </c>
       <c r="S542">
         <v>-1</v>
@@ -38917,25 +38920,25 @@
     </row>
     <row r="543" spans="1:33">
       <c r="A543">
-        <v>6963</v>
+        <v>5417</v>
       </c>
       <c r="B543" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C543" t="s">
         <v>58</v>
       </c>
       <c r="D543" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E543" t="s">
         <v>62</v>
       </c>
       <c r="F543" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G543">
-        <v>7022</v>
+        <v>9086</v>
       </c>
       <c r="H543">
         <v>0</v>
@@ -38944,16 +38947,19 @@
         <v>72</v>
       </c>
       <c r="J543" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="L543" s="1">
-        <v>46283</v>
+        <v>46282</v>
+      </c>
+      <c r="M543" t="s">
+        <v>207</v>
       </c>
       <c r="N543" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O543">
-        <v>18188665</v>
+        <v>17399363</v>
       </c>
       <c r="P543" t="s">
         <v>238</v>
@@ -38962,36 +38968,39 @@
         <v>245</v>
       </c>
       <c r="R543" s="1">
-        <v>46192.56342662037</v>
+        <v>46282.36440621527</v>
       </c>
       <c r="S543">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T543" t="s">
-        <v>252</v>
+        <v>253</v>
+      </c>
+      <c r="W543" t="s">
+        <v>404</v>
       </c>
       <c r="AA543">
         <v>0</v>
       </c>
       <c r="AB543" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG543" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="544" spans="1:33">
       <c r="A544">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B544" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C544" t="s">
         <v>58</v>
       </c>
       <c r="D544" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E544" t="s">
         <v>62</v>
@@ -39021,7 +39030,7 @@
         <v>214</v>
       </c>
       <c r="O544">
-        <v>17399363</v>
+        <v>16962380</v>
       </c>
       <c r="P544" t="s">
         <v>238</v>
@@ -39030,16 +39039,16 @@
         <v>245</v>
       </c>
       <c r="R544" s="1">
-        <v>46282.36440621527</v>
+        <v>46282.36462596065</v>
       </c>
       <c r="S544">
         <v>0</v>
       </c>
       <c r="T544" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="W544" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AA544">
         <v>0</v>
@@ -39053,16 +39062,16 @@
     </row>
     <row r="545" spans="1:33">
       <c r="A545">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B545" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C545" t="s">
         <v>58</v>
       </c>
       <c r="D545" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E545" t="s">
         <v>62</v>
@@ -39092,7 +39101,7 @@
         <v>214</v>
       </c>
       <c r="O545">
-        <v>16962380</v>
+        <v>16976270</v>
       </c>
       <c r="P545" t="s">
         <v>238</v>
@@ -39101,16 +39110,19 @@
         <v>245</v>
       </c>
       <c r="R545" s="1">
-        <v>46282.36462596065</v>
+        <v>46282.36464421296</v>
       </c>
       <c r="S545">
         <v>0</v>
       </c>
       <c r="T545" t="s">
-        <v>257</v>
+        <v>255</v>
+      </c>
+      <c r="V545" t="s">
+        <v>263</v>
       </c>
       <c r="W545" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AA545">
         <v>0</v>
@@ -39124,10 +39136,10 @@
     </row>
     <row r="546" spans="1:33">
       <c r="A546">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B546" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C546" t="s">
         <v>58</v>
@@ -39163,7 +39175,7 @@
         <v>214</v>
       </c>
       <c r="O546">
-        <v>16976270</v>
+        <v>17222865</v>
       </c>
       <c r="P546" t="s">
         <v>238</v>
@@ -39172,19 +39184,19 @@
         <v>245</v>
       </c>
       <c r="R546" s="1">
-        <v>46282.36464421296</v>
+        <v>46282.36467337963</v>
       </c>
       <c r="S546">
         <v>0</v>
       </c>
       <c r="T546" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="V546" t="s">
         <v>263</v>
       </c>
       <c r="W546" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AA546">
         <v>0</v>
@@ -39198,10 +39210,10 @@
     </row>
     <row r="547" spans="1:33">
       <c r="A547">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B547" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C547" t="s">
         <v>58</v>
@@ -39210,7 +39222,7 @@
         <v>59</v>
       </c>
       <c r="E547" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F547" t="s">
         <v>64</v>
@@ -39237,7 +39249,7 @@
         <v>214</v>
       </c>
       <c r="O547">
-        <v>17222865</v>
+        <v>17042587</v>
       </c>
       <c r="P547" t="s">
         <v>238</v>
@@ -39246,19 +39258,19 @@
         <v>245</v>
       </c>
       <c r="R547" s="1">
-        <v>46282.36467337963</v>
+        <v>46282.36469679398</v>
       </c>
       <c r="S547">
         <v>0</v>
       </c>
       <c r="T547" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="V547" t="s">
         <v>263</v>
       </c>
       <c r="W547" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AA547">
         <v>0</v>
@@ -39272,16 +39284,16 @@
     </row>
     <row r="548" spans="1:33">
       <c r="A548">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B548" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C548" t="s">
         <v>58</v>
       </c>
       <c r="D548" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E548" t="s">
         <v>63</v>
@@ -39311,7 +39323,7 @@
         <v>214</v>
       </c>
       <c r="O548">
-        <v>17042587</v>
+        <v>16960074</v>
       </c>
       <c r="P548" t="s">
         <v>238</v>
@@ -39320,7 +39332,7 @@
         <v>245</v>
       </c>
       <c r="R548" s="1">
-        <v>46282.36469679398</v>
+        <v>46282.36469869213</v>
       </c>
       <c r="S548">
         <v>0</v>
@@ -39332,7 +39344,7 @@
         <v>263</v>
       </c>
       <c r="W548" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AA548">
         <v>0</v>
@@ -39346,19 +39358,19 @@
     </row>
     <row r="549" spans="1:33">
       <c r="A549">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B549" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C549" t="s">
         <v>58</v>
       </c>
       <c r="D549" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E549" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F549" t="s">
         <v>64</v>
@@ -39385,7 +39397,7 @@
         <v>214</v>
       </c>
       <c r="O549">
-        <v>16960074</v>
+        <v>17941217</v>
       </c>
       <c r="P549" t="s">
         <v>238</v>
@@ -39394,19 +39406,16 @@
         <v>245</v>
       </c>
       <c r="R549" s="1">
-        <v>46282.36469869213</v>
+        <v>46282.36473159722</v>
       </c>
       <c r="S549">
         <v>0</v>
       </c>
       <c r="T549" t="s">
-        <v>249</v>
-      </c>
-      <c r="V549" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="W549" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AA549">
         <v>0</v>
@@ -39420,16 +39429,16 @@
     </row>
     <row r="550" spans="1:33">
       <c r="A550">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B550" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C550" t="s">
         <v>58</v>
       </c>
       <c r="D550" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E550" t="s">
         <v>62</v>
@@ -39459,7 +39468,7 @@
         <v>214</v>
       </c>
       <c r="O550">
-        <v>17941217</v>
+        <v>17952444</v>
       </c>
       <c r="P550" t="s">
         <v>238</v>
@@ -39468,16 +39477,19 @@
         <v>245</v>
       </c>
       <c r="R550" s="1">
-        <v>46282.36473159722</v>
+        <v>46282.36473394676</v>
       </c>
       <c r="S550">
         <v>0</v>
       </c>
       <c r="T550" t="s">
-        <v>256</v>
+        <v>254</v>
+      </c>
+      <c r="V550" t="s">
+        <v>263</v>
       </c>
       <c r="W550" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AA550">
         <v>0</v>
@@ -39491,16 +39503,16 @@
     </row>
     <row r="551" spans="1:33">
       <c r="A551">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B551" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C551" t="s">
         <v>58</v>
       </c>
       <c r="D551" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E551" t="s">
         <v>62</v>
@@ -39530,7 +39542,7 @@
         <v>214</v>
       </c>
       <c r="O551">
-        <v>17952444</v>
+        <v>17952624</v>
       </c>
       <c r="P551" t="s">
         <v>238</v>
@@ -39539,7 +39551,7 @@
         <v>245</v>
       </c>
       <c r="R551" s="1">
-        <v>46282.36473394676</v>
+        <v>46282.36473579861</v>
       </c>
       <c r="S551">
         <v>0</v>
@@ -39547,11 +39559,8 @@
       <c r="T551" t="s">
         <v>254</v>
       </c>
-      <c r="V551" t="s">
-        <v>263</v>
-      </c>
       <c r="W551" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AA551">
         <v>0</v>
@@ -39565,10 +39574,10 @@
     </row>
     <row r="552" spans="1:33">
       <c r="A552">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B552" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C552" t="s">
         <v>58</v>
@@ -39604,7 +39613,7 @@
         <v>214</v>
       </c>
       <c r="O552">
-        <v>17952624</v>
+        <v>18056801</v>
       </c>
       <c r="P552" t="s">
         <v>238</v>
@@ -39613,7 +39622,7 @@
         <v>245</v>
       </c>
       <c r="R552" s="1">
-        <v>46282.36473579861</v>
+        <v>46282.36475297454</v>
       </c>
       <c r="S552">
         <v>0</v>
@@ -39621,8 +39630,11 @@
       <c r="T552" t="s">
         <v>254</v>
       </c>
+      <c r="V552" t="s">
+        <v>263</v>
+      </c>
       <c r="W552" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AA552">
         <v>0</v>
@@ -39636,10 +39648,10 @@
     </row>
     <row r="553" spans="1:33">
       <c r="A553">
-        <v>6779</v>
+        <v>6945</v>
       </c>
       <c r="B553" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C553" t="s">
         <v>58</v>
@@ -39651,7 +39663,7 @@
         <v>62</v>
       </c>
       <c r="F553" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G553">
         <v>9086</v>
@@ -39675,7 +39687,7 @@
         <v>214</v>
       </c>
       <c r="O553">
-        <v>18056801</v>
+        <v>18164551</v>
       </c>
       <c r="P553" t="s">
         <v>238</v>
@@ -39684,19 +39696,16 @@
         <v>245</v>
       </c>
       <c r="R553" s="1">
-        <v>46282.36475297454</v>
+        <v>46282.36486408565</v>
       </c>
       <c r="S553">
         <v>0</v>
       </c>
       <c r="T553" t="s">
-        <v>254</v>
-      </c>
-      <c r="V553" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="W553" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AA553">
         <v>0</v>
@@ -39710,16 +39719,16 @@
     </row>
     <row r="554" spans="1:33">
       <c r="A554">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B554" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C554" t="s">
         <v>58</v>
       </c>
       <c r="D554" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E554" t="s">
         <v>62</v>
@@ -39749,7 +39758,7 @@
         <v>214</v>
       </c>
       <c r="O554">
-        <v>18164551</v>
+        <v>18178187</v>
       </c>
       <c r="P554" t="s">
         <v>238</v>
@@ -39758,13 +39767,13 @@
         <v>245</v>
       </c>
       <c r="R554" s="1">
-        <v>46282.36486408565</v>
+        <v>46282.36487561343</v>
       </c>
       <c r="S554">
         <v>0</v>
       </c>
       <c r="T554" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="W554" t="s">
         <v>405</v>
@@ -39781,16 +39790,16 @@
     </row>
     <row r="555" spans="1:33">
       <c r="A555">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B555" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C555" t="s">
         <v>58</v>
       </c>
       <c r="D555" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E555" t="s">
         <v>62</v>
@@ -39820,7 +39829,7 @@
         <v>214</v>
       </c>
       <c r="O555">
-        <v>18178187</v>
+        <v>18188774</v>
       </c>
       <c r="P555" t="s">
         <v>238</v>
@@ -39829,16 +39838,16 @@
         <v>245</v>
       </c>
       <c r="R555" s="1">
-        <v>46282.36487561343</v>
+        <v>46282.36486778935</v>
       </c>
       <c r="S555">
         <v>0</v>
       </c>
       <c r="T555" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="W555" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AA555">
         <v>0</v>
@@ -39852,10 +39861,10 @@
     </row>
     <row r="556" spans="1:33">
       <c r="A556">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B556" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C556" t="s">
         <v>58</v>
@@ -39891,7 +39900,7 @@
         <v>214</v>
       </c>
       <c r="O556">
-        <v>18188774</v>
+        <v>18188680</v>
       </c>
       <c r="P556" t="s">
         <v>238</v>
@@ -39900,7 +39909,7 @@
         <v>245</v>
       </c>
       <c r="R556" s="1">
-        <v>46282.36486778935</v>
+        <v>46282.36486851852</v>
       </c>
       <c r="S556">
         <v>0</v>
@@ -39909,7 +39918,7 @@
         <v>252</v>
       </c>
       <c r="W556" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AA556">
         <v>0</v>
@@ -39923,64 +39932,64 @@
     </row>
     <row r="557" spans="1:33">
       <c r="A557">
-        <v>6963</v>
+        <v>5417</v>
       </c>
       <c r="B557" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C557" t="s">
         <v>58</v>
       </c>
       <c r="D557" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E557" t="s">
         <v>62</v>
       </c>
       <c r="F557" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G557">
-        <v>9086</v>
+        <v>9088</v>
       </c>
       <c r="H557">
         <v>0</v>
       </c>
       <c r="I557" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J557" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L557" s="1">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="M557" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N557" t="s">
         <v>214</v>
       </c>
       <c r="O557">
-        <v>18188680</v>
+        <v>17399383</v>
       </c>
       <c r="P557" t="s">
-        <v>238</v>
+        <v>62</v>
       </c>
       <c r="Q557" t="s">
         <v>245</v>
       </c>
       <c r="R557" s="1">
-        <v>46282.36486851852</v>
+        <v>46282.3651903588</v>
       </c>
       <c r="S557">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T557" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="W557" t="s">
-        <v>405</v>
+        <v>362</v>
       </c>
       <c r="AA557">
         <v>0</v>
@@ -39994,16 +40003,16 @@
     </row>
     <row r="558" spans="1:33">
       <c r="A558">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B558" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C558" t="s">
         <v>58</v>
       </c>
       <c r="D558" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E558" t="s">
         <v>62</v>
@@ -40033,7 +40042,7 @@
         <v>214</v>
       </c>
       <c r="O558">
-        <v>17399383</v>
+        <v>16962400</v>
       </c>
       <c r="P558" t="s">
         <v>62</v>
@@ -40042,13 +40051,13 @@
         <v>245</v>
       </c>
       <c r="R558" s="1">
-        <v>46282.3651903588</v>
+        <v>46282.36525856482</v>
       </c>
       <c r="S558">
         <v>-1</v>
       </c>
       <c r="T558" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="W558" t="s">
         <v>362</v>
@@ -40065,16 +40074,16 @@
     </row>
     <row r="559" spans="1:33">
       <c r="A559">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B559" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C559" t="s">
         <v>58</v>
       </c>
       <c r="D559" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E559" t="s">
         <v>62</v>
@@ -40104,7 +40113,7 @@
         <v>214</v>
       </c>
       <c r="O559">
-        <v>16962400</v>
+        <v>16976290</v>
       </c>
       <c r="P559" t="s">
         <v>62</v>
@@ -40113,13 +40122,16 @@
         <v>245</v>
       </c>
       <c r="R559" s="1">
-        <v>46282.36525856482</v>
+        <v>46282.36526855324</v>
       </c>
       <c r="S559">
         <v>-1</v>
       </c>
       <c r="T559" t="s">
-        <v>257</v>
+        <v>255</v>
+      </c>
+      <c r="V559" t="s">
+        <v>263</v>
       </c>
       <c r="W559" t="s">
         <v>362</v>
@@ -40136,10 +40148,10 @@
     </row>
     <row r="560" spans="1:33">
       <c r="A560">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B560" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C560" t="s">
         <v>58</v>
@@ -40175,7 +40187,7 @@
         <v>214</v>
       </c>
       <c r="O560">
-        <v>16976290</v>
+        <v>17222899</v>
       </c>
       <c r="P560" t="s">
         <v>62</v>
@@ -40184,13 +40196,13 @@
         <v>245</v>
       </c>
       <c r="R560" s="1">
-        <v>46282.36526855324</v>
+        <v>46282.36527959491</v>
       </c>
       <c r="S560">
         <v>-1</v>
       </c>
       <c r="T560" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="V560" t="s">
         <v>263</v>
@@ -40210,10 +40222,10 @@
     </row>
     <row r="561" spans="1:33">
       <c r="A561">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B561" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C561" t="s">
         <v>58</v>
@@ -40222,7 +40234,7 @@
         <v>59</v>
       </c>
       <c r="E561" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F561" t="s">
         <v>64</v>
@@ -40249,22 +40261,22 @@
         <v>214</v>
       </c>
       <c r="O561">
-        <v>17222899</v>
+        <v>17042627</v>
       </c>
       <c r="P561" t="s">
-        <v>62</v>
+        <v>239</v>
       </c>
       <c r="Q561" t="s">
         <v>245</v>
       </c>
       <c r="R561" s="1">
-        <v>46282.36527959491</v>
+        <v>46282.36528526621</v>
       </c>
       <c r="S561">
         <v>-1</v>
       </c>
       <c r="T561" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="V561" t="s">
         <v>263</v>
@@ -40284,16 +40296,16 @@
     </row>
     <row r="562" spans="1:33">
       <c r="A562">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B562" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C562" t="s">
         <v>58</v>
       </c>
       <c r="D562" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E562" t="s">
         <v>63</v>
@@ -40323,16 +40335,16 @@
         <v>214</v>
       </c>
       <c r="O562">
-        <v>17042627</v>
+        <v>16960098</v>
       </c>
       <c r="P562" t="s">
-        <v>239</v>
+        <v>63</v>
       </c>
       <c r="Q562" t="s">
         <v>245</v>
       </c>
       <c r="R562" s="1">
-        <v>46282.36528526621</v>
+        <v>46282.36528619213</v>
       </c>
       <c r="S562">
         <v>-1</v>
@@ -40358,19 +40370,19 @@
     </row>
     <row r="563" spans="1:33">
       <c r="A563">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B563" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C563" t="s">
         <v>58</v>
       </c>
       <c r="D563" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E563" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F563" t="s">
         <v>64</v>
@@ -40397,25 +40409,22 @@
         <v>214</v>
       </c>
       <c r="O563">
-        <v>16960098</v>
+        <v>17941237</v>
       </c>
       <c r="P563" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q563" t="s">
         <v>245</v>
       </c>
       <c r="R563" s="1">
-        <v>46282.36528619213</v>
+        <v>46282.36529351852</v>
       </c>
       <c r="S563">
         <v>-1</v>
       </c>
       <c r="T563" t="s">
-        <v>249</v>
-      </c>
-      <c r="V563" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="W563" t="s">
         <v>362</v>
@@ -40432,16 +40441,16 @@
     </row>
     <row r="564" spans="1:33">
       <c r="A564">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B564" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C564" t="s">
         <v>58</v>
       </c>
       <c r="D564" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E564" t="s">
         <v>62</v>
@@ -40471,7 +40480,7 @@
         <v>214</v>
       </c>
       <c r="O564">
-        <v>17941237</v>
+        <v>17952466</v>
       </c>
       <c r="P564" t="s">
         <v>62</v>
@@ -40480,13 +40489,16 @@
         <v>245</v>
       </c>
       <c r="R564" s="1">
-        <v>46282.36529351852</v>
+        <v>46282.36529424768</v>
       </c>
       <c r="S564">
         <v>-1</v>
       </c>
       <c r="T564" t="s">
-        <v>256</v>
+        <v>254</v>
+      </c>
+      <c r="V564" t="s">
+        <v>263</v>
       </c>
       <c r="W564" t="s">
         <v>362</v>
@@ -40503,16 +40515,16 @@
     </row>
     <row r="565" spans="1:33">
       <c r="A565">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B565" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C565" t="s">
         <v>58</v>
       </c>
       <c r="D565" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E565" t="s">
         <v>62</v>
@@ -40542,7 +40554,7 @@
         <v>214</v>
       </c>
       <c r="O565">
-        <v>17952466</v>
+        <v>17952646</v>
       </c>
       <c r="P565" t="s">
         <v>62</v>
@@ -40551,7 +40563,7 @@
         <v>245</v>
       </c>
       <c r="R565" s="1">
-        <v>46282.36529424768</v>
+        <v>46282.36529490741</v>
       </c>
       <c r="S565">
         <v>-1</v>
@@ -40559,9 +40571,6 @@
       <c r="T565" t="s">
         <v>254</v>
       </c>
-      <c r="V565" t="s">
-        <v>263</v>
-      </c>
       <c r="W565" t="s">
         <v>362</v>
       </c>
@@ -40577,10 +40586,10 @@
     </row>
     <row r="566" spans="1:33">
       <c r="A566">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B566" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C566" t="s">
         <v>58</v>
@@ -40616,16 +40625,16 @@
         <v>214</v>
       </c>
       <c r="O566">
-        <v>17952646</v>
+        <v>18056821</v>
       </c>
       <c r="P566" t="s">
-        <v>62</v>
+        <v>239</v>
       </c>
       <c r="Q566" t="s">
         <v>245</v>
       </c>
       <c r="R566" s="1">
-        <v>46282.36529490741</v>
+        <v>46282.36529869213</v>
       </c>
       <c r="S566">
         <v>-1</v>
@@ -40633,6 +40642,9 @@
       <c r="T566" t="s">
         <v>254</v>
       </c>
+      <c r="V566" t="s">
+        <v>263</v>
+      </c>
       <c r="W566" t="s">
         <v>362</v>
       </c>
@@ -40648,10 +40660,10 @@
     </row>
     <row r="567" spans="1:33">
       <c r="A567">
-        <v>6779</v>
+        <v>6945</v>
       </c>
       <c r="B567" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C567" t="s">
         <v>58</v>
@@ -40663,7 +40675,7 @@
         <v>62</v>
       </c>
       <c r="F567" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G567">
         <v>9088</v>
@@ -40687,25 +40699,22 @@
         <v>214</v>
       </c>
       <c r="O567">
-        <v>18056821</v>
+        <v>18164565</v>
       </c>
       <c r="P567" t="s">
-        <v>239</v>
+        <v>62</v>
       </c>
       <c r="Q567" t="s">
         <v>245</v>
       </c>
       <c r="R567" s="1">
-        <v>46282.36529869213</v>
+        <v>46282.36531149306</v>
       </c>
       <c r="S567">
         <v>-1</v>
       </c>
       <c r="T567" t="s">
-        <v>254</v>
-      </c>
-      <c r="V567" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="W567" t="s">
         <v>362</v>
@@ -40722,16 +40731,16 @@
     </row>
     <row r="568" spans="1:33">
       <c r="A568">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B568" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C568" t="s">
         <v>58</v>
       </c>
       <c r="D568" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E568" t="s">
         <v>62</v>
@@ -40761,25 +40770,25 @@
         <v>214</v>
       </c>
       <c r="O568">
-        <v>18164565</v>
+        <v>18178199</v>
       </c>
       <c r="P568" t="s">
-        <v>62</v>
+        <v>239</v>
       </c>
       <c r="Q568" t="s">
         <v>245</v>
       </c>
       <c r="R568" s="1">
-        <v>46282.36531149306</v>
+        <v>46282.36531554398</v>
       </c>
       <c r="S568">
         <v>-1</v>
       </c>
       <c r="T568" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="W568" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AA568">
         <v>0</v>
@@ -40793,16 +40802,16 @@
     </row>
     <row r="569" spans="1:33">
       <c r="A569">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B569" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C569" t="s">
         <v>58</v>
       </c>
       <c r="D569" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E569" t="s">
         <v>62</v>
@@ -40832,25 +40841,25 @@
         <v>214</v>
       </c>
       <c r="O569">
-        <v>18178199</v>
+        <v>18188788</v>
       </c>
       <c r="P569" t="s">
-        <v>239</v>
+        <v>62</v>
       </c>
       <c r="Q569" t="s">
         <v>245</v>
       </c>
       <c r="R569" s="1">
-        <v>46282.36531554398</v>
+        <v>46282.36531253472</v>
       </c>
       <c r="S569">
         <v>-1</v>
       </c>
       <c r="T569" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="W569" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AA569">
         <v>0</v>
@@ -40864,10 +40873,10 @@
     </row>
     <row r="570" spans="1:33">
       <c r="A570">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B570" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C570" t="s">
         <v>58</v>
@@ -40903,7 +40912,7 @@
         <v>214</v>
       </c>
       <c r="O570">
-        <v>18188788</v>
+        <v>18188694</v>
       </c>
       <c r="P570" t="s">
         <v>62</v>
@@ -40912,7 +40921,7 @@
         <v>245</v>
       </c>
       <c r="R570" s="1">
-        <v>46282.36531253472</v>
+        <v>46282.36531288194</v>
       </c>
       <c r="S570">
         <v>-1</v>
@@ -40935,10 +40944,10 @@
     </row>
     <row r="571" spans="1:33">
       <c r="A571">
-        <v>6963</v>
+        <v>6404</v>
       </c>
       <c r="B571" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C571" t="s">
         <v>58</v>
@@ -40950,10 +40959,10 @@
         <v>62</v>
       </c>
       <c r="F571" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G571">
-        <v>9088</v>
+        <v>11001</v>
       </c>
       <c r="H571">
         <v>0</v>
@@ -40962,19 +40971,16 @@
         <v>73</v>
       </c>
       <c r="J571" t="s">
-        <v>177</v>
+        <v>135</v>
       </c>
       <c r="L571" s="1">
-        <v>46283</v>
-      </c>
-      <c r="M571" t="s">
-        <v>209</v>
+        <v>46290</v>
       </c>
       <c r="N571" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O571">
-        <v>18188694</v>
+        <v>16962454</v>
       </c>
       <c r="P571" t="s">
         <v>62</v>
@@ -40983,39 +40989,39 @@
         <v>245</v>
       </c>
       <c r="R571" s="1">
-        <v>46282.36531288194</v>
+        <v>46235.0433193287</v>
       </c>
       <c r="S571">
-        <v>-1</v>
+        <v>-8</v>
       </c>
       <c r="T571" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="W571" t="s">
-        <v>362</v>
+        <v>406</v>
       </c>
       <c r="AA571">
         <v>0</v>
       </c>
       <c r="AB571" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AG571" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="572" spans="1:33">
       <c r="A572">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B572" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C572" t="s">
         <v>58</v>
       </c>
       <c r="D572" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E572" t="s">
         <v>62</v>
@@ -41024,7 +41030,7 @@
         <v>64</v>
       </c>
       <c r="G572">
-        <v>11001</v>
+        <v>7877</v>
       </c>
       <c r="H572">
         <v>0</v>
@@ -41033,7 +41039,7 @@
         <v>73</v>
       </c>
       <c r="J572" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L572" s="1">
         <v>46290</v>
@@ -41042,7 +41048,7 @@
         <v>213</v>
       </c>
       <c r="O572">
-        <v>16962454</v>
+        <v>17399330</v>
       </c>
       <c r="P572" t="s">
         <v>62</v>
@@ -41051,13 +41057,13 @@
         <v>245</v>
       </c>
       <c r="R572" s="1">
-        <v>46235.0433193287</v>
+        <v>46235.04257873842</v>
       </c>
       <c r="S572">
         <v>-8</v>
       </c>
       <c r="T572" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="W572" t="s">
         <v>407</v>
@@ -41074,10 +41080,10 @@
     </row>
     <row r="573" spans="1:33">
       <c r="A573">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B573" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C573" t="s">
         <v>58</v>
@@ -41092,7 +41098,7 @@
         <v>64</v>
       </c>
       <c r="G573">
-        <v>7877</v>
+        <v>9774</v>
       </c>
       <c r="H573">
         <v>0</v>
@@ -41101,7 +41107,7 @@
         <v>73</v>
       </c>
       <c r="J573" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L573" s="1">
         <v>46290</v>
@@ -41110,7 +41116,7 @@
         <v>213</v>
       </c>
       <c r="O573">
-        <v>17399330</v>
+        <v>16976321</v>
       </c>
       <c r="P573" t="s">
         <v>62</v>
@@ -41119,13 +41125,16 @@
         <v>245</v>
       </c>
       <c r="R573" s="1">
-        <v>46235.04257873842</v>
+        <v>46235.04371431713</v>
       </c>
       <c r="S573">
         <v>-8</v>
       </c>
       <c r="T573" t="s">
-        <v>253</v>
+        <v>255</v>
+      </c>
+      <c r="V573" t="s">
+        <v>263</v>
       </c>
       <c r="W573" t="s">
         <v>408</v>
@@ -41142,10 +41151,10 @@
     </row>
     <row r="574" spans="1:33">
       <c r="A574">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B574" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C574" t="s">
         <v>58</v>
@@ -41160,7 +41169,7 @@
         <v>64</v>
       </c>
       <c r="G574">
-        <v>9774</v>
+        <v>7027</v>
       </c>
       <c r="H574">
         <v>0</v>
@@ -41169,16 +41178,16 @@
         <v>73</v>
       </c>
       <c r="J574" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="L574" s="1">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="N574" t="s">
         <v>213</v>
       </c>
       <c r="O574">
-        <v>16976321</v>
+        <v>17399290</v>
       </c>
       <c r="P574" t="s">
         <v>62</v>
@@ -41187,16 +41196,13 @@
         <v>245</v>
       </c>
       <c r="R574" s="1">
-        <v>46235.04371431713</v>
+        <v>46279.70955146991</v>
       </c>
       <c r="S574">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="T574" t="s">
-        <v>255</v>
-      </c>
-      <c r="V574" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="W574" t="s">
         <v>409</v>
@@ -41213,16 +41219,16 @@
     </row>
     <row r="575" spans="1:33">
       <c r="A575">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B575" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C575" t="s">
         <v>58</v>
       </c>
       <c r="D575" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E575" t="s">
         <v>62</v>
@@ -41249,7 +41255,7 @@
         <v>213</v>
       </c>
       <c r="O575">
-        <v>17399290</v>
+        <v>16962348</v>
       </c>
       <c r="P575" t="s">
         <v>62</v>
@@ -41258,13 +41264,13 @@
         <v>245</v>
       </c>
       <c r="R575" s="1">
-        <v>46279.70955146991</v>
+        <v>46282.64018086805</v>
       </c>
       <c r="S575">
         <v>-7</v>
       </c>
       <c r="T575" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="W575" t="s">
         <v>410</v>

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -1293,8 +1293,7 @@
 Falha na emissão do arquivo para baixa - Data Comentário: 17/09/2026 16:45</t>
   </si>
   <si>
-    <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 17/09/2026 
-Fechamento em andamento - Data Comentário: 15/09/2026 17:34</t>
+    <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 18/09/2026 - Data Comentário: 17/09/2026 17:50</t>
   </si>
   <si>
     <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 17/09/2026 - Data Comentário: 16/09/2026 18:49</t>
@@ -41728,7 +41727,7 @@
         <v>46280</v>
       </c>
       <c r="M582" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="N582" t="s">
         <v>214</v>

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8958" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8973" uniqueCount="463">
   <si>
     <t>CodCliente</t>
   </si>
@@ -1157,10 +1157,10 @@
     <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 18/09/2026 - Em andamento - Data Comentário: 15/09/2026 09:25</t>
   </si>
   <si>
-    <t>Imposto enviado via SCI Report - Data Comentário: 18/09/2026 08:52</t>
-  </si>
-  <si>
     <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 18/09/2026 - Em andamento - Data Comentário: 15/09/2026 09:26</t>
+  </si>
+  <si>
+    <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1879] sendo a ultima baixa feita [1879]-18/09/2026 09:57:01.. - Data Comentário: 18/09/2026 09:52</t>
   </si>
   <si>
     <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1805] sendo a ultima baixa feita [1805]-18/09/2026 08:30:31.. - Data Comentário: 18/09/2026 08:25</t>
@@ -1242,6 +1242,9 @@
     <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 11/09/2026 - Data Comentário: 15/09/2026 09:25</t>
   </si>
   <si>
+    <t>Imposto enviado via SCI Report - Data Comentário: 18/09/2026 08:52</t>
+  </si>
+  <si>
     <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 17/09/2026 17:56:12. - Data Comentário: 17/09/2026 17:51</t>
   </si>
   <si>
@@ -1264,9 +1267,6 @@
   </si>
   <si>
     <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 17/09/2026 12:58:09. - Data Comentário: 17/09/2026 12:53</t>
-  </si>
-  <si>
-    <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[1879]. - Data Comentário: 01/09/2026 00:58</t>
   </si>
   <si>
     <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[1879]. - Data Comentário: 01/09/2026 01:58</t>
@@ -1771,7 +1771,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AH613"/>
+  <dimension ref="A1:AH614"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:34">
@@ -24126,10 +24126,10 @@
     </row>
     <row r="322" spans="1:34">
       <c r="A322">
-        <v>6949</v>
+        <v>5417</v>
       </c>
       <c r="B322" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C322" t="s">
         <v>60</v>
@@ -24141,40 +24141,40 @@
         <v>64</v>
       </c>
       <c r="F322" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G322">
-        <v>1697</v>
+        <v>7868</v>
       </c>
       <c r="H322">
-        <v>1650</v>
+        <v>0</v>
       </c>
       <c r="I322" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J322" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="L322" s="1">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="N322" t="s">
         <v>224</v>
       </c>
       <c r="O322">
-        <v>18178280</v>
+        <v>17399310</v>
       </c>
       <c r="P322" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q322" t="s">
         <v>260</v>
       </c>
       <c r="S322">
-        <v>-3</v>
+        <v>-10</v>
       </c>
       <c r="T322" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AA322">
         <v>0</v>
@@ -24183,15 +24183,15 @@
         <v>453</v>
       </c>
       <c r="AH322" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="323" spans="1:34">
       <c r="A323">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B323" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C323" t="s">
         <v>60</v>
@@ -24224,10 +24224,10 @@
         <v>224</v>
       </c>
       <c r="O323">
-        <v>17399310</v>
+        <v>18114218</v>
       </c>
       <c r="P323" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="Q323" t="s">
         <v>260</v>
@@ -24236,7 +24236,10 @@
         <v>-10</v>
       </c>
       <c r="T323" t="s">
-        <v>266</v>
+        <v>268</v>
+      </c>
+      <c r="V323" t="s">
+        <v>277</v>
       </c>
       <c r="AA323">
         <v>0</v>
@@ -24250,10 +24253,10 @@
     </row>
     <row r="324" spans="1:34">
       <c r="A324">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B324" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C324" t="s">
         <v>60</v>
@@ -24268,7 +24271,7 @@
         <v>66</v>
       </c>
       <c r="G324">
-        <v>7868</v>
+        <v>6890</v>
       </c>
       <c r="H324">
         <v>0</v>
@@ -24277,37 +24280,34 @@
         <v>70</v>
       </c>
       <c r="J324" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L324" s="1">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="N324" t="s">
         <v>224</v>
       </c>
       <c r="O324">
-        <v>18114218</v>
+        <v>17399260</v>
       </c>
       <c r="P324" t="s">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="Q324" t="s">
         <v>260</v>
       </c>
       <c r="S324">
-        <v>-10</v>
+        <v>-7</v>
       </c>
       <c r="T324" t="s">
-        <v>268</v>
-      </c>
-      <c r="V324" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="AA324">
         <v>0</v>
       </c>
       <c r="AG324" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AH324" t="s">
         <v>458</v>
@@ -24315,16 +24315,16 @@
     </row>
     <row r="325" spans="1:34">
       <c r="A325">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B325" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C325" t="s">
         <v>60</v>
       </c>
       <c r="D325" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E325" t="s">
         <v>64</v>
@@ -24351,10 +24351,10 @@
         <v>224</v>
       </c>
       <c r="O325">
-        <v>17399260</v>
+        <v>16962328</v>
       </c>
       <c r="P325" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
       <c r="Q325" t="s">
         <v>260</v>
@@ -24363,7 +24363,7 @@
         <v>-7</v>
       </c>
       <c r="T325" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="AA325">
         <v>0</v>
@@ -24372,21 +24372,21 @@
         <v>455</v>
       </c>
       <c r="AH325" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="326" spans="1:34">
       <c r="A326">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B326" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C326" t="s">
         <v>60</v>
       </c>
       <c r="D326" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E326" t="s">
         <v>64</v>
@@ -24413,10 +24413,10 @@
         <v>224</v>
       </c>
       <c r="O326">
-        <v>16962328</v>
+        <v>18152538</v>
       </c>
       <c r="P326" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q326" t="s">
         <v>260</v>
@@ -24425,7 +24425,10 @@
         <v>-7</v>
       </c>
       <c r="T326" t="s">
-        <v>270</v>
+        <v>268</v>
+      </c>
+      <c r="V326" t="s">
+        <v>277</v>
       </c>
       <c r="AA326">
         <v>0</v>
@@ -24434,21 +24437,21 @@
         <v>455</v>
       </c>
       <c r="AH326" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="327" spans="1:34">
       <c r="A327">
-        <v>6486</v>
+        <v>6703</v>
       </c>
       <c r="B327" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C327" t="s">
         <v>60</v>
       </c>
       <c r="D327" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E327" t="s">
         <v>64</v>
@@ -24475,7 +24478,7 @@
         <v>224</v>
       </c>
       <c r="O327">
-        <v>18152538</v>
+        <v>17955186</v>
       </c>
       <c r="P327" t="s">
         <v>251</v>
@@ -24487,10 +24490,7 @@
         <v>-7</v>
       </c>
       <c r="T327" t="s">
-        <v>268</v>
-      </c>
-      <c r="V327" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="AA327">
         <v>0</v>
@@ -24504,16 +24504,16 @@
     </row>
     <row r="328" spans="1:34">
       <c r="A328">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B328" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C328" t="s">
         <v>60</v>
       </c>
       <c r="D328" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E328" t="s">
         <v>64</v>
@@ -24540,10 +24540,10 @@
         <v>224</v>
       </c>
       <c r="O328">
-        <v>17955186</v>
+        <v>17955399</v>
       </c>
       <c r="P328" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="Q328" t="s">
         <v>260</v>
@@ -24552,7 +24552,10 @@
         <v>-7</v>
       </c>
       <c r="T328" t="s">
-        <v>269</v>
+        <v>267</v>
+      </c>
+      <c r="V328" t="s">
+        <v>277</v>
       </c>
       <c r="AA328">
         <v>0</v>
@@ -24561,21 +24564,21 @@
         <v>455</v>
       </c>
       <c r="AH328" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="329" spans="1:34">
       <c r="A329">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B329" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C329" t="s">
         <v>60</v>
       </c>
       <c r="D329" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E329" t="s">
         <v>64</v>
@@ -24602,7 +24605,7 @@
         <v>224</v>
       </c>
       <c r="O329">
-        <v>17955399</v>
+        <v>17955249</v>
       </c>
       <c r="P329" t="s">
         <v>234</v>
@@ -24616,9 +24619,6 @@
       <c r="T329" t="s">
         <v>267</v>
       </c>
-      <c r="V329" t="s">
-        <v>277</v>
-      </c>
       <c r="AA329">
         <v>0</v>
       </c>
@@ -24631,10 +24631,10 @@
     </row>
     <row r="330" spans="1:34">
       <c r="A330">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B330" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C330" t="s">
         <v>60</v>
@@ -24667,7 +24667,7 @@
         <v>224</v>
       </c>
       <c r="O330">
-        <v>17955249</v>
+        <v>18056769</v>
       </c>
       <c r="P330" t="s">
         <v>234</v>
@@ -24681,6 +24681,9 @@
       <c r="T330" t="s">
         <v>267</v>
       </c>
+      <c r="V330" t="s">
+        <v>277</v>
+      </c>
       <c r="AA330">
         <v>0</v>
       </c>
@@ -24693,16 +24696,16 @@
     </row>
     <row r="331" spans="1:34">
       <c r="A331">
-        <v>6779</v>
+        <v>5417</v>
       </c>
       <c r="B331" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C331" t="s">
         <v>60</v>
       </c>
       <c r="D331" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E331" t="s">
         <v>64</v>
@@ -24711,7 +24714,7 @@
         <v>66</v>
       </c>
       <c r="G331">
-        <v>6890</v>
+        <v>11514</v>
       </c>
       <c r="H331">
         <v>0</v>
@@ -24720,7 +24723,7 @@
         <v>70</v>
       </c>
       <c r="J331" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L331" s="1">
         <v>46290</v>
@@ -24729,10 +24732,10 @@
         <v>224</v>
       </c>
       <c r="O331">
-        <v>18056769</v>
+        <v>17399465</v>
       </c>
       <c r="P331" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="Q331" t="s">
         <v>260</v>
@@ -24741,10 +24744,7 @@
         <v>-7</v>
       </c>
       <c r="T331" t="s">
-        <v>267</v>
-      </c>
-      <c r="V331" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="AA331">
         <v>0</v>
@@ -24753,21 +24753,21 @@
         <v>455</v>
       </c>
       <c r="AH331" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="332" spans="1:34">
       <c r="A332">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B332" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C332" t="s">
         <v>60</v>
       </c>
       <c r="D332" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E332" t="s">
         <v>64</v>
@@ -24794,10 +24794,10 @@
         <v>224</v>
       </c>
       <c r="O332">
-        <v>17399465</v>
+        <v>16962474</v>
       </c>
       <c r="P332" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
       <c r="Q332" t="s">
         <v>260</v>
@@ -24806,7 +24806,7 @@
         <v>-7</v>
       </c>
       <c r="T332" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="AA332">
         <v>0</v>
@@ -24815,21 +24815,21 @@
         <v>455</v>
       </c>
       <c r="AH332" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="333" spans="1:34">
       <c r="A333">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B333" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C333" t="s">
         <v>60</v>
       </c>
       <c r="D333" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E333" t="s">
         <v>64</v>
@@ -24856,10 +24856,10 @@
         <v>224</v>
       </c>
       <c r="O333">
-        <v>16962474</v>
+        <v>18114227</v>
       </c>
       <c r="P333" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q333" t="s">
         <v>260</v>
@@ -24868,7 +24868,10 @@
         <v>-7</v>
       </c>
       <c r="T333" t="s">
-        <v>270</v>
+        <v>268</v>
+      </c>
+      <c r="V333" t="s">
+        <v>277</v>
       </c>
       <c r="AA333">
         <v>0</v>
@@ -24877,21 +24880,21 @@
         <v>455</v>
       </c>
       <c r="AH333" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="334" spans="1:34">
       <c r="A334">
-        <v>6486</v>
+        <v>6703</v>
       </c>
       <c r="B334" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C334" t="s">
         <v>60</v>
       </c>
       <c r="D334" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E334" t="s">
         <v>64</v>
@@ -24918,7 +24921,7 @@
         <v>224</v>
       </c>
       <c r="O334">
-        <v>18114227</v>
+        <v>17955212</v>
       </c>
       <c r="P334" t="s">
         <v>251</v>
@@ -24930,10 +24933,7 @@
         <v>-7</v>
       </c>
       <c r="T334" t="s">
-        <v>268</v>
-      </c>
-      <c r="V334" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="AA334">
         <v>0</v>
@@ -24947,16 +24947,16 @@
     </row>
     <row r="335" spans="1:34">
       <c r="A335">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B335" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C335" t="s">
         <v>60</v>
       </c>
       <c r="D335" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E335" t="s">
         <v>64</v>
@@ -24983,10 +24983,10 @@
         <v>224</v>
       </c>
       <c r="O335">
-        <v>17955212</v>
+        <v>17955445</v>
       </c>
       <c r="P335" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="Q335" t="s">
         <v>260</v>
@@ -24995,7 +24995,10 @@
         <v>-7</v>
       </c>
       <c r="T335" t="s">
-        <v>269</v>
+        <v>267</v>
+      </c>
+      <c r="V335" t="s">
+        <v>277</v>
       </c>
       <c r="AA335">
         <v>0</v>
@@ -25004,21 +25007,21 @@
         <v>455</v>
       </c>
       <c r="AH335" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="336" spans="1:34">
       <c r="A336">
-        <v>6704</v>
+        <v>6404</v>
       </c>
       <c r="B336" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C336" t="s">
         <v>60</v>
       </c>
       <c r="D336" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E336" t="s">
         <v>64</v>
@@ -25027,7 +25030,7 @@
         <v>66</v>
       </c>
       <c r="G336">
-        <v>11514</v>
+        <v>10988</v>
       </c>
       <c r="H336">
         <v>0</v>
@@ -25036,37 +25039,34 @@
         <v>70</v>
       </c>
       <c r="J336" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L336" s="1">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="N336" t="s">
         <v>224</v>
       </c>
       <c r="O336">
-        <v>17955445</v>
+        <v>16962444</v>
       </c>
       <c r="P336" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="Q336" t="s">
         <v>260</v>
       </c>
       <c r="S336">
-        <v>-7</v>
+        <v>-12</v>
       </c>
       <c r="T336" t="s">
-        <v>267</v>
-      </c>
-      <c r="V336" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="AA336">
         <v>0</v>
       </c>
       <c r="AG336" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AH336" t="s">
         <v>459</v>
@@ -25074,10 +25074,10 @@
     </row>
     <row r="337" spans="1:34">
       <c r="A337">
-        <v>6404</v>
+        <v>6703</v>
       </c>
       <c r="B337" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C337" t="s">
         <v>60</v>
@@ -25110,10 +25110,10 @@
         <v>224</v>
       </c>
       <c r="O337">
-        <v>16962444</v>
+        <v>18112918</v>
       </c>
       <c r="P337" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q337" t="s">
         <v>260</v>
@@ -25122,7 +25122,7 @@
         <v>-12</v>
       </c>
       <c r="T337" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AA337">
         <v>0</v>
@@ -25131,21 +25131,21 @@
         <v>453</v>
       </c>
       <c r="AH337" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="338" spans="1:34">
       <c r="A338">
-        <v>6703</v>
+        <v>5417</v>
       </c>
       <c r="B338" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C338" t="s">
         <v>60</v>
       </c>
       <c r="D338" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E338" t="s">
         <v>64</v>
@@ -25154,7 +25154,7 @@
         <v>66</v>
       </c>
       <c r="G338">
-        <v>10988</v>
+        <v>7874</v>
       </c>
       <c r="H338">
         <v>0</v>
@@ -25163,7 +25163,7 @@
         <v>70</v>
       </c>
       <c r="J338" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L338" s="1">
         <v>46295</v>
@@ -25172,10 +25172,10 @@
         <v>224</v>
       </c>
       <c r="O338">
-        <v>18112918</v>
+        <v>17399320</v>
       </c>
       <c r="P338" t="s">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="Q338" t="s">
         <v>260</v>
@@ -25184,7 +25184,7 @@
         <v>-12</v>
       </c>
       <c r="T338" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AA338">
         <v>0</v>
@@ -25198,10 +25198,10 @@
     </row>
     <row r="339" spans="1:34">
       <c r="A339">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B339" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C339" t="s">
         <v>60</v>
@@ -25234,10 +25234,10 @@
         <v>224</v>
       </c>
       <c r="O339">
-        <v>17399320</v>
+        <v>18130463</v>
       </c>
       <c r="P339" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="Q339" t="s">
         <v>260</v>
@@ -25246,7 +25246,10 @@
         <v>-12</v>
       </c>
       <c r="T339" t="s">
-        <v>266</v>
+        <v>268</v>
+      </c>
+      <c r="V339" t="s">
+        <v>277</v>
       </c>
       <c r="AA339">
         <v>0</v>
@@ -25260,10 +25263,10 @@
     </row>
     <row r="340" spans="1:34">
       <c r="A340">
-        <v>6486</v>
+        <v>6704</v>
       </c>
       <c r="B340" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C340" t="s">
         <v>60</v>
@@ -25296,10 +25299,10 @@
         <v>224</v>
       </c>
       <c r="O340">
-        <v>18130463</v>
+        <v>18096767</v>
       </c>
       <c r="P340" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="Q340" t="s">
         <v>260</v>
@@ -25308,7 +25311,7 @@
         <v>-12</v>
       </c>
       <c r="T340" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="V340" t="s">
         <v>277</v>
@@ -25320,21 +25323,21 @@
         <v>453</v>
       </c>
       <c r="AH340" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="341" spans="1:34">
       <c r="A341">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B341" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C341" t="s">
         <v>60</v>
       </c>
       <c r="D341" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E341" t="s">
         <v>64</v>
@@ -25343,7 +25346,7 @@
         <v>66</v>
       </c>
       <c r="G341">
-        <v>7874</v>
+        <v>9762</v>
       </c>
       <c r="H341">
         <v>0</v>
@@ -25352,7 +25355,7 @@
         <v>70</v>
       </c>
       <c r="J341" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L341" s="1">
         <v>46295</v>
@@ -25361,7 +25364,7 @@
         <v>224</v>
       </c>
       <c r="O341">
-        <v>18096767</v>
+        <v>18096939</v>
       </c>
       <c r="P341" t="s">
         <v>234</v>
@@ -25375,9 +25378,6 @@
       <c r="T341" t="s">
         <v>267</v>
       </c>
-      <c r="V341" t="s">
-        <v>277</v>
-      </c>
       <c r="AA341">
         <v>0</v>
       </c>
@@ -25390,10 +25390,10 @@
     </row>
     <row r="342" spans="1:34">
       <c r="A342">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B342" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C342" t="s">
         <v>60</v>
@@ -25426,7 +25426,7 @@
         <v>224</v>
       </c>
       <c r="O342">
-        <v>18096939</v>
+        <v>18130484</v>
       </c>
       <c r="P342" t="s">
         <v>234</v>
@@ -25440,6 +25440,9 @@
       <c r="T342" t="s">
         <v>267</v>
       </c>
+      <c r="V342" t="s">
+        <v>277</v>
+      </c>
       <c r="AA342">
         <v>0</v>
       </c>
@@ -25452,16 +25455,16 @@
     </row>
     <row r="343" spans="1:34">
       <c r="A343">
-        <v>6779</v>
+        <v>6548</v>
       </c>
       <c r="B343" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C343" t="s">
         <v>60</v>
       </c>
       <c r="D343" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E343" t="s">
         <v>64</v>
@@ -25470,28 +25473,28 @@
         <v>66</v>
       </c>
       <c r="G343">
-        <v>9762</v>
+        <v>5859</v>
       </c>
       <c r="H343">
-        <v>0</v>
+        <v>5786</v>
       </c>
       <c r="I343" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J343" t="s">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="L343" s="1">
         <v>46295</v>
       </c>
       <c r="N343" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O343">
-        <v>18130484</v>
+        <v>17222602</v>
       </c>
       <c r="P343" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="Q343" t="s">
         <v>260</v>
@@ -25500,7 +25503,7 @@
         <v>-12</v>
       </c>
       <c r="T343" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="V343" t="s">
         <v>277</v>
@@ -25509,89 +25512,86 @@
         <v>0</v>
       </c>
       <c r="AG343" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AH343" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="344" spans="1:34">
       <c r="A344">
-        <v>6548</v>
+        <v>6945</v>
       </c>
       <c r="B344" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C344" t="s">
         <v>60</v>
       </c>
       <c r="D344" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E344" t="s">
         <v>64</v>
       </c>
       <c r="F344" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G344">
-        <v>5859</v>
+        <v>5883</v>
       </c>
       <c r="H344">
-        <v>5786</v>
+        <v>5792</v>
       </c>
       <c r="I344" t="s">
         <v>71</v>
       </c>
       <c r="J344" t="s">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="L344" s="1">
-        <v>46295</v>
+        <v>46286</v>
       </c>
       <c r="N344" t="s">
         <v>225</v>
       </c>
       <c r="O344">
-        <v>17222602</v>
+        <v>18179111</v>
       </c>
       <c r="P344" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="Q344" t="s">
         <v>260</v>
       </c>
       <c r="S344">
-        <v>-12</v>
+        <v>-3</v>
       </c>
       <c r="T344" t="s">
-        <v>261</v>
-      </c>
-      <c r="V344" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="AA344">
         <v>0</v>
       </c>
       <c r="AG344" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AH344" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="345" spans="1:34">
       <c r="A345">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B345" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C345" t="s">
         <v>60</v>
       </c>
       <c r="D345" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E345" t="s">
         <v>64</v>
@@ -25618,10 +25618,10 @@
         <v>225</v>
       </c>
       <c r="O345">
-        <v>18179111</v>
+        <v>18190420</v>
       </c>
       <c r="P345" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q345" t="s">
         <v>260</v>
@@ -25630,7 +25630,7 @@
         <v>-3</v>
       </c>
       <c r="T345" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AA345">
         <v>0</v>
@@ -25644,16 +25644,16 @@
     </row>
     <row r="346" spans="1:34">
       <c r="A346">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B346" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C346" t="s">
         <v>60</v>
       </c>
       <c r="D346" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E346" t="s">
         <v>64</v>
@@ -25662,7 +25662,7 @@
         <v>67</v>
       </c>
       <c r="G346">
-        <v>5883</v>
+        <v>5884</v>
       </c>
       <c r="H346">
         <v>5792</v>
@@ -25671,7 +25671,7 @@
         <v>71</v>
       </c>
       <c r="J346" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L346" s="1">
         <v>46286</v>
@@ -25680,10 +25680,10 @@
         <v>225</v>
       </c>
       <c r="O346">
-        <v>18190420</v>
+        <v>18179118</v>
       </c>
       <c r="P346" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Q346" t="s">
         <v>260</v>
@@ -25692,7 +25692,7 @@
         <v>-3</v>
       </c>
       <c r="T346" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AA346">
         <v>0</v>
@@ -25706,16 +25706,16 @@
     </row>
     <row r="347" spans="1:34">
       <c r="A347">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B347" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C347" t="s">
         <v>60</v>
       </c>
       <c r="D347" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E347" t="s">
         <v>64</v>
@@ -25742,10 +25742,10 @@
         <v>225</v>
       </c>
       <c r="O347">
-        <v>18179118</v>
+        <v>18190426</v>
       </c>
       <c r="P347" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q347" t="s">
         <v>260</v>
@@ -25754,7 +25754,7 @@
         <v>-3</v>
       </c>
       <c r="T347" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AA347">
         <v>0</v>
@@ -25768,10 +25768,10 @@
     </row>
     <row r="348" spans="1:34">
       <c r="A348">
-        <v>6949</v>
+        <v>5417</v>
       </c>
       <c r="B348" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C348" t="s">
         <v>60</v>
@@ -25783,19 +25783,19 @@
         <v>64</v>
       </c>
       <c r="F348" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G348">
-        <v>5884</v>
+        <v>5836</v>
       </c>
       <c r="H348">
-        <v>5792</v>
+        <v>5784</v>
       </c>
       <c r="I348" t="s">
         <v>71</v>
       </c>
       <c r="J348" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L348" s="1">
         <v>46286</v>
@@ -25804,10 +25804,10 @@
         <v>225</v>
       </c>
       <c r="O348">
-        <v>18190426</v>
+        <v>17399027</v>
       </c>
       <c r="P348" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q348" t="s">
         <v>260</v>
@@ -25816,7 +25816,7 @@
         <v>-3</v>
       </c>
       <c r="T348" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AA348">
         <v>0</v>
@@ -25824,16 +25824,13 @@
       <c r="AG348" t="s">
         <v>453</v>
       </c>
-      <c r="AH348" t="s">
-        <v>461</v>
-      </c>
     </row>
     <row r="349" spans="1:34">
       <c r="A349">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B349" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C349" t="s">
         <v>60</v>
@@ -25862,14 +25859,17 @@
       <c r="L349" s="1">
         <v>46286</v>
       </c>
+      <c r="M349" t="s">
+        <v>218</v>
+      </c>
       <c r="N349" t="s">
         <v>225</v>
       </c>
       <c r="O349">
-        <v>17399027</v>
+        <v>16976037</v>
       </c>
       <c r="P349" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="Q349" t="s">
         <v>260</v>
@@ -25878,7 +25878,13 @@
         <v>-3</v>
       </c>
       <c r="T349" t="s">
-        <v>266</v>
+        <v>268</v>
+      </c>
+      <c r="V349" t="s">
+        <v>277</v>
+      </c>
+      <c r="W349" t="s">
+        <v>364</v>
       </c>
       <c r="AA349">
         <v>0</v>
@@ -25886,13 +25892,16 @@
       <c r="AG349" t="s">
         <v>453</v>
       </c>
+      <c r="AH349" t="s">
+        <v>460</v>
+      </c>
     </row>
     <row r="350" spans="1:34">
       <c r="A350">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B350" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C350" t="s">
         <v>60</v>
@@ -25928,10 +25937,10 @@
         <v>225</v>
       </c>
       <c r="O350">
-        <v>16976037</v>
+        <v>17222579</v>
       </c>
       <c r="P350" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q350" t="s">
         <v>260</v>
@@ -25940,13 +25949,13 @@
         <v>-3</v>
       </c>
       <c r="T350" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="V350" t="s">
         <v>277</v>
       </c>
       <c r="W350" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AA350">
         <v>0</v>
@@ -25960,10 +25969,10 @@
     </row>
     <row r="351" spans="1:34">
       <c r="A351">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B351" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C351" t="s">
         <v>60</v>
@@ -25972,7 +25981,7 @@
         <v>61</v>
       </c>
       <c r="E351" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F351" t="s">
         <v>66</v>
@@ -25999,10 +26008,10 @@
         <v>225</v>
       </c>
       <c r="O351">
-        <v>17222579</v>
+        <v>18068500</v>
       </c>
       <c r="P351" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="Q351" t="s">
         <v>260</v>
@@ -26011,13 +26020,13 @@
         <v>-3</v>
       </c>
       <c r="T351" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="V351" t="s">
         <v>277</v>
       </c>
       <c r="W351" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AA351">
         <v>0</v>
@@ -26031,16 +26040,16 @@
     </row>
     <row r="352" spans="1:34">
       <c r="A352">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B352" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C352" t="s">
         <v>60</v>
       </c>
       <c r="D352" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E352" t="s">
         <v>65</v>
@@ -26070,7 +26079,7 @@
         <v>225</v>
       </c>
       <c r="O352">
-        <v>18068500</v>
+        <v>18052419</v>
       </c>
       <c r="P352" t="s">
         <v>235</v>
@@ -26102,19 +26111,19 @@
     </row>
     <row r="353" spans="1:34">
       <c r="A353">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B353" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C353" t="s">
         <v>60</v>
       </c>
       <c r="D353" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E353" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F353" t="s">
         <v>66</v>
@@ -26141,10 +26150,10 @@
         <v>225</v>
       </c>
       <c r="O353">
-        <v>18052419</v>
+        <v>18077082</v>
       </c>
       <c r="P353" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="Q353" t="s">
         <v>260</v>
@@ -26153,13 +26162,10 @@
         <v>-3</v>
       </c>
       <c r="T353" t="s">
-        <v>262</v>
-      </c>
-      <c r="V353" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="W353" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AA353">
         <v>0</v>
@@ -26173,16 +26179,16 @@
     </row>
     <row r="354" spans="1:34">
       <c r="A354">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B354" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C354" t="s">
         <v>60</v>
       </c>
       <c r="D354" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E354" t="s">
         <v>64</v>
@@ -26206,16 +26212,16 @@
         <v>46286</v>
       </c>
       <c r="M354" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="N354" t="s">
         <v>225</v>
       </c>
       <c r="O354">
-        <v>18077082</v>
+        <v>18090149</v>
       </c>
       <c r="P354" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q354" t="s">
         <v>260</v>
@@ -26224,10 +26230,13 @@
         <v>-3</v>
       </c>
       <c r="T354" t="s">
-        <v>269</v>
+        <v>267</v>
+      </c>
+      <c r="V354" t="s">
+        <v>277</v>
       </c>
       <c r="W354" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AA354">
         <v>0</v>
@@ -26236,15 +26245,15 @@
         <v>453</v>
       </c>
       <c r="AH354" t="s">
-        <v>460</v>
+        <v>444</v>
       </c>
     </row>
     <row r="355" spans="1:34">
       <c r="A355">
-        <v>6779</v>
+        <v>6945</v>
       </c>
       <c r="B355" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C355" t="s">
         <v>60</v>
@@ -26256,7 +26265,7 @@
         <v>64</v>
       </c>
       <c r="F355" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G355">
         <v>5836</v>
@@ -26273,17 +26282,14 @@
       <c r="L355" s="1">
         <v>46286</v>
       </c>
-      <c r="M355" t="s">
-        <v>216</v>
-      </c>
       <c r="N355" t="s">
         <v>225</v>
       </c>
       <c r="O355">
-        <v>18090149</v>
+        <v>18179083</v>
       </c>
       <c r="P355" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="Q355" t="s">
         <v>260</v>
@@ -26292,13 +26298,7 @@
         <v>-3</v>
       </c>
       <c r="T355" t="s">
-        <v>267</v>
-      </c>
-      <c r="V355" t="s">
-        <v>277</v>
-      </c>
-      <c r="W355" t="s">
-        <v>367</v>
+        <v>263</v>
       </c>
       <c r="AA355">
         <v>0</v>
@@ -26307,30 +26307,30 @@
         <v>453</v>
       </c>
       <c r="AH355" t="s">
-        <v>444</v>
+        <v>461</v>
       </c>
     </row>
     <row r="356" spans="1:34">
       <c r="A356">
-        <v>6945</v>
+        <v>6548</v>
       </c>
       <c r="B356" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C356" t="s">
         <v>60</v>
       </c>
       <c r="D356" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E356" t="s">
         <v>64</v>
       </c>
       <c r="F356" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G356">
-        <v>5836</v>
+        <v>5905</v>
       </c>
       <c r="H356">
         <v>5784</v>
@@ -26339,37 +26339,40 @@
         <v>71</v>
       </c>
       <c r="J356" t="s">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="L356" s="1">
-        <v>46286</v>
+        <v>46295</v>
       </c>
       <c r="N356" t="s">
         <v>225</v>
       </c>
       <c r="O356">
-        <v>18179083</v>
+        <v>17222671</v>
       </c>
       <c r="P356" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q356" t="s">
         <v>260</v>
       </c>
       <c r="S356">
-        <v>-3</v>
+        <v>-12</v>
       </c>
       <c r="T356" t="s">
-        <v>263</v>
+        <v>261</v>
+      </c>
+      <c r="V356" t="s">
+        <v>277</v>
       </c>
       <c r="AA356">
         <v>0</v>
       </c>
       <c r="AG356" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AH356" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="357" spans="1:34">
@@ -26392,7 +26395,7 @@
         <v>66</v>
       </c>
       <c r="G357">
-        <v>5905</v>
+        <v>5853</v>
       </c>
       <c r="H357">
         <v>5784</v>
@@ -26401,7 +26404,7 @@
         <v>71</v>
       </c>
       <c r="J357" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L357" s="1">
         <v>46295</v>
@@ -26410,7 +26413,7 @@
         <v>225</v>
       </c>
       <c r="O357">
-        <v>17222671</v>
+        <v>17222589</v>
       </c>
       <c r="P357" t="s">
         <v>239</v>
@@ -26431,7 +26434,7 @@
         <v>0</v>
       </c>
       <c r="AG357" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AH357" t="s">
         <v>460</v>
@@ -26439,10 +26442,10 @@
     </row>
     <row r="358" spans="1:34">
       <c r="A358">
-        <v>6548</v>
+        <v>5417</v>
       </c>
       <c r="B358" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C358" t="s">
         <v>60</v>
@@ -26457,7 +26460,7 @@
         <v>66</v>
       </c>
       <c r="G358">
-        <v>5853</v>
+        <v>5847</v>
       </c>
       <c r="H358">
         <v>5784</v>
@@ -26466,31 +26469,28 @@
         <v>71</v>
       </c>
       <c r="J358" t="s">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="L358" s="1">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="N358" t="s">
         <v>225</v>
       </c>
       <c r="O358">
-        <v>17222589</v>
+        <v>18158417</v>
       </c>
       <c r="P358" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q358" t="s">
         <v>260</v>
       </c>
       <c r="S358">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="T358" t="s">
-        <v>261</v>
-      </c>
-      <c r="V358" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="AA358">
         <v>0</v>
@@ -26498,22 +26498,19 @@
       <c r="AG358" t="s">
         <v>453</v>
       </c>
-      <c r="AH358" t="s">
-        <v>460</v>
-      </c>
     </row>
     <row r="359" spans="1:34">
       <c r="A359">
-        <v>5417</v>
+        <v>6779</v>
       </c>
       <c r="B359" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C359" t="s">
         <v>60</v>
       </c>
       <c r="D359" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E359" t="s">
         <v>64</v>
@@ -26540,10 +26537,10 @@
         <v>225</v>
       </c>
       <c r="O359">
-        <v>18158417</v>
+        <v>18158764</v>
       </c>
       <c r="P359" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q359" t="s">
         <v>260</v>
@@ -26552,7 +26549,10 @@
         <v>-10</v>
       </c>
       <c r="T359" t="s">
-        <v>266</v>
+        <v>267</v>
+      </c>
+      <c r="V359" t="s">
+        <v>277</v>
       </c>
       <c r="AA359">
         <v>0</v>
@@ -26560,19 +26560,22 @@
       <c r="AG359" t="s">
         <v>453</v>
       </c>
+      <c r="AH359" t="s">
+        <v>444</v>
+      </c>
     </row>
     <row r="360" spans="1:34">
       <c r="A360">
-        <v>6779</v>
+        <v>6548</v>
       </c>
       <c r="B360" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C360" t="s">
         <v>60</v>
       </c>
       <c r="D360" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E360" t="s">
         <v>64</v>
@@ -26581,7 +26584,7 @@
         <v>66</v>
       </c>
       <c r="G360">
-        <v>5847</v>
+        <v>5906</v>
       </c>
       <c r="H360">
         <v>5784</v>
@@ -26590,28 +26593,28 @@
         <v>71</v>
       </c>
       <c r="J360" t="s">
-        <v>143</v>
+        <v>89</v>
       </c>
       <c r="L360" s="1">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="N360" t="s">
         <v>225</v>
       </c>
       <c r="O360">
-        <v>18158764</v>
+        <v>17222688</v>
       </c>
       <c r="P360" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="Q360" t="s">
         <v>260</v>
       </c>
       <c r="S360">
-        <v>-10</v>
+        <v>-12</v>
       </c>
       <c r="T360" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="V360" t="s">
         <v>277</v>
@@ -26620,10 +26623,10 @@
         <v>0</v>
       </c>
       <c r="AG360" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AH360" t="s">
-        <v>444</v>
+        <v>460</v>
       </c>
     </row>
     <row r="361" spans="1:34">
@@ -26646,7 +26649,7 @@
         <v>66</v>
       </c>
       <c r="G361">
-        <v>5906</v>
+        <v>5907</v>
       </c>
       <c r="H361">
         <v>5784</v>
@@ -26655,7 +26658,7 @@
         <v>71</v>
       </c>
       <c r="J361" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="L361" s="1">
         <v>46295</v>
@@ -26664,7 +26667,7 @@
         <v>225</v>
       </c>
       <c r="O361">
-        <v>17222688</v>
+        <v>17222699</v>
       </c>
       <c r="P361" t="s">
         <v>239</v>
@@ -26685,7 +26688,7 @@
         <v>0</v>
       </c>
       <c r="AG361" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AH361" t="s">
         <v>460</v>
@@ -26693,10 +26696,10 @@
     </row>
     <row r="362" spans="1:34">
       <c r="A362">
-        <v>6548</v>
+        <v>5417</v>
       </c>
       <c r="B362" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C362" t="s">
         <v>60</v>
@@ -26711,57 +26714,57 @@
         <v>66</v>
       </c>
       <c r="G362">
-        <v>5907</v>
+        <v>6348</v>
       </c>
       <c r="H362">
-        <v>5784</v>
+        <v>0</v>
       </c>
       <c r="I362" t="s">
         <v>71</v>
       </c>
       <c r="J362" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L362" s="1">
-        <v>46295</v>
+        <v>46288</v>
+      </c>
+      <c r="M362" t="s">
+        <v>219</v>
       </c>
       <c r="N362" t="s">
         <v>225</v>
       </c>
       <c r="O362">
-        <v>17222699</v>
+        <v>18274307</v>
       </c>
       <c r="P362" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q362" t="s">
         <v>260</v>
       </c>
       <c r="S362">
-        <v>-12</v>
+        <v>-5</v>
       </c>
       <c r="T362" t="s">
-        <v>261</v>
-      </c>
-      <c r="V362" t="s">
-        <v>277</v>
+        <v>266</v>
+      </c>
+      <c r="W362" t="s">
+        <v>368</v>
       </c>
       <c r="AA362">
         <v>0</v>
       </c>
       <c r="AG362" t="s">
-        <v>453</v>
-      </c>
-      <c r="AH362" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
     </row>
     <row r="363" spans="1:34">
       <c r="A363">
-        <v>5417</v>
+        <v>6949</v>
       </c>
       <c r="B363" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C363" t="s">
         <v>60</v>
@@ -26773,7 +26776,7 @@
         <v>64</v>
       </c>
       <c r="F363" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G363">
         <v>6348</v>
@@ -26791,16 +26794,16 @@
         <v>46288</v>
       </c>
       <c r="M363" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N363" t="s">
         <v>225</v>
       </c>
       <c r="O363">
-        <v>18274307</v>
+        <v>18275979</v>
       </c>
       <c r="P363" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Q363" t="s">
         <v>260</v>
@@ -26809,10 +26812,10 @@
         <v>-5</v>
       </c>
       <c r="T363" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="W363" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AA363">
         <v>0</v>
@@ -26820,13 +26823,16 @@
       <c r="AG363" t="s">
         <v>454</v>
       </c>
+      <c r="AH363" t="s">
+        <v>461</v>
+      </c>
     </row>
     <row r="364" spans="1:34">
       <c r="A364">
-        <v>6949</v>
+        <v>6627</v>
       </c>
       <c r="B364" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C364" t="s">
         <v>60</v>
@@ -26835,66 +26841,60 @@
         <v>61</v>
       </c>
       <c r="E364" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F364" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G364">
-        <v>6348</v>
+        <v>1913</v>
       </c>
       <c r="H364">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="I364" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J364" t="s">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="L364" s="1">
-        <v>46288</v>
-      </c>
-      <c r="M364" t="s">
-        <v>220</v>
+        <v>46286</v>
       </c>
       <c r="N364" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O364">
-        <v>18275979</v>
+        <v>18048433</v>
       </c>
       <c r="P364" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="Q364" t="s">
         <v>260</v>
       </c>
       <c r="S364">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="T364" t="s">
-        <v>264</v>
-      </c>
-      <c r="W364" t="s">
-        <v>369</v>
+        <v>262</v>
+      </c>
+      <c r="V364" t="s">
+        <v>277</v>
       </c>
       <c r="AA364">
         <v>0</v>
       </c>
       <c r="AG364" t="s">
-        <v>454</v>
-      </c>
-      <c r="AH364" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
     </row>
     <row r="365" spans="1:34">
       <c r="A365">
-        <v>6627</v>
+        <v>6949</v>
       </c>
       <c r="B365" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C365" t="s">
         <v>60</v>
@@ -26903,10 +26903,10 @@
         <v>61</v>
       </c>
       <c r="E365" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F365" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G365">
         <v>1913</v>
@@ -26927,10 +26927,10 @@
         <v>224</v>
       </c>
       <c r="O365">
-        <v>18048433</v>
+        <v>18214877</v>
       </c>
       <c r="P365" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q365" t="s">
         <v>260</v>
@@ -26939,10 +26939,7 @@
         <v>-3</v>
       </c>
       <c r="T365" t="s">
-        <v>262</v>
-      </c>
-      <c r="V365" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="AA365">
         <v>0</v>
@@ -26950,19 +26947,22 @@
       <c r="AG365" t="s">
         <v>453</v>
       </c>
+      <c r="AH365" t="s">
+        <v>445</v>
+      </c>
     </row>
     <row r="366" spans="1:34">
       <c r="A366">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B366" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C366" t="s">
         <v>60</v>
       </c>
       <c r="D366" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E366" t="s">
         <v>64</v>
@@ -26971,37 +26971,43 @@
         <v>67</v>
       </c>
       <c r="G366">
-        <v>1913</v>
+        <v>11617</v>
       </c>
       <c r="H366">
-        <v>1862</v>
+        <v>0</v>
       </c>
       <c r="I366" t="s">
         <v>72</v>
       </c>
       <c r="J366" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L366" s="1">
-        <v>46286</v>
+        <v>46283</v>
+      </c>
+      <c r="M366" t="s">
+        <v>218</v>
       </c>
       <c r="N366" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O366">
-        <v>18214877</v>
+        <v>18186565</v>
       </c>
       <c r="P366" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="Q366" t="s">
         <v>260</v>
       </c>
       <c r="S366">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="T366" t="s">
-        <v>264</v>
+        <v>265</v>
+      </c>
+      <c r="W366" t="s">
+        <v>370</v>
       </c>
       <c r="AA366">
         <v>0</v>
@@ -27015,10 +27021,10 @@
     </row>
     <row r="367" spans="1:34">
       <c r="A367">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B367" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C367" t="s">
         <v>60</v>
@@ -27054,7 +27060,7 @@
         <v>226</v>
       </c>
       <c r="O367">
-        <v>18186565</v>
+        <v>18186566</v>
       </c>
       <c r="P367" t="s">
         <v>253</v>
@@ -27083,16 +27089,16 @@
     </row>
     <row r="368" spans="1:34">
       <c r="A368">
-        <v>6963</v>
+        <v>6945</v>
       </c>
       <c r="B368" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C368" t="s">
         <v>60</v>
       </c>
       <c r="D368" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E368" t="s">
         <v>64</v>
@@ -27101,7 +27107,7 @@
         <v>67</v>
       </c>
       <c r="G368">
-        <v>11617</v>
+        <v>5764</v>
       </c>
       <c r="H368">
         <v>0</v>
@@ -27110,66 +27116,57 @@
         <v>72</v>
       </c>
       <c r="J368" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L368" s="1">
-        <v>46283</v>
-      </c>
-      <c r="M368" t="s">
-        <v>218</v>
+        <v>46290</v>
       </c>
       <c r="N368" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="O368">
-        <v>18186566</v>
+        <v>18220203</v>
       </c>
       <c r="P368" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="Q368" t="s">
         <v>260</v>
       </c>
       <c r="S368">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="T368" t="s">
-        <v>265</v>
-      </c>
-      <c r="W368" t="s">
-        <v>370</v>
+        <v>263</v>
       </c>
       <c r="AA368">
         <v>0</v>
       </c>
       <c r="AG368" t="s">
-        <v>453</v>
-      </c>
-      <c r="AH368" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
     </row>
     <row r="369" spans="1:34">
       <c r="A369">
-        <v>6945</v>
+        <v>6548</v>
       </c>
       <c r="B369" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C369" t="s">
         <v>60</v>
       </c>
       <c r="D369" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E369" t="s">
         <v>64</v>
       </c>
       <c r="F369" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G369">
-        <v>5764</v>
+        <v>1876</v>
       </c>
       <c r="H369">
         <v>0</v>
@@ -27178,42 +27175,54 @@
         <v>72</v>
       </c>
       <c r="J369" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L369" s="1">
-        <v>46290</v>
+        <v>46283</v>
+      </c>
+      <c r="M369" t="s">
+        <v>218</v>
       </c>
       <c r="N369" t="s">
         <v>224</v>
       </c>
       <c r="O369">
-        <v>18220203</v>
+        <v>17988555</v>
       </c>
       <c r="P369" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q369" t="s">
         <v>260</v>
       </c>
       <c r="S369">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="T369" t="s">
-        <v>263</v>
+        <v>261</v>
+      </c>
+      <c r="V369" t="s">
+        <v>277</v>
+      </c>
+      <c r="W369" t="s">
+        <v>371</v>
       </c>
       <c r="AA369">
         <v>0</v>
       </c>
       <c r="AG369" t="s">
-        <v>455</v>
+        <v>454</v>
+      </c>
+      <c r="AH369" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="370" spans="1:34">
       <c r="A370">
-        <v>6548</v>
+        <v>6949</v>
       </c>
       <c r="B370" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C370" t="s">
         <v>60</v>
@@ -27225,7 +27234,7 @@
         <v>64</v>
       </c>
       <c r="F370" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G370">
         <v>1876</v>
@@ -27249,10 +27258,10 @@
         <v>224</v>
       </c>
       <c r="O370">
-        <v>17988555</v>
+        <v>18214865</v>
       </c>
       <c r="P370" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q370" t="s">
         <v>260</v>
@@ -27261,10 +27270,7 @@
         <v>0</v>
       </c>
       <c r="T370" t="s">
-        <v>261</v>
-      </c>
-      <c r="V370" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="W370" t="s">
         <v>371</v>
@@ -27281,10 +27287,10 @@
     </row>
     <row r="371" spans="1:34">
       <c r="A371">
-        <v>6949</v>
+        <v>6627</v>
       </c>
       <c r="B371" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C371" t="s">
         <v>60</v>
@@ -27293,13 +27299,13 @@
         <v>61</v>
       </c>
       <c r="E371" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F371" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G371">
-        <v>1876</v>
+        <v>11411</v>
       </c>
       <c r="H371">
         <v>0</v>
@@ -27308,7 +27314,7 @@
         <v>72</v>
       </c>
       <c r="J371" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L371" s="1">
         <v>46283</v>
@@ -27320,10 +27326,10 @@
         <v>224</v>
       </c>
       <c r="O371">
-        <v>18214865</v>
+        <v>18048483</v>
       </c>
       <c r="P371" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="Q371" t="s">
         <v>260</v>
@@ -27332,7 +27338,10 @@
         <v>0</v>
       </c>
       <c r="T371" t="s">
-        <v>264</v>
+        <v>262</v>
+      </c>
+      <c r="V371" t="s">
+        <v>277</v>
       </c>
       <c r="W371" t="s">
         <v>371</v>
@@ -27343,16 +27352,13 @@
       <c r="AG371" t="s">
         <v>454</v>
       </c>
-      <c r="AH371" t="s">
-        <v>445</v>
-      </c>
     </row>
     <row r="372" spans="1:34">
       <c r="A372">
-        <v>6627</v>
+        <v>6949</v>
       </c>
       <c r="B372" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C372" t="s">
         <v>60</v>
@@ -27361,10 +27367,10 @@
         <v>61</v>
       </c>
       <c r="E372" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F372" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G372">
         <v>11411</v>
@@ -27388,10 +27394,10 @@
         <v>224</v>
       </c>
       <c r="O372">
-        <v>18048483</v>
+        <v>18214925</v>
       </c>
       <c r="P372" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q372" t="s">
         <v>260</v>
@@ -27400,10 +27406,7 @@
         <v>0</v>
       </c>
       <c r="T372" t="s">
-        <v>262</v>
-      </c>
-      <c r="V372" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="W372" t="s">
         <v>371</v>
@@ -27414,19 +27417,22 @@
       <c r="AG372" t="s">
         <v>454</v>
       </c>
+      <c r="AH372" t="s">
+        <v>445</v>
+      </c>
     </row>
     <row r="373" spans="1:34">
       <c r="A373">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B373" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C373" t="s">
         <v>60</v>
       </c>
       <c r="D373" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E373" t="s">
         <v>64</v>
@@ -27435,7 +27441,7 @@
         <v>67</v>
       </c>
       <c r="G373">
-        <v>11411</v>
+        <v>1877</v>
       </c>
       <c r="H373">
         <v>0</v>
@@ -27444,43 +27450,34 @@
         <v>72</v>
       </c>
       <c r="J373" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L373" s="1">
-        <v>46283</v>
-      </c>
-      <c r="M373" t="s">
-        <v>218</v>
+        <v>46293</v>
       </c>
       <c r="N373" t="s">
         <v>224</v>
       </c>
       <c r="O373">
-        <v>18214925</v>
+        <v>18220188</v>
       </c>
       <c r="P373" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="Q373" t="s">
         <v>260</v>
       </c>
       <c r="S373">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="T373" t="s">
-        <v>264</v>
-      </c>
-      <c r="W373" t="s">
-        <v>371</v>
+        <v>263</v>
       </c>
       <c r="AA373">
         <v>0</v>
       </c>
       <c r="AG373" t="s">
         <v>454</v>
-      </c>
-      <c r="AH373" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="374" spans="1:34">
@@ -27503,7 +27500,7 @@
         <v>67</v>
       </c>
       <c r="G374">
-        <v>1877</v>
+        <v>1879</v>
       </c>
       <c r="H374">
         <v>0</v>
@@ -27512,16 +27509,19 @@
         <v>72</v>
       </c>
       <c r="J374" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L374" s="1">
-        <v>46293</v>
+        <v>46283</v>
+      </c>
+      <c r="M374" t="s">
+        <v>218</v>
       </c>
       <c r="N374" t="s">
         <v>224</v>
       </c>
       <c r="O374">
-        <v>18220188</v>
+        <v>18220194</v>
       </c>
       <c r="P374" t="s">
         <v>244</v>
@@ -27530,11 +27530,14 @@
         <v>260</v>
       </c>
       <c r="S374">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="T374" t="s">
         <v>263</v>
       </c>
+      <c r="W374" t="s">
+        <v>371</v>
+      </c>
       <c r="AA374">
         <v>0</v>
       </c>
@@ -27544,25 +27547,25 @@
     </row>
     <row r="375" spans="1:34">
       <c r="A375">
-        <v>6628</v>
+        <v>6962</v>
       </c>
       <c r="B375" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C375" t="s">
         <v>60</v>
       </c>
       <c r="D375" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E375" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F375" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G375">
-        <v>1879</v>
+        <v>1881</v>
       </c>
       <c r="H375">
         <v>0</v>
@@ -27571,34 +27574,28 @@
         <v>72</v>
       </c>
       <c r="J375" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L375" s="1">
-        <v>46283</v>
+        <v>46287</v>
       </c>
       <c r="N375" t="s">
         <v>224</v>
       </c>
       <c r="O375">
-        <v>17988684</v>
+        <v>18260044</v>
       </c>
       <c r="P375" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q375" t="s">
         <v>260</v>
       </c>
       <c r="S375">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="T375" t="s">
-        <v>262</v>
-      </c>
-      <c r="V375" t="s">
-        <v>277</v>
-      </c>
-      <c r="W375" t="s">
-        <v>372</v>
+        <v>265</v>
       </c>
       <c r="AA375">
         <v>0</v>
@@ -27612,16 +27609,16 @@
     </row>
     <row r="376" spans="1:34">
       <c r="A376">
-        <v>6945</v>
+        <v>6963</v>
       </c>
       <c r="B376" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C376" t="s">
         <v>60</v>
       </c>
       <c r="D376" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E376" t="s">
         <v>64</v>
@@ -27630,7 +27627,7 @@
         <v>67</v>
       </c>
       <c r="G376">
-        <v>1879</v>
+        <v>1881</v>
       </c>
       <c r="H376">
         <v>0</v>
@@ -27639,34 +27636,28 @@
         <v>72</v>
       </c>
       <c r="J376" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L376" s="1">
-        <v>46283</v>
-      </c>
-      <c r="M376" t="s">
-        <v>218</v>
+        <v>46287</v>
       </c>
       <c r="N376" t="s">
         <v>224</v>
       </c>
       <c r="O376">
-        <v>18220194</v>
+        <v>18260177</v>
       </c>
       <c r="P376" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q376" t="s">
         <v>260</v>
       </c>
       <c r="S376">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="T376" t="s">
-        <v>263</v>
-      </c>
-      <c r="W376" t="s">
-        <v>371</v>
+        <v>265</v>
       </c>
       <c r="AA376">
         <v>0</v>
@@ -27674,28 +27665,31 @@
       <c r="AG376" t="s">
         <v>454</v>
       </c>
+      <c r="AH376" t="s">
+        <v>445</v>
+      </c>
     </row>
     <row r="377" spans="1:34">
       <c r="A377">
-        <v>6962</v>
+        <v>6548</v>
       </c>
       <c r="B377" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C377" t="s">
         <v>60</v>
       </c>
       <c r="D377" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E377" t="s">
         <v>64</v>
       </c>
       <c r="F377" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G377">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="H377">
         <v>0</v>
@@ -27704,7 +27698,7 @@
         <v>72</v>
       </c>
       <c r="J377" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L377" s="1">
         <v>46287</v>
@@ -27713,10 +27707,10 @@
         <v>224</v>
       </c>
       <c r="O377">
-        <v>18260044</v>
+        <v>17988567</v>
       </c>
       <c r="P377" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="Q377" t="s">
         <v>260</v>
@@ -27725,7 +27719,10 @@
         <v>-4</v>
       </c>
       <c r="T377" t="s">
-        <v>265</v>
+        <v>261</v>
+      </c>
+      <c r="V377" t="s">
+        <v>277</v>
       </c>
       <c r="AA377">
         <v>0</v>
@@ -27739,25 +27736,25 @@
     </row>
     <row r="378" spans="1:34">
       <c r="A378">
-        <v>6963</v>
+        <v>6627</v>
       </c>
       <c r="B378" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C378" t="s">
         <v>60</v>
       </c>
       <c r="D378" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E378" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F378" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G378">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="H378">
         <v>0</v>
@@ -27766,7 +27763,7 @@
         <v>72</v>
       </c>
       <c r="J378" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L378" s="1">
         <v>46287</v>
@@ -27775,10 +27772,10 @@
         <v>224</v>
       </c>
       <c r="O378">
-        <v>18260177</v>
+        <v>17968390</v>
       </c>
       <c r="P378" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="Q378" t="s">
         <v>260</v>
@@ -27787,7 +27784,10 @@
         <v>-4</v>
       </c>
       <c r="T378" t="s">
-        <v>265</v>
+        <v>262</v>
+      </c>
+      <c r="V378" t="s">
+        <v>277</v>
       </c>
       <c r="AA378">
         <v>0</v>
@@ -27795,16 +27795,13 @@
       <c r="AG378" t="s">
         <v>454</v>
       </c>
-      <c r="AH378" t="s">
-        <v>445</v>
-      </c>
     </row>
     <row r="379" spans="1:34">
       <c r="A379">
-        <v>6548</v>
+        <v>6949</v>
       </c>
       <c r="B379" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C379" t="s">
         <v>60</v>
@@ -27816,7 +27813,7 @@
         <v>64</v>
       </c>
       <c r="F379" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G379">
         <v>1882</v>
@@ -27837,10 +27834,10 @@
         <v>224</v>
       </c>
       <c r="O379">
-        <v>17988567</v>
+        <v>18214871</v>
       </c>
       <c r="P379" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q379" t="s">
         <v>260</v>
@@ -27849,10 +27846,7 @@
         <v>-4</v>
       </c>
       <c r="T379" t="s">
-        <v>261</v>
-      </c>
-      <c r="V379" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="AA379">
         <v>0</v>
@@ -27866,10 +27860,10 @@
     </row>
     <row r="380" spans="1:34">
       <c r="A380">
-        <v>6627</v>
+        <v>6949</v>
       </c>
       <c r="B380" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C380" t="s">
         <v>60</v>
@@ -27878,60 +27872,60 @@
         <v>61</v>
       </c>
       <c r="E380" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F380" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G380">
-        <v>1882</v>
+        <v>1914</v>
       </c>
       <c r="H380">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="I380" t="s">
         <v>72</v>
       </c>
       <c r="J380" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L380" s="1">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="N380" t="s">
         <v>224</v>
       </c>
       <c r="O380">
-        <v>17968390</v>
+        <v>18214883</v>
       </c>
       <c r="P380" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q380" t="s">
         <v>260</v>
       </c>
       <c r="S380">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T380" t="s">
-        <v>262</v>
-      </c>
-      <c r="V380" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="AA380">
         <v>0</v>
       </c>
       <c r="AG380" t="s">
-        <v>454</v>
+        <v>453</v>
+      </c>
+      <c r="AH380" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="381" spans="1:34">
       <c r="A381">
-        <v>6949</v>
+        <v>5417</v>
       </c>
       <c r="B381" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C381" t="s">
         <v>60</v>
@@ -27943,57 +27937,57 @@
         <v>64</v>
       </c>
       <c r="F381" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G381">
-        <v>1882</v>
+        <v>6759</v>
       </c>
       <c r="H381">
-        <v>0</v>
+        <v>1788</v>
       </c>
       <c r="I381" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J381" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="L381" s="1">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="N381" t="s">
         <v>224</v>
       </c>
       <c r="O381">
-        <v>18214871</v>
+        <v>17399190</v>
       </c>
       <c r="P381" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q381" t="s">
         <v>260</v>
       </c>
       <c r="S381">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="T381" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AA381">
         <v>0</v>
       </c>
       <c r="AG381" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AH381" t="s">
-        <v>445</v>
+        <v>462</v>
       </c>
     </row>
     <row r="382" spans="1:34">
       <c r="A382">
-        <v>6949</v>
+        <v>6486</v>
       </c>
       <c r="B382" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C382" t="s">
         <v>60</v>
@@ -28005,40 +27999,43 @@
         <v>64</v>
       </c>
       <c r="F382" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G382">
-        <v>1914</v>
+        <v>6759</v>
       </c>
       <c r="H382">
-        <v>1862</v>
+        <v>1788</v>
       </c>
       <c r="I382" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J382" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L382" s="1">
-        <v>46286</v>
+        <v>46289</v>
       </c>
       <c r="N382" t="s">
         <v>224</v>
       </c>
       <c r="O382">
-        <v>18214883</v>
+        <v>16976177</v>
       </c>
       <c r="P382" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q382" t="s">
         <v>260</v>
       </c>
       <c r="S382">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="T382" t="s">
-        <v>264</v>
+        <v>268</v>
+      </c>
+      <c r="V382" t="s">
+        <v>277</v>
       </c>
       <c r="AA382">
         <v>0</v>
@@ -28047,21 +28044,21 @@
         <v>453</v>
       </c>
       <c r="AH382" t="s">
-        <v>445</v>
+        <v>462</v>
       </c>
     </row>
     <row r="383" spans="1:34">
       <c r="A383">
-        <v>5417</v>
+        <v>6705</v>
       </c>
       <c r="B383" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C383" t="s">
         <v>60</v>
       </c>
       <c r="D383" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E383" t="s">
         <v>64</v>
@@ -28088,7 +28085,7 @@
         <v>224</v>
       </c>
       <c r="O383">
-        <v>17399190</v>
+        <v>17949019</v>
       </c>
       <c r="P383" t="s">
         <v>248</v>
@@ -28100,7 +28097,7 @@
         <v>-6</v>
       </c>
       <c r="T383" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AA383">
         <v>0</v>
@@ -28114,16 +28111,16 @@
     </row>
     <row r="384" spans="1:34">
       <c r="A384">
-        <v>6486</v>
+        <v>6703</v>
       </c>
       <c r="B384" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C384" t="s">
         <v>60</v>
       </c>
       <c r="D384" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E384" t="s">
         <v>64</v>
@@ -28132,25 +28129,28 @@
         <v>66</v>
       </c>
       <c r="G384">
-        <v>6759</v>
+        <v>1802</v>
       </c>
       <c r="H384">
-        <v>1788</v>
+        <v>0</v>
       </c>
       <c r="I384" t="s">
         <v>73</v>
       </c>
       <c r="J384" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="L384" s="1">
-        <v>46289</v>
+        <v>46283</v>
+      </c>
+      <c r="M384" t="s">
+        <v>218</v>
       </c>
       <c r="N384" t="s">
         <v>224</v>
       </c>
       <c r="O384">
-        <v>16976177</v>
+        <v>17948796</v>
       </c>
       <c r="P384" t="s">
         <v>248</v>
@@ -28159,19 +28159,19 @@
         <v>260</v>
       </c>
       <c r="S384">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="T384" t="s">
-        <v>268</v>
-      </c>
-      <c r="V384" t="s">
-        <v>277</v>
+        <v>269</v>
+      </c>
+      <c r="W384" t="s">
+        <v>372</v>
       </c>
       <c r="AA384">
         <v>0</v>
       </c>
       <c r="AG384" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AH384" t="s">
         <v>462</v>
@@ -28179,16 +28179,16 @@
     </row>
     <row r="385" spans="1:34">
       <c r="A385">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B385" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C385" t="s">
         <v>60</v>
       </c>
       <c r="D385" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E385" t="s">
         <v>64</v>
@@ -28197,25 +28197,28 @@
         <v>66</v>
       </c>
       <c r="G385">
-        <v>6759</v>
+        <v>1802</v>
       </c>
       <c r="H385">
-        <v>1788</v>
+        <v>0</v>
       </c>
       <c r="I385" t="s">
         <v>73</v>
       </c>
       <c r="J385" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="L385" s="1">
-        <v>46289</v>
+        <v>46283</v>
+      </c>
+      <c r="M385" t="s">
+        <v>218</v>
       </c>
       <c r="N385" t="s">
         <v>224</v>
       </c>
       <c r="O385">
-        <v>17949019</v>
+        <v>18085198</v>
       </c>
       <c r="P385" t="s">
         <v>248</v>
@@ -28224,16 +28227,22 @@
         <v>260</v>
       </c>
       <c r="S385">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="T385" t="s">
         <v>267</v>
       </c>
+      <c r="V385" t="s">
+        <v>277</v>
+      </c>
+      <c r="W385" t="s">
+        <v>372</v>
+      </c>
       <c r="AA385">
         <v>0</v>
       </c>
       <c r="AG385" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AH385" t="s">
         <v>462</v>
@@ -28241,16 +28250,16 @@
     </row>
     <row r="386" spans="1:34">
       <c r="A386">
-        <v>6703</v>
+        <v>5417</v>
       </c>
       <c r="B386" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C386" t="s">
         <v>60</v>
       </c>
       <c r="D386" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E386" t="s">
         <v>64</v>
@@ -28259,7 +28268,7 @@
         <v>66</v>
       </c>
       <c r="G386">
-        <v>1802</v>
+        <v>11286</v>
       </c>
       <c r="H386">
         <v>0</v>
@@ -28268,7 +28277,7 @@
         <v>73</v>
       </c>
       <c r="J386" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L386" s="1">
         <v>46283</v>
@@ -28280,7 +28289,7 @@
         <v>224</v>
       </c>
       <c r="O386">
-        <v>17948796</v>
+        <v>17399434</v>
       </c>
       <c r="P386" t="s">
         <v>248</v>
@@ -28292,10 +28301,10 @@
         <v>0</v>
       </c>
       <c r="T386" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="W386" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AA386">
         <v>0</v>
@@ -28309,16 +28318,16 @@
     </row>
     <row r="387" spans="1:34">
       <c r="A387">
-        <v>6704</v>
+        <v>6404</v>
       </c>
       <c r="B387" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C387" t="s">
         <v>60</v>
       </c>
       <c r="D387" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E387" t="s">
         <v>64</v>
@@ -28327,7 +28336,7 @@
         <v>66</v>
       </c>
       <c r="G387">
-        <v>1802</v>
+        <v>11286</v>
       </c>
       <c r="H387">
         <v>0</v>
@@ -28336,7 +28345,7 @@
         <v>73</v>
       </c>
       <c r="J387" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L387" s="1">
         <v>46283</v>
@@ -28348,7 +28357,7 @@
         <v>224</v>
       </c>
       <c r="O387">
-        <v>18085198</v>
+        <v>16962464</v>
       </c>
       <c r="P387" t="s">
         <v>248</v>
@@ -28360,13 +28369,10 @@
         <v>0</v>
       </c>
       <c r="T387" t="s">
-        <v>267</v>
-      </c>
-      <c r="V387" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="W387" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AA387">
         <v>0</v>
@@ -28380,16 +28386,16 @@
     </row>
     <row r="388" spans="1:34">
       <c r="A388">
-        <v>5417</v>
+        <v>6705</v>
       </c>
       <c r="B388" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C388" t="s">
         <v>60</v>
       </c>
       <c r="D388" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E388" t="s">
         <v>64</v>
@@ -28398,7 +28404,7 @@
         <v>66</v>
       </c>
       <c r="G388">
-        <v>11286</v>
+        <v>1803</v>
       </c>
       <c r="H388">
         <v>0</v>
@@ -28407,19 +28413,16 @@
         <v>73</v>
       </c>
       <c r="J388" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L388" s="1">
-        <v>46283</v>
-      </c>
-      <c r="M388" t="s">
-        <v>218</v>
+        <v>46293</v>
       </c>
       <c r="N388" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="O388">
-        <v>17399434</v>
+        <v>17948937</v>
       </c>
       <c r="P388" t="s">
         <v>248</v>
@@ -28428,13 +28431,10 @@
         <v>260</v>
       </c>
       <c r="S388">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="T388" t="s">
-        <v>266</v>
-      </c>
-      <c r="W388" t="s">
-        <v>373</v>
+        <v>267</v>
       </c>
       <c r="AA388">
         <v>0</v>
@@ -28448,10 +28448,10 @@
     </row>
     <row r="389" spans="1:34">
       <c r="A389">
-        <v>6404</v>
+        <v>6703</v>
       </c>
       <c r="B389" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C389" t="s">
         <v>60</v>
@@ -28466,7 +28466,7 @@
         <v>66</v>
       </c>
       <c r="G389">
-        <v>11286</v>
+        <v>1811</v>
       </c>
       <c r="H389">
         <v>0</v>
@@ -28475,19 +28475,16 @@
         <v>73</v>
       </c>
       <c r="J389" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="L389" s="1">
-        <v>46283</v>
-      </c>
-      <c r="M389" t="s">
-        <v>218</v>
+        <v>46290</v>
       </c>
       <c r="N389" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O389">
-        <v>16962464</v>
+        <v>17948816</v>
       </c>
       <c r="P389" t="s">
         <v>248</v>
@@ -28496,13 +28493,10 @@
         <v>260</v>
       </c>
       <c r="S389">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="T389" t="s">
-        <v>270</v>
-      </c>
-      <c r="W389" t="s">
-        <v>373</v>
+        <v>269</v>
       </c>
       <c r="AA389">
         <v>0</v>
@@ -28516,16 +28510,16 @@
     </row>
     <row r="390" spans="1:34">
       <c r="A390">
-        <v>6705</v>
+        <v>6404</v>
       </c>
       <c r="B390" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C390" t="s">
         <v>60</v>
       </c>
       <c r="D390" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E390" t="s">
         <v>64</v>
@@ -28534,7 +28528,7 @@
         <v>66</v>
       </c>
       <c r="G390">
-        <v>1803</v>
+        <v>1807</v>
       </c>
       <c r="H390">
         <v>0</v>
@@ -28543,16 +28537,16 @@
         <v>73</v>
       </c>
       <c r="J390" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="L390" s="1">
-        <v>46293</v>
+        <v>46287</v>
       </c>
       <c r="N390" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O390">
-        <v>17948937</v>
+        <v>16962171</v>
       </c>
       <c r="P390" t="s">
         <v>248</v>
@@ -28561,10 +28555,10 @@
         <v>260</v>
       </c>
       <c r="S390">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="T390" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="AA390">
         <v>0</v>
@@ -28596,7 +28590,7 @@
         <v>66</v>
       </c>
       <c r="G391">
-        <v>1811</v>
+        <v>1807</v>
       </c>
       <c r="H391">
         <v>0</v>
@@ -28605,16 +28599,16 @@
         <v>73</v>
       </c>
       <c r="J391" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L391" s="1">
-        <v>46290</v>
+        <v>46287</v>
       </c>
       <c r="N391" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="O391">
-        <v>17948816</v>
+        <v>17948806</v>
       </c>
       <c r="P391" t="s">
         <v>248</v>
@@ -28623,7 +28617,7 @@
         <v>260</v>
       </c>
       <c r="S391">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="T391" t="s">
         <v>269</v>
@@ -28640,16 +28634,16 @@
     </row>
     <row r="392" spans="1:34">
       <c r="A392">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B392" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C392" t="s">
         <v>60</v>
       </c>
       <c r="D392" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E392" t="s">
         <v>64</v>
@@ -28658,7 +28652,7 @@
         <v>66</v>
       </c>
       <c r="G392">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="H392">
         <v>0</v>
@@ -28667,7 +28661,7 @@
         <v>73</v>
       </c>
       <c r="J392" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L392" s="1">
         <v>46287</v>
@@ -28676,7 +28670,7 @@
         <v>224</v>
       </c>
       <c r="O392">
-        <v>16962171</v>
+        <v>17398965</v>
       </c>
       <c r="P392" t="s">
         <v>248</v>
@@ -28688,7 +28682,7 @@
         <v>-4</v>
       </c>
       <c r="T392" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AA392">
         <v>0</v>
@@ -28702,16 +28696,16 @@
     </row>
     <row r="393" spans="1:34">
       <c r="A393">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B393" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C393" t="s">
         <v>60</v>
       </c>
       <c r="D393" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E393" t="s">
         <v>64</v>
@@ -28720,7 +28714,7 @@
         <v>66</v>
       </c>
       <c r="G393">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="H393">
         <v>0</v>
@@ -28729,7 +28723,7 @@
         <v>73</v>
       </c>
       <c r="J393" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L393" s="1">
         <v>46287</v>
@@ -28738,7 +28732,7 @@
         <v>224</v>
       </c>
       <c r="O393">
-        <v>17948806</v>
+        <v>18085209</v>
       </c>
       <c r="P393" t="s">
         <v>248</v>
@@ -28750,7 +28744,10 @@
         <v>-4</v>
       </c>
       <c r="T393" t="s">
-        <v>269</v>
+        <v>267</v>
+      </c>
+      <c r="V393" t="s">
+        <v>277</v>
       </c>
       <c r="AA393">
         <v>0</v>
@@ -28764,55 +28761,61 @@
     </row>
     <row r="394" spans="1:34">
       <c r="A394">
-        <v>5417</v>
+        <v>6628</v>
       </c>
       <c r="B394" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C394" t="s">
         <v>60</v>
       </c>
       <c r="D394" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E394" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F394" t="s">
         <v>66</v>
       </c>
       <c r="G394">
-        <v>1808</v>
+        <v>945</v>
       </c>
       <c r="H394">
         <v>0</v>
       </c>
       <c r="I394" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J394" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="L394" s="1">
-        <v>46287</v>
+        <v>46283</v>
       </c>
       <c r="N394" t="s">
         <v>224</v>
       </c>
       <c r="O394">
-        <v>17398965</v>
+        <v>16959938</v>
       </c>
       <c r="P394" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q394" t="s">
         <v>260</v>
       </c>
       <c r="S394">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="T394" t="s">
-        <v>266</v>
+        <v>262</v>
+      </c>
+      <c r="V394" t="s">
+        <v>277</v>
+      </c>
+      <c r="W394" t="s">
+        <v>373</v>
       </c>
       <c r="AA394">
         <v>0</v>
@@ -28820,22 +28823,19 @@
       <c r="AG394" t="s">
         <v>454</v>
       </c>
-      <c r="AH394" t="s">
-        <v>462</v>
-      </c>
     </row>
     <row r="395" spans="1:34">
       <c r="A395">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B395" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C395" t="s">
         <v>60</v>
       </c>
       <c r="D395" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E395" t="s">
         <v>64</v>
@@ -28844,40 +28844,40 @@
         <v>66</v>
       </c>
       <c r="G395">
-        <v>1808</v>
+        <v>945</v>
       </c>
       <c r="H395">
         <v>0</v>
       </c>
       <c r="I395" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J395" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="L395" s="1">
-        <v>46287</v>
+        <v>46283</v>
       </c>
       <c r="N395" t="s">
         <v>224</v>
       </c>
       <c r="O395">
-        <v>18085209</v>
+        <v>17952524</v>
       </c>
       <c r="P395" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q395" t="s">
         <v>260</v>
       </c>
       <c r="S395">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="T395" t="s">
         <v>267</v>
       </c>
-      <c r="V395" t="s">
-        <v>277</v>
+      <c r="W395" t="s">
+        <v>374</v>
       </c>
       <c r="AA395">
         <v>0</v>
@@ -28885,16 +28885,13 @@
       <c r="AG395" t="s">
         <v>454</v>
       </c>
-      <c r="AH395" t="s">
-        <v>462</v>
-      </c>
     </row>
     <row r="396" spans="1:34">
       <c r="A396">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B396" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C396" t="s">
         <v>60</v>
@@ -28927,7 +28924,7 @@
         <v>224</v>
       </c>
       <c r="O396">
-        <v>17952524</v>
+        <v>18056695</v>
       </c>
       <c r="P396" t="s">
         <v>249</v>
@@ -28941,6 +28938,9 @@
       <c r="T396" t="s">
         <v>267</v>
       </c>
+      <c r="V396" t="s">
+        <v>277</v>
+      </c>
       <c r="W396" t="s">
         <v>374</v>
       </c>
@@ -28953,25 +28953,25 @@
     </row>
     <row r="397" spans="1:34">
       <c r="A397">
-        <v>6779</v>
+        <v>6627</v>
       </c>
       <c r="B397" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="C397" t="s">
         <v>60</v>
       </c>
       <c r="D397" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E397" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F397" t="s">
         <v>66</v>
       </c>
       <c r="G397">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H397">
         <v>0</v>
@@ -28980,16 +28980,19 @@
         <v>74</v>
       </c>
       <c r="J397" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L397" s="1">
         <v>46283</v>
       </c>
+      <c r="M397" t="s">
+        <v>218</v>
+      </c>
       <c r="N397" t="s">
         <v>224</v>
       </c>
       <c r="O397">
-        <v>18056695</v>
+        <v>17042272</v>
       </c>
       <c r="P397" t="s">
         <v>249</v>
@@ -29001,13 +29004,13 @@
         <v>0</v>
       </c>
       <c r="T397" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="V397" t="s">
         <v>277</v>
       </c>
       <c r="W397" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AA397">
         <v>0</v>
@@ -29018,22 +29021,22 @@
     </row>
     <row r="398" spans="1:34">
       <c r="A398">
-        <v>6627</v>
+        <v>6945</v>
       </c>
       <c r="B398" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C398" t="s">
         <v>60</v>
       </c>
       <c r="D398" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E398" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F398" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G398">
         <v>946</v>
@@ -29057,7 +29060,7 @@
         <v>224</v>
       </c>
       <c r="O398">
-        <v>17042272</v>
+        <v>18164494</v>
       </c>
       <c r="P398" t="s">
         <v>249</v>
@@ -29069,13 +29072,10 @@
         <v>0</v>
       </c>
       <c r="T398" t="s">
-        <v>262</v>
-      </c>
-      <c r="V398" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="W398" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AA398">
         <v>0</v>
@@ -29086,25 +29086,25 @@
     </row>
     <row r="399" spans="1:34">
       <c r="A399">
-        <v>6945</v>
+        <v>5417</v>
       </c>
       <c r="B399" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C399" t="s">
         <v>60</v>
       </c>
       <c r="D399" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E399" t="s">
         <v>64</v>
       </c>
       <c r="F399" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G399">
-        <v>946</v>
+        <v>940</v>
       </c>
       <c r="H399">
         <v>0</v>
@@ -29113,7 +29113,7 @@
         <v>74</v>
       </c>
       <c r="J399" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L399" s="1">
         <v>46283</v>
@@ -29122,10 +29122,10 @@
         <v>218</v>
       </c>
       <c r="N399" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O399">
-        <v>18164494</v>
+        <v>17398840</v>
       </c>
       <c r="P399" t="s">
         <v>249</v>
@@ -29137,16 +29137,16 @@
         <v>0</v>
       </c>
       <c r="T399" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="W399" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AA399">
         <v>0</v>
       </c>
       <c r="AG399" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="400" spans="1:34">
@@ -29169,7 +29169,7 @@
         <v>66</v>
       </c>
       <c r="G400">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="H400">
         <v>0</v>
@@ -29178,19 +29178,16 @@
         <v>74</v>
       </c>
       <c r="J400" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L400" s="1">
-        <v>46283</v>
-      </c>
-      <c r="M400" t="s">
-        <v>218</v>
+        <v>46295</v>
       </c>
       <c r="N400" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O400">
-        <v>17398840</v>
+        <v>17398859</v>
       </c>
       <c r="P400" t="s">
         <v>249</v>
@@ -29199,27 +29196,24 @@
         <v>260</v>
       </c>
       <c r="S400">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="T400" t="s">
         <v>266</v>
       </c>
-      <c r="W400" t="s">
-        <v>375</v>
-      </c>
       <c r="AA400">
         <v>0</v>
       </c>
       <c r="AG400" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="401" spans="1:34">
       <c r="A401">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B401" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C401" t="s">
         <v>60</v>
@@ -29252,7 +29246,7 @@
         <v>224</v>
       </c>
       <c r="O401">
-        <v>17398859</v>
+        <v>16975890</v>
       </c>
       <c r="P401" t="s">
         <v>249</v>
@@ -29264,7 +29258,10 @@
         <v>-12</v>
       </c>
       <c r="T401" t="s">
-        <v>266</v>
+        <v>268</v>
+      </c>
+      <c r="V401" t="s">
+        <v>277</v>
       </c>
       <c r="AA401">
         <v>0</v>
@@ -29275,16 +29272,16 @@
     </row>
     <row r="402" spans="1:34">
       <c r="A402">
-        <v>6486</v>
+        <v>6703</v>
       </c>
       <c r="B402" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C402" t="s">
         <v>60</v>
       </c>
       <c r="D402" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E402" t="s">
         <v>64</v>
@@ -29311,7 +29308,7 @@
         <v>224</v>
       </c>
       <c r="O402">
-        <v>16975890</v>
+        <v>17941122</v>
       </c>
       <c r="P402" t="s">
         <v>249</v>
@@ -29323,10 +29320,7 @@
         <v>-12</v>
       </c>
       <c r="T402" t="s">
-        <v>268</v>
-      </c>
-      <c r="V402" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="AA402">
         <v>0</v>
@@ -29337,16 +29331,16 @@
     </row>
     <row r="403" spans="1:34">
       <c r="A403">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B403" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C403" t="s">
         <v>60</v>
       </c>
       <c r="D403" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E403" t="s">
         <v>64</v>
@@ -29373,7 +29367,7 @@
         <v>224</v>
       </c>
       <c r="O403">
-        <v>17941122</v>
+        <v>17952314</v>
       </c>
       <c r="P403" t="s">
         <v>249</v>
@@ -29385,7 +29379,10 @@
         <v>-12</v>
       </c>
       <c r="T403" t="s">
-        <v>269</v>
+        <v>267</v>
+      </c>
+      <c r="V403" t="s">
+        <v>277</v>
       </c>
       <c r="AA403">
         <v>0</v>
@@ -29396,16 +29393,16 @@
     </row>
     <row r="404" spans="1:34">
       <c r="A404">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B404" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C404" t="s">
         <v>60</v>
       </c>
       <c r="D404" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E404" t="s">
         <v>64</v>
@@ -29432,7 +29429,7 @@
         <v>224</v>
       </c>
       <c r="O404">
-        <v>17952314</v>
+        <v>17952513</v>
       </c>
       <c r="P404" t="s">
         <v>249</v>
@@ -29446,9 +29443,6 @@
       <c r="T404" t="s">
         <v>267</v>
       </c>
-      <c r="V404" t="s">
-        <v>277</v>
-      </c>
       <c r="AA404">
         <v>0</v>
       </c>
@@ -29458,22 +29452,22 @@
     </row>
     <row r="405" spans="1:34">
       <c r="A405">
-        <v>6705</v>
+        <v>6949</v>
       </c>
       <c r="B405" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C405" t="s">
         <v>60</v>
       </c>
       <c r="D405" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E405" t="s">
         <v>64</v>
       </c>
       <c r="F405" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G405">
         <v>943</v>
@@ -29494,7 +29488,7 @@
         <v>224</v>
       </c>
       <c r="O405">
-        <v>17952513</v>
+        <v>18178126</v>
       </c>
       <c r="P405" t="s">
         <v>249</v>
@@ -29506,7 +29500,7 @@
         <v>-12</v>
       </c>
       <c r="T405" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="AA405">
         <v>0</v>
@@ -29517,16 +29511,16 @@
     </row>
     <row r="406" spans="1:34">
       <c r="A406">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B406" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C406" t="s">
         <v>60</v>
       </c>
       <c r="D406" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E406" t="s">
         <v>64</v>
@@ -29553,7 +29547,7 @@
         <v>224</v>
       </c>
       <c r="O406">
-        <v>18178126</v>
+        <v>18188710</v>
       </c>
       <c r="P406" t="s">
         <v>249</v>
@@ -29565,7 +29559,7 @@
         <v>-12</v>
       </c>
       <c r="T406" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AA406">
         <v>0</v>
@@ -29576,10 +29570,10 @@
     </row>
     <row r="407" spans="1:34">
       <c r="A407">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B407" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C407" t="s">
         <v>60</v>
@@ -29612,7 +29606,7 @@
         <v>224</v>
       </c>
       <c r="O407">
-        <v>18188710</v>
+        <v>18188616</v>
       </c>
       <c r="P407" t="s">
         <v>249</v>
@@ -29635,61 +29629,67 @@
     </row>
     <row r="408" spans="1:34">
       <c r="A408">
-        <v>6963</v>
+        <v>5417</v>
       </c>
       <c r="B408" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C408" t="s">
         <v>60</v>
       </c>
       <c r="D408" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E408" t="s">
         <v>64</v>
       </c>
       <c r="F408" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G408">
-        <v>943</v>
+        <v>6813</v>
       </c>
       <c r="H408">
         <v>0</v>
       </c>
       <c r="I408" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J408" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L408" s="1">
-        <v>46295</v>
+        <v>46286</v>
+      </c>
+      <c r="M408" t="s">
+        <v>216</v>
       </c>
       <c r="N408" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O408">
-        <v>18188616</v>
+        <v>17399241</v>
       </c>
       <c r="P408" t="s">
-        <v>249</v>
+        <v>64</v>
       </c>
       <c r="Q408" t="s">
         <v>260</v>
       </c>
       <c r="S408">
-        <v>-12</v>
+        <v>-3</v>
       </c>
       <c r="T408" t="s">
-        <v>265</v>
+        <v>266</v>
+      </c>
+      <c r="W408" t="s">
+        <v>376</v>
       </c>
       <c r="AA408">
         <v>0</v>
       </c>
       <c r="AG408" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="409" spans="1:34">
@@ -29712,69 +29712,69 @@
         <v>66</v>
       </c>
       <c r="G409">
-        <v>6813</v>
+        <v>11056</v>
       </c>
       <c r="H409">
         <v>0</v>
       </c>
       <c r="I409" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J409" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="L409" s="1">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="M409" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N409" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O409">
-        <v>17399241</v>
+        <v>18275526</v>
       </c>
       <c r="P409" t="s">
-        <v>64</v>
+        <v>254</v>
       </c>
       <c r="Q409" t="s">
         <v>260</v>
       </c>
       <c r="S409">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="T409" t="s">
         <v>266</v>
       </c>
       <c r="W409" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AA409">
         <v>0</v>
       </c>
       <c r="AG409" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="410" spans="1:34">
       <c r="A410">
-        <v>5417</v>
+        <v>6962</v>
       </c>
       <c r="B410" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C410" t="s">
         <v>60</v>
       </c>
       <c r="D410" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E410" t="s">
         <v>64</v>
       </c>
       <c r="F410" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G410">
         <v>11056</v>
@@ -29791,14 +29791,11 @@
       <c r="L410" s="1">
         <v>46287</v>
       </c>
-      <c r="M410" t="s">
-        <v>221</v>
-      </c>
       <c r="N410" t="s">
         <v>224</v>
       </c>
       <c r="O410">
-        <v>18275526</v>
+        <v>18274091</v>
       </c>
       <c r="P410" t="s">
         <v>254</v>
@@ -29810,10 +29807,10 @@
         <v>-4</v>
       </c>
       <c r="T410" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="W410" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AA410">
         <v>0</v>
@@ -29824,72 +29821,81 @@
     </row>
     <row r="411" spans="1:34">
       <c r="A411">
-        <v>6962</v>
+        <v>6628</v>
       </c>
       <c r="B411" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C411" t="s">
         <v>60</v>
       </c>
       <c r="D411" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E411" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F411" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G411">
-        <v>11056</v>
+        <v>1650</v>
       </c>
       <c r="H411">
         <v>0</v>
       </c>
       <c r="I411" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="J411" t="s">
-        <v>131</v>
+        <v>161</v>
       </c>
       <c r="L411" s="1">
-        <v>46287</v>
+        <v>46293</v>
       </c>
       <c r="N411" t="s">
         <v>224</v>
       </c>
       <c r="O411">
-        <v>18274091</v>
+        <v>16959974</v>
       </c>
       <c r="P411" t="s">
-        <v>254</v>
+        <v>230</v>
       </c>
       <c r="Q411" t="s">
-        <v>260</v>
+        <v>258</v>
+      </c>
+      <c r="R411" s="1">
+        <v>46265.00248284722</v>
       </c>
       <c r="S411">
-        <v>-4</v>
+        <v>-10</v>
       </c>
       <c r="T411" t="s">
-        <v>265</v>
-      </c>
-      <c r="W411" t="s">
-        <v>378</v>
+        <v>262</v>
+      </c>
+      <c r="V411" t="s">
+        <v>277</v>
       </c>
       <c r="AA411">
         <v>0</v>
+      </c>
+      <c r="AB411" t="s">
+        <v>446</v>
       </c>
       <c r="AG411" t="s">
         <v>453</v>
       </c>
+      <c r="AH411" t="s">
+        <v>457</v>
+      </c>
     </row>
     <row r="412" spans="1:34">
       <c r="A412">
-        <v>6628</v>
+        <v>6945</v>
       </c>
       <c r="B412" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C412" t="s">
         <v>60</v>
@@ -29898,10 +29904,10 @@
         <v>62</v>
       </c>
       <c r="E412" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F412" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G412">
         <v>1650</v>
@@ -29922,25 +29928,22 @@
         <v>224</v>
       </c>
       <c r="O412">
-        <v>16959974</v>
+        <v>18163667</v>
       </c>
       <c r="P412" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q412" t="s">
         <v>258</v>
       </c>
       <c r="R412" s="1">
-        <v>46265.00248284722</v>
+        <v>46265.00255472222</v>
       </c>
       <c r="S412">
         <v>-10</v>
       </c>
       <c r="T412" t="s">
-        <v>262</v>
-      </c>
-      <c r="V412" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="AA412">
         <v>0</v>
@@ -29957,25 +29960,25 @@
     </row>
     <row r="413" spans="1:34">
       <c r="A413">
-        <v>6945</v>
+        <v>6548</v>
       </c>
       <c r="B413" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C413" t="s">
         <v>60</v>
       </c>
       <c r="D413" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E413" t="s">
         <v>64</v>
       </c>
       <c r="F413" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G413">
-        <v>1650</v>
+        <v>1652</v>
       </c>
       <c r="H413">
         <v>0</v>
@@ -29984,31 +29987,37 @@
         <v>69</v>
       </c>
       <c r="J413" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L413" s="1">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="N413" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O413">
-        <v>18163667</v>
+        <v>17967989</v>
       </c>
       <c r="P413" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="Q413" t="s">
         <v>258</v>
       </c>
       <c r="R413" s="1">
-        <v>46265.00255472222</v>
+        <v>46234.66180127315</v>
       </c>
       <c r="S413">
-        <v>-10</v>
+        <v>-7</v>
       </c>
       <c r="T413" t="s">
-        <v>263</v>
+        <v>261</v>
+      </c>
+      <c r="V413" t="s">
+        <v>277</v>
+      </c>
+      <c r="W413" t="s">
+        <v>379</v>
       </c>
       <c r="AA413">
         <v>0</v>
@@ -30017,18 +30026,18 @@
         <v>446</v>
       </c>
       <c r="AG413" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AH413" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="414" spans="1:34">
       <c r="A414">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B414" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C414" t="s">
         <v>60</v>
@@ -30037,7 +30046,7 @@
         <v>61</v>
       </c>
       <c r="E414" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F414" t="s">
         <v>66</v>
@@ -30061,28 +30070,28 @@
         <v>226</v>
       </c>
       <c r="O414">
-        <v>17967989</v>
+        <v>17042389</v>
       </c>
       <c r="P414" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q414" t="s">
         <v>258</v>
       </c>
       <c r="R414" s="1">
-        <v>46234.66180127315</v>
+        <v>46245.76585582176</v>
       </c>
       <c r="S414">
         <v>-7</v>
       </c>
       <c r="T414" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="V414" t="s">
         <v>277</v>
       </c>
       <c r="W414" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AA414">
         <v>0</v>
@@ -30094,15 +30103,15 @@
         <v>454</v>
       </c>
       <c r="AH414" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="415" spans="1:34">
       <c r="A415">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B415" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C415" t="s">
         <v>60</v>
@@ -30111,72 +30120,69 @@
         <v>61</v>
       </c>
       <c r="E415" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F415" t="s">
         <v>66</v>
       </c>
       <c r="G415">
-        <v>1652</v>
+        <v>1697</v>
       </c>
       <c r="H415">
-        <v>0</v>
+        <v>1650</v>
       </c>
       <c r="I415" t="s">
         <v>69</v>
       </c>
       <c r="J415" t="s">
-        <v>162</v>
+        <v>139</v>
       </c>
       <c r="L415" s="1">
-        <v>46290</v>
+        <v>46286</v>
       </c>
       <c r="N415" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="O415">
-        <v>17042389</v>
+        <v>17968001</v>
       </c>
       <c r="P415" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Q415" t="s">
         <v>258</v>
       </c>
       <c r="R415" s="1">
-        <v>46245.76585582176</v>
+        <v>46282.62254486111</v>
       </c>
       <c r="S415">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="T415" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="V415" t="s">
         <v>277</v>
       </c>
-      <c r="W415" t="s">
-        <v>380</v>
-      </c>
       <c r="AA415">
         <v>0</v>
       </c>
       <c r="AB415" t="s">
-        <v>446</v>
+        <v>229</v>
       </c>
       <c r="AG415" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AH415" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="416" spans="1:34">
       <c r="A416">
-        <v>6548</v>
+        <v>6949</v>
       </c>
       <c r="B416" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C416" t="s">
         <v>60</v>
@@ -30188,7 +30194,7 @@
         <v>64</v>
       </c>
       <c r="F416" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G416">
         <v>1697</v>
@@ -30209,7 +30215,7 @@
         <v>224</v>
       </c>
       <c r="O416">
-        <v>17968001</v>
+        <v>18178280</v>
       </c>
       <c r="P416" t="s">
         <v>229</v>
@@ -30218,16 +30224,13 @@
         <v>258</v>
       </c>
       <c r="R416" s="1">
-        <v>46282.62254486111</v>
+        <v>46283.44840582176</v>
       </c>
       <c r="S416">
         <v>-3</v>
       </c>
       <c r="T416" t="s">
-        <v>261</v>
-      </c>
-      <c r="V416" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="AA416">
         <v>0</v>
@@ -35081,25 +35084,25 @@
     </row>
     <row r="485" spans="1:34">
       <c r="A485">
-        <v>6548</v>
+        <v>6628</v>
       </c>
       <c r="B485" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C485" t="s">
         <v>60</v>
       </c>
       <c r="D485" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E485" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F485" t="s">
         <v>66</v>
       </c>
       <c r="G485">
-        <v>7026</v>
+        <v>1879</v>
       </c>
       <c r="H485">
         <v>0</v>
@@ -35108,31 +35111,31 @@
         <v>72</v>
       </c>
       <c r="J485" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="L485" s="1">
-        <v>46288</v>
+        <v>46283</v>
       </c>
       <c r="N485" t="s">
         <v>224</v>
       </c>
       <c r="O485">
-        <v>18094899</v>
+        <v>17988684</v>
       </c>
       <c r="P485" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q485" t="s">
         <v>258</v>
       </c>
       <c r="R485" s="1">
-        <v>46282.74573174769</v>
+        <v>46283.41459880787</v>
       </c>
       <c r="S485">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="T485" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="V485" t="s">
         <v>277</v>
@@ -35144,10 +35147,10 @@
         <v>0</v>
       </c>
       <c r="AB485" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="AG485" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AH485" t="s">
         <v>445</v>
@@ -35155,10 +35158,10 @@
     </row>
     <row r="486" spans="1:34">
       <c r="A486">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B486" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C486" t="s">
         <v>60</v>
@@ -35167,7 +35170,7 @@
         <v>61</v>
       </c>
       <c r="E486" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F486" t="s">
         <v>66</v>
@@ -35191,22 +35194,22 @@
         <v>224</v>
       </c>
       <c r="O486">
-        <v>18048473</v>
+        <v>18094899</v>
       </c>
       <c r="P486" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q486" t="s">
         <v>258</v>
       </c>
       <c r="R486" s="1">
-        <v>46282.74485532408</v>
+        <v>46282.74573174769</v>
       </c>
       <c r="S486">
         <v>-5</v>
       </c>
       <c r="T486" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="V486" t="s">
         <v>277</v>
@@ -35223,19 +35226,22 @@
       <c r="AG486" t="s">
         <v>453</v>
       </c>
+      <c r="AH486" t="s">
+        <v>445</v>
+      </c>
     </row>
     <row r="487" spans="1:34">
       <c r="A487">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B487" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C487" t="s">
         <v>60</v>
       </c>
       <c r="D487" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E487" t="s">
         <v>65</v>
@@ -35262,16 +35268,16 @@
         <v>224</v>
       </c>
       <c r="O487">
-        <v>18094910</v>
+        <v>18048473</v>
       </c>
       <c r="P487" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q487" t="s">
         <v>258</v>
       </c>
       <c r="R487" s="1">
-        <v>46280.66345891204</v>
+        <v>46282.74485532408</v>
       </c>
       <c r="S487">
         <v>-5</v>
@@ -35294,73 +35300,73 @@
       <c r="AG487" t="s">
         <v>453</v>
       </c>
-      <c r="AH487" t="s">
-        <v>445</v>
-      </c>
     </row>
     <row r="488" spans="1:34">
       <c r="A488">
-        <v>6548</v>
+        <v>6628</v>
       </c>
       <c r="B488" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C488" t="s">
         <v>60</v>
       </c>
       <c r="D488" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E488" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F488" t="s">
         <v>66</v>
       </c>
       <c r="G488">
-        <v>1914</v>
+        <v>7026</v>
       </c>
       <c r="H488">
-        <v>1862</v>
+        <v>0</v>
       </c>
       <c r="I488" t="s">
         <v>72</v>
       </c>
       <c r="J488" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="L488" s="1">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="N488" t="s">
         <v>224</v>
       </c>
       <c r="O488">
-        <v>17988591</v>
+        <v>18094910</v>
       </c>
       <c r="P488" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q488" t="s">
         <v>258</v>
       </c>
       <c r="R488" s="1">
-        <v>46283.39413969908</v>
+        <v>46280.66345891204</v>
       </c>
       <c r="S488">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="T488" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="V488" t="s">
         <v>277</v>
       </c>
+      <c r="W488" t="s">
+        <v>402</v>
+      </c>
       <c r="AA488">
         <v>0</v>
       </c>
       <c r="AB488" t="s">
-        <v>243</v>
+        <v>446</v>
       </c>
       <c r="AG488" t="s">
         <v>453</v>
@@ -35371,10 +35377,10 @@
     </row>
     <row r="489" spans="1:34">
       <c r="A489">
-        <v>6704</v>
+        <v>6548</v>
       </c>
       <c r="B489" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C489" t="s">
         <v>60</v>
@@ -35389,75 +35395,69 @@
         <v>66</v>
       </c>
       <c r="G489">
-        <v>11874</v>
+        <v>1914</v>
       </c>
       <c r="H489">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="I489" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J489" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="L489" s="1">
-        <v>46281</v>
-      </c>
-      <c r="M489" t="s">
-        <v>223</v>
+        <v>46286</v>
       </c>
       <c r="N489" t="s">
         <v>224</v>
       </c>
       <c r="O489">
-        <v>18273589</v>
+        <v>17988591</v>
       </c>
       <c r="P489" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="Q489" t="s">
         <v>258</v>
       </c>
       <c r="R489" s="1">
-        <v>46282.70138376157</v>
+        <v>46283.39413969908</v>
       </c>
       <c r="S489">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="T489" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="V489" t="s">
         <v>277</v>
       </c>
-      <c r="W489" t="s">
-        <v>402</v>
-      </c>
       <c r="AA489">
         <v>0</v>
       </c>
       <c r="AB489" t="s">
-        <v>441</v>
+        <v>243</v>
       </c>
       <c r="AG489" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AH489" t="s">
-        <v>462</v>
+        <v>445</v>
       </c>
     </row>
     <row r="490" spans="1:34">
       <c r="A490">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B490" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C490" t="s">
         <v>60</v>
       </c>
       <c r="D490" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E490" t="s">
         <v>64</v>
@@ -35487,7 +35487,7 @@
         <v>224</v>
       </c>
       <c r="O490">
-        <v>18239293</v>
+        <v>18273589</v>
       </c>
       <c r="P490" t="s">
         <v>248</v>
@@ -35496,7 +35496,7 @@
         <v>258</v>
       </c>
       <c r="R490" s="1">
-        <v>46282.7013840625</v>
+        <v>46282.70138376157</v>
       </c>
       <c r="S490">
         <v>2</v>
@@ -35504,8 +35504,11 @@
       <c r="T490" t="s">
         <v>267</v>
       </c>
+      <c r="V490" t="s">
+        <v>277</v>
+      </c>
       <c r="W490" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AA490">
         <v>0</v>
@@ -35522,16 +35525,16 @@
     </row>
     <row r="491" spans="1:34">
       <c r="A491">
-        <v>6486</v>
+        <v>6705</v>
       </c>
       <c r="B491" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C491" t="s">
         <v>60</v>
       </c>
       <c r="D491" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E491" t="s">
         <v>64</v>
@@ -35540,7 +35543,7 @@
         <v>66</v>
       </c>
       <c r="G491">
-        <v>11286</v>
+        <v>11874</v>
       </c>
       <c r="H491">
         <v>0</v>
@@ -35549,16 +35552,19 @@
         <v>73</v>
       </c>
       <c r="J491" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="L491" s="1">
-        <v>46283</v>
+        <v>46281</v>
+      </c>
+      <c r="M491" t="s">
+        <v>223</v>
       </c>
       <c r="N491" t="s">
         <v>224</v>
       </c>
       <c r="O491">
-        <v>18155336</v>
+        <v>18239293</v>
       </c>
       <c r="P491" t="s">
         <v>248</v>
@@ -35567,16 +35573,13 @@
         <v>258</v>
       </c>
       <c r="R491" s="1">
-        <v>46280.59788275463</v>
+        <v>46282.7013840625</v>
       </c>
       <c r="S491">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T491" t="s">
-        <v>268</v>
-      </c>
-      <c r="V491" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="W491" t="s">
         <v>403</v>
@@ -35585,7 +35588,7 @@
         <v>0</v>
       </c>
       <c r="AB491" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="AG491" t="s">
         <v>454</v>
@@ -35596,10 +35599,10 @@
     </row>
     <row r="492" spans="1:34">
       <c r="A492">
-        <v>6704</v>
+        <v>6486</v>
       </c>
       <c r="B492" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C492" t="s">
         <v>60</v>
@@ -35614,7 +35617,7 @@
         <v>66</v>
       </c>
       <c r="G492">
-        <v>1788</v>
+        <v>11286</v>
       </c>
       <c r="H492">
         <v>0</v>
@@ -35623,16 +35626,16 @@
         <v>73</v>
       </c>
       <c r="J492" t="s">
-        <v>175</v>
+        <v>148</v>
       </c>
       <c r="L492" s="1">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="N492" t="s">
         <v>224</v>
       </c>
       <c r="O492">
-        <v>18085132</v>
+        <v>18155336</v>
       </c>
       <c r="P492" t="s">
         <v>248</v>
@@ -35641,25 +35644,28 @@
         <v>258</v>
       </c>
       <c r="R492" s="1">
-        <v>46266.45957931713</v>
+        <v>46280.59788275463</v>
       </c>
       <c r="S492">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T492" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="V492" t="s">
         <v>277</v>
       </c>
+      <c r="W492" t="s">
+        <v>404</v>
+      </c>
       <c r="AA492">
         <v>0</v>
       </c>
       <c r="AB492" t="s">
-        <v>248</v>
+        <v>446</v>
       </c>
       <c r="AG492" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AH492" t="s">
         <v>462</v>
@@ -35667,16 +35673,16 @@
     </row>
     <row r="493" spans="1:34">
       <c r="A493">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B493" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C493" t="s">
         <v>60</v>
       </c>
       <c r="D493" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E493" t="s">
         <v>64</v>
@@ -35685,7 +35691,7 @@
         <v>66</v>
       </c>
       <c r="G493">
-        <v>1805</v>
+        <v>1788</v>
       </c>
       <c r="H493">
         <v>0</v>
@@ -35694,16 +35700,16 @@
         <v>73</v>
       </c>
       <c r="J493" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="L493" s="1">
-        <v>46283</v>
+        <v>46281</v>
       </c>
       <c r="N493" t="s">
         <v>224</v>
       </c>
       <c r="O493">
-        <v>17948948</v>
+        <v>18085132</v>
       </c>
       <c r="P493" t="s">
         <v>248</v>
@@ -35712,25 +35718,25 @@
         <v>258</v>
       </c>
       <c r="R493" s="1">
-        <v>46283.35452896991</v>
+        <v>46266.45957931713</v>
       </c>
       <c r="S493">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T493" t="s">
         <v>267</v>
       </c>
-      <c r="W493" t="s">
-        <v>404</v>
+      <c r="V493" t="s">
+        <v>277</v>
       </c>
       <c r="AA493">
         <v>0</v>
       </c>
       <c r="AB493" t="s">
-        <v>441</v>
+        <v>248</v>
       </c>
       <c r="AG493" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AH493" t="s">
         <v>462</v>
@@ -35738,10 +35744,10 @@
     </row>
     <row r="494" spans="1:34">
       <c r="A494">
-        <v>6779</v>
+        <v>6705</v>
       </c>
       <c r="B494" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C494" t="s">
         <v>60</v>
@@ -35774,7 +35780,7 @@
         <v>224</v>
       </c>
       <c r="O494">
-        <v>18084966</v>
+        <v>17948948</v>
       </c>
       <c r="P494" t="s">
         <v>248</v>
@@ -35783,7 +35789,7 @@
         <v>258</v>
       </c>
       <c r="R494" s="1">
-        <v>46283.35453171296</v>
+        <v>46283.35452896991</v>
       </c>
       <c r="S494">
         <v>0</v>
@@ -35791,11 +35797,8 @@
       <c r="T494" t="s">
         <v>267</v>
       </c>
-      <c r="V494" t="s">
-        <v>277</v>
-      </c>
       <c r="W494" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AA494">
         <v>0</v>
@@ -35812,16 +35815,16 @@
     </row>
     <row r="495" spans="1:34">
       <c r="A495">
-        <v>6404</v>
+        <v>6779</v>
       </c>
       <c r="B495" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C495" t="s">
         <v>60</v>
       </c>
       <c r="D495" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E495" t="s">
         <v>64</v>
@@ -35830,7 +35833,7 @@
         <v>66</v>
       </c>
       <c r="G495">
-        <v>1811</v>
+        <v>1805</v>
       </c>
       <c r="H495">
         <v>0</v>
@@ -35839,16 +35842,16 @@
         <v>73</v>
       </c>
       <c r="J495" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="L495" s="1">
-        <v>46290</v>
+        <v>46283</v>
       </c>
       <c r="N495" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="O495">
-        <v>16962181</v>
+        <v>18084966</v>
       </c>
       <c r="P495" t="s">
         <v>248</v>
@@ -35857,19 +35860,25 @@
         <v>258</v>
       </c>
       <c r="R495" s="1">
-        <v>46240.6829959838</v>
+        <v>46283.35453171296</v>
       </c>
       <c r="S495">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="T495" t="s">
-        <v>270</v>
+        <v>267</v>
+      </c>
+      <c r="V495" t="s">
+        <v>277</v>
+      </c>
+      <c r="W495" t="s">
+        <v>405</v>
       </c>
       <c r="AA495">
         <v>0</v>
       </c>
       <c r="AB495" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="AG495" t="s">
         <v>454</v>
@@ -35880,16 +35889,16 @@
     </row>
     <row r="496" spans="1:34">
       <c r="A496">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B496" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C496" t="s">
         <v>60</v>
       </c>
       <c r="D496" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E496" t="s">
         <v>64</v>
@@ -35898,7 +35907,7 @@
         <v>66</v>
       </c>
       <c r="G496">
-        <v>7025</v>
+        <v>1811</v>
       </c>
       <c r="H496">
         <v>0</v>
@@ -35907,16 +35916,16 @@
         <v>73</v>
       </c>
       <c r="J496" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="L496" s="1">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="N496" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O496">
-        <v>17399280</v>
+        <v>16962181</v>
       </c>
       <c r="P496" t="s">
         <v>248</v>
@@ -35925,25 +35934,22 @@
         <v>258</v>
       </c>
       <c r="R496" s="1">
-        <v>46283.38367943287</v>
+        <v>46240.6829959838</v>
       </c>
       <c r="S496">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="T496" t="s">
-        <v>266</v>
-      </c>
-      <c r="W496" t="s">
-        <v>405</v>
+        <v>270</v>
       </c>
       <c r="AA496">
         <v>0</v>
       </c>
       <c r="AB496" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="AG496" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AH496" t="s">
         <v>462</v>
@@ -35951,16 +35957,16 @@
     </row>
     <row r="497" spans="1:34">
       <c r="A497">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B497" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C497" t="s">
         <v>60</v>
       </c>
       <c r="D497" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E497" t="s">
         <v>64</v>
@@ -35987,7 +35993,7 @@
         <v>224</v>
       </c>
       <c r="O497">
-        <v>16962338</v>
+        <v>17399280</v>
       </c>
       <c r="P497" t="s">
         <v>248</v>
@@ -35996,13 +36002,13 @@
         <v>258</v>
       </c>
       <c r="R497" s="1">
-        <v>46282.54038741898</v>
+        <v>46283.38367943287</v>
       </c>
       <c r="S497">
         <v>-5</v>
       </c>
       <c r="T497" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="W497" t="s">
         <v>406</v>
@@ -36022,16 +36028,16 @@
     </row>
     <row r="498" spans="1:34">
       <c r="A498">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B498" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C498" t="s">
         <v>60</v>
       </c>
       <c r="D498" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E498" t="s">
         <v>64</v>
@@ -36040,7 +36046,7 @@
         <v>66</v>
       </c>
       <c r="G498">
-        <v>1793</v>
+        <v>7025</v>
       </c>
       <c r="H498">
         <v>0</v>
@@ -36049,19 +36055,16 @@
         <v>73</v>
       </c>
       <c r="J498" t="s">
-        <v>107</v>
+        <v>174</v>
       </c>
       <c r="L498" s="1">
-        <v>46283</v>
-      </c>
-      <c r="M498" t="s">
-        <v>218</v>
+        <v>46288</v>
       </c>
       <c r="N498" t="s">
         <v>224</v>
       </c>
       <c r="O498">
-        <v>17398945</v>
+        <v>16962338</v>
       </c>
       <c r="P498" t="s">
         <v>248</v>
@@ -36070,25 +36073,25 @@
         <v>258</v>
       </c>
       <c r="R498" s="1">
-        <v>46280.74859975695</v>
+        <v>46282.54038741898</v>
       </c>
       <c r="S498">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="T498" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="W498" t="s">
-        <v>373</v>
+        <v>407</v>
       </c>
       <c r="AA498">
         <v>0</v>
       </c>
       <c r="AB498" t="s">
-        <v>248</v>
+        <v>446</v>
       </c>
       <c r="AG498" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AH498" t="s">
         <v>462</v>
@@ -36096,73 +36099,76 @@
     </row>
     <row r="499" spans="1:34">
       <c r="A499">
-        <v>6628</v>
+        <v>5417</v>
       </c>
       <c r="B499" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C499" t="s">
         <v>60</v>
       </c>
       <c r="D499" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E499" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F499" t="s">
         <v>66</v>
       </c>
       <c r="G499">
-        <v>945</v>
+        <v>1793</v>
       </c>
       <c r="H499">
         <v>0</v>
       </c>
       <c r="I499" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J499" t="s">
-        <v>156</v>
+        <v>107</v>
       </c>
       <c r="L499" s="1">
         <v>46283</v>
       </c>
+      <c r="M499" t="s">
+        <v>218</v>
+      </c>
       <c r="N499" t="s">
         <v>224</v>
       </c>
       <c r="O499">
-        <v>16959938</v>
+        <v>17398945</v>
       </c>
       <c r="P499" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="Q499" t="s">
         <v>258</v>
       </c>
       <c r="R499" s="1">
-        <v>46266.04180934028</v>
+        <v>46280.74859975695</v>
       </c>
       <c r="S499">
         <v>0</v>
       </c>
       <c r="T499" t="s">
-        <v>262</v>
-      </c>
-      <c r="V499" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="W499" t="s">
-        <v>407</v>
+        <v>372</v>
       </c>
       <c r="AA499">
         <v>0</v>
       </c>
       <c r="AB499" t="s">
-        <v>446</v>
+        <v>248</v>
       </c>
       <c r="AG499" t="s">
         <v>454</v>
+      </c>
+      <c r="AH499" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="500" spans="1:34">
@@ -37445,7 +37451,7 @@
         <v>267</v>
       </c>
       <c r="W518" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AA518">
         <v>0</v>
@@ -43723,7 +43729,7 @@
         <v>275</v>
       </c>
       <c r="W609" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG609" t="s">
         <v>454</v>
@@ -43788,7 +43794,7 @@
         <v>275</v>
       </c>
       <c r="W610" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG610" t="s">
         <v>454</v>
@@ -43853,7 +43859,7 @@
         <v>275</v>
       </c>
       <c r="W611" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG611" t="s">
         <v>454</v>
@@ -43977,6 +43983,71 @@
         <v>263</v>
       </c>
       <c r="AG613" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="614" spans="1:34">
+      <c r="A614">
+        <v>7095</v>
+      </c>
+      <c r="B614" t="s">
+        <v>54</v>
+      </c>
+      <c r="C614" t="s">
+        <v>60</v>
+      </c>
+      <c r="D614" t="s">
+        <v>62</v>
+      </c>
+      <c r="E614" t="s">
+        <v>64</v>
+      </c>
+      <c r="F614" t="s">
+        <v>67</v>
+      </c>
+      <c r="G614">
+        <v>6813</v>
+      </c>
+      <c r="H614">
+        <v>0</v>
+      </c>
+      <c r="I614" t="s">
+        <v>75</v>
+      </c>
+      <c r="J614" t="s">
+        <v>160</v>
+      </c>
+      <c r="K614" s="1">
+        <v>46293</v>
+      </c>
+      <c r="L614" s="1">
+        <v>46283</v>
+      </c>
+      <c r="M614" t="s">
+        <v>216</v>
+      </c>
+      <c r="N614" t="s">
+        <v>225</v>
+      </c>
+      <c r="O614">
+        <v>18274356</v>
+      </c>
+      <c r="P614" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q614" t="s">
+        <v>260</v>
+      </c>
+      <c r="S614">
+        <v>0</v>
+      </c>
+      <c r="T614" t="s">
+        <v>263</v>
+      </c>
+      <c r="W614" t="s">
+        <v>376</v>
+      </c>
+      <c r="AG614" t="s">
         <v>455</v>
       </c>
     </row>

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8958" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8961" uniqueCount="464">
   <si>
     <t>CodCliente</t>
   </si>
@@ -1136,9 +1136,6 @@
 em processo de emissão e liberação - Data Comentário: 18/09/2026 10:59</t>
   </si>
   <si>
-    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 18/09/2026 - Data Comentário: 15/09/2026 15:19</t>
-  </si>
-  <si>
     <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 18/09/2026 - Data Comentário: 10/09/2026 08:23</t>
   </si>
   <si>
@@ -1233,6 +1230,9 @@
   </si>
   <si>
     <t>Imposto enviado via SCI Report - Data Comentário: 15/09/2026 11:25</t>
+  </si>
+  <si>
+    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 18/09/2026 - Data Comentário: 15/09/2026 15:19</t>
   </si>
   <si>
     <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 18/09/2026 
@@ -25840,10 +25840,10 @@
     </row>
     <row r="349" spans="1:34">
       <c r="A349">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B349" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C349" t="s">
         <v>60</v>
@@ -25879,10 +25879,10 @@
         <v>225</v>
       </c>
       <c r="O349">
-        <v>16976037</v>
+        <v>17222579</v>
       </c>
       <c r="P349" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q349" t="s">
         <v>260</v>
@@ -25891,7 +25891,7 @@
         <v>-3</v>
       </c>
       <c r="T349" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="V349" t="s">
         <v>277</v>
@@ -25911,16 +25911,16 @@
     </row>
     <row r="350" spans="1:34">
       <c r="A350">
-        <v>6548</v>
+        <v>6703</v>
       </c>
       <c r="B350" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C350" t="s">
         <v>60</v>
       </c>
       <c r="D350" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E350" t="s">
         <v>64</v>
@@ -25950,10 +25950,10 @@
         <v>225</v>
       </c>
       <c r="O350">
-        <v>17222579</v>
+        <v>18077082</v>
       </c>
       <c r="P350" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q350" t="s">
         <v>260</v>
@@ -25962,10 +25962,7 @@
         <v>-3</v>
       </c>
       <c r="T350" t="s">
-        <v>261</v>
-      </c>
-      <c r="V350" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="W350" t="s">
         <v>366</v>
@@ -25982,19 +25979,19 @@
     </row>
     <row r="351" spans="1:34">
       <c r="A351">
-        <v>6627</v>
+        <v>6779</v>
       </c>
       <c r="B351" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C351" t="s">
         <v>60</v>
       </c>
       <c r="D351" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E351" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F351" t="s">
         <v>66</v>
@@ -26015,16 +26012,16 @@
         <v>46286</v>
       </c>
       <c r="M351" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="N351" t="s">
         <v>225</v>
       </c>
       <c r="O351">
-        <v>18068500</v>
+        <v>18090149</v>
       </c>
       <c r="P351" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="Q351" t="s">
         <v>260</v>
@@ -26033,13 +26030,13 @@
         <v>-3</v>
       </c>
       <c r="T351" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="V351" t="s">
         <v>277</v>
       </c>
       <c r="W351" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AA351">
         <v>0</v>
@@ -26048,15 +26045,15 @@
         <v>454</v>
       </c>
       <c r="AH351" t="s">
-        <v>461</v>
+        <v>256</v>
       </c>
     </row>
     <row r="352" spans="1:34">
       <c r="A352">
-        <v>6628</v>
+        <v>6945</v>
       </c>
       <c r="B352" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C352" t="s">
         <v>60</v>
@@ -26065,10 +26062,10 @@
         <v>62</v>
       </c>
       <c r="E352" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F352" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G352">
         <v>5836</v>
@@ -26085,17 +26082,14 @@
       <c r="L352" s="1">
         <v>46286</v>
       </c>
-      <c r="M352" t="s">
-        <v>217</v>
-      </c>
       <c r="N352" t="s">
         <v>225</v>
       </c>
       <c r="O352">
-        <v>18052419</v>
+        <v>18179083</v>
       </c>
       <c r="P352" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q352" t="s">
         <v>260</v>
@@ -26104,13 +26098,7 @@
         <v>-3</v>
       </c>
       <c r="T352" t="s">
-        <v>262</v>
-      </c>
-      <c r="V352" t="s">
-        <v>277</v>
-      </c>
-      <c r="W352" t="s">
-        <v>365</v>
+        <v>263</v>
       </c>
       <c r="AA352">
         <v>0</v>
@@ -26119,21 +26107,21 @@
         <v>454</v>
       </c>
       <c r="AH352" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="353" spans="1:34">
       <c r="A353">
-        <v>6703</v>
+        <v>6548</v>
       </c>
       <c r="B353" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C353" t="s">
         <v>60</v>
       </c>
       <c r="D353" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E353" t="s">
         <v>64</v>
@@ -26142,7 +26130,7 @@
         <v>66</v>
       </c>
       <c r="G353">
-        <v>5836</v>
+        <v>5905</v>
       </c>
       <c r="H353">
         <v>5784</v>
@@ -26151,40 +26139,37 @@
         <v>71</v>
       </c>
       <c r="J353" t="s">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="L353" s="1">
-        <v>46286</v>
-      </c>
-      <c r="M353" t="s">
-        <v>217</v>
+        <v>46295</v>
       </c>
       <c r="N353" t="s">
         <v>225</v>
       </c>
       <c r="O353">
-        <v>18077082</v>
+        <v>17222671</v>
       </c>
       <c r="P353" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q353" t="s">
         <v>260</v>
       </c>
       <c r="S353">
-        <v>-3</v>
+        <v>-12</v>
       </c>
       <c r="T353" t="s">
-        <v>269</v>
-      </c>
-      <c r="W353" t="s">
-        <v>367</v>
+        <v>261</v>
+      </c>
+      <c r="V353" t="s">
+        <v>277</v>
       </c>
       <c r="AA353">
         <v>0</v>
       </c>
       <c r="AG353" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AH353" t="s">
         <v>461</v>
@@ -26192,16 +26177,16 @@
     </row>
     <row r="354" spans="1:34">
       <c r="A354">
-        <v>6779</v>
+        <v>6548</v>
       </c>
       <c r="B354" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C354" t="s">
         <v>60</v>
       </c>
       <c r="D354" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E354" t="s">
         <v>64</v>
@@ -26210,7 +26195,7 @@
         <v>66</v>
       </c>
       <c r="G354">
-        <v>5836</v>
+        <v>5853</v>
       </c>
       <c r="H354">
         <v>5784</v>
@@ -26219,38 +26204,32 @@
         <v>71</v>
       </c>
       <c r="J354" t="s">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="L354" s="1">
-        <v>46286</v>
-      </c>
-      <c r="M354" t="s">
-        <v>215</v>
+        <v>46295</v>
       </c>
       <c r="N354" t="s">
         <v>225</v>
       </c>
       <c r="O354">
-        <v>18090149</v>
+        <v>17222589</v>
       </c>
       <c r="P354" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="Q354" t="s">
         <v>260</v>
       </c>
       <c r="S354">
-        <v>-3</v>
+        <v>-12</v>
       </c>
       <c r="T354" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="V354" t="s">
         <v>277</v>
       </c>
-      <c r="W354" t="s">
-        <v>368</v>
-      </c>
       <c r="AA354">
         <v>0</v>
       </c>
@@ -26258,30 +26237,30 @@
         <v>454</v>
       </c>
       <c r="AH354" t="s">
-        <v>256</v>
+        <v>461</v>
       </c>
     </row>
     <row r="355" spans="1:34">
       <c r="A355">
-        <v>6945</v>
+        <v>5417</v>
       </c>
       <c r="B355" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C355" t="s">
         <v>60</v>
       </c>
       <c r="D355" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E355" t="s">
         <v>64</v>
       </c>
       <c r="F355" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G355">
-        <v>5836</v>
+        <v>5847</v>
       </c>
       <c r="H355">
         <v>5784</v>
@@ -26290,28 +26269,28 @@
         <v>71</v>
       </c>
       <c r="J355" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L355" s="1">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="N355" t="s">
         <v>225</v>
       </c>
       <c r="O355">
-        <v>18179083</v>
+        <v>18158417</v>
       </c>
       <c r="P355" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q355" t="s">
         <v>260</v>
       </c>
       <c r="S355">
-        <v>-3</v>
+        <v>-10</v>
       </c>
       <c r="T355" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="AA355">
         <v>0</v>
@@ -26319,22 +26298,19 @@
       <c r="AG355" t="s">
         <v>454</v>
       </c>
-      <c r="AH355" t="s">
-        <v>462</v>
-      </c>
     </row>
     <row r="356" spans="1:34">
       <c r="A356">
-        <v>6548</v>
+        <v>6779</v>
       </c>
       <c r="B356" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="C356" t="s">
         <v>60</v>
       </c>
       <c r="D356" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E356" t="s">
         <v>64</v>
@@ -26343,7 +26319,7 @@
         <v>66</v>
       </c>
       <c r="G356">
-        <v>5905</v>
+        <v>5847</v>
       </c>
       <c r="H356">
         <v>5784</v>
@@ -26352,28 +26328,28 @@
         <v>71</v>
       </c>
       <c r="J356" t="s">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="L356" s="1">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="N356" t="s">
         <v>225</v>
       </c>
       <c r="O356">
-        <v>17222671</v>
+        <v>18158764</v>
       </c>
       <c r="P356" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q356" t="s">
         <v>260</v>
       </c>
       <c r="S356">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="T356" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="V356" t="s">
         <v>277</v>
@@ -26382,10 +26358,10 @@
         <v>0</v>
       </c>
       <c r="AG356" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="AH356" t="s">
-        <v>461</v>
+        <v>256</v>
       </c>
     </row>
     <row r="357" spans="1:34">
@@ -26408,7 +26384,7 @@
         <v>66</v>
       </c>
       <c r="G357">
-        <v>5853</v>
+        <v>5906</v>
       </c>
       <c r="H357">
         <v>5784</v>
@@ -26417,7 +26393,7 @@
         <v>71</v>
       </c>
       <c r="J357" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="L357" s="1">
         <v>46295</v>
@@ -26426,7 +26402,7 @@
         <v>225</v>
       </c>
       <c r="O357">
-        <v>17222589</v>
+        <v>17222688</v>
       </c>
       <c r="P357" t="s">
         <v>239</v>
@@ -26447,7 +26423,7 @@
         <v>0</v>
       </c>
       <c r="AG357" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AH357" t="s">
         <v>461</v>
@@ -26455,10 +26431,10 @@
     </row>
     <row r="358" spans="1:34">
       <c r="A358">
-        <v>5417</v>
+        <v>6548</v>
       </c>
       <c r="B358" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C358" t="s">
         <v>60</v>
@@ -26473,7 +26449,7 @@
         <v>66</v>
       </c>
       <c r="G358">
-        <v>5847</v>
+        <v>5907</v>
       </c>
       <c r="H358">
         <v>5784</v>
@@ -26482,28 +26458,31 @@
         <v>71</v>
       </c>
       <c r="J358" t="s">
-        <v>143</v>
+        <v>91</v>
       </c>
       <c r="L358" s="1">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="N358" t="s">
         <v>225</v>
       </c>
       <c r="O358">
-        <v>18158417</v>
+        <v>17222699</v>
       </c>
       <c r="P358" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q358" t="s">
         <v>260</v>
       </c>
       <c r="S358">
-        <v>-10</v>
+        <v>-12</v>
       </c>
       <c r="T358" t="s">
-        <v>266</v>
+        <v>261</v>
+      </c>
+      <c r="V358" t="s">
+        <v>277</v>
       </c>
       <c r="AA358">
         <v>0</v>
@@ -26511,19 +26490,22 @@
       <c r="AG358" t="s">
         <v>454</v>
       </c>
+      <c r="AH358" t="s">
+        <v>461</v>
+      </c>
     </row>
     <row r="359" spans="1:34">
       <c r="A359">
-        <v>6779</v>
+        <v>5417</v>
       </c>
       <c r="B359" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C359" t="s">
         <v>60</v>
       </c>
       <c r="D359" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E359" t="s">
         <v>64</v>
@@ -26532,57 +26514,57 @@
         <v>66</v>
       </c>
       <c r="G359">
-        <v>5847</v>
+        <v>6348</v>
       </c>
       <c r="H359">
-        <v>5784</v>
+        <v>0</v>
       </c>
       <c r="I359" t="s">
         <v>71</v>
       </c>
       <c r="J359" t="s">
-        <v>143</v>
+        <v>92</v>
       </c>
       <c r="L359" s="1">
-        <v>46293</v>
+        <v>46288</v>
+      </c>
+      <c r="M359" t="s">
+        <v>218</v>
       </c>
       <c r="N359" t="s">
         <v>225</v>
       </c>
       <c r="O359">
-        <v>18158764</v>
+        <v>18274307</v>
       </c>
       <c r="P359" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="Q359" t="s">
         <v>260</v>
       </c>
       <c r="S359">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="T359" t="s">
-        <v>267</v>
-      </c>
-      <c r="V359" t="s">
-        <v>277</v>
+        <v>266</v>
+      </c>
+      <c r="W359" t="s">
+        <v>368</v>
       </c>
       <c r="AA359">
         <v>0</v>
       </c>
       <c r="AG359" t="s">
-        <v>454</v>
-      </c>
-      <c r="AH359" t="s">
-        <v>256</v>
+        <v>455</v>
       </c>
     </row>
     <row r="360" spans="1:34">
       <c r="A360">
-        <v>6548</v>
+        <v>6949</v>
       </c>
       <c r="B360" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C360" t="s">
         <v>60</v>
@@ -26594,60 +26576,63 @@
         <v>64</v>
       </c>
       <c r="F360" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G360">
-        <v>5906</v>
+        <v>6348</v>
       </c>
       <c r="H360">
-        <v>5784</v>
+        <v>0</v>
       </c>
       <c r="I360" t="s">
         <v>71</v>
       </c>
       <c r="J360" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="L360" s="1">
-        <v>46295</v>
+        <v>46288</v>
+      </c>
+      <c r="M360" t="s">
+        <v>219</v>
       </c>
       <c r="N360" t="s">
         <v>225</v>
       </c>
       <c r="O360">
-        <v>17222688</v>
+        <v>18275979</v>
       </c>
       <c r="P360" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Q360" t="s">
         <v>260</v>
       </c>
       <c r="S360">
-        <v>-12</v>
+        <v>-5</v>
       </c>
       <c r="T360" t="s">
-        <v>261</v>
-      </c>
-      <c r="V360" t="s">
-        <v>277</v>
+        <v>264</v>
+      </c>
+      <c r="W360" t="s">
+        <v>369</v>
       </c>
       <c r="AA360">
         <v>0</v>
       </c>
       <c r="AG360" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AH360" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="361" spans="1:34">
       <c r="A361">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B361" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C361" t="s">
         <v>60</v>
@@ -26656,43 +26641,43 @@
         <v>61</v>
       </c>
       <c r="E361" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F361" t="s">
         <v>66</v>
       </c>
       <c r="G361">
-        <v>5907</v>
+        <v>1913</v>
       </c>
       <c r="H361">
-        <v>5784</v>
+        <v>1862</v>
       </c>
       <c r="I361" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J361" t="s">
-        <v>91</v>
+        <v>144</v>
       </c>
       <c r="L361" s="1">
-        <v>46295</v>
+        <v>46286</v>
       </c>
       <c r="N361" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O361">
-        <v>17222699</v>
+        <v>18048433</v>
       </c>
       <c r="P361" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="Q361" t="s">
         <v>260</v>
       </c>
       <c r="S361">
-        <v>-12</v>
+        <v>-3</v>
       </c>
       <c r="T361" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="V361" t="s">
         <v>277</v>
@@ -26703,16 +26688,13 @@
       <c r="AG361" t="s">
         <v>454</v>
       </c>
-      <c r="AH361" t="s">
-        <v>461</v>
-      </c>
     </row>
     <row r="362" spans="1:34">
       <c r="A362">
-        <v>5417</v>
+        <v>6949</v>
       </c>
       <c r="B362" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C362" t="s">
         <v>60</v>
@@ -26724,66 +26706,63 @@
         <v>64</v>
       </c>
       <c r="F362" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G362">
-        <v>6348</v>
+        <v>1913</v>
       </c>
       <c r="H362">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="I362" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J362" t="s">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="L362" s="1">
-        <v>46288</v>
-      </c>
-      <c r="M362" t="s">
-        <v>218</v>
+        <v>46286</v>
       </c>
       <c r="N362" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O362">
-        <v>18274307</v>
+        <v>18214877</v>
       </c>
       <c r="P362" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="Q362" t="s">
         <v>260</v>
       </c>
       <c r="S362">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="T362" t="s">
-        <v>266</v>
-      </c>
-      <c r="W362" t="s">
-        <v>369</v>
+        <v>264</v>
       </c>
       <c r="AA362">
         <v>0</v>
       </c>
       <c r="AG362" t="s">
-        <v>455</v>
+        <v>454</v>
+      </c>
+      <c r="AH362" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="363" spans="1:34">
       <c r="A363">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B363" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C363" t="s">
         <v>60</v>
       </c>
       <c r="D363" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E363" t="s">
         <v>64</v>
@@ -26792,40 +26771,40 @@
         <v>67</v>
       </c>
       <c r="G363">
-        <v>6348</v>
+        <v>11617</v>
       </c>
       <c r="H363">
         <v>0</v>
       </c>
       <c r="I363" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J363" t="s">
-        <v>92</v>
+        <v>145</v>
       </c>
       <c r="L363" s="1">
-        <v>46288</v>
+        <v>46283</v>
       </c>
       <c r="M363" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N363" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O363">
-        <v>18275979</v>
+        <v>18186565</v>
       </c>
       <c r="P363" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="Q363" t="s">
         <v>260</v>
       </c>
       <c r="S363">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="T363" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="W363" t="s">
         <v>370</v>
@@ -26834,66 +26813,69 @@
         <v>0</v>
       </c>
       <c r="AG363" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AH363" t="s">
-        <v>462</v>
+        <v>447</v>
       </c>
     </row>
     <row r="364" spans="1:34">
       <c r="A364">
-        <v>6627</v>
+        <v>6963</v>
       </c>
       <c r="B364" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C364" t="s">
         <v>60</v>
       </c>
       <c r="D364" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E364" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F364" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G364">
-        <v>1913</v>
+        <v>11617</v>
       </c>
       <c r="H364">
-        <v>1862</v>
+        <v>0</v>
       </c>
       <c r="I364" t="s">
         <v>72</v>
       </c>
       <c r="J364" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L364" s="1">
-        <v>46286</v>
+        <v>46283</v>
+      </c>
+      <c r="M364" t="s">
+        <v>220</v>
       </c>
       <c r="N364" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O364">
-        <v>18048433</v>
+        <v>18186566</v>
       </c>
       <c r="P364" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="Q364" t="s">
         <v>260</v>
       </c>
       <c r="S364">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="T364" t="s">
-        <v>262</v>
-      </c>
-      <c r="V364" t="s">
-        <v>277</v>
+        <v>265</v>
+      </c>
+      <c r="W364" t="s">
+        <v>370</v>
       </c>
       <c r="AA364">
         <v>0</v>
@@ -26901,19 +26883,22 @@
       <c r="AG364" t="s">
         <v>454</v>
       </c>
+      <c r="AH364" t="s">
+        <v>447</v>
+      </c>
     </row>
     <row r="365" spans="1:34">
       <c r="A365">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B365" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C365" t="s">
         <v>60</v>
       </c>
       <c r="D365" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E365" t="s">
         <v>64</v>
@@ -26922,69 +26907,66 @@
         <v>67</v>
       </c>
       <c r="G365">
-        <v>1913</v>
+        <v>5764</v>
       </c>
       <c r="H365">
-        <v>1862</v>
+        <v>0</v>
       </c>
       <c r="I365" t="s">
         <v>72</v>
       </c>
       <c r="J365" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="L365" s="1">
-        <v>46286</v>
+        <v>46290</v>
       </c>
       <c r="N365" t="s">
         <v>224</v>
       </c>
       <c r="O365">
-        <v>18214877</v>
+        <v>18220203</v>
       </c>
       <c r="P365" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="Q365" t="s">
         <v>260</v>
       </c>
       <c r="S365">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="T365" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AA365">
         <v>0</v>
       </c>
       <c r="AG365" t="s">
-        <v>454</v>
-      </c>
-      <c r="AH365" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
     </row>
     <row r="366" spans="1:34">
       <c r="A366">
-        <v>6962</v>
+        <v>6548</v>
       </c>
       <c r="B366" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C366" t="s">
         <v>60</v>
       </c>
       <c r="D366" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E366" t="s">
         <v>64</v>
       </c>
       <c r="F366" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G366">
-        <v>11617</v>
+        <v>1876</v>
       </c>
       <c r="H366">
         <v>0</v>
@@ -26993,22 +26975,22 @@
         <v>72</v>
       </c>
       <c r="J366" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="L366" s="1">
         <v>46283</v>
       </c>
       <c r="M366" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="N366" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="O366">
-        <v>18186565</v>
+        <v>17988555</v>
       </c>
       <c r="P366" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="Q366" t="s">
         <v>260</v>
@@ -27017,7 +26999,10 @@
         <v>0</v>
       </c>
       <c r="T366" t="s">
-        <v>265</v>
+        <v>261</v>
+      </c>
+      <c r="V366" t="s">
+        <v>277</v>
       </c>
       <c r="W366" t="s">
         <v>371</v>
@@ -27026,7 +27011,7 @@
         <v>0</v>
       </c>
       <c r="AG366" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AH366" t="s">
         <v>447</v>
@@ -27034,16 +27019,16 @@
     </row>
     <row r="367" spans="1:34">
       <c r="A367">
-        <v>6963</v>
+        <v>6949</v>
       </c>
       <c r="B367" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C367" t="s">
         <v>60</v>
       </c>
       <c r="D367" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E367" t="s">
         <v>64</v>
@@ -27052,7 +27037,7 @@
         <v>67</v>
       </c>
       <c r="G367">
-        <v>11617</v>
+        <v>1876</v>
       </c>
       <c r="H367">
         <v>0</v>
@@ -27061,22 +27046,22 @@
         <v>72</v>
       </c>
       <c r="J367" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="L367" s="1">
         <v>46283</v>
       </c>
       <c r="M367" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="N367" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="O367">
-        <v>18186566</v>
+        <v>18214865</v>
       </c>
       <c r="P367" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="Q367" t="s">
         <v>260</v>
@@ -27085,7 +27070,7 @@
         <v>0</v>
       </c>
       <c r="T367" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="W367" t="s">
         <v>371</v>
@@ -27094,7 +27079,7 @@
         <v>0</v>
       </c>
       <c r="AG367" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AH367" t="s">
         <v>447</v>
@@ -27102,25 +27087,25 @@
     </row>
     <row r="368" spans="1:34">
       <c r="A368">
-        <v>6945</v>
+        <v>6627</v>
       </c>
       <c r="B368" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C368" t="s">
         <v>60</v>
       </c>
       <c r="D368" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E368" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F368" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G368">
-        <v>5764</v>
+        <v>11411</v>
       </c>
       <c r="H368">
         <v>0</v>
@@ -27129,16 +27114,19 @@
         <v>72</v>
       </c>
       <c r="J368" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="L368" s="1">
-        <v>46290</v>
+        <v>46283</v>
+      </c>
+      <c r="M368" t="s">
+        <v>217</v>
       </c>
       <c r="N368" t="s">
         <v>224</v>
       </c>
       <c r="O368">
-        <v>18220203</v>
+        <v>18048483</v>
       </c>
       <c r="P368" t="s">
         <v>244</v>
@@ -27147,24 +27135,30 @@
         <v>260</v>
       </c>
       <c r="S368">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="T368" t="s">
-        <v>263</v>
+        <v>262</v>
+      </c>
+      <c r="V368" t="s">
+        <v>277</v>
+      </c>
+      <c r="W368" t="s">
+        <v>371</v>
       </c>
       <c r="AA368">
         <v>0</v>
       </c>
       <c r="AG368" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="369" spans="1:34">
       <c r="A369">
-        <v>6548</v>
+        <v>6949</v>
       </c>
       <c r="B369" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C369" t="s">
         <v>60</v>
@@ -27176,10 +27170,10 @@
         <v>64</v>
       </c>
       <c r="F369" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G369">
-        <v>1876</v>
+        <v>11411</v>
       </c>
       <c r="H369">
         <v>0</v>
@@ -27188,7 +27182,7 @@
         <v>72</v>
       </c>
       <c r="J369" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L369" s="1">
         <v>46283</v>
@@ -27200,10 +27194,10 @@
         <v>224</v>
       </c>
       <c r="O369">
-        <v>17988555</v>
+        <v>18214925</v>
       </c>
       <c r="P369" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q369" t="s">
         <v>260</v>
@@ -27212,13 +27206,10 @@
         <v>0</v>
       </c>
       <c r="T369" t="s">
-        <v>261</v>
-      </c>
-      <c r="V369" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="W369" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AA369">
         <v>0</v>
@@ -27232,16 +27223,16 @@
     </row>
     <row r="370" spans="1:34">
       <c r="A370">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B370" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C370" t="s">
         <v>60</v>
       </c>
       <c r="D370" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E370" t="s">
         <v>64</v>
@@ -27250,7 +27241,7 @@
         <v>67</v>
       </c>
       <c r="G370">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="H370">
         <v>0</v>
@@ -27259,34 +27250,28 @@
         <v>72</v>
       </c>
       <c r="J370" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="L370" s="1">
-        <v>46283</v>
-      </c>
-      <c r="M370" t="s">
-        <v>217</v>
+        <v>46293</v>
       </c>
       <c r="N370" t="s">
         <v>224</v>
       </c>
       <c r="O370">
-        <v>18214865</v>
+        <v>18220188</v>
       </c>
       <c r="P370" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="Q370" t="s">
         <v>260</v>
       </c>
       <c r="S370">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="T370" t="s">
-        <v>264</v>
-      </c>
-      <c r="W370" t="s">
-        <v>372</v>
+        <v>263</v>
       </c>
       <c r="AA370">
         <v>0</v>
@@ -27294,31 +27279,28 @@
       <c r="AG370" t="s">
         <v>455</v>
       </c>
-      <c r="AH370" t="s">
-        <v>447</v>
-      </c>
     </row>
     <row r="371" spans="1:34">
       <c r="A371">
-        <v>6627</v>
+        <v>6945</v>
       </c>
       <c r="B371" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C371" t="s">
         <v>60</v>
       </c>
       <c r="D371" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E371" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F371" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G371">
-        <v>11411</v>
+        <v>1879</v>
       </c>
       <c r="H371">
         <v>0</v>
@@ -27327,7 +27309,7 @@
         <v>72</v>
       </c>
       <c r="J371" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="L371" s="1">
         <v>46283</v>
@@ -27339,7 +27321,7 @@
         <v>224</v>
       </c>
       <c r="O371">
-        <v>18048483</v>
+        <v>18220194</v>
       </c>
       <c r="P371" t="s">
         <v>244</v>
@@ -27351,13 +27333,10 @@
         <v>0</v>
       </c>
       <c r="T371" t="s">
-        <v>262</v>
-      </c>
-      <c r="V371" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="W371" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AA371">
         <v>0</v>
@@ -27368,16 +27347,16 @@
     </row>
     <row r="372" spans="1:34">
       <c r="A372">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B372" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C372" t="s">
         <v>60</v>
       </c>
       <c r="D372" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E372" t="s">
         <v>64</v>
@@ -27386,7 +27365,7 @@
         <v>67</v>
       </c>
       <c r="G372">
-        <v>11411</v>
+        <v>1881</v>
       </c>
       <c r="H372">
         <v>0</v>
@@ -27395,34 +27374,28 @@
         <v>72</v>
       </c>
       <c r="J372" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L372" s="1">
-        <v>46283</v>
-      </c>
-      <c r="M372" t="s">
-        <v>217</v>
+        <v>46287</v>
       </c>
       <c r="N372" t="s">
         <v>224</v>
       </c>
       <c r="O372">
-        <v>18214925</v>
+        <v>18260044</v>
       </c>
       <c r="P372" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q372" t="s">
         <v>260</v>
       </c>
       <c r="S372">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="T372" t="s">
-        <v>264</v>
-      </c>
-      <c r="W372" t="s">
-        <v>372</v>
+        <v>265</v>
       </c>
       <c r="AA372">
         <v>0</v>
@@ -27436,16 +27409,16 @@
     </row>
     <row r="373" spans="1:34">
       <c r="A373">
-        <v>6945</v>
+        <v>6963</v>
       </c>
       <c r="B373" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C373" t="s">
         <v>60</v>
       </c>
       <c r="D373" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E373" t="s">
         <v>64</v>
@@ -27454,7 +27427,7 @@
         <v>67</v>
       </c>
       <c r="G373">
-        <v>1877</v>
+        <v>1881</v>
       </c>
       <c r="H373">
         <v>0</v>
@@ -27463,28 +27436,28 @@
         <v>72</v>
       </c>
       <c r="J373" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="L373" s="1">
-        <v>46293</v>
+        <v>46287</v>
       </c>
       <c r="N373" t="s">
         <v>224</v>
       </c>
       <c r="O373">
-        <v>18220188</v>
+        <v>18260177</v>
       </c>
       <c r="P373" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q373" t="s">
         <v>260</v>
       </c>
       <c r="S373">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="T373" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AA373">
         <v>0</v>
@@ -27492,28 +27465,31 @@
       <c r="AG373" t="s">
         <v>455</v>
       </c>
+      <c r="AH373" t="s">
+        <v>447</v>
+      </c>
     </row>
     <row r="374" spans="1:34">
       <c r="A374">
-        <v>6945</v>
+        <v>6548</v>
       </c>
       <c r="B374" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C374" t="s">
         <v>60</v>
       </c>
       <c r="D374" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E374" t="s">
         <v>64</v>
       </c>
       <c r="F374" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G374">
-        <v>1879</v>
+        <v>1882</v>
       </c>
       <c r="H374">
         <v>0</v>
@@ -27522,34 +27498,31 @@
         <v>72</v>
       </c>
       <c r="J374" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="L374" s="1">
-        <v>46283</v>
-      </c>
-      <c r="M374" t="s">
-        <v>217</v>
+        <v>46287</v>
       </c>
       <c r="N374" t="s">
         <v>224</v>
       </c>
       <c r="O374">
-        <v>18220194</v>
+        <v>17988567</v>
       </c>
       <c r="P374" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q374" t="s">
         <v>260</v>
       </c>
       <c r="S374">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="T374" t="s">
-        <v>263</v>
-      </c>
-      <c r="W374" t="s">
-        <v>372</v>
+        <v>261</v>
+      </c>
+      <c r="V374" t="s">
+        <v>277</v>
       </c>
       <c r="AA374">
         <v>0</v>
@@ -27557,28 +27530,31 @@
       <c r="AG374" t="s">
         <v>455</v>
       </c>
+      <c r="AH374" t="s">
+        <v>447</v>
+      </c>
     </row>
     <row r="375" spans="1:34">
       <c r="A375">
-        <v>6962</v>
+        <v>6627</v>
       </c>
       <c r="B375" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C375" t="s">
         <v>60</v>
       </c>
       <c r="D375" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E375" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F375" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G375">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="H375">
         <v>0</v>
@@ -27587,7 +27563,7 @@
         <v>72</v>
       </c>
       <c r="J375" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L375" s="1">
         <v>46287</v>
@@ -27596,10 +27572,10 @@
         <v>224</v>
       </c>
       <c r="O375">
-        <v>18260044</v>
+        <v>17968390</v>
       </c>
       <c r="P375" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="Q375" t="s">
         <v>260</v>
@@ -27608,7 +27584,10 @@
         <v>-4</v>
       </c>
       <c r="T375" t="s">
-        <v>265</v>
+        <v>262</v>
+      </c>
+      <c r="V375" t="s">
+        <v>277</v>
       </c>
       <c r="AA375">
         <v>0</v>
@@ -27616,22 +27595,19 @@
       <c r="AG375" t="s">
         <v>455</v>
       </c>
-      <c r="AH375" t="s">
-        <v>447</v>
-      </c>
     </row>
     <row r="376" spans="1:34">
       <c r="A376">
-        <v>6963</v>
+        <v>6949</v>
       </c>
       <c r="B376" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C376" t="s">
         <v>60</v>
       </c>
       <c r="D376" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E376" t="s">
         <v>64</v>
@@ -27640,7 +27616,7 @@
         <v>67</v>
       </c>
       <c r="G376">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="H376">
         <v>0</v>
@@ -27649,7 +27625,7 @@
         <v>72</v>
       </c>
       <c r="J376" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L376" s="1">
         <v>46287</v>
@@ -27658,10 +27634,10 @@
         <v>224</v>
       </c>
       <c r="O376">
-        <v>18260177</v>
+        <v>18214871</v>
       </c>
       <c r="P376" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q376" t="s">
         <v>260</v>
@@ -27670,7 +27646,7 @@
         <v>-4</v>
       </c>
       <c r="T376" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AA376">
         <v>0</v>
@@ -27684,10 +27660,10 @@
     </row>
     <row r="377" spans="1:34">
       <c r="A377">
-        <v>6548</v>
+        <v>6949</v>
       </c>
       <c r="B377" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C377" t="s">
         <v>60</v>
@@ -27699,49 +27675,46 @@
         <v>64</v>
       </c>
       <c r="F377" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G377">
-        <v>1882</v>
+        <v>1914</v>
       </c>
       <c r="H377">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="I377" t="s">
         <v>72</v>
       </c>
       <c r="J377" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L377" s="1">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="N377" t="s">
         <v>224</v>
       </c>
       <c r="O377">
-        <v>17988567</v>
+        <v>18214883</v>
       </c>
       <c r="P377" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q377" t="s">
         <v>260</v>
       </c>
       <c r="S377">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T377" t="s">
-        <v>261</v>
-      </c>
-      <c r="V377" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="AA377">
         <v>0</v>
       </c>
       <c r="AG377" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AH377" t="s">
         <v>447</v>
@@ -27749,10 +27722,10 @@
     </row>
     <row r="378" spans="1:34">
       <c r="A378">
-        <v>6627</v>
+        <v>6486</v>
       </c>
       <c r="B378" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C378" t="s">
         <v>60</v>
@@ -27761,43 +27734,43 @@
         <v>61</v>
       </c>
       <c r="E378" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F378" t="s">
         <v>66</v>
       </c>
       <c r="G378">
-        <v>1882</v>
+        <v>6759</v>
       </c>
       <c r="H378">
-        <v>0</v>
+        <v>1788</v>
       </c>
       <c r="I378" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J378" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="L378" s="1">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="N378" t="s">
         <v>224</v>
       </c>
       <c r="O378">
-        <v>17968390</v>
+        <v>16976177</v>
       </c>
       <c r="P378" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q378" t="s">
         <v>260</v>
       </c>
       <c r="S378">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="T378" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="V378" t="s">
         <v>277</v>
@@ -27806,139 +27779,148 @@
         <v>0</v>
       </c>
       <c r="AG378" t="s">
-        <v>455</v>
+        <v>454</v>
+      </c>
+      <c r="AH378" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="379" spans="1:34">
       <c r="A379">
-        <v>6949</v>
+        <v>6705</v>
       </c>
       <c r="B379" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C379" t="s">
         <v>60</v>
       </c>
       <c r="D379" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E379" t="s">
         <v>64</v>
       </c>
       <c r="F379" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G379">
-        <v>1882</v>
+        <v>6759</v>
       </c>
       <c r="H379">
-        <v>0</v>
+        <v>1788</v>
       </c>
       <c r="I379" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J379" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="L379" s="1">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="N379" t="s">
         <v>224</v>
       </c>
       <c r="O379">
-        <v>18214871</v>
+        <v>17949019</v>
       </c>
       <c r="P379" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q379" t="s">
         <v>260</v>
       </c>
       <c r="S379">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="T379" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="AA379">
         <v>0</v>
       </c>
       <c r="AG379" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AH379" t="s">
-        <v>447</v>
+        <v>463</v>
       </c>
     </row>
     <row r="380" spans="1:34">
       <c r="A380">
-        <v>6949</v>
+        <v>6703</v>
       </c>
       <c r="B380" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C380" t="s">
         <v>60</v>
       </c>
       <c r="D380" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E380" t="s">
         <v>64</v>
       </c>
       <c r="F380" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G380">
-        <v>1914</v>
+        <v>1802</v>
       </c>
       <c r="H380">
-        <v>1862</v>
+        <v>0</v>
       </c>
       <c r="I380" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J380" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="L380" s="1">
-        <v>46286</v>
+        <v>46283</v>
+      </c>
+      <c r="M380" t="s">
+        <v>217</v>
       </c>
       <c r="N380" t="s">
         <v>224</v>
       </c>
       <c r="O380">
-        <v>18214883</v>
+        <v>17948796</v>
       </c>
       <c r="P380" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q380" t="s">
         <v>260</v>
       </c>
       <c r="S380">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="T380" t="s">
-        <v>264</v>
+        <v>269</v>
+      </c>
+      <c r="W380" t="s">
+        <v>372</v>
       </c>
       <c r="AA380">
         <v>0</v>
       </c>
       <c r="AG380" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AH380" t="s">
-        <v>447</v>
+        <v>463</v>
       </c>
     </row>
     <row r="381" spans="1:34">
       <c r="A381">
-        <v>6486</v>
+        <v>6704</v>
       </c>
       <c r="B381" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C381" t="s">
         <v>60</v>
@@ -27953,25 +27935,28 @@
         <v>66</v>
       </c>
       <c r="G381">
-        <v>6759</v>
+        <v>1802</v>
       </c>
       <c r="H381">
-        <v>1788</v>
+        <v>0</v>
       </c>
       <c r="I381" t="s">
         <v>73</v>
       </c>
       <c r="J381" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="L381" s="1">
-        <v>46289</v>
+        <v>46283</v>
+      </c>
+      <c r="M381" t="s">
+        <v>217</v>
       </c>
       <c r="N381" t="s">
         <v>224</v>
       </c>
       <c r="O381">
-        <v>16976177</v>
+        <v>18085198</v>
       </c>
       <c r="P381" t="s">
         <v>248</v>
@@ -27980,19 +27965,22 @@
         <v>260</v>
       </c>
       <c r="S381">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="T381" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="V381" t="s">
         <v>277</v>
       </c>
+      <c r="W381" t="s">
+        <v>372</v>
+      </c>
       <c r="AA381">
         <v>0</v>
       </c>
       <c r="AG381" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AH381" t="s">
         <v>463</v>
@@ -28000,16 +27988,16 @@
     </row>
     <row r="382" spans="1:34">
       <c r="A382">
-        <v>6705</v>
+        <v>5417</v>
       </c>
       <c r="B382" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C382" t="s">
         <v>60</v>
       </c>
       <c r="D382" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E382" t="s">
         <v>64</v>
@@ -28018,25 +28006,28 @@
         <v>66</v>
       </c>
       <c r="G382">
-        <v>6759</v>
+        <v>11286</v>
       </c>
       <c r="H382">
-        <v>1788</v>
+        <v>0</v>
       </c>
       <c r="I382" t="s">
         <v>73</v>
       </c>
       <c r="J382" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="L382" s="1">
-        <v>46289</v>
+        <v>46283</v>
+      </c>
+      <c r="M382" t="s">
+        <v>217</v>
       </c>
       <c r="N382" t="s">
         <v>224</v>
       </c>
       <c r="O382">
-        <v>17949019</v>
+        <v>17399434</v>
       </c>
       <c r="P382" t="s">
         <v>248</v>
@@ -28045,16 +28036,19 @@
         <v>260</v>
       </c>
       <c r="S382">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="T382" t="s">
-        <v>267</v>
+        <v>266</v>
+      </c>
+      <c r="W382" t="s">
+        <v>372</v>
       </c>
       <c r="AA382">
         <v>0</v>
       </c>
       <c r="AG382" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AH382" t="s">
         <v>463</v>
@@ -28062,10 +28056,10 @@
     </row>
     <row r="383" spans="1:34">
       <c r="A383">
-        <v>6703</v>
+        <v>6404</v>
       </c>
       <c r="B383" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C383" t="s">
         <v>60</v>
@@ -28080,7 +28074,7 @@
         <v>66</v>
       </c>
       <c r="G383">
-        <v>1802</v>
+        <v>11286</v>
       </c>
       <c r="H383">
         <v>0</v>
@@ -28089,7 +28083,7 @@
         <v>73</v>
       </c>
       <c r="J383" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L383" s="1">
         <v>46283</v>
@@ -28101,7 +28095,7 @@
         <v>224</v>
       </c>
       <c r="O383">
-        <v>17948796</v>
+        <v>16962464</v>
       </c>
       <c r="P383" t="s">
         <v>248</v>
@@ -28113,10 +28107,10 @@
         <v>0</v>
       </c>
       <c r="T383" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="W383" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AA383">
         <v>0</v>
@@ -28130,16 +28124,16 @@
     </row>
     <row r="384" spans="1:34">
       <c r="A384">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B384" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C384" t="s">
         <v>60</v>
       </c>
       <c r="D384" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E384" t="s">
         <v>64</v>
@@ -28148,7 +28142,7 @@
         <v>66</v>
       </c>
       <c r="G384">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="H384">
         <v>0</v>
@@ -28157,19 +28151,16 @@
         <v>73</v>
       </c>
       <c r="J384" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="L384" s="1">
-        <v>46283</v>
-      </c>
-      <c r="M384" t="s">
-        <v>217</v>
+        <v>46293</v>
       </c>
       <c r="N384" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="O384">
-        <v>18085198</v>
+        <v>17948937</v>
       </c>
       <c r="P384" t="s">
         <v>248</v>
@@ -28178,17 +28169,11 @@
         <v>260</v>
       </c>
       <c r="S384">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="T384" t="s">
         <v>267</v>
       </c>
-      <c r="V384" t="s">
-        <v>277</v>
-      </c>
-      <c r="W384" t="s">
-        <v>373</v>
-      </c>
       <c r="AA384">
         <v>0</v>
       </c>
@@ -28201,16 +28186,16 @@
     </row>
     <row r="385" spans="1:34">
       <c r="A385">
-        <v>5417</v>
+        <v>6703</v>
       </c>
       <c r="B385" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C385" t="s">
         <v>60</v>
       </c>
       <c r="D385" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E385" t="s">
         <v>64</v>
@@ -28219,7 +28204,7 @@
         <v>66</v>
       </c>
       <c r="G385">
-        <v>11286</v>
+        <v>1811</v>
       </c>
       <c r="H385">
         <v>0</v>
@@ -28228,19 +28213,16 @@
         <v>73</v>
       </c>
       <c r="J385" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="L385" s="1">
-        <v>46283</v>
-      </c>
-      <c r="M385" t="s">
-        <v>217</v>
+        <v>46290</v>
       </c>
       <c r="N385" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O385">
-        <v>17399434</v>
+        <v>17948816</v>
       </c>
       <c r="P385" t="s">
         <v>248</v>
@@ -28249,13 +28231,10 @@
         <v>260</v>
       </c>
       <c r="S385">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="T385" t="s">
-        <v>266</v>
-      </c>
-      <c r="W385" t="s">
-        <v>373</v>
+        <v>269</v>
       </c>
       <c r="AA385">
         <v>0</v>
@@ -28287,7 +28266,7 @@
         <v>66</v>
       </c>
       <c r="G386">
-        <v>11286</v>
+        <v>1807</v>
       </c>
       <c r="H386">
         <v>0</v>
@@ -28296,19 +28275,16 @@
         <v>73</v>
       </c>
       <c r="J386" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L386" s="1">
-        <v>46283</v>
-      </c>
-      <c r="M386" t="s">
-        <v>217</v>
+        <v>46287</v>
       </c>
       <c r="N386" t="s">
         <v>224</v>
       </c>
       <c r="O386">
-        <v>16962464</v>
+        <v>16962171</v>
       </c>
       <c r="P386" t="s">
         <v>248</v>
@@ -28317,14 +28293,11 @@
         <v>260</v>
       </c>
       <c r="S386">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="T386" t="s">
         <v>270</v>
       </c>
-      <c r="W386" t="s">
-        <v>373</v>
-      </c>
       <c r="AA386">
         <v>0</v>
       </c>
@@ -28337,16 +28310,16 @@
     </row>
     <row r="387" spans="1:34">
       <c r="A387">
-        <v>6705</v>
+        <v>6703</v>
       </c>
       <c r="B387" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C387" t="s">
         <v>60</v>
       </c>
       <c r="D387" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E387" t="s">
         <v>64</v>
@@ -28355,7 +28328,7 @@
         <v>66</v>
       </c>
       <c r="G387">
-        <v>1803</v>
+        <v>1807</v>
       </c>
       <c r="H387">
         <v>0</v>
@@ -28364,16 +28337,16 @@
         <v>73</v>
       </c>
       <c r="J387" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="L387" s="1">
-        <v>46293</v>
+        <v>46287</v>
       </c>
       <c r="N387" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O387">
-        <v>17948937</v>
+        <v>17948806</v>
       </c>
       <c r="P387" t="s">
         <v>248</v>
@@ -28382,10 +28355,10 @@
         <v>260</v>
       </c>
       <c r="S387">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="T387" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AA387">
         <v>0</v>
@@ -28399,16 +28372,16 @@
     </row>
     <row r="388" spans="1:34">
       <c r="A388">
-        <v>6703</v>
+        <v>5417</v>
       </c>
       <c r="B388" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C388" t="s">
         <v>60</v>
       </c>
       <c r="D388" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E388" t="s">
         <v>64</v>
@@ -28417,7 +28390,7 @@
         <v>66</v>
       </c>
       <c r="G388">
-        <v>1811</v>
+        <v>1808</v>
       </c>
       <c r="H388">
         <v>0</v>
@@ -28426,16 +28399,16 @@
         <v>73</v>
       </c>
       <c r="J388" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="L388" s="1">
-        <v>46290</v>
+        <v>46287</v>
       </c>
       <c r="N388" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="O388">
-        <v>17948816</v>
+        <v>17398965</v>
       </c>
       <c r="P388" t="s">
         <v>248</v>
@@ -28444,10 +28417,10 @@
         <v>260</v>
       </c>
       <c r="S388">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="T388" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AA388">
         <v>0</v>
@@ -28461,16 +28434,16 @@
     </row>
     <row r="389" spans="1:34">
       <c r="A389">
-        <v>6404</v>
+        <v>6704</v>
       </c>
       <c r="B389" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C389" t="s">
         <v>60</v>
       </c>
       <c r="D389" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E389" t="s">
         <v>64</v>
@@ -28479,7 +28452,7 @@
         <v>66</v>
       </c>
       <c r="G389">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="H389">
         <v>0</v>
@@ -28488,7 +28461,7 @@
         <v>73</v>
       </c>
       <c r="J389" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L389" s="1">
         <v>46287</v>
@@ -28497,7 +28470,7 @@
         <v>224</v>
       </c>
       <c r="O389">
-        <v>16962171</v>
+        <v>18085209</v>
       </c>
       <c r="P389" t="s">
         <v>248</v>
@@ -28509,7 +28482,10 @@
         <v>-4</v>
       </c>
       <c r="T389" t="s">
-        <v>270</v>
+        <v>267</v>
+      </c>
+      <c r="V389" t="s">
+        <v>277</v>
       </c>
       <c r="AA389">
         <v>0</v>
@@ -28523,55 +28499,61 @@
     </row>
     <row r="390" spans="1:34">
       <c r="A390">
-        <v>6703</v>
+        <v>6628</v>
       </c>
       <c r="B390" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C390" t="s">
         <v>60</v>
       </c>
       <c r="D390" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E390" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F390" t="s">
         <v>66</v>
       </c>
       <c r="G390">
-        <v>1807</v>
+        <v>945</v>
       </c>
       <c r="H390">
         <v>0</v>
       </c>
       <c r="I390" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J390" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="L390" s="1">
-        <v>46287</v>
+        <v>46283</v>
       </c>
       <c r="N390" t="s">
         <v>224</v>
       </c>
       <c r="O390">
-        <v>17948806</v>
+        <v>16959938</v>
       </c>
       <c r="P390" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q390" t="s">
         <v>260</v>
       </c>
       <c r="S390">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="T390" t="s">
-        <v>269</v>
+        <v>262</v>
+      </c>
+      <c r="V390" t="s">
+        <v>277</v>
+      </c>
+      <c r="W390" t="s">
+        <v>373</v>
       </c>
       <c r="AA390">
         <v>0</v>
@@ -28579,22 +28561,19 @@
       <c r="AG390" t="s">
         <v>455</v>
       </c>
-      <c r="AH390" t="s">
-        <v>463</v>
-      </c>
     </row>
     <row r="391" spans="1:34">
       <c r="A391">
-        <v>5417</v>
+        <v>6705</v>
       </c>
       <c r="B391" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C391" t="s">
         <v>60</v>
       </c>
       <c r="D391" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E391" t="s">
         <v>64</v>
@@ -28603,37 +28582,40 @@
         <v>66</v>
       </c>
       <c r="G391">
-        <v>1808</v>
+        <v>945</v>
       </c>
       <c r="H391">
         <v>0</v>
       </c>
       <c r="I391" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J391" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="L391" s="1">
-        <v>46287</v>
+        <v>46283</v>
       </c>
       <c r="N391" t="s">
         <v>224</v>
       </c>
       <c r="O391">
-        <v>17398965</v>
+        <v>17952524</v>
       </c>
       <c r="P391" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q391" t="s">
         <v>260</v>
       </c>
       <c r="S391">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="T391" t="s">
-        <v>266</v>
+        <v>267</v>
+      </c>
+      <c r="W391" t="s">
+        <v>374</v>
       </c>
       <c r="AA391">
         <v>0</v>
@@ -28641,22 +28623,19 @@
       <c r="AG391" t="s">
         <v>455</v>
       </c>
-      <c r="AH391" t="s">
-        <v>463</v>
-      </c>
     </row>
     <row r="392" spans="1:34">
       <c r="A392">
-        <v>6704</v>
+        <v>6779</v>
       </c>
       <c r="B392" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C392" t="s">
         <v>60</v>
       </c>
       <c r="D392" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E392" t="s">
         <v>64</v>
@@ -28665,34 +28644,34 @@
         <v>66</v>
       </c>
       <c r="G392">
-        <v>1808</v>
+        <v>945</v>
       </c>
       <c r="H392">
         <v>0</v>
       </c>
       <c r="I392" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J392" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="L392" s="1">
-        <v>46287</v>
+        <v>46283</v>
       </c>
       <c r="N392" t="s">
         <v>224</v>
       </c>
       <c r="O392">
-        <v>18085209</v>
+        <v>18056695</v>
       </c>
       <c r="P392" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q392" t="s">
         <v>260</v>
       </c>
       <c r="S392">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="T392" t="s">
         <v>267</v>
@@ -28700,28 +28679,28 @@
       <c r="V392" t="s">
         <v>277</v>
       </c>
+      <c r="W392" t="s">
+        <v>374</v>
+      </c>
       <c r="AA392">
         <v>0</v>
       </c>
       <c r="AG392" t="s">
         <v>455</v>
       </c>
-      <c r="AH392" t="s">
-        <v>463</v>
-      </c>
     </row>
     <row r="393" spans="1:34">
       <c r="A393">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B393" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C393" t="s">
         <v>60</v>
       </c>
       <c r="D393" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E393" t="s">
         <v>65</v>
@@ -28730,7 +28709,7 @@
         <v>66</v>
       </c>
       <c r="G393">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H393">
         <v>0</v>
@@ -28739,16 +28718,19 @@
         <v>74</v>
       </c>
       <c r="J393" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L393" s="1">
         <v>46283</v>
       </c>
+      <c r="M393" t="s">
+        <v>217</v>
+      </c>
       <c r="N393" t="s">
         <v>224</v>
       </c>
       <c r="O393">
-        <v>16959938</v>
+        <v>17042272</v>
       </c>
       <c r="P393" t="s">
         <v>249</v>
@@ -28766,7 +28748,7 @@
         <v>277</v>
       </c>
       <c r="W393" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AA393">
         <v>0</v>
@@ -28777,10 +28759,10 @@
     </row>
     <row r="394" spans="1:34">
       <c r="A394">
-        <v>6705</v>
+        <v>6945</v>
       </c>
       <c r="B394" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C394" t="s">
         <v>60</v>
@@ -28792,10 +28774,10 @@
         <v>64</v>
       </c>
       <c r="F394" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G394">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H394">
         <v>0</v>
@@ -28804,16 +28786,19 @@
         <v>74</v>
       </c>
       <c r="J394" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L394" s="1">
         <v>46283</v>
       </c>
+      <c r="M394" t="s">
+        <v>217</v>
+      </c>
       <c r="N394" t="s">
         <v>224</v>
       </c>
       <c r="O394">
-        <v>17952524</v>
+        <v>18164494</v>
       </c>
       <c r="P394" t="s">
         <v>249</v>
@@ -28825,10 +28810,10 @@
         <v>0</v>
       </c>
       <c r="T394" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="W394" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="AA394">
         <v>0</v>
@@ -28839,16 +28824,16 @@
     </row>
     <row r="395" spans="1:34">
       <c r="A395">
-        <v>6779</v>
+        <v>5417</v>
       </c>
       <c r="B395" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C395" t="s">
         <v>60</v>
       </c>
       <c r="D395" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E395" t="s">
         <v>64</v>
@@ -28857,7 +28842,7 @@
         <v>66</v>
       </c>
       <c r="G395">
-        <v>945</v>
+        <v>940</v>
       </c>
       <c r="H395">
         <v>0</v>
@@ -28866,16 +28851,19 @@
         <v>74</v>
       </c>
       <c r="J395" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="L395" s="1">
         <v>46283</v>
       </c>
+      <c r="M395" t="s">
+        <v>217</v>
+      </c>
       <c r="N395" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O395">
-        <v>18056695</v>
+        <v>17398840</v>
       </c>
       <c r="P395" t="s">
         <v>249</v>
@@ -28887,10 +28875,7 @@
         <v>0</v>
       </c>
       <c r="T395" t="s">
-        <v>267</v>
-      </c>
-      <c r="V395" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="W395" t="s">
         <v>375</v>
@@ -28899,15 +28884,15 @@
         <v>0</v>
       </c>
       <c r="AG395" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="396" spans="1:34">
       <c r="A396">
-        <v>6627</v>
+        <v>5417</v>
       </c>
       <c r="B396" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C396" t="s">
         <v>60</v>
@@ -28916,13 +28901,13 @@
         <v>61</v>
       </c>
       <c r="E396" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F396" t="s">
         <v>66</v>
       </c>
       <c r="G396">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="H396">
         <v>0</v>
@@ -28931,19 +28916,16 @@
         <v>74</v>
       </c>
       <c r="J396" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="L396" s="1">
-        <v>46283</v>
-      </c>
-      <c r="M396" t="s">
-        <v>217</v>
+        <v>46295</v>
       </c>
       <c r="N396" t="s">
         <v>224</v>
       </c>
       <c r="O396">
-        <v>17042272</v>
+        <v>17398859</v>
       </c>
       <c r="P396" t="s">
         <v>249</v>
@@ -28952,45 +28934,39 @@
         <v>260</v>
       </c>
       <c r="S396">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="T396" t="s">
-        <v>262</v>
-      </c>
-      <c r="V396" t="s">
-        <v>277</v>
-      </c>
-      <c r="W396" t="s">
-        <v>373</v>
+        <v>266</v>
       </c>
       <c r="AA396">
         <v>0</v>
       </c>
       <c r="AG396" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="397" spans="1:34">
       <c r="A397">
-        <v>6945</v>
+        <v>6486</v>
       </c>
       <c r="B397" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C397" t="s">
         <v>60</v>
       </c>
       <c r="D397" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E397" t="s">
         <v>64</v>
       </c>
       <c r="F397" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G397">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="H397">
         <v>0</v>
@@ -28999,19 +28975,16 @@
         <v>74</v>
       </c>
       <c r="J397" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="L397" s="1">
-        <v>46283</v>
-      </c>
-      <c r="M397" t="s">
-        <v>217</v>
+        <v>46295</v>
       </c>
       <c r="N397" t="s">
         <v>224</v>
       </c>
       <c r="O397">
-        <v>18164494</v>
+        <v>16975890</v>
       </c>
       <c r="P397" t="s">
         <v>249</v>
@@ -29020,33 +28993,33 @@
         <v>260</v>
       </c>
       <c r="S397">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="T397" t="s">
-        <v>263</v>
-      </c>
-      <c r="W397" t="s">
-        <v>373</v>
+        <v>268</v>
+      </c>
+      <c r="V397" t="s">
+        <v>277</v>
       </c>
       <c r="AA397">
         <v>0</v>
       </c>
       <c r="AG397" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="398" spans="1:34">
       <c r="A398">
-        <v>5417</v>
+        <v>6703</v>
       </c>
       <c r="B398" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C398" t="s">
         <v>60</v>
       </c>
       <c r="D398" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E398" t="s">
         <v>64</v>
@@ -29055,7 +29028,7 @@
         <v>66</v>
       </c>
       <c r="G398">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="H398">
         <v>0</v>
@@ -29064,19 +29037,16 @@
         <v>74</v>
       </c>
       <c r="J398" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L398" s="1">
-        <v>46283</v>
-      </c>
-      <c r="M398" t="s">
-        <v>217</v>
+        <v>46295</v>
       </c>
       <c r="N398" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O398">
-        <v>17398840</v>
+        <v>17941122</v>
       </c>
       <c r="P398" t="s">
         <v>249</v>
@@ -29085,27 +29055,24 @@
         <v>260</v>
       </c>
       <c r="S398">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="T398" t="s">
-        <v>266</v>
-      </c>
-      <c r="W398" t="s">
-        <v>376</v>
+        <v>269</v>
       </c>
       <c r="AA398">
         <v>0</v>
       </c>
       <c r="AG398" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="399" spans="1:34">
       <c r="A399">
-        <v>5417</v>
+        <v>6704</v>
       </c>
       <c r="B399" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C399" t="s">
         <v>60</v>
@@ -29138,7 +29105,7 @@
         <v>224</v>
       </c>
       <c r="O399">
-        <v>17398859</v>
+        <v>17952314</v>
       </c>
       <c r="P399" t="s">
         <v>249</v>
@@ -29150,7 +29117,10 @@
         <v>-12</v>
       </c>
       <c r="T399" t="s">
-        <v>266</v>
+        <v>267</v>
+      </c>
+      <c r="V399" t="s">
+        <v>277</v>
       </c>
       <c r="AA399">
         <v>0</v>
@@ -29161,16 +29131,16 @@
     </row>
     <row r="400" spans="1:34">
       <c r="A400">
-        <v>6486</v>
+        <v>6705</v>
       </c>
       <c r="B400" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C400" t="s">
         <v>60</v>
       </c>
       <c r="D400" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E400" t="s">
         <v>64</v>
@@ -29197,7 +29167,7 @@
         <v>224</v>
       </c>
       <c r="O400">
-        <v>16975890</v>
+        <v>17952513</v>
       </c>
       <c r="P400" t="s">
         <v>249</v>
@@ -29209,10 +29179,7 @@
         <v>-12</v>
       </c>
       <c r="T400" t="s">
-        <v>268</v>
-      </c>
-      <c r="V400" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="AA400">
         <v>0</v>
@@ -29223,22 +29190,22 @@
     </row>
     <row r="401" spans="1:34">
       <c r="A401">
-        <v>6703</v>
+        <v>6949</v>
       </c>
       <c r="B401" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C401" t="s">
         <v>60</v>
       </c>
       <c r="D401" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E401" t="s">
         <v>64</v>
       </c>
       <c r="F401" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G401">
         <v>943</v>
@@ -29259,7 +29226,7 @@
         <v>224</v>
       </c>
       <c r="O401">
-        <v>17941122</v>
+        <v>18178126</v>
       </c>
       <c r="P401" t="s">
         <v>249</v>
@@ -29271,7 +29238,7 @@
         <v>-12</v>
       </c>
       <c r="T401" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="AA401">
         <v>0</v>
@@ -29282,22 +29249,22 @@
     </row>
     <row r="402" spans="1:34">
       <c r="A402">
-        <v>6704</v>
+        <v>6962</v>
       </c>
       <c r="B402" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C402" t="s">
         <v>60</v>
       </c>
       <c r="D402" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E402" t="s">
         <v>64</v>
       </c>
       <c r="F402" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G402">
         <v>943</v>
@@ -29318,7 +29285,7 @@
         <v>224</v>
       </c>
       <c r="O402">
-        <v>17952314</v>
+        <v>18188710</v>
       </c>
       <c r="P402" t="s">
         <v>249</v>
@@ -29330,10 +29297,7 @@
         <v>-12</v>
       </c>
       <c r="T402" t="s">
-        <v>267</v>
-      </c>
-      <c r="V402" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="AA402">
         <v>0</v>
@@ -29344,22 +29308,22 @@
     </row>
     <row r="403" spans="1:34">
       <c r="A403">
-        <v>6705</v>
+        <v>6963</v>
       </c>
       <c r="B403" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C403" t="s">
         <v>60</v>
       </c>
       <c r="D403" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E403" t="s">
         <v>64</v>
       </c>
       <c r="F403" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G403">
         <v>943</v>
@@ -29380,7 +29344,7 @@
         <v>224</v>
       </c>
       <c r="O403">
-        <v>17952513</v>
+        <v>18188616</v>
       </c>
       <c r="P403" t="s">
         <v>249</v>
@@ -29392,7 +29356,7 @@
         <v>-12</v>
       </c>
       <c r="T403" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="AA403">
         <v>0</v>
@@ -29403,10 +29367,10 @@
     </row>
     <row r="404" spans="1:34">
       <c r="A404">
-        <v>6949</v>
+        <v>5417</v>
       </c>
       <c r="B404" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C404" t="s">
         <v>60</v>
@@ -29418,99 +29382,111 @@
         <v>64</v>
       </c>
       <c r="F404" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G404">
-        <v>943</v>
+        <v>6813</v>
       </c>
       <c r="H404">
         <v>0</v>
       </c>
       <c r="I404" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J404" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L404" s="1">
-        <v>46295</v>
+        <v>46286</v>
+      </c>
+      <c r="M404" t="s">
+        <v>215</v>
       </c>
       <c r="N404" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O404">
-        <v>18178126</v>
+        <v>17399241</v>
       </c>
       <c r="P404" t="s">
-        <v>249</v>
+        <v>64</v>
       </c>
       <c r="Q404" t="s">
         <v>260</v>
       </c>
       <c r="S404">
-        <v>-12</v>
+        <v>-3</v>
       </c>
       <c r="T404" t="s">
-        <v>264</v>
+        <v>266</v>
+      </c>
+      <c r="W404" t="s">
+        <v>376</v>
       </c>
       <c r="AA404">
         <v>0</v>
       </c>
       <c r="AG404" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="405" spans="1:34">
       <c r="A405">
-        <v>6962</v>
+        <v>5417</v>
       </c>
       <c r="B405" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C405" t="s">
         <v>60</v>
       </c>
       <c r="D405" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E405" t="s">
         <v>64</v>
       </c>
       <c r="F405" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G405">
-        <v>943</v>
+        <v>11056</v>
       </c>
       <c r="H405">
         <v>0</v>
       </c>
       <c r="I405" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J405" t="s">
-        <v>159</v>
+        <v>131</v>
       </c>
       <c r="L405" s="1">
-        <v>46295</v>
+        <v>46287</v>
+      </c>
+      <c r="M405" t="s">
+        <v>221</v>
       </c>
       <c r="N405" t="s">
         <v>224</v>
       </c>
       <c r="O405">
-        <v>18188710</v>
+        <v>18275526</v>
       </c>
       <c r="P405" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="Q405" t="s">
         <v>260</v>
       </c>
       <c r="S405">
-        <v>-12</v>
+        <v>-4</v>
       </c>
       <c r="T405" t="s">
-        <v>265</v>
+        <v>266</v>
+      </c>
+      <c r="W405" t="s">
+        <v>377</v>
       </c>
       <c r="AA405">
         <v>0</v>
@@ -29521,10 +29497,10 @@
     </row>
     <row r="406" spans="1:34">
       <c r="A406">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B406" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C406" t="s">
         <v>60</v>
@@ -29539,38 +29515,41 @@
         <v>67</v>
       </c>
       <c r="G406">
-        <v>943</v>
+        <v>11056</v>
       </c>
       <c r="H406">
         <v>0</v>
       </c>
       <c r="I406" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J406" t="s">
-        <v>159</v>
+        <v>131</v>
       </c>
       <c r="L406" s="1">
-        <v>46295</v>
+        <v>46287</v>
       </c>
       <c r="N406" t="s">
         <v>224</v>
       </c>
       <c r="O406">
-        <v>18188616</v>
+        <v>18274091</v>
       </c>
       <c r="P406" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="Q406" t="s">
         <v>260</v>
       </c>
       <c r="S406">
-        <v>-12</v>
+        <v>-4</v>
       </c>
       <c r="T406" t="s">
         <v>265</v>
       </c>
+      <c r="W406" t="s">
+        <v>378</v>
+      </c>
       <c r="AA406">
         <v>0</v>
       </c>
@@ -29580,185 +29559,200 @@
     </row>
     <row r="407" spans="1:34">
       <c r="A407">
-        <v>5417</v>
+        <v>6628</v>
       </c>
       <c r="B407" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C407" t="s">
         <v>60</v>
       </c>
       <c r="D407" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E407" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F407" t="s">
         <v>66</v>
       </c>
       <c r="G407">
-        <v>6813</v>
+        <v>1650</v>
       </c>
       <c r="H407">
         <v>0</v>
       </c>
       <c r="I407" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="J407" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L407" s="1">
-        <v>46286</v>
-      </c>
-      <c r="M407" t="s">
-        <v>215</v>
+        <v>46293</v>
       </c>
       <c r="N407" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O407">
-        <v>17399241</v>
+        <v>16959974</v>
       </c>
       <c r="P407" t="s">
-        <v>64</v>
+        <v>230</v>
       </c>
       <c r="Q407" t="s">
-        <v>260</v>
+        <v>258</v>
+      </c>
+      <c r="R407" s="1">
+        <v>46265.00248284722</v>
       </c>
       <c r="S407">
-        <v>-3</v>
+        <v>-10</v>
       </c>
       <c r="T407" t="s">
-        <v>266</v>
-      </c>
-      <c r="W407" t="s">
-        <v>377</v>
+        <v>262</v>
+      </c>
+      <c r="V407" t="s">
+        <v>277</v>
       </c>
       <c r="AA407">
         <v>0</v>
       </c>
+      <c r="AB407" t="s">
+        <v>448</v>
+      </c>
       <c r="AG407" t="s">
-        <v>456</v>
+        <v>454</v>
+      </c>
+      <c r="AH407" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="408" spans="1:34">
       <c r="A408">
-        <v>5417</v>
+        <v>6945</v>
       </c>
       <c r="B408" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C408" t="s">
         <v>60</v>
       </c>
       <c r="D408" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E408" t="s">
         <v>64</v>
       </c>
       <c r="F408" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G408">
-        <v>11056</v>
+        <v>1650</v>
       </c>
       <c r="H408">
         <v>0</v>
       </c>
       <c r="I408" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="J408" t="s">
-        <v>131</v>
+        <v>161</v>
       </c>
       <c r="L408" s="1">
-        <v>46287</v>
-      </c>
-      <c r="M408" t="s">
-        <v>221</v>
+        <v>46293</v>
       </c>
       <c r="N408" t="s">
         <v>224</v>
       </c>
       <c r="O408">
-        <v>18275526</v>
+        <v>18163667</v>
       </c>
       <c r="P408" t="s">
-        <v>254</v>
+        <v>231</v>
       </c>
       <c r="Q408" t="s">
-        <v>260</v>
+        <v>258</v>
+      </c>
+      <c r="R408" s="1">
+        <v>46265.00255472222</v>
       </c>
       <c r="S408">
-        <v>-4</v>
+        <v>-10</v>
       </c>
       <c r="T408" t="s">
-        <v>266</v>
-      </c>
-      <c r="W408" t="s">
-        <v>378</v>
+        <v>263</v>
       </c>
       <c r="AA408">
         <v>0</v>
+      </c>
+      <c r="AB408" t="s">
+        <v>448</v>
       </c>
       <c r="AG408" t="s">
         <v>454</v>
       </c>
+      <c r="AH408" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="409" spans="1:34">
       <c r="A409">
-        <v>6962</v>
+        <v>6548</v>
       </c>
       <c r="B409" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C409" t="s">
         <v>60</v>
       </c>
       <c r="D409" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E409" t="s">
         <v>64</v>
       </c>
       <c r="F409" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G409">
-        <v>11056</v>
+        <v>1652</v>
       </c>
       <c r="H409">
         <v>0</v>
       </c>
       <c r="I409" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="J409" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="L409" s="1">
-        <v>46287</v>
+        <v>46290</v>
       </c>
       <c r="N409" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O409">
-        <v>18274091</v>
+        <v>17967989</v>
       </c>
       <c r="P409" t="s">
-        <v>254</v>
+        <v>229</v>
       </c>
       <c r="Q409" t="s">
-        <v>260</v>
+        <v>258</v>
+      </c>
+      <c r="R409" s="1">
+        <v>46234.66180127315</v>
       </c>
       <c r="S409">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="T409" t="s">
-        <v>265</v>
+        <v>261</v>
+      </c>
+      <c r="V409" t="s">
+        <v>277</v>
       </c>
       <c r="W409" t="s">
         <v>379</v>
@@ -29766,22 +29760,28 @@
       <c r="AA409">
         <v>0</v>
       </c>
+      <c r="AB409" t="s">
+        <v>448</v>
+      </c>
       <c r="AG409" t="s">
-        <v>454</v>
+        <v>455</v>
+      </c>
+      <c r="AH409" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="410" spans="1:34">
       <c r="A410">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B410" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C410" t="s">
         <v>60</v>
       </c>
       <c r="D410" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E410" t="s">
         <v>65</v>
@@ -29790,7 +29790,7 @@
         <v>66</v>
       </c>
       <c r="G410">
-        <v>1650</v>
+        <v>1652</v>
       </c>
       <c r="H410">
         <v>0</v>
@@ -29799,16 +29799,16 @@
         <v>69</v>
       </c>
       <c r="J410" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L410" s="1">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="N410" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O410">
-        <v>16959974</v>
+        <v>17042389</v>
       </c>
       <c r="P410" t="s">
         <v>230</v>
@@ -29817,10 +29817,10 @@
         <v>258</v>
       </c>
       <c r="R410" s="1">
-        <v>46265.00248284722</v>
+        <v>46245.76585582176</v>
       </c>
       <c r="S410">
-        <v>-10</v>
+        <v>-7</v>
       </c>
       <c r="T410" t="s">
         <v>262</v>
@@ -29828,6 +29828,9 @@
       <c r="V410" t="s">
         <v>277</v>
       </c>
+      <c r="W410" t="s">
+        <v>380</v>
+      </c>
       <c r="AA410">
         <v>0</v>
       </c>
@@ -29835,7 +29838,7 @@
         <v>448</v>
       </c>
       <c r="AG410" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AH410" t="s">
         <v>458</v>
@@ -29843,78 +29846,81 @@
     </row>
     <row r="411" spans="1:34">
       <c r="A411">
-        <v>6945</v>
+        <v>6548</v>
       </c>
       <c r="B411" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C411" t="s">
         <v>60</v>
       </c>
       <c r="D411" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E411" t="s">
         <v>64</v>
       </c>
       <c r="F411" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G411">
+        <v>1697</v>
+      </c>
+      <c r="H411">
         <v>1650</v>
-      </c>
-      <c r="H411">
-        <v>0</v>
       </c>
       <c r="I411" t="s">
         <v>69</v>
       </c>
       <c r="J411" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="L411" s="1">
-        <v>46293</v>
+        <v>46286</v>
       </c>
       <c r="N411" t="s">
         <v>224</v>
       </c>
       <c r="O411">
-        <v>18163667</v>
+        <v>17968001</v>
       </c>
       <c r="P411" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="Q411" t="s">
         <v>258</v>
       </c>
       <c r="R411" s="1">
-        <v>46265.00255472222</v>
+        <v>46282.62254486111</v>
       </c>
       <c r="S411">
-        <v>-10</v>
+        <v>-3</v>
       </c>
       <c r="T411" t="s">
-        <v>263</v>
+        <v>261</v>
+      </c>
+      <c r="V411" t="s">
+        <v>277</v>
       </c>
       <c r="AA411">
         <v>0</v>
       </c>
       <c r="AB411" t="s">
-        <v>448</v>
+        <v>229</v>
       </c>
       <c r="AG411" t="s">
         <v>454</v>
       </c>
       <c r="AH411" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="412" spans="1:34">
       <c r="A412">
-        <v>6548</v>
+        <v>6949</v>
       </c>
       <c r="B412" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C412" t="s">
         <v>60</v>
@@ -29926,28 +29932,28 @@
         <v>64</v>
       </c>
       <c r="F412" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G412">
-        <v>1652</v>
+        <v>1697</v>
       </c>
       <c r="H412">
-        <v>0</v>
+        <v>1650</v>
       </c>
       <c r="I412" t="s">
         <v>69</v>
       </c>
       <c r="J412" t="s">
-        <v>162</v>
+        <v>139</v>
       </c>
       <c r="L412" s="1">
-        <v>46290</v>
+        <v>46286</v>
       </c>
       <c r="N412" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="O412">
-        <v>17967989</v>
+        <v>18178280</v>
       </c>
       <c r="P412" t="s">
         <v>229</v>
@@ -29956,28 +29962,22 @@
         <v>258</v>
       </c>
       <c r="R412" s="1">
-        <v>46234.66180127315</v>
+        <v>46283.44840582176</v>
       </c>
       <c r="S412">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="T412" t="s">
-        <v>261</v>
-      </c>
-      <c r="V412" t="s">
-        <v>277</v>
-      </c>
-      <c r="W412" t="s">
-        <v>380</v>
+        <v>264</v>
       </c>
       <c r="AA412">
         <v>0</v>
       </c>
       <c r="AB412" t="s">
-        <v>448</v>
+        <v>229</v>
       </c>
       <c r="AG412" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AH412" t="s">
         <v>457</v>
@@ -29985,10 +29985,10 @@
     </row>
     <row r="413" spans="1:34">
       <c r="A413">
-        <v>6627</v>
+        <v>6704</v>
       </c>
       <c r="B413" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C413" t="s">
         <v>60</v>
@@ -29997,72 +29997,69 @@
         <v>61</v>
       </c>
       <c r="E413" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F413" t="s">
         <v>66</v>
       </c>
       <c r="G413">
-        <v>1652</v>
+        <v>7868</v>
       </c>
       <c r="H413">
         <v>0</v>
       </c>
       <c r="I413" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J413" t="s">
-        <v>162</v>
+        <v>133</v>
       </c>
       <c r="L413" s="1">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="N413" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="O413">
-        <v>17042389</v>
+        <v>17955421</v>
       </c>
       <c r="P413" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q413" t="s">
         <v>258</v>
       </c>
       <c r="R413" s="1">
-        <v>46245.76585582176</v>
+        <v>46267.47365627315</v>
       </c>
       <c r="S413">
-        <v>-7</v>
+        <v>-10</v>
       </c>
       <c r="T413" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="V413" t="s">
         <v>277</v>
       </c>
-      <c r="W413" t="s">
-        <v>381</v>
-      </c>
       <c r="AA413">
         <v>0</v>
       </c>
       <c r="AB413" t="s">
-        <v>448</v>
+        <v>234</v>
       </c>
       <c r="AG413" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AH413" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="414" spans="1:34">
       <c r="A414">
-        <v>6548</v>
+        <v>5417</v>
       </c>
       <c r="B414" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C414" t="s">
         <v>60</v>
@@ -30077,63 +30074,60 @@
         <v>66</v>
       </c>
       <c r="G414">
-        <v>1697</v>
+        <v>11276</v>
       </c>
       <c r="H414">
-        <v>1650</v>
+        <v>0</v>
       </c>
       <c r="I414" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J414" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="L414" s="1">
-        <v>46286</v>
+        <v>46283</v>
       </c>
       <c r="N414" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="O414">
-        <v>17968001</v>
+        <v>17399423</v>
       </c>
       <c r="P414" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q414" t="s">
         <v>258</v>
       </c>
       <c r="R414" s="1">
-        <v>46282.62254486111</v>
+        <v>46266.47620831019</v>
       </c>
       <c r="S414">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="T414" t="s">
-        <v>261</v>
-      </c>
-      <c r="V414" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="AA414">
         <v>0</v>
       </c>
       <c r="AB414" t="s">
-        <v>229</v>
+        <v>450</v>
       </c>
       <c r="AG414" t="s">
         <v>454</v>
       </c>
       <c r="AH414" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="415" spans="1:34">
       <c r="A415">
-        <v>6949</v>
+        <v>6486</v>
       </c>
       <c r="B415" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C415" t="s">
         <v>60</v>
@@ -30145,63 +30139,66 @@
         <v>64</v>
       </c>
       <c r="F415" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G415">
-        <v>1697</v>
+        <v>11276</v>
       </c>
       <c r="H415">
-        <v>1650</v>
+        <v>0</v>
       </c>
       <c r="I415" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J415" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="L415" s="1">
-        <v>46286</v>
+        <v>46283</v>
       </c>
       <c r="N415" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="O415">
-        <v>18178280</v>
+        <v>18152557</v>
       </c>
       <c r="P415" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="Q415" t="s">
         <v>258</v>
       </c>
       <c r="R415" s="1">
-        <v>46283.44840582176</v>
+        <v>46267.57586420139</v>
       </c>
       <c r="S415">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="T415" t="s">
-        <v>264</v>
+        <v>268</v>
+      </c>
+      <c r="V415" t="s">
+        <v>277</v>
       </c>
       <c r="AA415">
         <v>0</v>
       </c>
       <c r="AB415" t="s">
-        <v>229</v>
+        <v>451</v>
       </c>
       <c r="AG415" t="s">
         <v>454</v>
       </c>
       <c r="AH415" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="416" spans="1:34">
       <c r="A416">
-        <v>6704</v>
+        <v>5417</v>
       </c>
       <c r="B416" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C416" t="s">
         <v>60</v>
@@ -30216,7 +30213,7 @@
         <v>66</v>
       </c>
       <c r="G416">
-        <v>7868</v>
+        <v>1583</v>
       </c>
       <c r="H416">
         <v>0</v>
@@ -30225,54 +30222,51 @@
         <v>70</v>
       </c>
       <c r="J416" t="s">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="L416" s="1">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="N416" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O416">
-        <v>17955421</v>
+        <v>17398917</v>
       </c>
       <c r="P416" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="Q416" t="s">
         <v>258</v>
       </c>
       <c r="R416" s="1">
-        <v>46267.47365627315</v>
+        <v>46233.72355880787</v>
       </c>
       <c r="S416">
-        <v>-10</v>
+        <v>-7</v>
       </c>
       <c r="T416" t="s">
-        <v>267</v>
-      </c>
-      <c r="V416" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="AA416">
         <v>0</v>
       </c>
       <c r="AB416" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG416" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AH416" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="417" spans="1:34">
       <c r="A417">
-        <v>5417</v>
+        <v>5617</v>
       </c>
       <c r="B417" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C417" t="s">
         <v>60</v>
@@ -30287,7 +30281,7 @@
         <v>66</v>
       </c>
       <c r="G417">
-        <v>11276</v>
+        <v>1583</v>
       </c>
       <c r="H417">
         <v>0</v>
@@ -30296,51 +30290,45 @@
         <v>70</v>
       </c>
       <c r="J417" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L417" s="1">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="N417" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O417">
-        <v>17399423</v>
-      </c>
-      <c r="P417" t="s">
-        <v>233</v>
+        <v>17407553</v>
       </c>
       <c r="Q417" t="s">
         <v>258</v>
       </c>
       <c r="R417" s="1">
-        <v>46266.47620831019</v>
+        <v>46261.36669849537</v>
       </c>
       <c r="S417">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="T417" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="AA417">
         <v>0</v>
       </c>
       <c r="AB417" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="AG417" t="s">
-        <v>454</v>
-      </c>
-      <c r="AH417" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
     </row>
     <row r="418" spans="1:34">
       <c r="A418">
-        <v>6486</v>
+        <v>6224</v>
       </c>
       <c r="B418" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C418" t="s">
         <v>60</v>
@@ -30352,10 +30340,10 @@
         <v>64</v>
       </c>
       <c r="F418" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G418">
-        <v>11276</v>
+        <v>1583</v>
       </c>
       <c r="H418">
         <v>0</v>
@@ -30364,31 +30352,28 @@
         <v>70</v>
       </c>
       <c r="J418" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L418" s="1">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="N418" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O418">
-        <v>18152557</v>
-      </c>
-      <c r="P418" t="s">
-        <v>251</v>
+        <v>17688645</v>
       </c>
       <c r="Q418" t="s">
         <v>258</v>
       </c>
       <c r="R418" s="1">
-        <v>46267.57586420139</v>
+        <v>46266.44156952546</v>
       </c>
       <c r="S418">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="T418" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="V418" t="s">
         <v>277</v>
@@ -30397,21 +30382,18 @@
         <v>0</v>
       </c>
       <c r="AB418" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="AG418" t="s">
-        <v>454</v>
-      </c>
-      <c r="AH418" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
     </row>
     <row r="419" spans="1:34">
       <c r="A419">
-        <v>5417</v>
+        <v>6278</v>
       </c>
       <c r="B419" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C419" t="s">
         <v>60</v>
@@ -30444,42 +30426,42 @@
         <v>226</v>
       </c>
       <c r="O419">
-        <v>17398917</v>
-      </c>
-      <c r="P419" t="s">
-        <v>233</v>
+        <v>18166312</v>
       </c>
       <c r="Q419" t="s">
         <v>258</v>
       </c>
       <c r="R419" s="1">
-        <v>46233.72355880787</v>
+        <v>46233.50562820602</v>
       </c>
       <c r="S419">
         <v>-7</v>
       </c>
       <c r="T419" t="s">
-        <v>266</v>
+        <v>272</v>
+      </c>
+      <c r="V419" t="s">
+        <v>277</v>
+      </c>
+      <c r="W419" t="s">
+        <v>381</v>
       </c>
       <c r="AA419">
         <v>0</v>
       </c>
       <c r="AB419" t="s">
-        <v>233</v>
+        <v>448</v>
       </c>
       <c r="AG419" t="s">
         <v>455</v>
       </c>
-      <c r="AH419" t="s">
-        <v>459</v>
-      </c>
     </row>
     <row r="420" spans="1:34">
       <c r="A420">
-        <v>5617</v>
+        <v>6486</v>
       </c>
       <c r="B420" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C420" t="s">
         <v>60</v>
@@ -30512,36 +30494,45 @@
         <v>226</v>
       </c>
       <c r="O420">
-        <v>17407553</v>
+        <v>18114208</v>
+      </c>
+      <c r="P420" t="s">
+        <v>251</v>
       </c>
       <c r="Q420" t="s">
         <v>258</v>
       </c>
       <c r="R420" s="1">
-        <v>46261.36669849537</v>
+        <v>46233.80164280093</v>
       </c>
       <c r="S420">
         <v>-7</v>
       </c>
       <c r="T420" t="s">
-        <v>271</v>
+        <v>268</v>
+      </c>
+      <c r="V420" t="s">
+        <v>277</v>
       </c>
       <c r="AA420">
         <v>0</v>
       </c>
       <c r="AB420" t="s">
-        <v>446</v>
+        <v>251</v>
       </c>
       <c r="AG420" t="s">
         <v>455</v>
       </c>
+      <c r="AH420" t="s">
+        <v>459</v>
+      </c>
     </row>
     <row r="421" spans="1:34">
       <c r="A421">
-        <v>6224</v>
+        <v>6704</v>
       </c>
       <c r="B421" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C421" t="s">
         <v>60</v>
@@ -30553,7 +30544,7 @@
         <v>64</v>
       </c>
       <c r="F421" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G421">
         <v>1583</v>
@@ -30574,19 +30565,22 @@
         <v>226</v>
       </c>
       <c r="O421">
-        <v>17688645</v>
+        <v>17955373</v>
+      </c>
+      <c r="P421" t="s">
+        <v>234</v>
       </c>
       <c r="Q421" t="s">
         <v>258</v>
       </c>
       <c r="R421" s="1">
-        <v>46266.44156952546</v>
+        <v>46232.72913953703</v>
       </c>
       <c r="S421">
         <v>-7</v>
       </c>
       <c r="T421" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="V421" t="s">
         <v>277</v>
@@ -30595,18 +30589,21 @@
         <v>0</v>
       </c>
       <c r="AB421" t="s">
-        <v>444</v>
+        <v>234</v>
       </c>
       <c r="AG421" t="s">
         <v>455</v>
       </c>
+      <c r="AH421" t="s">
+        <v>460</v>
+      </c>
     </row>
     <row r="422" spans="1:34">
       <c r="A422">
-        <v>6278</v>
+        <v>5417</v>
       </c>
       <c r="B422" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="C422" t="s">
         <v>60</v>
@@ -30621,66 +30618,66 @@
         <v>66</v>
       </c>
       <c r="G422">
-        <v>1583</v>
+        <v>1628</v>
       </c>
       <c r="H422">
-        <v>0</v>
+        <v>1581</v>
       </c>
       <c r="I422" t="s">
         <v>70</v>
       </c>
       <c r="J422" t="s">
-        <v>162</v>
+        <v>139</v>
       </c>
       <c r="L422" s="1">
-        <v>46290</v>
+        <v>46286</v>
       </c>
       <c r="N422" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="O422">
-        <v>18166312</v>
+        <v>17398925</v>
+      </c>
+      <c r="P422" t="s">
+        <v>233</v>
       </c>
       <c r="Q422" t="s">
         <v>258</v>
       </c>
       <c r="R422" s="1">
-        <v>46233.50562820602</v>
+        <v>46280.37528408565</v>
       </c>
       <c r="S422">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="T422" t="s">
-        <v>272</v>
-      </c>
-      <c r="V422" t="s">
-        <v>277</v>
-      </c>
-      <c r="W422" t="s">
-        <v>382</v>
+        <v>266</v>
       </c>
       <c r="AA422">
         <v>0</v>
       </c>
       <c r="AB422" t="s">
-        <v>448</v>
+        <v>233</v>
       </c>
       <c r="AG422" t="s">
-        <v>455</v>
+        <v>454</v>
+      </c>
+      <c r="AH422" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="423" spans="1:34">
       <c r="A423">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B423" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C423" t="s">
         <v>60</v>
       </c>
       <c r="D423" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E423" t="s">
         <v>64</v>
@@ -30689,69 +30686,66 @@
         <v>66</v>
       </c>
       <c r="G423">
-        <v>1583</v>
+        <v>1628</v>
       </c>
       <c r="H423">
-        <v>0</v>
+        <v>1581</v>
       </c>
       <c r="I423" t="s">
         <v>70</v>
       </c>
       <c r="J423" t="s">
-        <v>162</v>
+        <v>139</v>
       </c>
       <c r="L423" s="1">
-        <v>46290</v>
+        <v>46286</v>
       </c>
       <c r="N423" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="O423">
-        <v>18114208</v>
+        <v>16962141</v>
       </c>
       <c r="P423" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q423" t="s">
         <v>258</v>
       </c>
       <c r="R423" s="1">
-        <v>46233.80164280093</v>
+        <v>46266.37634084491</v>
       </c>
       <c r="S423">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="T423" t="s">
-        <v>268</v>
-      </c>
-      <c r="V423" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="AA423">
         <v>0</v>
       </c>
       <c r="AB423" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG423" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AH423" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="424" spans="1:34">
       <c r="A424">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B424" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C424" t="s">
         <v>60</v>
       </c>
       <c r="D424" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E424" t="s">
         <v>64</v>
@@ -30760,63 +30754,60 @@
         <v>66</v>
       </c>
       <c r="G424">
-        <v>1583</v>
+        <v>1628</v>
       </c>
       <c r="H424">
-        <v>0</v>
+        <v>1581</v>
       </c>
       <c r="I424" t="s">
         <v>70</v>
       </c>
       <c r="J424" t="s">
-        <v>162</v>
+        <v>139</v>
       </c>
       <c r="L424" s="1">
-        <v>46290</v>
+        <v>46286</v>
       </c>
       <c r="N424" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="O424">
-        <v>17955373</v>
+        <v>17955176</v>
       </c>
       <c r="P424" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="Q424" t="s">
         <v>258</v>
       </c>
       <c r="R424" s="1">
-        <v>46232.72913953703</v>
+        <v>46282.42251184028</v>
       </c>
       <c r="S424">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="T424" t="s">
-        <v>267</v>
-      </c>
-      <c r="V424" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="AA424">
         <v>0</v>
       </c>
       <c r="AB424" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="AG424" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AH424" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="425" spans="1:34">
       <c r="A425">
-        <v>5417</v>
+        <v>6704</v>
       </c>
       <c r="B425" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C425" t="s">
         <v>60</v>
@@ -30849,48 +30840,51 @@
         <v>224</v>
       </c>
       <c r="O425">
-        <v>17398925</v>
+        <v>17955384</v>
       </c>
       <c r="P425" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q425" t="s">
         <v>258</v>
       </c>
       <c r="R425" s="1">
-        <v>46280.37528408565</v>
+        <v>46267.47452163194</v>
       </c>
       <c r="S425">
         <v>-3</v>
       </c>
       <c r="T425" t="s">
-        <v>266</v>
+        <v>267</v>
+      </c>
+      <c r="V425" t="s">
+        <v>277</v>
       </c>
       <c r="AA425">
         <v>0</v>
       </c>
       <c r="AB425" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG425" t="s">
         <v>454</v>
       </c>
       <c r="AH425" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="426" spans="1:34">
       <c r="A426">
-        <v>6404</v>
+        <v>6705</v>
       </c>
       <c r="B426" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C426" t="s">
         <v>60</v>
       </c>
       <c r="D426" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E426" t="s">
         <v>64</v>
@@ -30917,28 +30911,28 @@
         <v>224</v>
       </c>
       <c r="O426">
-        <v>16962141</v>
+        <v>17955238</v>
       </c>
       <c r="P426" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="Q426" t="s">
         <v>258</v>
       </c>
       <c r="R426" s="1">
-        <v>46266.37634084491</v>
+        <v>46267.4745221412</v>
       </c>
       <c r="S426">
         <v>-3</v>
       </c>
       <c r="T426" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="AA426">
         <v>0</v>
       </c>
       <c r="AB426" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="AG426" t="s">
         <v>454</v>
@@ -30949,16 +30943,16 @@
     </row>
     <row r="427" spans="1:34">
       <c r="A427">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B427" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C427" t="s">
         <v>60</v>
       </c>
       <c r="D427" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E427" t="s">
         <v>64</v>
@@ -30985,42 +30979,45 @@
         <v>224</v>
       </c>
       <c r="O427">
-        <v>17955176</v>
+        <v>18056729</v>
       </c>
       <c r="P427" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="Q427" t="s">
         <v>258</v>
       </c>
       <c r="R427" s="1">
-        <v>46282.42251184028</v>
+        <v>46267.47452299768</v>
       </c>
       <c r="S427">
         <v>-3</v>
       </c>
       <c r="T427" t="s">
-        <v>269</v>
+        <v>267</v>
+      </c>
+      <c r="V427" t="s">
+        <v>277</v>
       </c>
       <c r="AA427">
         <v>0</v>
       </c>
       <c r="AB427" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="AG427" t="s">
         <v>454</v>
       </c>
       <c r="AH427" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="428" spans="1:34">
       <c r="A428">
-        <v>6704</v>
+        <v>6627</v>
       </c>
       <c r="B428" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C428" t="s">
         <v>60</v>
@@ -31029,69 +31026,75 @@
         <v>61</v>
       </c>
       <c r="E428" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F428" t="s">
         <v>66</v>
       </c>
       <c r="G428">
-        <v>1628</v>
+        <v>5885</v>
       </c>
       <c r="H428">
-        <v>1581</v>
+        <v>5784</v>
       </c>
       <c r="I428" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J428" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="L428" s="1">
-        <v>46286</v>
+        <v>46283</v>
+      </c>
+      <c r="M428" t="s">
+        <v>222</v>
       </c>
       <c r="N428" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O428">
-        <v>17955384</v>
+        <v>18068566</v>
       </c>
       <c r="P428" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q428" t="s">
         <v>258</v>
       </c>
       <c r="R428" s="1">
-        <v>46267.47452163194</v>
+        <v>46281.63558861111</v>
       </c>
       <c r="S428">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="T428" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="V428" t="s">
         <v>277</v>
       </c>
+      <c r="W428" t="s">
+        <v>382</v>
+      </c>
       <c r="AA428">
         <v>0</v>
       </c>
       <c r="AB428" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG428" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AH428" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="429" spans="1:34">
       <c r="A429">
-        <v>6705</v>
+        <v>6628</v>
       </c>
       <c r="B429" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C429" t="s">
         <v>60</v>
@@ -31100,66 +31103,75 @@
         <v>62</v>
       </c>
       <c r="E429" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F429" t="s">
         <v>66</v>
       </c>
       <c r="G429">
-        <v>1628</v>
+        <v>5885</v>
       </c>
       <c r="H429">
-        <v>1581</v>
+        <v>5784</v>
       </c>
       <c r="I429" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J429" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="L429" s="1">
-        <v>46286</v>
+        <v>46283</v>
+      </c>
+      <c r="M429" t="s">
+        <v>222</v>
       </c>
       <c r="N429" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O429">
-        <v>17955238</v>
+        <v>18052485</v>
       </c>
       <c r="P429" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q429" t="s">
         <v>258</v>
       </c>
       <c r="R429" s="1">
-        <v>46267.4745221412</v>
+        <v>46281.6358927662</v>
       </c>
       <c r="S429">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="T429" t="s">
-        <v>267</v>
+        <v>262</v>
+      </c>
+      <c r="V429" t="s">
+        <v>277</v>
+      </c>
+      <c r="W429" t="s">
+        <v>382</v>
       </c>
       <c r="AA429">
         <v>0</v>
       </c>
       <c r="AB429" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG429" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AH429" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="430" spans="1:34">
       <c r="A430">
-        <v>6779</v>
+        <v>6945</v>
       </c>
       <c r="B430" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C430" t="s">
         <v>60</v>
@@ -31171,132 +31183,126 @@
         <v>64</v>
       </c>
       <c r="F430" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G430">
-        <v>1628</v>
+        <v>5885</v>
       </c>
       <c r="H430">
-        <v>1581</v>
+        <v>5784</v>
       </c>
       <c r="I430" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J430" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="L430" s="1">
-        <v>46286</v>
+        <v>46283</v>
+      </c>
+      <c r="M430" t="s">
+        <v>217</v>
       </c>
       <c r="N430" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O430">
-        <v>18056729</v>
+        <v>18206577</v>
       </c>
       <c r="P430" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q430" t="s">
         <v>258</v>
       </c>
       <c r="R430" s="1">
-        <v>46267.47452299768</v>
+        <v>46281.47564895833</v>
       </c>
       <c r="S430">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="T430" t="s">
-        <v>267</v>
-      </c>
-      <c r="V430" t="s">
-        <v>277</v>
+        <v>263</v>
+      </c>
+      <c r="W430" t="s">
+        <v>383</v>
       </c>
       <c r="AA430">
         <v>0</v>
       </c>
       <c r="AB430" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AG430" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AH430" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="431" spans="1:34">
       <c r="A431">
-        <v>6627</v>
+        <v>6703</v>
       </c>
       <c r="B431" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C431" t="s">
         <v>60</v>
       </c>
       <c r="D431" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E431" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F431" t="s">
         <v>66</v>
       </c>
       <c r="G431">
-        <v>5885</v>
+        <v>6395</v>
       </c>
       <c r="H431">
-        <v>5784</v>
+        <v>5792</v>
       </c>
       <c r="I431" t="s">
         <v>71</v>
       </c>
       <c r="J431" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L431" s="1">
         <v>46283</v>
       </c>
-      <c r="M431" t="s">
-        <v>222</v>
-      </c>
       <c r="N431" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O431">
-        <v>18068566</v>
+        <v>18105120</v>
       </c>
       <c r="P431" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="Q431" t="s">
         <v>258</v>
       </c>
       <c r="R431" s="1">
-        <v>46281.63558861111</v>
+        <v>46268.58940019676</v>
       </c>
       <c r="S431">
         <v>0</v>
       </c>
       <c r="T431" t="s">
-        <v>262</v>
-      </c>
-      <c r="V431" t="s">
-        <v>277</v>
-      </c>
-      <c r="W431" t="s">
-        <v>383</v>
+        <v>269</v>
       </c>
       <c r="AA431">
         <v>0</v>
       </c>
       <c r="AB431" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="AG431" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AH431" t="s">
         <v>461</v>
@@ -31304,10 +31310,10 @@
     </row>
     <row r="432" spans="1:34">
       <c r="A432">
-        <v>6628</v>
+        <v>6779</v>
       </c>
       <c r="B432" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C432" t="s">
         <v>60</v>
@@ -31316,155 +31322,146 @@
         <v>62</v>
       </c>
       <c r="E432" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F432" t="s">
         <v>66</v>
       </c>
       <c r="G432">
-        <v>5885</v>
+        <v>5882</v>
       </c>
       <c r="H432">
-        <v>5784</v>
+        <v>5792</v>
       </c>
       <c r="I432" t="s">
         <v>71</v>
       </c>
       <c r="J432" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="L432" s="1">
         <v>46283</v>
       </c>
       <c r="M432" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="N432" t="s">
         <v>225</v>
       </c>
       <c r="O432">
-        <v>18052485</v>
+        <v>18195621</v>
       </c>
       <c r="P432" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="Q432" t="s">
         <v>258</v>
       </c>
       <c r="R432" s="1">
-        <v>46281.6358927662</v>
+        <v>46279.66710767361</v>
       </c>
       <c r="S432">
         <v>0</v>
       </c>
       <c r="T432" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="V432" t="s">
         <v>277</v>
       </c>
       <c r="W432" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AA432">
         <v>0</v>
       </c>
       <c r="AB432" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="AG432" t="s">
         <v>455</v>
       </c>
       <c r="AH432" t="s">
-        <v>461</v>
+        <v>256</v>
       </c>
     </row>
     <row r="433" spans="1:34">
       <c r="A433">
-        <v>6945</v>
+        <v>5417</v>
       </c>
       <c r="B433" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C433" t="s">
         <v>60</v>
       </c>
       <c r="D433" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E433" t="s">
         <v>64</v>
       </c>
       <c r="F433" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G433">
-        <v>5885</v>
+        <v>5883</v>
       </c>
       <c r="H433">
-        <v>5784</v>
+        <v>5792</v>
       </c>
       <c r="I433" t="s">
         <v>71</v>
       </c>
       <c r="J433" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="L433" s="1">
-        <v>46283</v>
-      </c>
-      <c r="M433" t="s">
-        <v>217</v>
+        <v>46286</v>
       </c>
       <c r="N433" t="s">
         <v>225</v>
       </c>
       <c r="O433">
-        <v>18206577</v>
+        <v>17399067</v>
       </c>
       <c r="P433" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q433" t="s">
         <v>258</v>
       </c>
       <c r="R433" s="1">
-        <v>46281.47564895833</v>
+        <v>46282.47420876157</v>
       </c>
       <c r="S433">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="T433" t="s">
-        <v>263</v>
-      </c>
-      <c r="W433" t="s">
-        <v>384</v>
+        <v>266</v>
       </c>
       <c r="AA433">
         <v>0</v>
       </c>
       <c r="AB433" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AG433" t="s">
-        <v>455</v>
-      </c>
-      <c r="AH433" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="434" spans="1:34">
       <c r="A434">
-        <v>6703</v>
+        <v>6486</v>
       </c>
       <c r="B434" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C434" t="s">
         <v>60</v>
       </c>
       <c r="D434" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E434" t="s">
         <v>64</v>
@@ -31473,7 +31470,7 @@
         <v>66</v>
       </c>
       <c r="G434">
-        <v>6395</v>
+        <v>5883</v>
       </c>
       <c r="H434">
         <v>5792</v>
@@ -31482,37 +31479,46 @@
         <v>71</v>
       </c>
       <c r="J434" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="L434" s="1">
-        <v>46283</v>
+        <v>46286</v>
+      </c>
+      <c r="M434" t="s">
+        <v>223</v>
       </c>
       <c r="N434" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O434">
-        <v>18105120</v>
+        <v>16976067</v>
       </c>
       <c r="P434" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="Q434" t="s">
         <v>258</v>
       </c>
       <c r="R434" s="1">
-        <v>46268.58940019676</v>
+        <v>46281.68877074074</v>
       </c>
       <c r="S434">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="T434" t="s">
-        <v>269</v>
+        <v>268</v>
+      </c>
+      <c r="V434" t="s">
+        <v>277</v>
+      </c>
+      <c r="W434" t="s">
+        <v>385</v>
       </c>
       <c r="AA434">
         <v>0</v>
       </c>
       <c r="AB434" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="AG434" t="s">
         <v>454</v>
@@ -31523,16 +31529,16 @@
     </row>
     <row r="435" spans="1:34">
       <c r="A435">
-        <v>6779</v>
+        <v>6548</v>
       </c>
       <c r="B435" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C435" t="s">
         <v>60</v>
       </c>
       <c r="D435" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E435" t="s">
         <v>64</v>
@@ -31541,7 +31547,7 @@
         <v>66</v>
       </c>
       <c r="G435">
-        <v>5882</v>
+        <v>5883</v>
       </c>
       <c r="H435">
         <v>5792</v>
@@ -31550,60 +31556,60 @@
         <v>71</v>
       </c>
       <c r="J435" t="s">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="L435" s="1">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="M435" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="N435" t="s">
         <v>225</v>
       </c>
       <c r="O435">
-        <v>18195621</v>
+        <v>17222629</v>
       </c>
       <c r="P435" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="Q435" t="s">
         <v>258</v>
       </c>
       <c r="R435" s="1">
-        <v>46279.66710767361</v>
+        <v>46280.57958537037</v>
       </c>
       <c r="S435">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="T435" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="V435" t="s">
         <v>277</v>
       </c>
       <c r="W435" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AA435">
         <v>0</v>
       </c>
       <c r="AB435" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="AG435" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AH435" t="s">
-        <v>256</v>
+        <v>461</v>
       </c>
     </row>
     <row r="436" spans="1:34">
       <c r="A436">
-        <v>5417</v>
+        <v>6627</v>
       </c>
       <c r="B436" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C436" t="s">
         <v>60</v>
@@ -31612,7 +31618,7 @@
         <v>61</v>
       </c>
       <c r="E436" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F436" t="s">
         <v>66</v>
@@ -31632,52 +31638,64 @@
       <c r="L436" s="1">
         <v>46286</v>
       </c>
+      <c r="M436" t="s">
+        <v>223</v>
+      </c>
       <c r="N436" t="s">
         <v>225</v>
       </c>
       <c r="O436">
-        <v>17399067</v>
+        <v>18068544</v>
       </c>
       <c r="P436" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="Q436" t="s">
         <v>258</v>
       </c>
       <c r="R436" s="1">
-        <v>46282.47420876157</v>
+        <v>46281.63570936343</v>
       </c>
       <c r="S436">
         <v>-3</v>
       </c>
       <c r="T436" t="s">
-        <v>266</v>
+        <v>262</v>
+      </c>
+      <c r="V436" t="s">
+        <v>277</v>
+      </c>
+      <c r="W436" t="s">
+        <v>385</v>
       </c>
       <c r="AA436">
         <v>0</v>
       </c>
       <c r="AB436" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="AG436" t="s">
         <v>454</v>
       </c>
+      <c r="AH436" t="s">
+        <v>461</v>
+      </c>
     </row>
     <row r="437" spans="1:34">
       <c r="A437">
-        <v>6486</v>
+        <v>6628</v>
       </c>
       <c r="B437" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C437" t="s">
         <v>60</v>
       </c>
       <c r="D437" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E437" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F437" t="s">
         <v>66</v>
@@ -31704,7 +31722,7 @@
         <v>225</v>
       </c>
       <c r="O437">
-        <v>16976067</v>
+        <v>18052463</v>
       </c>
       <c r="P437" t="s">
         <v>235</v>
@@ -31713,19 +31731,19 @@
         <v>258</v>
       </c>
       <c r="R437" s="1">
-        <v>46281.68877074074</v>
+        <v>46281.63595871528</v>
       </c>
       <c r="S437">
         <v>-3</v>
       </c>
       <c r="T437" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="V437" t="s">
         <v>277</v>
       </c>
       <c r="W437" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AA437">
         <v>0</v>
@@ -31742,16 +31760,16 @@
     </row>
     <row r="438" spans="1:34">
       <c r="A438">
-        <v>6548</v>
+        <v>6703</v>
       </c>
       <c r="B438" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C438" t="s">
         <v>60</v>
       </c>
       <c r="D438" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E438" t="s">
         <v>64</v>
@@ -31774,41 +31792,32 @@
       <c r="L438" s="1">
         <v>46286</v>
       </c>
-      <c r="M438" t="s">
-        <v>214</v>
-      </c>
       <c r="N438" t="s">
         <v>225</v>
       </c>
       <c r="O438">
-        <v>17222629</v>
+        <v>18077112</v>
       </c>
       <c r="P438" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q438" t="s">
         <v>258</v>
       </c>
       <c r="R438" s="1">
-        <v>46280.57958537037</v>
+        <v>46279.62681744213</v>
       </c>
       <c r="S438">
         <v>-3</v>
       </c>
       <c r="T438" t="s">
-        <v>261</v>
-      </c>
-      <c r="V438" t="s">
-        <v>277</v>
-      </c>
-      <c r="W438" t="s">
-        <v>387</v>
+        <v>269</v>
       </c>
       <c r="AA438">
         <v>0</v>
       </c>
       <c r="AB438" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG438" t="s">
         <v>454</v>
@@ -31819,19 +31828,19 @@
     </row>
     <row r="439" spans="1:34">
       <c r="A439">
-        <v>6627</v>
+        <v>6779</v>
       </c>
       <c r="B439" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C439" t="s">
         <v>60</v>
       </c>
       <c r="D439" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E439" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F439" t="s">
         <v>66</v>
@@ -31851,70 +31860,64 @@
       <c r="L439" s="1">
         <v>46286</v>
       </c>
-      <c r="M439" t="s">
-        <v>223</v>
-      </c>
       <c r="N439" t="s">
         <v>225</v>
       </c>
       <c r="O439">
-        <v>18068544</v>
+        <v>18090189</v>
       </c>
       <c r="P439" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="Q439" t="s">
         <v>258</v>
       </c>
       <c r="R439" s="1">
-        <v>46281.63570936343</v>
+        <v>46279.66707821759</v>
       </c>
       <c r="S439">
         <v>-3</v>
       </c>
       <c r="T439" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="V439" t="s">
         <v>277</v>
       </c>
-      <c r="W439" t="s">
-        <v>386</v>
-      </c>
       <c r="AA439">
         <v>0</v>
       </c>
       <c r="AB439" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="AG439" t="s">
         <v>454</v>
       </c>
       <c r="AH439" t="s">
-        <v>461</v>
+        <v>256</v>
       </c>
     </row>
     <row r="440" spans="1:34">
       <c r="A440">
-        <v>6628</v>
+        <v>5417</v>
       </c>
       <c r="B440" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C440" t="s">
         <v>60</v>
       </c>
       <c r="D440" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E440" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F440" t="s">
         <v>66</v>
       </c>
       <c r="G440">
-        <v>5883</v>
+        <v>5884</v>
       </c>
       <c r="H440">
         <v>5792</v>
@@ -31923,66 +31926,54 @@
         <v>71</v>
       </c>
       <c r="J440" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L440" s="1">
         <v>46286</v>
       </c>
-      <c r="M440" t="s">
-        <v>223</v>
-      </c>
       <c r="N440" t="s">
         <v>225</v>
       </c>
       <c r="O440">
-        <v>18052463</v>
+        <v>17399077</v>
       </c>
       <c r="P440" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q440" t="s">
         <v>258</v>
       </c>
       <c r="R440" s="1">
-        <v>46281.63595871528</v>
+        <v>46282.47437324074</v>
       </c>
       <c r="S440">
         <v>-3</v>
       </c>
       <c r="T440" t="s">
-        <v>262</v>
-      </c>
-      <c r="V440" t="s">
-        <v>277</v>
-      </c>
-      <c r="W440" t="s">
-        <v>386</v>
+        <v>266</v>
       </c>
       <c r="AA440">
         <v>0</v>
       </c>
       <c r="AB440" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="AG440" t="s">
         <v>454</v>
       </c>
-      <c r="AH440" t="s">
-        <v>461</v>
-      </c>
     </row>
     <row r="441" spans="1:34">
       <c r="A441">
-        <v>6703</v>
+        <v>6486</v>
       </c>
       <c r="B441" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C441" t="s">
         <v>60</v>
       </c>
       <c r="D441" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E441" t="s">
         <v>64</v>
@@ -31991,7 +31982,7 @@
         <v>66</v>
       </c>
       <c r="G441">
-        <v>5883</v>
+        <v>5884</v>
       </c>
       <c r="H441">
         <v>5792</v>
@@ -32000,37 +31991,46 @@
         <v>71</v>
       </c>
       <c r="J441" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L441" s="1">
         <v>46286</v>
       </c>
+      <c r="M441" t="s">
+        <v>223</v>
+      </c>
       <c r="N441" t="s">
         <v>225</v>
       </c>
       <c r="O441">
-        <v>18077112</v>
+        <v>16976077</v>
       </c>
       <c r="P441" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="Q441" t="s">
         <v>258</v>
       </c>
       <c r="R441" s="1">
-        <v>46279.62681744213</v>
+        <v>46281.68880230324</v>
       </c>
       <c r="S441">
         <v>-3</v>
       </c>
       <c r="T441" t="s">
-        <v>269</v>
+        <v>268</v>
+      </c>
+      <c r="V441" t="s">
+        <v>277</v>
+      </c>
+      <c r="W441" t="s">
+        <v>385</v>
       </c>
       <c r="AA441">
         <v>0</v>
       </c>
       <c r="AB441" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="AG441" t="s">
         <v>454</v>
@@ -32041,16 +32041,16 @@
     </row>
     <row r="442" spans="1:34">
       <c r="A442">
-        <v>6779</v>
+        <v>6548</v>
       </c>
       <c r="B442" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C442" t="s">
         <v>60</v>
       </c>
       <c r="D442" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E442" t="s">
         <v>64</v>
@@ -32059,7 +32059,7 @@
         <v>66</v>
       </c>
       <c r="G442">
-        <v>5883</v>
+        <v>5884</v>
       </c>
       <c r="H442">
         <v>5792</v>
@@ -32068,54 +32068,60 @@
         <v>71</v>
       </c>
       <c r="J442" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L442" s="1">
         <v>46286</v>
       </c>
+      <c r="M442" t="s">
+        <v>214</v>
+      </c>
       <c r="N442" t="s">
         <v>225</v>
       </c>
       <c r="O442">
-        <v>18090189</v>
+        <v>17222647</v>
       </c>
       <c r="P442" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="Q442" t="s">
         <v>258</v>
       </c>
       <c r="R442" s="1">
-        <v>46279.66707821759</v>
+        <v>46280.57972293982</v>
       </c>
       <c r="S442">
         <v>-3</v>
       </c>
       <c r="T442" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="V442" t="s">
         <v>277</v>
       </c>
+      <c r="W442" t="s">
+        <v>387</v>
+      </c>
       <c r="AA442">
         <v>0</v>
       </c>
       <c r="AB442" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="AG442" t="s">
         <v>454</v>
       </c>
       <c r="AH442" t="s">
-        <v>256</v>
+        <v>461</v>
       </c>
     </row>
     <row r="443" spans="1:34">
       <c r="A443">
-        <v>5417</v>
+        <v>6627</v>
       </c>
       <c r="B443" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C443" t="s">
         <v>60</v>
@@ -32124,7 +32130,7 @@
         <v>61</v>
       </c>
       <c r="E443" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F443" t="s">
         <v>66</v>
@@ -32144,52 +32150,64 @@
       <c r="L443" s="1">
         <v>46286</v>
       </c>
+      <c r="M443" t="s">
+        <v>223</v>
+      </c>
       <c r="N443" t="s">
         <v>225</v>
       </c>
       <c r="O443">
-        <v>17399077</v>
+        <v>18068555</v>
       </c>
       <c r="P443" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="Q443" t="s">
         <v>258</v>
       </c>
       <c r="R443" s="1">
-        <v>46282.47437324074</v>
+        <v>46281.63575075231</v>
       </c>
       <c r="S443">
         <v>-3</v>
       </c>
       <c r="T443" t="s">
-        <v>266</v>
+        <v>262</v>
+      </c>
+      <c r="V443" t="s">
+        <v>277</v>
+      </c>
+      <c r="W443" t="s">
+        <v>385</v>
       </c>
       <c r="AA443">
         <v>0</v>
       </c>
       <c r="AB443" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="AG443" t="s">
         <v>454</v>
       </c>
+      <c r="AH443" t="s">
+        <v>461</v>
+      </c>
     </row>
     <row r="444" spans="1:34">
       <c r="A444">
-        <v>6486</v>
+        <v>6628</v>
       </c>
       <c r="B444" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C444" t="s">
         <v>60</v>
       </c>
       <c r="D444" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E444" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F444" t="s">
         <v>66</v>
@@ -32216,7 +32234,7 @@
         <v>225</v>
       </c>
       <c r="O444">
-        <v>16976077</v>
+        <v>18052474</v>
       </c>
       <c r="P444" t="s">
         <v>235</v>
@@ -32225,19 +32243,19 @@
         <v>258</v>
       </c>
       <c r="R444" s="1">
-        <v>46281.68880230324</v>
+        <v>46281.63599785879</v>
       </c>
       <c r="S444">
         <v>-3</v>
       </c>
       <c r="T444" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="V444" t="s">
         <v>277</v>
       </c>
       <c r="W444" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AA444">
         <v>0</v>
@@ -32254,16 +32272,16 @@
     </row>
     <row r="445" spans="1:34">
       <c r="A445">
-        <v>6548</v>
+        <v>6703</v>
       </c>
       <c r="B445" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C445" t="s">
         <v>60</v>
       </c>
       <c r="D445" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E445" t="s">
         <v>64</v>
@@ -32286,41 +32304,32 @@
       <c r="L445" s="1">
         <v>46286</v>
       </c>
-      <c r="M445" t="s">
-        <v>214</v>
-      </c>
       <c r="N445" t="s">
         <v>225</v>
       </c>
       <c r="O445">
-        <v>17222647</v>
+        <v>18077122</v>
       </c>
       <c r="P445" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q445" t="s">
         <v>258</v>
       </c>
       <c r="R445" s="1">
-        <v>46280.57972293982</v>
+        <v>46279.6268503125</v>
       </c>
       <c r="S445">
         <v>-3</v>
       </c>
       <c r="T445" t="s">
-        <v>261</v>
-      </c>
-      <c r="V445" t="s">
-        <v>277</v>
-      </c>
-      <c r="W445" t="s">
-        <v>388</v>
+        <v>269</v>
       </c>
       <c r="AA445">
         <v>0</v>
       </c>
       <c r="AB445" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG445" t="s">
         <v>454</v>
@@ -32331,19 +32340,19 @@
     </row>
     <row r="446" spans="1:34">
       <c r="A446">
-        <v>6627</v>
+        <v>6779</v>
       </c>
       <c r="B446" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C446" t="s">
         <v>60</v>
       </c>
       <c r="D446" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E446" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F446" t="s">
         <v>66</v>
@@ -32363,132 +32372,117 @@
       <c r="L446" s="1">
         <v>46286</v>
       </c>
-      <c r="M446" t="s">
-        <v>223</v>
-      </c>
       <c r="N446" t="s">
         <v>225</v>
       </c>
       <c r="O446">
-        <v>18068555</v>
+        <v>18090199</v>
       </c>
       <c r="P446" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="Q446" t="s">
         <v>258</v>
       </c>
       <c r="R446" s="1">
-        <v>46281.63575075231</v>
+        <v>46279.66698128472</v>
       </c>
       <c r="S446">
         <v>-3</v>
       </c>
       <c r="T446" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="V446" t="s">
         <v>277</v>
       </c>
-      <c r="W446" t="s">
-        <v>386</v>
-      </c>
       <c r="AA446">
         <v>0</v>
       </c>
       <c r="AB446" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="AG446" t="s">
         <v>454</v>
       </c>
       <c r="AH446" t="s">
-        <v>461</v>
+        <v>256</v>
       </c>
     </row>
     <row r="447" spans="1:34">
       <c r="A447">
-        <v>6628</v>
+        <v>5417</v>
       </c>
       <c r="B447" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C447" t="s">
         <v>60</v>
       </c>
       <c r="D447" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E447" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F447" t="s">
         <v>66</v>
       </c>
       <c r="G447">
-        <v>5884</v>
+        <v>7012</v>
       </c>
       <c r="H447">
-        <v>5792</v>
+        <v>0</v>
       </c>
       <c r="I447" t="s">
         <v>71</v>
       </c>
       <c r="J447" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="L447" s="1">
-        <v>46286</v>
-      </c>
-      <c r="M447" t="s">
-        <v>223</v>
+        <v>46281</v>
       </c>
       <c r="N447" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O447">
-        <v>18052474</v>
+        <v>18257773</v>
       </c>
       <c r="P447" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q447" t="s">
         <v>258</v>
       </c>
       <c r="R447" s="1">
-        <v>46281.63599785879</v>
+        <v>46279.66929922454</v>
       </c>
       <c r="S447">
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="T447" t="s">
-        <v>262</v>
-      </c>
-      <c r="V447" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="W447" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AA447">
         <v>0</v>
       </c>
       <c r="AB447" t="s">
-        <v>235</v>
+        <v>444</v>
       </c>
       <c r="AG447" t="s">
         <v>454</v>
       </c>
-      <c r="AH447" t="s">
-        <v>461</v>
-      </c>
     </row>
     <row r="448" spans="1:34">
       <c r="A448">
-        <v>6703</v>
+        <v>6404</v>
       </c>
       <c r="B448" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C448" t="s">
         <v>60</v>
@@ -32503,66 +32497,69 @@
         <v>66</v>
       </c>
       <c r="G448">
-        <v>5884</v>
+        <v>7012</v>
       </c>
       <c r="H448">
-        <v>5792</v>
+        <v>0</v>
       </c>
       <c r="I448" t="s">
         <v>71</v>
       </c>
       <c r="J448" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="L448" s="1">
-        <v>46286</v>
+        <v>46281</v>
       </c>
       <c r="N448" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O448">
-        <v>18077122</v>
+        <v>18258536</v>
       </c>
       <c r="P448" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q448" t="s">
         <v>258</v>
       </c>
       <c r="R448" s="1">
-        <v>46279.6268503125</v>
+        <v>46280.61353684028</v>
       </c>
       <c r="S448">
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="T448" t="s">
-        <v>269</v>
+        <v>270</v>
+      </c>
+      <c r="W448" t="s">
+        <v>389</v>
       </c>
       <c r="AA448">
         <v>0</v>
       </c>
       <c r="AB448" t="s">
-        <v>240</v>
+        <v>444</v>
       </c>
       <c r="AG448" t="s">
         <v>454</v>
       </c>
       <c r="AH448" t="s">
-        <v>461</v>
+        <v>256</v>
       </c>
     </row>
     <row r="449" spans="1:34">
       <c r="A449">
-        <v>6779</v>
+        <v>6486</v>
       </c>
       <c r="B449" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C449" t="s">
         <v>60</v>
       </c>
       <c r="D449" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E449" t="s">
         <v>64</v>
@@ -32571,63 +32568,66 @@
         <v>66</v>
       </c>
       <c r="G449">
-        <v>5884</v>
+        <v>7012</v>
       </c>
       <c r="H449">
-        <v>5792</v>
+        <v>0</v>
       </c>
       <c r="I449" t="s">
         <v>71</v>
       </c>
       <c r="J449" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="L449" s="1">
-        <v>46286</v>
+        <v>46281</v>
       </c>
       <c r="N449" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O449">
-        <v>18090199</v>
+        <v>18254964</v>
       </c>
       <c r="P449" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="Q449" t="s">
         <v>258</v>
       </c>
       <c r="R449" s="1">
-        <v>46279.66698128472</v>
+        <v>46280.61353920139</v>
       </c>
       <c r="S449">
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="T449" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="V449" t="s">
         <v>277</v>
       </c>
+      <c r="W449" t="s">
+        <v>390</v>
+      </c>
       <c r="AA449">
         <v>0</v>
       </c>
       <c r="AB449" t="s">
-        <v>242</v>
+        <v>444</v>
       </c>
       <c r="AG449" t="s">
         <v>454</v>
       </c>
       <c r="AH449" t="s">
-        <v>256</v>
+        <v>461</v>
       </c>
     </row>
     <row r="450" spans="1:34">
       <c r="A450">
-        <v>5417</v>
+        <v>6548</v>
       </c>
       <c r="B450" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C450" t="s">
         <v>60</v>
@@ -32660,25 +32660,28 @@
         <v>224</v>
       </c>
       <c r="O450">
-        <v>18257773</v>
+        <v>18255116</v>
       </c>
       <c r="P450" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q450" t="s">
         <v>258</v>
       </c>
       <c r="R450" s="1">
-        <v>46279.66929922454</v>
+        <v>46279.63250563657</v>
       </c>
       <c r="S450">
         <v>2</v>
       </c>
       <c r="T450" t="s">
-        <v>266</v>
+        <v>261</v>
+      </c>
+      <c r="V450" t="s">
+        <v>277</v>
       </c>
       <c r="W450" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AA450">
         <v>0</v>
@@ -32689,22 +32692,25 @@
       <c r="AG450" t="s">
         <v>454</v>
       </c>
+      <c r="AH450" t="s">
+        <v>461</v>
+      </c>
     </row>
     <row r="451" spans="1:34">
       <c r="A451">
-        <v>6404</v>
+        <v>6627</v>
       </c>
       <c r="B451" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C451" t="s">
         <v>60</v>
       </c>
       <c r="D451" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E451" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F451" t="s">
         <v>66</v>
@@ -32728,22 +32734,25 @@
         <v>224</v>
       </c>
       <c r="O451">
-        <v>18258536</v>
+        <v>18257668</v>
       </c>
       <c r="P451" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="Q451" t="s">
         <v>258</v>
       </c>
       <c r="R451" s="1">
-        <v>46280.61353684028</v>
+        <v>46280.61354019676</v>
       </c>
       <c r="S451">
         <v>2</v>
       </c>
       <c r="T451" t="s">
-        <v>270</v>
+        <v>262</v>
+      </c>
+      <c r="V451" t="s">
+        <v>277</v>
       </c>
       <c r="W451" t="s">
         <v>390</v>
@@ -32758,24 +32767,24 @@
         <v>454</v>
       </c>
       <c r="AH451" t="s">
-        <v>256</v>
+        <v>461</v>
       </c>
     </row>
     <row r="452" spans="1:34">
       <c r="A452">
-        <v>6486</v>
+        <v>6628</v>
       </c>
       <c r="B452" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C452" t="s">
         <v>60</v>
       </c>
       <c r="D452" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E452" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F452" t="s">
         <v>66</v>
@@ -32799,7 +32808,7 @@
         <v>224</v>
       </c>
       <c r="O452">
-        <v>18254964</v>
+        <v>18256366</v>
       </c>
       <c r="P452" t="s">
         <v>235</v>
@@ -32808,19 +32817,19 @@
         <v>258</v>
       </c>
       <c r="R452" s="1">
-        <v>46280.61353920139</v>
+        <v>46280.6135403125</v>
       </c>
       <c r="S452">
         <v>2</v>
       </c>
       <c r="T452" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="V452" t="s">
         <v>277</v>
       </c>
       <c r="W452" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AA452">
         <v>0</v>
@@ -32837,16 +32846,16 @@
     </row>
     <row r="453" spans="1:34">
       <c r="A453">
-        <v>6548</v>
+        <v>6703</v>
       </c>
       <c r="B453" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C453" t="s">
         <v>60</v>
       </c>
       <c r="D453" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E453" t="s">
         <v>64</v>
@@ -32869,29 +32878,29 @@
       <c r="L453" s="1">
         <v>46281</v>
       </c>
+      <c r="M453" t="s">
+        <v>222</v>
+      </c>
       <c r="N453" t="s">
         <v>224</v>
       </c>
       <c r="O453">
-        <v>18255116</v>
+        <v>18256433</v>
       </c>
       <c r="P453" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q453" t="s">
         <v>258</v>
       </c>
       <c r="R453" s="1">
-        <v>46279.63250563657</v>
+        <v>46281.71218414352</v>
       </c>
       <c r="S453">
         <v>2</v>
       </c>
       <c r="T453" t="s">
-        <v>261</v>
-      </c>
-      <c r="V453" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="W453" t="s">
         <v>392</v>
@@ -32900,7 +32909,7 @@
         <v>0</v>
       </c>
       <c r="AB453" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="AG453" t="s">
         <v>454</v>
@@ -32911,19 +32920,19 @@
     </row>
     <row r="454" spans="1:34">
       <c r="A454">
-        <v>6627</v>
+        <v>6779</v>
       </c>
       <c r="B454" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C454" t="s">
         <v>60</v>
       </c>
       <c r="D454" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E454" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F454" t="s">
         <v>66</v>
@@ -32947,28 +32956,28 @@
         <v>224</v>
       </c>
       <c r="O454">
-        <v>18257668</v>
+        <v>18255012</v>
       </c>
       <c r="P454" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="Q454" t="s">
         <v>258</v>
       </c>
       <c r="R454" s="1">
-        <v>46280.61354019676</v>
+        <v>46281.41576883102</v>
       </c>
       <c r="S454">
         <v>2</v>
       </c>
       <c r="T454" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="V454" t="s">
         <v>277</v>
       </c>
       <c r="W454" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AA454">
         <v>0</v>
@@ -32980,15 +32989,15 @@
         <v>454</v>
       </c>
       <c r="AH454" t="s">
-        <v>461</v>
+        <v>256</v>
       </c>
     </row>
     <row r="455" spans="1:34">
       <c r="A455">
-        <v>6628</v>
+        <v>6945</v>
       </c>
       <c r="B455" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C455" t="s">
         <v>60</v>
@@ -32997,10 +33006,10 @@
         <v>62</v>
       </c>
       <c r="E455" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F455" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G455">
         <v>7012</v>
@@ -33021,28 +33030,25 @@
         <v>224</v>
       </c>
       <c r="O455">
-        <v>18256366</v>
+        <v>18254903</v>
       </c>
       <c r="P455" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q455" t="s">
         <v>258</v>
       </c>
       <c r="R455" s="1">
-        <v>46280.6135403125</v>
+        <v>46280.43132989584</v>
       </c>
       <c r="S455">
         <v>2</v>
       </c>
       <c r="T455" t="s">
-        <v>262</v>
-      </c>
-      <c r="V455" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="W455" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AA455">
         <v>0</v>
@@ -33054,27 +33060,27 @@
         <v>454</v>
       </c>
       <c r="AH455" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="456" spans="1:34">
       <c r="A456">
-        <v>6703</v>
+        <v>6949</v>
       </c>
       <c r="B456" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C456" t="s">
         <v>60</v>
       </c>
       <c r="D456" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E456" t="s">
         <v>64</v>
       </c>
       <c r="F456" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G456">
         <v>7012</v>
@@ -33091,58 +33097,55 @@
       <c r="L456" s="1">
         <v>46281</v>
       </c>
-      <c r="M456" t="s">
-        <v>222</v>
-      </c>
       <c r="N456" t="s">
         <v>224</v>
       </c>
       <c r="O456">
-        <v>18256433</v>
+        <v>18258489</v>
       </c>
       <c r="P456" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="Q456" t="s">
         <v>258</v>
       </c>
       <c r="R456" s="1">
-        <v>46281.71218414352</v>
+        <v>46280.61367623843</v>
       </c>
       <c r="S456">
         <v>2</v>
       </c>
       <c r="T456" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="W456" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AA456">
         <v>0</v>
       </c>
       <c r="AB456" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="AG456" t="s">
         <v>454</v>
       </c>
       <c r="AH456" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="457" spans="1:34">
       <c r="A457">
-        <v>6779</v>
+        <v>6486</v>
       </c>
       <c r="B457" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C457" t="s">
         <v>60</v>
       </c>
       <c r="D457" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E457" t="s">
         <v>64</v>
@@ -33151,185 +33154,200 @@
         <v>66</v>
       </c>
       <c r="G457">
-        <v>7012</v>
+        <v>5836</v>
       </c>
       <c r="H457">
-        <v>0</v>
+        <v>5784</v>
       </c>
       <c r="I457" t="s">
         <v>71</v>
       </c>
       <c r="J457" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="L457" s="1">
-        <v>46281</v>
+        <v>46286</v>
+      </c>
+      <c r="M457" t="s">
+        <v>217</v>
       </c>
       <c r="N457" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O457">
-        <v>18255012</v>
+        <v>16976037</v>
       </c>
       <c r="P457" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="Q457" t="s">
         <v>258</v>
       </c>
       <c r="R457" s="1">
-        <v>46281.41576883102</v>
+        <v>46283.59424842593</v>
       </c>
       <c r="S457">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="T457" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="V457" t="s">
         <v>277</v>
       </c>
       <c r="W457" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AA457">
         <v>0</v>
       </c>
       <c r="AB457" t="s">
-        <v>444</v>
+        <v>235</v>
       </c>
       <c r="AG457" t="s">
         <v>454</v>
       </c>
       <c r="AH457" t="s">
-        <v>256</v>
+        <v>461</v>
       </c>
     </row>
     <row r="458" spans="1:34">
       <c r="A458">
-        <v>6945</v>
+        <v>6627</v>
       </c>
       <c r="B458" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C458" t="s">
         <v>60</v>
       </c>
       <c r="D458" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E458" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F458" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G458">
-        <v>7012</v>
+        <v>5836</v>
       </c>
       <c r="H458">
-        <v>0</v>
+        <v>5784</v>
       </c>
       <c r="I458" t="s">
         <v>71</v>
       </c>
       <c r="J458" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="L458" s="1">
-        <v>46281</v>
+        <v>46286</v>
+      </c>
+      <c r="M458" t="s">
+        <v>217</v>
       </c>
       <c r="N458" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O458">
-        <v>18254903</v>
+        <v>18068500</v>
       </c>
       <c r="P458" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q458" t="s">
         <v>258</v>
       </c>
       <c r="R458" s="1">
-        <v>46280.43132989584</v>
+        <v>46283.5942487037</v>
       </c>
       <c r="S458">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="T458" t="s">
-        <v>263</v>
+        <v>262</v>
+      </c>
+      <c r="V458" t="s">
+        <v>277</v>
       </c>
       <c r="W458" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AA458">
         <v>0</v>
       </c>
       <c r="AB458" t="s">
-        <v>444</v>
+        <v>235</v>
       </c>
       <c r="AG458" t="s">
         <v>454</v>
       </c>
       <c r="AH458" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="459" spans="1:34">
       <c r="A459">
-        <v>6949</v>
+        <v>6628</v>
       </c>
       <c r="B459" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C459" t="s">
         <v>60</v>
       </c>
       <c r="D459" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E459" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F459" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G459">
-        <v>7012</v>
+        <v>5836</v>
       </c>
       <c r="H459">
-        <v>0</v>
+        <v>5784</v>
       </c>
       <c r="I459" t="s">
         <v>71</v>
       </c>
       <c r="J459" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="L459" s="1">
-        <v>46281</v>
+        <v>46286</v>
+      </c>
+      <c r="M459" t="s">
+        <v>217</v>
       </c>
       <c r="N459" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O459">
-        <v>18258489</v>
+        <v>18052419</v>
       </c>
       <c r="P459" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="Q459" t="s">
         <v>258</v>
       </c>
       <c r="R459" s="1">
-        <v>46280.61367623843</v>
+        <v>46283.59424924768</v>
       </c>
       <c r="S459">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="T459" t="s">
-        <v>264</v>
+        <v>262</v>
+      </c>
+      <c r="V459" t="s">
+        <v>277</v>
       </c>
       <c r="W459" t="s">
         <v>396</v>
@@ -33338,13 +33356,13 @@
         <v>0</v>
       </c>
       <c r="AB459" t="s">
-        <v>444</v>
+        <v>235</v>
       </c>
       <c r="AG459" t="s">
         <v>454</v>
       </c>
       <c r="AH459" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="460" spans="1:34">
@@ -34385,7 +34403,7 @@
         <v>277</v>
       </c>
       <c r="W474" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AA474">
         <v>0</v>
@@ -36178,7 +36196,7 @@
         <v>266</v>
       </c>
       <c r="W499" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AA499">
         <v>0</v>
@@ -37473,7 +37491,7 @@
         <v>267</v>
       </c>
       <c r="W518" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AA518">
         <v>0</v>
@@ -38819,7 +38837,7 @@
         <v>270</v>
       </c>
       <c r="W537" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AA537">
         <v>0</v>
@@ -38893,7 +38911,7 @@
         <v>277</v>
       </c>
       <c r="W538" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AA538">
         <v>0</v>
@@ -38967,7 +38985,7 @@
         <v>277</v>
       </c>
       <c r="W539" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AA539">
         <v>0</v>
@@ -39041,7 +39059,7 @@
         <v>277</v>
       </c>
       <c r="W540" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AA540">
         <v>0</v>
@@ -39115,7 +39133,7 @@
         <v>277</v>
       </c>
       <c r="W541" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AA541">
         <v>0</v>
@@ -39186,7 +39204,7 @@
         <v>269</v>
       </c>
       <c r="W542" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AA542">
         <v>0</v>
@@ -39260,7 +39278,7 @@
         <v>277</v>
       </c>
       <c r="W543" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AA543">
         <v>0</v>
@@ -39331,7 +39349,7 @@
         <v>267</v>
       </c>
       <c r="W544" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AA544">
         <v>0</v>
@@ -43204,7 +43222,7 @@
         <v>265</v>
       </c>
       <c r="W601" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AG601" t="s">
         <v>455</v>
@@ -43674,7 +43692,7 @@
         <v>275</v>
       </c>
       <c r="W608" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG608" t="s">
         <v>455</v>
@@ -43739,7 +43757,7 @@
         <v>275</v>
       </c>
       <c r="W609" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG609" t="s">
         <v>455</v>
@@ -43804,7 +43822,7 @@
         <v>275</v>
       </c>
       <c r="W610" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG610" t="s">
         <v>455</v>
@@ -43990,7 +44008,7 @@
         <v>263</v>
       </c>
       <c r="W613" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AG613" t="s">
         <v>456</v>

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9097" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9099" uniqueCount="478">
   <si>
     <t>CodCliente</t>
   </si>
@@ -1131,19 +1131,16 @@
     <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 21/09/2026 - Data Comentário: 16/09/2026 16:51</t>
   </si>
   <si>
-    <t>Imposto enviado via SCI Report - Data Comentário: 18/09/2026 17:44</t>
-  </si>
-  <si>
-    <t>Imposto enviado via SCI Report - Data Comentário: 18/09/2026 18:02</t>
-  </si>
-  <si>
-    <t>Imposto enviado via SCI Report - Data Comentário: 18/09/2026 17:53</t>
-  </si>
-  <si>
     <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1879] sendo a ultima baixa feita [1879]-18/09/2026 17:43:16.. - Data Comentário: 18/09/2026 17:38</t>
   </si>
   <si>
+    <t>Reaberto via Rotina Configuração Após Baixa de tarefa [11286] sendo a ultima baixa feita [11286]-21/09/2026 08:40:46.. - Data Comentário: 21/09/2026 08:35</t>
+  </si>
+  <si>
     <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1802] sendo a ultima baixa feita [1802]-18/09/2026 18:01:06.. - Data Comentário: 18/09/2026 17:56</t>
+  </si>
+  <si>
+    <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1802] sendo a ultima baixa feita [1802]-21/09/2026 08:40:45.. - Data Comentário: 21/09/2026 08:35</t>
   </si>
   <si>
     <t>Comentário Colaborador + Previsão de Conclusão. Previsto para: 28/09/2026 - Data Comentário: 18/09/2026 15:26</t>
@@ -1312,6 +1309,15 @@
     <t>Imposto enviado via SCI Report - Data Comentário: 18/09/2026 17:40</t>
   </si>
   <si>
+    <t>Imposto enviado via SCI Report - Data Comentário: 18/09/2026 17:44</t>
+  </si>
+  <si>
+    <t>Imposto enviado via SCI Report - Data Comentário: 18/09/2026 18:02</t>
+  </si>
+  <si>
+    <t>Imposto enviado via SCI Report - Data Comentário: 18/09/2026 17:53</t>
+  </si>
+  <si>
     <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 15/09/2026 14:24:29. - Data Comentário: 15/09/2026 14:19</t>
   </si>
   <si>
@@ -1331,12 +1337,6 @@
   </si>
   <si>
     <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1805] sendo a ultima baixa feita [1805]-18/09/2026 08:30:31.. - Data Comentário: 18/09/2026 15:28</t>
-  </si>
-  <si>
-    <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[11286]. - Data Comentário: 01/09/2026 05:59</t>
-  </si>
-  <si>
-    <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[11286]. - Data Comentário: 01/09/2026 05:58</t>
   </si>
   <si>
     <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[1808]. - Data Comentário: 01/09/2026 06:03</t>
@@ -1405,7 +1405,7 @@
     <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 21/09/2026 - Data Comentário: 18/09/2026 17:23</t>
   </si>
   <si>
-    <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1879] sendo a ultima baixa feita [1879]-18/09/2026 17:50:14.. - Data Comentário: 18/09/2026 17:45</t>
+    <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1879] sendo a ultima baixa feita [1879]-21/09/2026 17:50:14.. - Data Comentário: 21/09/2026 08:55</t>
   </si>
   <si>
     <t>Comentário Colaborador + Previsão de Conclusão. Previsto para: 18/09/2026 - Data Comentário: 18/09/2026 17:23</t>
@@ -22784,34 +22784,34 @@
     </row>
     <row r="300" spans="1:34">
       <c r="A300">
-        <v>6704</v>
+        <v>6945</v>
       </c>
       <c r="B300" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C300" t="s">
         <v>60</v>
       </c>
       <c r="D300" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E300" t="s">
         <v>64</v>
       </c>
       <c r="F300" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G300">
-        <v>1802</v>
+        <v>945</v>
       </c>
       <c r="H300">
         <v>0</v>
       </c>
       <c r="I300" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J300" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="L300" s="1">
         <v>46283</v>
@@ -22820,10 +22820,10 @@
         <v>223</v>
       </c>
       <c r="O300">
-        <v>18085198</v>
+        <v>18164487</v>
       </c>
       <c r="P300" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q300" t="s">
         <v>257</v>
@@ -22832,10 +22832,7 @@
         <v>3</v>
       </c>
       <c r="T300" t="s">
-        <v>265</v>
-      </c>
-      <c r="V300" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="W300" t="s">
         <v>363</v>
@@ -22845,9 +22842,6 @@
       </c>
       <c r="AG300" t="s">
         <v>468</v>
-      </c>
-      <c r="AH300" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="301" spans="1:34">
@@ -22870,16 +22864,16 @@
         <v>66</v>
       </c>
       <c r="G301">
-        <v>11286</v>
+        <v>946</v>
       </c>
       <c r="H301">
         <v>0</v>
       </c>
       <c r="I301" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J301" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="L301" s="1">
         <v>46283</v>
@@ -22888,10 +22882,10 @@
         <v>223</v>
       </c>
       <c r="O301">
-        <v>17399434</v>
+        <v>17398869</v>
       </c>
       <c r="P301" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q301" t="s">
         <v>257</v>
@@ -22910,9 +22904,6 @@
       </c>
       <c r="AG301" t="s">
         <v>468</v>
-      </c>
-      <c r="AH301" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="302" spans="1:34">
@@ -22935,16 +22926,16 @@
         <v>66</v>
       </c>
       <c r="G302">
-        <v>11286</v>
+        <v>946</v>
       </c>
       <c r="H302">
         <v>0</v>
       </c>
       <c r="I302" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J302" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="L302" s="1">
         <v>46283</v>
@@ -22953,10 +22944,10 @@
         <v>223</v>
       </c>
       <c r="O302">
-        <v>16962464</v>
+        <v>16962093</v>
       </c>
       <c r="P302" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q302" t="s">
         <v>257</v>
@@ -22968,7 +22959,7 @@
         <v>268</v>
       </c>
       <c r="W302" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AA302">
         <v>0</v>
@@ -22976,31 +22967,28 @@
       <c r="AG302" t="s">
         <v>468</v>
       </c>
-      <c r="AH302" t="s">
-        <v>476</v>
-      </c>
     </row>
     <row r="303" spans="1:34">
       <c r="A303">
-        <v>6945</v>
+        <v>6703</v>
       </c>
       <c r="B303" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C303" t="s">
         <v>60</v>
       </c>
       <c r="D303" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E303" t="s">
         <v>64</v>
       </c>
       <c r="F303" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G303">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H303">
         <v>0</v>
@@ -23009,7 +22997,7 @@
         <v>74</v>
       </c>
       <c r="J303" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L303" s="1">
         <v>46283</v>
@@ -23018,7 +23006,7 @@
         <v>223</v>
       </c>
       <c r="O303">
-        <v>18164487</v>
+        <v>17941132</v>
       </c>
       <c r="P303" t="s">
         <v>248</v>
@@ -23030,10 +23018,10 @@
         <v>3</v>
       </c>
       <c r="T303" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="W303" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AA303">
         <v>0</v>
@@ -23044,16 +23032,16 @@
     </row>
     <row r="304" spans="1:34">
       <c r="A304">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B304" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C304" t="s">
         <v>60</v>
       </c>
       <c r="D304" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E304" t="s">
         <v>64</v>
@@ -23080,7 +23068,7 @@
         <v>223</v>
       </c>
       <c r="O304">
-        <v>17941132</v>
+        <v>17952325</v>
       </c>
       <c r="P304" t="s">
         <v>248</v>
@@ -23092,10 +23080,13 @@
         <v>3</v>
       </c>
       <c r="T304" t="s">
-        <v>267</v>
+        <v>265</v>
+      </c>
+      <c r="V304" t="s">
+        <v>275</v>
       </c>
       <c r="W304" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AA304">
         <v>0</v>
@@ -23228,7 +23219,7 @@
         <v>275</v>
       </c>
       <c r="W306" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AA306">
         <v>0</v>
@@ -23299,7 +23290,7 @@
         <v>275</v>
       </c>
       <c r="W307" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AA307">
         <v>0</v>
@@ -23367,7 +23358,7 @@
         <v>262</v>
       </c>
       <c r="W308" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AA308">
         <v>0</v>
@@ -23438,7 +23429,7 @@
         <v>275</v>
       </c>
       <c r="W309" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AA309">
         <v>0</v>
@@ -23509,7 +23500,7 @@
         <v>275</v>
       </c>
       <c r="W310" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AA310">
         <v>0</v>
@@ -23580,7 +23571,7 @@
         <v>275</v>
       </c>
       <c r="W311" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AA311">
         <v>0</v>
@@ -23648,7 +23639,7 @@
         <v>261</v>
       </c>
       <c r="W312" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AA312">
         <v>0</v>
@@ -23716,7 +23707,7 @@
         <v>262</v>
       </c>
       <c r="W313" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AA313">
         <v>0</v>
@@ -23784,7 +23775,7 @@
         <v>263</v>
       </c>
       <c r="W314" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AA314">
         <v>0</v>
@@ -23852,7 +23843,7 @@
         <v>263</v>
       </c>
       <c r="W315" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AA315">
         <v>0</v>
@@ -23923,7 +23914,7 @@
         <v>275</v>
       </c>
       <c r="W316" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AA316">
         <v>0</v>
@@ -23994,7 +23985,7 @@
         <v>275</v>
       </c>
       <c r="W317" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AA317">
         <v>0</v>
@@ -24062,7 +24053,7 @@
         <v>262</v>
       </c>
       <c r="W318" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AA318">
         <v>0</v>
@@ -24130,7 +24121,7 @@
         <v>263</v>
       </c>
       <c r="W319" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AA319">
         <v>0</v>
@@ -24198,7 +24189,7 @@
         <v>263</v>
       </c>
       <c r="W320" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AA320">
         <v>0</v>
@@ -24266,7 +24257,7 @@
         <v>263</v>
       </c>
       <c r="W321" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AA321">
         <v>0</v>
@@ -24334,7 +24325,7 @@
         <v>263</v>
       </c>
       <c r="W322" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AA322">
         <v>0</v>
@@ -24405,7 +24396,7 @@
         <v>275</v>
       </c>
       <c r="W323" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AA323">
         <v>0</v>
@@ -24476,7 +24467,7 @@
         <v>275</v>
       </c>
       <c r="W324" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AA324">
         <v>0</v>
@@ -24544,7 +24535,7 @@
         <v>262</v>
       </c>
       <c r="W325" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AA325">
         <v>0</v>
@@ -24612,7 +24603,7 @@
         <v>263</v>
       </c>
       <c r="W326" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AA326">
         <v>0</v>
@@ -24680,7 +24671,7 @@
         <v>263</v>
       </c>
       <c r="W327" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AA327">
         <v>0</v>
@@ -24751,7 +24742,7 @@
         <v>275</v>
       </c>
       <c r="W328" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AA328">
         <v>0</v>
@@ -24819,7 +24810,7 @@
         <v>261</v>
       </c>
       <c r="W329" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AA329">
         <v>0</v>
@@ -24890,7 +24881,7 @@
         <v>275</v>
       </c>
       <c r="W330" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AA330">
         <v>0</v>
@@ -24958,7 +24949,7 @@
         <v>264</v>
       </c>
       <c r="W331" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AA331">
         <v>0</v>
@@ -25029,7 +25020,7 @@
         <v>275</v>
       </c>
       <c r="W332" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AA332">
         <v>0</v>
@@ -25097,7 +25088,7 @@
         <v>264</v>
       </c>
       <c r="W333" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AA333">
         <v>0</v>
@@ -25165,7 +25156,7 @@
         <v>268</v>
       </c>
       <c r="W334" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AA334">
         <v>0</v>
@@ -25236,7 +25227,7 @@
         <v>275</v>
       </c>
       <c r="W335" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AA335">
         <v>0</v>
@@ -25304,7 +25295,7 @@
         <v>267</v>
       </c>
       <c r="W336" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AA336">
         <v>0</v>
@@ -25375,7 +25366,7 @@
         <v>275</v>
       </c>
       <c r="W337" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AA337">
         <v>0</v>
@@ -25443,7 +25434,7 @@
         <v>265</v>
       </c>
       <c r="W338" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AA338">
         <v>0</v>
@@ -25514,7 +25505,7 @@
         <v>275</v>
       </c>
       <c r="W339" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AA339">
         <v>0</v>
@@ -25582,7 +25573,7 @@
         <v>264</v>
       </c>
       <c r="W340" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AA340">
         <v>0</v>
@@ -25650,7 +25641,7 @@
         <v>268</v>
       </c>
       <c r="W341" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AA341">
         <v>0</v>
@@ -25721,7 +25712,7 @@
         <v>275</v>
       </c>
       <c r="W342" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AA342">
         <v>0</v>
@@ -25789,7 +25780,7 @@
         <v>267</v>
       </c>
       <c r="W343" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AA343">
         <v>0</v>
@@ -25860,7 +25851,7 @@
         <v>275</v>
       </c>
       <c r="W344" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AA344">
         <v>0</v>
@@ -25928,7 +25919,7 @@
         <v>268</v>
       </c>
       <c r="W345" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AA345">
         <v>0</v>
@@ -25996,7 +25987,7 @@
         <v>267</v>
       </c>
       <c r="W346" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AA346">
         <v>0</v>
@@ -26067,7 +26058,7 @@
         <v>275</v>
       </c>
       <c r="W347" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AA347">
         <v>0</v>
@@ -26138,7 +26129,7 @@
         <v>275</v>
       </c>
       <c r="W348" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AA348">
         <v>0</v>
@@ -26206,7 +26197,7 @@
         <v>265</v>
       </c>
       <c r="W349" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AA349">
         <v>0</v>
@@ -26277,7 +26268,7 @@
         <v>275</v>
       </c>
       <c r="W350" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AA350">
         <v>0</v>
@@ -26348,7 +26339,7 @@
         <v>275</v>
       </c>
       <c r="W351" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AA351">
         <v>0</v>
@@ -26416,7 +26407,7 @@
         <v>261</v>
       </c>
       <c r="W352" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AA352">
         <v>0</v>
@@ -26484,7 +26475,7 @@
         <v>262</v>
       </c>
       <c r="W353" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AA353">
         <v>0</v>
@@ -26552,7 +26543,7 @@
         <v>261</v>
       </c>
       <c r="W354" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AA354">
         <v>0</v>
@@ -26620,7 +26611,7 @@
         <v>262</v>
       </c>
       <c r="W355" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AA355">
         <v>0</v>
@@ -26688,7 +26679,7 @@
         <v>264</v>
       </c>
       <c r="W356" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA356">
         <v>0</v>
@@ -26756,7 +26747,7 @@
         <v>275</v>
       </c>
       <c r="W357" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AA357">
         <v>0</v>
@@ -26824,7 +26815,7 @@
         <v>261</v>
       </c>
       <c r="W358" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AA358">
         <v>0</v>
@@ -26895,7 +26886,7 @@
         <v>275</v>
       </c>
       <c r="W359" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AA359">
         <v>0</v>
@@ -26966,7 +26957,7 @@
         <v>275</v>
       </c>
       <c r="W360" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AA360">
         <v>0</v>
@@ -27034,7 +27025,7 @@
         <v>264</v>
       </c>
       <c r="W361" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AA361">
         <v>0</v>
@@ -27102,7 +27093,7 @@
         <v>275</v>
       </c>
       <c r="W362" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AA362">
         <v>0</v>
@@ -27173,7 +27164,7 @@
         <v>275</v>
       </c>
       <c r="W363" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AA363">
         <v>0</v>
@@ -27244,7 +27235,7 @@
         <v>275</v>
       </c>
       <c r="W364" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AA364">
         <v>0</v>
@@ -27312,7 +27303,7 @@
         <v>264</v>
       </c>
       <c r="W365" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AA365">
         <v>0</v>
@@ -27377,7 +27368,7 @@
         <v>262</v>
       </c>
       <c r="W366" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AA366">
         <v>0</v>
@@ -27448,7 +27439,7 @@
         <v>275</v>
       </c>
       <c r="W367" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AA367">
         <v>0</v>
@@ -27513,7 +27504,7 @@
         <v>262</v>
       </c>
       <c r="W368" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AA368">
         <v>0</v>
@@ -27581,7 +27572,7 @@
         <v>261</v>
       </c>
       <c r="W369" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AA369">
         <v>0</v>
@@ -27646,7 +27637,7 @@
         <v>261</v>
       </c>
       <c r="W370" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AA370">
         <v>0</v>
@@ -27711,7 +27702,7 @@
         <v>263</v>
       </c>
       <c r="W371" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AA371">
         <v>0</v>
@@ -27779,7 +27770,7 @@
         <v>263</v>
       </c>
       <c r="W372" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AA372">
         <v>0</v>
@@ -27850,7 +27841,7 @@
         <v>275</v>
       </c>
       <c r="W373" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AA373">
         <v>0</v>
@@ -27918,7 +27909,7 @@
         <v>262</v>
       </c>
       <c r="W374" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AA374">
         <v>0</v>
@@ -27986,7 +27977,7 @@
         <v>262</v>
       </c>
       <c r="W375" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AA375">
         <v>0</v>
@@ -28057,7 +28048,7 @@
         <v>275</v>
       </c>
       <c r="W376" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AA376">
         <v>0</v>
@@ -28125,7 +28116,7 @@
         <v>265</v>
       </c>
       <c r="W377" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AA377">
         <v>0</v>
@@ -28193,7 +28184,7 @@
         <v>265</v>
       </c>
       <c r="W378" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AA378">
         <v>0</v>
@@ -28261,7 +28252,7 @@
         <v>267</v>
       </c>
       <c r="W379" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AA379">
         <v>0</v>
@@ -28329,7 +28320,7 @@
         <v>268</v>
       </c>
       <c r="W380" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AA380">
         <v>0</v>
@@ -28397,7 +28388,7 @@
         <v>267</v>
       </c>
       <c r="W381" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AA381">
         <v>0</v>
@@ -28465,7 +28456,7 @@
         <v>264</v>
       </c>
       <c r="W382" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AA382">
         <v>0</v>
@@ -28536,7 +28527,7 @@
         <v>275</v>
       </c>
       <c r="W383" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AA383">
         <v>0</v>
@@ -28604,7 +28595,7 @@
         <v>275</v>
       </c>
       <c r="W384" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AA384">
         <v>0</v>
@@ -28669,7 +28660,7 @@
         <v>264</v>
       </c>
       <c r="W385" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AA385">
         <v>0</v>
@@ -28737,7 +28728,7 @@
         <v>275</v>
       </c>
       <c r="W386" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AA386">
         <v>0</v>
@@ -28802,7 +28793,7 @@
         <v>267</v>
       </c>
       <c r="W387" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AA387">
         <v>0</v>
@@ -28870,7 +28861,7 @@
         <v>275</v>
       </c>
       <c r="W388" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AA388">
         <v>0</v>
@@ -28935,7 +28926,7 @@
         <v>265</v>
       </c>
       <c r="W389" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AA389">
         <v>0</v>
@@ -29000,7 +28991,7 @@
         <v>262</v>
       </c>
       <c r="W390" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AA390">
         <v>0</v>
@@ -29065,7 +29056,7 @@
         <v>263</v>
       </c>
       <c r="W391" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AA391">
         <v>0</v>
@@ -29130,7 +29121,7 @@
         <v>263</v>
       </c>
       <c r="W392" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AA392">
         <v>0</v>
@@ -29195,7 +29186,7 @@
         <v>264</v>
       </c>
       <c r="W393" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AA393">
         <v>0</v>
@@ -29257,7 +29248,7 @@
         <v>264</v>
       </c>
       <c r="W394" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AA394">
         <v>0</v>
@@ -29322,7 +29313,7 @@
         <v>264</v>
       </c>
       <c r="W395" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AA395">
         <v>0</v>
@@ -29387,7 +29378,7 @@
         <v>263</v>
       </c>
       <c r="W396" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AA396">
         <v>0</v>
@@ -29594,7 +29585,7 @@
         <v>275</v>
       </c>
       <c r="W399" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AA399">
         <v>0</v>
@@ -29668,7 +29659,7 @@
         <v>275</v>
       </c>
       <c r="W400" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AA400">
         <v>0</v>
@@ -30283,7 +30274,7 @@
         <v>275</v>
       </c>
       <c r="W409" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AA409">
         <v>0</v>
@@ -30493,7 +30484,7 @@
         <v>264</v>
       </c>
       <c r="W412" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AA412">
         <v>0</v>
@@ -30984,7 +30975,7 @@
         <v>275</v>
       </c>
       <c r="W419" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AA419">
         <v>0</v>
@@ -31061,7 +31052,7 @@
         <v>275</v>
       </c>
       <c r="W420" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AA420">
         <v>0</v>
@@ -31135,7 +31126,7 @@
         <v>261</v>
       </c>
       <c r="W421" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AA421">
         <v>0</v>
@@ -31280,7 +31271,7 @@
         <v>275</v>
       </c>
       <c r="W423" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AA423">
         <v>0</v>
@@ -31422,7 +31413,7 @@
         <v>275</v>
       </c>
       <c r="W425" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AA425">
         <v>0</v>
@@ -31499,7 +31490,7 @@
         <v>275</v>
       </c>
       <c r="W426" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AA426">
         <v>0</v>
@@ -31576,7 +31567,7 @@
         <v>275</v>
       </c>
       <c r="W427" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AA427">
         <v>0</v>
@@ -31653,7 +31644,7 @@
         <v>275</v>
       </c>
       <c r="W428" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AA428">
         <v>0</v>
@@ -31934,7 +31925,7 @@
         <v>275</v>
       </c>
       <c r="W432" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AA432">
         <v>0</v>
@@ -32011,7 +32002,7 @@
         <v>275</v>
       </c>
       <c r="W433" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA433">
         <v>0</v>
@@ -32088,7 +32079,7 @@
         <v>275</v>
       </c>
       <c r="W434" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AA434">
         <v>0</v>
@@ -32165,7 +32156,7 @@
         <v>275</v>
       </c>
       <c r="W435" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AA435">
         <v>0</v>
@@ -32375,7 +32366,7 @@
         <v>264</v>
       </c>
       <c r="W438" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AA438">
         <v>0</v>
@@ -32443,7 +32434,7 @@
         <v>268</v>
       </c>
       <c r="W439" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AA439">
         <v>0</v>
@@ -32517,7 +32508,7 @@
         <v>275</v>
       </c>
       <c r="W440" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AA440">
         <v>0</v>
@@ -32591,7 +32582,7 @@
         <v>275</v>
       </c>
       <c r="W441" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AA441">
         <v>0</v>
@@ -32665,7 +32656,7 @@
         <v>275</v>
       </c>
       <c r="W442" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AA442">
         <v>0</v>
@@ -32739,7 +32730,7 @@
         <v>275</v>
       </c>
       <c r="W443" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AA443">
         <v>0</v>
@@ -32813,7 +32804,7 @@
         <v>267</v>
       </c>
       <c r="W444" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AA444">
         <v>0</v>
@@ -32887,7 +32878,7 @@
         <v>275</v>
       </c>
       <c r="W445" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AA445">
         <v>0</v>
@@ -32958,7 +32949,7 @@
         <v>261</v>
       </c>
       <c r="W446" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AA446">
         <v>0</v>
@@ -33029,7 +33020,7 @@
         <v>262</v>
       </c>
       <c r="W447" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AA447">
         <v>0</v>
@@ -33106,7 +33097,7 @@
         <v>275</v>
       </c>
       <c r="W448" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AA448">
         <v>0</v>
@@ -33183,7 +33174,7 @@
         <v>275</v>
       </c>
       <c r="W449" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AA449">
         <v>0</v>
@@ -33260,7 +33251,7 @@
         <v>275</v>
       </c>
       <c r="W450" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AA450">
         <v>0</v>
@@ -33337,7 +33328,7 @@
         <v>275</v>
       </c>
       <c r="W451" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AA451">
         <v>0</v>
@@ -33411,7 +33402,7 @@
         <v>267</v>
       </c>
       <c r="W452" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AA452">
         <v>0</v>
@@ -33485,7 +33476,7 @@
         <v>268</v>
       </c>
       <c r="W453" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AA453">
         <v>0</v>
@@ -34464,7 +34455,7 @@
         <v>275</v>
       </c>
       <c r="W467" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AA467">
         <v>0</v>
@@ -34538,7 +34529,7 @@
         <v>275</v>
       </c>
       <c r="W468" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AA468">
         <v>0</v>
@@ -34887,7 +34878,7 @@
         <v>263</v>
       </c>
       <c r="W473" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AA473">
         <v>0</v>
@@ -34961,7 +34952,7 @@
         <v>263</v>
       </c>
       <c r="W474" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AA474">
         <v>0</v>
@@ -35035,7 +35026,7 @@
         <v>275</v>
       </c>
       <c r="W475" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AA475">
         <v>0</v>
@@ -35245,7 +35236,7 @@
         <v>275</v>
       </c>
       <c r="W478" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AA478">
         <v>0</v>
@@ -35316,7 +35307,7 @@
         <v>261</v>
       </c>
       <c r="W479" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AA479">
         <v>0</v>
@@ -35387,7 +35378,7 @@
         <v>275</v>
       </c>
       <c r="W480" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AA480">
         <v>0</v>
@@ -35458,7 +35449,7 @@
         <v>275</v>
       </c>
       <c r="W481" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AA481">
         <v>0</v>
@@ -35532,7 +35523,7 @@
         <v>275</v>
       </c>
       <c r="W482" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AA482">
         <v>0</v>
@@ -35603,7 +35594,7 @@
         <v>275</v>
       </c>
       <c r="W483" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AA483">
         <v>0</v>
@@ -35748,7 +35739,7 @@
         <v>264</v>
       </c>
       <c r="W485" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AA485">
         <v>0</v>
@@ -35825,7 +35816,7 @@
         <v>275</v>
       </c>
       <c r="W486" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AA486">
         <v>0</v>
@@ -35899,7 +35890,7 @@
         <v>265</v>
       </c>
       <c r="W487" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AA487">
         <v>0</v>
@@ -35970,7 +35961,7 @@
         <v>267</v>
       </c>
       <c r="W488" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AA488">
         <v>0</v>
@@ -35987,10 +35978,10 @@
     </row>
     <row r="489" spans="1:34">
       <c r="A489">
-        <v>6486</v>
+        <v>6704</v>
       </c>
       <c r="B489" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C489" t="s">
         <v>60</v>
@@ -36005,7 +35996,7 @@
         <v>66</v>
       </c>
       <c r="G489">
-        <v>11286</v>
+        <v>1802</v>
       </c>
       <c r="H489">
         <v>0</v>
@@ -36014,7 +36005,7 @@
         <v>73</v>
       </c>
       <c r="J489" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L489" s="1">
         <v>46283</v>
@@ -36023,7 +36014,7 @@
         <v>223</v>
       </c>
       <c r="O489">
-        <v>18155336</v>
+        <v>18085198</v>
       </c>
       <c r="P489" t="s">
         <v>247</v>
@@ -36032,25 +36023,25 @@
         <v>256</v>
       </c>
       <c r="R489" s="1">
-        <v>46280.59788275463</v>
+        <v>46286.36164050926</v>
       </c>
       <c r="S489">
         <v>3</v>
       </c>
       <c r="T489" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="V489" t="s">
         <v>275</v>
       </c>
       <c r="W489" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AA489">
         <v>0</v>
       </c>
       <c r="AB489" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="AG489" t="s">
         <v>468</v>
@@ -36061,10 +36052,10 @@
     </row>
     <row r="490" spans="1:34">
       <c r="A490">
-        <v>6704</v>
+        <v>5417</v>
       </c>
       <c r="B490" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C490" t="s">
         <v>60</v>
@@ -36079,7 +36070,7 @@
         <v>66</v>
       </c>
       <c r="G490">
-        <v>1788</v>
+        <v>11286</v>
       </c>
       <c r="H490">
         <v>0</v>
@@ -36088,16 +36079,16 @@
         <v>73</v>
       </c>
       <c r="J490" t="s">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="L490" s="1">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="N490" t="s">
         <v>223</v>
       </c>
       <c r="O490">
-        <v>18085132</v>
+        <v>17399434</v>
       </c>
       <c r="P490" t="s">
         <v>247</v>
@@ -36106,25 +36097,25 @@
         <v>256</v>
       </c>
       <c r="R490" s="1">
-        <v>46266.45957931713</v>
+        <v>46286.36164494213</v>
       </c>
       <c r="S490">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T490" t="s">
-        <v>265</v>
-      </c>
-      <c r="V490" t="s">
-        <v>275</v>
+        <v>264</v>
+      </c>
+      <c r="W490" t="s">
+        <v>421</v>
       </c>
       <c r="AA490">
         <v>0</v>
       </c>
       <c r="AB490" t="s">
-        <v>247</v>
+        <v>455</v>
       </c>
       <c r="AG490" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AH490" t="s">
         <v>476</v>
@@ -36132,16 +36123,16 @@
     </row>
     <row r="491" spans="1:34">
       <c r="A491">
-        <v>6705</v>
+        <v>6404</v>
       </c>
       <c r="B491" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C491" t="s">
         <v>60</v>
       </c>
       <c r="D491" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E491" t="s">
         <v>64</v>
@@ -36150,7 +36141,7 @@
         <v>66</v>
       </c>
       <c r="G491">
-        <v>1805</v>
+        <v>11286</v>
       </c>
       <c r="H491">
         <v>0</v>
@@ -36159,7 +36150,7 @@
         <v>73</v>
       </c>
       <c r="J491" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="L491" s="1">
         <v>46283</v>
@@ -36168,7 +36159,7 @@
         <v>223</v>
       </c>
       <c r="O491">
-        <v>17948948</v>
+        <v>16962464</v>
       </c>
       <c r="P491" t="s">
         <v>247</v>
@@ -36177,13 +36168,13 @@
         <v>256</v>
       </c>
       <c r="R491" s="1">
-        <v>46283.35452896991</v>
+        <v>46286.36164826389</v>
       </c>
       <c r="S491">
         <v>3</v>
       </c>
       <c r="T491" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="W491" t="s">
         <v>422</v>
@@ -36203,16 +36194,16 @@
     </row>
     <row r="492" spans="1:34">
       <c r="A492">
-        <v>6779</v>
+        <v>6486</v>
       </c>
       <c r="B492" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C492" t="s">
         <v>60</v>
       </c>
       <c r="D492" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E492" t="s">
         <v>64</v>
@@ -36221,7 +36212,7 @@
         <v>66</v>
       </c>
       <c r="G492">
-        <v>1805</v>
+        <v>11286</v>
       </c>
       <c r="H492">
         <v>0</v>
@@ -36230,7 +36221,7 @@
         <v>73</v>
       </c>
       <c r="J492" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="L492" s="1">
         <v>46283</v>
@@ -36239,7 +36230,7 @@
         <v>223</v>
       </c>
       <c r="O492">
-        <v>18084966</v>
+        <v>18155336</v>
       </c>
       <c r="P492" t="s">
         <v>247</v>
@@ -36248,25 +36239,25 @@
         <v>256</v>
       </c>
       <c r="R492" s="1">
-        <v>46283.35453171296</v>
+        <v>46280.59788275463</v>
       </c>
       <c r="S492">
         <v>3</v>
       </c>
       <c r="T492" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="V492" t="s">
         <v>275</v>
       </c>
       <c r="W492" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AA492">
         <v>0</v>
       </c>
       <c r="AB492" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="AG492" t="s">
         <v>468</v>
@@ -36277,16 +36268,16 @@
     </row>
     <row r="493" spans="1:34">
       <c r="A493">
-        <v>6404</v>
+        <v>6704</v>
       </c>
       <c r="B493" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C493" t="s">
         <v>60</v>
       </c>
       <c r="D493" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E493" t="s">
         <v>64</v>
@@ -36295,7 +36286,7 @@
         <v>66</v>
       </c>
       <c r="G493">
-        <v>1811</v>
+        <v>1788</v>
       </c>
       <c r="H493">
         <v>0</v>
@@ -36304,16 +36295,16 @@
         <v>73</v>
       </c>
       <c r="J493" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="L493" s="1">
-        <v>46290</v>
+        <v>46281</v>
       </c>
       <c r="N493" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="O493">
-        <v>16962181</v>
+        <v>18085132</v>
       </c>
       <c r="P493" t="s">
         <v>247</v>
@@ -36322,22 +36313,25 @@
         <v>256</v>
       </c>
       <c r="R493" s="1">
-        <v>46240.6829959838</v>
+        <v>46266.45957931713</v>
       </c>
       <c r="S493">
-        <v>-4</v>
+        <v>5</v>
       </c>
       <c r="T493" t="s">
-        <v>268</v>
+        <v>265</v>
+      </c>
+      <c r="V493" t="s">
+        <v>275</v>
       </c>
       <c r="AA493">
         <v>0</v>
       </c>
       <c r="AB493" t="s">
-        <v>457</v>
+        <v>247</v>
       </c>
       <c r="AG493" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AH493" t="s">
         <v>476</v>
@@ -36345,16 +36339,16 @@
     </row>
     <row r="494" spans="1:34">
       <c r="A494">
-        <v>5417</v>
+        <v>6705</v>
       </c>
       <c r="B494" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C494" t="s">
         <v>60</v>
       </c>
       <c r="D494" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E494" t="s">
         <v>64</v>
@@ -36363,7 +36357,7 @@
         <v>66</v>
       </c>
       <c r="G494">
-        <v>7025</v>
+        <v>1805</v>
       </c>
       <c r="H494">
         <v>0</v>
@@ -36372,16 +36366,16 @@
         <v>73</v>
       </c>
       <c r="J494" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L494" s="1">
-        <v>46288</v>
+        <v>46283</v>
       </c>
       <c r="N494" t="s">
         <v>223</v>
       </c>
       <c r="O494">
-        <v>17399280</v>
+        <v>17948948</v>
       </c>
       <c r="P494" t="s">
         <v>247</v>
@@ -36390,25 +36384,25 @@
         <v>256</v>
       </c>
       <c r="R494" s="1">
-        <v>46283.38367943287</v>
+        <v>46283.35452896991</v>
       </c>
       <c r="S494">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="T494" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="W494" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AA494">
         <v>0</v>
       </c>
       <c r="AB494" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="AG494" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AH494" t="s">
         <v>476</v>
@@ -36416,16 +36410,16 @@
     </row>
     <row r="495" spans="1:34">
       <c r="A495">
-        <v>6404</v>
+        <v>6779</v>
       </c>
       <c r="B495" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C495" t="s">
         <v>60</v>
       </c>
       <c r="D495" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E495" t="s">
         <v>64</v>
@@ -36434,7 +36428,7 @@
         <v>66</v>
       </c>
       <c r="G495">
-        <v>7025</v>
+        <v>1805</v>
       </c>
       <c r="H495">
         <v>0</v>
@@ -36443,16 +36437,16 @@
         <v>73</v>
       </c>
       <c r="J495" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L495" s="1">
-        <v>46288</v>
+        <v>46283</v>
       </c>
       <c r="N495" t="s">
         <v>223</v>
       </c>
       <c r="O495">
-        <v>16962338</v>
+        <v>18084966</v>
       </c>
       <c r="P495" t="s">
         <v>247</v>
@@ -36461,13 +36455,16 @@
         <v>256</v>
       </c>
       <c r="R495" s="1">
-        <v>46282.54038741898</v>
+        <v>46283.35453171296</v>
       </c>
       <c r="S495">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="T495" t="s">
-        <v>268</v>
+        <v>265</v>
+      </c>
+      <c r="V495" t="s">
+        <v>275</v>
       </c>
       <c r="W495" t="s">
         <v>424</v>
@@ -36476,10 +36473,10 @@
         <v>0</v>
       </c>
       <c r="AB495" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="AG495" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AH495" t="s">
         <v>476</v>
@@ -36487,16 +36484,16 @@
     </row>
     <row r="496" spans="1:34">
       <c r="A496">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B496" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C496" t="s">
         <v>60</v>
       </c>
       <c r="D496" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E496" t="s">
         <v>64</v>
@@ -36505,7 +36502,7 @@
         <v>66</v>
       </c>
       <c r="G496">
-        <v>1793</v>
+        <v>1811</v>
       </c>
       <c r="H496">
         <v>0</v>
@@ -36514,19 +36511,16 @@
         <v>73</v>
       </c>
       <c r="J496" t="s">
-        <v>108</v>
+        <v>157</v>
       </c>
       <c r="L496" s="1">
-        <v>46283</v>
-      </c>
-      <c r="M496" t="s">
-        <v>221</v>
+        <v>46290</v>
       </c>
       <c r="N496" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="O496">
-        <v>17398945</v>
+        <v>16962181</v>
       </c>
       <c r="P496" t="s">
         <v>247</v>
@@ -36535,22 +36529,19 @@
         <v>256</v>
       </c>
       <c r="R496" s="1">
-        <v>46280.74859975695</v>
+        <v>46240.6829959838</v>
       </c>
       <c r="S496">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="T496" t="s">
-        <v>264</v>
-      </c>
-      <c r="W496" t="s">
-        <v>425</v>
+        <v>268</v>
       </c>
       <c r="AA496">
         <v>0</v>
       </c>
       <c r="AB496" t="s">
-        <v>247</v>
+        <v>457</v>
       </c>
       <c r="AG496" t="s">
         <v>468</v>
@@ -36559,92 +36550,89 @@
         <v>476</v>
       </c>
     </row>
-    <row r="497" spans="1:33">
+    <row r="497" spans="1:34">
       <c r="A497">
-        <v>6628</v>
+        <v>5417</v>
       </c>
       <c r="B497" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C497" t="s">
         <v>60</v>
       </c>
       <c r="D497" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E497" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F497" t="s">
         <v>66</v>
       </c>
       <c r="G497">
-        <v>945</v>
+        <v>7025</v>
       </c>
       <c r="H497">
         <v>0</v>
       </c>
       <c r="I497" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J497" t="s">
-        <v>136</v>
+        <v>175</v>
       </c>
       <c r="L497" s="1">
-        <v>46283</v>
-      </c>
-      <c r="M497" t="s">
-        <v>221</v>
+        <v>46288</v>
       </c>
       <c r="N497" t="s">
         <v>223</v>
       </c>
       <c r="O497">
-        <v>16959938</v>
+        <v>17399280</v>
       </c>
       <c r="P497" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Q497" t="s">
         <v>256</v>
       </c>
       <c r="R497" s="1">
-        <v>46283.64213659722</v>
+        <v>46283.38367943287</v>
       </c>
       <c r="S497">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="T497" t="s">
-        <v>260</v>
-      </c>
-      <c r="V497" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="W497" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AA497">
         <v>0</v>
       </c>
       <c r="AB497" t="s">
-        <v>248</v>
+        <v>460</v>
       </c>
       <c r="AG497" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="498" spans="1:33">
+        <v>467</v>
+      </c>
+      <c r="AH497" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="498" spans="1:34">
       <c r="A498">
-        <v>6705</v>
+        <v>6404</v>
       </c>
       <c r="B498" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C498" t="s">
         <v>60</v>
       </c>
       <c r="D498" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E498" t="s">
         <v>64</v>
@@ -36653,69 +36641,69 @@
         <v>66</v>
       </c>
       <c r="G498">
-        <v>945</v>
+        <v>7025</v>
       </c>
       <c r="H498">
         <v>0</v>
       </c>
       <c r="I498" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J498" t="s">
-        <v>136</v>
+        <v>175</v>
       </c>
       <c r="L498" s="1">
-        <v>46283</v>
-      </c>
-      <c r="M498" t="s">
-        <v>221</v>
+        <v>46288</v>
       </c>
       <c r="N498" t="s">
         <v>223</v>
       </c>
       <c r="O498">
-        <v>17952524</v>
+        <v>16962338</v>
       </c>
       <c r="P498" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Q498" t="s">
         <v>256</v>
       </c>
       <c r="R498" s="1">
-        <v>46283.65291121528</v>
+        <v>46282.54038741898</v>
       </c>
       <c r="S498">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="T498" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="W498" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AA498">
         <v>0</v>
       </c>
       <c r="AB498" t="s">
-        <v>248</v>
+        <v>460</v>
       </c>
       <c r="AG498" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="499" spans="1:33">
+        <v>467</v>
+      </c>
+      <c r="AH498" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="499" spans="1:34">
       <c r="A499">
-        <v>6779</v>
+        <v>5417</v>
       </c>
       <c r="B499" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C499" t="s">
         <v>60</v>
       </c>
       <c r="D499" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E499" t="s">
         <v>64</v>
@@ -36724,16 +36712,16 @@
         <v>66</v>
       </c>
       <c r="G499">
-        <v>945</v>
+        <v>1793</v>
       </c>
       <c r="H499">
         <v>0</v>
       </c>
       <c r="I499" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J499" t="s">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="L499" s="1">
         <v>46283</v>
@@ -36745,25 +36733,22 @@
         <v>223</v>
       </c>
       <c r="O499">
-        <v>18056695</v>
+        <v>17398945</v>
       </c>
       <c r="P499" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Q499" t="s">
         <v>256</v>
       </c>
       <c r="R499" s="1">
-        <v>46283.65291194445</v>
+        <v>46280.74859975695</v>
       </c>
       <c r="S499">
         <v>3</v>
       </c>
       <c r="T499" t="s">
-        <v>265</v>
-      </c>
-      <c r="V499" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="W499" t="s">
         <v>427</v>
@@ -36772,33 +36757,36 @@
         <v>0</v>
       </c>
       <c r="AB499" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AG499" t="s">
         <v>468</v>
       </c>
-    </row>
-    <row r="500" spans="1:33">
+      <c r="AH499" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="500" spans="1:34">
       <c r="A500">
-        <v>5417</v>
+        <v>6628</v>
       </c>
       <c r="B500" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C500" t="s">
         <v>60</v>
       </c>
       <c r="D500" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E500" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F500" t="s">
         <v>66</v>
       </c>
       <c r="G500">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H500">
         <v>0</v>
@@ -36807,16 +36795,19 @@
         <v>74</v>
       </c>
       <c r="J500" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L500" s="1">
         <v>46283</v>
       </c>
+      <c r="M500" t="s">
+        <v>221</v>
+      </c>
       <c r="N500" t="s">
         <v>223</v>
       </c>
       <c r="O500">
-        <v>17398869</v>
+        <v>16959938</v>
       </c>
       <c r="P500" t="s">
         <v>248</v>
@@ -36825,13 +36816,16 @@
         <v>256</v>
       </c>
       <c r="R500" s="1">
-        <v>46266.25077376157</v>
+        <v>46283.64213659722</v>
       </c>
       <c r="S500">
         <v>3</v>
       </c>
       <c r="T500" t="s">
-        <v>264</v>
+        <v>260</v>
+      </c>
+      <c r="V500" t="s">
+        <v>275</v>
       </c>
       <c r="W500" t="s">
         <v>428</v>
@@ -36840,24 +36834,24 @@
         <v>0</v>
       </c>
       <c r="AB500" t="s">
-        <v>460</v>
+        <v>248</v>
       </c>
       <c r="AG500" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="501" spans="1:33">
+    <row r="501" spans="1:34">
       <c r="A501">
-        <v>6278</v>
+        <v>6705</v>
       </c>
       <c r="B501" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C501" t="s">
         <v>60</v>
       </c>
       <c r="D501" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E501" t="s">
         <v>64</v>
@@ -36866,7 +36860,7 @@
         <v>66</v>
       </c>
       <c r="G501">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H501">
         <v>0</v>
@@ -36875,54 +36869,60 @@
         <v>74</v>
       </c>
       <c r="J501" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L501" s="1">
         <v>46283</v>
       </c>
+      <c r="M501" t="s">
+        <v>221</v>
+      </c>
       <c r="N501" t="s">
         <v>223</v>
       </c>
       <c r="O501">
-        <v>17539710</v>
+        <v>17952524</v>
+      </c>
+      <c r="P501" t="s">
+        <v>248</v>
       </c>
       <c r="Q501" t="s">
         <v>256</v>
       </c>
       <c r="R501" s="1">
-        <v>46023.15052320602</v>
+        <v>46283.65291121528</v>
       </c>
       <c r="S501">
         <v>3</v>
       </c>
       <c r="T501" t="s">
-        <v>270</v>
-      </c>
-      <c r="V501" t="s">
-        <v>275</v>
+        <v>265</v>
+      </c>
+      <c r="W501" t="s">
+        <v>429</v>
       </c>
       <c r="AA501">
         <v>0</v>
       </c>
       <c r="AB501" t="s">
-        <v>460</v>
+        <v>248</v>
       </c>
       <c r="AG501" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="502" spans="1:33">
+    <row r="502" spans="1:34">
       <c r="A502">
-        <v>6404</v>
+        <v>6779</v>
       </c>
       <c r="B502" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C502" t="s">
         <v>60</v>
       </c>
       <c r="D502" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E502" t="s">
         <v>64</v>
@@ -36931,7 +36931,7 @@
         <v>66</v>
       </c>
       <c r="G502">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H502">
         <v>0</v>
@@ -36940,16 +36940,19 @@
         <v>74</v>
       </c>
       <c r="J502" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L502" s="1">
         <v>46283</v>
       </c>
+      <c r="M502" t="s">
+        <v>221</v>
+      </c>
       <c r="N502" t="s">
         <v>223</v>
       </c>
       <c r="O502">
-        <v>16962093</v>
+        <v>18056695</v>
       </c>
       <c r="P502" t="s">
         <v>248</v>
@@ -36958,13 +36961,16 @@
         <v>256</v>
       </c>
       <c r="R502" s="1">
-        <v>46266.25004302083</v>
+        <v>46283.65291194445</v>
       </c>
       <c r="S502">
         <v>3</v>
       </c>
       <c r="T502" t="s">
-        <v>268</v>
+        <v>265</v>
+      </c>
+      <c r="V502" t="s">
+        <v>275</v>
       </c>
       <c r="W502" t="s">
         <v>429</v>
@@ -36973,18 +36979,18 @@
         <v>0</v>
       </c>
       <c r="AB502" t="s">
-        <v>460</v>
+        <v>248</v>
       </c>
       <c r="AG502" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="503" spans="1:33">
+    <row r="503" spans="1:34">
       <c r="A503">
-        <v>6627</v>
+        <v>6278</v>
       </c>
       <c r="B503" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="C503" t="s">
         <v>60</v>
@@ -36993,7 +36999,7 @@
         <v>61</v>
       </c>
       <c r="E503" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F503" t="s">
         <v>66</v>
@@ -37013,52 +37019,43 @@
       <c r="L503" s="1">
         <v>46283</v>
       </c>
-      <c r="M503" t="s">
-        <v>221</v>
-      </c>
       <c r="N503" t="s">
         <v>223</v>
       </c>
       <c r="O503">
-        <v>17042272</v>
-      </c>
-      <c r="P503" t="s">
-        <v>248</v>
+        <v>17539710</v>
       </c>
       <c r="Q503" t="s">
         <v>256</v>
       </c>
       <c r="R503" s="1">
-        <v>46283.67999300926</v>
+        <v>46023.15052320602</v>
       </c>
       <c r="S503">
         <v>3</v>
       </c>
       <c r="T503" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="V503" t="s">
         <v>275</v>
       </c>
-      <c r="W503" t="s">
-        <v>425</v>
-      </c>
       <c r="AA503">
         <v>0</v>
       </c>
       <c r="AB503" t="s">
-        <v>248</v>
+        <v>460</v>
       </c>
       <c r="AG503" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="504" spans="1:33">
+    <row r="504" spans="1:34">
       <c r="A504">
-        <v>6704</v>
+        <v>6627</v>
       </c>
       <c r="B504" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C504" t="s">
         <v>60</v>
@@ -37067,7 +37064,7 @@
         <v>61</v>
       </c>
       <c r="E504" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F504" t="s">
         <v>66</v>
@@ -37087,11 +37084,14 @@
       <c r="L504" s="1">
         <v>46283</v>
       </c>
+      <c r="M504" t="s">
+        <v>221</v>
+      </c>
       <c r="N504" t="s">
         <v>223</v>
       </c>
       <c r="O504">
-        <v>17952325</v>
+        <v>17042272</v>
       </c>
       <c r="P504" t="s">
         <v>248</v>
@@ -37100,28 +37100,31 @@
         <v>256</v>
       </c>
       <c r="R504" s="1">
-        <v>46057.39078453703</v>
+        <v>46283.67999300926</v>
       </c>
       <c r="S504">
         <v>3</v>
       </c>
       <c r="T504" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="V504" t="s">
         <v>275</v>
       </c>
+      <c r="W504" t="s">
+        <v>427</v>
+      </c>
       <c r="AA504">
         <v>0</v>
       </c>
       <c r="AB504" t="s">
-        <v>460</v>
+        <v>248</v>
       </c>
       <c r="AG504" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="505" spans="1:33">
+    <row r="505" spans="1:34">
       <c r="A505">
         <v>6945</v>
       </c>
@@ -37180,7 +37183,7 @@
         <v>261</v>
       </c>
       <c r="W505" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AA505">
         <v>0</v>
@@ -37192,7 +37195,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="506" spans="1:33">
+    <row r="506" spans="1:34">
       <c r="A506">
         <v>5417</v>
       </c>
@@ -37260,7 +37263,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="507" spans="1:33">
+    <row r="507" spans="1:34">
       <c r="A507">
         <v>6278</v>
       </c>
@@ -37325,7 +37328,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="508" spans="1:33">
+    <row r="508" spans="1:34">
       <c r="A508">
         <v>6404</v>
       </c>
@@ -37393,7 +37396,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="509" spans="1:33">
+    <row r="509" spans="1:34">
       <c r="A509">
         <v>6703</v>
       </c>
@@ -37461,7 +37464,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="510" spans="1:33">
+    <row r="510" spans="1:34">
       <c r="A510">
         <v>6704</v>
       </c>
@@ -37529,7 +37532,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="511" spans="1:33">
+    <row r="511" spans="1:34">
       <c r="A511">
         <v>6949</v>
       </c>
@@ -37597,7 +37600,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="512" spans="1:33">
+    <row r="512" spans="1:34">
       <c r="A512">
         <v>6962</v>
       </c>
@@ -37996,7 +37999,7 @@
         <v>265</v>
       </c>
       <c r="W517" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AA517">
         <v>0</v>
@@ -42769,6 +42772,9 @@
       <c r="L585" s="1">
         <v>46283</v>
       </c>
+      <c r="M585" t="s">
+        <v>212</v>
+      </c>
       <c r="N585" t="s">
         <v>223</v>
       </c>
@@ -42921,7 +42927,7 @@
         <v>261</v>
       </c>
       <c r="W587" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AG587" t="s">
         <v>469</v>
@@ -42983,7 +42989,7 @@
         <v>273</v>
       </c>
       <c r="W588" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG588" t="s">
         <v>467</v>
@@ -43048,7 +43054,7 @@
         <v>274</v>
       </c>
       <c r="W589" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG589" t="s">
         <v>467</v>
@@ -43113,7 +43119,7 @@
         <v>273</v>
       </c>
       <c r="W590" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG590" t="s">
         <v>467</v>
@@ -43178,7 +43184,7 @@
         <v>274</v>
       </c>
       <c r="W591" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG591" t="s">
         <v>467</v>
@@ -43243,7 +43249,7 @@
         <v>273</v>
       </c>
       <c r="W592" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG592" t="s">
         <v>467</v>
@@ -43308,7 +43314,7 @@
         <v>274</v>
       </c>
       <c r="W593" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG593" t="s">
         <v>467</v>
@@ -43373,7 +43379,7 @@
         <v>273</v>
       </c>
       <c r="W594" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG594" t="s">
         <v>467</v>
@@ -43438,7 +43444,7 @@
         <v>274</v>
       </c>
       <c r="W595" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG595" t="s">
         <v>467</v>
@@ -43503,7 +43509,7 @@
         <v>274</v>
       </c>
       <c r="W596" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG596" t="s">
         <v>467</v>

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8975" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8974" uniqueCount="481">
   <si>
     <t>CodCliente</t>
   </si>
@@ -475,6 +475,9 @@
     <t>Fed - PIS/COFINS Não Cumul/Mon - 5856</t>
   </si>
   <si>
+    <t>Movimento - Sistema de Análise</t>
+  </si>
+  <si>
     <t>Receitas Financeiras ( Aplicação Financeira )</t>
   </si>
   <si>
@@ -530,9 +533,6 @@
   </si>
   <si>
     <t>Fed - DAS</t>
-  </si>
-  <si>
-    <t>Movimento - Sistema de Análise</t>
   </si>
   <si>
     <t>Fechamento Fiscal</t>
@@ -1172,6 +1172,9 @@
   </si>
   <si>
     <t>Comentário Colaborador + Previsão de Conclusão. Previsto para: 22/09/2026 - Data Comentário: 18/09/2026 15:24</t>
+  </si>
+  <si>
+    <t>Reaberto via API integração MGC x Sistema de Analise Fiscal em 21/09/2026 12:44:23. - Data Comentário: 21/09/2026 12:41</t>
   </si>
   <si>
     <t>Comentário Colaborador + Previsão de Conclusão. Previsto para: 24/09/2026 - Data Comentário: 18/09/2026 15:24</t>
@@ -1284,9 +1287,6 @@
   </si>
   <si>
     <t>Tarefa baixada via Rotina SisAnalise x MGC - ExecutarPisCofinsZeradosOuComCredito. - Data Comentário: 18/09/2026 18:03</t>
-  </si>
-  <si>
-    <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 17/09/2026 17:56:12. - Data Comentário: 17/09/2026 17:51</t>
   </si>
   <si>
     <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 17/09/2026 17:55:53. - Data Comentário: 17/09/2026 17:50</t>
@@ -27316,10 +27316,10 @@
     </row>
     <row r="369" spans="1:34">
       <c r="A369">
-        <v>6949</v>
+        <v>6548</v>
       </c>
       <c r="B369" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C369" t="s">
         <v>60</v>
@@ -27331,13 +27331,13 @@
         <v>64</v>
       </c>
       <c r="F369" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G369">
-        <v>1914</v>
+        <v>7026</v>
       </c>
       <c r="H369">
-        <v>1862</v>
+        <v>0</v>
       </c>
       <c r="I369" t="s">
         <v>72</v>
@@ -27346,31 +27346,31 @@
         <v>153</v>
       </c>
       <c r="L369" s="1">
-        <v>46286</v>
-      </c>
-      <c r="M369" t="s">
-        <v>213</v>
+        <v>46288</v>
       </c>
       <c r="N369" t="s">
         <v>224</v>
       </c>
       <c r="O369">
-        <v>18214883</v>
+        <v>18094899</v>
       </c>
       <c r="P369" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="Q369" t="s">
         <v>254</v>
       </c>
       <c r="S369">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="T369" t="s">
-        <v>258</v>
+        <v>255</v>
+      </c>
+      <c r="V369" t="s">
+        <v>271</v>
       </c>
       <c r="W369" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="AA369">
         <v>0</v>
@@ -27384,10 +27384,10 @@
     </row>
     <row r="370" spans="1:34">
       <c r="A370">
-        <v>6486</v>
+        <v>6949</v>
       </c>
       <c r="B370" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C370" t="s">
         <v>60</v>
@@ -27399,49 +27399,46 @@
         <v>64</v>
       </c>
       <c r="F370" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G370">
-        <v>6759</v>
+        <v>1914</v>
       </c>
       <c r="H370">
-        <v>1788</v>
+        <v>1862</v>
       </c>
       <c r="I370" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J370" t="s">
         <v>154</v>
       </c>
       <c r="L370" s="1">
-        <v>46289</v>
+        <v>46286</v>
       </c>
       <c r="M370" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="N370" t="s">
         <v>224</v>
       </c>
       <c r="O370">
-        <v>16976177</v>
+        <v>18214883</v>
       </c>
       <c r="P370" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="Q370" t="s">
         <v>254</v>
       </c>
       <c r="S370">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="T370" t="s">
-        <v>262</v>
-      </c>
-      <c r="V370" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="W370" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="AA370">
         <v>0</v>
@@ -27450,21 +27447,21 @@
         <v>470</v>
       </c>
       <c r="AH370" t="s">
-        <v>478</v>
+        <v>463</v>
       </c>
     </row>
     <row r="371" spans="1:34">
       <c r="A371">
-        <v>6705</v>
+        <v>6486</v>
       </c>
       <c r="B371" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C371" t="s">
         <v>60</v>
       </c>
       <c r="D371" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E371" t="s">
         <v>64</v>
@@ -27482,7 +27479,7 @@
         <v>73</v>
       </c>
       <c r="J371" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L371" s="1">
         <v>46289</v>
@@ -27494,7 +27491,7 @@
         <v>224</v>
       </c>
       <c r="O371">
-        <v>17949019</v>
+        <v>16976177</v>
       </c>
       <c r="P371" t="s">
         <v>242</v>
@@ -27506,10 +27503,13 @@
         <v>-3</v>
       </c>
       <c r="T371" t="s">
-        <v>261</v>
+        <v>262</v>
+      </c>
+      <c r="V371" t="s">
+        <v>271</v>
       </c>
       <c r="W371" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AA371">
         <v>0</v>
@@ -27541,28 +27541,28 @@
         <v>66</v>
       </c>
       <c r="G372">
-        <v>1803</v>
+        <v>6759</v>
       </c>
       <c r="H372">
-        <v>0</v>
+        <v>1788</v>
       </c>
       <c r="I372" t="s">
         <v>73</v>
       </c>
       <c r="J372" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="L372" s="1">
-        <v>46293</v>
+        <v>46289</v>
       </c>
       <c r="M372" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="N372" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="O372">
-        <v>17948937</v>
+        <v>17949019</v>
       </c>
       <c r="P372" t="s">
         <v>242</v>
@@ -27571,7 +27571,7 @@
         <v>254</v>
       </c>
       <c r="S372">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="T372" t="s">
         <v>261</v>
@@ -27583,7 +27583,7 @@
         <v>0</v>
       </c>
       <c r="AG372" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AH372" t="s">
         <v>478</v>
@@ -27591,16 +27591,16 @@
     </row>
     <row r="373" spans="1:34">
       <c r="A373">
-        <v>6703</v>
+        <v>6705</v>
       </c>
       <c r="B373" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C373" t="s">
         <v>60</v>
       </c>
       <c r="D373" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E373" t="s">
         <v>64</v>
@@ -27609,7 +27609,7 @@
         <v>66</v>
       </c>
       <c r="G373">
-        <v>1811</v>
+        <v>1803</v>
       </c>
       <c r="H373">
         <v>0</v>
@@ -27618,19 +27618,19 @@
         <v>73</v>
       </c>
       <c r="J373" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="L373" s="1">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="M373" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="N373" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O373">
-        <v>17948816</v>
+        <v>17948937</v>
       </c>
       <c r="P373" t="s">
         <v>242</v>
@@ -27639,13 +27639,13 @@
         <v>254</v>
       </c>
       <c r="S373">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="T373" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="W373" t="s">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="AA373">
         <v>0</v>
@@ -27659,10 +27659,10 @@
     </row>
     <row r="374" spans="1:34">
       <c r="A374">
-        <v>6404</v>
+        <v>6703</v>
       </c>
       <c r="B374" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C374" t="s">
         <v>60</v>
@@ -27677,7 +27677,7 @@
         <v>66</v>
       </c>
       <c r="G374">
-        <v>1807</v>
+        <v>1811</v>
       </c>
       <c r="H374">
         <v>0</v>
@@ -27686,19 +27686,19 @@
         <v>73</v>
       </c>
       <c r="J374" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="L374" s="1">
-        <v>46287</v>
+        <v>46290</v>
       </c>
       <c r="M374" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="N374" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="O374">
-        <v>16962171</v>
+        <v>17948816</v>
       </c>
       <c r="P374" t="s">
         <v>242</v>
@@ -27707,13 +27707,13 @@
         <v>254</v>
       </c>
       <c r="S374">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="T374" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="W374" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="AA374">
         <v>0</v>
@@ -27727,10 +27727,10 @@
     </row>
     <row r="375" spans="1:34">
       <c r="A375">
-        <v>6703</v>
+        <v>6404</v>
       </c>
       <c r="B375" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C375" t="s">
         <v>60</v>
@@ -27766,7 +27766,7 @@
         <v>224</v>
       </c>
       <c r="O375">
-        <v>17948806</v>
+        <v>16962171</v>
       </c>
       <c r="P375" t="s">
         <v>242</v>
@@ -27778,7 +27778,7 @@
         <v>-1</v>
       </c>
       <c r="T375" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="W375" t="s">
         <v>374</v>
@@ -27795,16 +27795,16 @@
     </row>
     <row r="376" spans="1:34">
       <c r="A376">
-        <v>5417</v>
+        <v>6703</v>
       </c>
       <c r="B376" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C376" t="s">
         <v>60</v>
       </c>
       <c r="D376" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E376" t="s">
         <v>64</v>
@@ -27813,7 +27813,7 @@
         <v>66</v>
       </c>
       <c r="G376">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="H376">
         <v>0</v>
@@ -27822,7 +27822,7 @@
         <v>73</v>
       </c>
       <c r="J376" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L376" s="1">
         <v>46287</v>
@@ -27834,7 +27834,7 @@
         <v>224</v>
       </c>
       <c r="O376">
-        <v>17398965</v>
+        <v>17948806</v>
       </c>
       <c r="P376" t="s">
         <v>242</v>
@@ -27846,7 +27846,7 @@
         <v>-1</v>
       </c>
       <c r="T376" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="W376" t="s">
         <v>374</v>
@@ -27863,10 +27863,10 @@
     </row>
     <row r="377" spans="1:34">
       <c r="A377">
-        <v>6704</v>
+        <v>5417</v>
       </c>
       <c r="B377" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C377" t="s">
         <v>60</v>
@@ -27902,7 +27902,7 @@
         <v>224</v>
       </c>
       <c r="O377">
-        <v>18085209</v>
+        <v>17398965</v>
       </c>
       <c r="P377" t="s">
         <v>242</v>
@@ -27914,10 +27914,7 @@
         <v>-1</v>
       </c>
       <c r="T377" t="s">
-        <v>261</v>
-      </c>
-      <c r="V377" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="W377" t="s">
         <v>374</v>
@@ -27934,10 +27931,10 @@
     </row>
     <row r="378" spans="1:34">
       <c r="A378">
-        <v>6627</v>
+        <v>6704</v>
       </c>
       <c r="B378" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C378" t="s">
         <v>60</v>
@@ -27946,52 +27943,52 @@
         <v>61</v>
       </c>
       <c r="E378" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F378" t="s">
         <v>66</v>
       </c>
       <c r="G378">
-        <v>953</v>
+        <v>1808</v>
       </c>
       <c r="H378">
         <v>0</v>
       </c>
       <c r="I378" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J378" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="L378" s="1">
-        <v>46290</v>
+        <v>46287</v>
       </c>
       <c r="M378" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N378" t="s">
         <v>224</v>
       </c>
       <c r="O378">
-        <v>17042317</v>
+        <v>18085209</v>
       </c>
       <c r="P378" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q378" t="s">
         <v>254</v>
       </c>
       <c r="S378">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="T378" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="V378" t="s">
         <v>271</v>
       </c>
       <c r="W378" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="AA378">
         <v>0</v>
@@ -27999,13 +27996,16 @@
       <c r="AG378" t="s">
         <v>471</v>
       </c>
+      <c r="AH378" t="s">
+        <v>478</v>
+      </c>
     </row>
     <row r="379" spans="1:34">
       <c r="A379">
-        <v>5417</v>
+        <v>6627</v>
       </c>
       <c r="B379" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C379" t="s">
         <v>60</v>
@@ -28014,13 +28014,13 @@
         <v>61</v>
       </c>
       <c r="E379" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F379" t="s">
         <v>66</v>
       </c>
       <c r="G379">
-        <v>943</v>
+        <v>953</v>
       </c>
       <c r="H379">
         <v>0</v>
@@ -28032,16 +28032,16 @@
         <v>157</v>
       </c>
       <c r="L379" s="1">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="M379" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N379" t="s">
         <v>224</v>
       </c>
       <c r="O379">
-        <v>17398859</v>
+        <v>17042317</v>
       </c>
       <c r="P379" t="s">
         <v>243</v>
@@ -28050,27 +28050,30 @@
         <v>254</v>
       </c>
       <c r="S379">
-        <v>-9</v>
+        <v>-4</v>
       </c>
       <c r="T379" t="s">
-        <v>260</v>
+        <v>256</v>
+      </c>
+      <c r="V379" t="s">
+        <v>271</v>
       </c>
       <c r="W379" t="s">
-        <v>361</v>
+        <v>378</v>
       </c>
       <c r="AA379">
         <v>0</v>
       </c>
       <c r="AG379" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="380" spans="1:34">
       <c r="A380">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B380" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C380" t="s">
         <v>60</v>
@@ -28094,7 +28097,7 @@
         <v>74</v>
       </c>
       <c r="J380" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L380" s="1">
         <v>46295</v>
@@ -28106,7 +28109,7 @@
         <v>224</v>
       </c>
       <c r="O380">
-        <v>16975890</v>
+        <v>17398859</v>
       </c>
       <c r="P380" t="s">
         <v>243</v>
@@ -28118,13 +28121,10 @@
         <v>-9</v>
       </c>
       <c r="T380" t="s">
-        <v>262</v>
-      </c>
-      <c r="V380" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="W380" t="s">
-        <v>378</v>
+        <v>361</v>
       </c>
       <c r="AA380">
         <v>0</v>
@@ -28135,16 +28135,16 @@
     </row>
     <row r="381" spans="1:34">
       <c r="A381">
-        <v>6703</v>
+        <v>6486</v>
       </c>
       <c r="B381" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C381" t="s">
         <v>60</v>
       </c>
       <c r="D381" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E381" t="s">
         <v>64</v>
@@ -28162,7 +28162,7 @@
         <v>74</v>
       </c>
       <c r="J381" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L381" s="1">
         <v>46295</v>
@@ -28174,7 +28174,7 @@
         <v>224</v>
       </c>
       <c r="O381">
-        <v>17941122</v>
+        <v>16975890</v>
       </c>
       <c r="P381" t="s">
         <v>243</v>
@@ -28186,10 +28186,13 @@
         <v>-9</v>
       </c>
       <c r="T381" t="s">
-        <v>263</v>
+        <v>262</v>
+      </c>
+      <c r="V381" t="s">
+        <v>271</v>
       </c>
       <c r="W381" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AA381">
         <v>0</v>
@@ -28200,16 +28203,16 @@
     </row>
     <row r="382" spans="1:34">
       <c r="A382">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B382" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C382" t="s">
         <v>60</v>
       </c>
       <c r="D382" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E382" t="s">
         <v>64</v>
@@ -28227,7 +28230,7 @@
         <v>74</v>
       </c>
       <c r="J382" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L382" s="1">
         <v>46295</v>
@@ -28239,7 +28242,7 @@
         <v>224</v>
       </c>
       <c r="O382">
-        <v>17952314</v>
+        <v>17941122</v>
       </c>
       <c r="P382" t="s">
         <v>243</v>
@@ -28251,13 +28254,10 @@
         <v>-9</v>
       </c>
       <c r="T382" t="s">
-        <v>261</v>
-      </c>
-      <c r="V382" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="W382" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AA382">
         <v>0</v>
@@ -28268,16 +28268,16 @@
     </row>
     <row r="383" spans="1:34">
       <c r="A383">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B383" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C383" t="s">
         <v>60</v>
       </c>
       <c r="D383" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E383" t="s">
         <v>64</v>
@@ -28295,7 +28295,7 @@
         <v>74</v>
       </c>
       <c r="J383" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L383" s="1">
         <v>46295</v>
@@ -28307,7 +28307,7 @@
         <v>224</v>
       </c>
       <c r="O383">
-        <v>17952513</v>
+        <v>17952314</v>
       </c>
       <c r="P383" t="s">
         <v>243</v>
@@ -28321,8 +28321,11 @@
       <c r="T383" t="s">
         <v>261</v>
       </c>
+      <c r="V383" t="s">
+        <v>271</v>
+      </c>
       <c r="W383" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AA383">
         <v>0</v>
@@ -28333,22 +28336,22 @@
     </row>
     <row r="384" spans="1:34">
       <c r="A384">
-        <v>6949</v>
+        <v>6705</v>
       </c>
       <c r="B384" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C384" t="s">
         <v>60</v>
       </c>
       <c r="D384" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E384" t="s">
         <v>64</v>
       </c>
       <c r="F384" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G384">
         <v>943</v>
@@ -28360,7 +28363,7 @@
         <v>74</v>
       </c>
       <c r="J384" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L384" s="1">
         <v>46295</v>
@@ -28372,7 +28375,7 @@
         <v>224</v>
       </c>
       <c r="O384">
-        <v>18178126</v>
+        <v>17952513</v>
       </c>
       <c r="P384" t="s">
         <v>243</v>
@@ -28384,10 +28387,10 @@
         <v>-9</v>
       </c>
       <c r="T384" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="W384" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AA384">
         <v>0</v>
@@ -28398,16 +28401,16 @@
     </row>
     <row r="385" spans="1:34">
       <c r="A385">
-        <v>6962</v>
+        <v>6949</v>
       </c>
       <c r="B385" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C385" t="s">
         <v>60</v>
       </c>
       <c r="D385" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E385" t="s">
         <v>64</v>
@@ -28425,7 +28428,7 @@
         <v>74</v>
       </c>
       <c r="J385" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L385" s="1">
         <v>46295</v>
@@ -28437,7 +28440,7 @@
         <v>224</v>
       </c>
       <c r="O385">
-        <v>18188710</v>
+        <v>18178126</v>
       </c>
       <c r="P385" t="s">
         <v>243</v>
@@ -28449,10 +28452,10 @@
         <v>-9</v>
       </c>
       <c r="T385" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="W385" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AA385">
         <v>0</v>
@@ -28463,10 +28466,10 @@
     </row>
     <row r="386" spans="1:34">
       <c r="A386">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B386" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C386" t="s">
         <v>60</v>
@@ -28490,7 +28493,7 @@
         <v>74</v>
       </c>
       <c r="J386" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L386" s="1">
         <v>46295</v>
@@ -28502,7 +28505,7 @@
         <v>224</v>
       </c>
       <c r="O386">
-        <v>18188616</v>
+        <v>18188710</v>
       </c>
       <c r="P386" t="s">
         <v>243</v>
@@ -28517,7 +28520,7 @@
         <v>259</v>
       </c>
       <c r="W386" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AA386">
         <v>0</v>
@@ -28528,58 +28531,58 @@
     </row>
     <row r="387" spans="1:34">
       <c r="A387">
-        <v>5417</v>
+        <v>6963</v>
       </c>
       <c r="B387" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C387" t="s">
         <v>60</v>
       </c>
       <c r="D387" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E387" t="s">
         <v>64</v>
       </c>
       <c r="F387" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G387">
-        <v>7877</v>
+        <v>943</v>
       </c>
       <c r="H387">
         <v>0</v>
       </c>
       <c r="I387" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J387" t="s">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="L387" s="1">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="M387" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N387" t="s">
         <v>224</v>
       </c>
       <c r="O387">
-        <v>17399330</v>
+        <v>18188616</v>
       </c>
       <c r="P387" t="s">
-        <v>64</v>
+        <v>243</v>
       </c>
       <c r="Q387" t="s">
         <v>254</v>
       </c>
       <c r="S387">
-        <v>-4</v>
+        <v>-9</v>
       </c>
       <c r="T387" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="W387" t="s">
         <v>379</v>
@@ -28611,37 +28614,37 @@
         <v>66</v>
       </c>
       <c r="G388">
-        <v>11056</v>
+        <v>7877</v>
       </c>
       <c r="H388">
         <v>0</v>
       </c>
       <c r="I388" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J388" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="L388" s="1">
-        <v>46287</v>
+        <v>46290</v>
       </c>
       <c r="M388" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="N388" t="s">
         <v>224</v>
       </c>
       <c r="O388">
-        <v>18275526</v>
+        <v>17399330</v>
       </c>
       <c r="P388" t="s">
-        <v>249</v>
+        <v>64</v>
       </c>
       <c r="Q388" t="s">
         <v>254</v>
       </c>
       <c r="S388">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="T388" t="s">
         <v>260</v>
@@ -28658,22 +28661,22 @@
     </row>
     <row r="389" spans="1:34">
       <c r="A389">
-        <v>6962</v>
+        <v>5417</v>
       </c>
       <c r="B389" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C389" t="s">
         <v>60</v>
       </c>
       <c r="D389" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E389" t="s">
         <v>64</v>
       </c>
       <c r="F389" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G389">
         <v>11056</v>
@@ -28691,13 +28694,13 @@
         <v>46287</v>
       </c>
       <c r="M389" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="N389" t="s">
         <v>224</v>
       </c>
       <c r="O389">
-        <v>18274091</v>
+        <v>18275526</v>
       </c>
       <c r="P389" t="s">
         <v>249</v>
@@ -28709,7 +28712,7 @@
         <v>-1</v>
       </c>
       <c r="T389" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="W389" t="s">
         <v>381</v>
@@ -28723,81 +28726,75 @@
     </row>
     <row r="390" spans="1:34">
       <c r="A390">
-        <v>6628</v>
+        <v>6962</v>
       </c>
       <c r="B390" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C390" t="s">
         <v>60</v>
       </c>
       <c r="D390" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E390" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F390" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G390">
-        <v>1650</v>
+        <v>11056</v>
       </c>
       <c r="H390">
         <v>0</v>
       </c>
       <c r="I390" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="J390" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="L390" s="1">
-        <v>46293</v>
+        <v>46287</v>
+      </c>
+      <c r="M390" t="s">
+        <v>217</v>
       </c>
       <c r="N390" t="s">
         <v>224</v>
       </c>
       <c r="O390">
-        <v>16959974</v>
+        <v>18274091</v>
       </c>
       <c r="P390" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="Q390" t="s">
-        <v>252</v>
-      </c>
-      <c r="R390" s="1">
-        <v>46265.00248284722</v>
+        <v>254</v>
       </c>
       <c r="S390">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="T390" t="s">
-        <v>256</v>
-      </c>
-      <c r="V390" t="s">
-        <v>271</v>
+        <v>259</v>
+      </c>
+      <c r="W390" t="s">
+        <v>382</v>
       </c>
       <c r="AA390">
         <v>0</v>
-      </c>
-      <c r="AB390" t="s">
-        <v>464</v>
       </c>
       <c r="AG390" t="s">
         <v>470</v>
       </c>
-      <c r="AH390" t="s">
-        <v>474</v>
-      </c>
     </row>
     <row r="391" spans="1:34">
       <c r="A391">
-        <v>6945</v>
+        <v>6628</v>
       </c>
       <c r="B391" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C391" t="s">
         <v>60</v>
@@ -28806,10 +28803,10 @@
         <v>62</v>
       </c>
       <c r="E391" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F391" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G391">
         <v>1650</v>
@@ -28821,7 +28818,7 @@
         <v>69</v>
       </c>
       <c r="J391" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L391" s="1">
         <v>46293</v>
@@ -28830,22 +28827,25 @@
         <v>224</v>
       </c>
       <c r="O391">
-        <v>18163667</v>
+        <v>16959974</v>
       </c>
       <c r="P391" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q391" t="s">
         <v>252</v>
       </c>
       <c r="R391" s="1">
-        <v>46265.00255472222</v>
+        <v>46265.00248284722</v>
       </c>
       <c r="S391">
         <v>-7</v>
       </c>
       <c r="T391" t="s">
-        <v>257</v>
+        <v>256</v>
+      </c>
+      <c r="V391" t="s">
+        <v>271</v>
       </c>
       <c r="AA391">
         <v>0</v>
@@ -28862,25 +28862,25 @@
     </row>
     <row r="392" spans="1:34">
       <c r="A392">
-        <v>6548</v>
+        <v>6945</v>
       </c>
       <c r="B392" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C392" t="s">
         <v>60</v>
       </c>
       <c r="D392" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E392" t="s">
         <v>64</v>
       </c>
       <c r="F392" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G392">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="H392">
         <v>0</v>
@@ -28892,34 +28892,28 @@
         <v>159</v>
       </c>
       <c r="L392" s="1">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="N392" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O392">
-        <v>17967989</v>
+        <v>18163667</v>
       </c>
       <c r="P392" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q392" t="s">
         <v>252</v>
       </c>
       <c r="R392" s="1">
-        <v>46234.66180127315</v>
+        <v>46265.00255472222</v>
       </c>
       <c r="S392">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="T392" t="s">
-        <v>255</v>
-      </c>
-      <c r="V392" t="s">
-        <v>271</v>
-      </c>
-      <c r="W392" t="s">
-        <v>382</v>
+        <v>257</v>
       </c>
       <c r="AA392">
         <v>0</v>
@@ -28928,18 +28922,18 @@
         <v>464</v>
       </c>
       <c r="AG392" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AH392" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="393" spans="1:34">
       <c r="A393">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B393" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C393" t="s">
         <v>60</v>
@@ -28948,7 +28942,7 @@
         <v>61</v>
       </c>
       <c r="E393" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F393" t="s">
         <v>66</v>
@@ -28963,7 +28957,7 @@
         <v>69</v>
       </c>
       <c r="J393" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L393" s="1">
         <v>46290</v>
@@ -28972,22 +28966,22 @@
         <v>227</v>
       </c>
       <c r="O393">
-        <v>17042389</v>
+        <v>17967989</v>
       </c>
       <c r="P393" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Q393" t="s">
         <v>252</v>
       </c>
       <c r="R393" s="1">
-        <v>46245.76585582176</v>
+        <v>46234.66180127315</v>
       </c>
       <c r="S393">
         <v>-4</v>
       </c>
       <c r="T393" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="V393" t="s">
         <v>271</v>
@@ -29005,15 +28999,15 @@
         <v>471</v>
       </c>
       <c r="AH393" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="394" spans="1:34">
       <c r="A394">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B394" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C394" t="s">
         <v>60</v>
@@ -29022,69 +29016,72 @@
         <v>61</v>
       </c>
       <c r="E394" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F394" t="s">
         <v>66</v>
       </c>
       <c r="G394">
-        <v>1697</v>
+        <v>1652</v>
       </c>
       <c r="H394">
-        <v>1650</v>
+        <v>0</v>
       </c>
       <c r="I394" t="s">
         <v>69</v>
       </c>
       <c r="J394" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="L394" s="1">
-        <v>46286</v>
+        <v>46290</v>
       </c>
       <c r="N394" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="O394">
-        <v>17968001</v>
+        <v>17042389</v>
       </c>
       <c r="P394" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q394" t="s">
         <v>252</v>
       </c>
       <c r="R394" s="1">
-        <v>46282.62254486111</v>
+        <v>46245.76585582176</v>
       </c>
       <c r="S394">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="T394" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="V394" t="s">
         <v>271</v>
       </c>
+      <c r="W394" t="s">
+        <v>384</v>
+      </c>
       <c r="AA394">
         <v>0</v>
       </c>
       <c r="AB394" t="s">
-        <v>229</v>
+        <v>464</v>
       </c>
       <c r="AG394" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AH394" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="395" spans="1:34">
       <c r="A395">
-        <v>6949</v>
+        <v>6548</v>
       </c>
       <c r="B395" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C395" t="s">
         <v>60</v>
@@ -29096,7 +29093,7 @@
         <v>64</v>
       </c>
       <c r="F395" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G395">
         <v>1697</v>
@@ -29117,7 +29114,7 @@
         <v>224</v>
       </c>
       <c r="O395">
-        <v>18178280</v>
+        <v>17968001</v>
       </c>
       <c r="P395" t="s">
         <v>229</v>
@@ -29126,13 +29123,16 @@
         <v>252</v>
       </c>
       <c r="R395" s="1">
-        <v>46283.44840582176</v>
+        <v>46282.62254486111</v>
       </c>
       <c r="S395">
         <v>0</v>
       </c>
       <c r="T395" t="s">
-        <v>258</v>
+        <v>255</v>
+      </c>
+      <c r="V395" t="s">
+        <v>271</v>
       </c>
       <c r="AA395">
         <v>0</v>
@@ -29149,10 +29149,10 @@
     </row>
     <row r="396" spans="1:34">
       <c r="A396">
-        <v>6704</v>
+        <v>6949</v>
       </c>
       <c r="B396" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C396" t="s">
         <v>60</v>
@@ -29164,66 +29164,63 @@
         <v>64</v>
       </c>
       <c r="F396" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G396">
-        <v>7868</v>
+        <v>1697</v>
       </c>
       <c r="H396">
-        <v>0</v>
+        <v>1650</v>
       </c>
       <c r="I396" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J396" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="L396" s="1">
-        <v>46293</v>
+        <v>46286</v>
       </c>
       <c r="N396" t="s">
         <v>224</v>
       </c>
       <c r="O396">
-        <v>17955421</v>
+        <v>18178280</v>
       </c>
       <c r="P396" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="Q396" t="s">
         <v>252</v>
       </c>
       <c r="R396" s="1">
-        <v>46267.47365627315</v>
+        <v>46283.44840582176</v>
       </c>
       <c r="S396">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="T396" t="s">
-        <v>261</v>
-      </c>
-      <c r="V396" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="AA396">
         <v>0</v>
       </c>
       <c r="AB396" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="AG396" t="s">
         <v>470</v>
       </c>
       <c r="AH396" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="397" spans="1:34">
       <c r="A397">
-        <v>5417</v>
+        <v>6704</v>
       </c>
       <c r="B397" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C397" t="s">
         <v>60</v>
@@ -29238,7 +29235,7 @@
         <v>66</v>
       </c>
       <c r="G397">
-        <v>11276</v>
+        <v>7868</v>
       </c>
       <c r="H397">
         <v>0</v>
@@ -29247,51 +29244,54 @@
         <v>70</v>
       </c>
       <c r="J397" t="s">
-        <v>160</v>
+        <v>136</v>
       </c>
       <c r="L397" s="1">
-        <v>46283</v>
+        <v>46293</v>
       </c>
       <c r="N397" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="O397">
-        <v>17399423</v>
+        <v>17955421</v>
       </c>
       <c r="P397" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q397" t="s">
         <v>252</v>
       </c>
       <c r="R397" s="1">
-        <v>46266.47620831019</v>
+        <v>46267.47365627315</v>
       </c>
       <c r="S397">
-        <v>3</v>
+        <v>-7</v>
       </c>
       <c r="T397" t="s">
-        <v>260</v>
+        <v>261</v>
+      </c>
+      <c r="V397" t="s">
+        <v>271</v>
       </c>
       <c r="AA397">
         <v>0</v>
       </c>
       <c r="AB397" t="s">
-        <v>466</v>
+        <v>234</v>
       </c>
       <c r="AG397" t="s">
         <v>470</v>
       </c>
       <c r="AH397" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="398" spans="1:34">
       <c r="A398">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B398" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C398" t="s">
         <v>60</v>
@@ -29315,7 +29315,7 @@
         <v>70</v>
       </c>
       <c r="J398" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L398" s="1">
         <v>46283</v>
@@ -29324,31 +29324,28 @@
         <v>226</v>
       </c>
       <c r="O398">
-        <v>18152557</v>
+        <v>17399423</v>
       </c>
       <c r="P398" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="Q398" t="s">
         <v>252</v>
       </c>
       <c r="R398" s="1">
-        <v>46267.57586420139</v>
+        <v>46266.47620831019</v>
       </c>
       <c r="S398">
         <v>3</v>
       </c>
       <c r="T398" t="s">
-        <v>262</v>
-      </c>
-      <c r="V398" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="AA398">
         <v>0</v>
       </c>
       <c r="AB398" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AG398" t="s">
         <v>470</v>
@@ -29359,10 +29356,10 @@
     </row>
     <row r="399" spans="1:34">
       <c r="A399">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B399" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C399" t="s">
         <v>60</v>
@@ -29377,7 +29374,7 @@
         <v>66</v>
       </c>
       <c r="G399">
-        <v>1583</v>
+        <v>11276</v>
       </c>
       <c r="H399">
         <v>0</v>
@@ -29386,40 +29383,43 @@
         <v>70</v>
       </c>
       <c r="J399" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="L399" s="1">
-        <v>46290</v>
+        <v>46283</v>
       </c>
       <c r="N399" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O399">
-        <v>17398917</v>
+        <v>18152557</v>
       </c>
       <c r="P399" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="Q399" t="s">
         <v>252</v>
       </c>
       <c r="R399" s="1">
-        <v>46233.72355880787</v>
+        <v>46267.57586420139</v>
       </c>
       <c r="S399">
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="T399" t="s">
-        <v>260</v>
+        <v>262</v>
+      </c>
+      <c r="V399" t="s">
+        <v>271</v>
       </c>
       <c r="AA399">
         <v>0</v>
       </c>
       <c r="AB399" t="s">
-        <v>233</v>
+        <v>467</v>
       </c>
       <c r="AG399" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AH399" t="s">
         <v>475</v>
@@ -29427,10 +29427,10 @@
     </row>
     <row r="400" spans="1:34">
       <c r="A400">
-        <v>5617</v>
+        <v>5417</v>
       </c>
       <c r="B400" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C400" t="s">
         <v>60</v>
@@ -29454,7 +29454,7 @@
         <v>70</v>
       </c>
       <c r="J400" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L400" s="1">
         <v>46290</v>
@@ -29463,36 +29463,42 @@
         <v>227</v>
       </c>
       <c r="O400">
-        <v>17407553</v>
+        <v>17398917</v>
+      </c>
+      <c r="P400" t="s">
+        <v>233</v>
       </c>
       <c r="Q400" t="s">
         <v>252</v>
       </c>
       <c r="R400" s="1">
-        <v>46261.36669849537</v>
+        <v>46233.72355880787</v>
       </c>
       <c r="S400">
         <v>-4</v>
       </c>
       <c r="T400" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="AA400">
         <v>0</v>
       </c>
       <c r="AB400" t="s">
-        <v>460</v>
+        <v>233</v>
       </c>
       <c r="AG400" t="s">
         <v>471</v>
       </c>
+      <c r="AH400" t="s">
+        <v>475</v>
+      </c>
     </row>
     <row r="401" spans="1:34">
       <c r="A401">
-        <v>6224</v>
+        <v>5617</v>
       </c>
       <c r="B401" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C401" t="s">
         <v>60</v>
@@ -29504,7 +29510,7 @@
         <v>64</v>
       </c>
       <c r="F401" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G401">
         <v>1583</v>
@@ -29516,7 +29522,7 @@
         <v>70</v>
       </c>
       <c r="J401" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L401" s="1">
         <v>46290</v>
@@ -29525,13 +29531,13 @@
         <v>227</v>
       </c>
       <c r="O401">
-        <v>17688645</v>
+        <v>17407553</v>
       </c>
       <c r="Q401" t="s">
         <v>252</v>
       </c>
       <c r="R401" s="1">
-        <v>46266.44156952546</v>
+        <v>46261.36669849537</v>
       </c>
       <c r="S401">
         <v>-4</v>
@@ -29539,14 +29545,11 @@
       <c r="T401" t="s">
         <v>265</v>
       </c>
-      <c r="V401" t="s">
-        <v>271</v>
-      </c>
       <c r="AA401">
         <v>0</v>
       </c>
       <c r="AB401" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="AG401" t="s">
         <v>471</v>
@@ -29554,10 +29557,10 @@
     </row>
     <row r="402" spans="1:34">
       <c r="A402">
-        <v>6278</v>
+        <v>6224</v>
       </c>
       <c r="B402" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C402" t="s">
         <v>60</v>
@@ -29569,7 +29572,7 @@
         <v>64</v>
       </c>
       <c r="F402" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G402">
         <v>1583</v>
@@ -29581,7 +29584,7 @@
         <v>70</v>
       </c>
       <c r="J402" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L402" s="1">
         <v>46290</v>
@@ -29590,31 +29593,28 @@
         <v>227</v>
       </c>
       <c r="O402">
-        <v>18166312</v>
+        <v>17688645</v>
       </c>
       <c r="Q402" t="s">
         <v>252</v>
       </c>
       <c r="R402" s="1">
-        <v>46233.50562820602</v>
+        <v>46266.44156952546</v>
       </c>
       <c r="S402">
         <v>-4</v>
       </c>
       <c r="T402" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="V402" t="s">
         <v>271</v>
       </c>
-      <c r="W402" t="s">
-        <v>384</v>
-      </c>
       <c r="AA402">
         <v>0</v>
       </c>
       <c r="AB402" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="AG402" t="s">
         <v>471</v>
@@ -29622,10 +29622,10 @@
     </row>
     <row r="403" spans="1:34">
       <c r="A403">
-        <v>6486</v>
+        <v>6278</v>
       </c>
       <c r="B403" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C403" t="s">
         <v>60</v>
@@ -29649,7 +29649,7 @@
         <v>70</v>
       </c>
       <c r="J403" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L403" s="1">
         <v>46290</v>
@@ -29658,45 +29658,42 @@
         <v>227</v>
       </c>
       <c r="O403">
-        <v>18114208</v>
-      </c>
-      <c r="P403" t="s">
-        <v>245</v>
+        <v>18166312</v>
       </c>
       <c r="Q403" t="s">
         <v>252</v>
       </c>
       <c r="R403" s="1">
-        <v>46233.80164280093</v>
+        <v>46233.50562820602</v>
       </c>
       <c r="S403">
         <v>-4</v>
       </c>
       <c r="T403" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="V403" t="s">
         <v>271</v>
       </c>
+      <c r="W403" t="s">
+        <v>385</v>
+      </c>
       <c r="AA403">
         <v>0</v>
       </c>
       <c r="AB403" t="s">
-        <v>245</v>
+        <v>464</v>
       </c>
       <c r="AG403" t="s">
         <v>471</v>
       </c>
-      <c r="AH403" t="s">
-        <v>475</v>
-      </c>
     </row>
     <row r="404" spans="1:34">
       <c r="A404">
-        <v>6704</v>
+        <v>6486</v>
       </c>
       <c r="B404" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C404" t="s">
         <v>60</v>
@@ -29720,7 +29717,7 @@
         <v>70</v>
       </c>
       <c r="J404" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L404" s="1">
         <v>46290</v>
@@ -29729,22 +29726,22 @@
         <v>227</v>
       </c>
       <c r="O404">
-        <v>17955373</v>
+        <v>18114208</v>
       </c>
       <c r="P404" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="Q404" t="s">
         <v>252</v>
       </c>
       <c r="R404" s="1">
-        <v>46232.72913953703</v>
+        <v>46233.80164280093</v>
       </c>
       <c r="S404">
         <v>-4</v>
       </c>
       <c r="T404" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="V404" t="s">
         <v>271</v>
@@ -29753,21 +29750,21 @@
         <v>0</v>
       </c>
       <c r="AB404" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="AG404" t="s">
         <v>471</v>
       </c>
       <c r="AH404" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="405" spans="1:34">
       <c r="A405">
-        <v>5417</v>
+        <v>6704</v>
       </c>
       <c r="B405" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C405" t="s">
         <v>60</v>
@@ -29782,7 +29779,7 @@
         <v>66</v>
       </c>
       <c r="G405">
-        <v>7874</v>
+        <v>1583</v>
       </c>
       <c r="H405">
         <v>0</v>
@@ -29791,46 +29788,46 @@
         <v>70</v>
       </c>
       <c r="J405" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="L405" s="1">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="N405" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="O405">
-        <v>17399320</v>
+        <v>17955373</v>
       </c>
       <c r="P405" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q405" t="s">
         <v>252</v>
       </c>
       <c r="R405" s="1">
-        <v>46283.6781059838</v>
+        <v>46232.72913953703</v>
       </c>
       <c r="S405">
-        <v>-9</v>
+        <v>-4</v>
       </c>
       <c r="T405" t="s">
-        <v>260</v>
-      </c>
-      <c r="W405" t="s">
-        <v>385</v>
+        <v>261</v>
+      </c>
+      <c r="V405" t="s">
+        <v>271</v>
       </c>
       <c r="AA405">
         <v>0</v>
       </c>
       <c r="AB405" t="s">
-        <v>464</v>
+        <v>234</v>
       </c>
       <c r="AG405" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AH405" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="406" spans="1:34">
@@ -29853,25 +29850,25 @@
         <v>66</v>
       </c>
       <c r="G406">
-        <v>1628</v>
+        <v>7874</v>
       </c>
       <c r="H406">
-        <v>1581</v>
+        <v>0</v>
       </c>
       <c r="I406" t="s">
         <v>70</v>
       </c>
       <c r="J406" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="L406" s="1">
-        <v>46286</v>
+        <v>46295</v>
       </c>
       <c r="N406" t="s">
         <v>224</v>
       </c>
       <c r="O406">
-        <v>17398925</v>
+        <v>17399320</v>
       </c>
       <c r="P406" t="s">
         <v>233</v>
@@ -29880,19 +29877,22 @@
         <v>252</v>
       </c>
       <c r="R406" s="1">
-        <v>46280.37528408565</v>
+        <v>46283.6781059838</v>
       </c>
       <c r="S406">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="T406" t="s">
         <v>260</v>
       </c>
+      <c r="W406" t="s">
+        <v>386</v>
+      </c>
       <c r="AA406">
         <v>0</v>
       </c>
       <c r="AB406" t="s">
-        <v>233</v>
+        <v>464</v>
       </c>
       <c r="AG406" t="s">
         <v>470</v>
@@ -29903,16 +29903,16 @@
     </row>
     <row r="407" spans="1:34">
       <c r="A407">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B407" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C407" t="s">
         <v>60</v>
       </c>
       <c r="D407" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E407" t="s">
         <v>64</v>
@@ -29939,42 +29939,42 @@
         <v>224</v>
       </c>
       <c r="O407">
-        <v>16962141</v>
+        <v>17398925</v>
       </c>
       <c r="P407" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="Q407" t="s">
         <v>252</v>
       </c>
       <c r="R407" s="1">
-        <v>46266.37634084491</v>
+        <v>46280.37528408565</v>
       </c>
       <c r="S407">
         <v>0</v>
       </c>
       <c r="T407" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="AA407">
         <v>0</v>
       </c>
       <c r="AB407" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="AG407" t="s">
         <v>470</v>
       </c>
       <c r="AH407" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="408" spans="1:34">
       <c r="A408">
-        <v>6703</v>
+        <v>6404</v>
       </c>
       <c r="B408" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C408" t="s">
         <v>60</v>
@@ -30007,48 +30007,48 @@
         <v>224</v>
       </c>
       <c r="O408">
-        <v>17955176</v>
+        <v>16962141</v>
       </c>
       <c r="P408" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q408" t="s">
         <v>252</v>
       </c>
       <c r="R408" s="1">
-        <v>46282.42251184028</v>
+        <v>46266.37634084491</v>
       </c>
       <c r="S408">
         <v>0</v>
       </c>
       <c r="T408" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AA408">
         <v>0</v>
       </c>
       <c r="AB408" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG408" t="s">
         <v>470</v>
       </c>
       <c r="AH408" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="409" spans="1:34">
       <c r="A409">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B409" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C409" t="s">
         <v>60</v>
       </c>
       <c r="D409" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E409" t="s">
         <v>64</v>
@@ -30075,51 +30075,48 @@
         <v>224</v>
       </c>
       <c r="O409">
-        <v>17955384</v>
+        <v>17955176</v>
       </c>
       <c r="P409" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="Q409" t="s">
         <v>252</v>
       </c>
       <c r="R409" s="1">
-        <v>46267.47452163194</v>
+        <v>46282.42251184028</v>
       </c>
       <c r="S409">
         <v>0</v>
       </c>
       <c r="T409" t="s">
-        <v>261</v>
-      </c>
-      <c r="V409" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="AA409">
         <v>0</v>
       </c>
       <c r="AB409" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="AG409" t="s">
         <v>470</v>
       </c>
       <c r="AH409" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="410" spans="1:34">
       <c r="A410">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B410" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C410" t="s">
         <v>60</v>
       </c>
       <c r="D410" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E410" t="s">
         <v>64</v>
@@ -30146,7 +30143,7 @@
         <v>224</v>
       </c>
       <c r="O410">
-        <v>17955238</v>
+        <v>17955384</v>
       </c>
       <c r="P410" t="s">
         <v>234</v>
@@ -30155,7 +30152,7 @@
         <v>252</v>
       </c>
       <c r="R410" s="1">
-        <v>46267.4745221412</v>
+        <v>46267.47452163194</v>
       </c>
       <c r="S410">
         <v>0</v>
@@ -30163,6 +30160,9 @@
       <c r="T410" t="s">
         <v>261</v>
       </c>
+      <c r="V410" t="s">
+        <v>271</v>
+      </c>
       <c r="AA410">
         <v>0</v>
       </c>
@@ -30178,10 +30178,10 @@
     </row>
     <row r="411" spans="1:34">
       <c r="A411">
-        <v>6779</v>
+        <v>6705</v>
       </c>
       <c r="B411" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C411" t="s">
         <v>60</v>
@@ -30214,7 +30214,7 @@
         <v>224</v>
       </c>
       <c r="O411">
-        <v>18056729</v>
+        <v>17955238</v>
       </c>
       <c r="P411" t="s">
         <v>234</v>
@@ -30223,7 +30223,7 @@
         <v>252</v>
       </c>
       <c r="R411" s="1">
-        <v>46267.47452299768</v>
+        <v>46267.4745221412</v>
       </c>
       <c r="S411">
         <v>0</v>
@@ -30231,9 +30231,6 @@
       <c r="T411" t="s">
         <v>261</v>
       </c>
-      <c r="V411" t="s">
-        <v>271</v>
-      </c>
       <c r="AA411">
         <v>0</v>
       </c>
@@ -30249,90 +30246,87 @@
     </row>
     <row r="412" spans="1:34">
       <c r="A412">
-        <v>6627</v>
+        <v>6779</v>
       </c>
       <c r="B412" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C412" t="s">
         <v>60</v>
       </c>
       <c r="D412" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E412" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F412" t="s">
         <v>66</v>
       </c>
       <c r="G412">
-        <v>5885</v>
+        <v>1628</v>
       </c>
       <c r="H412">
-        <v>5784</v>
+        <v>1581</v>
       </c>
       <c r="I412" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J412" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="L412" s="1">
-        <v>46283</v>
-      </c>
-      <c r="M412" t="s">
-        <v>221</v>
+        <v>46286</v>
       </c>
       <c r="N412" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O412">
-        <v>18068566</v>
+        <v>18056729</v>
       </c>
       <c r="P412" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="Q412" t="s">
         <v>252</v>
       </c>
       <c r="R412" s="1">
-        <v>46281.63558861111</v>
+        <v>46267.47452299768</v>
       </c>
       <c r="S412">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T412" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="V412" t="s">
         <v>271</v>
       </c>
-      <c r="W412" t="s">
-        <v>386</v>
-      </c>
       <c r="AA412">
         <v>0</v>
       </c>
       <c r="AB412" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AG412" t="s">
-        <v>471</v>
+        <v>470</v>
+      </c>
+      <c r="AH412" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="413" spans="1:34">
       <c r="A413">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B413" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C413" t="s">
         <v>60</v>
       </c>
       <c r="D413" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E413" t="s">
         <v>65</v>
@@ -30350,7 +30344,7 @@
         <v>71</v>
       </c>
       <c r="J413" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L413" s="1">
         <v>46283</v>
@@ -30362,7 +30356,7 @@
         <v>225</v>
       </c>
       <c r="O413">
-        <v>18052485</v>
+        <v>18068566</v>
       </c>
       <c r="P413" t="s">
         <v>235</v>
@@ -30371,7 +30365,7 @@
         <v>252</v>
       </c>
       <c r="R413" s="1">
-        <v>46281.6358927662</v>
+        <v>46281.63558861111</v>
       </c>
       <c r="S413">
         <v>3</v>
@@ -30383,7 +30377,7 @@
         <v>271</v>
       </c>
       <c r="W413" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AA413">
         <v>0</v>
@@ -30397,10 +30391,10 @@
     </row>
     <row r="414" spans="1:34">
       <c r="A414">
-        <v>6945</v>
+        <v>6628</v>
       </c>
       <c r="B414" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C414" t="s">
         <v>60</v>
@@ -30409,10 +30403,10 @@
         <v>62</v>
       </c>
       <c r="E414" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F414" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G414">
         <v>5885</v>
@@ -30424,19 +30418,19 @@
         <v>71</v>
       </c>
       <c r="J414" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L414" s="1">
         <v>46283</v>
       </c>
       <c r="M414" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="N414" t="s">
         <v>225</v>
       </c>
       <c r="O414">
-        <v>18206577</v>
+        <v>18052485</v>
       </c>
       <c r="P414" t="s">
         <v>235</v>
@@ -30445,13 +30439,16 @@
         <v>252</v>
       </c>
       <c r="R414" s="1">
-        <v>46281.47564895833</v>
+        <v>46281.6358927662</v>
       </c>
       <c r="S414">
         <v>3</v>
       </c>
       <c r="T414" t="s">
-        <v>257</v>
+        <v>256</v>
+      </c>
+      <c r="V414" t="s">
+        <v>271</v>
       </c>
       <c r="W414" t="s">
         <v>387</v>
@@ -30460,7 +30457,7 @@
         <v>0</v>
       </c>
       <c r="AB414" t="s">
-        <v>456</v>
+        <v>236</v>
       </c>
       <c r="AG414" t="s">
         <v>471</v>
@@ -30468,28 +30465,28 @@
     </row>
     <row r="415" spans="1:34">
       <c r="A415">
-        <v>6703</v>
+        <v>6945</v>
       </c>
       <c r="B415" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C415" t="s">
         <v>60</v>
       </c>
       <c r="D415" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E415" t="s">
         <v>64</v>
       </c>
       <c r="F415" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G415">
-        <v>6395</v>
+        <v>5885</v>
       </c>
       <c r="H415">
-        <v>5792</v>
+        <v>5784</v>
       </c>
       <c r="I415" t="s">
         <v>71</v>
@@ -30500,11 +30497,14 @@
       <c r="L415" s="1">
         <v>46283</v>
       </c>
+      <c r="M415" t="s">
+        <v>222</v>
+      </c>
       <c r="N415" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O415">
-        <v>18105120</v>
+        <v>18206577</v>
       </c>
       <c r="P415" t="s">
         <v>235</v>
@@ -30513,36 +30513,39 @@
         <v>252</v>
       </c>
       <c r="R415" s="1">
-        <v>46268.58940019676</v>
+        <v>46281.47564895833</v>
       </c>
       <c r="S415">
         <v>3</v>
       </c>
       <c r="T415" t="s">
-        <v>263</v>
+        <v>257</v>
+      </c>
+      <c r="W415" t="s">
+        <v>388</v>
       </c>
       <c r="AA415">
         <v>0</v>
       </c>
       <c r="AB415" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AG415" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="416" spans="1:34">
       <c r="A416">
-        <v>6779</v>
+        <v>6703</v>
       </c>
       <c r="B416" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C416" t="s">
         <v>60</v>
       </c>
       <c r="D416" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E416" t="s">
         <v>64</v>
@@ -30551,7 +30554,7 @@
         <v>66</v>
       </c>
       <c r="G416">
-        <v>5882</v>
+        <v>6395</v>
       </c>
       <c r="H416">
         <v>5792</v>
@@ -30565,14 +30568,11 @@
       <c r="L416" s="1">
         <v>46283</v>
       </c>
-      <c r="M416" t="s">
-        <v>222</v>
-      </c>
       <c r="N416" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O416">
-        <v>18195621</v>
+        <v>18105120</v>
       </c>
       <c r="P416" t="s">
         <v>235</v>
@@ -30581,42 +30581,36 @@
         <v>252</v>
       </c>
       <c r="R416" s="1">
-        <v>46279.66710767361</v>
+        <v>46268.58940019676</v>
       </c>
       <c r="S416">
         <v>3</v>
       </c>
       <c r="T416" t="s">
-        <v>261</v>
-      </c>
-      <c r="V416" t="s">
-        <v>271</v>
-      </c>
-      <c r="W416" t="s">
-        <v>388</v>
+        <v>263</v>
       </c>
       <c r="AA416">
         <v>0</v>
       </c>
       <c r="AB416" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AG416" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="417" spans="1:33">
       <c r="A417">
-        <v>5417</v>
+        <v>6779</v>
       </c>
       <c r="B417" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C417" t="s">
         <v>60</v>
       </c>
       <c r="D417" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E417" t="s">
         <v>64</v>
@@ -30625,7 +30619,7 @@
         <v>66</v>
       </c>
       <c r="G417">
-        <v>5883</v>
+        <v>5882</v>
       </c>
       <c r="H417">
         <v>5792</v>
@@ -30634,16 +30628,19 @@
         <v>71</v>
       </c>
       <c r="J417" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="L417" s="1">
-        <v>46286</v>
+        <v>46283</v>
+      </c>
+      <c r="M417" t="s">
+        <v>222</v>
       </c>
       <c r="N417" t="s">
         <v>225</v>
       </c>
       <c r="O417">
-        <v>17399067</v>
+        <v>18195621</v>
       </c>
       <c r="P417" t="s">
         <v>235</v>
@@ -30652,30 +30649,36 @@
         <v>252</v>
       </c>
       <c r="R417" s="1">
-        <v>46282.47420876157</v>
+        <v>46279.66710767361</v>
       </c>
       <c r="S417">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T417" t="s">
-        <v>260</v>
+        <v>261</v>
+      </c>
+      <c r="V417" t="s">
+        <v>271</v>
+      </c>
+      <c r="W417" t="s">
+        <v>389</v>
       </c>
       <c r="AA417">
         <v>0</v>
       </c>
       <c r="AB417" t="s">
-        <v>247</v>
+        <v>461</v>
       </c>
       <c r="AG417" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="418" spans="1:33">
       <c r="A418">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B418" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C418" t="s">
         <v>60</v>
@@ -30704,14 +30707,11 @@
       <c r="L418" s="1">
         <v>46286</v>
       </c>
-      <c r="M418" t="s">
-        <v>223</v>
-      </c>
       <c r="N418" t="s">
         <v>225</v>
       </c>
       <c r="O418">
-        <v>16976067</v>
+        <v>17399067</v>
       </c>
       <c r="P418" t="s">
         <v>235</v>
@@ -30720,25 +30720,19 @@
         <v>252</v>
       </c>
       <c r="R418" s="1">
-        <v>46281.68877074074</v>
+        <v>46282.47420876157</v>
       </c>
       <c r="S418">
         <v>0</v>
       </c>
       <c r="T418" t="s">
-        <v>262</v>
-      </c>
-      <c r="V418" t="s">
-        <v>271</v>
-      </c>
-      <c r="W418" t="s">
-        <v>389</v>
+        <v>260</v>
       </c>
       <c r="AA418">
         <v>0</v>
       </c>
       <c r="AB418" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="AG418" t="s">
         <v>470</v>
@@ -30746,10 +30740,10 @@
     </row>
     <row r="419" spans="1:33">
       <c r="A419">
-        <v>6548</v>
+        <v>6486</v>
       </c>
       <c r="B419" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C419" t="s">
         <v>60</v>
@@ -30779,13 +30773,13 @@
         <v>46286</v>
       </c>
       <c r="M419" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="N419" t="s">
         <v>225</v>
       </c>
       <c r="O419">
-        <v>17222629</v>
+        <v>16976067</v>
       </c>
       <c r="P419" t="s">
         <v>235</v>
@@ -30794,13 +30788,13 @@
         <v>252</v>
       </c>
       <c r="R419" s="1">
-        <v>46280.57958537037</v>
+        <v>46281.68877074074</v>
       </c>
       <c r="S419">
         <v>0</v>
       </c>
       <c r="T419" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="V419" t="s">
         <v>271</v>
@@ -30812,7 +30806,7 @@
         <v>0</v>
       </c>
       <c r="AB419" t="s">
-        <v>457</v>
+        <v>236</v>
       </c>
       <c r="AG419" t="s">
         <v>470</v>
@@ -30820,10 +30814,10 @@
     </row>
     <row r="420" spans="1:33">
       <c r="A420">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B420" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C420" t="s">
         <v>60</v>
@@ -30832,7 +30826,7 @@
         <v>61</v>
       </c>
       <c r="E420" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F420" t="s">
         <v>66</v>
@@ -30853,13 +30847,13 @@
         <v>46286</v>
       </c>
       <c r="M420" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="N420" t="s">
         <v>225</v>
       </c>
       <c r="O420">
-        <v>18068544</v>
+        <v>17222629</v>
       </c>
       <c r="P420" t="s">
         <v>235</v>
@@ -30868,25 +30862,25 @@
         <v>252</v>
       </c>
       <c r="R420" s="1">
-        <v>46281.63570936343</v>
+        <v>46280.57958537037</v>
       </c>
       <c r="S420">
         <v>0</v>
       </c>
       <c r="T420" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="V420" t="s">
         <v>271</v>
       </c>
       <c r="W420" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AA420">
         <v>0</v>
       </c>
       <c r="AB420" t="s">
-        <v>236</v>
+        <v>457</v>
       </c>
       <c r="AG420" t="s">
         <v>470</v>
@@ -30894,16 +30888,16 @@
     </row>
     <row r="421" spans="1:33">
       <c r="A421">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B421" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C421" t="s">
         <v>60</v>
       </c>
       <c r="D421" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E421" t="s">
         <v>65</v>
@@ -30933,7 +30927,7 @@
         <v>225</v>
       </c>
       <c r="O421">
-        <v>18052463</v>
+        <v>18068544</v>
       </c>
       <c r="P421" t="s">
         <v>235</v>
@@ -30942,7 +30936,7 @@
         <v>252</v>
       </c>
       <c r="R421" s="1">
-        <v>46281.63595871528</v>
+        <v>46281.63570936343</v>
       </c>
       <c r="S421">
         <v>0</v>
@@ -30954,7 +30948,7 @@
         <v>271</v>
       </c>
       <c r="W421" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AA421">
         <v>0</v>
@@ -30968,19 +30962,19 @@
     </row>
     <row r="422" spans="1:33">
       <c r="A422">
-        <v>6703</v>
+        <v>6628</v>
       </c>
       <c r="B422" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C422" t="s">
         <v>60</v>
       </c>
       <c r="D422" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E422" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F422" t="s">
         <v>66</v>
@@ -31000,11 +30994,14 @@
       <c r="L422" s="1">
         <v>46286</v>
       </c>
+      <c r="M422" t="s">
+        <v>223</v>
+      </c>
       <c r="N422" t="s">
         <v>225</v>
       </c>
       <c r="O422">
-        <v>18077112</v>
+        <v>18052463</v>
       </c>
       <c r="P422" t="s">
         <v>235</v>
@@ -31013,19 +31010,25 @@
         <v>252</v>
       </c>
       <c r="R422" s="1">
-        <v>46279.62681744213</v>
+        <v>46281.63595871528</v>
       </c>
       <c r="S422">
         <v>0</v>
       </c>
       <c r="T422" t="s">
-        <v>263</v>
+        <v>256</v>
+      </c>
+      <c r="V422" t="s">
+        <v>271</v>
+      </c>
+      <c r="W422" t="s">
+        <v>390</v>
       </c>
       <c r="AA422">
         <v>0</v>
       </c>
       <c r="AB422" t="s">
-        <v>458</v>
+        <v>236</v>
       </c>
       <c r="AG422" t="s">
         <v>470</v>
@@ -31033,16 +31036,16 @@
     </row>
     <row r="423" spans="1:33">
       <c r="A423">
-        <v>6779</v>
+        <v>6703</v>
       </c>
       <c r="B423" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C423" t="s">
         <v>60</v>
       </c>
       <c r="D423" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E423" t="s">
         <v>64</v>
@@ -31069,7 +31072,7 @@
         <v>225</v>
       </c>
       <c r="O423">
-        <v>18090189</v>
+        <v>18077112</v>
       </c>
       <c r="P423" t="s">
         <v>235</v>
@@ -31078,22 +31081,19 @@
         <v>252</v>
       </c>
       <c r="R423" s="1">
-        <v>46279.66707821759</v>
+        <v>46279.62681744213</v>
       </c>
       <c r="S423">
         <v>0</v>
       </c>
       <c r="T423" t="s">
-        <v>261</v>
-      </c>
-      <c r="V423" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="AA423">
         <v>0</v>
       </c>
       <c r="AB423" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AG423" t="s">
         <v>470</v>
@@ -31101,16 +31101,16 @@
     </row>
     <row r="424" spans="1:33">
       <c r="A424">
-        <v>5417</v>
+        <v>6779</v>
       </c>
       <c r="B424" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C424" t="s">
         <v>60</v>
       </c>
       <c r="D424" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E424" t="s">
         <v>64</v>
@@ -31119,7 +31119,7 @@
         <v>66</v>
       </c>
       <c r="G424">
-        <v>5884</v>
+        <v>5883</v>
       </c>
       <c r="H424">
         <v>5792</v>
@@ -31128,7 +31128,7 @@
         <v>71</v>
       </c>
       <c r="J424" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L424" s="1">
         <v>46286</v>
@@ -31137,7 +31137,7 @@
         <v>225</v>
       </c>
       <c r="O424">
-        <v>17399077</v>
+        <v>18090189</v>
       </c>
       <c r="P424" t="s">
         <v>235</v>
@@ -31146,19 +31146,22 @@
         <v>252</v>
       </c>
       <c r="R424" s="1">
-        <v>46282.47437324074</v>
+        <v>46279.66707821759</v>
       </c>
       <c r="S424">
         <v>0</v>
       </c>
       <c r="T424" t="s">
-        <v>260</v>
+        <v>261</v>
+      </c>
+      <c r="V424" t="s">
+        <v>271</v>
       </c>
       <c r="AA424">
         <v>0</v>
       </c>
       <c r="AB424" t="s">
-        <v>247</v>
+        <v>461</v>
       </c>
       <c r="AG424" t="s">
         <v>470</v>
@@ -31166,10 +31169,10 @@
     </row>
     <row r="425" spans="1:33">
       <c r="A425">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B425" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C425" t="s">
         <v>60</v>
@@ -31198,14 +31201,11 @@
       <c r="L425" s="1">
         <v>46286</v>
       </c>
-      <c r="M425" t="s">
-        <v>223</v>
-      </c>
       <c r="N425" t="s">
         <v>225</v>
       </c>
       <c r="O425">
-        <v>16976077</v>
+        <v>17399077</v>
       </c>
       <c r="P425" t="s">
         <v>235</v>
@@ -31214,25 +31214,19 @@
         <v>252</v>
       </c>
       <c r="R425" s="1">
-        <v>46281.68880230324</v>
+        <v>46282.47437324074</v>
       </c>
       <c r="S425">
         <v>0</v>
       </c>
       <c r="T425" t="s">
-        <v>262</v>
-      </c>
-      <c r="V425" t="s">
-        <v>271</v>
-      </c>
-      <c r="W425" t="s">
-        <v>389</v>
+        <v>260</v>
       </c>
       <c r="AA425">
         <v>0</v>
       </c>
       <c r="AB425" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="AG425" t="s">
         <v>470</v>
@@ -31240,10 +31234,10 @@
     </row>
     <row r="426" spans="1:33">
       <c r="A426">
-        <v>6548</v>
+        <v>6486</v>
       </c>
       <c r="B426" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C426" t="s">
         <v>60</v>
@@ -31273,13 +31267,13 @@
         <v>46286</v>
       </c>
       <c r="M426" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="N426" t="s">
         <v>225</v>
       </c>
       <c r="O426">
-        <v>17222647</v>
+        <v>16976077</v>
       </c>
       <c r="P426" t="s">
         <v>235</v>
@@ -31288,25 +31282,25 @@
         <v>252</v>
       </c>
       <c r="R426" s="1">
-        <v>46280.57972293982</v>
+        <v>46281.68880230324</v>
       </c>
       <c r="S426">
         <v>0</v>
       </c>
       <c r="T426" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="V426" t="s">
         <v>271</v>
       </c>
       <c r="W426" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AA426">
         <v>0</v>
       </c>
       <c r="AB426" t="s">
-        <v>457</v>
+        <v>236</v>
       </c>
       <c r="AG426" t="s">
         <v>470</v>
@@ -31314,10 +31308,10 @@
     </row>
     <row r="427" spans="1:33">
       <c r="A427">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B427" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C427" t="s">
         <v>60</v>
@@ -31326,7 +31320,7 @@
         <v>61</v>
       </c>
       <c r="E427" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F427" t="s">
         <v>66</v>
@@ -31347,13 +31341,13 @@
         <v>46286</v>
       </c>
       <c r="M427" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="N427" t="s">
         <v>225</v>
       </c>
       <c r="O427">
-        <v>18068555</v>
+        <v>17222647</v>
       </c>
       <c r="P427" t="s">
         <v>235</v>
@@ -31362,25 +31356,25 @@
         <v>252</v>
       </c>
       <c r="R427" s="1">
-        <v>46281.63575075231</v>
+        <v>46280.57972293982</v>
       </c>
       <c r="S427">
         <v>0</v>
       </c>
       <c r="T427" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="V427" t="s">
         <v>271</v>
       </c>
       <c r="W427" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="AA427">
         <v>0</v>
       </c>
       <c r="AB427" t="s">
-        <v>236</v>
+        <v>457</v>
       </c>
       <c r="AG427" t="s">
         <v>470</v>
@@ -31388,16 +31382,16 @@
     </row>
     <row r="428" spans="1:33">
       <c r="A428">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B428" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C428" t="s">
         <v>60</v>
       </c>
       <c r="D428" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E428" t="s">
         <v>65</v>
@@ -31427,7 +31421,7 @@
         <v>225</v>
       </c>
       <c r="O428">
-        <v>18052474</v>
+        <v>18068555</v>
       </c>
       <c r="P428" t="s">
         <v>235</v>
@@ -31436,7 +31430,7 @@
         <v>252</v>
       </c>
       <c r="R428" s="1">
-        <v>46281.63599785879</v>
+        <v>46281.63575075231</v>
       </c>
       <c r="S428">
         <v>0</v>
@@ -31448,7 +31442,7 @@
         <v>271</v>
       </c>
       <c r="W428" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AA428">
         <v>0</v>
@@ -31462,19 +31456,19 @@
     </row>
     <row r="429" spans="1:33">
       <c r="A429">
-        <v>6703</v>
+        <v>6628</v>
       </c>
       <c r="B429" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C429" t="s">
         <v>60</v>
       </c>
       <c r="D429" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E429" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F429" t="s">
         <v>66</v>
@@ -31494,11 +31488,14 @@
       <c r="L429" s="1">
         <v>46286</v>
       </c>
+      <c r="M429" t="s">
+        <v>223</v>
+      </c>
       <c r="N429" t="s">
         <v>225</v>
       </c>
       <c r="O429">
-        <v>18077122</v>
+        <v>18052474</v>
       </c>
       <c r="P429" t="s">
         <v>235</v>
@@ -31507,19 +31504,25 @@
         <v>252</v>
       </c>
       <c r="R429" s="1">
-        <v>46279.6268503125</v>
+        <v>46281.63599785879</v>
       </c>
       <c r="S429">
         <v>0</v>
       </c>
       <c r="T429" t="s">
-        <v>263</v>
+        <v>256</v>
+      </c>
+      <c r="V429" t="s">
+        <v>271</v>
+      </c>
+      <c r="W429" t="s">
+        <v>390</v>
       </c>
       <c r="AA429">
         <v>0</v>
       </c>
       <c r="AB429" t="s">
-        <v>458</v>
+        <v>236</v>
       </c>
       <c r="AG429" t="s">
         <v>470</v>
@@ -31527,16 +31530,16 @@
     </row>
     <row r="430" spans="1:33">
       <c r="A430">
-        <v>6779</v>
+        <v>6703</v>
       </c>
       <c r="B430" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C430" t="s">
         <v>60</v>
       </c>
       <c r="D430" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E430" t="s">
         <v>64</v>
@@ -31563,7 +31566,7 @@
         <v>225</v>
       </c>
       <c r="O430">
-        <v>18090199</v>
+        <v>18077122</v>
       </c>
       <c r="P430" t="s">
         <v>235</v>
@@ -31572,22 +31575,19 @@
         <v>252</v>
       </c>
       <c r="R430" s="1">
-        <v>46279.66698128472</v>
+        <v>46279.6268503125</v>
       </c>
       <c r="S430">
         <v>0</v>
       </c>
       <c r="T430" t="s">
-        <v>261</v>
-      </c>
-      <c r="V430" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="AA430">
         <v>0</v>
       </c>
       <c r="AB430" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AG430" t="s">
         <v>470</v>
@@ -31595,16 +31595,16 @@
     </row>
     <row r="431" spans="1:33">
       <c r="A431">
-        <v>5417</v>
+        <v>6779</v>
       </c>
       <c r="B431" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C431" t="s">
         <v>60</v>
       </c>
       <c r="D431" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E431" t="s">
         <v>64</v>
@@ -31613,25 +31613,25 @@
         <v>66</v>
       </c>
       <c r="G431">
-        <v>7012</v>
+        <v>5884</v>
       </c>
       <c r="H431">
-        <v>0</v>
+        <v>5792</v>
       </c>
       <c r="I431" t="s">
         <v>71</v>
       </c>
       <c r="J431" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="L431" s="1">
-        <v>46281</v>
+        <v>46286</v>
       </c>
       <c r="N431" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O431">
-        <v>18257773</v>
+        <v>18090199</v>
       </c>
       <c r="P431" t="s">
         <v>235</v>
@@ -31640,22 +31640,22 @@
         <v>252</v>
       </c>
       <c r="R431" s="1">
-        <v>46279.66929922454</v>
+        <v>46279.66698128472</v>
       </c>
       <c r="S431">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T431" t="s">
-        <v>260</v>
-      </c>
-      <c r="W431" t="s">
-        <v>392</v>
+        <v>261</v>
+      </c>
+      <c r="V431" t="s">
+        <v>271</v>
       </c>
       <c r="AA431">
         <v>0</v>
       </c>
       <c r="AB431" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="AG431" t="s">
         <v>470</v>
@@ -31663,16 +31663,16 @@
     </row>
     <row r="432" spans="1:33">
       <c r="A432">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B432" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C432" t="s">
         <v>60</v>
       </c>
       <c r="D432" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E432" t="s">
         <v>64</v>
@@ -31690,7 +31690,7 @@
         <v>71</v>
       </c>
       <c r="J432" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L432" s="1">
         <v>46281</v>
@@ -31699,7 +31699,7 @@
         <v>224</v>
       </c>
       <c r="O432">
-        <v>18258536</v>
+        <v>18257773</v>
       </c>
       <c r="P432" t="s">
         <v>235</v>
@@ -31708,13 +31708,13 @@
         <v>252</v>
       </c>
       <c r="R432" s="1">
-        <v>46280.61353684028</v>
+        <v>46279.66929922454</v>
       </c>
       <c r="S432">
         <v>5</v>
       </c>
       <c r="T432" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="W432" t="s">
         <v>393</v>
@@ -31731,16 +31731,16 @@
     </row>
     <row r="433" spans="1:33">
       <c r="A433">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B433" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C433" t="s">
         <v>60</v>
       </c>
       <c r="D433" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E433" t="s">
         <v>64</v>
@@ -31758,7 +31758,7 @@
         <v>71</v>
       </c>
       <c r="J433" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L433" s="1">
         <v>46281</v>
@@ -31767,7 +31767,7 @@
         <v>224</v>
       </c>
       <c r="O433">
-        <v>18254964</v>
+        <v>18258536</v>
       </c>
       <c r="P433" t="s">
         <v>235</v>
@@ -31776,16 +31776,13 @@
         <v>252</v>
       </c>
       <c r="R433" s="1">
-        <v>46280.61353920139</v>
+        <v>46280.61353684028</v>
       </c>
       <c r="S433">
         <v>5</v>
       </c>
       <c r="T433" t="s">
-        <v>262</v>
-      </c>
-      <c r="V433" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="W433" t="s">
         <v>394</v>
@@ -31802,10 +31799,10 @@
     </row>
     <row r="434" spans="1:33">
       <c r="A434">
-        <v>6548</v>
+        <v>6486</v>
       </c>
       <c r="B434" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C434" t="s">
         <v>60</v>
@@ -31829,7 +31826,7 @@
         <v>71</v>
       </c>
       <c r="J434" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L434" s="1">
         <v>46281</v>
@@ -31838,7 +31835,7 @@
         <v>224</v>
       </c>
       <c r="O434">
-        <v>18255116</v>
+        <v>18254964</v>
       </c>
       <c r="P434" t="s">
         <v>235</v>
@@ -31847,13 +31844,13 @@
         <v>252</v>
       </c>
       <c r="R434" s="1">
-        <v>46279.63250563657</v>
+        <v>46280.61353920139</v>
       </c>
       <c r="S434">
         <v>5</v>
       </c>
       <c r="T434" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="V434" t="s">
         <v>271</v>
@@ -31873,10 +31870,10 @@
     </row>
     <row r="435" spans="1:33">
       <c r="A435">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B435" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C435" t="s">
         <v>60</v>
@@ -31885,7 +31882,7 @@
         <v>61</v>
       </c>
       <c r="E435" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F435" t="s">
         <v>66</v>
@@ -31900,7 +31897,7 @@
         <v>71</v>
       </c>
       <c r="J435" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L435" s="1">
         <v>46281</v>
@@ -31909,7 +31906,7 @@
         <v>224</v>
       </c>
       <c r="O435">
-        <v>18257668</v>
+        <v>18255116</v>
       </c>
       <c r="P435" t="s">
         <v>235</v>
@@ -31918,19 +31915,19 @@
         <v>252</v>
       </c>
       <c r="R435" s="1">
-        <v>46280.61354019676</v>
+        <v>46279.63250563657</v>
       </c>
       <c r="S435">
         <v>5</v>
       </c>
       <c r="T435" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="V435" t="s">
         <v>271</v>
       </c>
       <c r="W435" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AA435">
         <v>0</v>
@@ -31944,16 +31941,16 @@
     </row>
     <row r="436" spans="1:33">
       <c r="A436">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B436" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C436" t="s">
         <v>60</v>
       </c>
       <c r="D436" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E436" t="s">
         <v>65</v>
@@ -31971,7 +31968,7 @@
         <v>71</v>
       </c>
       <c r="J436" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L436" s="1">
         <v>46281</v>
@@ -31980,7 +31977,7 @@
         <v>224</v>
       </c>
       <c r="O436">
-        <v>18256366</v>
+        <v>18257668</v>
       </c>
       <c r="P436" t="s">
         <v>235</v>
@@ -31989,7 +31986,7 @@
         <v>252</v>
       </c>
       <c r="R436" s="1">
-        <v>46280.6135403125</v>
+        <v>46280.61354019676</v>
       </c>
       <c r="S436">
         <v>5</v>
@@ -32001,7 +31998,7 @@
         <v>271</v>
       </c>
       <c r="W436" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AA436">
         <v>0</v>
@@ -32015,19 +32012,19 @@
     </row>
     <row r="437" spans="1:33">
       <c r="A437">
-        <v>6703</v>
+        <v>6628</v>
       </c>
       <c r="B437" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C437" t="s">
         <v>60</v>
       </c>
       <c r="D437" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E437" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F437" t="s">
         <v>66</v>
@@ -32042,19 +32039,16 @@
         <v>71</v>
       </c>
       <c r="J437" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L437" s="1">
         <v>46281</v>
       </c>
-      <c r="M437" t="s">
-        <v>221</v>
-      </c>
       <c r="N437" t="s">
         <v>224</v>
       </c>
       <c r="O437">
-        <v>18256433</v>
+        <v>18256366</v>
       </c>
       <c r="P437" t="s">
         <v>235</v>
@@ -32063,22 +32057,25 @@
         <v>252</v>
       </c>
       <c r="R437" s="1">
-        <v>46281.71218414352</v>
+        <v>46280.6135403125</v>
       </c>
       <c r="S437">
         <v>5</v>
       </c>
       <c r="T437" t="s">
-        <v>263</v>
+        <v>256</v>
+      </c>
+      <c r="V437" t="s">
+        <v>271</v>
       </c>
       <c r="W437" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AA437">
         <v>0</v>
       </c>
       <c r="AB437" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="AG437" t="s">
         <v>470</v>
@@ -32086,16 +32083,16 @@
     </row>
     <row r="438" spans="1:33">
       <c r="A438">
-        <v>6779</v>
+        <v>6703</v>
       </c>
       <c r="B438" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C438" t="s">
         <v>60</v>
       </c>
       <c r="D438" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E438" t="s">
         <v>64</v>
@@ -32113,16 +32110,19 @@
         <v>71</v>
       </c>
       <c r="J438" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L438" s="1">
         <v>46281</v>
       </c>
+      <c r="M438" t="s">
+        <v>221</v>
+      </c>
       <c r="N438" t="s">
         <v>224</v>
       </c>
       <c r="O438">
-        <v>18255012</v>
+        <v>18256433</v>
       </c>
       <c r="P438" t="s">
         <v>235</v>
@@ -32131,16 +32131,13 @@
         <v>252</v>
       </c>
       <c r="R438" s="1">
-        <v>46281.41576883102</v>
+        <v>46281.71218414352</v>
       </c>
       <c r="S438">
         <v>5</v>
       </c>
       <c r="T438" t="s">
-        <v>261</v>
-      </c>
-      <c r="V438" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="W438" t="s">
         <v>397</v>
@@ -32149,7 +32146,7 @@
         <v>0</v>
       </c>
       <c r="AB438" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="AG438" t="s">
         <v>470</v>
@@ -32157,10 +32154,10 @@
     </row>
     <row r="439" spans="1:33">
       <c r="A439">
-        <v>6945</v>
+        <v>6779</v>
       </c>
       <c r="B439" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C439" t="s">
         <v>60</v>
@@ -32172,7 +32169,7 @@
         <v>64</v>
       </c>
       <c r="F439" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G439">
         <v>7012</v>
@@ -32184,7 +32181,7 @@
         <v>71</v>
       </c>
       <c r="J439" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L439" s="1">
         <v>46281</v>
@@ -32193,7 +32190,7 @@
         <v>224</v>
       </c>
       <c r="O439">
-        <v>18254903</v>
+        <v>18255012</v>
       </c>
       <c r="P439" t="s">
         <v>235</v>
@@ -32202,13 +32199,16 @@
         <v>252</v>
       </c>
       <c r="R439" s="1">
-        <v>46280.43132989584</v>
+        <v>46281.41576883102</v>
       </c>
       <c r="S439">
         <v>5</v>
       </c>
       <c r="T439" t="s">
-        <v>257</v>
+        <v>261</v>
+      </c>
+      <c r="V439" t="s">
+        <v>271</v>
       </c>
       <c r="W439" t="s">
         <v>398</v>
@@ -32225,16 +32225,16 @@
     </row>
     <row r="440" spans="1:33">
       <c r="A440">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B440" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C440" t="s">
         <v>60</v>
       </c>
       <c r="D440" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E440" t="s">
         <v>64</v>
@@ -32252,7 +32252,7 @@
         <v>71</v>
       </c>
       <c r="J440" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L440" s="1">
         <v>46281</v>
@@ -32261,7 +32261,7 @@
         <v>224</v>
       </c>
       <c r="O440">
-        <v>18258489</v>
+        <v>18254903</v>
       </c>
       <c r="P440" t="s">
         <v>235</v>
@@ -32270,13 +32270,13 @@
         <v>252</v>
       </c>
       <c r="R440" s="1">
-        <v>46280.61367623843</v>
+        <v>46280.43132989584</v>
       </c>
       <c r="S440">
         <v>5</v>
       </c>
       <c r="T440" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="W440" t="s">
         <v>399</v>
@@ -32293,10 +32293,10 @@
     </row>
     <row r="441" spans="1:33">
       <c r="A441">
-        <v>6486</v>
+        <v>6949</v>
       </c>
       <c r="B441" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C441" t="s">
         <v>60</v>
@@ -32308,31 +32308,28 @@
         <v>64</v>
       </c>
       <c r="F441" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G441">
-        <v>5836</v>
+        <v>7012</v>
       </c>
       <c r="H441">
-        <v>5784</v>
+        <v>0</v>
       </c>
       <c r="I441" t="s">
         <v>71</v>
       </c>
       <c r="J441" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="L441" s="1">
-        <v>46286</v>
-      </c>
-      <c r="M441" t="s">
-        <v>222</v>
+        <v>46281</v>
       </c>
       <c r="N441" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O441">
-        <v>16976037</v>
+        <v>18258489</v>
       </c>
       <c r="P441" t="s">
         <v>235</v>
@@ -32341,16 +32338,13 @@
         <v>252</v>
       </c>
       <c r="R441" s="1">
-        <v>46283.59424842593</v>
+        <v>46280.61367623843</v>
       </c>
       <c r="S441">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T441" t="s">
-        <v>262</v>
-      </c>
-      <c r="V441" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="W441" t="s">
         <v>400</v>
@@ -32359,7 +32353,7 @@
         <v>0</v>
       </c>
       <c r="AB441" t="s">
-        <v>236</v>
+        <v>455</v>
       </c>
       <c r="AG441" t="s">
         <v>470</v>
@@ -32367,10 +32361,10 @@
     </row>
     <row r="442" spans="1:33">
       <c r="A442">
-        <v>6548</v>
+        <v>6486</v>
       </c>
       <c r="B442" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C442" t="s">
         <v>60</v>
@@ -32406,7 +32400,7 @@
         <v>225</v>
       </c>
       <c r="O442">
-        <v>17222579</v>
+        <v>16976037</v>
       </c>
       <c r="P442" t="s">
         <v>235</v>
@@ -32415,13 +32409,13 @@
         <v>252</v>
       </c>
       <c r="R442" s="1">
-        <v>46283.68435655093</v>
+        <v>46283.59424842593</v>
       </c>
       <c r="S442">
         <v>0</v>
       </c>
       <c r="T442" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="V442" t="s">
         <v>271</v>
@@ -32433,7 +32427,7 @@
         <v>0</v>
       </c>
       <c r="AB442" t="s">
-        <v>457</v>
+        <v>236</v>
       </c>
       <c r="AG442" t="s">
         <v>470</v>
@@ -32441,10 +32435,10 @@
     </row>
     <row r="443" spans="1:33">
       <c r="A443">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B443" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C443" t="s">
         <v>60</v>
@@ -32453,7 +32447,7 @@
         <v>61</v>
       </c>
       <c r="E443" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F443" t="s">
         <v>66</v>
@@ -32480,7 +32474,7 @@
         <v>225</v>
       </c>
       <c r="O443">
-        <v>18068500</v>
+        <v>17222579</v>
       </c>
       <c r="P443" t="s">
         <v>235</v>
@@ -32489,25 +32483,25 @@
         <v>252</v>
       </c>
       <c r="R443" s="1">
-        <v>46283.5942487037</v>
+        <v>46283.68435655093</v>
       </c>
       <c r="S443">
         <v>0</v>
       </c>
       <c r="T443" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="V443" t="s">
         <v>271</v>
       </c>
       <c r="W443" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AA443">
         <v>0</v>
       </c>
       <c r="AB443" t="s">
-        <v>236</v>
+        <v>457</v>
       </c>
       <c r="AG443" t="s">
         <v>470</v>
@@ -32515,16 +32509,16 @@
     </row>
     <row r="444" spans="1:33">
       <c r="A444">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B444" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C444" t="s">
         <v>60</v>
       </c>
       <c r="D444" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E444" t="s">
         <v>65</v>
@@ -32554,7 +32548,7 @@
         <v>225</v>
       </c>
       <c r="O444">
-        <v>18052419</v>
+        <v>18068500</v>
       </c>
       <c r="P444" t="s">
         <v>235</v>
@@ -32563,7 +32557,7 @@
         <v>252</v>
       </c>
       <c r="R444" s="1">
-        <v>46283.59424924768</v>
+        <v>46283.5942487037</v>
       </c>
       <c r="S444">
         <v>0</v>
@@ -32575,7 +32569,7 @@
         <v>271</v>
       </c>
       <c r="W444" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AA444">
         <v>0</v>
@@ -32589,19 +32583,19 @@
     </row>
     <row r="445" spans="1:33">
       <c r="A445">
-        <v>6703</v>
+        <v>6628</v>
       </c>
       <c r="B445" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C445" t="s">
         <v>60</v>
       </c>
       <c r="D445" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E445" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F445" t="s">
         <v>66</v>
@@ -32628,7 +32622,7 @@
         <v>225</v>
       </c>
       <c r="O445">
-        <v>18077082</v>
+        <v>18052419</v>
       </c>
       <c r="P445" t="s">
         <v>235</v>
@@ -32637,22 +32631,25 @@
         <v>252</v>
       </c>
       <c r="R445" s="1">
-        <v>46283.68161918982</v>
+        <v>46283.59424924768</v>
       </c>
       <c r="S445">
         <v>0</v>
       </c>
       <c r="T445" t="s">
-        <v>263</v>
+        <v>256</v>
+      </c>
+      <c r="V445" t="s">
+        <v>271</v>
       </c>
       <c r="W445" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AA445">
         <v>0</v>
       </c>
       <c r="AB445" t="s">
-        <v>458</v>
+        <v>236</v>
       </c>
       <c r="AG445" t="s">
         <v>470</v>
@@ -32660,10 +32657,10 @@
     </row>
     <row r="446" spans="1:33">
       <c r="A446">
-        <v>6404</v>
+        <v>6703</v>
       </c>
       <c r="B446" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C446" t="s">
         <v>60</v>
@@ -32678,16 +32675,16 @@
         <v>66</v>
       </c>
       <c r="G446">
-        <v>5903</v>
+        <v>5836</v>
       </c>
       <c r="H446">
-        <v>5830</v>
+        <v>5784</v>
       </c>
       <c r="I446" t="s">
         <v>71</v>
       </c>
       <c r="J446" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="L446" s="1">
         <v>46286</v>
@@ -32699,7 +32696,7 @@
         <v>225</v>
       </c>
       <c r="O446">
-        <v>16962221</v>
+        <v>18077082</v>
       </c>
       <c r="P446" t="s">
         <v>235</v>
@@ -32708,13 +32705,13 @@
         <v>252</v>
       </c>
       <c r="R446" s="1">
-        <v>46282.42048836806</v>
+        <v>46283.68161918982</v>
       </c>
       <c r="S446">
         <v>0</v>
       </c>
       <c r="T446" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="W446" t="s">
         <v>403</v>
@@ -32723,7 +32720,7 @@
         <v>0</v>
       </c>
       <c r="AB446" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="AG446" t="s">
         <v>470</v>
@@ -32749,10 +32746,10 @@
         <v>66</v>
       </c>
       <c r="G447">
+        <v>5903</v>
+      </c>
+      <c r="H447">
         <v>5830</v>
-      </c>
-      <c r="H447">
-        <v>5784</v>
       </c>
       <c r="I447" t="s">
         <v>71</v>
@@ -32763,11 +32760,14 @@
       <c r="L447" s="1">
         <v>46286</v>
       </c>
+      <c r="M447" t="s">
+        <v>222</v>
+      </c>
       <c r="N447" t="s">
         <v>225</v>
       </c>
       <c r="O447">
-        <v>16962211</v>
+        <v>16962221</v>
       </c>
       <c r="P447" t="s">
         <v>235</v>
@@ -32776,7 +32776,7 @@
         <v>252</v>
       </c>
       <c r="R447" s="1">
-        <v>46282.42138976852</v>
+        <v>46282.42048836806</v>
       </c>
       <c r="S447">
         <v>0</v>
@@ -32784,6 +32784,9 @@
       <c r="T447" t="s">
         <v>264</v>
       </c>
+      <c r="W447" t="s">
+        <v>404</v>
+      </c>
       <c r="AA447">
         <v>0</v>
       </c>
@@ -32796,16 +32799,16 @@
     </row>
     <row r="448" spans="1:33">
       <c r="A448">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B448" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C448" t="s">
         <v>60</v>
       </c>
       <c r="D448" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E448" t="s">
         <v>64</v>
@@ -32814,10 +32817,10 @@
         <v>66</v>
       </c>
       <c r="G448">
-        <v>5786</v>
+        <v>5830</v>
       </c>
       <c r="H448">
-        <v>0</v>
+        <v>5784</v>
       </c>
       <c r="I448" t="s">
         <v>71</v>
@@ -32826,13 +32829,13 @@
         <v>167</v>
       </c>
       <c r="L448" s="1">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="N448" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O448">
-        <v>17398997</v>
+        <v>16962211</v>
       </c>
       <c r="P448" t="s">
         <v>235</v>
@@ -32841,36 +32844,36 @@
         <v>252</v>
       </c>
       <c r="R448" s="1">
-        <v>46279.66936339121</v>
+        <v>46282.42138976852</v>
       </c>
       <c r="S448">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T448" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="AA448">
         <v>0</v>
       </c>
       <c r="AB448" t="s">
-        <v>455</v>
+        <v>468</v>
       </c>
       <c r="AG448" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="449" spans="1:34">
       <c r="A449">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B449" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C449" t="s">
         <v>60</v>
       </c>
       <c r="D449" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E449" t="s">
         <v>64</v>
@@ -32888,7 +32891,7 @@
         <v>71</v>
       </c>
       <c r="J449" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L449" s="1">
         <v>46283</v>
@@ -32897,7 +32900,7 @@
         <v>224</v>
       </c>
       <c r="O449">
-        <v>16962199</v>
+        <v>17398997</v>
       </c>
       <c r="P449" t="s">
         <v>235</v>
@@ -32906,19 +32909,19 @@
         <v>252</v>
       </c>
       <c r="R449" s="1">
-        <v>46264.0028866088</v>
+        <v>46279.66936339121</v>
       </c>
       <c r="S449">
         <v>3</v>
       </c>
       <c r="T449" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="AA449">
         <v>0</v>
       </c>
       <c r="AB449" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="AG449" t="s">
         <v>471</v>
@@ -32926,16 +32929,16 @@
     </row>
     <row r="450" spans="1:34">
       <c r="A450">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B450" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C450" t="s">
         <v>60</v>
       </c>
       <c r="D450" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E450" t="s">
         <v>64</v>
@@ -32953,7 +32956,7 @@
         <v>71</v>
       </c>
       <c r="J450" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L450" s="1">
         <v>46283</v>
@@ -32962,7 +32965,7 @@
         <v>224</v>
       </c>
       <c r="O450">
-        <v>16976005</v>
+        <v>16962199</v>
       </c>
       <c r="P450" t="s">
         <v>235</v>
@@ -32971,22 +32974,19 @@
         <v>252</v>
       </c>
       <c r="R450" s="1">
-        <v>46279.62931917824</v>
+        <v>46264.0028866088</v>
       </c>
       <c r="S450">
         <v>3</v>
       </c>
       <c r="T450" t="s">
-        <v>262</v>
-      </c>
-      <c r="V450" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="AA450">
         <v>0</v>
       </c>
       <c r="AB450" t="s">
-        <v>236</v>
+        <v>464</v>
       </c>
       <c r="AG450" t="s">
         <v>471</v>
@@ -32994,10 +32994,10 @@
     </row>
     <row r="451" spans="1:34">
       <c r="A451">
-        <v>6548</v>
+        <v>6486</v>
       </c>
       <c r="B451" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C451" t="s">
         <v>60</v>
@@ -33021,7 +33021,7 @@
         <v>71</v>
       </c>
       <c r="J451" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L451" s="1">
         <v>46283</v>
@@ -33030,7 +33030,7 @@
         <v>224</v>
       </c>
       <c r="O451">
-        <v>17222531</v>
+        <v>16976005</v>
       </c>
       <c r="P451" t="s">
         <v>235</v>
@@ -33039,13 +33039,13 @@
         <v>252</v>
       </c>
       <c r="R451" s="1">
-        <v>46279.40189447917</v>
+        <v>46279.62931917824</v>
       </c>
       <c r="S451">
         <v>3</v>
       </c>
       <c r="T451" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="V451" t="s">
         <v>271</v>
@@ -33054,7 +33054,7 @@
         <v>0</v>
       </c>
       <c r="AB451" t="s">
-        <v>455</v>
+        <v>236</v>
       </c>
       <c r="AG451" t="s">
         <v>471</v>
@@ -33062,10 +33062,10 @@
     </row>
     <row r="452" spans="1:34">
       <c r="A452">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B452" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C452" t="s">
         <v>60</v>
@@ -33074,7 +33074,7 @@
         <v>61</v>
       </c>
       <c r="E452" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F452" t="s">
         <v>66</v>
@@ -33089,7 +33089,7 @@
         <v>71</v>
       </c>
       <c r="J452" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L452" s="1">
         <v>46283</v>
@@ -33098,7 +33098,7 @@
         <v>224</v>
       </c>
       <c r="O452">
-        <v>18068463</v>
+        <v>17222531</v>
       </c>
       <c r="P452" t="s">
         <v>235</v>
@@ -33107,13 +33107,13 @@
         <v>252</v>
       </c>
       <c r="R452" s="1">
-        <v>46279.62936614583</v>
+        <v>46279.40189447917</v>
       </c>
       <c r="S452">
         <v>3</v>
       </c>
       <c r="T452" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="V452" t="s">
         <v>271</v>
@@ -33122,7 +33122,7 @@
         <v>0</v>
       </c>
       <c r="AB452" t="s">
-        <v>236</v>
+        <v>455</v>
       </c>
       <c r="AG452" t="s">
         <v>471</v>
@@ -33130,16 +33130,16 @@
     </row>
     <row r="453" spans="1:34">
       <c r="A453">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B453" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C453" t="s">
         <v>60</v>
       </c>
       <c r="D453" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E453" t="s">
         <v>65</v>
@@ -33157,7 +33157,7 @@
         <v>71</v>
       </c>
       <c r="J453" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L453" s="1">
         <v>46283</v>
@@ -33166,7 +33166,7 @@
         <v>224</v>
       </c>
       <c r="O453">
-        <v>18052384</v>
+        <v>18068463</v>
       </c>
       <c r="P453" t="s">
         <v>235</v>
@@ -33175,7 +33175,7 @@
         <v>252</v>
       </c>
       <c r="R453" s="1">
-        <v>46279.62936509259</v>
+        <v>46279.62936614583</v>
       </c>
       <c r="S453">
         <v>3</v>
@@ -33198,10 +33198,10 @@
     </row>
     <row r="454" spans="1:34">
       <c r="A454">
-        <v>6779</v>
+        <v>6628</v>
       </c>
       <c r="B454" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C454" t="s">
         <v>60</v>
@@ -33210,7 +33210,7 @@
         <v>62</v>
       </c>
       <c r="E454" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F454" t="s">
         <v>66</v>
@@ -33225,7 +33225,7 @@
         <v>71</v>
       </c>
       <c r="J454" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L454" s="1">
         <v>46283</v>
@@ -33234,7 +33234,7 @@
         <v>224</v>
       </c>
       <c r="O454">
-        <v>18090113</v>
+        <v>18052384</v>
       </c>
       <c r="P454" t="s">
         <v>235</v>
@@ -33243,13 +33243,13 @@
         <v>252</v>
       </c>
       <c r="R454" s="1">
-        <v>46276.63187607639</v>
+        <v>46279.62936509259</v>
       </c>
       <c r="S454">
         <v>3</v>
       </c>
       <c r="T454" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="V454" t="s">
         <v>271</v>
@@ -33258,7 +33258,7 @@
         <v>0</v>
       </c>
       <c r="AB454" t="s">
-        <v>455</v>
+        <v>236</v>
       </c>
       <c r="AG454" t="s">
         <v>471</v>
@@ -33266,10 +33266,10 @@
     </row>
     <row r="455" spans="1:34">
       <c r="A455">
-        <v>6945</v>
+        <v>6779</v>
       </c>
       <c r="B455" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C455" t="s">
         <v>60</v>
@@ -33281,7 +33281,7 @@
         <v>64</v>
       </c>
       <c r="F455" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G455">
         <v>5786</v>
@@ -33293,7 +33293,7 @@
         <v>71</v>
       </c>
       <c r="J455" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L455" s="1">
         <v>46283</v>
@@ -33302,7 +33302,7 @@
         <v>224</v>
       </c>
       <c r="O455">
-        <v>18179053</v>
+        <v>18090113</v>
       </c>
       <c r="P455" t="s">
         <v>235</v>
@@ -33311,13 +33311,16 @@
         <v>252</v>
       </c>
       <c r="R455" s="1">
-        <v>46279.62658503472</v>
+        <v>46276.63187607639</v>
       </c>
       <c r="S455">
         <v>3</v>
       </c>
       <c r="T455" t="s">
-        <v>257</v>
+        <v>261</v>
+      </c>
+      <c r="V455" t="s">
+        <v>271</v>
       </c>
       <c r="AA455">
         <v>0</v>
@@ -33331,16 +33334,16 @@
     </row>
     <row r="456" spans="1:34">
       <c r="A456">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B456" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C456" t="s">
         <v>60</v>
       </c>
       <c r="D456" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E456" t="s">
         <v>64</v>
@@ -33358,7 +33361,7 @@
         <v>71</v>
       </c>
       <c r="J456" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L456" s="1">
         <v>46283</v>
@@ -33367,7 +33370,7 @@
         <v>224</v>
       </c>
       <c r="O456">
-        <v>18190370</v>
+        <v>18179053</v>
       </c>
       <c r="P456" t="s">
         <v>235</v>
@@ -33376,13 +33379,13 @@
         <v>252</v>
       </c>
       <c r="R456" s="1">
-        <v>46279.63255474537</v>
+        <v>46279.62658503472</v>
       </c>
       <c r="S456">
         <v>3</v>
       </c>
       <c r="T456" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AA456">
         <v>0</v>
@@ -33396,10 +33399,10 @@
     </row>
     <row r="457" spans="1:34">
       <c r="A457">
-        <v>6486</v>
+        <v>6949</v>
       </c>
       <c r="B457" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C457" t="s">
         <v>60</v>
@@ -33411,10 +33414,10 @@
         <v>64</v>
       </c>
       <c r="F457" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G457">
-        <v>5787</v>
+        <v>5786</v>
       </c>
       <c r="H457">
         <v>0</v>
@@ -33426,51 +33429,51 @@
         <v>168</v>
       </c>
       <c r="L457" s="1">
-        <v>46286</v>
+        <v>46283</v>
       </c>
       <c r="N457" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="O457">
-        <v>16976010</v>
+        <v>18190370</v>
+      </c>
+      <c r="P457" t="s">
+        <v>235</v>
       </c>
       <c r="Q457" t="s">
         <v>252</v>
       </c>
       <c r="R457" s="1">
-        <v>46256.00536641204</v>
+        <v>46279.63255474537</v>
       </c>
       <c r="S457">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T457" t="s">
-        <v>262</v>
-      </c>
-      <c r="V457" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="AA457">
         <v>0</v>
       </c>
       <c r="AB457" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="AG457" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="458" spans="1:34">
       <c r="A458">
-        <v>6779</v>
+        <v>6486</v>
       </c>
       <c r="B458" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C458" t="s">
         <v>60</v>
       </c>
       <c r="D458" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E458" t="s">
         <v>64</v>
@@ -33488,7 +33491,7 @@
         <v>71</v>
       </c>
       <c r="J458" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L458" s="1">
         <v>46286</v>
@@ -33497,19 +33500,19 @@
         <v>228</v>
       </c>
       <c r="O458">
-        <v>18090118</v>
+        <v>16976010</v>
       </c>
       <c r="Q458" t="s">
         <v>252</v>
       </c>
       <c r="R458" s="1">
-        <v>46256.00539434027</v>
+        <v>46256.00536641204</v>
       </c>
       <c r="S458">
         <v>0</v>
       </c>
       <c r="T458" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="V458" t="s">
         <v>271</v>
@@ -33526,10 +33529,10 @@
     </row>
     <row r="459" spans="1:34">
       <c r="A459">
-        <v>6945</v>
+        <v>6779</v>
       </c>
       <c r="B459" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C459" t="s">
         <v>60</v>
@@ -33541,7 +33544,7 @@
         <v>64</v>
       </c>
       <c r="F459" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G459">
         <v>5787</v>
@@ -33553,7 +33556,7 @@
         <v>71</v>
       </c>
       <c r="J459" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L459" s="1">
         <v>46286</v>
@@ -33562,19 +33565,22 @@
         <v>228</v>
       </c>
       <c r="O459">
-        <v>18179058</v>
+        <v>18090118</v>
       </c>
       <c r="Q459" t="s">
         <v>252</v>
       </c>
       <c r="R459" s="1">
-        <v>46256.00540109954</v>
+        <v>46256.00539434027</v>
       </c>
       <c r="S459">
         <v>0</v>
       </c>
       <c r="T459" t="s">
-        <v>257</v>
+        <v>261</v>
+      </c>
+      <c r="V459" t="s">
+        <v>271</v>
       </c>
       <c r="AA459">
         <v>0</v>
@@ -33588,10 +33594,10 @@
     </row>
     <row r="460" spans="1:34">
       <c r="A460">
-        <v>6779</v>
+        <v>6945</v>
       </c>
       <c r="B460" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C460" t="s">
         <v>60</v>
@@ -33603,13 +33609,13 @@
         <v>64</v>
       </c>
       <c r="F460" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G460">
-        <v>5837</v>
+        <v>5787</v>
       </c>
       <c r="H460">
-        <v>5784</v>
+        <v>0</v>
       </c>
       <c r="I460" t="s">
         <v>71</v>
@@ -33618,60 +33624,48 @@
         <v>169</v>
       </c>
       <c r="L460" s="1">
-        <v>46283</v>
-      </c>
-      <c r="M460" t="s">
-        <v>222</v>
+        <v>46286</v>
       </c>
       <c r="N460" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="O460">
-        <v>18195614</v>
-      </c>
-      <c r="P460" t="s">
-        <v>235</v>
+        <v>18179058</v>
       </c>
       <c r="Q460" t="s">
         <v>252</v>
       </c>
       <c r="R460" s="1">
-        <v>46279.66713805556</v>
+        <v>46256.00540109954</v>
       </c>
       <c r="S460">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T460" t="s">
-        <v>261</v>
-      </c>
-      <c r="V460" t="s">
-        <v>271</v>
-      </c>
-      <c r="W460" t="s">
-        <v>388</v>
+        <v>257</v>
       </c>
       <c r="AA460">
         <v>0</v>
       </c>
       <c r="AB460" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="AG460" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="461" spans="1:34">
       <c r="A461">
-        <v>6486</v>
+        <v>6779</v>
       </c>
       <c r="B461" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C461" t="s">
         <v>60</v>
       </c>
       <c r="D461" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E461" t="s">
         <v>64</v>
@@ -33680,52 +33674,55 @@
         <v>66</v>
       </c>
       <c r="G461">
-        <v>6348</v>
+        <v>5837</v>
       </c>
       <c r="H461">
-        <v>0</v>
+        <v>5784</v>
       </c>
       <c r="I461" t="s">
         <v>71</v>
       </c>
       <c r="J461" t="s">
-        <v>93</v>
+        <v>170</v>
       </c>
       <c r="L461" s="1">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="M461" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N461" t="s">
         <v>225</v>
       </c>
       <c r="O461">
-        <v>18271101</v>
+        <v>18195614</v>
+      </c>
+      <c r="P461" t="s">
+        <v>235</v>
       </c>
       <c r="Q461" t="s">
         <v>252</v>
       </c>
       <c r="R461" s="1">
-        <v>46281.63317659722</v>
+        <v>46279.66713805556</v>
       </c>
       <c r="S461">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T461" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="V461" t="s">
         <v>271</v>
       </c>
       <c r="W461" t="s">
-        <v>404</v>
+        <v>389</v>
       </c>
       <c r="AA461">
         <v>0</v>
       </c>
       <c r="AB461" t="s">
-        <v>236</v>
+        <v>461</v>
       </c>
       <c r="AG461" t="s">
         <v>471</v>
@@ -33733,10 +33730,10 @@
     </row>
     <row r="462" spans="1:34">
       <c r="A462">
-        <v>6548</v>
+        <v>6486</v>
       </c>
       <c r="B462" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C462" t="s">
         <v>60</v>
@@ -33751,63 +33748,63 @@
         <v>66</v>
       </c>
       <c r="G462">
-        <v>11550</v>
+        <v>6348</v>
       </c>
       <c r="H462">
-        <v>1862</v>
+        <v>0</v>
       </c>
       <c r="I462" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J462" t="s">
-        <v>170</v>
+        <v>93</v>
       </c>
       <c r="L462" s="1">
-        <v>46286</v>
+        <v>46282</v>
+      </c>
+      <c r="M462" t="s">
+        <v>221</v>
       </c>
       <c r="N462" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O462">
-        <v>17988603</v>
-      </c>
-      <c r="P462" t="s">
-        <v>237</v>
+        <v>18271101</v>
       </c>
       <c r="Q462" t="s">
         <v>252</v>
       </c>
       <c r="R462" s="1">
-        <v>46267.72055925926</v>
+        <v>46281.63317659722</v>
       </c>
       <c r="S462">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T462" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="V462" t="s">
         <v>271</v>
       </c>
+      <c r="W462" t="s">
+        <v>405</v>
+      </c>
       <c r="AA462">
         <v>0</v>
       </c>
       <c r="AB462" t="s">
-        <v>463</v>
+        <v>236</v>
       </c>
       <c r="AG462" t="s">
-        <v>470</v>
-      </c>
-      <c r="AH462" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
     </row>
     <row r="463" spans="1:34">
       <c r="A463">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B463" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C463" t="s">
         <v>60</v>
@@ -33816,7 +33813,7 @@
         <v>61</v>
       </c>
       <c r="E463" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F463" t="s">
         <v>66</v>
@@ -33831,7 +33828,7 @@
         <v>72</v>
       </c>
       <c r="J463" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L463" s="1">
         <v>46286</v>
@@ -33840,22 +33837,22 @@
         <v>224</v>
       </c>
       <c r="O463">
-        <v>18048493</v>
+        <v>17988603</v>
       </c>
       <c r="P463" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Q463" t="s">
         <v>252</v>
       </c>
       <c r="R463" s="1">
-        <v>46267.79441380787</v>
+        <v>46267.72055925926</v>
       </c>
       <c r="S463">
         <v>0</v>
       </c>
       <c r="T463" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="V463" t="s">
         <v>271</v>
@@ -33869,13 +33866,16 @@
       <c r="AG463" t="s">
         <v>470</v>
       </c>
+      <c r="AH463" t="s">
+        <v>463</v>
+      </c>
     </row>
     <row r="464" spans="1:34">
       <c r="A464">
-        <v>6949</v>
+        <v>6627</v>
       </c>
       <c r="B464" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C464" t="s">
         <v>60</v>
@@ -33884,10 +33884,10 @@
         <v>61</v>
       </c>
       <c r="E464" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F464" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G464">
         <v>11550</v>
@@ -33899,7 +33899,7 @@
         <v>72</v>
       </c>
       <c r="J464" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L464" s="1">
         <v>46286</v>
@@ -33908,42 +33908,42 @@
         <v>224</v>
       </c>
       <c r="O464">
-        <v>18214931</v>
+        <v>18048493</v>
       </c>
       <c r="P464" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="Q464" t="s">
         <v>252</v>
       </c>
       <c r="R464" s="1">
-        <v>46267.79441215278</v>
+        <v>46267.79441380787</v>
       </c>
       <c r="S464">
         <v>0</v>
       </c>
       <c r="T464" t="s">
-        <v>258</v>
+        <v>256</v>
+      </c>
+      <c r="V464" t="s">
+        <v>271</v>
       </c>
       <c r="AA464">
         <v>0</v>
       </c>
       <c r="AB464" t="s">
-        <v>240</v>
+        <v>463</v>
       </c>
       <c r="AG464" t="s">
         <v>470</v>
       </c>
-      <c r="AH464" t="s">
-        <v>463</v>
-      </c>
     </row>
     <row r="465" spans="1:34">
       <c r="A465">
-        <v>6548</v>
+        <v>6949</v>
       </c>
       <c r="B465" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C465" t="s">
         <v>60</v>
@@ -33955,10 +33955,10 @@
         <v>64</v>
       </c>
       <c r="F465" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G465">
-        <v>1913</v>
+        <v>11550</v>
       </c>
       <c r="H465">
         <v>1862</v>
@@ -33967,7 +33967,7 @@
         <v>72</v>
       </c>
       <c r="J465" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="L465" s="1">
         <v>46286</v>
@@ -33976,31 +33976,28 @@
         <v>224</v>
       </c>
       <c r="O465">
-        <v>17988579</v>
+        <v>18214931</v>
       </c>
       <c r="P465" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q465" t="s">
         <v>252</v>
       </c>
       <c r="R465" s="1">
-        <v>46283.3939177662</v>
+        <v>46267.79441215278</v>
       </c>
       <c r="S465">
         <v>0</v>
       </c>
       <c r="T465" t="s">
-        <v>255</v>
-      </c>
-      <c r="V465" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="AA465">
         <v>0</v>
       </c>
       <c r="AB465" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="AG465" t="s">
         <v>470</v>
@@ -34011,73 +34008,70 @@
     </row>
     <row r="466" spans="1:34">
       <c r="A466">
-        <v>6962</v>
+        <v>6548</v>
       </c>
       <c r="B466" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C466" t="s">
         <v>60</v>
       </c>
       <c r="D466" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E466" t="s">
         <v>64</v>
       </c>
       <c r="F466" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G466">
-        <v>11873</v>
+        <v>1913</v>
       </c>
       <c r="H466">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="I466" t="s">
         <v>72</v>
       </c>
       <c r="J466" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="L466" s="1">
-        <v>46281</v>
-      </c>
-      <c r="M466" t="s">
-        <v>221</v>
+        <v>46286</v>
       </c>
       <c r="N466" t="s">
         <v>224</v>
       </c>
       <c r="O466">
-        <v>18223029</v>
+        <v>17988579</v>
       </c>
       <c r="P466" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="Q466" t="s">
         <v>252</v>
       </c>
       <c r="R466" s="1">
-        <v>46280.62789608796</v>
+        <v>46283.3939177662</v>
       </c>
       <c r="S466">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T466" t="s">
-        <v>259</v>
-      </c>
-      <c r="W466" t="s">
-        <v>405</v>
+        <v>255</v>
+      </c>
+      <c r="V466" t="s">
+        <v>271</v>
       </c>
       <c r="AA466">
         <v>0</v>
       </c>
       <c r="AB466" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="AG466" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AH466" t="s">
         <v>463</v>
@@ -34085,10 +34079,10 @@
     </row>
     <row r="467" spans="1:34">
       <c r="A467">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B467" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C467" t="s">
         <v>60</v>
@@ -34112,7 +34106,7 @@
         <v>72</v>
       </c>
       <c r="J467" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L467" s="1">
         <v>46281</v>
@@ -34124,7 +34118,7 @@
         <v>224</v>
       </c>
       <c r="O467">
-        <v>18222688</v>
+        <v>18223029</v>
       </c>
       <c r="P467" t="s">
         <v>241</v>
@@ -34133,7 +34127,7 @@
         <v>252</v>
       </c>
       <c r="R467" s="1">
-        <v>46280.63189497685</v>
+        <v>46280.62789608796</v>
       </c>
       <c r="S467">
         <v>5</v>
@@ -34142,7 +34136,7 @@
         <v>259</v>
       </c>
       <c r="W467" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AA467">
         <v>0</v>
@@ -34159,25 +34153,25 @@
     </row>
     <row r="468" spans="1:34">
       <c r="A468">
-        <v>6548</v>
+        <v>6963</v>
       </c>
       <c r="B468" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C468" t="s">
         <v>60</v>
       </c>
       <c r="D468" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E468" t="s">
         <v>64</v>
       </c>
       <c r="F468" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G468">
-        <v>1876</v>
+        <v>11873</v>
       </c>
       <c r="H468">
         <v>0</v>
@@ -34186,34 +34180,34 @@
         <v>72</v>
       </c>
       <c r="J468" t="s">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="L468" s="1">
-        <v>46283</v>
+        <v>46281</v>
+      </c>
+      <c r="M468" t="s">
+        <v>221</v>
       </c>
       <c r="N468" t="s">
         <v>224</v>
       </c>
       <c r="O468">
-        <v>17988555</v>
+        <v>18222688</v>
       </c>
       <c r="P468" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q468" t="s">
         <v>252</v>
       </c>
       <c r="R468" s="1">
-        <v>46283.66538607639</v>
+        <v>46280.63189497685</v>
       </c>
       <c r="S468">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T468" t="s">
-        <v>255</v>
-      </c>
-      <c r="V468" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="W468" t="s">
         <v>406</v>
@@ -34222,7 +34216,7 @@
         <v>0</v>
       </c>
       <c r="AB468" t="s">
-        <v>464</v>
+        <v>241</v>
       </c>
       <c r="AG468" t="s">
         <v>471</v>
@@ -34233,10 +34227,10 @@
     </row>
     <row r="469" spans="1:34">
       <c r="A469">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B469" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C469" t="s">
         <v>60</v>
@@ -34245,13 +34239,13 @@
         <v>61</v>
       </c>
       <c r="E469" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F469" t="s">
         <v>66</v>
       </c>
       <c r="G469">
-        <v>11411</v>
+        <v>1876</v>
       </c>
       <c r="H469">
         <v>0</v>
@@ -34260,7 +34254,7 @@
         <v>72</v>
       </c>
       <c r="J469" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L469" s="1">
         <v>46283</v>
@@ -34269,22 +34263,22 @@
         <v>224</v>
       </c>
       <c r="O469">
-        <v>18048483</v>
+        <v>17988555</v>
       </c>
       <c r="P469" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Q469" t="s">
         <v>252</v>
       </c>
       <c r="R469" s="1">
-        <v>46286.43482986111</v>
+        <v>46283.66538607639</v>
       </c>
       <c r="S469">
         <v>3</v>
       </c>
       <c r="T469" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="V469" t="s">
         <v>271</v>
@@ -34296,24 +34290,27 @@
         <v>0</v>
       </c>
       <c r="AB469" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="AG469" t="s">
         <v>471</v>
       </c>
+      <c r="AH469" t="s">
+        <v>463</v>
+      </c>
     </row>
     <row r="470" spans="1:34">
       <c r="A470">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B470" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C470" t="s">
         <v>60</v>
       </c>
       <c r="D470" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E470" t="s">
         <v>65</v>
@@ -34322,7 +34319,7 @@
         <v>66</v>
       </c>
       <c r="G470">
-        <v>1862</v>
+        <v>11411</v>
       </c>
       <c r="H470">
         <v>0</v>
@@ -34331,28 +34328,28 @@
         <v>72</v>
       </c>
       <c r="J470" t="s">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="L470" s="1">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="N470" t="s">
         <v>224</v>
       </c>
       <c r="O470">
-        <v>18047772</v>
+        <v>18048483</v>
       </c>
       <c r="P470" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q470" t="s">
         <v>252</v>
       </c>
       <c r="R470" s="1">
-        <v>46265.00319547454</v>
+        <v>46286.43482986111</v>
       </c>
       <c r="S470">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T470" t="s">
         <v>256</v>
@@ -34360,25 +34357,25 @@
       <c r="V470" t="s">
         <v>271</v>
       </c>
+      <c r="W470" t="s">
+        <v>408</v>
+      </c>
       <c r="AA470">
         <v>0</v>
       </c>
       <c r="AB470" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="AG470" t="s">
-        <v>470</v>
-      </c>
-      <c r="AH470" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
     </row>
     <row r="471" spans="1:34">
       <c r="A471">
-        <v>6945</v>
+        <v>6628</v>
       </c>
       <c r="B471" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C471" t="s">
         <v>60</v>
@@ -34387,10 +34384,10 @@
         <v>62</v>
       </c>
       <c r="E471" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F471" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G471">
         <v>1862</v>
@@ -34402,7 +34399,7 @@
         <v>72</v>
       </c>
       <c r="J471" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L471" s="1">
         <v>46281</v>
@@ -34411,39 +34408,45 @@
         <v>224</v>
       </c>
       <c r="O471">
-        <v>18220176</v>
+        <v>18047772</v>
       </c>
       <c r="P471" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q471" t="s">
         <v>252</v>
       </c>
       <c r="R471" s="1">
-        <v>46276.37795540509</v>
+        <v>46265.00319547454</v>
       </c>
       <c r="S471">
         <v>5</v>
       </c>
       <c r="T471" t="s">
-        <v>257</v>
+        <v>256</v>
+      </c>
+      <c r="V471" t="s">
+        <v>271</v>
       </c>
       <c r="AA471">
         <v>0</v>
       </c>
       <c r="AB471" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AG471" t="s">
         <v>470</v>
       </c>
+      <c r="AH471" t="s">
+        <v>463</v>
+      </c>
     </row>
     <row r="472" spans="1:34">
       <c r="A472">
-        <v>6628</v>
+        <v>6945</v>
       </c>
       <c r="B472" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C472" t="s">
         <v>60</v>
@@ -34452,13 +34455,13 @@
         <v>62</v>
       </c>
       <c r="E472" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F472" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G472">
-        <v>1879</v>
+        <v>1862</v>
       </c>
       <c r="H472">
         <v>0</v>
@@ -34467,57 +34470,48 @@
         <v>72</v>
       </c>
       <c r="J472" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="L472" s="1">
-        <v>46283</v>
+        <v>46281</v>
       </c>
       <c r="N472" t="s">
         <v>224</v>
       </c>
       <c r="O472">
-        <v>17988684</v>
+        <v>18220176</v>
       </c>
       <c r="P472" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q472" t="s">
         <v>252</v>
       </c>
       <c r="R472" s="1">
-        <v>46283.41459880787</v>
+        <v>46276.37795540509</v>
       </c>
       <c r="S472">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T472" t="s">
-        <v>256</v>
-      </c>
-      <c r="V472" t="s">
-        <v>271</v>
-      </c>
-      <c r="W472" t="s">
-        <v>408</v>
+        <v>257</v>
       </c>
       <c r="AA472">
         <v>0</v>
       </c>
       <c r="AB472" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="AG472" t="s">
-        <v>471</v>
-      </c>
-      <c r="AH472" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
     </row>
     <row r="473" spans="1:34">
       <c r="A473">
-        <v>6945</v>
+        <v>6628</v>
       </c>
       <c r="B473" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C473" t="s">
         <v>60</v>
@@ -34526,10 +34520,10 @@
         <v>62</v>
       </c>
       <c r="E473" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F473" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G473">
         <v>1879</v>
@@ -34541,7 +34535,7 @@
         <v>72</v>
       </c>
       <c r="J473" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L473" s="1">
         <v>46283</v>
@@ -34550,22 +34544,25 @@
         <v>224</v>
       </c>
       <c r="O473">
-        <v>18220194</v>
+        <v>17988684</v>
       </c>
       <c r="P473" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q473" t="s">
         <v>252</v>
       </c>
       <c r="R473" s="1">
-        <v>46283.73838344908</v>
+        <v>46283.41459880787</v>
       </c>
       <c r="S473">
         <v>3</v>
       </c>
       <c r="T473" t="s">
-        <v>257</v>
+        <v>256</v>
+      </c>
+      <c r="V473" t="s">
+        <v>271</v>
       </c>
       <c r="W473" t="s">
         <v>409</v>
@@ -34579,28 +34576,31 @@
       <c r="AG473" t="s">
         <v>471</v>
       </c>
+      <c r="AH473" t="s">
+        <v>463</v>
+      </c>
     </row>
     <row r="474" spans="1:34">
       <c r="A474">
-        <v>6627</v>
+        <v>6945</v>
       </c>
       <c r="B474" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C474" t="s">
         <v>60</v>
       </c>
       <c r="D474" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E474" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F474" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G474">
-        <v>1882</v>
+        <v>1879</v>
       </c>
       <c r="H474">
         <v>0</v>
@@ -34609,16 +34609,16 @@
         <v>72</v>
       </c>
       <c r="J474" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="L474" s="1">
-        <v>46287</v>
+        <v>46283</v>
       </c>
       <c r="N474" t="s">
         <v>224</v>
       </c>
       <c r="O474">
-        <v>17968390</v>
+        <v>18220194</v>
       </c>
       <c r="P474" t="s">
         <v>238</v>
@@ -34627,16 +34627,13 @@
         <v>252</v>
       </c>
       <c r="R474" s="1">
-        <v>46283.75381304398</v>
+        <v>46283.73838344908</v>
       </c>
       <c r="S474">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="T474" t="s">
-        <v>256</v>
-      </c>
-      <c r="V474" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="W474" t="s">
         <v>410</v>
@@ -34645,7 +34642,7 @@
         <v>0</v>
       </c>
       <c r="AB474" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="AG474" t="s">
         <v>471</v>
@@ -34653,10 +34650,10 @@
     </row>
     <row r="475" spans="1:34">
       <c r="A475">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B475" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C475" t="s">
         <v>60</v>
@@ -34665,13 +34662,13 @@
         <v>61</v>
       </c>
       <c r="E475" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F475" t="s">
         <v>66</v>
       </c>
       <c r="G475">
-        <v>7026</v>
+        <v>1882</v>
       </c>
       <c r="H475">
         <v>0</v>
@@ -34680,31 +34677,31 @@
         <v>72</v>
       </c>
       <c r="J475" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="L475" s="1">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="N475" t="s">
         <v>224</v>
       </c>
       <c r="O475">
-        <v>18094899</v>
+        <v>17968390</v>
       </c>
       <c r="P475" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q475" t="s">
         <v>252</v>
       </c>
       <c r="R475" s="1">
-        <v>46282.74573174769</v>
+        <v>46283.75381304398</v>
       </c>
       <c r="S475">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T475" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="V475" t="s">
         <v>271</v>
@@ -34719,10 +34716,7 @@
         <v>464</v>
       </c>
       <c r="AG475" t="s">
-        <v>470</v>
-      </c>
-      <c r="AH475" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
     </row>
     <row r="476" spans="1:34">
@@ -34754,7 +34748,7 @@
         <v>72</v>
       </c>
       <c r="J476" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="L476" s="1">
         <v>46288</v>
@@ -34825,7 +34819,7 @@
         <v>72</v>
       </c>
       <c r="J477" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="L477" s="1">
         <v>46288</v>
@@ -34899,7 +34893,7 @@
         <v>72</v>
       </c>
       <c r="J478" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L478" s="1">
         <v>46286</v>
@@ -34970,7 +34964,7 @@
         <v>73</v>
       </c>
       <c r="J479" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L479" s="1">
         <v>46289</v>
@@ -35000,7 +34994,7 @@
         <v>260</v>
       </c>
       <c r="W479" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AA479">
         <v>0</v>
@@ -35044,7 +35038,7 @@
         <v>73</v>
       </c>
       <c r="J480" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L480" s="1">
         <v>46281</v>
@@ -35121,7 +35115,7 @@
         <v>73</v>
       </c>
       <c r="J481" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L481" s="1">
         <v>46281</v>
@@ -35636,7 +35630,7 @@
         <v>73</v>
       </c>
       <c r="J488" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L488" s="1">
         <v>46283</v>
@@ -35707,7 +35701,7 @@
         <v>73</v>
       </c>
       <c r="J489" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L489" s="1">
         <v>46283</v>
@@ -35781,7 +35775,7 @@
         <v>73</v>
       </c>
       <c r="J490" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L490" s="1">
         <v>46290</v>
@@ -35849,7 +35843,7 @@
         <v>73</v>
       </c>
       <c r="J491" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="L491" s="1">
         <v>46288</v>
@@ -35920,7 +35914,7 @@
         <v>73</v>
       </c>
       <c r="J492" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="L492" s="1">
         <v>46288</v>
@@ -36843,7 +36837,7 @@
         <v>74</v>
       </c>
       <c r="J505" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L505" s="1">
         <v>46290</v>
@@ -36911,7 +36905,7 @@
         <v>74</v>
       </c>
       <c r="J506" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L506" s="1">
         <v>46290</v>
@@ -36976,7 +36970,7 @@
         <v>74</v>
       </c>
       <c r="J507" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L507" s="1">
         <v>46290</v>
@@ -37044,7 +37038,7 @@
         <v>74</v>
       </c>
       <c r="J508" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L508" s="1">
         <v>46290</v>
@@ -37112,7 +37106,7 @@
         <v>74</v>
       </c>
       <c r="J509" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L509" s="1">
         <v>46290</v>
@@ -37180,7 +37174,7 @@
         <v>74</v>
       </c>
       <c r="J510" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L510" s="1">
         <v>46290</v>
@@ -37248,7 +37242,7 @@
         <v>74</v>
       </c>
       <c r="J511" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L511" s="1">
         <v>46290</v>
@@ -37313,7 +37307,7 @@
         <v>74</v>
       </c>
       <c r="J512" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L512" s="1">
         <v>46290</v>
@@ -41677,7 +41671,7 @@
         <v>75</v>
       </c>
       <c r="J573" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="L573" s="1">
         <v>46289</v>
@@ -41745,7 +41739,7 @@
         <v>75</v>
       </c>
       <c r="J574" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="L574" s="1">
         <v>46289</v>
@@ -43092,7 +43086,7 @@
         <v>71</v>
       </c>
       <c r="J595" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L595" s="1">
         <v>46286</v>
@@ -43154,7 +43148,7 @@
         <v>71</v>
       </c>
       <c r="J596" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L596" s="1">
         <v>46286</v>

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -1174,7 +1174,9 @@
     <t>Comentário Colaborador + Previsão de Conclusão. Previsto para: 22/09/2026 - Data Comentário: 18/09/2026 15:24</t>
   </si>
   <si>
-    <t>Reaberto via API integração MGC x Sistema de Analise Fiscal em 21/09/2026 12:44:23. - Data Comentário: 21/09/2026 12:41</t>
+    <t>Integração com Sistema de Análise 
+Nenhum comentário informado pelo GC 
+Data Simulação: 21/09/2026 12:44:24 - Data Comentário: 21/09/2026 13:15</t>
   </si>
   <si>
     <t>Comentário Colaborador + Previsão de Conclusão. Previsto para: 24/09/2026 - Data Comentário: 18/09/2026 15:24</t>

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9028" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9029" uniqueCount="481">
   <si>
     <t>CodCliente</t>
   </si>
@@ -454,82 +454,82 @@
     <t>Digitalização de NF Ativo</t>
   </si>
   <si>
+    <t>Fed - PIS/COFINS Cumulativo - 2172</t>
+  </si>
+  <si>
+    <t>Confirm Rec - PIS/COFINS</t>
+  </si>
+  <si>
+    <t>Inclusão de Ata de Reunião</t>
+  </si>
+  <si>
+    <t>Fechamento Mensal</t>
+  </si>
+  <si>
+    <t>Fed - IRPJ/CSLL - 3ª Quota corrigida</t>
+  </si>
+  <si>
+    <t>Outras Receitas</t>
+  </si>
+  <si>
+    <t>Fed - DIRBI</t>
+  </si>
+  <si>
+    <t>Adiantamento Salarial (20)</t>
+  </si>
+  <si>
+    <t>Cartão de Ponto</t>
+  </si>
+  <si>
+    <t>Controle Afastamento</t>
+  </si>
+  <si>
+    <t>Envio de Impostos - DCTF Web</t>
+  </si>
+  <si>
+    <t>Folha Pró-Lab/Autônomo</t>
+  </si>
+  <si>
+    <t>Folha Pró-Lab/Autônomo - Impressão PDF</t>
+  </si>
+  <si>
+    <t>Impostos Folha Mensal</t>
+  </si>
+  <si>
+    <t>PAT</t>
+  </si>
+  <si>
+    <t>Prévias rescisões individuais</t>
+  </si>
+  <si>
+    <t>Relação de Aniversariantes</t>
+  </si>
+  <si>
+    <t>Bloco K</t>
+  </si>
+  <si>
+    <t>Depreciação</t>
+  </si>
+  <si>
+    <t>Est - ICMS RPA - CÓD. 046-2</t>
+  </si>
+  <si>
+    <t>Est - ICMS RPA - CÓD. 046-2 (GO)</t>
+  </si>
+  <si>
+    <t>Fed - DAS</t>
+  </si>
+  <si>
+    <t>Movimento - Sistema de Análise</t>
+  </si>
+  <si>
+    <t>Receitas Financeiras ( Aplicação Financeira )</t>
+  </si>
+  <si>
+    <t>Fechamento Fiscal</t>
+  </si>
+  <si>
     <t>Fed - IRPJ/CSLL 3ª Quota corrigida</t>
-  </si>
-  <si>
-    <t>Fed - PIS/COFINS Cumulativo - 2172</t>
-  </si>
-  <si>
-    <t>Confirm Rec - PIS/COFINS</t>
-  </si>
-  <si>
-    <t>Inclusão de Ata de Reunião</t>
-  </si>
-  <si>
-    <t>Fechamento Mensal</t>
-  </si>
-  <si>
-    <t>Fed - IRPJ/CSLL - 3ª Quota corrigida</t>
-  </si>
-  <si>
-    <t>Outras Receitas</t>
-  </si>
-  <si>
-    <t>Fed - DIRBI</t>
-  </si>
-  <si>
-    <t>Adiantamento Salarial (20)</t>
-  </si>
-  <si>
-    <t>Cartão de Ponto</t>
-  </si>
-  <si>
-    <t>Controle Afastamento</t>
-  </si>
-  <si>
-    <t>Envio de Impostos - DCTF Web</t>
-  </si>
-  <si>
-    <t>Folha Pró-Lab/Autônomo</t>
-  </si>
-  <si>
-    <t>Folha Pró-Lab/Autônomo - Impressão PDF</t>
-  </si>
-  <si>
-    <t>Impostos Folha Mensal</t>
-  </si>
-  <si>
-    <t>PAT</t>
-  </si>
-  <si>
-    <t>Prévias rescisões individuais</t>
-  </si>
-  <si>
-    <t>Relação de Aniversariantes</t>
-  </si>
-  <si>
-    <t>Bloco K</t>
-  </si>
-  <si>
-    <t>Depreciação</t>
-  </si>
-  <si>
-    <t>Est - ICMS RPA - CÓD. 046-2</t>
-  </si>
-  <si>
-    <t>Est - ICMS RPA - CÓD. 046-2 (GO)</t>
-  </si>
-  <si>
-    <t>Fed - DAS</t>
-  </si>
-  <si>
-    <t>Movimento - Sistema de Análise</t>
-  </si>
-  <si>
-    <t>Receitas Financeiras ( Aplicação Financeira )</t>
-  </si>
-  <si>
-    <t>Fechamento Fiscal</t>
   </si>
   <si>
     <t>Confirm Rec - DAS</t>
@@ -1152,9 +1152,6 @@
   </si>
   <si>
     <t>Comentário Colaborador + Previsão de Conclusão. Previsto para: 28/09/2026 - Data Comentário: 18/09/2026 15:27</t>
-  </si>
-  <si>
-    <t>Imposto enviado via SCI Report - Data Comentário: 21/09/2026 16:19</t>
   </si>
   <si>
     <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1882] sendo a ultima baixa feita [1882]-18/09/2026 18:05:29.. - Data Comentário: 21/09/2026 09:20</t>
@@ -1324,6 +1321,9 @@
   </si>
   <si>
     <t>Imposto enviado via SCI Report - Data Comentário: 17/09/2026 20:06</t>
+  </si>
+  <si>
+    <t>Imposto enviado via SCI Report - Data Comentário: 21/09/2026 16:19</t>
   </si>
   <si>
     <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 18/09/2026 09:12:28. - Data Comentário: 18/09/2026 09:07</t>
@@ -26805,10 +26805,10 @@
     </row>
     <row r="358" spans="1:34">
       <c r="A358">
-        <v>6703</v>
+        <v>6404</v>
       </c>
       <c r="B358" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C358" t="s">
         <v>58</v>
@@ -26823,7 +26823,7 @@
         <v>64</v>
       </c>
       <c r="G358">
-        <v>1811</v>
+        <v>1807</v>
       </c>
       <c r="H358">
         <v>0</v>
@@ -26835,16 +26835,16 @@
         <v>146</v>
       </c>
       <c r="L358" s="1">
-        <v>46290</v>
+        <v>46287</v>
       </c>
       <c r="M358" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="N358" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O358">
-        <v>17948816</v>
+        <v>16962171</v>
       </c>
       <c r="P358" t="s">
         <v>243</v>
@@ -26853,13 +26853,13 @@
         <v>254</v>
       </c>
       <c r="S358">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="T358" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="W358" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="AA358">
         <v>0</v>
@@ -26873,10 +26873,10 @@
     </row>
     <row r="359" spans="1:34">
       <c r="A359">
-        <v>6404</v>
+        <v>6703</v>
       </c>
       <c r="B359" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C359" t="s">
         <v>58</v>
@@ -26900,7 +26900,7 @@
         <v>71</v>
       </c>
       <c r="J359" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="L359" s="1">
         <v>46287</v>
@@ -26912,7 +26912,7 @@
         <v>219</v>
       </c>
       <c r="O359">
-        <v>16962171</v>
+        <v>17948806</v>
       </c>
       <c r="P359" t="s">
         <v>243</v>
@@ -26924,7 +26924,7 @@
         <v>0</v>
       </c>
       <c r="T359" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="W359" t="s">
         <v>367</v>
@@ -26941,16 +26941,16 @@
     </row>
     <row r="360" spans="1:34">
       <c r="A360">
-        <v>6703</v>
+        <v>5417</v>
       </c>
       <c r="B360" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C360" t="s">
         <v>58</v>
       </c>
       <c r="D360" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E360" t="s">
         <v>62</v>
@@ -26959,7 +26959,7 @@
         <v>64</v>
       </c>
       <c r="G360">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="H360">
         <v>0</v>
@@ -26968,7 +26968,7 @@
         <v>71</v>
       </c>
       <c r="J360" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="L360" s="1">
         <v>46287</v>
@@ -26980,7 +26980,7 @@
         <v>219</v>
       </c>
       <c r="O360">
-        <v>17948806</v>
+        <v>17398965</v>
       </c>
       <c r="P360" t="s">
         <v>243</v>
@@ -26992,7 +26992,7 @@
         <v>0</v>
       </c>
       <c r="T360" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="W360" t="s">
         <v>367</v>
@@ -27009,10 +27009,10 @@
     </row>
     <row r="361" spans="1:34">
       <c r="A361">
-        <v>5417</v>
+        <v>6704</v>
       </c>
       <c r="B361" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C361" t="s">
         <v>58</v>
@@ -27048,7 +27048,7 @@
         <v>219</v>
       </c>
       <c r="O361">
-        <v>17398965</v>
+        <v>18085209</v>
       </c>
       <c r="P361" t="s">
         <v>243</v>
@@ -27060,7 +27060,10 @@
         <v>0</v>
       </c>
       <c r="T361" t="s">
-        <v>260</v>
+        <v>261</v>
+      </c>
+      <c r="V361" t="s">
+        <v>271</v>
       </c>
       <c r="W361" t="s">
         <v>367</v>
@@ -27077,10 +27080,10 @@
     </row>
     <row r="362" spans="1:34">
       <c r="A362">
-        <v>6704</v>
+        <v>6627</v>
       </c>
       <c r="B362" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C362" t="s">
         <v>58</v>
@@ -27089,52 +27092,52 @@
         <v>59</v>
       </c>
       <c r="E362" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F362" t="s">
         <v>64</v>
       </c>
       <c r="G362">
-        <v>1808</v>
+        <v>953</v>
       </c>
       <c r="H362">
         <v>0</v>
       </c>
       <c r="I362" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J362" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="L362" s="1">
-        <v>46287</v>
+        <v>46290</v>
       </c>
       <c r="M362" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="N362" t="s">
         <v>219</v>
       </c>
       <c r="O362">
-        <v>18085209</v>
+        <v>17042317</v>
       </c>
       <c r="P362" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q362" t="s">
         <v>254</v>
       </c>
       <c r="S362">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="T362" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="V362" t="s">
         <v>271</v>
       </c>
       <c r="W362" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="AA362">
         <v>0</v>
@@ -27142,28 +27145,25 @@
       <c r="AG362" t="s">
         <v>472</v>
       </c>
-      <c r="AH362" t="s">
-        <v>480</v>
-      </c>
     </row>
     <row r="363" spans="1:34">
       <c r="A363">
-        <v>6627</v>
+        <v>6962</v>
       </c>
       <c r="B363" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C363" t="s">
         <v>58</v>
       </c>
       <c r="D363" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E363" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F363" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G363">
         <v>953</v>
@@ -27175,19 +27175,16 @@
         <v>72</v>
       </c>
       <c r="J363" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L363" s="1">
         <v>46290</v>
       </c>
-      <c r="M363" t="s">
-        <v>211</v>
-      </c>
       <c r="N363" t="s">
         <v>219</v>
       </c>
       <c r="O363">
-        <v>17042317</v>
+        <v>18188731</v>
       </c>
       <c r="P363" t="s">
         <v>244</v>
@@ -27199,10 +27196,7 @@
         <v>-3</v>
       </c>
       <c r="T363" t="s">
-        <v>256</v>
-      </c>
-      <c r="V363" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="W363" t="s">
         <v>371</v>
@@ -27216,10 +27210,10 @@
     </row>
     <row r="364" spans="1:34">
       <c r="A364">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B364" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C364" t="s">
         <v>58</v>
@@ -27243,7 +27237,7 @@
         <v>72</v>
       </c>
       <c r="J364" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L364" s="1">
         <v>46290</v>
@@ -27252,7 +27246,7 @@
         <v>219</v>
       </c>
       <c r="O364">
-        <v>18188731</v>
+        <v>18188637</v>
       </c>
       <c r="P364" t="s">
         <v>244</v>
@@ -27278,25 +27272,25 @@
     </row>
     <row r="365" spans="1:34">
       <c r="A365">
-        <v>6963</v>
+        <v>5417</v>
       </c>
       <c r="B365" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C365" t="s">
         <v>58</v>
       </c>
       <c r="D365" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E365" t="s">
         <v>62</v>
       </c>
       <c r="F365" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G365">
-        <v>953</v>
+        <v>943</v>
       </c>
       <c r="H365">
         <v>0</v>
@@ -27308,13 +27302,16 @@
         <v>148</v>
       </c>
       <c r="L365" s="1">
-        <v>46290</v>
+        <v>46295</v>
+      </c>
+      <c r="M365" t="s">
+        <v>212</v>
       </c>
       <c r="N365" t="s">
         <v>219</v>
       </c>
       <c r="O365">
-        <v>18188637</v>
+        <v>17398859</v>
       </c>
       <c r="P365" t="s">
         <v>244</v>
@@ -27323,27 +27320,27 @@
         <v>254</v>
       </c>
       <c r="S365">
-        <v>-3</v>
+        <v>-8</v>
       </c>
       <c r="T365" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="W365" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="AA365">
         <v>0</v>
       </c>
       <c r="AG365" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="366" spans="1:34">
       <c r="A366">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B366" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C366" t="s">
         <v>58</v>
@@ -27367,7 +27364,7 @@
         <v>72</v>
       </c>
       <c r="J366" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="L366" s="1">
         <v>46295</v>
@@ -27379,7 +27376,7 @@
         <v>219</v>
       </c>
       <c r="O366">
-        <v>17398859</v>
+        <v>16975890</v>
       </c>
       <c r="P366" t="s">
         <v>244</v>
@@ -27391,10 +27388,13 @@
         <v>-8</v>
       </c>
       <c r="T366" t="s">
-        <v>260</v>
+        <v>262</v>
+      </c>
+      <c r="V366" t="s">
+        <v>271</v>
       </c>
       <c r="W366" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="AA366">
         <v>0</v>
@@ -27405,16 +27405,16 @@
     </row>
     <row r="367" spans="1:34">
       <c r="A367">
-        <v>6486</v>
+        <v>6703</v>
       </c>
       <c r="B367" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C367" t="s">
         <v>58</v>
       </c>
       <c r="D367" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E367" t="s">
         <v>62</v>
@@ -27432,7 +27432,7 @@
         <v>72</v>
       </c>
       <c r="J367" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="L367" s="1">
         <v>46295</v>
@@ -27444,7 +27444,7 @@
         <v>219</v>
       </c>
       <c r="O367">
-        <v>16975890</v>
+        <v>17941122</v>
       </c>
       <c r="P367" t="s">
         <v>244</v>
@@ -27456,13 +27456,10 @@
         <v>-8</v>
       </c>
       <c r="T367" t="s">
-        <v>262</v>
-      </c>
-      <c r="V367" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="W367" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA367">
         <v>0</v>
@@ -27473,16 +27470,16 @@
     </row>
     <row r="368" spans="1:34">
       <c r="A368">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B368" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C368" t="s">
         <v>58</v>
       </c>
       <c r="D368" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E368" t="s">
         <v>62</v>
@@ -27500,7 +27497,7 @@
         <v>72</v>
       </c>
       <c r="J368" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="L368" s="1">
         <v>46295</v>
@@ -27512,7 +27509,7 @@
         <v>219</v>
       </c>
       <c r="O368">
-        <v>17941122</v>
+        <v>17952314</v>
       </c>
       <c r="P368" t="s">
         <v>244</v>
@@ -27524,10 +27521,13 @@
         <v>-8</v>
       </c>
       <c r="T368" t="s">
-        <v>263</v>
+        <v>261</v>
+      </c>
+      <c r="V368" t="s">
+        <v>271</v>
       </c>
       <c r="W368" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA368">
         <v>0</v>
@@ -27538,16 +27538,16 @@
     </row>
     <row r="369" spans="1:34">
       <c r="A369">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B369" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C369" t="s">
         <v>58</v>
       </c>
       <c r="D369" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E369" t="s">
         <v>62</v>
@@ -27565,7 +27565,7 @@
         <v>72</v>
       </c>
       <c r="J369" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="L369" s="1">
         <v>46295</v>
@@ -27577,7 +27577,7 @@
         <v>219</v>
       </c>
       <c r="O369">
-        <v>17952314</v>
+        <v>17952513</v>
       </c>
       <c r="P369" t="s">
         <v>244</v>
@@ -27591,11 +27591,8 @@
       <c r="T369" t="s">
         <v>261</v>
       </c>
-      <c r="V369" t="s">
-        <v>271</v>
-      </c>
       <c r="W369" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA369">
         <v>0</v>
@@ -27606,22 +27603,22 @@
     </row>
     <row r="370" spans="1:34">
       <c r="A370">
-        <v>6705</v>
+        <v>6949</v>
       </c>
       <c r="B370" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C370" t="s">
         <v>58</v>
       </c>
       <c r="D370" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E370" t="s">
         <v>62</v>
       </c>
       <c r="F370" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G370">
         <v>943</v>
@@ -27633,7 +27630,7 @@
         <v>72</v>
       </c>
       <c r="J370" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="L370" s="1">
         <v>46295</v>
@@ -27645,7 +27642,7 @@
         <v>219</v>
       </c>
       <c r="O370">
-        <v>17952513</v>
+        <v>18178126</v>
       </c>
       <c r="P370" t="s">
         <v>244</v>
@@ -27657,10 +27654,10 @@
         <v>-8</v>
       </c>
       <c r="T370" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="W370" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA370">
         <v>0</v>
@@ -27671,16 +27668,16 @@
     </row>
     <row r="371" spans="1:34">
       <c r="A371">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B371" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C371" t="s">
         <v>58</v>
       </c>
       <c r="D371" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E371" t="s">
         <v>62</v>
@@ -27698,7 +27695,7 @@
         <v>72</v>
       </c>
       <c r="J371" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="L371" s="1">
         <v>46295</v>
@@ -27710,7 +27707,7 @@
         <v>219</v>
       </c>
       <c r="O371">
-        <v>18178126</v>
+        <v>18188710</v>
       </c>
       <c r="P371" t="s">
         <v>244</v>
@@ -27722,10 +27719,10 @@
         <v>-8</v>
       </c>
       <c r="T371" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="W371" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA371">
         <v>0</v>
@@ -27736,10 +27733,10 @@
     </row>
     <row r="372" spans="1:34">
       <c r="A372">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B372" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C372" t="s">
         <v>58</v>
@@ -27763,7 +27760,7 @@
         <v>72</v>
       </c>
       <c r="J372" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="L372" s="1">
         <v>46295</v>
@@ -27775,7 +27772,7 @@
         <v>219</v>
       </c>
       <c r="O372">
-        <v>18188710</v>
+        <v>18188616</v>
       </c>
       <c r="P372" t="s">
         <v>244</v>
@@ -27790,7 +27787,7 @@
         <v>259</v>
       </c>
       <c r="W372" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA372">
         <v>0</v>
@@ -27801,58 +27798,58 @@
     </row>
     <row r="373" spans="1:34">
       <c r="A373">
-        <v>6963</v>
+        <v>5417</v>
       </c>
       <c r="B373" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C373" t="s">
         <v>58</v>
       </c>
       <c r="D373" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E373" t="s">
         <v>62</v>
       </c>
       <c r="F373" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G373">
-        <v>943</v>
+        <v>7877</v>
       </c>
       <c r="H373">
         <v>0</v>
       </c>
       <c r="I373" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J373" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="L373" s="1">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="M373" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="N373" t="s">
         <v>219</v>
       </c>
       <c r="O373">
-        <v>18188616</v>
+        <v>17399330</v>
       </c>
       <c r="P373" t="s">
-        <v>244</v>
+        <v>62</v>
       </c>
       <c r="Q373" t="s">
         <v>254</v>
       </c>
       <c r="S373">
-        <v>-8</v>
+        <v>-3</v>
       </c>
       <c r="T373" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="W373" t="s">
         <v>374</v>
@@ -27884,37 +27881,37 @@
         <v>64</v>
       </c>
       <c r="G374">
-        <v>7877</v>
+        <v>11056</v>
       </c>
       <c r="H374">
         <v>0</v>
       </c>
       <c r="I374" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J374" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="L374" s="1">
-        <v>46290</v>
+        <v>46287</v>
       </c>
       <c r="M374" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="N374" t="s">
         <v>219</v>
       </c>
       <c r="O374">
-        <v>17399330</v>
+        <v>18275526</v>
       </c>
       <c r="P374" t="s">
-        <v>62</v>
+        <v>248</v>
       </c>
       <c r="Q374" t="s">
         <v>254</v>
       </c>
       <c r="S374">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="T374" t="s">
         <v>260</v>
@@ -27931,10 +27928,10 @@
     </row>
     <row r="375" spans="1:34">
       <c r="A375">
-        <v>5417</v>
+        <v>6949</v>
       </c>
       <c r="B375" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C375" t="s">
         <v>58</v>
@@ -27946,7 +27943,7 @@
         <v>62</v>
       </c>
       <c r="F375" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G375">
         <v>11056</v>
@@ -27961,16 +27958,16 @@
         <v>130</v>
       </c>
       <c r="L375" s="1">
-        <v>46287</v>
+        <v>46293</v>
       </c>
       <c r="M375" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="N375" t="s">
         <v>219</v>
       </c>
       <c r="O375">
-        <v>18275526</v>
+        <v>18279142</v>
       </c>
       <c r="P375" t="s">
         <v>248</v>
@@ -27979,10 +27976,10 @@
         <v>254</v>
       </c>
       <c r="S375">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="T375" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="W375" t="s">
         <v>376</v>
@@ -27996,16 +27993,16 @@
     </row>
     <row r="376" spans="1:34">
       <c r="A376">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B376" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C376" t="s">
         <v>58</v>
       </c>
       <c r="D376" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E376" t="s">
         <v>62</v>
@@ -28026,16 +28023,16 @@
         <v>130</v>
       </c>
       <c r="L376" s="1">
-        <v>46293</v>
+        <v>46287</v>
       </c>
       <c r="M376" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N376" t="s">
         <v>219</v>
       </c>
       <c r="O376">
-        <v>18279142</v>
+        <v>18274091</v>
       </c>
       <c r="P376" t="s">
         <v>248</v>
@@ -28044,10 +28041,10 @@
         <v>254</v>
       </c>
       <c r="S376">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="T376" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="W376" t="s">
         <v>377</v>
@@ -28061,75 +28058,81 @@
     </row>
     <row r="377" spans="1:34">
       <c r="A377">
-        <v>6962</v>
+        <v>6628</v>
       </c>
       <c r="B377" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C377" t="s">
         <v>58</v>
       </c>
       <c r="D377" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E377" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F377" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G377">
-        <v>11056</v>
+        <v>1650</v>
       </c>
       <c r="H377">
         <v>0</v>
       </c>
       <c r="I377" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="J377" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="L377" s="1">
-        <v>46287</v>
-      </c>
-      <c r="M377" t="s">
-        <v>208</v>
+        <v>46293</v>
       </c>
       <c r="N377" t="s">
         <v>219</v>
       </c>
       <c r="O377">
-        <v>18274091</v>
+        <v>16959974</v>
       </c>
       <c r="P377" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="Q377" t="s">
-        <v>254</v>
+        <v>252</v>
+      </c>
+      <c r="R377" s="1">
+        <v>46265.00248284722</v>
       </c>
       <c r="S377">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="T377" t="s">
-        <v>259</v>
-      </c>
-      <c r="W377" t="s">
-        <v>378</v>
+        <v>256</v>
+      </c>
+      <c r="V377" t="s">
+        <v>271</v>
       </c>
       <c r="AA377">
         <v>0</v>
+      </c>
+      <c r="AB377" t="s">
+        <v>465</v>
       </c>
       <c r="AG377" t="s">
         <v>471</v>
       </c>
+      <c r="AH377" t="s">
+        <v>475</v>
+      </c>
     </row>
     <row r="378" spans="1:34">
       <c r="A378">
-        <v>6628</v>
+        <v>6945</v>
       </c>
       <c r="B378" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C378" t="s">
         <v>58</v>
@@ -28138,10 +28141,10 @@
         <v>60</v>
       </c>
       <c r="E378" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F378" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G378">
         <v>1650</v>
@@ -28153,7 +28156,7 @@
         <v>67</v>
       </c>
       <c r="J378" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L378" s="1">
         <v>46293</v>
@@ -28162,25 +28165,22 @@
         <v>219</v>
       </c>
       <c r="O378">
-        <v>16959974</v>
+        <v>18163667</v>
       </c>
       <c r="P378" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q378" t="s">
         <v>252</v>
       </c>
       <c r="R378" s="1">
-        <v>46265.00248284722</v>
+        <v>46265.00255472222</v>
       </c>
       <c r="S378">
         <v>-6</v>
       </c>
       <c r="T378" t="s">
-        <v>256</v>
-      </c>
-      <c r="V378" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="AA378">
         <v>0</v>
@@ -28197,25 +28197,25 @@
     </row>
     <row r="379" spans="1:34">
       <c r="A379">
-        <v>6945</v>
+        <v>6548</v>
       </c>
       <c r="B379" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C379" t="s">
         <v>58</v>
       </c>
       <c r="D379" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E379" t="s">
         <v>62</v>
       </c>
       <c r="F379" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G379">
-        <v>1650</v>
+        <v>1652</v>
       </c>
       <c r="H379">
         <v>0</v>
@@ -28227,28 +28227,34 @@
         <v>150</v>
       </c>
       <c r="L379" s="1">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="N379" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="O379">
-        <v>18163667</v>
+        <v>17967989</v>
       </c>
       <c r="P379" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="Q379" t="s">
         <v>252</v>
       </c>
       <c r="R379" s="1">
-        <v>46265.00255472222</v>
+        <v>46234.66180127315</v>
       </c>
       <c r="S379">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="T379" t="s">
-        <v>257</v>
+        <v>255</v>
+      </c>
+      <c r="V379" t="s">
+        <v>271</v>
+      </c>
+      <c r="W379" t="s">
+        <v>378</v>
       </c>
       <c r="AA379">
         <v>0</v>
@@ -28257,18 +28263,18 @@
         <v>465</v>
       </c>
       <c r="AG379" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH379" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="380" spans="1:34">
       <c r="A380">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B380" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C380" t="s">
         <v>58</v>
@@ -28277,7 +28283,7 @@
         <v>59</v>
       </c>
       <c r="E380" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F380" t="s">
         <v>64</v>
@@ -28292,7 +28298,7 @@
         <v>67</v>
       </c>
       <c r="J380" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L380" s="1">
         <v>46290</v>
@@ -28301,22 +28307,22 @@
         <v>222</v>
       </c>
       <c r="O380">
-        <v>17967989</v>
+        <v>17042389</v>
       </c>
       <c r="P380" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q380" t="s">
         <v>252</v>
       </c>
       <c r="R380" s="1">
-        <v>46234.66180127315</v>
+        <v>46245.76585582176</v>
       </c>
       <c r="S380">
         <v>-3</v>
       </c>
       <c r="T380" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="V380" t="s">
         <v>271</v>
@@ -28334,15 +28340,15 @@
         <v>472</v>
       </c>
       <c r="AH380" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="381" spans="1:34">
       <c r="A381">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B381" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C381" t="s">
         <v>58</v>
@@ -28351,16 +28357,16 @@
         <v>59</v>
       </c>
       <c r="E381" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F381" t="s">
         <v>64</v>
       </c>
       <c r="G381">
-        <v>1652</v>
+        <v>1697</v>
       </c>
       <c r="H381">
-        <v>0</v>
+        <v>1650</v>
       </c>
       <c r="I381" t="s">
         <v>67</v>
@@ -28369,54 +28375,51 @@
         <v>151</v>
       </c>
       <c r="L381" s="1">
-        <v>46290</v>
+        <v>46286</v>
       </c>
       <c r="N381" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O381">
-        <v>17042389</v>
+        <v>17968001</v>
       </c>
       <c r="P381" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q381" t="s">
         <v>252</v>
       </c>
       <c r="R381" s="1">
-        <v>46245.76585582176</v>
+        <v>46282.62254486111</v>
       </c>
       <c r="S381">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="T381" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="V381" t="s">
         <v>271</v>
       </c>
-      <c r="W381" t="s">
-        <v>380</v>
-      </c>
       <c r="AA381">
         <v>0</v>
       </c>
       <c r="AB381" t="s">
-        <v>465</v>
+        <v>224</v>
       </c>
       <c r="AG381" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AH381" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="382" spans="1:34">
       <c r="A382">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B382" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C382" t="s">
         <v>58</v>
@@ -28425,7 +28428,7 @@
         <v>59</v>
       </c>
       <c r="E382" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F382" t="s">
         <v>64</v>
@@ -28440,54 +28443,60 @@
         <v>67</v>
       </c>
       <c r="J382" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L382" s="1">
         <v>46286</v>
       </c>
+      <c r="M382" t="s">
+        <v>215</v>
+      </c>
       <c r="N382" t="s">
         <v>219</v>
       </c>
       <c r="O382">
-        <v>17968001</v>
+        <v>17042403</v>
       </c>
       <c r="P382" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q382" t="s">
         <v>252</v>
       </c>
       <c r="R382" s="1">
-        <v>46282.62254486111</v>
+        <v>46286.64173940972</v>
       </c>
       <c r="S382">
         <v>1</v>
       </c>
       <c r="T382" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="V382" t="s">
         <v>271</v>
       </c>
+      <c r="W382" t="s">
+        <v>380</v>
+      </c>
       <c r="AA382">
         <v>0</v>
       </c>
       <c r="AB382" t="s">
-        <v>224</v>
+        <v>467</v>
       </c>
       <c r="AG382" t="s">
         <v>471</v>
       </c>
       <c r="AH382" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="383" spans="1:34">
       <c r="A383">
-        <v>6627</v>
+        <v>6949</v>
       </c>
       <c r="B383" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C383" t="s">
         <v>58</v>
@@ -28496,10 +28505,10 @@
         <v>59</v>
       </c>
       <c r="E383" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F383" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G383">
         <v>1697</v>
@@ -28511,60 +28520,51 @@
         <v>67</v>
       </c>
       <c r="J383" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L383" s="1">
         <v>46286</v>
       </c>
-      <c r="M383" t="s">
-        <v>215</v>
-      </c>
       <c r="N383" t="s">
         <v>219</v>
       </c>
       <c r="O383">
-        <v>17042403</v>
+        <v>18178280</v>
       </c>
       <c r="P383" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q383" t="s">
         <v>252</v>
       </c>
       <c r="R383" s="1">
-        <v>46286.64173940972</v>
+        <v>46283.44840582176</v>
       </c>
       <c r="S383">
         <v>1</v>
       </c>
       <c r="T383" t="s">
-        <v>256</v>
-      </c>
-      <c r="V383" t="s">
-        <v>271</v>
-      </c>
-      <c r="W383" t="s">
-        <v>381</v>
+        <v>258</v>
       </c>
       <c r="AA383">
         <v>0</v>
       </c>
       <c r="AB383" t="s">
-        <v>467</v>
+        <v>224</v>
       </c>
       <c r="AG383" t="s">
         <v>471</v>
       </c>
       <c r="AH383" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="384" spans="1:34">
       <c r="A384">
-        <v>6949</v>
+        <v>6704</v>
       </c>
       <c r="B384" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C384" t="s">
         <v>58</v>
@@ -28576,63 +28576,66 @@
         <v>62</v>
       </c>
       <c r="F384" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G384">
-        <v>1697</v>
+        <v>7868</v>
       </c>
       <c r="H384">
-        <v>1650</v>
+        <v>0</v>
       </c>
       <c r="I384" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J384" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="L384" s="1">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="N384" t="s">
         <v>219</v>
       </c>
       <c r="O384">
-        <v>18178280</v>
+        <v>17955421</v>
       </c>
       <c r="P384" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="Q384" t="s">
         <v>252</v>
       </c>
       <c r="R384" s="1">
-        <v>46283.44840582176</v>
+        <v>46267.47365627315</v>
       </c>
       <c r="S384">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="T384" t="s">
-        <v>258</v>
+        <v>261</v>
+      </c>
+      <c r="V384" t="s">
+        <v>271</v>
       </c>
       <c r="AA384">
         <v>0</v>
       </c>
       <c r="AB384" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="AG384" t="s">
         <v>471</v>
       </c>
       <c r="AH384" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="385" spans="1:34">
       <c r="A385">
-        <v>6704</v>
+        <v>5417</v>
       </c>
       <c r="B385" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C385" t="s">
         <v>58</v>
@@ -28647,7 +28650,7 @@
         <v>64</v>
       </c>
       <c r="G385">
-        <v>7868</v>
+        <v>11276</v>
       </c>
       <c r="H385">
         <v>0</v>
@@ -28656,54 +28659,51 @@
         <v>68</v>
       </c>
       <c r="J385" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="L385" s="1">
-        <v>46293</v>
+        <v>46283</v>
       </c>
       <c r="N385" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O385">
-        <v>17955421</v>
+        <v>17399423</v>
       </c>
       <c r="P385" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Q385" t="s">
         <v>252</v>
       </c>
       <c r="R385" s="1">
-        <v>46267.47365627315</v>
+        <v>46266.47620831019</v>
       </c>
       <c r="S385">
-        <v>-6</v>
+        <v>4</v>
       </c>
       <c r="T385" t="s">
-        <v>261</v>
-      </c>
-      <c r="V385" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="AA385">
         <v>0</v>
       </c>
       <c r="AB385" t="s">
-        <v>229</v>
+        <v>468</v>
       </c>
       <c r="AG385" t="s">
         <v>471</v>
       </c>
       <c r="AH385" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="386" spans="1:34">
       <c r="A386">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B386" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C386" t="s">
         <v>58</v>
@@ -28727,7 +28727,7 @@
         <v>68</v>
       </c>
       <c r="J386" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="L386" s="1">
         <v>46283</v>
@@ -28736,28 +28736,31 @@
         <v>221</v>
       </c>
       <c r="O386">
-        <v>17399423</v>
+        <v>18152557</v>
       </c>
       <c r="P386" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="Q386" t="s">
         <v>252</v>
       </c>
       <c r="R386" s="1">
-        <v>46266.47620831019</v>
+        <v>46267.57586420139</v>
       </c>
       <c r="S386">
         <v>4</v>
       </c>
       <c r="T386" t="s">
-        <v>260</v>
+        <v>262</v>
+      </c>
+      <c r="V386" t="s">
+        <v>271</v>
       </c>
       <c r="AA386">
         <v>0</v>
       </c>
       <c r="AB386" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG386" t="s">
         <v>471</v>
@@ -28768,10 +28771,10 @@
     </row>
     <row r="387" spans="1:34">
       <c r="A387">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B387" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C387" t="s">
         <v>58</v>
@@ -28786,7 +28789,7 @@
         <v>64</v>
       </c>
       <c r="G387">
-        <v>11276</v>
+        <v>1583</v>
       </c>
       <c r="H387">
         <v>0</v>
@@ -28795,43 +28798,40 @@
         <v>68</v>
       </c>
       <c r="J387" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="L387" s="1">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="N387" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O387">
-        <v>18152557</v>
+        <v>17398917</v>
       </c>
       <c r="P387" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="Q387" t="s">
         <v>252</v>
       </c>
       <c r="R387" s="1">
-        <v>46267.57586420139</v>
+        <v>46233.72355880787</v>
       </c>
       <c r="S387">
-        <v>4</v>
+        <v>-3</v>
       </c>
       <c r="T387" t="s">
-        <v>262</v>
-      </c>
-      <c r="V387" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="AA387">
         <v>0</v>
       </c>
       <c r="AB387" t="s">
-        <v>469</v>
+        <v>228</v>
       </c>
       <c r="AG387" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH387" t="s">
         <v>476</v>
@@ -28839,10 +28839,10 @@
     </row>
     <row r="388" spans="1:34">
       <c r="A388">
-        <v>5417</v>
+        <v>5617</v>
       </c>
       <c r="B388" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C388" t="s">
         <v>58</v>
@@ -28866,7 +28866,7 @@
         <v>68</v>
       </c>
       <c r="J388" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L388" s="1">
         <v>46290</v>
@@ -28875,42 +28875,36 @@
         <v>222</v>
       </c>
       <c r="O388">
-        <v>17398917</v>
-      </c>
-      <c r="P388" t="s">
-        <v>228</v>
+        <v>17407553</v>
       </c>
       <c r="Q388" t="s">
         <v>252</v>
       </c>
       <c r="R388" s="1">
-        <v>46233.72355880787</v>
+        <v>46261.36669849537</v>
       </c>
       <c r="S388">
         <v>-3</v>
       </c>
       <c r="T388" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="AA388">
         <v>0</v>
       </c>
       <c r="AB388" t="s">
-        <v>228</v>
+        <v>462</v>
       </c>
       <c r="AG388" t="s">
         <v>472</v>
       </c>
-      <c r="AH388" t="s">
-        <v>476</v>
-      </c>
     </row>
     <row r="389" spans="1:34">
       <c r="A389">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B389" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C389" t="s">
         <v>58</v>
@@ -28922,7 +28916,7 @@
         <v>62</v>
       </c>
       <c r="F389" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G389">
         <v>1583</v>
@@ -28934,7 +28928,7 @@
         <v>68</v>
       </c>
       <c r="J389" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L389" s="1">
         <v>46290</v>
@@ -28943,13 +28937,13 @@
         <v>222</v>
       </c>
       <c r="O389">
-        <v>17407553</v>
+        <v>17688645</v>
       </c>
       <c r="Q389" t="s">
         <v>252</v>
       </c>
       <c r="R389" s="1">
-        <v>46261.36669849537</v>
+        <v>46266.44156952546</v>
       </c>
       <c r="S389">
         <v>-3</v>
@@ -28957,11 +28951,14 @@
       <c r="T389" t="s">
         <v>265</v>
       </c>
+      <c r="V389" t="s">
+        <v>271</v>
+      </c>
       <c r="AA389">
         <v>0</v>
       </c>
       <c r="AB389" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AG389" t="s">
         <v>472</v>
@@ -28969,10 +28966,10 @@
     </row>
     <row r="390" spans="1:34">
       <c r="A390">
-        <v>6224</v>
+        <v>6278</v>
       </c>
       <c r="B390" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C390" t="s">
         <v>58</v>
@@ -28984,7 +28981,7 @@
         <v>62</v>
       </c>
       <c r="F390" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G390">
         <v>1583</v>
@@ -28996,7 +28993,7 @@
         <v>68</v>
       </c>
       <c r="J390" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L390" s="1">
         <v>46290</v>
@@ -29005,28 +29002,31 @@
         <v>222</v>
       </c>
       <c r="O390">
-        <v>17688645</v>
+        <v>18166312</v>
       </c>
       <c r="Q390" t="s">
         <v>252</v>
       </c>
       <c r="R390" s="1">
-        <v>46266.44156952546</v>
+        <v>46233.50562820602</v>
       </c>
       <c r="S390">
         <v>-3</v>
       </c>
       <c r="T390" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="V390" t="s">
         <v>271</v>
       </c>
+      <c r="W390" t="s">
+        <v>381</v>
+      </c>
       <c r="AA390">
         <v>0</v>
       </c>
       <c r="AB390" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="AG390" t="s">
         <v>472</v>
@@ -29034,10 +29034,10 @@
     </row>
     <row r="391" spans="1:34">
       <c r="A391">
-        <v>6278</v>
+        <v>6486</v>
       </c>
       <c r="B391" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C391" t="s">
         <v>58</v>
@@ -29061,7 +29061,7 @@
         <v>68</v>
       </c>
       <c r="J391" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L391" s="1">
         <v>46290</v>
@@ -29070,42 +29070,45 @@
         <v>222</v>
       </c>
       <c r="O391">
-        <v>18166312</v>
+        <v>18114208</v>
+      </c>
+      <c r="P391" t="s">
+        <v>246</v>
       </c>
       <c r="Q391" t="s">
         <v>252</v>
       </c>
       <c r="R391" s="1">
-        <v>46233.50562820602</v>
+        <v>46233.80164280093</v>
       </c>
       <c r="S391">
         <v>-3</v>
       </c>
       <c r="T391" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="V391" t="s">
         <v>271</v>
       </c>
-      <c r="W391" t="s">
-        <v>382</v>
-      </c>
       <c r="AA391">
         <v>0</v>
       </c>
       <c r="AB391" t="s">
-        <v>465</v>
+        <v>246</v>
       </c>
       <c r="AG391" t="s">
         <v>472</v>
       </c>
+      <c r="AH391" t="s">
+        <v>476</v>
+      </c>
     </row>
     <row r="392" spans="1:34">
       <c r="A392">
-        <v>6486</v>
+        <v>6704</v>
       </c>
       <c r="B392" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C392" t="s">
         <v>58</v>
@@ -29129,7 +29132,7 @@
         <v>68</v>
       </c>
       <c r="J392" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L392" s="1">
         <v>46290</v>
@@ -29138,22 +29141,22 @@
         <v>222</v>
       </c>
       <c r="O392">
-        <v>18114208</v>
+        <v>17955373</v>
       </c>
       <c r="P392" t="s">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="Q392" t="s">
         <v>252</v>
       </c>
       <c r="R392" s="1">
-        <v>46233.80164280093</v>
+        <v>46232.72913953703</v>
       </c>
       <c r="S392">
         <v>-3</v>
       </c>
       <c r="T392" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="V392" t="s">
         <v>271</v>
@@ -29162,21 +29165,21 @@
         <v>0</v>
       </c>
       <c r="AB392" t="s">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="AG392" t="s">
         <v>472</v>
       </c>
       <c r="AH392" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="393" spans="1:34">
       <c r="A393">
-        <v>6704</v>
+        <v>5417</v>
       </c>
       <c r="B393" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C393" t="s">
         <v>58</v>
@@ -29191,7 +29194,7 @@
         <v>64</v>
       </c>
       <c r="G393">
-        <v>1583</v>
+        <v>7874</v>
       </c>
       <c r="H393">
         <v>0</v>
@@ -29200,46 +29203,46 @@
         <v>68</v>
       </c>
       <c r="J393" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="L393" s="1">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="N393" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O393">
-        <v>17955373</v>
+        <v>17399320</v>
       </c>
       <c r="P393" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Q393" t="s">
         <v>252</v>
       </c>
       <c r="R393" s="1">
-        <v>46232.72913953703</v>
+        <v>46283.6781059838</v>
       </c>
       <c r="S393">
-        <v>-3</v>
+        <v>-8</v>
       </c>
       <c r="T393" t="s">
-        <v>261</v>
-      </c>
-      <c r="V393" t="s">
-        <v>271</v>
+        <v>260</v>
+      </c>
+      <c r="W393" t="s">
+        <v>382</v>
       </c>
       <c r="AA393">
         <v>0</v>
       </c>
       <c r="AB393" t="s">
-        <v>229</v>
+        <v>465</v>
       </c>
       <c r="AG393" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AH393" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="394" spans="1:34">
@@ -29262,25 +29265,25 @@
         <v>64</v>
       </c>
       <c r="G394">
-        <v>7874</v>
+        <v>1628</v>
       </c>
       <c r="H394">
-        <v>0</v>
+        <v>1581</v>
       </c>
       <c r="I394" t="s">
         <v>68</v>
       </c>
       <c r="J394" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="L394" s="1">
-        <v>46295</v>
+        <v>46286</v>
       </c>
       <c r="N394" t="s">
         <v>219</v>
       </c>
       <c r="O394">
-        <v>17399320</v>
+        <v>17398925</v>
       </c>
       <c r="P394" t="s">
         <v>228</v>
@@ -29289,22 +29292,19 @@
         <v>252</v>
       </c>
       <c r="R394" s="1">
-        <v>46283.6781059838</v>
+        <v>46280.37528408565</v>
       </c>
       <c r="S394">
-        <v>-8</v>
+        <v>1</v>
       </c>
       <c r="T394" t="s">
         <v>260</v>
       </c>
-      <c r="W394" t="s">
-        <v>383</v>
-      </c>
       <c r="AA394">
         <v>0</v>
       </c>
       <c r="AB394" t="s">
-        <v>465</v>
+        <v>228</v>
       </c>
       <c r="AG394" t="s">
         <v>471</v>
@@ -29315,16 +29315,16 @@
     </row>
     <row r="395" spans="1:34">
       <c r="A395">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B395" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C395" t="s">
         <v>58</v>
       </c>
       <c r="D395" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E395" t="s">
         <v>62</v>
@@ -29342,7 +29342,7 @@
         <v>68</v>
       </c>
       <c r="J395" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L395" s="1">
         <v>46286</v>
@@ -29351,42 +29351,42 @@
         <v>219</v>
       </c>
       <c r="O395">
-        <v>17398925</v>
+        <v>16962141</v>
       </c>
       <c r="P395" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="Q395" t="s">
         <v>252</v>
       </c>
       <c r="R395" s="1">
-        <v>46280.37528408565</v>
+        <v>46266.37634084491</v>
       </c>
       <c r="S395">
         <v>1</v>
       </c>
       <c r="T395" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="AA395">
         <v>0</v>
       </c>
       <c r="AB395" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="AG395" t="s">
         <v>471</v>
       </c>
       <c r="AH395" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="396" spans="1:34">
       <c r="A396">
-        <v>6404</v>
+        <v>6703</v>
       </c>
       <c r="B396" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C396" t="s">
         <v>58</v>
@@ -29410,7 +29410,7 @@
         <v>68</v>
       </c>
       <c r="J396" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L396" s="1">
         <v>46286</v>
@@ -29419,48 +29419,48 @@
         <v>219</v>
       </c>
       <c r="O396">
-        <v>16962141</v>
+        <v>17955176</v>
       </c>
       <c r="P396" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q396" t="s">
         <v>252</v>
       </c>
       <c r="R396" s="1">
-        <v>46266.37634084491</v>
+        <v>46282.42251184028</v>
       </c>
       <c r="S396">
         <v>1</v>
       </c>
       <c r="T396" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AA396">
         <v>0</v>
       </c>
       <c r="AB396" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AG396" t="s">
         <v>471</v>
       </c>
       <c r="AH396" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="397" spans="1:34">
       <c r="A397">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B397" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C397" t="s">
         <v>58</v>
       </c>
       <c r="D397" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E397" t="s">
         <v>62</v>
@@ -29478,7 +29478,7 @@
         <v>68</v>
       </c>
       <c r="J397" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L397" s="1">
         <v>46286</v>
@@ -29487,48 +29487,51 @@
         <v>219</v>
       </c>
       <c r="O397">
-        <v>17955176</v>
+        <v>17955384</v>
       </c>
       <c r="P397" t="s">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="Q397" t="s">
         <v>252</v>
       </c>
       <c r="R397" s="1">
-        <v>46282.42251184028</v>
+        <v>46267.47452163194</v>
       </c>
       <c r="S397">
         <v>1</v>
       </c>
       <c r="T397" t="s">
-        <v>263</v>
+        <v>261</v>
+      </c>
+      <c r="V397" t="s">
+        <v>271</v>
       </c>
       <c r="AA397">
         <v>0</v>
       </c>
       <c r="AB397" t="s">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="AG397" t="s">
         <v>471</v>
       </c>
       <c r="AH397" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="398" spans="1:34">
       <c r="A398">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B398" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C398" t="s">
         <v>58</v>
       </c>
       <c r="D398" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E398" t="s">
         <v>62</v>
@@ -29546,7 +29549,7 @@
         <v>68</v>
       </c>
       <c r="J398" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L398" s="1">
         <v>46286</v>
@@ -29555,7 +29558,7 @@
         <v>219</v>
       </c>
       <c r="O398">
-        <v>17955384</v>
+        <v>17955238</v>
       </c>
       <c r="P398" t="s">
         <v>229</v>
@@ -29564,7 +29567,7 @@
         <v>252</v>
       </c>
       <c r="R398" s="1">
-        <v>46267.47452163194</v>
+        <v>46267.4745221412</v>
       </c>
       <c r="S398">
         <v>1</v>
@@ -29572,9 +29575,6 @@
       <c r="T398" t="s">
         <v>261</v>
       </c>
-      <c r="V398" t="s">
-        <v>271</v>
-      </c>
       <c r="AA398">
         <v>0</v>
       </c>
@@ -29590,10 +29590,10 @@
     </row>
     <row r="399" spans="1:34">
       <c r="A399">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B399" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C399" t="s">
         <v>58</v>
@@ -29617,7 +29617,7 @@
         <v>68</v>
       </c>
       <c r="J399" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L399" s="1">
         <v>46286</v>
@@ -29626,7 +29626,7 @@
         <v>219</v>
       </c>
       <c r="O399">
-        <v>17955238</v>
+        <v>18056729</v>
       </c>
       <c r="P399" t="s">
         <v>229</v>
@@ -29635,7 +29635,7 @@
         <v>252</v>
       </c>
       <c r="R399" s="1">
-        <v>46267.4745221412</v>
+        <v>46267.47452299768</v>
       </c>
       <c r="S399">
         <v>1</v>
@@ -29643,6 +29643,9 @@
       <c r="T399" t="s">
         <v>261</v>
       </c>
+      <c r="V399" t="s">
+        <v>271</v>
+      </c>
       <c r="AA399">
         <v>0</v>
       </c>
@@ -29658,87 +29661,93 @@
     </row>
     <row r="400" spans="1:34">
       <c r="A400">
-        <v>6779</v>
+        <v>6627</v>
       </c>
       <c r="B400" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="C400" t="s">
         <v>58</v>
       </c>
       <c r="D400" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E400" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F400" t="s">
         <v>64</v>
       </c>
       <c r="G400">
-        <v>1628</v>
+        <v>5885</v>
       </c>
       <c r="H400">
-        <v>1581</v>
+        <v>5784</v>
       </c>
       <c r="I400" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J400" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L400" s="1">
-        <v>46286</v>
+        <v>46283</v>
+      </c>
+      <c r="M400" t="s">
+        <v>216</v>
       </c>
       <c r="N400" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O400">
-        <v>18056729</v>
+        <v>18068566</v>
       </c>
       <c r="P400" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q400" t="s">
         <v>252</v>
       </c>
       <c r="R400" s="1">
-        <v>46267.47452299768</v>
+        <v>46281.63558861111</v>
       </c>
       <c r="S400">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T400" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="V400" t="s">
         <v>271</v>
       </c>
+      <c r="W400" t="s">
+        <v>383</v>
+      </c>
       <c r="AA400">
         <v>0</v>
       </c>
       <c r="AB400" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG400" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH400" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="401" spans="1:34">
       <c r="A401">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B401" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C401" t="s">
         <v>58</v>
       </c>
       <c r="D401" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E401" t="s">
         <v>63</v>
@@ -29756,7 +29765,7 @@
         <v>69</v>
       </c>
       <c r="J401" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L401" s="1">
         <v>46283</v>
@@ -29768,7 +29777,7 @@
         <v>220</v>
       </c>
       <c r="O401">
-        <v>18068566</v>
+        <v>18052485</v>
       </c>
       <c r="P401" t="s">
         <v>230</v>
@@ -29777,7 +29786,7 @@
         <v>252</v>
       </c>
       <c r="R401" s="1">
-        <v>46281.63558861111</v>
+        <v>46281.6358927662</v>
       </c>
       <c r="S401">
         <v>4</v>
@@ -29789,7 +29798,7 @@
         <v>271</v>
       </c>
       <c r="W401" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AA401">
         <v>0</v>
@@ -29806,10 +29815,10 @@
     </row>
     <row r="402" spans="1:34">
       <c r="A402">
-        <v>6628</v>
+        <v>6945</v>
       </c>
       <c r="B402" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C402" t="s">
         <v>58</v>
@@ -29818,10 +29827,10 @@
         <v>60</v>
       </c>
       <c r="E402" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F402" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G402">
         <v>5885</v>
@@ -29833,37 +29842,34 @@
         <v>69</v>
       </c>
       <c r="J402" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L402" s="1">
         <v>46283</v>
       </c>
       <c r="M402" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N402" t="s">
         <v>220</v>
       </c>
       <c r="O402">
-        <v>18052485</v>
+        <v>18206577</v>
       </c>
       <c r="P402" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q402" t="s">
         <v>252</v>
       </c>
       <c r="R402" s="1">
-        <v>46281.6358927662</v>
+        <v>46281.47564895833</v>
       </c>
       <c r="S402">
         <v>4</v>
       </c>
       <c r="T402" t="s">
-        <v>256</v>
-      </c>
-      <c r="V402" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="W402" t="s">
         <v>384</v>
@@ -29872,7 +29878,7 @@
         <v>0</v>
       </c>
       <c r="AB402" t="s">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="AG402" t="s">
         <v>472</v>
@@ -29883,28 +29889,28 @@
     </row>
     <row r="403" spans="1:34">
       <c r="A403">
-        <v>6945</v>
+        <v>6703</v>
       </c>
       <c r="B403" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C403" t="s">
         <v>58</v>
       </c>
       <c r="D403" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E403" t="s">
         <v>62</v>
       </c>
       <c r="F403" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G403">
-        <v>5885</v>
+        <v>6395</v>
       </c>
       <c r="H403">
-        <v>5784</v>
+        <v>5792</v>
       </c>
       <c r="I403" t="s">
         <v>69</v>
@@ -29915,41 +29921,35 @@
       <c r="L403" s="1">
         <v>46283</v>
       </c>
-      <c r="M403" t="s">
-        <v>217</v>
-      </c>
       <c r="N403" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O403">
-        <v>18206577</v>
+        <v>18105120</v>
       </c>
       <c r="P403" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q403" t="s">
         <v>252</v>
       </c>
       <c r="R403" s="1">
-        <v>46281.47564895833</v>
+        <v>46268.58940019676</v>
       </c>
       <c r="S403">
         <v>4</v>
       </c>
       <c r="T403" t="s">
-        <v>257</v>
-      </c>
-      <c r="W403" t="s">
-        <v>385</v>
+        <v>263</v>
       </c>
       <c r="AA403">
         <v>0</v>
       </c>
       <c r="AB403" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="AG403" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AH403" t="s">
         <v>478</v>
@@ -29957,16 +29957,16 @@
     </row>
     <row r="404" spans="1:34">
       <c r="A404">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B404" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C404" t="s">
         <v>58</v>
       </c>
       <c r="D404" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E404" t="s">
         <v>62</v>
@@ -29975,7 +29975,7 @@
         <v>64</v>
       </c>
       <c r="G404">
-        <v>6395</v>
+        <v>5882</v>
       </c>
       <c r="H404">
         <v>5792</v>
@@ -29989,52 +29989,61 @@
       <c r="L404" s="1">
         <v>46283</v>
       </c>
+      <c r="M404" t="s">
+        <v>217</v>
+      </c>
       <c r="N404" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O404">
-        <v>18105120</v>
+        <v>18195621</v>
       </c>
       <c r="P404" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q404" t="s">
         <v>252</v>
       </c>
       <c r="R404" s="1">
-        <v>46268.58940019676</v>
+        <v>46279.66710767361</v>
       </c>
       <c r="S404">
         <v>4</v>
       </c>
       <c r="T404" t="s">
-        <v>263</v>
+        <v>261</v>
+      </c>
+      <c r="V404" t="s">
+        <v>271</v>
+      </c>
+      <c r="W404" t="s">
+        <v>385</v>
       </c>
       <c r="AA404">
         <v>0</v>
       </c>
       <c r="AB404" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG404" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH404" t="s">
-        <v>478</v>
+        <v>463</v>
       </c>
     </row>
     <row r="405" spans="1:34">
       <c r="A405">
-        <v>6779</v>
+        <v>5417</v>
       </c>
       <c r="B405" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C405" t="s">
         <v>58</v>
       </c>
       <c r="D405" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E405" t="s">
         <v>62</v>
@@ -30043,7 +30052,7 @@
         <v>64</v>
       </c>
       <c r="G405">
-        <v>5882</v>
+        <v>5883</v>
       </c>
       <c r="H405">
         <v>5792</v>
@@ -30052,60 +30061,48 @@
         <v>69</v>
       </c>
       <c r="J405" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="L405" s="1">
-        <v>46283</v>
-      </c>
-      <c r="M405" t="s">
-        <v>217</v>
+        <v>46286</v>
       </c>
       <c r="N405" t="s">
         <v>220</v>
       </c>
       <c r="O405">
-        <v>18195621</v>
+        <v>17399067</v>
       </c>
       <c r="P405" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="Q405" t="s">
         <v>252</v>
       </c>
       <c r="R405" s="1">
-        <v>46279.66710767361</v>
+        <v>46282.47420876157</v>
       </c>
       <c r="S405">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T405" t="s">
-        <v>261</v>
-      </c>
-      <c r="V405" t="s">
-        <v>271</v>
-      </c>
-      <c r="W405" t="s">
-        <v>386</v>
+        <v>260</v>
       </c>
       <c r="AA405">
         <v>0</v>
       </c>
       <c r="AB405" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="AG405" t="s">
-        <v>472</v>
-      </c>
-      <c r="AH405" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
     </row>
     <row r="406" spans="1:34">
       <c r="A406">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B406" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C406" t="s">
         <v>58</v>
@@ -30134,43 +30131,55 @@
       <c r="L406" s="1">
         <v>46286</v>
       </c>
+      <c r="M406" t="s">
+        <v>218</v>
+      </c>
       <c r="N406" t="s">
         <v>220</v>
       </c>
       <c r="O406">
-        <v>17399067</v>
+        <v>16976067</v>
       </c>
       <c r="P406" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="Q406" t="s">
         <v>252</v>
       </c>
       <c r="R406" s="1">
-        <v>46282.47420876157</v>
+        <v>46281.68877074074</v>
       </c>
       <c r="S406">
         <v>1</v>
       </c>
       <c r="T406" t="s">
-        <v>260</v>
+        <v>262</v>
+      </c>
+      <c r="V406" t="s">
+        <v>271</v>
+      </c>
+      <c r="W406" t="s">
+        <v>386</v>
       </c>
       <c r="AA406">
         <v>0</v>
       </c>
       <c r="AB406" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="AG406" t="s">
         <v>471</v>
       </c>
+      <c r="AH406" t="s">
+        <v>478</v>
+      </c>
     </row>
     <row r="407" spans="1:34">
       <c r="A407">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B407" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C407" t="s">
         <v>58</v>
@@ -30200,28 +30209,28 @@
         <v>46286</v>
       </c>
       <c r="M407" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="N407" t="s">
         <v>220</v>
       </c>
       <c r="O407">
-        <v>16976067</v>
+        <v>17222629</v>
       </c>
       <c r="P407" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q407" t="s">
         <v>252</v>
       </c>
       <c r="R407" s="1">
-        <v>46281.68877074074</v>
+        <v>46280.57958537037</v>
       </c>
       <c r="S407">
         <v>1</v>
       </c>
       <c r="T407" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="V407" t="s">
         <v>271</v>
@@ -30233,7 +30242,7 @@
         <v>0</v>
       </c>
       <c r="AB407" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="AG407" t="s">
         <v>471</v>
@@ -30244,10 +30253,10 @@
     </row>
     <row r="408" spans="1:34">
       <c r="A408">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B408" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C408" t="s">
         <v>58</v>
@@ -30256,7 +30265,7 @@
         <v>59</v>
       </c>
       <c r="E408" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F408" t="s">
         <v>64</v>
@@ -30277,40 +30286,40 @@
         <v>46286</v>
       </c>
       <c r="M408" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="N408" t="s">
         <v>220</v>
       </c>
       <c r="O408">
-        <v>17222629</v>
+        <v>18068544</v>
       </c>
       <c r="P408" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="Q408" t="s">
         <v>252</v>
       </c>
       <c r="R408" s="1">
-        <v>46280.57958537037</v>
+        <v>46281.63570936343</v>
       </c>
       <c r="S408">
         <v>1</v>
       </c>
       <c r="T408" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="V408" t="s">
         <v>271</v>
       </c>
       <c r="W408" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="AA408">
         <v>0</v>
       </c>
       <c r="AB408" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="AG408" t="s">
         <v>471</v>
@@ -30321,16 +30330,16 @@
     </row>
     <row r="409" spans="1:34">
       <c r="A409">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B409" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C409" t="s">
         <v>58</v>
       </c>
       <c r="D409" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E409" t="s">
         <v>63</v>
@@ -30360,7 +30369,7 @@
         <v>220</v>
       </c>
       <c r="O409">
-        <v>18068544</v>
+        <v>18052463</v>
       </c>
       <c r="P409" t="s">
         <v>230</v>
@@ -30369,7 +30378,7 @@
         <v>252</v>
       </c>
       <c r="R409" s="1">
-        <v>46281.63570936343</v>
+        <v>46281.63595871528</v>
       </c>
       <c r="S409">
         <v>1</v>
@@ -30381,7 +30390,7 @@
         <v>271</v>
       </c>
       <c r="W409" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AA409">
         <v>0</v>
@@ -30398,19 +30407,19 @@
     </row>
     <row r="410" spans="1:34">
       <c r="A410">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B410" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C410" t="s">
         <v>58</v>
       </c>
       <c r="D410" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E410" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F410" t="s">
         <v>64</v>
@@ -30430,41 +30439,32 @@
       <c r="L410" s="1">
         <v>46286</v>
       </c>
-      <c r="M410" t="s">
-        <v>218</v>
-      </c>
       <c r="N410" t="s">
         <v>220</v>
       </c>
       <c r="O410">
-        <v>18052463</v>
+        <v>18077112</v>
       </c>
       <c r="P410" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="Q410" t="s">
         <v>252</v>
       </c>
       <c r="R410" s="1">
-        <v>46281.63595871528</v>
+        <v>46279.62681744213</v>
       </c>
       <c r="S410">
         <v>1</v>
       </c>
       <c r="T410" t="s">
-        <v>256</v>
-      </c>
-      <c r="V410" t="s">
-        <v>271</v>
-      </c>
-      <c r="W410" t="s">
-        <v>387</v>
+        <v>263</v>
       </c>
       <c r="AA410">
         <v>0</v>
       </c>
       <c r="AB410" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="AG410" t="s">
         <v>471</v>
@@ -30475,16 +30475,16 @@
     </row>
     <row r="411" spans="1:34">
       <c r="A411">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B411" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C411" t="s">
         <v>58</v>
       </c>
       <c r="D411" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E411" t="s">
         <v>62</v>
@@ -30511,42 +30511,45 @@
         <v>220</v>
       </c>
       <c r="O411">
-        <v>18077112</v>
+        <v>18090189</v>
       </c>
       <c r="P411" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q411" t="s">
         <v>252</v>
       </c>
       <c r="R411" s="1">
-        <v>46279.62681744213</v>
+        <v>46279.66707821759</v>
       </c>
       <c r="S411">
         <v>1</v>
       </c>
       <c r="T411" t="s">
-        <v>263</v>
+        <v>261</v>
+      </c>
+      <c r="V411" t="s">
+        <v>271</v>
       </c>
       <c r="AA411">
         <v>0</v>
       </c>
       <c r="AB411" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG411" t="s">
         <v>471</v>
       </c>
       <c r="AH411" t="s">
-        <v>478</v>
+        <v>463</v>
       </c>
     </row>
     <row r="412" spans="1:34">
       <c r="A412">
-        <v>6779</v>
+        <v>6945</v>
       </c>
       <c r="B412" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C412" t="s">
         <v>58</v>
@@ -30558,7 +30561,7 @@
         <v>62</v>
       </c>
       <c r="F412" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G412">
         <v>5883</v>
@@ -30575,64 +30578,67 @@
       <c r="L412" s="1">
         <v>46286</v>
       </c>
+      <c r="M412" t="s">
+        <v>208</v>
+      </c>
       <c r="N412" t="s">
         <v>220</v>
       </c>
       <c r="O412">
-        <v>18090189</v>
+        <v>18179111</v>
       </c>
       <c r="P412" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="Q412" t="s">
         <v>252</v>
       </c>
       <c r="R412" s="1">
-        <v>46279.66707821759</v>
+        <v>46286.7220354051</v>
       </c>
       <c r="S412">
         <v>1</v>
       </c>
       <c r="T412" t="s">
-        <v>261</v>
-      </c>
-      <c r="V412" t="s">
-        <v>271</v>
+        <v>257</v>
+      </c>
+      <c r="W412" t="s">
+        <v>388</v>
       </c>
       <c r="AA412">
         <v>0</v>
       </c>
       <c r="AB412" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="AG412" t="s">
         <v>471</v>
       </c>
       <c r="AH412" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
     </row>
     <row r="413" spans="1:34">
       <c r="A413">
-        <v>6945</v>
+        <v>5417</v>
       </c>
       <c r="B413" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C413" t="s">
         <v>58</v>
       </c>
       <c r="D413" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E413" t="s">
         <v>62</v>
       </c>
       <c r="F413" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G413">
-        <v>5883</v>
+        <v>5884</v>
       </c>
       <c r="H413">
         <v>5792</v>
@@ -30641,57 +30647,48 @@
         <v>69</v>
       </c>
       <c r="J413" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L413" s="1">
         <v>46286</v>
       </c>
-      <c r="M413" t="s">
-        <v>208</v>
-      </c>
       <c r="N413" t="s">
         <v>220</v>
       </c>
       <c r="O413">
-        <v>18179111</v>
+        <v>17399077</v>
       </c>
       <c r="P413" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q413" t="s">
         <v>252</v>
       </c>
       <c r="R413" s="1">
-        <v>46286.7220354051</v>
+        <v>46282.47437324074</v>
       </c>
       <c r="S413">
         <v>1</v>
       </c>
       <c r="T413" t="s">
-        <v>257</v>
-      </c>
-      <c r="W413" t="s">
-        <v>389</v>
+        <v>260</v>
       </c>
       <c r="AA413">
         <v>0</v>
       </c>
       <c r="AB413" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AG413" t="s">
         <v>471</v>
       </c>
-      <c r="AH413" t="s">
-        <v>478</v>
-      </c>
     </row>
     <row r="414" spans="1:34">
       <c r="A414">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B414" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C414" t="s">
         <v>58</v>
@@ -30720,43 +30717,55 @@
       <c r="L414" s="1">
         <v>46286</v>
       </c>
+      <c r="M414" t="s">
+        <v>218</v>
+      </c>
       <c r="N414" t="s">
         <v>220</v>
       </c>
       <c r="O414">
-        <v>17399077</v>
+        <v>16976077</v>
       </c>
       <c r="P414" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="Q414" t="s">
         <v>252</v>
       </c>
       <c r="R414" s="1">
-        <v>46282.47437324074</v>
+        <v>46281.68880230324</v>
       </c>
       <c r="S414">
         <v>1</v>
       </c>
       <c r="T414" t="s">
-        <v>260</v>
+        <v>262</v>
+      </c>
+      <c r="V414" t="s">
+        <v>271</v>
+      </c>
+      <c r="W414" t="s">
+        <v>386</v>
       </c>
       <c r="AA414">
         <v>0</v>
       </c>
       <c r="AB414" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="AG414" t="s">
         <v>471</v>
       </c>
+      <c r="AH414" t="s">
+        <v>478</v>
+      </c>
     </row>
     <row r="415" spans="1:34">
       <c r="A415">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B415" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C415" t="s">
         <v>58</v>
@@ -30786,40 +30795,40 @@
         <v>46286</v>
       </c>
       <c r="M415" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="N415" t="s">
         <v>220</v>
       </c>
       <c r="O415">
-        <v>16976077</v>
+        <v>17222647</v>
       </c>
       <c r="P415" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q415" t="s">
         <v>252</v>
       </c>
       <c r="R415" s="1">
-        <v>46281.68880230324</v>
+        <v>46280.57972293982</v>
       </c>
       <c r="S415">
         <v>1</v>
       </c>
       <c r="T415" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="V415" t="s">
         <v>271</v>
       </c>
       <c r="W415" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AA415">
         <v>0</v>
       </c>
       <c r="AB415" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="AG415" t="s">
         <v>471</v>
@@ -30830,10 +30839,10 @@
     </row>
     <row r="416" spans="1:34">
       <c r="A416">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B416" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C416" t="s">
         <v>58</v>
@@ -30842,7 +30851,7 @@
         <v>59</v>
       </c>
       <c r="E416" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F416" t="s">
         <v>64</v>
@@ -30863,40 +30872,40 @@
         <v>46286</v>
       </c>
       <c r="M416" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="N416" t="s">
         <v>220</v>
       </c>
       <c r="O416">
-        <v>17222647</v>
+        <v>18068555</v>
       </c>
       <c r="P416" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="Q416" t="s">
         <v>252</v>
       </c>
       <c r="R416" s="1">
-        <v>46280.57972293982</v>
+        <v>46281.63575075231</v>
       </c>
       <c r="S416">
         <v>1</v>
       </c>
       <c r="T416" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="V416" t="s">
         <v>271</v>
       </c>
       <c r="W416" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="AA416">
         <v>0</v>
       </c>
       <c r="AB416" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="AG416" t="s">
         <v>471</v>
@@ -30907,16 +30916,16 @@
     </row>
     <row r="417" spans="1:34">
       <c r="A417">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B417" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C417" t="s">
         <v>58</v>
       </c>
       <c r="D417" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E417" t="s">
         <v>63</v>
@@ -30946,7 +30955,7 @@
         <v>220</v>
       </c>
       <c r="O417">
-        <v>18068555</v>
+        <v>18052474</v>
       </c>
       <c r="P417" t="s">
         <v>230</v>
@@ -30955,7 +30964,7 @@
         <v>252</v>
       </c>
       <c r="R417" s="1">
-        <v>46281.63575075231</v>
+        <v>46281.63599785879</v>
       </c>
       <c r="S417">
         <v>1</v>
@@ -30967,7 +30976,7 @@
         <v>271</v>
       </c>
       <c r="W417" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AA417">
         <v>0</v>
@@ -30984,19 +30993,19 @@
     </row>
     <row r="418" spans="1:34">
       <c r="A418">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B418" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C418" t="s">
         <v>58</v>
       </c>
       <c r="D418" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E418" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F418" t="s">
         <v>64</v>
@@ -31016,41 +31025,32 @@
       <c r="L418" s="1">
         <v>46286</v>
       </c>
-      <c r="M418" t="s">
-        <v>218</v>
-      </c>
       <c r="N418" t="s">
         <v>220</v>
       </c>
       <c r="O418">
-        <v>18052474</v>
+        <v>18077122</v>
       </c>
       <c r="P418" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="Q418" t="s">
         <v>252</v>
       </c>
       <c r="R418" s="1">
-        <v>46281.63599785879</v>
+        <v>46279.6268503125</v>
       </c>
       <c r="S418">
         <v>1</v>
       </c>
       <c r="T418" t="s">
-        <v>256</v>
-      </c>
-      <c r="V418" t="s">
-        <v>271</v>
-      </c>
-      <c r="W418" t="s">
-        <v>387</v>
+        <v>263</v>
       </c>
       <c r="AA418">
         <v>0</v>
       </c>
       <c r="AB418" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="AG418" t="s">
         <v>471</v>
@@ -31061,16 +31061,16 @@
     </row>
     <row r="419" spans="1:34">
       <c r="A419">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B419" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C419" t="s">
         <v>58</v>
       </c>
       <c r="D419" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E419" t="s">
         <v>62</v>
@@ -31097,42 +31097,45 @@
         <v>220</v>
       </c>
       <c r="O419">
-        <v>18077122</v>
+        <v>18090199</v>
       </c>
       <c r="P419" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q419" t="s">
         <v>252</v>
       </c>
       <c r="R419" s="1">
-        <v>46279.6268503125</v>
+        <v>46279.66698128472</v>
       </c>
       <c r="S419">
         <v>1</v>
       </c>
       <c r="T419" t="s">
-        <v>263</v>
+        <v>261</v>
+      </c>
+      <c r="V419" t="s">
+        <v>271</v>
       </c>
       <c r="AA419">
         <v>0</v>
       </c>
       <c r="AB419" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG419" t="s">
         <v>471</v>
       </c>
       <c r="AH419" t="s">
-        <v>478</v>
+        <v>463</v>
       </c>
     </row>
     <row r="420" spans="1:34">
       <c r="A420">
-        <v>6779</v>
+        <v>6945</v>
       </c>
       <c r="B420" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C420" t="s">
         <v>58</v>
@@ -31144,7 +31147,7 @@
         <v>62</v>
       </c>
       <c r="F420" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G420">
         <v>5884</v>
@@ -31161,129 +31164,126 @@
       <c r="L420" s="1">
         <v>46286</v>
       </c>
+      <c r="M420" t="s">
+        <v>208</v>
+      </c>
       <c r="N420" t="s">
         <v>220</v>
       </c>
       <c r="O420">
-        <v>18090199</v>
+        <v>18179118</v>
       </c>
       <c r="P420" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="Q420" t="s">
         <v>252</v>
       </c>
       <c r="R420" s="1">
-        <v>46279.66698128472</v>
+        <v>46286.7221544213</v>
       </c>
       <c r="S420">
         <v>1</v>
       </c>
       <c r="T420" t="s">
-        <v>261</v>
-      </c>
-      <c r="V420" t="s">
-        <v>271</v>
+        <v>257</v>
+      </c>
+      <c r="W420" t="s">
+        <v>356</v>
       </c>
       <c r="AA420">
         <v>0</v>
       </c>
       <c r="AB420" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="AG420" t="s">
         <v>471</v>
       </c>
       <c r="AH420" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
     </row>
     <row r="421" spans="1:34">
       <c r="A421">
-        <v>6945</v>
+        <v>5417</v>
       </c>
       <c r="B421" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C421" t="s">
         <v>58</v>
       </c>
       <c r="D421" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E421" t="s">
         <v>62</v>
       </c>
       <c r="F421" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G421">
-        <v>5884</v>
+        <v>7012</v>
       </c>
       <c r="H421">
-        <v>5792</v>
+        <v>0</v>
       </c>
       <c r="I421" t="s">
         <v>69</v>
       </c>
       <c r="J421" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="L421" s="1">
-        <v>46286</v>
-      </c>
-      <c r="M421" t="s">
-        <v>208</v>
+        <v>46281</v>
       </c>
       <c r="N421" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O421">
-        <v>18179118</v>
+        <v>18257773</v>
       </c>
       <c r="P421" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q421" t="s">
         <v>252</v>
       </c>
       <c r="R421" s="1">
-        <v>46286.7221544213</v>
+        <v>46279.66929922454</v>
       </c>
       <c r="S421">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T421" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="W421" t="s">
-        <v>356</v>
+        <v>390</v>
       </c>
       <c r="AA421">
         <v>0</v>
       </c>
       <c r="AB421" t="s">
-        <v>231</v>
+        <v>460</v>
       </c>
       <c r="AG421" t="s">
         <v>471</v>
       </c>
-      <c r="AH421" t="s">
-        <v>478</v>
-      </c>
     </row>
     <row r="422" spans="1:34">
       <c r="A422">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B422" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C422" t="s">
         <v>58</v>
       </c>
       <c r="D422" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E422" t="s">
         <v>62</v>
@@ -31301,7 +31301,7 @@
         <v>69</v>
       </c>
       <c r="J422" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L422" s="1">
         <v>46281</v>
@@ -31310,22 +31310,22 @@
         <v>219</v>
       </c>
       <c r="O422">
-        <v>18257773</v>
+        <v>18258536</v>
       </c>
       <c r="P422" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q422" t="s">
         <v>252</v>
       </c>
       <c r="R422" s="1">
-        <v>46279.66929922454</v>
+        <v>46280.61353684028</v>
       </c>
       <c r="S422">
         <v>6</v>
       </c>
       <c r="T422" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="W422" t="s">
         <v>391</v>
@@ -31339,19 +31339,22 @@
       <c r="AG422" t="s">
         <v>471</v>
       </c>
+      <c r="AH422" t="s">
+        <v>463</v>
+      </c>
     </row>
     <row r="423" spans="1:34">
       <c r="A423">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B423" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C423" t="s">
         <v>58</v>
       </c>
       <c r="D423" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E423" t="s">
         <v>62</v>
@@ -31369,7 +31372,7 @@
         <v>69</v>
       </c>
       <c r="J423" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L423" s="1">
         <v>46281</v>
@@ -31378,22 +31381,25 @@
         <v>219</v>
       </c>
       <c r="O423">
-        <v>18258536</v>
+        <v>18254964</v>
       </c>
       <c r="P423" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="Q423" t="s">
         <v>252</v>
       </c>
       <c r="R423" s="1">
-        <v>46280.61353684028</v>
+        <v>46280.61353920139</v>
       </c>
       <c r="S423">
         <v>6</v>
       </c>
       <c r="T423" t="s">
-        <v>264</v>
+        <v>262</v>
+      </c>
+      <c r="V423" t="s">
+        <v>271</v>
       </c>
       <c r="W423" t="s">
         <v>392</v>
@@ -31408,15 +31414,15 @@
         <v>471</v>
       </c>
       <c r="AH423" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
     </row>
     <row r="424" spans="1:34">
       <c r="A424">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B424" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C424" t="s">
         <v>58</v>
@@ -31440,7 +31446,7 @@
         <v>69</v>
       </c>
       <c r="J424" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L424" s="1">
         <v>46281</v>
@@ -31449,22 +31455,22 @@
         <v>219</v>
       </c>
       <c r="O424">
-        <v>18254964</v>
+        <v>18255116</v>
       </c>
       <c r="P424" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q424" t="s">
         <v>252</v>
       </c>
       <c r="R424" s="1">
-        <v>46280.61353920139</v>
+        <v>46279.63250563657</v>
       </c>
       <c r="S424">
         <v>6</v>
       </c>
       <c r="T424" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="V424" t="s">
         <v>271</v>
@@ -31487,10 +31493,10 @@
     </row>
     <row r="425" spans="1:34">
       <c r="A425">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B425" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C425" t="s">
         <v>58</v>
@@ -31499,7 +31505,7 @@
         <v>59</v>
       </c>
       <c r="E425" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F425" t="s">
         <v>64</v>
@@ -31514,7 +31520,7 @@
         <v>69</v>
       </c>
       <c r="J425" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L425" s="1">
         <v>46281</v>
@@ -31523,28 +31529,28 @@
         <v>219</v>
       </c>
       <c r="O425">
-        <v>18255116</v>
+        <v>18257668</v>
       </c>
       <c r="P425" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="Q425" t="s">
         <v>252</v>
       </c>
       <c r="R425" s="1">
-        <v>46279.63250563657</v>
+        <v>46280.61354019676</v>
       </c>
       <c r="S425">
         <v>6</v>
       </c>
       <c r="T425" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="V425" t="s">
         <v>271</v>
       </c>
       <c r="W425" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="AA425">
         <v>0</v>
@@ -31561,16 +31567,16 @@
     </row>
     <row r="426" spans="1:34">
       <c r="A426">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B426" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C426" t="s">
         <v>58</v>
       </c>
       <c r="D426" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E426" t="s">
         <v>63</v>
@@ -31588,7 +31594,7 @@
         <v>69</v>
       </c>
       <c r="J426" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L426" s="1">
         <v>46281</v>
@@ -31597,7 +31603,7 @@
         <v>219</v>
       </c>
       <c r="O426">
-        <v>18257668</v>
+        <v>18256366</v>
       </c>
       <c r="P426" t="s">
         <v>230</v>
@@ -31606,7 +31612,7 @@
         <v>252</v>
       </c>
       <c r="R426" s="1">
-        <v>46280.61354019676</v>
+        <v>46280.6135403125</v>
       </c>
       <c r="S426">
         <v>6</v>
@@ -31618,7 +31624,7 @@
         <v>271</v>
       </c>
       <c r="W426" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AA426">
         <v>0</v>
@@ -31635,19 +31641,19 @@
     </row>
     <row r="427" spans="1:34">
       <c r="A427">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B427" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C427" t="s">
         <v>58</v>
       </c>
       <c r="D427" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E427" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F427" t="s">
         <v>64</v>
@@ -31662,43 +31668,43 @@
         <v>69</v>
       </c>
       <c r="J427" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L427" s="1">
         <v>46281</v>
       </c>
+      <c r="M427" t="s">
+        <v>216</v>
+      </c>
       <c r="N427" t="s">
         <v>219</v>
       </c>
       <c r="O427">
-        <v>18256366</v>
+        <v>18256433</v>
       </c>
       <c r="P427" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="Q427" t="s">
         <v>252</v>
       </c>
       <c r="R427" s="1">
-        <v>46280.6135403125</v>
+        <v>46281.71218414352</v>
       </c>
       <c r="S427">
         <v>6</v>
       </c>
       <c r="T427" t="s">
-        <v>256</v>
-      </c>
-      <c r="V427" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="W427" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AA427">
         <v>0</v>
       </c>
       <c r="AB427" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="AG427" t="s">
         <v>471</v>
@@ -31709,16 +31715,16 @@
     </row>
     <row r="428" spans="1:34">
       <c r="A428">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B428" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C428" t="s">
         <v>58</v>
       </c>
       <c r="D428" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E428" t="s">
         <v>62</v>
@@ -31736,34 +31742,34 @@
         <v>69</v>
       </c>
       <c r="J428" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L428" s="1">
         <v>46281</v>
       </c>
-      <c r="M428" t="s">
-        <v>216</v>
-      </c>
       <c r="N428" t="s">
         <v>219</v>
       </c>
       <c r="O428">
-        <v>18256433</v>
+        <v>18255012</v>
       </c>
       <c r="P428" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q428" t="s">
         <v>252</v>
       </c>
       <c r="R428" s="1">
-        <v>46281.71218414352</v>
+        <v>46281.41576883102</v>
       </c>
       <c r="S428">
         <v>6</v>
       </c>
       <c r="T428" t="s">
-        <v>263</v>
+        <v>261</v>
+      </c>
+      <c r="V428" t="s">
+        <v>271</v>
       </c>
       <c r="W428" t="s">
         <v>395</v>
@@ -31772,21 +31778,21 @@
         <v>0</v>
       </c>
       <c r="AB428" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="AG428" t="s">
         <v>471</v>
       </c>
       <c r="AH428" t="s">
-        <v>478</v>
+        <v>463</v>
       </c>
     </row>
     <row r="429" spans="1:34">
       <c r="A429">
-        <v>6779</v>
+        <v>6945</v>
       </c>
       <c r="B429" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C429" t="s">
         <v>58</v>
@@ -31798,7 +31804,7 @@
         <v>62</v>
       </c>
       <c r="F429" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G429">
         <v>7012</v>
@@ -31810,7 +31816,7 @@
         <v>69</v>
       </c>
       <c r="J429" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L429" s="1">
         <v>46281</v>
@@ -31819,25 +31825,22 @@
         <v>219</v>
       </c>
       <c r="O429">
-        <v>18255012</v>
+        <v>18254903</v>
       </c>
       <c r="P429" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="Q429" t="s">
         <v>252</v>
       </c>
       <c r="R429" s="1">
-        <v>46281.41576883102</v>
+        <v>46280.43132989584</v>
       </c>
       <c r="S429">
         <v>6</v>
       </c>
       <c r="T429" t="s">
-        <v>261</v>
-      </c>
-      <c r="V429" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="W429" t="s">
         <v>396</v>
@@ -31852,21 +31855,21 @@
         <v>471</v>
       </c>
       <c r="AH429" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
     </row>
     <row r="430" spans="1:34">
       <c r="A430">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B430" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C430" t="s">
         <v>58</v>
       </c>
       <c r="D430" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E430" t="s">
         <v>62</v>
@@ -31884,7 +31887,7 @@
         <v>69</v>
       </c>
       <c r="J430" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L430" s="1">
         <v>46281</v>
@@ -31893,22 +31896,22 @@
         <v>219</v>
       </c>
       <c r="O430">
-        <v>18254903</v>
+        <v>18258489</v>
       </c>
       <c r="P430" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q430" t="s">
         <v>252</v>
       </c>
       <c r="R430" s="1">
-        <v>46280.43132989584</v>
+        <v>46280.61367623843</v>
       </c>
       <c r="S430">
         <v>6</v>
       </c>
       <c r="T430" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="W430" t="s">
         <v>397</v>
@@ -31923,15 +31926,15 @@
         <v>471</v>
       </c>
       <c r="AH430" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="431" spans="1:34">
       <c r="A431">
-        <v>6949</v>
+        <v>5417</v>
       </c>
       <c r="B431" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C431" t="s">
         <v>58</v>
@@ -31943,43 +31946,46 @@
         <v>62</v>
       </c>
       <c r="F431" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G431">
-        <v>7012</v>
+        <v>5836</v>
       </c>
       <c r="H431">
-        <v>0</v>
+        <v>5784</v>
       </c>
       <c r="I431" t="s">
         <v>69</v>
       </c>
       <c r="J431" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="L431" s="1">
-        <v>46281</v>
+        <v>46286</v>
+      </c>
+      <c r="M431" t="s">
+        <v>215</v>
       </c>
       <c r="N431" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O431">
-        <v>18258489</v>
+        <v>17399027</v>
       </c>
       <c r="P431" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q431" t="s">
         <v>252</v>
       </c>
       <c r="R431" s="1">
-        <v>46280.61367623843</v>
+        <v>46286.71510853009</v>
       </c>
       <c r="S431">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T431" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="W431" t="s">
         <v>398</v>
@@ -31988,21 +31994,18 @@
         <v>0</v>
       </c>
       <c r="AB431" t="s">
-        <v>460</v>
+        <v>233</v>
       </c>
       <c r="AG431" t="s">
         <v>471</v>
       </c>
-      <c r="AH431" t="s">
-        <v>479</v>
-      </c>
     </row>
     <row r="432" spans="1:34">
       <c r="A432">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B432" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C432" t="s">
         <v>58</v>
@@ -32032,28 +32035,31 @@
         <v>46286</v>
       </c>
       <c r="M432" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N432" t="s">
         <v>220</v>
       </c>
       <c r="O432">
-        <v>17399027</v>
+        <v>16976037</v>
       </c>
       <c r="P432" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="Q432" t="s">
         <v>252</v>
       </c>
       <c r="R432" s="1">
-        <v>46286.71510853009</v>
+        <v>46283.59424842593</v>
       </c>
       <c r="S432">
         <v>1</v>
       </c>
       <c r="T432" t="s">
-        <v>260</v>
+        <v>262</v>
+      </c>
+      <c r="V432" t="s">
+        <v>271</v>
       </c>
       <c r="W432" t="s">
         <v>399</v>
@@ -32062,18 +32068,21 @@
         <v>0</v>
       </c>
       <c r="AB432" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="AG432" t="s">
         <v>471</v>
       </c>
+      <c r="AH432" t="s">
+        <v>478</v>
+      </c>
     </row>
     <row r="433" spans="1:34">
       <c r="A433">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B433" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C433" t="s">
         <v>58</v>
@@ -32109,22 +32118,22 @@
         <v>220</v>
       </c>
       <c r="O433">
-        <v>16976037</v>
+        <v>17222579</v>
       </c>
       <c r="P433" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q433" t="s">
         <v>252</v>
       </c>
       <c r="R433" s="1">
-        <v>46283.59424842593</v>
+        <v>46283.68435655093</v>
       </c>
       <c r="S433">
         <v>1</v>
       </c>
       <c r="T433" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="V433" t="s">
         <v>271</v>
@@ -32136,7 +32145,7 @@
         <v>0</v>
       </c>
       <c r="AB433" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="AG433" t="s">
         <v>471</v>
@@ -32147,10 +32156,10 @@
     </row>
     <row r="434" spans="1:34">
       <c r="A434">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B434" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C434" t="s">
         <v>58</v>
@@ -32159,7 +32168,7 @@
         <v>59</v>
       </c>
       <c r="E434" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F434" t="s">
         <v>64</v>
@@ -32186,34 +32195,34 @@
         <v>220</v>
       </c>
       <c r="O434">
-        <v>17222579</v>
+        <v>18068500</v>
       </c>
       <c r="P434" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="Q434" t="s">
         <v>252</v>
       </c>
       <c r="R434" s="1">
-        <v>46283.68435655093</v>
+        <v>46283.5942487037</v>
       </c>
       <c r="S434">
         <v>1</v>
       </c>
       <c r="T434" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="V434" t="s">
         <v>271</v>
       </c>
       <c r="W434" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="AA434">
         <v>0</v>
       </c>
       <c r="AB434" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="AG434" t="s">
         <v>471</v>
@@ -32224,16 +32233,16 @@
     </row>
     <row r="435" spans="1:34">
       <c r="A435">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B435" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C435" t="s">
         <v>58</v>
       </c>
       <c r="D435" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E435" t="s">
         <v>63</v>
@@ -32263,7 +32272,7 @@
         <v>220</v>
       </c>
       <c r="O435">
-        <v>18068500</v>
+        <v>18052419</v>
       </c>
       <c r="P435" t="s">
         <v>230</v>
@@ -32272,7 +32281,7 @@
         <v>252</v>
       </c>
       <c r="R435" s="1">
-        <v>46283.5942487037</v>
+        <v>46283.59424924768</v>
       </c>
       <c r="S435">
         <v>1</v>
@@ -32284,7 +32293,7 @@
         <v>271</v>
       </c>
       <c r="W435" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AA435">
         <v>0</v>
@@ -32301,19 +32310,19 @@
     </row>
     <row r="436" spans="1:34">
       <c r="A436">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B436" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C436" t="s">
         <v>58</v>
       </c>
       <c r="D436" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E436" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F436" t="s">
         <v>64</v>
@@ -32340,34 +32349,31 @@
         <v>220</v>
       </c>
       <c r="O436">
-        <v>18052419</v>
+        <v>18077082</v>
       </c>
       <c r="P436" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="Q436" t="s">
         <v>252</v>
       </c>
       <c r="R436" s="1">
-        <v>46283.59424924768</v>
+        <v>46283.68161918982</v>
       </c>
       <c r="S436">
         <v>1</v>
       </c>
       <c r="T436" t="s">
-        <v>256</v>
-      </c>
-      <c r="V436" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="W436" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AA436">
         <v>0</v>
       </c>
       <c r="AB436" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="AG436" t="s">
         <v>471</v>
@@ -32378,16 +32384,16 @@
     </row>
     <row r="437" spans="1:34">
       <c r="A437">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B437" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C437" t="s">
         <v>58</v>
       </c>
       <c r="D437" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E437" t="s">
         <v>62</v>
@@ -32411,28 +32417,31 @@
         <v>46286</v>
       </c>
       <c r="M437" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="N437" t="s">
         <v>220</v>
       </c>
       <c r="O437">
-        <v>18077082</v>
+        <v>18090149</v>
       </c>
       <c r="P437" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q437" t="s">
         <v>252</v>
       </c>
       <c r="R437" s="1">
-        <v>46283.68161918982</v>
+        <v>46286.6489187037</v>
       </c>
       <c r="S437">
         <v>1</v>
       </c>
       <c r="T437" t="s">
-        <v>263</v>
+        <v>261</v>
+      </c>
+      <c r="V437" t="s">
+        <v>271</v>
       </c>
       <c r="W437" t="s">
         <v>402</v>
@@ -32441,27 +32450,27 @@
         <v>0</v>
       </c>
       <c r="AB437" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG437" t="s">
         <v>471</v>
       </c>
       <c r="AH437" t="s">
-        <v>478</v>
+        <v>463</v>
       </c>
     </row>
     <row r="438" spans="1:34">
       <c r="A438">
-        <v>6779</v>
+        <v>6404</v>
       </c>
       <c r="B438" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C438" t="s">
         <v>58</v>
       </c>
       <c r="D438" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E438" t="s">
         <v>62</v>
@@ -32470,46 +32479,43 @@
         <v>64</v>
       </c>
       <c r="G438">
-        <v>5836</v>
+        <v>5903</v>
       </c>
       <c r="H438">
-        <v>5784</v>
+        <v>5830</v>
       </c>
       <c r="I438" t="s">
         <v>69</v>
       </c>
       <c r="J438" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="L438" s="1">
         <v>46286</v>
       </c>
       <c r="M438" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N438" t="s">
         <v>220</v>
       </c>
       <c r="O438">
-        <v>18090149</v>
+        <v>16962221</v>
       </c>
       <c r="P438" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Q438" t="s">
         <v>252</v>
       </c>
       <c r="R438" s="1">
-        <v>46286.6489187037</v>
+        <v>46282.42048836806</v>
       </c>
       <c r="S438">
         <v>1</v>
       </c>
       <c r="T438" t="s">
-        <v>261</v>
-      </c>
-      <c r="V438" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="W438" t="s">
         <v>403</v>
@@ -32518,7 +32524,7 @@
         <v>0</v>
       </c>
       <c r="AB438" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AG438" t="s">
         <v>471</v>
@@ -32547,10 +32553,10 @@
         <v>64</v>
       </c>
       <c r="G439">
-        <v>5903</v>
+        <v>5830</v>
       </c>
       <c r="H439">
-        <v>5830</v>
+        <v>5784</v>
       </c>
       <c r="I439" t="s">
         <v>69</v>
@@ -32561,14 +32567,11 @@
       <c r="L439" s="1">
         <v>46286</v>
       </c>
-      <c r="M439" t="s">
-        <v>217</v>
-      </c>
       <c r="N439" t="s">
         <v>220</v>
       </c>
       <c r="O439">
-        <v>16962221</v>
+        <v>16962211</v>
       </c>
       <c r="P439" t="s">
         <v>236</v>
@@ -32577,7 +32580,7 @@
         <v>252</v>
       </c>
       <c r="R439" s="1">
-        <v>46282.42048836806</v>
+        <v>46282.42138976852</v>
       </c>
       <c r="S439">
         <v>1</v>
@@ -32585,9 +32588,6 @@
       <c r="T439" t="s">
         <v>264</v>
       </c>
-      <c r="W439" t="s">
-        <v>404</v>
-      </c>
       <c r="AA439">
         <v>0</v>
       </c>
@@ -32603,16 +32603,16 @@
     </row>
     <row r="440" spans="1:34">
       <c r="A440">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B440" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C440" t="s">
         <v>58</v>
       </c>
       <c r="D440" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E440" t="s">
         <v>62</v>
@@ -32621,10 +32621,10 @@
         <v>64</v>
       </c>
       <c r="G440">
-        <v>5830</v>
+        <v>5786</v>
       </c>
       <c r="H440">
-        <v>5784</v>
+        <v>0</v>
       </c>
       <c r="I440" t="s">
         <v>69</v>
@@ -32633,54 +32633,51 @@
         <v>159</v>
       </c>
       <c r="L440" s="1">
-        <v>46286</v>
+        <v>46283</v>
       </c>
       <c r="N440" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O440">
-        <v>16962211</v>
+        <v>17398997</v>
       </c>
       <c r="P440" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="Q440" t="s">
         <v>252</v>
       </c>
       <c r="R440" s="1">
-        <v>46282.42138976852</v>
+        <v>46279.66936339121</v>
       </c>
       <c r="S440">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T440" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="AA440">
         <v>0</v>
       </c>
       <c r="AB440" t="s">
-        <v>236</v>
+        <v>460</v>
       </c>
       <c r="AG440" t="s">
-        <v>471</v>
-      </c>
-      <c r="AH440" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
     </row>
     <row r="441" spans="1:34">
       <c r="A441">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B441" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C441" t="s">
         <v>58</v>
       </c>
       <c r="D441" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E441" t="s">
         <v>62</v>
@@ -32698,7 +32695,7 @@
         <v>69</v>
       </c>
       <c r="J441" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L441" s="1">
         <v>46283</v>
@@ -32707,45 +32704,48 @@
         <v>219</v>
       </c>
       <c r="O441">
-        <v>17398997</v>
+        <v>16962199</v>
       </c>
       <c r="P441" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q441" t="s">
         <v>252</v>
       </c>
       <c r="R441" s="1">
-        <v>46279.66936339121</v>
+        <v>46264.0028866088</v>
       </c>
       <c r="S441">
         <v>4</v>
       </c>
       <c r="T441" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="AA441">
         <v>0</v>
       </c>
       <c r="AB441" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="AG441" t="s">
         <v>472</v>
       </c>
+      <c r="AH441" t="s">
+        <v>463</v>
+      </c>
     </row>
     <row r="442" spans="1:34">
       <c r="A442">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B442" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C442" t="s">
         <v>58</v>
       </c>
       <c r="D442" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E442" t="s">
         <v>62</v>
@@ -32763,7 +32763,7 @@
         <v>69</v>
       </c>
       <c r="J442" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L442" s="1">
         <v>46283</v>
@@ -32772,42 +32772,45 @@
         <v>219</v>
       </c>
       <c r="O442">
-        <v>16962199</v>
+        <v>16976005</v>
       </c>
       <c r="P442" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="Q442" t="s">
         <v>252</v>
       </c>
       <c r="R442" s="1">
-        <v>46264.0028866088</v>
+        <v>46279.62931917824</v>
       </c>
       <c r="S442">
         <v>4</v>
       </c>
       <c r="T442" t="s">
-        <v>264</v>
+        <v>262</v>
+      </c>
+      <c r="V442" t="s">
+        <v>271</v>
       </c>
       <c r="AA442">
         <v>0</v>
       </c>
       <c r="AB442" t="s">
-        <v>465</v>
+        <v>230</v>
       </c>
       <c r="AG442" t="s">
         <v>472</v>
       </c>
       <c r="AH442" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
     </row>
     <row r="443" spans="1:34">
       <c r="A443">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B443" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C443" t="s">
         <v>58</v>
@@ -32831,7 +32834,7 @@
         <v>69</v>
       </c>
       <c r="J443" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L443" s="1">
         <v>46283</v>
@@ -32840,22 +32843,22 @@
         <v>219</v>
       </c>
       <c r="O443">
-        <v>16976005</v>
+        <v>17222531</v>
       </c>
       <c r="P443" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q443" t="s">
         <v>252</v>
       </c>
       <c r="R443" s="1">
-        <v>46279.62931917824</v>
+        <v>46279.40189447917</v>
       </c>
       <c r="S443">
         <v>4</v>
       </c>
       <c r="T443" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="V443" t="s">
         <v>271</v>
@@ -32864,7 +32867,7 @@
         <v>0</v>
       </c>
       <c r="AB443" t="s">
-        <v>230</v>
+        <v>460</v>
       </c>
       <c r="AG443" t="s">
         <v>472</v>
@@ -32875,10 +32878,10 @@
     </row>
     <row r="444" spans="1:34">
       <c r="A444">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B444" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C444" t="s">
         <v>58</v>
@@ -32887,7 +32890,7 @@
         <v>59</v>
       </c>
       <c r="E444" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F444" t="s">
         <v>64</v>
@@ -32902,7 +32905,7 @@
         <v>69</v>
       </c>
       <c r="J444" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L444" s="1">
         <v>46283</v>
@@ -32911,22 +32914,22 @@
         <v>219</v>
       </c>
       <c r="O444">
-        <v>17222531</v>
+        <v>18068463</v>
       </c>
       <c r="P444" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="Q444" t="s">
         <v>252</v>
       </c>
       <c r="R444" s="1">
-        <v>46279.40189447917</v>
+        <v>46279.62936614583</v>
       </c>
       <c r="S444">
         <v>4</v>
       </c>
       <c r="T444" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="V444" t="s">
         <v>271</v>
@@ -32935,7 +32938,7 @@
         <v>0</v>
       </c>
       <c r="AB444" t="s">
-        <v>460</v>
+        <v>230</v>
       </c>
       <c r="AG444" t="s">
         <v>472</v>
@@ -32946,16 +32949,16 @@
     </row>
     <row r="445" spans="1:34">
       <c r="A445">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B445" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C445" t="s">
         <v>58</v>
       </c>
       <c r="D445" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E445" t="s">
         <v>63</v>
@@ -32973,7 +32976,7 @@
         <v>69</v>
       </c>
       <c r="J445" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L445" s="1">
         <v>46283</v>
@@ -32982,7 +32985,7 @@
         <v>219</v>
       </c>
       <c r="O445">
-        <v>18068463</v>
+        <v>18052384</v>
       </c>
       <c r="P445" t="s">
         <v>230</v>
@@ -32991,7 +32994,7 @@
         <v>252</v>
       </c>
       <c r="R445" s="1">
-        <v>46279.62936614583</v>
+        <v>46279.62936509259</v>
       </c>
       <c r="S445">
         <v>4</v>
@@ -33017,10 +33020,10 @@
     </row>
     <row r="446" spans="1:34">
       <c r="A446">
-        <v>6628</v>
+        <v>6779</v>
       </c>
       <c r="B446" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C446" t="s">
         <v>58</v>
@@ -33029,7 +33032,7 @@
         <v>60</v>
       </c>
       <c r="E446" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F446" t="s">
         <v>64</v>
@@ -33044,7 +33047,7 @@
         <v>69</v>
       </c>
       <c r="J446" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L446" s="1">
         <v>46283</v>
@@ -33053,22 +33056,22 @@
         <v>219</v>
       </c>
       <c r="O446">
-        <v>18052384</v>
+        <v>18090113</v>
       </c>
       <c r="P446" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="Q446" t="s">
         <v>252</v>
       </c>
       <c r="R446" s="1">
-        <v>46279.62936509259</v>
+        <v>46276.63187607639</v>
       </c>
       <c r="S446">
         <v>4</v>
       </c>
       <c r="T446" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="V446" t="s">
         <v>271</v>
@@ -33077,21 +33080,21 @@
         <v>0</v>
       </c>
       <c r="AB446" t="s">
-        <v>230</v>
+        <v>460</v>
       </c>
       <c r="AG446" t="s">
         <v>472</v>
       </c>
       <c r="AH446" t="s">
-        <v>478</v>
+        <v>463</v>
       </c>
     </row>
     <row r="447" spans="1:34">
       <c r="A447">
-        <v>6779</v>
+        <v>6945</v>
       </c>
       <c r="B447" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C447" t="s">
         <v>58</v>
@@ -33103,7 +33106,7 @@
         <v>62</v>
       </c>
       <c r="F447" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G447">
         <v>5786</v>
@@ -33115,7 +33118,7 @@
         <v>69</v>
       </c>
       <c r="J447" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L447" s="1">
         <v>46283</v>
@@ -33124,25 +33127,22 @@
         <v>219</v>
       </c>
       <c r="O447">
-        <v>18090113</v>
+        <v>18179053</v>
       </c>
       <c r="P447" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="Q447" t="s">
         <v>252</v>
       </c>
       <c r="R447" s="1">
-        <v>46276.63187607639</v>
+        <v>46279.62658503472</v>
       </c>
       <c r="S447">
         <v>4</v>
       </c>
       <c r="T447" t="s">
-        <v>261</v>
-      </c>
-      <c r="V447" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="AA447">
         <v>0</v>
@@ -33154,21 +33154,21 @@
         <v>472</v>
       </c>
       <c r="AH447" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
     </row>
     <row r="448" spans="1:34">
       <c r="A448">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B448" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C448" t="s">
         <v>58</v>
       </c>
       <c r="D448" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E448" t="s">
         <v>62</v>
@@ -33186,7 +33186,7 @@
         <v>69</v>
       </c>
       <c r="J448" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L448" s="1">
         <v>46283</v>
@@ -33195,22 +33195,22 @@
         <v>219</v>
       </c>
       <c r="O448">
-        <v>18179053</v>
+        <v>18190370</v>
       </c>
       <c r="P448" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q448" t="s">
         <v>252</v>
       </c>
       <c r="R448" s="1">
-        <v>46279.62658503472</v>
+        <v>46279.63255474537</v>
       </c>
       <c r="S448">
         <v>4</v>
       </c>
       <c r="T448" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AA448">
         <v>0</v>
@@ -33222,15 +33222,15 @@
         <v>472</v>
       </c>
       <c r="AH448" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="449" spans="1:34">
       <c r="A449">
-        <v>6949</v>
+        <v>6486</v>
       </c>
       <c r="B449" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C449" t="s">
         <v>58</v>
@@ -33242,10 +33242,10 @@
         <v>62</v>
       </c>
       <c r="F449" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G449">
-        <v>5786</v>
+        <v>5787</v>
       </c>
       <c r="H449">
         <v>0</v>
@@ -33257,54 +33257,51 @@
         <v>160</v>
       </c>
       <c r="L449" s="1">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="N449" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="O449">
-        <v>18190370</v>
-      </c>
-      <c r="P449" t="s">
-        <v>232</v>
+        <v>16976010</v>
       </c>
       <c r="Q449" t="s">
         <v>252</v>
       </c>
       <c r="R449" s="1">
-        <v>46279.63255474537</v>
+        <v>46256.00536641204</v>
       </c>
       <c r="S449">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T449" t="s">
-        <v>258</v>
+        <v>262</v>
+      </c>
+      <c r="V449" t="s">
+        <v>271</v>
       </c>
       <c r="AA449">
         <v>0</v>
       </c>
       <c r="AB449" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="AG449" t="s">
-        <v>472</v>
-      </c>
-      <c r="AH449" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
     </row>
     <row r="450" spans="1:34">
       <c r="A450">
-        <v>6486</v>
+        <v>6779</v>
       </c>
       <c r="B450" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C450" t="s">
         <v>58</v>
       </c>
       <c r="D450" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E450" t="s">
         <v>62</v>
@@ -33322,7 +33319,7 @@
         <v>69</v>
       </c>
       <c r="J450" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="L450" s="1">
         <v>46286</v>
@@ -33331,19 +33328,19 @@
         <v>223</v>
       </c>
       <c r="O450">
-        <v>16976010</v>
+        <v>18090118</v>
       </c>
       <c r="Q450" t="s">
         <v>252</v>
       </c>
       <c r="R450" s="1">
-        <v>46256.00536641204</v>
+        <v>46256.00539434027</v>
       </c>
       <c r="S450">
         <v>1</v>
       </c>
       <c r="T450" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="V450" t="s">
         <v>271</v>
@@ -33360,10 +33357,10 @@
     </row>
     <row r="451" spans="1:34">
       <c r="A451">
-        <v>6779</v>
+        <v>6945</v>
       </c>
       <c r="B451" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C451" t="s">
         <v>58</v>
@@ -33375,7 +33372,7 @@
         <v>62</v>
       </c>
       <c r="F451" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G451">
         <v>5787</v>
@@ -33387,7 +33384,7 @@
         <v>69</v>
       </c>
       <c r="J451" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="L451" s="1">
         <v>46286</v>
@@ -33396,22 +33393,19 @@
         <v>223</v>
       </c>
       <c r="O451">
-        <v>18090118</v>
+        <v>18179058</v>
       </c>
       <c r="Q451" t="s">
         <v>252</v>
       </c>
       <c r="R451" s="1">
-        <v>46256.00539434027</v>
+        <v>46256.00540109954</v>
       </c>
       <c r="S451">
         <v>1</v>
       </c>
       <c r="T451" t="s">
-        <v>261</v>
-      </c>
-      <c r="V451" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="AA451">
         <v>0</v>
@@ -33425,10 +33419,10 @@
     </row>
     <row r="452" spans="1:34">
       <c r="A452">
-        <v>6945</v>
+        <v>6628</v>
       </c>
       <c r="B452" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C452" t="s">
         <v>58</v>
@@ -33437,13 +33431,13 @@
         <v>60</v>
       </c>
       <c r="E452" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F452" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G452">
-        <v>5787</v>
+        <v>11810</v>
       </c>
       <c r="H452">
         <v>0</v>
@@ -33457,29 +33451,38 @@
       <c r="L452" s="1">
         <v>46286</v>
       </c>
+      <c r="M452" t="s">
+        <v>215</v>
+      </c>
       <c r="N452" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="O452">
-        <v>18179058</v>
+        <v>18278512</v>
       </c>
       <c r="Q452" t="s">
         <v>252</v>
       </c>
       <c r="R452" s="1">
-        <v>46256.00540109954</v>
+        <v>46286.6987844213</v>
       </c>
       <c r="S452">
         <v>1</v>
       </c>
       <c r="T452" t="s">
-        <v>257</v>
+        <v>256</v>
+      </c>
+      <c r="V452" t="s">
+        <v>271</v>
+      </c>
+      <c r="W452" t="s">
+        <v>404</v>
       </c>
       <c r="AA452">
         <v>0</v>
       </c>
       <c r="AB452" t="s">
-        <v>465</v>
+        <v>230</v>
       </c>
       <c r="AG452" t="s">
         <v>471</v>
@@ -33487,10 +33490,10 @@
     </row>
     <row r="453" spans="1:34">
       <c r="A453">
-        <v>6628</v>
+        <v>6779</v>
       </c>
       <c r="B453" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C453" t="s">
         <v>58</v>
@@ -33499,16 +33502,16 @@
         <v>60</v>
       </c>
       <c r="E453" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F453" t="s">
         <v>64</v>
       </c>
       <c r="G453">
-        <v>11810</v>
+        <v>5837</v>
       </c>
       <c r="H453">
-        <v>0</v>
+        <v>5784</v>
       </c>
       <c r="I453" t="s">
         <v>69</v>
@@ -33517,57 +33520,63 @@
         <v>162</v>
       </c>
       <c r="L453" s="1">
-        <v>46286</v>
+        <v>46283</v>
       </c>
       <c r="M453" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N453" t="s">
         <v>220</v>
       </c>
       <c r="O453">
-        <v>18278512</v>
+        <v>18195614</v>
+      </c>
+      <c r="P453" t="s">
+        <v>237</v>
       </c>
       <c r="Q453" t="s">
         <v>252</v>
       </c>
       <c r="R453" s="1">
-        <v>46286.6987844213</v>
+        <v>46279.66713805556</v>
       </c>
       <c r="S453">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T453" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="V453" t="s">
         <v>271</v>
       </c>
       <c r="W453" t="s">
-        <v>405</v>
+        <v>385</v>
       </c>
       <c r="AA453">
         <v>0</v>
       </c>
       <c r="AB453" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="AG453" t="s">
-        <v>471</v>
+        <v>472</v>
+      </c>
+      <c r="AH453" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="454" spans="1:34">
       <c r="A454">
-        <v>6779</v>
+        <v>6486</v>
       </c>
       <c r="B454" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C454" t="s">
         <v>58</v>
       </c>
       <c r="D454" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E454" t="s">
         <v>62</v>
@@ -33576,69 +33585,63 @@
         <v>64</v>
       </c>
       <c r="G454">
-        <v>5837</v>
+        <v>6348</v>
       </c>
       <c r="H454">
-        <v>5784</v>
+        <v>0</v>
       </c>
       <c r="I454" t="s">
         <v>69</v>
       </c>
       <c r="J454" t="s">
-        <v>163</v>
+        <v>91</v>
       </c>
       <c r="L454" s="1">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="M454" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N454" t="s">
         <v>220</v>
       </c>
       <c r="O454">
-        <v>18195614</v>
-      </c>
-      <c r="P454" t="s">
-        <v>237</v>
+        <v>18271101</v>
       </c>
       <c r="Q454" t="s">
         <v>252</v>
       </c>
       <c r="R454" s="1">
-        <v>46279.66713805556</v>
+        <v>46281.63317659722</v>
       </c>
       <c r="S454">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T454" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="V454" t="s">
         <v>271</v>
       </c>
       <c r="W454" t="s">
-        <v>386</v>
+        <v>405</v>
       </c>
       <c r="AA454">
         <v>0</v>
       </c>
       <c r="AB454" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="AG454" t="s">
         <v>472</v>
       </c>
-      <c r="AH454" t="s">
-        <v>463</v>
-      </c>
     </row>
     <row r="455" spans="1:34">
       <c r="A455">
-        <v>6486</v>
+        <v>6949</v>
       </c>
       <c r="B455" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C455" t="s">
         <v>58</v>
@@ -33650,7 +33653,7 @@
         <v>62</v>
       </c>
       <c r="F455" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G455">
         <v>6348</v>
@@ -33665,31 +33668,31 @@
         <v>91</v>
       </c>
       <c r="L455" s="1">
-        <v>46282</v>
+        <v>46288</v>
       </c>
       <c r="M455" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="N455" t="s">
         <v>220</v>
       </c>
       <c r="O455">
-        <v>18271101</v>
+        <v>18275979</v>
+      </c>
+      <c r="P455" t="s">
+        <v>232</v>
       </c>
       <c r="Q455" t="s">
         <v>252</v>
       </c>
       <c r="R455" s="1">
-        <v>46281.63317659722</v>
+        <v>46286.74096042824</v>
       </c>
       <c r="S455">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="T455" t="s">
-        <v>262</v>
-      </c>
-      <c r="V455" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="W455" t="s">
         <v>406</v>
@@ -33698,18 +33701,21 @@
         <v>0</v>
       </c>
       <c r="AB455" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG455" t="s">
         <v>472</v>
       </c>
+      <c r="AH455" t="s">
+        <v>479</v>
+      </c>
     </row>
     <row r="456" spans="1:34">
       <c r="A456">
-        <v>6949</v>
+        <v>6548</v>
       </c>
       <c r="B456" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C456" t="s">
         <v>58</v>
@@ -33721,69 +33727,66 @@
         <v>62</v>
       </c>
       <c r="F456" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G456">
-        <v>6348</v>
+        <v>11550</v>
       </c>
       <c r="H456">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="I456" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J456" t="s">
-        <v>91</v>
+        <v>163</v>
       </c>
       <c r="L456" s="1">
-        <v>46288</v>
-      </c>
-      <c r="M456" t="s">
-        <v>209</v>
+        <v>46286</v>
       </c>
       <c r="N456" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O456">
-        <v>18275979</v>
+        <v>17988603</v>
       </c>
       <c r="P456" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="Q456" t="s">
         <v>252</v>
       </c>
       <c r="R456" s="1">
-        <v>46286.74096042824</v>
+        <v>46267.72055925926</v>
       </c>
       <c r="S456">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="T456" t="s">
-        <v>258</v>
-      </c>
-      <c r="W456" t="s">
-        <v>407</v>
+        <v>255</v>
+      </c>
+      <c r="V456" t="s">
+        <v>271</v>
       </c>
       <c r="AA456">
         <v>0</v>
       </c>
       <c r="AB456" t="s">
-        <v>232</v>
+        <v>464</v>
       </c>
       <c r="AG456" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AH456" t="s">
-        <v>479</v>
+        <v>464</v>
       </c>
     </row>
     <row r="457" spans="1:34">
       <c r="A457">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B457" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C457" t="s">
         <v>58</v>
@@ -33792,7 +33795,7 @@
         <v>59</v>
       </c>
       <c r="E457" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F457" t="s">
         <v>64</v>
@@ -33807,7 +33810,7 @@
         <v>70</v>
       </c>
       <c r="J457" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L457" s="1">
         <v>46286</v>
@@ -33816,22 +33819,22 @@
         <v>219</v>
       </c>
       <c r="O457">
-        <v>17988603</v>
+        <v>18048493</v>
       </c>
       <c r="P457" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q457" t="s">
         <v>252</v>
       </c>
       <c r="R457" s="1">
-        <v>46267.72055925926</v>
+        <v>46267.79441380787</v>
       </c>
       <c r="S457">
         <v>1</v>
       </c>
       <c r="T457" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="V457" t="s">
         <v>271</v>
@@ -33845,16 +33848,13 @@
       <c r="AG457" t="s">
         <v>471</v>
       </c>
-      <c r="AH457" t="s">
-        <v>464</v>
-      </c>
     </row>
     <row r="458" spans="1:34">
       <c r="A458">
-        <v>6627</v>
+        <v>6949</v>
       </c>
       <c r="B458" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C458" t="s">
         <v>58</v>
@@ -33863,10 +33863,10 @@
         <v>59</v>
       </c>
       <c r="E458" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F458" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G458">
         <v>11550</v>
@@ -33878,7 +33878,7 @@
         <v>70</v>
       </c>
       <c r="J458" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L458" s="1">
         <v>46286</v>
@@ -33887,42 +33887,42 @@
         <v>219</v>
       </c>
       <c r="O458">
-        <v>18048493</v>
+        <v>18214931</v>
       </c>
       <c r="P458" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q458" t="s">
         <v>252</v>
       </c>
       <c r="R458" s="1">
-        <v>46267.79441380787</v>
+        <v>46267.79441215278</v>
       </c>
       <c r="S458">
         <v>1</v>
       </c>
       <c r="T458" t="s">
-        <v>256</v>
-      </c>
-      <c r="V458" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="AA458">
         <v>0</v>
       </c>
       <c r="AB458" t="s">
-        <v>464</v>
+        <v>241</v>
       </c>
       <c r="AG458" t="s">
         <v>471</v>
       </c>
+      <c r="AH458" t="s">
+        <v>464</v>
+      </c>
     </row>
     <row r="459" spans="1:34">
       <c r="A459">
-        <v>6949</v>
+        <v>6548</v>
       </c>
       <c r="B459" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C459" t="s">
         <v>58</v>
@@ -33934,10 +33934,10 @@
         <v>62</v>
       </c>
       <c r="F459" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G459">
-        <v>11550</v>
+        <v>1913</v>
       </c>
       <c r="H459">
         <v>1862</v>
@@ -33955,28 +33955,31 @@
         <v>219</v>
       </c>
       <c r="O459">
-        <v>18214931</v>
+        <v>17988579</v>
       </c>
       <c r="P459" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="Q459" t="s">
         <v>252</v>
       </c>
       <c r="R459" s="1">
-        <v>46267.79441215278</v>
+        <v>46283.3939177662</v>
       </c>
       <c r="S459">
         <v>1</v>
       </c>
       <c r="T459" t="s">
-        <v>258</v>
+        <v>255</v>
+      </c>
+      <c r="V459" t="s">
+        <v>271</v>
       </c>
       <c r="AA459">
         <v>0</v>
       </c>
       <c r="AB459" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="AG459" t="s">
         <v>471</v>
@@ -33987,10 +33990,10 @@
     </row>
     <row r="460" spans="1:34">
       <c r="A460">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B460" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C460" t="s">
         <v>58</v>
@@ -33999,7 +34002,7 @@
         <v>59</v>
       </c>
       <c r="E460" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F460" t="s">
         <v>64</v>
@@ -34014,54 +34017,57 @@
         <v>70</v>
       </c>
       <c r="J460" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L460" s="1">
         <v>46286</v>
       </c>
+      <c r="M460" t="s">
+        <v>215</v>
+      </c>
       <c r="N460" t="s">
         <v>219</v>
       </c>
       <c r="O460">
-        <v>17988579</v>
+        <v>18048433</v>
       </c>
       <c r="P460" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q460" t="s">
         <v>252</v>
       </c>
       <c r="R460" s="1">
-        <v>46283.3939177662</v>
+        <v>46286.64017539352</v>
       </c>
       <c r="S460">
         <v>1</v>
       </c>
       <c r="T460" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="V460" t="s">
         <v>271</v>
       </c>
+      <c r="W460" t="s">
+        <v>380</v>
+      </c>
       <c r="AA460">
         <v>0</v>
       </c>
       <c r="AB460" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG460" t="s">
         <v>471</v>
       </c>
-      <c r="AH460" t="s">
-        <v>464</v>
-      </c>
     </row>
     <row r="461" spans="1:34">
       <c r="A461">
-        <v>6627</v>
+        <v>6949</v>
       </c>
       <c r="B461" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C461" t="s">
         <v>58</v>
@@ -34070,10 +34076,10 @@
         <v>59</v>
       </c>
       <c r="E461" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F461" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G461">
         <v>1913</v>
@@ -34085,7 +34091,7 @@
         <v>70</v>
       </c>
       <c r="J461" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L461" s="1">
         <v>46286</v>
@@ -34097,51 +34103,51 @@
         <v>219</v>
       </c>
       <c r="O461">
-        <v>18048433</v>
+        <v>18214877</v>
       </c>
       <c r="P461" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q461" t="s">
         <v>252</v>
       </c>
       <c r="R461" s="1">
-        <v>46286.64017539352</v>
+        <v>46286.7204416551</v>
       </c>
       <c r="S461">
         <v>1</v>
       </c>
       <c r="T461" t="s">
-        <v>256</v>
-      </c>
-      <c r="V461" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="W461" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AA461">
         <v>0</v>
       </c>
       <c r="AB461" t="s">
-        <v>239</v>
+        <v>464</v>
       </c>
       <c r="AG461" t="s">
         <v>471</v>
       </c>
+      <c r="AH461" t="s">
+        <v>464</v>
+      </c>
     </row>
     <row r="462" spans="1:34">
       <c r="A462">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B462" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C462" t="s">
         <v>58</v>
       </c>
       <c r="D462" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E462" t="s">
         <v>62</v>
@@ -34150,55 +34156,55 @@
         <v>65</v>
       </c>
       <c r="G462">
-        <v>1913</v>
+        <v>11873</v>
       </c>
       <c r="H462">
-        <v>1862</v>
+        <v>0</v>
       </c>
       <c r="I462" t="s">
         <v>70</v>
       </c>
       <c r="J462" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="L462" s="1">
-        <v>46286</v>
+        <v>46281</v>
       </c>
       <c r="M462" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N462" t="s">
         <v>219</v>
       </c>
       <c r="O462">
-        <v>18214877</v>
+        <v>18223029</v>
       </c>
       <c r="P462" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q462" t="s">
         <v>252</v>
       </c>
       <c r="R462" s="1">
-        <v>46286.7204416551</v>
+        <v>46280.62789608796</v>
       </c>
       <c r="S462">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T462" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="W462" t="s">
-        <v>381</v>
+        <v>407</v>
       </c>
       <c r="AA462">
         <v>0</v>
       </c>
       <c r="AB462" t="s">
-        <v>464</v>
+        <v>242</v>
       </c>
       <c r="AG462" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH462" t="s">
         <v>464</v>
@@ -34206,10 +34212,10 @@
     </row>
     <row r="463" spans="1:34">
       <c r="A463">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B463" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C463" t="s">
         <v>58</v>
@@ -34233,7 +34239,7 @@
         <v>70</v>
       </c>
       <c r="J463" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L463" s="1">
         <v>46281</v>
@@ -34245,7 +34251,7 @@
         <v>219</v>
       </c>
       <c r="O463">
-        <v>18223029</v>
+        <v>18222688</v>
       </c>
       <c r="P463" t="s">
         <v>242</v>
@@ -34254,7 +34260,7 @@
         <v>252</v>
       </c>
       <c r="R463" s="1">
-        <v>46280.62789608796</v>
+        <v>46280.63189497685</v>
       </c>
       <c r="S463">
         <v>6</v>
@@ -34263,7 +34269,7 @@
         <v>259</v>
       </c>
       <c r="W463" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AA463">
         <v>0</v>
@@ -34280,25 +34286,25 @@
     </row>
     <row r="464" spans="1:34">
       <c r="A464">
-        <v>6963</v>
+        <v>6548</v>
       </c>
       <c r="B464" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C464" t="s">
         <v>58</v>
       </c>
       <c r="D464" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E464" t="s">
         <v>62</v>
       </c>
       <c r="F464" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G464">
-        <v>11873</v>
+        <v>1876</v>
       </c>
       <c r="H464">
         <v>0</v>
@@ -34307,34 +34313,34 @@
         <v>70</v>
       </c>
       <c r="J464" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="L464" s="1">
-        <v>46281</v>
-      </c>
-      <c r="M464" t="s">
-        <v>216</v>
+        <v>46283</v>
       </c>
       <c r="N464" t="s">
         <v>219</v>
       </c>
       <c r="O464">
-        <v>18222688</v>
+        <v>17988555</v>
       </c>
       <c r="P464" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="Q464" t="s">
         <v>252</v>
       </c>
       <c r="R464" s="1">
-        <v>46280.63189497685</v>
+        <v>46283.66538607639</v>
       </c>
       <c r="S464">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T464" t="s">
-        <v>259</v>
+        <v>255</v>
+      </c>
+      <c r="V464" t="s">
+        <v>271</v>
       </c>
       <c r="W464" t="s">
         <v>408</v>
@@ -34343,7 +34349,7 @@
         <v>0</v>
       </c>
       <c r="AB464" t="s">
-        <v>242</v>
+        <v>465</v>
       </c>
       <c r="AG464" t="s">
         <v>472</v>
@@ -34354,10 +34360,10 @@
     </row>
     <row r="465" spans="1:34">
       <c r="A465">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B465" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C465" t="s">
         <v>58</v>
@@ -34366,13 +34372,13 @@
         <v>59</v>
       </c>
       <c r="E465" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F465" t="s">
         <v>64</v>
       </c>
       <c r="G465">
-        <v>1876</v>
+        <v>11411</v>
       </c>
       <c r="H465">
         <v>0</v>
@@ -34390,22 +34396,22 @@
         <v>219</v>
       </c>
       <c r="O465">
-        <v>17988555</v>
+        <v>18048483</v>
       </c>
       <c r="P465" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q465" t="s">
         <v>252</v>
       </c>
       <c r="R465" s="1">
-        <v>46283.66538607639</v>
+        <v>46286.43482986111</v>
       </c>
       <c r="S465">
         <v>4</v>
       </c>
       <c r="T465" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="V465" t="s">
         <v>271</v>
@@ -34417,21 +34423,18 @@
         <v>0</v>
       </c>
       <c r="AB465" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="AG465" t="s">
         <v>472</v>
       </c>
-      <c r="AH465" t="s">
-        <v>464</v>
-      </c>
     </row>
     <row r="466" spans="1:34">
       <c r="A466">
-        <v>6627</v>
+        <v>6949</v>
       </c>
       <c r="B466" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C466" t="s">
         <v>58</v>
@@ -34440,10 +34443,10 @@
         <v>59</v>
       </c>
       <c r="E466" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F466" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G466">
         <v>11411</v>
@@ -34455,7 +34458,7 @@
         <v>70</v>
       </c>
       <c r="J466" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L466" s="1">
         <v>46283</v>
@@ -34464,25 +34467,22 @@
         <v>219</v>
       </c>
       <c r="O466">
-        <v>18048483</v>
+        <v>18214925</v>
       </c>
       <c r="P466" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q466" t="s">
         <v>252</v>
       </c>
       <c r="R466" s="1">
-        <v>46286.43482986111</v>
+        <v>46286.74368133102</v>
       </c>
       <c r="S466">
         <v>4</v>
       </c>
       <c r="T466" t="s">
-        <v>256</v>
-      </c>
-      <c r="V466" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="W466" t="s">
         <v>410</v>
@@ -34496,28 +34496,31 @@
       <c r="AG466" t="s">
         <v>472</v>
       </c>
+      <c r="AH466" t="s">
+        <v>464</v>
+      </c>
     </row>
     <row r="467" spans="1:34">
       <c r="A467">
-        <v>6949</v>
+        <v>6628</v>
       </c>
       <c r="B467" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C467" t="s">
         <v>58</v>
       </c>
       <c r="D467" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E467" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F467" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G467">
-        <v>11411</v>
+        <v>1862</v>
       </c>
       <c r="H467">
         <v>0</v>
@@ -34526,43 +34529,43 @@
         <v>70</v>
       </c>
       <c r="J467" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="L467" s="1">
-        <v>46283</v>
+        <v>46281</v>
       </c>
       <c r="N467" t="s">
         <v>219</v>
       </c>
       <c r="O467">
-        <v>18214925</v>
+        <v>18047772</v>
       </c>
       <c r="P467" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q467" t="s">
         <v>252</v>
       </c>
       <c r="R467" s="1">
-        <v>46286.74368133102</v>
+        <v>46265.00319547454</v>
       </c>
       <c r="S467">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T467" t="s">
-        <v>258</v>
-      </c>
-      <c r="W467" t="s">
-        <v>411</v>
+        <v>256</v>
+      </c>
+      <c r="V467" t="s">
+        <v>271</v>
       </c>
       <c r="AA467">
         <v>0</v>
       </c>
       <c r="AB467" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="AG467" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AH467" t="s">
         <v>464</v>
@@ -34570,10 +34573,10 @@
     </row>
     <row r="468" spans="1:34">
       <c r="A468">
-        <v>6628</v>
+        <v>6945</v>
       </c>
       <c r="B468" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C468" t="s">
         <v>58</v>
@@ -34582,10 +34585,10 @@
         <v>60</v>
       </c>
       <c r="E468" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F468" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G468">
         <v>1862</v>
@@ -34597,7 +34600,7 @@
         <v>70</v>
       </c>
       <c r="J468" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L468" s="1">
         <v>46281</v>
@@ -34606,45 +34609,39 @@
         <v>219</v>
       </c>
       <c r="O468">
-        <v>18047772</v>
+        <v>18220176</v>
       </c>
       <c r="P468" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q468" t="s">
         <v>252</v>
       </c>
       <c r="R468" s="1">
-        <v>46265.00319547454</v>
+        <v>46276.37795540509</v>
       </c>
       <c r="S468">
         <v>6</v>
       </c>
       <c r="T468" t="s">
-        <v>256</v>
-      </c>
-      <c r="V468" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="AA468">
         <v>0</v>
       </c>
       <c r="AB468" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG468" t="s">
         <v>471</v>
       </c>
-      <c r="AH468" t="s">
-        <v>464</v>
-      </c>
     </row>
     <row r="469" spans="1:34">
       <c r="A469">
-        <v>6945</v>
+        <v>6628</v>
       </c>
       <c r="B469" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C469" t="s">
         <v>58</v>
@@ -34653,13 +34650,13 @@
         <v>60</v>
       </c>
       <c r="E469" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F469" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G469">
-        <v>1862</v>
+        <v>1879</v>
       </c>
       <c r="H469">
         <v>0</v>
@@ -34668,48 +34665,57 @@
         <v>70</v>
       </c>
       <c r="J469" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="L469" s="1">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="N469" t="s">
         <v>219</v>
       </c>
       <c r="O469">
-        <v>18220176</v>
+        <v>17988684</v>
       </c>
       <c r="P469" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q469" t="s">
         <v>252</v>
       </c>
       <c r="R469" s="1">
-        <v>46276.37795540509</v>
+        <v>46283.41459880787</v>
       </c>
       <c r="S469">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T469" t="s">
-        <v>257</v>
+        <v>256</v>
+      </c>
+      <c r="V469" t="s">
+        <v>271</v>
+      </c>
+      <c r="W469" t="s">
+        <v>411</v>
       </c>
       <c r="AA469">
         <v>0</v>
       </c>
       <c r="AB469" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="AG469" t="s">
-        <v>471</v>
+        <v>472</v>
+      </c>
+      <c r="AH469" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="470" spans="1:34">
       <c r="A470">
-        <v>6628</v>
+        <v>6945</v>
       </c>
       <c r="B470" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C470" t="s">
         <v>58</v>
@@ -34718,10 +34724,10 @@
         <v>60</v>
       </c>
       <c r="E470" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F470" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G470">
         <v>1879</v>
@@ -34733,7 +34739,7 @@
         <v>70</v>
       </c>
       <c r="J470" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L470" s="1">
         <v>46283</v>
@@ -34742,25 +34748,22 @@
         <v>219</v>
       </c>
       <c r="O470">
-        <v>17988684</v>
+        <v>18220194</v>
       </c>
       <c r="P470" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q470" t="s">
         <v>252</v>
       </c>
       <c r="R470" s="1">
-        <v>46283.41459880787</v>
+        <v>46283.73838344908</v>
       </c>
       <c r="S470">
         <v>4</v>
       </c>
       <c r="T470" t="s">
-        <v>256</v>
-      </c>
-      <c r="V470" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="W470" t="s">
         <v>412</v>
@@ -34774,22 +34777,19 @@
       <c r="AG470" t="s">
         <v>472</v>
       </c>
-      <c r="AH470" t="s">
-        <v>464</v>
-      </c>
     </row>
     <row r="471" spans="1:34">
       <c r="A471">
-        <v>6945</v>
+        <v>6962</v>
       </c>
       <c r="B471" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C471" t="s">
         <v>58</v>
       </c>
       <c r="D471" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E471" t="s">
         <v>62</v>
@@ -34798,7 +34798,7 @@
         <v>65</v>
       </c>
       <c r="G471">
-        <v>1879</v>
+        <v>1881</v>
       </c>
       <c r="H471">
         <v>0</v>
@@ -34807,31 +34807,31 @@
         <v>70</v>
       </c>
       <c r="J471" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="L471" s="1">
-        <v>46283</v>
+        <v>46287</v>
       </c>
       <c r="N471" t="s">
         <v>219</v>
       </c>
       <c r="O471">
-        <v>18220194</v>
+        <v>18260044</v>
       </c>
       <c r="P471" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q471" t="s">
         <v>252</v>
       </c>
       <c r="R471" s="1">
-        <v>46283.73838344908</v>
+        <v>46286.76327152778</v>
       </c>
       <c r="S471">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T471" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W471" t="s">
         <v>413</v>
@@ -34845,13 +34845,16 @@
       <c r="AG471" t="s">
         <v>472</v>
       </c>
+      <c r="AH471" t="s">
+        <v>464</v>
+      </c>
     </row>
     <row r="472" spans="1:34">
       <c r="A472">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B472" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C472" t="s">
         <v>58</v>
@@ -34875,7 +34878,7 @@
         <v>70</v>
       </c>
       <c r="J472" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="L472" s="1">
         <v>46287</v>
@@ -34884,7 +34887,7 @@
         <v>219</v>
       </c>
       <c r="O472">
-        <v>18260044</v>
+        <v>18260177</v>
       </c>
       <c r="P472" t="s">
         <v>242</v>
@@ -34893,7 +34896,7 @@
         <v>252</v>
       </c>
       <c r="R472" s="1">
-        <v>46286.76327152778</v>
+        <v>46286.76330447917</v>
       </c>
       <c r="S472">
         <v>0</v>
@@ -34902,7 +34905,7 @@
         <v>259</v>
       </c>
       <c r="W472" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AA472">
         <v>0</v>
@@ -34919,25 +34922,25 @@
     </row>
     <row r="473" spans="1:34">
       <c r="A473">
-        <v>6963</v>
+        <v>6627</v>
       </c>
       <c r="B473" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C473" t="s">
         <v>58</v>
       </c>
       <c r="D473" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E473" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F473" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G473">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="H473">
         <v>0</v>
@@ -34946,7 +34949,7 @@
         <v>70</v>
       </c>
       <c r="J473" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="L473" s="1">
         <v>46287</v>
@@ -34955,22 +34958,25 @@
         <v>219</v>
       </c>
       <c r="O473">
-        <v>18260177</v>
+        <v>17968390</v>
       </c>
       <c r="P473" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="Q473" t="s">
         <v>252</v>
       </c>
       <c r="R473" s="1">
-        <v>46286.76330447917</v>
+        <v>46283.75381304398</v>
       </c>
       <c r="S473">
         <v>0</v>
       </c>
       <c r="T473" t="s">
-        <v>259</v>
+        <v>256</v>
+      </c>
+      <c r="V473" t="s">
+        <v>271</v>
       </c>
       <c r="W473" t="s">
         <v>414</v>
@@ -34979,21 +34985,18 @@
         <v>0</v>
       </c>
       <c r="AB473" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="AG473" t="s">
         <v>472</v>
       </c>
-      <c r="AH473" t="s">
-        <v>464</v>
-      </c>
     </row>
     <row r="474" spans="1:34">
       <c r="A474">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B474" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C474" t="s">
         <v>58</v>
@@ -35002,13 +35005,13 @@
         <v>59</v>
       </c>
       <c r="E474" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F474" t="s">
         <v>64</v>
       </c>
       <c r="G474">
-        <v>1882</v>
+        <v>7026</v>
       </c>
       <c r="H474">
         <v>0</v>
@@ -35017,31 +35020,31 @@
         <v>70</v>
       </c>
       <c r="J474" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="L474" s="1">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="N474" t="s">
         <v>219</v>
       </c>
       <c r="O474">
-        <v>17968390</v>
+        <v>18094899</v>
       </c>
       <c r="P474" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q474" t="s">
         <v>252</v>
       </c>
       <c r="R474" s="1">
-        <v>46283.75381304398</v>
+        <v>46286.59476721065</v>
       </c>
       <c r="S474">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T474" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="V474" t="s">
         <v>271</v>
@@ -35056,15 +35059,18 @@
         <v>465</v>
       </c>
       <c r="AG474" t="s">
-        <v>472</v>
+        <v>471</v>
+      </c>
+      <c r="AH474" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="475" spans="1:34">
       <c r="A475">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B475" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C475" t="s">
         <v>58</v>
@@ -35073,7 +35079,7 @@
         <v>59</v>
       </c>
       <c r="E475" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F475" t="s">
         <v>64</v>
@@ -35088,7 +35094,7 @@
         <v>70</v>
       </c>
       <c r="J475" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L475" s="1">
         <v>46288</v>
@@ -35097,22 +35103,22 @@
         <v>219</v>
       </c>
       <c r="O475">
-        <v>18094899</v>
+        <v>18048473</v>
       </c>
       <c r="P475" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q475" t="s">
         <v>252</v>
       </c>
       <c r="R475" s="1">
-        <v>46286.59476721065</v>
+        <v>46282.74485532408</v>
       </c>
       <c r="S475">
         <v>-1</v>
       </c>
       <c r="T475" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="V475" t="s">
         <v>271</v>
@@ -35129,22 +35135,19 @@
       <c r="AG475" t="s">
         <v>471</v>
       </c>
-      <c r="AH475" t="s">
-        <v>464</v>
-      </c>
     </row>
     <row r="476" spans="1:34">
       <c r="A476">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B476" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C476" t="s">
         <v>58</v>
       </c>
       <c r="D476" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E476" t="s">
         <v>63</v>
@@ -35162,7 +35165,7 @@
         <v>70</v>
       </c>
       <c r="J476" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L476" s="1">
         <v>46288</v>
@@ -35171,16 +35174,16 @@
         <v>219</v>
       </c>
       <c r="O476">
-        <v>18048473</v>
+        <v>18094910</v>
       </c>
       <c r="P476" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q476" t="s">
         <v>252</v>
       </c>
       <c r="R476" s="1">
-        <v>46282.74485532408</v>
+        <v>46280.66345891204</v>
       </c>
       <c r="S476">
         <v>-1</v>
@@ -35203,31 +35206,34 @@
       <c r="AG476" t="s">
         <v>471</v>
       </c>
+      <c r="AH476" t="s">
+        <v>464</v>
+      </c>
     </row>
     <row r="477" spans="1:34">
       <c r="A477">
-        <v>6628</v>
+        <v>6548</v>
       </c>
       <c r="B477" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C477" t="s">
         <v>58</v>
       </c>
       <c r="D477" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E477" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F477" t="s">
         <v>64</v>
       </c>
       <c r="G477">
-        <v>7026</v>
+        <v>1914</v>
       </c>
       <c r="H477">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="I477" t="s">
         <v>70</v>
@@ -35236,40 +35242,37 @@
         <v>169</v>
       </c>
       <c r="L477" s="1">
-        <v>46288</v>
+        <v>46286</v>
       </c>
       <c r="N477" t="s">
         <v>219</v>
       </c>
       <c r="O477">
-        <v>18094910</v>
+        <v>17988591</v>
       </c>
       <c r="P477" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="Q477" t="s">
         <v>252</v>
       </c>
       <c r="R477" s="1">
-        <v>46280.66345891204</v>
+        <v>46283.39413969908</v>
       </c>
       <c r="S477">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="T477" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="V477" t="s">
         <v>271</v>
       </c>
-      <c r="W477" t="s">
-        <v>418</v>
-      </c>
       <c r="AA477">
         <v>0</v>
       </c>
       <c r="AB477" t="s">
-        <v>465</v>
+        <v>238</v>
       </c>
       <c r="AG477" t="s">
         <v>471</v>
@@ -35280,10 +35283,10 @@
     </row>
     <row r="478" spans="1:34">
       <c r="A478">
-        <v>6548</v>
+        <v>6949</v>
       </c>
       <c r="B478" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C478" t="s">
         <v>58</v>
@@ -35295,7 +35298,7 @@
         <v>62</v>
       </c>
       <c r="F478" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G478">
         <v>1914</v>
@@ -35307,40 +35310,43 @@
         <v>70</v>
       </c>
       <c r="J478" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L478" s="1">
         <v>46286</v>
       </c>
+      <c r="M478" t="s">
+        <v>215</v>
+      </c>
       <c r="N478" t="s">
         <v>219</v>
       </c>
       <c r="O478">
-        <v>17988591</v>
+        <v>18214883</v>
       </c>
       <c r="P478" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q478" t="s">
         <v>252</v>
       </c>
       <c r="R478" s="1">
-        <v>46283.39413969908</v>
+        <v>46286.72051887732</v>
       </c>
       <c r="S478">
         <v>1</v>
       </c>
       <c r="T478" t="s">
-        <v>255</v>
-      </c>
-      <c r="V478" t="s">
-        <v>271</v>
+        <v>258</v>
+      </c>
+      <c r="W478" t="s">
+        <v>380</v>
       </c>
       <c r="AA478">
         <v>0</v>
       </c>
       <c r="AB478" t="s">
-        <v>238</v>
+        <v>464</v>
       </c>
       <c r="AG478" t="s">
         <v>471</v>
@@ -35351,10 +35357,10 @@
     </row>
     <row r="479" spans="1:34">
       <c r="A479">
-        <v>6949</v>
+        <v>5417</v>
       </c>
       <c r="B479" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C479" t="s">
         <v>58</v>
@@ -35366,69 +35372,69 @@
         <v>62</v>
       </c>
       <c r="F479" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G479">
-        <v>1914</v>
+        <v>6759</v>
       </c>
       <c r="H479">
-        <v>1862</v>
+        <v>1788</v>
       </c>
       <c r="I479" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J479" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="L479" s="1">
-        <v>46286</v>
+        <v>46289</v>
       </c>
       <c r="M479" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="N479" t="s">
         <v>219</v>
       </c>
       <c r="O479">
-        <v>18214883</v>
+        <v>17399190</v>
       </c>
       <c r="P479" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q479" t="s">
         <v>252</v>
       </c>
       <c r="R479" s="1">
-        <v>46286.72051887732</v>
+        <v>46283.54620269676</v>
       </c>
       <c r="S479">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="T479" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="W479" t="s">
-        <v>381</v>
+        <v>368</v>
       </c>
       <c r="AA479">
         <v>0</v>
       </c>
       <c r="AB479" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG479" t="s">
         <v>471</v>
       </c>
       <c r="AH479" t="s">
-        <v>464</v>
+        <v>480</v>
       </c>
     </row>
     <row r="480" spans="1:34">
       <c r="A480">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B480" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C480" t="s">
         <v>58</v>
@@ -35443,28 +35449,28 @@
         <v>64</v>
       </c>
       <c r="G480">
-        <v>6759</v>
+        <v>11678</v>
       </c>
       <c r="H480">
-        <v>1788</v>
+        <v>0</v>
       </c>
       <c r="I480" t="s">
         <v>71</v>
       </c>
       <c r="J480" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="L480" s="1">
-        <v>46289</v>
+        <v>46281</v>
       </c>
       <c r="M480" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N480" t="s">
         <v>219</v>
       </c>
       <c r="O480">
-        <v>17399190</v>
+        <v>16976381</v>
       </c>
       <c r="P480" t="s">
         <v>243</v>
@@ -35473,22 +35479,25 @@
         <v>252</v>
       </c>
       <c r="R480" s="1">
-        <v>46283.54620269676</v>
+        <v>46286.72594498843</v>
       </c>
       <c r="S480">
-        <v>-2</v>
+        <v>6</v>
       </c>
       <c r="T480" t="s">
-        <v>260</v>
+        <v>262</v>
+      </c>
+      <c r="V480" t="s">
+        <v>271</v>
       </c>
       <c r="W480" t="s">
-        <v>368</v>
+        <v>418</v>
       </c>
       <c r="AA480">
         <v>0</v>
       </c>
       <c r="AB480" t="s">
-        <v>465</v>
+        <v>243</v>
       </c>
       <c r="AG480" t="s">
         <v>471</v>
@@ -35499,10 +35508,10 @@
     </row>
     <row r="481" spans="1:34">
       <c r="A481">
-        <v>6486</v>
+        <v>6704</v>
       </c>
       <c r="B481" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C481" t="s">
         <v>58</v>
@@ -35517,7 +35526,7 @@
         <v>64</v>
       </c>
       <c r="G481">
-        <v>11678</v>
+        <v>11874</v>
       </c>
       <c r="H481">
         <v>0</v>
@@ -35526,19 +35535,19 @@
         <v>71</v>
       </c>
       <c r="J481" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="L481" s="1">
         <v>46281</v>
       </c>
       <c r="M481" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="N481" t="s">
         <v>219</v>
       </c>
       <c r="O481">
-        <v>16976381</v>
+        <v>18273589</v>
       </c>
       <c r="P481" t="s">
         <v>243</v>
@@ -35547,13 +35556,13 @@
         <v>252</v>
       </c>
       <c r="R481" s="1">
-        <v>46286.72594498843</v>
+        <v>46282.70138376157</v>
       </c>
       <c r="S481">
         <v>6</v>
       </c>
       <c r="T481" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="V481" t="s">
         <v>271</v>
@@ -35565,10 +35574,10 @@
         <v>0</v>
       </c>
       <c r="AB481" t="s">
-        <v>243</v>
+        <v>460</v>
       </c>
       <c r="AG481" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH481" t="s">
         <v>480</v>
@@ -35576,16 +35585,16 @@
     </row>
     <row r="482" spans="1:34">
       <c r="A482">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B482" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C482" t="s">
         <v>58</v>
       </c>
       <c r="D482" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E482" t="s">
         <v>62</v>
@@ -35603,7 +35612,7 @@
         <v>71</v>
       </c>
       <c r="J482" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L482" s="1">
         <v>46281</v>
@@ -35615,7 +35624,7 @@
         <v>219</v>
       </c>
       <c r="O482">
-        <v>18273589</v>
+        <v>18239293</v>
       </c>
       <c r="P482" t="s">
         <v>243</v>
@@ -35624,7 +35633,7 @@
         <v>252</v>
       </c>
       <c r="R482" s="1">
-        <v>46282.70138376157</v>
+        <v>46282.7013840625</v>
       </c>
       <c r="S482">
         <v>6</v>
@@ -35632,11 +35641,8 @@
       <c r="T482" t="s">
         <v>261</v>
       </c>
-      <c r="V482" t="s">
-        <v>271</v>
-      </c>
       <c r="W482" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AA482">
         <v>0</v>
@@ -35653,16 +35659,16 @@
     </row>
     <row r="483" spans="1:34">
       <c r="A483">
-        <v>6705</v>
+        <v>6703</v>
       </c>
       <c r="B483" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C483" t="s">
         <v>58</v>
       </c>
       <c r="D483" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E483" t="s">
         <v>62</v>
@@ -35671,7 +35677,7 @@
         <v>64</v>
       </c>
       <c r="G483">
-        <v>11874</v>
+        <v>1802</v>
       </c>
       <c r="H483">
         <v>0</v>
@@ -35680,19 +35686,16 @@
         <v>71</v>
       </c>
       <c r="J483" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="L483" s="1">
-        <v>46281</v>
-      </c>
-      <c r="M483" t="s">
-        <v>218</v>
+        <v>46283</v>
       </c>
       <c r="N483" t="s">
         <v>219</v>
       </c>
       <c r="O483">
-        <v>18239293</v>
+        <v>17948796</v>
       </c>
       <c r="P483" t="s">
         <v>243</v>
@@ -35701,13 +35704,13 @@
         <v>252</v>
       </c>
       <c r="R483" s="1">
-        <v>46282.7013840625</v>
+        <v>46283.75077045139</v>
       </c>
       <c r="S483">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T483" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="W483" t="s">
         <v>420</v>
@@ -35727,16 +35730,16 @@
     </row>
     <row r="484" spans="1:34">
       <c r="A484">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B484" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C484" t="s">
         <v>58</v>
       </c>
       <c r="D484" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E484" t="s">
         <v>62</v>
@@ -35754,16 +35757,19 @@
         <v>71</v>
       </c>
       <c r="J484" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L484" s="1">
         <v>46283</v>
       </c>
+      <c r="M484" t="s">
+        <v>215</v>
+      </c>
       <c r="N484" t="s">
         <v>219</v>
       </c>
       <c r="O484">
-        <v>17948796</v>
+        <v>18085198</v>
       </c>
       <c r="P484" t="s">
         <v>243</v>
@@ -35772,13 +35778,16 @@
         <v>252</v>
       </c>
       <c r="R484" s="1">
-        <v>46283.75077045139</v>
+        <v>46286.36164050926</v>
       </c>
       <c r="S484">
         <v>4</v>
       </c>
       <c r="T484" t="s">
-        <v>263</v>
+        <v>261</v>
+      </c>
+      <c r="V484" t="s">
+        <v>271</v>
       </c>
       <c r="W484" t="s">
         <v>421</v>
@@ -35798,10 +35807,10 @@
     </row>
     <row r="485" spans="1:34">
       <c r="A485">
-        <v>6704</v>
+        <v>5417</v>
       </c>
       <c r="B485" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C485" t="s">
         <v>58</v>
@@ -35816,7 +35825,7 @@
         <v>64</v>
       </c>
       <c r="G485">
-        <v>1802</v>
+        <v>11286</v>
       </c>
       <c r="H485">
         <v>0</v>
@@ -35837,7 +35846,7 @@
         <v>219</v>
       </c>
       <c r="O485">
-        <v>18085198</v>
+        <v>17399434</v>
       </c>
       <c r="P485" t="s">
         <v>243</v>
@@ -35846,19 +35855,16 @@
         <v>252</v>
       </c>
       <c r="R485" s="1">
-        <v>46286.36164050926</v>
+        <v>46286.36164494213</v>
       </c>
       <c r="S485">
         <v>4</v>
       </c>
       <c r="T485" t="s">
-        <v>261</v>
-      </c>
-      <c r="V485" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="W485" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AA485">
         <v>0</v>
@@ -35875,16 +35881,16 @@
     </row>
     <row r="486" spans="1:34">
       <c r="A486">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B486" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C486" t="s">
         <v>58</v>
       </c>
       <c r="D486" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E486" t="s">
         <v>62</v>
@@ -35902,7 +35908,7 @@
         <v>71</v>
       </c>
       <c r="J486" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L486" s="1">
         <v>46283</v>
@@ -35914,7 +35920,7 @@
         <v>219</v>
       </c>
       <c r="O486">
-        <v>17399434</v>
+        <v>16962464</v>
       </c>
       <c r="P486" t="s">
         <v>243</v>
@@ -35923,16 +35929,16 @@
         <v>252</v>
       </c>
       <c r="R486" s="1">
-        <v>46286.36164494213</v>
+        <v>46286.36164826389</v>
       </c>
       <c r="S486">
         <v>4</v>
       </c>
       <c r="T486" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="W486" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AA486">
         <v>0</v>
@@ -35949,16 +35955,16 @@
     </row>
     <row r="487" spans="1:34">
       <c r="A487">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B487" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C487" t="s">
         <v>58</v>
       </c>
       <c r="D487" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E487" t="s">
         <v>62</v>
@@ -35976,19 +35982,16 @@
         <v>71</v>
       </c>
       <c r="J487" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L487" s="1">
         <v>46283</v>
       </c>
-      <c r="M487" t="s">
-        <v>215</v>
-      </c>
       <c r="N487" t="s">
         <v>219</v>
       </c>
       <c r="O487">
-        <v>16962464</v>
+        <v>18155336</v>
       </c>
       <c r="P487" t="s">
         <v>243</v>
@@ -35997,13 +36000,16 @@
         <v>252</v>
       </c>
       <c r="R487" s="1">
-        <v>46286.36164826389</v>
+        <v>46280.59788275463</v>
       </c>
       <c r="S487">
         <v>4</v>
       </c>
       <c r="T487" t="s">
-        <v>264</v>
+        <v>262</v>
+      </c>
+      <c r="V487" t="s">
+        <v>271</v>
       </c>
       <c r="W487" t="s">
         <v>422</v>
@@ -36012,7 +36018,7 @@
         <v>0</v>
       </c>
       <c r="AB487" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="AG487" t="s">
         <v>472</v>
@@ -36023,10 +36029,10 @@
     </row>
     <row r="488" spans="1:34">
       <c r="A488">
-        <v>6486</v>
+        <v>6704</v>
       </c>
       <c r="B488" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C488" t="s">
         <v>58</v>
@@ -36041,7 +36047,7 @@
         <v>64</v>
       </c>
       <c r="G488">
-        <v>11286</v>
+        <v>1788</v>
       </c>
       <c r="H488">
         <v>0</v>
@@ -36050,16 +36056,16 @@
         <v>71</v>
       </c>
       <c r="J488" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="L488" s="1">
-        <v>46283</v>
+        <v>46281</v>
       </c>
       <c r="N488" t="s">
         <v>219</v>
       </c>
       <c r="O488">
-        <v>18155336</v>
+        <v>18085132</v>
       </c>
       <c r="P488" t="s">
         <v>243</v>
@@ -36068,28 +36074,25 @@
         <v>252</v>
       </c>
       <c r="R488" s="1">
-        <v>46280.59788275463</v>
+        <v>46266.45957931713</v>
       </c>
       <c r="S488">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T488" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="V488" t="s">
         <v>271</v>
       </c>
-      <c r="W488" t="s">
-        <v>423</v>
-      </c>
       <c r="AA488">
         <v>0</v>
       </c>
       <c r="AB488" t="s">
-        <v>465</v>
+        <v>243</v>
       </c>
       <c r="AG488" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AH488" t="s">
         <v>480</v>
@@ -36097,16 +36100,16 @@
     </row>
     <row r="489" spans="1:34">
       <c r="A489">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B489" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C489" t="s">
         <v>58</v>
       </c>
       <c r="D489" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E489" t="s">
         <v>62</v>
@@ -36115,7 +36118,7 @@
         <v>64</v>
       </c>
       <c r="G489">
-        <v>1788</v>
+        <v>1805</v>
       </c>
       <c r="H489">
         <v>0</v>
@@ -36124,16 +36127,16 @@
         <v>71</v>
       </c>
       <c r="J489" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="L489" s="1">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="N489" t="s">
         <v>219</v>
       </c>
       <c r="O489">
-        <v>18085132</v>
+        <v>17948948</v>
       </c>
       <c r="P489" t="s">
         <v>243</v>
@@ -36142,25 +36145,25 @@
         <v>252</v>
       </c>
       <c r="R489" s="1">
-        <v>46266.45957931713</v>
+        <v>46283.35452896991</v>
       </c>
       <c r="S489">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T489" t="s">
         <v>261</v>
       </c>
-      <c r="V489" t="s">
-        <v>271</v>
+      <c r="W489" t="s">
+        <v>423</v>
       </c>
       <c r="AA489">
         <v>0</v>
       </c>
       <c r="AB489" t="s">
-        <v>243</v>
+        <v>460</v>
       </c>
       <c r="AG489" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH489" t="s">
         <v>480</v>
@@ -36168,10 +36171,10 @@
     </row>
     <row r="490" spans="1:34">
       <c r="A490">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B490" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C490" t="s">
         <v>58</v>
@@ -36195,7 +36198,7 @@
         <v>71</v>
       </c>
       <c r="J490" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L490" s="1">
         <v>46283</v>
@@ -36204,7 +36207,7 @@
         <v>219</v>
       </c>
       <c r="O490">
-        <v>17948948</v>
+        <v>18084966</v>
       </c>
       <c r="P490" t="s">
         <v>243</v>
@@ -36213,7 +36216,7 @@
         <v>252</v>
       </c>
       <c r="R490" s="1">
-        <v>46283.35452896991</v>
+        <v>46283.35453171296</v>
       </c>
       <c r="S490">
         <v>4</v>
@@ -36221,8 +36224,11 @@
       <c r="T490" t="s">
         <v>261</v>
       </c>
+      <c r="V490" t="s">
+        <v>271</v>
+      </c>
       <c r="W490" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AA490">
         <v>0</v>
@@ -36239,16 +36245,16 @@
     </row>
     <row r="491" spans="1:34">
       <c r="A491">
-        <v>6779</v>
+        <v>6404</v>
       </c>
       <c r="B491" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C491" t="s">
         <v>58</v>
       </c>
       <c r="D491" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E491" t="s">
         <v>62</v>
@@ -36257,7 +36263,7 @@
         <v>64</v>
       </c>
       <c r="G491">
-        <v>1805</v>
+        <v>1811</v>
       </c>
       <c r="H491">
         <v>0</v>
@@ -36266,16 +36272,16 @@
         <v>71</v>
       </c>
       <c r="J491" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="L491" s="1">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="N491" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="O491">
-        <v>18084966</v>
+        <v>16962181</v>
       </c>
       <c r="P491" t="s">
         <v>243</v>
@@ -36284,25 +36290,19 @@
         <v>252</v>
       </c>
       <c r="R491" s="1">
-        <v>46283.35453171296</v>
+        <v>46240.6829959838</v>
       </c>
       <c r="S491">
-        <v>4</v>
+        <v>-3</v>
       </c>
       <c r="T491" t="s">
-        <v>261</v>
-      </c>
-      <c r="V491" t="s">
-        <v>271</v>
-      </c>
-      <c r="W491" t="s">
-        <v>424</v>
+        <v>264</v>
       </c>
       <c r="AA491">
         <v>0</v>
       </c>
       <c r="AB491" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AG491" t="s">
         <v>472</v>
@@ -36313,10 +36313,10 @@
     </row>
     <row r="492" spans="1:34">
       <c r="A492">
-        <v>6404</v>
+        <v>6703</v>
       </c>
       <c r="B492" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C492" t="s">
         <v>58</v>
@@ -36340,16 +36340,19 @@
         <v>71</v>
       </c>
       <c r="J492" t="s">
-        <v>146</v>
+        <v>171</v>
       </c>
       <c r="L492" s="1">
         <v>46290</v>
       </c>
+      <c r="M492" t="s">
+        <v>211</v>
+      </c>
       <c r="N492" t="s">
         <v>222</v>
       </c>
       <c r="O492">
-        <v>16962181</v>
+        <v>17948816</v>
       </c>
       <c r="P492" t="s">
         <v>243</v>
@@ -36358,19 +36361,22 @@
         <v>252</v>
       </c>
       <c r="R492" s="1">
-        <v>46240.6829959838</v>
+        <v>46287.36782538195</v>
       </c>
       <c r="S492">
         <v>-3</v>
       </c>
       <c r="T492" t="s">
-        <v>264</v>
+        <v>263</v>
+      </c>
+      <c r="W492" t="s">
+        <v>424</v>
       </c>
       <c r="AA492">
         <v>0</v>
       </c>
       <c r="AB492" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AG492" t="s">
         <v>472</v>
@@ -36408,7 +36414,7 @@
         <v>71</v>
       </c>
       <c r="J493" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L493" s="1">
         <v>46288</v>
@@ -36479,7 +36485,7 @@
         <v>71</v>
       </c>
       <c r="J494" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L494" s="1">
         <v>46288</v>
@@ -37402,7 +37408,7 @@
         <v>72</v>
       </c>
       <c r="J507" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L507" s="1">
         <v>46290</v>
@@ -37470,7 +37476,7 @@
         <v>72</v>
       </c>
       <c r="J508" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L508" s="1">
         <v>46290</v>
@@ -37535,7 +37541,7 @@
         <v>72</v>
       </c>
       <c r="J509" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L509" s="1">
         <v>46290</v>
@@ -37603,7 +37609,7 @@
         <v>72</v>
       </c>
       <c r="J510" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L510" s="1">
         <v>46290</v>
@@ -37671,7 +37677,7 @@
         <v>72</v>
       </c>
       <c r="J511" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L511" s="1">
         <v>46290</v>
@@ -37739,7 +37745,7 @@
         <v>72</v>
       </c>
       <c r="J512" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L512" s="1">
         <v>46290</v>
@@ -42106,7 +42112,7 @@
         <v>73</v>
       </c>
       <c r="J573" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L573" s="1">
         <v>46289</v>
@@ -42174,7 +42180,7 @@
         <v>73</v>
       </c>
       <c r="J574" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L574" s="1">
         <v>46289</v>
@@ -42535,7 +42541,7 @@
         <v>269</v>
       </c>
       <c r="W579" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AG579" t="s">
         <v>471</v>
@@ -42898,7 +42904,7 @@
         <v>69</v>
       </c>
       <c r="J585" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L585" s="1">
         <v>46286</v>
@@ -42963,7 +42969,7 @@
         <v>69</v>
       </c>
       <c r="J586" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L586" s="1">
         <v>46286</v>
@@ -44180,7 +44186,7 @@
         <v>269</v>
       </c>
       <c r="W605" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AG605" t="s">
         <v>471</v>

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9029" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9031" uniqueCount="482">
   <si>
     <t>CodCliente</t>
   </si>
@@ -1154,13 +1154,16 @@
     <t>Comentário Colaborador + Previsão de Conclusão. Previsto para: 28/09/2026 - Data Comentário: 18/09/2026 15:27</t>
   </si>
   <si>
+    <t>Imposto enviado via SCI Report   Previsão para conclusão dia 22/09/2026 - Data Comentário: 22/09/2026 09:13</t>
+  </si>
+  <si>
     <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1882] sendo a ultima baixa feita [1882]-18/09/2026 18:05:29.. - Data Comentário: 21/09/2026 09:20</t>
   </si>
   <si>
-    <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1881] sendo a ultima baixa feita [1881]-21/09/2026 18:19:06.. - Data Comentário: 21/09/2026 18:14</t>
-  </si>
-  <si>
-    <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1881] sendo a ultima baixa feita [1881]-21/09/2026 18:19:09.. - Data Comentário: 21/09/2026 18:14</t>
+    <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1881] sendo a ultima baixa feita [1881]-21/09/2026 18:19:06.. - Data Comentário: 22/09/2026 09:15</t>
+  </si>
+  <si>
+    <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1881] sendo a ultima baixa feita [1881]-21/09/2026 18:19:09.. - Data Comentário: 22/09/2026 09:15</t>
   </si>
   <si>
     <t>Comentário Colaborador + Previsão de Conclusão. Previsto para: 30/09/2026 - Data Comentário: 18/09/2026 15:28</t>
@@ -2000,13 +2003,13 @@
         <v>0</v>
       </c>
       <c r="AB2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="3" spans="1:34">
@@ -2071,13 +2074,13 @@
         <v>0</v>
       </c>
       <c r="AB3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="4" spans="1:34">
@@ -2142,13 +2145,13 @@
         <v>0</v>
       </c>
       <c r="AB4" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG4" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="5" spans="1:34">
@@ -2210,13 +2213,13 @@
         <v>0</v>
       </c>
       <c r="AB5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG5" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH5" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="6" spans="1:34">
@@ -2278,13 +2281,13 @@
         <v>0</v>
       </c>
       <c r="AB6" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG6" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH6" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="7" spans="1:34">
@@ -2346,13 +2349,13 @@
         <v>0</v>
       </c>
       <c r="AB7" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG7" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH7" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="8" spans="1:34">
@@ -2414,13 +2417,13 @@
         <v>0</v>
       </c>
       <c r="AB8" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG8" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH8" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="9" spans="1:34">
@@ -2482,13 +2485,13 @@
         <v>0</v>
       </c>
       <c r="AB9" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG9" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH9" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="10" spans="1:34">
@@ -2553,13 +2556,13 @@
         <v>0</v>
       </c>
       <c r="AB10" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG10" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH10" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="11" spans="1:34">
@@ -2621,13 +2624,13 @@
         <v>0</v>
       </c>
       <c r="AB11" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG11" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH11" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="12" spans="1:34">
@@ -2692,13 +2695,13 @@
         <v>0</v>
       </c>
       <c r="AB12" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG12" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH12" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="13" spans="1:34">
@@ -2772,10 +2775,10 @@
         <v>230</v>
       </c>
       <c r="AG13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH13" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="14" spans="1:34">
@@ -2840,10 +2843,10 @@
         <v>250</v>
       </c>
       <c r="AG14" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH14" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="15" spans="1:34">
@@ -2914,10 +2917,10 @@
         <v>232</v>
       </c>
       <c r="AG15" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH15" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="16" spans="1:34">
@@ -2988,7 +2991,7 @@
         <v>233</v>
       </c>
       <c r="AG16" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="17" spans="1:34">
@@ -3056,10 +3059,10 @@
         <v>230</v>
       </c>
       <c r="AG17" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH17" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="18" spans="1:34">
@@ -3133,10 +3136,10 @@
         <v>234</v>
       </c>
       <c r="AG18" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH18" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="19" spans="1:34">
@@ -3207,10 +3210,10 @@
         <v>235</v>
       </c>
       <c r="AG19" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH19" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="20" spans="1:34">
@@ -3275,10 +3278,10 @@
         <v>232</v>
       </c>
       <c r="AG20" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH20" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="21" spans="1:34">
@@ -3349,7 +3352,7 @@
         <v>233</v>
       </c>
       <c r="AG21" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="22" spans="1:34">
@@ -3417,13 +3420,13 @@
         <v>0</v>
       </c>
       <c r="AB22" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG22" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH22" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="23" spans="1:34">
@@ -3497,10 +3500,10 @@
         <v>230</v>
       </c>
       <c r="AG23" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH23" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="24" spans="1:34">
@@ -3574,10 +3577,10 @@
         <v>234</v>
       </c>
       <c r="AG24" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH24" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="25" spans="1:34">
@@ -3651,10 +3654,10 @@
         <v>230</v>
       </c>
       <c r="AG25" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH25" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="26" spans="1:34">
@@ -3725,13 +3728,13 @@
         <v>0</v>
       </c>
       <c r="AB26" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG26" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH26" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="27" spans="1:34">
@@ -3802,10 +3805,10 @@
         <v>235</v>
       </c>
       <c r="AG27" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH27" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="28" spans="1:34">
@@ -3879,10 +3882,10 @@
         <v>237</v>
       </c>
       <c r="AG28" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH28" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="29" spans="1:34">
@@ -3953,10 +3956,10 @@
         <v>250</v>
       </c>
       <c r="AG29" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH29" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="30" spans="1:34">
@@ -4021,10 +4024,10 @@
         <v>232</v>
       </c>
       <c r="AG30" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH30" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="31" spans="1:34">
@@ -4092,10 +4095,10 @@
         <v>0</v>
       </c>
       <c r="AB31" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG31" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="32" spans="1:34">
@@ -4169,10 +4172,10 @@
         <v>230</v>
       </c>
       <c r="AG32" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH32" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="33" spans="1:34">
@@ -4246,10 +4249,10 @@
         <v>230</v>
       </c>
       <c r="AG33" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH33" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="34" spans="1:34">
@@ -4323,10 +4326,10 @@
         <v>230</v>
       </c>
       <c r="AG34" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH34" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="35" spans="1:34">
@@ -4397,10 +4400,10 @@
         <v>235</v>
       </c>
       <c r="AG35" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH35" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="36" spans="1:34">
@@ -4474,10 +4477,10 @@
         <v>237</v>
       </c>
       <c r="AG36" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH36" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="37" spans="1:34">
@@ -4548,10 +4551,10 @@
         <v>250</v>
       </c>
       <c r="AG37" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH37" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="38" spans="1:34">
@@ -4622,10 +4625,10 @@
         <v>232</v>
       </c>
       <c r="AG38" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH38" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="39" spans="1:34">
@@ -4690,7 +4693,7 @@
         <v>233</v>
       </c>
       <c r="AG39" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="40" spans="1:34">
@@ -4758,10 +4761,10 @@
         <v>230</v>
       </c>
       <c r="AG40" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH40" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="41" spans="1:34">
@@ -4829,10 +4832,10 @@
         <v>230</v>
       </c>
       <c r="AG41" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH41" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="42" spans="1:34">
@@ -4900,10 +4903,10 @@
         <v>230</v>
       </c>
       <c r="AG42" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH42" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="43" spans="1:34">
@@ -4968,10 +4971,10 @@
         <v>235</v>
       </c>
       <c r="AG43" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH43" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="44" spans="1:34">
@@ -5039,10 +5042,10 @@
         <v>237</v>
       </c>
       <c r="AG44" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH44" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="45" spans="1:34">
@@ -5113,10 +5116,10 @@
         <v>250</v>
       </c>
       <c r="AG45" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH45" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="46" spans="1:34">
@@ -5181,10 +5184,10 @@
         <v>232</v>
       </c>
       <c r="AG46" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH46" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="47" spans="1:34">
@@ -5249,10 +5252,10 @@
         <v>0</v>
       </c>
       <c r="AB47" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG47" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="48" spans="1:34">
@@ -5326,10 +5329,10 @@
         <v>230</v>
       </c>
       <c r="AG48" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH48" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="49" spans="1:34">
@@ -5397,13 +5400,13 @@
         <v>0</v>
       </c>
       <c r="AB49" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG49" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH49" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="50" spans="1:34">
@@ -5477,10 +5480,10 @@
         <v>230</v>
       </c>
       <c r="AG50" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH50" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="51" spans="1:34">
@@ -5554,10 +5557,10 @@
         <v>230</v>
       </c>
       <c r="AG51" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH51" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="52" spans="1:34">
@@ -5622,13 +5625,13 @@
         <v>0</v>
       </c>
       <c r="AB52" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG52" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH52" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="53" spans="1:34">
@@ -5696,13 +5699,13 @@
         <v>0</v>
       </c>
       <c r="AB53" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG53" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH53" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="54" spans="1:34">
@@ -5767,13 +5770,13 @@
         <v>0</v>
       </c>
       <c r="AB54" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG54" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH54" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="55" spans="1:34">
@@ -5838,13 +5841,13 @@
         <v>0</v>
       </c>
       <c r="AB55" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG55" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH55" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="56" spans="1:34">
@@ -5909,7 +5912,7 @@
         <v>233</v>
       </c>
       <c r="AG56" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="57" spans="1:34">
@@ -5977,10 +5980,10 @@
         <v>230</v>
       </c>
       <c r="AG57" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH57" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="58" spans="1:34">
@@ -6054,10 +6057,10 @@
         <v>234</v>
       </c>
       <c r="AG58" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH58" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="59" spans="1:34">
@@ -6128,10 +6131,10 @@
         <v>235</v>
       </c>
       <c r="AG59" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH59" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="60" spans="1:34">
@@ -6196,10 +6199,10 @@
         <v>232</v>
       </c>
       <c r="AG60" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH60" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="61" spans="1:34">
@@ -6264,7 +6267,7 @@
         <v>233</v>
       </c>
       <c r="AG61" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="62" spans="1:34">
@@ -6332,10 +6335,10 @@
         <v>230</v>
       </c>
       <c r="AG62" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH62" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="63" spans="1:34">
@@ -6403,10 +6406,10 @@
         <v>234</v>
       </c>
       <c r="AG63" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH63" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="64" spans="1:34">
@@ -6474,10 +6477,10 @@
         <v>230</v>
       </c>
       <c r="AG64" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH64" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="65" spans="1:34">
@@ -6545,10 +6548,10 @@
         <v>230</v>
       </c>
       <c r="AG65" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH65" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="66" spans="1:34">
@@ -6616,10 +6619,10 @@
         <v>237</v>
       </c>
       <c r="AG66" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH66" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="67" spans="1:34">
@@ -6684,10 +6687,10 @@
         <v>250</v>
       </c>
       <c r="AG67" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH67" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="68" spans="1:34">
@@ -6752,10 +6755,10 @@
         <v>232</v>
       </c>
       <c r="AG68" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH68" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="69" spans="1:34">
@@ -6829,10 +6832,10 @@
         <v>230</v>
       </c>
       <c r="AG69" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH69" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="70" spans="1:34">
@@ -6906,10 +6909,10 @@
         <v>230</v>
       </c>
       <c r="AG70" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH70" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="71" spans="1:34">
@@ -6983,10 +6986,10 @@
         <v>230</v>
       </c>
       <c r="AG71" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH71" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="72" spans="1:34">
@@ -7057,10 +7060,10 @@
         <v>235</v>
       </c>
       <c r="AG72" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH72" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="73" spans="1:34">
@@ -7128,10 +7131,10 @@
         <v>234</v>
       </c>
       <c r="AG73" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH73" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="74" spans="1:34">
@@ -7202,7 +7205,7 @@
         <v>233</v>
       </c>
       <c r="AG74" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="75" spans="1:34">
@@ -7270,13 +7273,13 @@
         <v>0</v>
       </c>
       <c r="AB75" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG75" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH75" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="76" spans="1:34">
@@ -7350,10 +7353,10 @@
         <v>230</v>
       </c>
       <c r="AG76" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH76" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="77" spans="1:34">
@@ -7427,10 +7430,10 @@
         <v>230</v>
       </c>
       <c r="AG77" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH77" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="78" spans="1:34">
@@ -7504,10 +7507,10 @@
         <v>230</v>
       </c>
       <c r="AG78" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH78" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="79" spans="1:34">
@@ -7578,10 +7581,10 @@
         <v>235</v>
       </c>
       <c r="AG79" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH79" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="80" spans="1:34">
@@ -7655,10 +7658,10 @@
         <v>237</v>
       </c>
       <c r="AG80" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH80" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="81" spans="1:34">
@@ -7729,10 +7732,10 @@
         <v>250</v>
       </c>
       <c r="AG81" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH81" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="82" spans="1:34">
@@ -7803,10 +7806,10 @@
         <v>232</v>
       </c>
       <c r="AG82" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH82" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="83" spans="1:34">
@@ -7880,10 +7883,10 @@
         <v>230</v>
       </c>
       <c r="AG83" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH83" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="84" spans="1:34">
@@ -7948,7 +7951,7 @@
         <v>233</v>
       </c>
       <c r="AG84" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="85" spans="1:34">
@@ -8010,13 +8013,13 @@
         <v>0</v>
       </c>
       <c r="AB85" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG85" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH85" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="86" spans="1:34">
@@ -8084,10 +8087,10 @@
         <v>230</v>
       </c>
       <c r="AG86" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH86" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="87" spans="1:34">
@@ -8155,10 +8158,10 @@
         <v>230</v>
       </c>
       <c r="AG87" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH87" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="88" spans="1:34">
@@ -8226,10 +8229,10 @@
         <v>230</v>
       </c>
       <c r="AG88" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH88" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="89" spans="1:34">
@@ -8294,10 +8297,10 @@
         <v>235</v>
       </c>
       <c r="AG89" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH89" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="90" spans="1:34">
@@ -8365,10 +8368,10 @@
         <v>237</v>
       </c>
       <c r="AG90" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH90" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="91" spans="1:34">
@@ -8433,10 +8436,10 @@
         <v>250</v>
       </c>
       <c r="AG91" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH91" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="92" spans="1:34">
@@ -8501,10 +8504,10 @@
         <v>232</v>
       </c>
       <c r="AG92" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH92" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="93" spans="1:34">
@@ -8575,7 +8578,7 @@
         <v>230</v>
       </c>
       <c r="AG93" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="94" spans="1:34">
@@ -8646,7 +8649,7 @@
         <v>230</v>
       </c>
       <c r="AG94" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="95" spans="1:34">
@@ -8714,7 +8717,7 @@
         <v>232</v>
       </c>
       <c r="AG95" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="96" spans="1:34">
@@ -8782,7 +8785,7 @@
         <v>232</v>
       </c>
       <c r="AG96" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="97" spans="1:34">
@@ -8850,7 +8853,7 @@
         <v>232</v>
       </c>
       <c r="AG97" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="98" spans="1:34">
@@ -8915,13 +8918,13 @@
         <v>0</v>
       </c>
       <c r="AB98" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG98" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH98" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="99" spans="1:34">
@@ -8986,10 +8989,10 @@
         <v>0</v>
       </c>
       <c r="AB99" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG99" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="100" spans="1:34">
@@ -9054,10 +9057,10 @@
         <v>0</v>
       </c>
       <c r="AB100" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG100" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="101" spans="1:34">
@@ -9119,7 +9122,7 @@
         <v>241</v>
       </c>
       <c r="AG101" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="102" spans="1:34">
@@ -9184,13 +9187,13 @@
         <v>0</v>
       </c>
       <c r="AB102" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG102" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH102" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="103" spans="1:34">
@@ -9255,10 +9258,10 @@
         <v>0</v>
       </c>
       <c r="AB103" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG103" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="104" spans="1:34">
@@ -9323,13 +9326,13 @@
         <v>0</v>
       </c>
       <c r="AB104" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG104" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH104" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="105" spans="1:34">
@@ -9388,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AB105" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG105" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="106" spans="1:34">
@@ -9453,7 +9456,7 @@
         <v>241</v>
       </c>
       <c r="AG106" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="107" spans="1:34">
@@ -9518,13 +9521,13 @@
         <v>0</v>
       </c>
       <c r="AB107" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG107" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH107" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="108" spans="1:34">
@@ -9589,10 +9592,10 @@
         <v>0</v>
       </c>
       <c r="AB108" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG108" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="109" spans="1:34">
@@ -9657,13 +9660,13 @@
         <v>0</v>
       </c>
       <c r="AB109" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG109" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH109" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="110" spans="1:34">
@@ -9722,10 +9725,10 @@
         <v>0</v>
       </c>
       <c r="AB110" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG110" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="111" spans="1:34">
@@ -9787,7 +9790,7 @@
         <v>241</v>
       </c>
       <c r="AG111" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="112" spans="1:34">
@@ -9852,13 +9855,13 @@
         <v>0</v>
       </c>
       <c r="AB112" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG112" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH112" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="113" spans="1:34">
@@ -9923,10 +9926,10 @@
         <v>0</v>
       </c>
       <c r="AB113" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG113" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="114" spans="1:34">
@@ -9991,10 +9994,10 @@
         <v>241</v>
       </c>
       <c r="AG114" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH114" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="115" spans="1:34">
@@ -10062,13 +10065,13 @@
         <v>0</v>
       </c>
       <c r="AB115" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG115" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH115" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="116" spans="1:34">
@@ -10130,10 +10133,10 @@
         <v>0</v>
       </c>
       <c r="AB116" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG116" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="117" spans="1:34">
@@ -10198,13 +10201,13 @@
         <v>0</v>
       </c>
       <c r="AB117" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG117" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH117" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="118" spans="1:34">
@@ -10269,10 +10272,10 @@
         <v>0</v>
       </c>
       <c r="AB118" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG118" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="119" spans="1:34">
@@ -10337,13 +10340,13 @@
         <v>0</v>
       </c>
       <c r="AB119" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG119" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH119" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="120" spans="1:34">
@@ -10402,10 +10405,10 @@
         <v>0</v>
       </c>
       <c r="AB120" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG120" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="121" spans="1:34">
@@ -10467,7 +10470,7 @@
         <v>241</v>
       </c>
       <c r="AG121" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="122" spans="1:34">
@@ -10529,13 +10532,13 @@
         <v>0</v>
       </c>
       <c r="AB122" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG122" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH122" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="123" spans="1:34">
@@ -10600,13 +10603,13 @@
         <v>0</v>
       </c>
       <c r="AB123" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG123" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH123" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="124" spans="1:34">
@@ -10668,10 +10671,10 @@
         <v>0</v>
       </c>
       <c r="AB124" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG124" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="125" spans="1:34">
@@ -10736,10 +10739,10 @@
         <v>241</v>
       </c>
       <c r="AG125" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH125" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="126" spans="1:34">
@@ -10801,10 +10804,10 @@
         <v>0</v>
       </c>
       <c r="AB126" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG126" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="127" spans="1:34">
@@ -10866,13 +10869,13 @@
         <v>0</v>
       </c>
       <c r="AB127" t="s">
+        <v>466</v>
+      </c>
+      <c r="AG127" t="s">
+        <v>472</v>
+      </c>
+      <c r="AH127" t="s">
         <v>465</v>
-      </c>
-      <c r="AG127" t="s">
-        <v>471</v>
-      </c>
-      <c r="AH127" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="128" spans="1:34">
@@ -10937,13 +10940,13 @@
         <v>0</v>
       </c>
       <c r="AB128" t="s">
+        <v>466</v>
+      </c>
+      <c r="AG128" t="s">
+        <v>472</v>
+      </c>
+      <c r="AH128" t="s">
         <v>465</v>
-      </c>
-      <c r="AG128" t="s">
-        <v>471</v>
-      </c>
-      <c r="AH128" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="129" spans="1:34">
@@ -11005,10 +11008,10 @@
         <v>0</v>
       </c>
       <c r="AB129" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG129" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="130" spans="1:34">
@@ -11070,13 +11073,13 @@
         <v>0</v>
       </c>
       <c r="AB130" t="s">
+        <v>466</v>
+      </c>
+      <c r="AG130" t="s">
+        <v>472</v>
+      </c>
+      <c r="AH130" t="s">
         <v>465</v>
-      </c>
-      <c r="AG130" t="s">
-        <v>471</v>
-      </c>
-      <c r="AH130" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="131" spans="1:34">
@@ -11141,13 +11144,13 @@
         <v>0</v>
       </c>
       <c r="AB131" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG131" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH131" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="132" spans="1:34">
@@ -11212,10 +11215,10 @@
         <v>0</v>
       </c>
       <c r="AB132" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG132" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="133" spans="1:34">
@@ -11280,13 +11283,13 @@
         <v>0</v>
       </c>
       <c r="AB133" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG133" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH133" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="134" spans="1:34">
@@ -11345,10 +11348,10 @@
         <v>0</v>
       </c>
       <c r="AB134" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG134" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="135" spans="1:34">
@@ -11410,7 +11413,7 @@
         <v>241</v>
       </c>
       <c r="AG135" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="136" spans="1:34">
@@ -11475,13 +11478,13 @@
         <v>0</v>
       </c>
       <c r="AB136" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG136" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH136" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="137" spans="1:34">
@@ -11546,10 +11549,10 @@
         <v>0</v>
       </c>
       <c r="AB137" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG137" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="138" spans="1:34">
@@ -11614,13 +11617,13 @@
         <v>0</v>
       </c>
       <c r="AB138" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG138" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH138" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="139" spans="1:34">
@@ -11679,10 +11682,10 @@
         <v>0</v>
       </c>
       <c r="AB139" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG139" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="140" spans="1:34">
@@ -11744,7 +11747,7 @@
         <v>241</v>
       </c>
       <c r="AG140" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="141" spans="1:34">
@@ -11818,10 +11821,10 @@
         <v>240</v>
       </c>
       <c r="AG141" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH141" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="142" spans="1:34">
@@ -11895,10 +11898,10 @@
         <v>238</v>
       </c>
       <c r="AG142" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH142" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="143" spans="1:34">
@@ -11963,10 +11966,10 @@
         <v>0</v>
       </c>
       <c r="AB143" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG143" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="144" spans="1:34">
@@ -12037,13 +12040,13 @@
         <v>0</v>
       </c>
       <c r="AB144" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG144" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH144" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="145" spans="1:34">
@@ -12114,7 +12117,7 @@
         <v>239</v>
       </c>
       <c r="AG145" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="146" spans="1:34">
@@ -12185,10 +12188,10 @@
         <v>241</v>
       </c>
       <c r="AG146" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH146" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="147" spans="1:34">
@@ -12253,13 +12256,13 @@
         <v>0</v>
       </c>
       <c r="AB147" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG147" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH147" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="148" spans="1:34">
@@ -12330,10 +12333,10 @@
         <v>242</v>
       </c>
       <c r="AG148" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH148" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="149" spans="1:34">
@@ -12401,10 +12404,10 @@
         <v>0</v>
       </c>
       <c r="AB149" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG149" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="150" spans="1:34">
@@ -12475,10 +12478,10 @@
         <v>241</v>
       </c>
       <c r="AG150" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH150" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="151" spans="1:34">
@@ -12543,13 +12546,13 @@
         <v>0</v>
       </c>
       <c r="AB151" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG151" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH151" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="152" spans="1:34">
@@ -12617,10 +12620,10 @@
         <v>242</v>
       </c>
       <c r="AG152" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH152" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="153" spans="1:34">
@@ -12694,10 +12697,10 @@
         <v>238</v>
       </c>
       <c r="AG153" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH153" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="154" spans="1:34">
@@ -12762,10 +12765,10 @@
         <v>0</v>
       </c>
       <c r="AB154" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG154" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="155" spans="1:34">
@@ -12836,7 +12839,7 @@
         <v>239</v>
       </c>
       <c r="AG155" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="156" spans="1:34">
@@ -12907,10 +12910,10 @@
         <v>241</v>
       </c>
       <c r="AG156" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH156" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="157" spans="1:34">
@@ -12975,10 +12978,10 @@
         <v>242</v>
       </c>
       <c r="AG157" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH157" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="158" spans="1:34">
@@ -13043,10 +13046,10 @@
         <v>242</v>
       </c>
       <c r="AG158" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH158" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="159" spans="1:34">
@@ -13111,10 +13114,10 @@
         <v>241</v>
       </c>
       <c r="AG159" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH159" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="160" spans="1:34">
@@ -13188,7 +13191,7 @@
         <v>239</v>
       </c>
       <c r="AG160" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="161" spans="1:34">
@@ -13259,7 +13262,7 @@
         <v>239</v>
       </c>
       <c r="AG161" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="162" spans="1:34">
@@ -13330,10 +13333,10 @@
         <v>241</v>
       </c>
       <c r="AG162" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH162" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="163" spans="1:34">
@@ -13398,10 +13401,10 @@
         <v>243</v>
       </c>
       <c r="AG163" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH163" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="164" spans="1:34">
@@ -13466,10 +13469,10 @@
         <v>243</v>
       </c>
       <c r="AG164" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH164" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="165" spans="1:34">
@@ -13543,10 +13546,10 @@
         <v>243</v>
       </c>
       <c r="AG165" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH165" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="166" spans="1:34">
@@ -13614,10 +13617,10 @@
         <v>243</v>
       </c>
       <c r="AG166" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH166" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="167" spans="1:34">
@@ -13682,10 +13685,10 @@
         <v>243</v>
       </c>
       <c r="AG167" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH167" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="168" spans="1:34">
@@ -13750,10 +13753,10 @@
         <v>243</v>
       </c>
       <c r="AG168" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH168" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="169" spans="1:34">
@@ -13818,10 +13821,10 @@
         <v>243</v>
       </c>
       <c r="AG169" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH169" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="170" spans="1:34">
@@ -13895,10 +13898,10 @@
         <v>243</v>
       </c>
       <c r="AG170" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH170" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="171" spans="1:34">
@@ -13966,10 +13969,10 @@
         <v>243</v>
       </c>
       <c r="AG171" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH171" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="172" spans="1:34">
@@ -14031,13 +14034,13 @@
         <v>0</v>
       </c>
       <c r="AB172" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG172" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH172" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="173" spans="1:34">
@@ -14099,13 +14102,13 @@
         <v>0</v>
       </c>
       <c r="AB173" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG173" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH173" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="174" spans="1:34">
@@ -14176,13 +14179,13 @@
         <v>0</v>
       </c>
       <c r="AB174" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG174" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH174" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="175" spans="1:34">
@@ -14244,13 +14247,13 @@
         <v>0</v>
       </c>
       <c r="AB175" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG175" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH175" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="176" spans="1:34">
@@ -14315,13 +14318,13 @@
         <v>0</v>
       </c>
       <c r="AB176" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG176" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH176" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="177" spans="1:34">
@@ -14383,13 +14386,13 @@
         <v>0</v>
       </c>
       <c r="AB177" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG177" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH177" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="178" spans="1:34">
@@ -14463,10 +14466,10 @@
         <v>243</v>
       </c>
       <c r="AG178" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH178" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="179" spans="1:34">
@@ -14534,10 +14537,10 @@
         <v>243</v>
       </c>
       <c r="AG179" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH179" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="180" spans="1:34">
@@ -14599,13 +14602,13 @@
         <v>0</v>
       </c>
       <c r="AB180" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG180" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH180" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="181" spans="1:34">
@@ -14667,13 +14670,13 @@
         <v>0</v>
       </c>
       <c r="AB181" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG181" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH181" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="182" spans="1:34">
@@ -14738,13 +14741,13 @@
         <v>0</v>
       </c>
       <c r="AB182" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG182" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH182" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="183" spans="1:34">
@@ -14806,13 +14809,13 @@
         <v>0</v>
       </c>
       <c r="AB183" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG183" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH183" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="184" spans="1:34">
@@ -14877,13 +14880,13 @@
         <v>0</v>
       </c>
       <c r="AB184" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG184" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH184" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="185" spans="1:34">
@@ -14945,13 +14948,13 @@
         <v>0</v>
       </c>
       <c r="AB185" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG185" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH185" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="186" spans="1:34">
@@ -15022,10 +15025,10 @@
         <v>243</v>
       </c>
       <c r="AG186" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH186" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="187" spans="1:34">
@@ -15090,10 +15093,10 @@
         <v>243</v>
       </c>
       <c r="AG187" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH187" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="188" spans="1:34">
@@ -15158,10 +15161,10 @@
         <v>243</v>
       </c>
       <c r="AG188" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH188" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="189" spans="1:34">
@@ -15229,10 +15232,10 @@
         <v>243</v>
       </c>
       <c r="AG189" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH189" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="190" spans="1:34">
@@ -15297,10 +15300,10 @@
         <v>243</v>
       </c>
       <c r="AG190" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH190" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="191" spans="1:34">
@@ -15368,10 +15371,10 @@
         <v>243</v>
       </c>
       <c r="AG191" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH191" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="192" spans="1:34">
@@ -15442,10 +15445,10 @@
         <v>243</v>
       </c>
       <c r="AG192" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH192" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="193" spans="1:34">
@@ -15513,10 +15516,10 @@
         <v>243</v>
       </c>
       <c r="AG193" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH193" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="194" spans="1:34">
@@ -15587,10 +15590,10 @@
         <v>243</v>
       </c>
       <c r="AG194" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH194" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="195" spans="1:34">
@@ -15655,10 +15658,10 @@
         <v>243</v>
       </c>
       <c r="AG195" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH195" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="196" spans="1:34">
@@ -15723,10 +15726,10 @@
         <v>243</v>
       </c>
       <c r="AG196" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH196" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="197" spans="1:34">
@@ -15794,10 +15797,10 @@
         <v>243</v>
       </c>
       <c r="AG197" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH197" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="198" spans="1:34">
@@ -15862,10 +15865,10 @@
         <v>243</v>
       </c>
       <c r="AG198" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH198" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="199" spans="1:34">
@@ -15933,10 +15936,10 @@
         <v>243</v>
       </c>
       <c r="AG199" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH199" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="200" spans="1:34">
@@ -16001,10 +16004,10 @@
         <v>243</v>
       </c>
       <c r="AG200" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH200" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="201" spans="1:34">
@@ -16072,10 +16075,10 @@
         <v>243</v>
       </c>
       <c r="AG201" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH201" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="202" spans="1:34">
@@ -16140,10 +16143,10 @@
         <v>243</v>
       </c>
       <c r="AG202" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH202" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="203" spans="1:34">
@@ -16211,10 +16214,10 @@
         <v>243</v>
       </c>
       <c r="AG203" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH203" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="204" spans="1:34">
@@ -16285,10 +16288,10 @@
         <v>243</v>
       </c>
       <c r="AG204" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH204" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="205" spans="1:34">
@@ -16362,10 +16365,10 @@
         <v>243</v>
       </c>
       <c r="AG205" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH205" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="206" spans="1:34">
@@ -16433,10 +16436,10 @@
         <v>243</v>
       </c>
       <c r="AG206" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH206" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="207" spans="1:34">
@@ -16501,10 +16504,10 @@
         <v>243</v>
       </c>
       <c r="AG207" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH207" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="208" spans="1:34">
@@ -16575,10 +16578,10 @@
         <v>243</v>
       </c>
       <c r="AG208" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH208" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="209" spans="1:34">
@@ -16643,13 +16646,13 @@
         <v>0</v>
       </c>
       <c r="AB209" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG209" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH209" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="210" spans="1:34">
@@ -16717,13 +16720,13 @@
         <v>0</v>
       </c>
       <c r="AB210" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG210" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH210" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="211" spans="1:34">
@@ -16785,13 +16788,13 @@
         <v>0</v>
       </c>
       <c r="AB211" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG211" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH211" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="212" spans="1:34">
@@ -16862,7 +16865,7 @@
         <v>244</v>
       </c>
       <c r="AG212" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="213" spans="1:34">
@@ -16936,7 +16939,7 @@
         <v>244</v>
       </c>
       <c r="AG213" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="214" spans="1:34">
@@ -17004,7 +17007,7 @@
         <v>244</v>
       </c>
       <c r="AG214" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="215" spans="1:34">
@@ -17072,7 +17075,7 @@
         <v>244</v>
       </c>
       <c r="AG215" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="216" spans="1:34">
@@ -17140,7 +17143,7 @@
         <v>244</v>
       </c>
       <c r="AG216" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="217" spans="1:34">
@@ -17211,7 +17214,7 @@
         <v>244</v>
       </c>
       <c r="AG217" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="218" spans="1:34">
@@ -17279,7 +17282,7 @@
         <v>244</v>
       </c>
       <c r="AG218" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="219" spans="1:34">
@@ -17350,7 +17353,7 @@
         <v>244</v>
       </c>
       <c r="AG219" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="220" spans="1:34">
@@ -17424,7 +17427,7 @@
         <v>244</v>
       </c>
       <c r="AG220" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="221" spans="1:34">
@@ -17495,7 +17498,7 @@
         <v>244</v>
       </c>
       <c r="AG221" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="222" spans="1:34">
@@ -17569,7 +17572,7 @@
         <v>244</v>
       </c>
       <c r="AG222" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="223" spans="1:34">
@@ -17640,7 +17643,7 @@
         <v>244</v>
       </c>
       <c r="AG223" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="224" spans="1:34">
@@ -17708,7 +17711,7 @@
         <v>244</v>
       </c>
       <c r="AG224" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="225" spans="1:33">
@@ -17776,7 +17779,7 @@
         <v>244</v>
       </c>
       <c r="AG225" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="226" spans="1:33">
@@ -17844,7 +17847,7 @@
         <v>244</v>
       </c>
       <c r="AG226" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="227" spans="1:33">
@@ -17912,10 +17915,10 @@
         <v>0</v>
       </c>
       <c r="AB227" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG227" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="228" spans="1:33">
@@ -17983,10 +17986,10 @@
         <v>0</v>
       </c>
       <c r="AB228" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG228" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="229" spans="1:33">
@@ -18057,10 +18060,10 @@
         <v>0</v>
       </c>
       <c r="AB229" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG229" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="230" spans="1:33">
@@ -18131,10 +18134,10 @@
         <v>0</v>
       </c>
       <c r="AB230" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG230" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="231" spans="1:33">
@@ -18205,10 +18208,10 @@
         <v>0</v>
       </c>
       <c r="AB231" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG231" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="232" spans="1:33">
@@ -18279,10 +18282,10 @@
         <v>0</v>
       </c>
       <c r="AB232" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG232" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="233" spans="1:33">
@@ -18350,10 +18353,10 @@
         <v>0</v>
       </c>
       <c r="AB233" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG233" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="234" spans="1:33">
@@ -18424,10 +18427,10 @@
         <v>0</v>
       </c>
       <c r="AB234" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG234" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="235" spans="1:33">
@@ -18495,10 +18498,10 @@
         <v>0</v>
       </c>
       <c r="AB235" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG235" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="236" spans="1:33">
@@ -18569,10 +18572,10 @@
         <v>0</v>
       </c>
       <c r="AB236" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG236" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="237" spans="1:33">
@@ -18640,10 +18643,10 @@
         <v>0</v>
       </c>
       <c r="AB237" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG237" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="238" spans="1:33">
@@ -18711,10 +18714,10 @@
         <v>0</v>
       </c>
       <c r="AB238" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG238" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="239" spans="1:33">
@@ -18782,10 +18785,10 @@
         <v>0</v>
       </c>
       <c r="AB239" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG239" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="240" spans="1:33">
@@ -18853,10 +18856,10 @@
         <v>0</v>
       </c>
       <c r="AB240" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG240" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="241" spans="1:33">
@@ -18918,10 +18921,10 @@
         <v>0</v>
       </c>
       <c r="AB241" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG241" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="242" spans="1:33">
@@ -18983,10 +18986,10 @@
         <v>0</v>
       </c>
       <c r="AB242" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG242" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="243" spans="1:33">
@@ -19051,10 +19054,10 @@
         <v>0</v>
       </c>
       <c r="AB243" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG243" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="244" spans="1:33">
@@ -19119,10 +19122,10 @@
         <v>0</v>
       </c>
       <c r="AB244" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG244" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="245" spans="1:33">
@@ -19187,10 +19190,10 @@
         <v>0</v>
       </c>
       <c r="AB245" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG245" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="246" spans="1:33">
@@ -19255,10 +19258,10 @@
         <v>0</v>
       </c>
       <c r="AB246" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG246" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="247" spans="1:33">
@@ -19320,10 +19323,10 @@
         <v>0</v>
       </c>
       <c r="AB247" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG247" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="248" spans="1:33">
@@ -19388,10 +19391,10 @@
         <v>0</v>
       </c>
       <c r="AB248" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG248" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="249" spans="1:33">
@@ -19453,10 +19456,10 @@
         <v>0</v>
       </c>
       <c r="AB249" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG249" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="250" spans="1:33">
@@ -19518,10 +19521,10 @@
         <v>0</v>
       </c>
       <c r="AB250" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG250" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="251" spans="1:33">
@@ -19583,10 +19586,10 @@
         <v>0</v>
       </c>
       <c r="AB251" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG251" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="252" spans="1:33">
@@ -19651,7 +19654,7 @@
         <v>244</v>
       </c>
       <c r="AG252" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="253" spans="1:33">
@@ -19716,7 +19719,7 @@
         <v>244</v>
       </c>
       <c r="AG253" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="254" spans="1:33">
@@ -19784,7 +19787,7 @@
         <v>244</v>
       </c>
       <c r="AG254" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="255" spans="1:33">
@@ -19852,7 +19855,7 @@
         <v>244</v>
       </c>
       <c r="AG255" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="256" spans="1:33">
@@ -19920,7 +19923,7 @@
         <v>244</v>
       </c>
       <c r="AG256" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="257" spans="1:33">
@@ -19985,7 +19988,7 @@
         <v>244</v>
       </c>
       <c r="AG257" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="258" spans="1:33">
@@ -20050,7 +20053,7 @@
         <v>244</v>
       </c>
       <c r="AG258" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="259" spans="1:33">
@@ -20112,10 +20115,10 @@
         <v>0</v>
       </c>
       <c r="AB259" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG259" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="260" spans="1:33">
@@ -20177,10 +20180,10 @@
         <v>0</v>
       </c>
       <c r="AB260" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG260" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="261" spans="1:33">
@@ -20245,10 +20248,10 @@
         <v>0</v>
       </c>
       <c r="AB261" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG261" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="262" spans="1:33">
@@ -20313,10 +20316,10 @@
         <v>0</v>
       </c>
       <c r="AB262" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG262" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="263" spans="1:33">
@@ -20381,10 +20384,10 @@
         <v>0</v>
       </c>
       <c r="AB263" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG263" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="264" spans="1:33">
@@ -20449,10 +20452,10 @@
         <v>0</v>
       </c>
       <c r="AB264" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG264" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="265" spans="1:33">
@@ -20514,10 +20517,10 @@
         <v>0</v>
       </c>
       <c r="AB265" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG265" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="266" spans="1:33">
@@ -20582,10 +20585,10 @@
         <v>0</v>
       </c>
       <c r="AB266" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG266" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="267" spans="1:33">
@@ -20647,10 +20650,10 @@
         <v>0</v>
       </c>
       <c r="AB267" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG267" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="268" spans="1:33">
@@ -20715,10 +20718,10 @@
         <v>0</v>
       </c>
       <c r="AB268" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG268" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="269" spans="1:33">
@@ -20780,10 +20783,10 @@
         <v>0</v>
       </c>
       <c r="AB269" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG269" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="270" spans="1:33">
@@ -20845,10 +20848,10 @@
         <v>0</v>
       </c>
       <c r="AB270" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG270" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="271" spans="1:33">
@@ -20910,10 +20913,10 @@
         <v>0</v>
       </c>
       <c r="AB271" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG271" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="272" spans="1:33">
@@ -20975,10 +20978,10 @@
         <v>0</v>
       </c>
       <c r="AB272" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG272" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="273" spans="1:33">
@@ -21040,10 +21043,10 @@
         <v>0</v>
       </c>
       <c r="AB273" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG273" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="274" spans="1:33">
@@ -21105,10 +21108,10 @@
         <v>0</v>
       </c>
       <c r="AB274" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG274" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="275" spans="1:33">
@@ -21173,10 +21176,10 @@
         <v>0</v>
       </c>
       <c r="AB275" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG275" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="276" spans="1:33">
@@ -21241,10 +21244,10 @@
         <v>0</v>
       </c>
       <c r="AB276" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG276" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="277" spans="1:33">
@@ -21309,10 +21312,10 @@
         <v>0</v>
       </c>
       <c r="AB277" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG277" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="278" spans="1:33">
@@ -21377,10 +21380,10 @@
         <v>0</v>
       </c>
       <c r="AB278" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG278" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="279" spans="1:33">
@@ -21442,10 +21445,10 @@
         <v>0</v>
       </c>
       <c r="AB279" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG279" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="280" spans="1:33">
@@ -21510,10 +21513,10 @@
         <v>0</v>
       </c>
       <c r="AB280" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG280" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="281" spans="1:33">
@@ -21575,10 +21578,10 @@
         <v>0</v>
       </c>
       <c r="AB281" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG281" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="282" spans="1:33">
@@ -21640,10 +21643,10 @@
         <v>0</v>
       </c>
       <c r="AB282" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG282" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="283" spans="1:33">
@@ -21705,10 +21708,10 @@
         <v>0</v>
       </c>
       <c r="AB283" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG283" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="284" spans="1:33">
@@ -21773,7 +21776,7 @@
         <v>245</v>
       </c>
       <c r="AG284" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="285" spans="1:33">
@@ -21838,7 +21841,7 @@
         <v>245</v>
       </c>
       <c r="AG285" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="286" spans="1:33">
@@ -21906,7 +21909,7 @@
         <v>245</v>
       </c>
       <c r="AG286" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="287" spans="1:33">
@@ -21974,7 +21977,7 @@
         <v>245</v>
       </c>
       <c r="AG287" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="288" spans="1:33">
@@ -22042,7 +22045,7 @@
         <v>245</v>
       </c>
       <c r="AG288" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="289" spans="1:34">
@@ -22107,7 +22110,7 @@
         <v>245</v>
       </c>
       <c r="AG289" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="290" spans="1:34">
@@ -22175,7 +22178,7 @@
         <v>245</v>
       </c>
       <c r="AG290" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="291" spans="1:34">
@@ -22240,7 +22243,7 @@
         <v>245</v>
       </c>
       <c r="AG291" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="292" spans="1:34">
@@ -22311,7 +22314,7 @@
         <v>248</v>
       </c>
       <c r="AG292" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="293" spans="1:34">
@@ -22379,7 +22382,7 @@
         <v>248</v>
       </c>
       <c r="AG293" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="294" spans="1:34">
@@ -22444,10 +22447,10 @@
         <v>0</v>
       </c>
       <c r="AG294" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH294" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="295" spans="1:34">
@@ -22512,10 +22515,10 @@
         <v>0</v>
       </c>
       <c r="AG295" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH295" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="296" spans="1:34">
@@ -22580,10 +22583,10 @@
         <v>0</v>
       </c>
       <c r="AG296" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH296" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="297" spans="1:34">
@@ -22648,10 +22651,10 @@
         <v>0</v>
       </c>
       <c r="AG297" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH297" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="298" spans="1:34">
@@ -22716,10 +22719,10 @@
         <v>0</v>
       </c>
       <c r="AG298" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH298" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="299" spans="1:34">
@@ -22787,10 +22790,10 @@
         <v>0</v>
       </c>
       <c r="AG299" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH299" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="300" spans="1:34">
@@ -22858,10 +22861,10 @@
         <v>0</v>
       </c>
       <c r="AG300" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH300" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="301" spans="1:34">
@@ -22926,10 +22929,10 @@
         <v>0</v>
       </c>
       <c r="AG301" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH301" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="302" spans="1:34">
@@ -22997,10 +23000,10 @@
         <v>0</v>
       </c>
       <c r="AG302" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH302" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="303" spans="1:34">
@@ -23068,10 +23071,10 @@
         <v>0</v>
       </c>
       <c r="AG303" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH303" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="304" spans="1:34">
@@ -23139,10 +23142,10 @@
         <v>0</v>
       </c>
       <c r="AG304" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH304" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="305" spans="1:34">
@@ -23207,10 +23210,10 @@
         <v>0</v>
       </c>
       <c r="AG305" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH305" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="306" spans="1:34">
@@ -23275,10 +23278,10 @@
         <v>0</v>
       </c>
       <c r="AG306" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH306" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="307" spans="1:34">
@@ -23343,10 +23346,10 @@
         <v>0</v>
       </c>
       <c r="AG307" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH307" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="308" spans="1:34">
@@ -23411,10 +23414,10 @@
         <v>0</v>
       </c>
       <c r="AG308" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH308" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="309" spans="1:34">
@@ -23482,10 +23485,10 @@
         <v>0</v>
       </c>
       <c r="AG309" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH309" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="310" spans="1:34">
@@ -23553,10 +23556,10 @@
         <v>0</v>
       </c>
       <c r="AG310" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH310" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="311" spans="1:34">
@@ -23621,10 +23624,10 @@
         <v>0</v>
       </c>
       <c r="AG311" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH311" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="312" spans="1:34">
@@ -23689,10 +23692,10 @@
         <v>0</v>
       </c>
       <c r="AG312" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH312" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="313" spans="1:34">
@@ -23757,10 +23760,10 @@
         <v>0</v>
       </c>
       <c r="AG313" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH313" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="314" spans="1:34">
@@ -23825,10 +23828,10 @@
         <v>0</v>
       </c>
       <c r="AG314" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH314" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="315" spans="1:34">
@@ -23893,10 +23896,10 @@
         <v>0</v>
       </c>
       <c r="AG315" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH315" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="316" spans="1:34">
@@ -23964,10 +23967,10 @@
         <v>0</v>
       </c>
       <c r="AG316" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH316" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="317" spans="1:34">
@@ -24035,10 +24038,10 @@
         <v>0</v>
       </c>
       <c r="AG317" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH317" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="318" spans="1:34">
@@ -24103,10 +24106,10 @@
         <v>0</v>
       </c>
       <c r="AG318" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH318" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="319" spans="1:34">
@@ -24171,10 +24174,10 @@
         <v>0</v>
       </c>
       <c r="AG319" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH319" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="320" spans="1:34">
@@ -24239,10 +24242,10 @@
         <v>0</v>
       </c>
       <c r="AG320" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH320" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="321" spans="1:34">
@@ -24310,10 +24313,10 @@
         <v>0</v>
       </c>
       <c r="AG321" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH321" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="322" spans="1:34">
@@ -24378,10 +24381,10 @@
         <v>0</v>
       </c>
       <c r="AG322" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH322" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="323" spans="1:34">
@@ -24446,10 +24449,10 @@
         <v>0</v>
       </c>
       <c r="AG323" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH323" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="324" spans="1:34">
@@ -24517,10 +24520,10 @@
         <v>0</v>
       </c>
       <c r="AG324" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH324" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="325" spans="1:34">
@@ -24585,10 +24588,10 @@
         <v>0</v>
       </c>
       <c r="AG325" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH325" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="326" spans="1:34">
@@ -24653,10 +24656,10 @@
         <v>0</v>
       </c>
       <c r="AG326" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH326" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="327" spans="1:34">
@@ -24724,10 +24727,10 @@
         <v>0</v>
       </c>
       <c r="AG327" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH327" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="328" spans="1:34">
@@ -24792,10 +24795,10 @@
         <v>0</v>
       </c>
       <c r="AG328" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH328" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="329" spans="1:34">
@@ -24863,10 +24866,10 @@
         <v>0</v>
       </c>
       <c r="AG329" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH329" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="330" spans="1:34">
@@ -24931,10 +24934,10 @@
         <v>0</v>
       </c>
       <c r="AG330" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH330" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="331" spans="1:34">
@@ -25002,10 +25005,10 @@
         <v>0</v>
       </c>
       <c r="AG331" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH331" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="332" spans="1:34">
@@ -25070,10 +25073,10 @@
         <v>0</v>
       </c>
       <c r="AG332" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH332" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="333" spans="1:34">
@@ -25138,10 +25141,10 @@
         <v>0</v>
       </c>
       <c r="AG333" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH333" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="334" spans="1:34">
@@ -25209,10 +25212,10 @@
         <v>0</v>
       </c>
       <c r="AG334" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH334" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="335" spans="1:34">
@@ -25277,10 +25280,10 @@
         <v>0</v>
       </c>
       <c r="AG335" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH335" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="336" spans="1:34">
@@ -25348,10 +25351,10 @@
         <v>0</v>
       </c>
       <c r="AG336" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH336" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="337" spans="1:34">
@@ -25416,10 +25419,10 @@
         <v>0</v>
       </c>
       <c r="AG337" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH337" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="338" spans="1:34">
@@ -25484,10 +25487,10 @@
         <v>0</v>
       </c>
       <c r="AG338" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH338" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="339" spans="1:34">
@@ -25555,10 +25558,10 @@
         <v>0</v>
       </c>
       <c r="AG339" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH339" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="340" spans="1:34">
@@ -25626,10 +25629,10 @@
         <v>0</v>
       </c>
       <c r="AG340" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH340" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="341" spans="1:34">
@@ -25694,10 +25697,10 @@
         <v>0</v>
       </c>
       <c r="AG341" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH341" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="342" spans="1:34">
@@ -25765,10 +25768,10 @@
         <v>0</v>
       </c>
       <c r="AG342" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH342" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="343" spans="1:34">
@@ -25836,10 +25839,10 @@
         <v>0</v>
       </c>
       <c r="AG343" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH343" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="344" spans="1:34">
@@ -25907,10 +25910,10 @@
         <v>0</v>
       </c>
       <c r="AG344" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH344" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="345" spans="1:34">
@@ -25978,10 +25981,10 @@
         <v>0</v>
       </c>
       <c r="AG345" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH345" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="346" spans="1:34">
@@ -26046,7 +26049,7 @@
         <v>0</v>
       </c>
       <c r="AG346" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="347" spans="1:34">
@@ -26114,10 +26117,10 @@
         <v>0</v>
       </c>
       <c r="AG347" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH347" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="348" spans="1:34">
@@ -26185,10 +26188,10 @@
         <v>0</v>
       </c>
       <c r="AG348" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH348" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="349" spans="1:34">
@@ -26256,10 +26259,10 @@
         <v>0</v>
       </c>
       <c r="AG349" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH349" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="350" spans="1:34">
@@ -26324,7 +26327,7 @@
         <v>0</v>
       </c>
       <c r="AG350" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="351" spans="1:34">
@@ -26389,7 +26392,7 @@
         <v>0</v>
       </c>
       <c r="AG351" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="352" spans="1:34">
@@ -26454,7 +26457,7 @@
         <v>0</v>
       </c>
       <c r="AG352" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="353" spans="1:34">
@@ -26522,10 +26525,10 @@
         <v>0</v>
       </c>
       <c r="AG353" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH353" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="354" spans="1:34">
@@ -26590,10 +26593,10 @@
         <v>0</v>
       </c>
       <c r="AG354" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH354" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="355" spans="1:34">
@@ -26661,10 +26664,10 @@
         <v>0</v>
       </c>
       <c r="AG355" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH355" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="356" spans="1:34">
@@ -26729,10 +26732,10 @@
         <v>0</v>
       </c>
       <c r="AG356" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH356" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="357" spans="1:34">
@@ -26797,10 +26800,10 @@
         <v>0</v>
       </c>
       <c r="AG357" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH357" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="358" spans="1:34">
@@ -26859,16 +26862,16 @@
         <v>264</v>
       </c>
       <c r="W358" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="AA358">
         <v>0</v>
       </c>
       <c r="AG358" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH358" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="359" spans="1:34">
@@ -26933,10 +26936,10 @@
         <v>0</v>
       </c>
       <c r="AG359" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH359" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="360" spans="1:34">
@@ -27001,10 +27004,10 @@
         <v>0</v>
       </c>
       <c r="AG360" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH360" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="361" spans="1:34">
@@ -27072,10 +27075,10 @@
         <v>0</v>
       </c>
       <c r="AG361" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH361" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="362" spans="1:34">
@@ -27137,13 +27140,13 @@
         <v>271</v>
       </c>
       <c r="W362" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AA362">
         <v>0</v>
       </c>
       <c r="AG362" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="363" spans="1:34">
@@ -27180,6 +27183,9 @@
       <c r="L363" s="1">
         <v>46290</v>
       </c>
+      <c r="M363" t="s">
+        <v>211</v>
+      </c>
       <c r="N363" t="s">
         <v>219</v>
       </c>
@@ -27199,13 +27205,13 @@
         <v>259</v>
       </c>
       <c r="W363" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AA363">
         <v>0</v>
       </c>
       <c r="AG363" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="364" spans="1:34">
@@ -27242,6 +27248,9 @@
       <c r="L364" s="1">
         <v>46290</v>
       </c>
+      <c r="M364" t="s">
+        <v>211</v>
+      </c>
       <c r="N364" t="s">
         <v>219</v>
       </c>
@@ -27261,13 +27270,13 @@
         <v>259</v>
       </c>
       <c r="W364" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AA364">
         <v>0</v>
       </c>
       <c r="AG364" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="365" spans="1:34">
@@ -27332,7 +27341,7 @@
         <v>0</v>
       </c>
       <c r="AG365" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="366" spans="1:34">
@@ -27394,13 +27403,13 @@
         <v>271</v>
       </c>
       <c r="W366" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AA366">
         <v>0</v>
       </c>
       <c r="AG366" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="367" spans="1:34">
@@ -27459,13 +27468,13 @@
         <v>263</v>
       </c>
       <c r="W367" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AA367">
         <v>0</v>
       </c>
       <c r="AG367" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="368" spans="1:34">
@@ -27527,13 +27536,13 @@
         <v>271</v>
       </c>
       <c r="W368" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AA368">
         <v>0</v>
       </c>
       <c r="AG368" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="369" spans="1:34">
@@ -27592,13 +27601,13 @@
         <v>261</v>
       </c>
       <c r="W369" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AA369">
         <v>0</v>
       </c>
       <c r="AG369" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="370" spans="1:34">
@@ -27657,13 +27666,13 @@
         <v>258</v>
       </c>
       <c r="W370" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AA370">
         <v>0</v>
       </c>
       <c r="AG370" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="371" spans="1:34">
@@ -27722,13 +27731,13 @@
         <v>259</v>
       </c>
       <c r="W371" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AA371">
         <v>0</v>
       </c>
       <c r="AG371" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="372" spans="1:34">
@@ -27787,13 +27796,13 @@
         <v>259</v>
       </c>
       <c r="W372" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AA372">
         <v>0</v>
       </c>
       <c r="AG372" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="373" spans="1:34">
@@ -27852,13 +27861,13 @@
         <v>260</v>
       </c>
       <c r="W373" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AA373">
         <v>0</v>
       </c>
       <c r="AG373" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="374" spans="1:34">
@@ -27917,13 +27926,13 @@
         <v>260</v>
       </c>
       <c r="W374" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AA374">
         <v>0</v>
       </c>
       <c r="AG374" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="375" spans="1:34">
@@ -27982,13 +27991,13 @@
         <v>258</v>
       </c>
       <c r="W375" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AA375">
         <v>0</v>
       </c>
       <c r="AG375" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="376" spans="1:34">
@@ -28047,13 +28056,13 @@
         <v>259</v>
       </c>
       <c r="W376" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AA376">
         <v>0</v>
       </c>
       <c r="AG376" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="377" spans="1:34">
@@ -28118,13 +28127,13 @@
         <v>0</v>
       </c>
       <c r="AB377" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG377" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH377" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="378" spans="1:34">
@@ -28186,13 +28195,13 @@
         <v>0</v>
       </c>
       <c r="AB378" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG378" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH378" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="379" spans="1:34">
@@ -28254,19 +28263,19 @@
         <v>271</v>
       </c>
       <c r="W379" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AA379">
         <v>0</v>
       </c>
       <c r="AB379" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG379" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH379" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="380" spans="1:34">
@@ -28328,19 +28337,19 @@
         <v>271</v>
       </c>
       <c r="W380" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AA380">
         <v>0</v>
       </c>
       <c r="AB380" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG380" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH380" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="381" spans="1:34">
@@ -28408,10 +28417,10 @@
         <v>224</v>
       </c>
       <c r="AG381" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH381" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="382" spans="1:34">
@@ -28476,19 +28485,19 @@
         <v>271</v>
       </c>
       <c r="W382" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AA382">
         <v>0</v>
       </c>
       <c r="AB382" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG382" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH382" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="383" spans="1:34">
@@ -28553,10 +28562,10 @@
         <v>224</v>
       </c>
       <c r="AG383" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH383" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="384" spans="1:34">
@@ -28624,10 +28633,10 @@
         <v>229</v>
       </c>
       <c r="AG384" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH384" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="385" spans="1:34">
@@ -28689,13 +28698,13 @@
         <v>0</v>
       </c>
       <c r="AB385" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG385" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH385" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="386" spans="1:34">
@@ -28760,13 +28769,13 @@
         <v>0</v>
       </c>
       <c r="AB386" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG386" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH386" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="387" spans="1:34">
@@ -28831,10 +28840,10 @@
         <v>228</v>
       </c>
       <c r="AG387" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH387" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="388" spans="1:34">
@@ -28893,10 +28902,10 @@
         <v>0</v>
       </c>
       <c r="AB388" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG388" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="389" spans="1:34">
@@ -28958,10 +28967,10 @@
         <v>0</v>
       </c>
       <c r="AB389" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG389" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="390" spans="1:34">
@@ -29020,16 +29029,16 @@
         <v>271</v>
       </c>
       <c r="W390" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AA390">
         <v>0</v>
       </c>
       <c r="AB390" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG390" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="391" spans="1:34">
@@ -29097,10 +29106,10 @@
         <v>246</v>
       </c>
       <c r="AG391" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH391" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="392" spans="1:34">
@@ -29168,10 +29177,10 @@
         <v>229</v>
       </c>
       <c r="AG392" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH392" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="393" spans="1:34">
@@ -29230,19 +29239,19 @@
         <v>260</v>
       </c>
       <c r="W393" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AA393">
         <v>0</v>
       </c>
       <c r="AB393" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG393" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH393" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="394" spans="1:34">
@@ -29307,10 +29316,10 @@
         <v>228</v>
       </c>
       <c r="AG394" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH394" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="395" spans="1:34">
@@ -29375,10 +29384,10 @@
         <v>247</v>
       </c>
       <c r="AG395" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH395" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="396" spans="1:34">
@@ -29443,10 +29452,10 @@
         <v>246</v>
       </c>
       <c r="AG396" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH396" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="397" spans="1:34">
@@ -29514,10 +29523,10 @@
         <v>229</v>
       </c>
       <c r="AG397" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH397" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="398" spans="1:34">
@@ -29582,10 +29591,10 @@
         <v>229</v>
       </c>
       <c r="AG398" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH398" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="399" spans="1:34">
@@ -29653,10 +29662,10 @@
         <v>229</v>
       </c>
       <c r="AG399" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH399" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="400" spans="1:34">
@@ -29721,7 +29730,7 @@
         <v>271</v>
       </c>
       <c r="W400" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AA400">
         <v>0</v>
@@ -29730,10 +29739,10 @@
         <v>230</v>
       </c>
       <c r="AG400" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH400" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="401" spans="1:34">
@@ -29798,7 +29807,7 @@
         <v>271</v>
       </c>
       <c r="W401" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AA401">
         <v>0</v>
@@ -29807,10 +29816,10 @@
         <v>230</v>
       </c>
       <c r="AG401" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH401" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="402" spans="1:34">
@@ -29872,7 +29881,7 @@
         <v>257</v>
       </c>
       <c r="W402" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AA402">
         <v>0</v>
@@ -29881,10 +29890,10 @@
         <v>250</v>
       </c>
       <c r="AG402" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH402" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="403" spans="1:34">
@@ -29949,10 +29958,10 @@
         <v>235</v>
       </c>
       <c r="AG403" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH403" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="404" spans="1:34">
@@ -30017,7 +30026,7 @@
         <v>271</v>
       </c>
       <c r="W404" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AA404">
         <v>0</v>
@@ -30026,10 +30035,10 @@
         <v>237</v>
       </c>
       <c r="AG404" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH404" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="405" spans="1:34">
@@ -30094,7 +30103,7 @@
         <v>233</v>
       </c>
       <c r="AG405" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="406" spans="1:34">
@@ -30159,7 +30168,7 @@
         <v>271</v>
       </c>
       <c r="W406" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AA406">
         <v>0</v>
@@ -30168,10 +30177,10 @@
         <v>230</v>
       </c>
       <c r="AG406" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH406" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="407" spans="1:34">
@@ -30236,7 +30245,7 @@
         <v>271</v>
       </c>
       <c r="W407" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AA407">
         <v>0</v>
@@ -30245,10 +30254,10 @@
         <v>234</v>
       </c>
       <c r="AG407" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH407" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="408" spans="1:34">
@@ -30313,7 +30322,7 @@
         <v>271</v>
       </c>
       <c r="W408" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AA408">
         <v>0</v>
@@ -30322,10 +30331,10 @@
         <v>230</v>
       </c>
       <c r="AG408" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH408" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="409" spans="1:34">
@@ -30390,7 +30399,7 @@
         <v>271</v>
       </c>
       <c r="W409" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AA409">
         <v>0</v>
@@ -30399,10 +30408,10 @@
         <v>230</v>
       </c>
       <c r="AG409" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH409" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="410" spans="1:34">
@@ -30467,10 +30476,10 @@
         <v>235</v>
       </c>
       <c r="AG410" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH410" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="411" spans="1:34">
@@ -30538,10 +30547,10 @@
         <v>237</v>
       </c>
       <c r="AG411" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH411" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="412" spans="1:34">
@@ -30603,7 +30612,7 @@
         <v>257</v>
       </c>
       <c r="W412" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AA412">
         <v>0</v>
@@ -30612,10 +30621,10 @@
         <v>231</v>
       </c>
       <c r="AG412" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH412" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="413" spans="1:34">
@@ -30680,7 +30689,7 @@
         <v>233</v>
       </c>
       <c r="AG413" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="414" spans="1:34">
@@ -30745,7 +30754,7 @@
         <v>271</v>
       </c>
       <c r="W414" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AA414">
         <v>0</v>
@@ -30754,10 +30763,10 @@
         <v>230</v>
       </c>
       <c r="AG414" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH414" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="415" spans="1:34">
@@ -30822,7 +30831,7 @@
         <v>271</v>
       </c>
       <c r="W415" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AA415">
         <v>0</v>
@@ -30831,10 +30840,10 @@
         <v>234</v>
       </c>
       <c r="AG415" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH415" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="416" spans="1:34">
@@ -30899,7 +30908,7 @@
         <v>271</v>
       </c>
       <c r="W416" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AA416">
         <v>0</v>
@@ -30908,10 +30917,10 @@
         <v>230</v>
       </c>
       <c r="AG416" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH416" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="417" spans="1:34">
@@ -30976,7 +30985,7 @@
         <v>271</v>
       </c>
       <c r="W417" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AA417">
         <v>0</v>
@@ -30985,10 +30994,10 @@
         <v>230</v>
       </c>
       <c r="AG417" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH417" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="418" spans="1:34">
@@ -31053,10 +31062,10 @@
         <v>235</v>
       </c>
       <c r="AG418" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH418" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="419" spans="1:34">
@@ -31124,10 +31133,10 @@
         <v>237</v>
       </c>
       <c r="AG419" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH419" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="420" spans="1:34">
@@ -31198,10 +31207,10 @@
         <v>231</v>
       </c>
       <c r="AG420" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH420" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="421" spans="1:34">
@@ -31260,16 +31269,16 @@
         <v>260</v>
       </c>
       <c r="W421" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AA421">
         <v>0</v>
       </c>
       <c r="AB421" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG421" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="422" spans="1:34">
@@ -31328,19 +31337,19 @@
         <v>264</v>
       </c>
       <c r="W422" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AA422">
         <v>0</v>
       </c>
       <c r="AB422" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG422" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH422" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="423" spans="1:34">
@@ -31402,19 +31411,19 @@
         <v>271</v>
       </c>
       <c r="W423" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AA423">
         <v>0</v>
       </c>
       <c r="AB423" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG423" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH423" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="424" spans="1:34">
@@ -31476,19 +31485,19 @@
         <v>271</v>
       </c>
       <c r="W424" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AA424">
         <v>0</v>
       </c>
       <c r="AB424" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG424" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH424" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="425" spans="1:34">
@@ -31550,19 +31559,19 @@
         <v>271</v>
       </c>
       <c r="W425" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AA425">
         <v>0</v>
       </c>
       <c r="AB425" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG425" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH425" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="426" spans="1:34">
@@ -31624,19 +31633,19 @@
         <v>271</v>
       </c>
       <c r="W426" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AA426">
         <v>0</v>
       </c>
       <c r="AB426" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG426" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH426" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="427" spans="1:34">
@@ -31698,19 +31707,19 @@
         <v>263</v>
       </c>
       <c r="W427" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AA427">
         <v>0</v>
       </c>
       <c r="AB427" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG427" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH427" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="428" spans="1:34">
@@ -31772,19 +31781,19 @@
         <v>271</v>
       </c>
       <c r="W428" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AA428">
         <v>0</v>
       </c>
       <c r="AB428" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG428" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH428" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="429" spans="1:34">
@@ -31843,19 +31852,19 @@
         <v>257</v>
       </c>
       <c r="W429" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AA429">
         <v>0</v>
       </c>
       <c r="AB429" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG429" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH429" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="430" spans="1:34">
@@ -31914,19 +31923,19 @@
         <v>258</v>
       </c>
       <c r="W430" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AA430">
         <v>0</v>
       </c>
       <c r="AB430" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG430" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH430" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="431" spans="1:34">
@@ -31988,7 +31997,7 @@
         <v>260</v>
       </c>
       <c r="W431" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AA431">
         <v>0</v>
@@ -31997,7 +32006,7 @@
         <v>233</v>
       </c>
       <c r="AG431" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="432" spans="1:34">
@@ -32062,7 +32071,7 @@
         <v>271</v>
       </c>
       <c r="W432" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AA432">
         <v>0</v>
@@ -32071,10 +32080,10 @@
         <v>230</v>
       </c>
       <c r="AG432" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH432" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="433" spans="1:34">
@@ -32139,7 +32148,7 @@
         <v>271</v>
       </c>
       <c r="W433" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AA433">
         <v>0</v>
@@ -32148,10 +32157,10 @@
         <v>234</v>
       </c>
       <c r="AG433" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH433" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="434" spans="1:34">
@@ -32216,7 +32225,7 @@
         <v>271</v>
       </c>
       <c r="W434" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AA434">
         <v>0</v>
@@ -32225,10 +32234,10 @@
         <v>230</v>
       </c>
       <c r="AG434" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH434" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="435" spans="1:34">
@@ -32293,7 +32302,7 @@
         <v>271</v>
       </c>
       <c r="W435" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AA435">
         <v>0</v>
@@ -32302,10 +32311,10 @@
         <v>230</v>
       </c>
       <c r="AG435" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH435" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="436" spans="1:34">
@@ -32367,7 +32376,7 @@
         <v>263</v>
       </c>
       <c r="W436" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AA436">
         <v>0</v>
@@ -32376,10 +32385,10 @@
         <v>235</v>
       </c>
       <c r="AG436" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH436" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="437" spans="1:34">
@@ -32444,7 +32453,7 @@
         <v>271</v>
       </c>
       <c r="W437" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AA437">
         <v>0</v>
@@ -32453,10 +32462,10 @@
         <v>237</v>
       </c>
       <c r="AG437" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH437" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="438" spans="1:34">
@@ -32518,7 +32527,7 @@
         <v>264</v>
       </c>
       <c r="W438" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AA438">
         <v>0</v>
@@ -32527,10 +32536,10 @@
         <v>236</v>
       </c>
       <c r="AG438" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH438" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="439" spans="1:34">
@@ -32595,10 +32604,10 @@
         <v>236</v>
       </c>
       <c r="AG439" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH439" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="440" spans="1:34">
@@ -32660,10 +32669,10 @@
         <v>0</v>
       </c>
       <c r="AB440" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG440" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="441" spans="1:34">
@@ -32725,13 +32734,13 @@
         <v>0</v>
       </c>
       <c r="AB441" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG441" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH441" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="442" spans="1:34">
@@ -32799,10 +32808,10 @@
         <v>230</v>
       </c>
       <c r="AG442" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH442" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="443" spans="1:34">
@@ -32867,13 +32876,13 @@
         <v>0</v>
       </c>
       <c r="AB443" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG443" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH443" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="444" spans="1:34">
@@ -32941,10 +32950,10 @@
         <v>230</v>
       </c>
       <c r="AG444" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH444" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="445" spans="1:34">
@@ -33012,10 +33021,10 @@
         <v>230</v>
       </c>
       <c r="AG445" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH445" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="446" spans="1:34">
@@ -33080,13 +33089,13 @@
         <v>0</v>
       </c>
       <c r="AB446" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG446" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH446" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="447" spans="1:34">
@@ -33148,13 +33157,13 @@
         <v>0</v>
       </c>
       <c r="AB447" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG447" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH447" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="448" spans="1:34">
@@ -33216,13 +33225,13 @@
         <v>0</v>
       </c>
       <c r="AB448" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG448" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH448" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="449" spans="1:34">
@@ -33284,10 +33293,10 @@
         <v>0</v>
       </c>
       <c r="AB449" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG449" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="450" spans="1:34">
@@ -33349,10 +33358,10 @@
         <v>0</v>
       </c>
       <c r="AB450" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG450" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="451" spans="1:34">
@@ -33411,10 +33420,10 @@
         <v>0</v>
       </c>
       <c r="AB451" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG451" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="452" spans="1:34">
@@ -33476,7 +33485,7 @@
         <v>271</v>
       </c>
       <c r="W452" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AA452">
         <v>0</v>
@@ -33485,7 +33494,7 @@
         <v>230</v>
       </c>
       <c r="AG452" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="453" spans="1:34">
@@ -33550,7 +33559,7 @@
         <v>271</v>
       </c>
       <c r="W453" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AA453">
         <v>0</v>
@@ -33559,10 +33568,10 @@
         <v>237</v>
       </c>
       <c r="AG453" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH453" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="454" spans="1:34">
@@ -33624,7 +33633,7 @@
         <v>271</v>
       </c>
       <c r="W454" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AA454">
         <v>0</v>
@@ -33633,7 +33642,7 @@
         <v>230</v>
       </c>
       <c r="AG454" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="455" spans="1:34">
@@ -33695,7 +33704,7 @@
         <v>258</v>
       </c>
       <c r="W455" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AA455">
         <v>0</v>
@@ -33704,10 +33713,10 @@
         <v>232</v>
       </c>
       <c r="AG455" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH455" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="456" spans="1:34">
@@ -33772,13 +33781,13 @@
         <v>0</v>
       </c>
       <c r="AB456" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG456" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH456" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="457" spans="1:34">
@@ -33843,10 +33852,10 @@
         <v>0</v>
       </c>
       <c r="AB457" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG457" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="458" spans="1:34">
@@ -33911,10 +33920,10 @@
         <v>241</v>
       </c>
       <c r="AG458" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH458" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="459" spans="1:34">
@@ -33982,10 +33991,10 @@
         <v>238</v>
       </c>
       <c r="AG459" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH459" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="460" spans="1:34">
@@ -34050,7 +34059,7 @@
         <v>271</v>
       </c>
       <c r="W460" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AA460">
         <v>0</v>
@@ -34059,7 +34068,7 @@
         <v>239</v>
       </c>
       <c r="AG460" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="461" spans="1:34">
@@ -34121,19 +34130,19 @@
         <v>258</v>
       </c>
       <c r="W461" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AA461">
         <v>0</v>
       </c>
       <c r="AB461" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG461" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH461" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="462" spans="1:34">
@@ -34195,7 +34204,7 @@
         <v>259</v>
       </c>
       <c r="W462" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AA462">
         <v>0</v>
@@ -34204,10 +34213,10 @@
         <v>242</v>
       </c>
       <c r="AG462" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH462" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="463" spans="1:34">
@@ -34269,7 +34278,7 @@
         <v>259</v>
       </c>
       <c r="W463" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AA463">
         <v>0</v>
@@ -34278,10 +34287,10 @@
         <v>242</v>
       </c>
       <c r="AG463" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH463" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="464" spans="1:34">
@@ -34343,19 +34352,19 @@
         <v>271</v>
       </c>
       <c r="W464" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AA464">
         <v>0</v>
       </c>
       <c r="AB464" t="s">
+        <v>466</v>
+      </c>
+      <c r="AG464" t="s">
+        <v>473</v>
+      </c>
+      <c r="AH464" t="s">
         <v>465</v>
-      </c>
-      <c r="AG464" t="s">
-        <v>472</v>
-      </c>
-      <c r="AH464" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="465" spans="1:34">
@@ -34417,16 +34426,16 @@
         <v>271</v>
       </c>
       <c r="W465" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AA465">
         <v>0</v>
       </c>
       <c r="AB465" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG465" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="466" spans="1:34">
@@ -34485,19 +34494,19 @@
         <v>258</v>
       </c>
       <c r="W466" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AA466">
         <v>0</v>
       </c>
       <c r="AB466" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG466" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH466" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="467" spans="1:34">
@@ -34562,13 +34571,13 @@
         <v>0</v>
       </c>
       <c r="AB467" t="s">
+        <v>466</v>
+      </c>
+      <c r="AG467" t="s">
+        <v>472</v>
+      </c>
+      <c r="AH467" t="s">
         <v>465</v>
-      </c>
-      <c r="AG467" t="s">
-        <v>471</v>
-      </c>
-      <c r="AH467" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="468" spans="1:34">
@@ -34630,10 +34639,10 @@
         <v>0</v>
       </c>
       <c r="AB468" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG468" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="469" spans="1:34">
@@ -34695,19 +34704,19 @@
         <v>271</v>
       </c>
       <c r="W469" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AA469">
         <v>0</v>
       </c>
       <c r="AB469" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG469" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH469" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="470" spans="1:34">
@@ -34766,16 +34775,16 @@
         <v>257</v>
       </c>
       <c r="W470" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AA470">
         <v>0</v>
       </c>
       <c r="AB470" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG470" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="471" spans="1:34">
@@ -34834,19 +34843,19 @@
         <v>259</v>
       </c>
       <c r="W471" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AA471">
         <v>0</v>
       </c>
       <c r="AB471" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG471" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH471" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="472" spans="1:34">
@@ -34905,19 +34914,19 @@
         <v>259</v>
       </c>
       <c r="W472" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AA472">
         <v>0</v>
       </c>
       <c r="AB472" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG472" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH472" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="473" spans="1:34">
@@ -34979,16 +34988,16 @@
         <v>271</v>
       </c>
       <c r="W473" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AA473">
         <v>0</v>
       </c>
       <c r="AB473" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG473" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="474" spans="1:34">
@@ -35050,19 +35059,19 @@
         <v>271</v>
       </c>
       <c r="W474" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AA474">
         <v>0</v>
       </c>
       <c r="AB474" t="s">
+        <v>466</v>
+      </c>
+      <c r="AG474" t="s">
+        <v>472</v>
+      </c>
+      <c r="AH474" t="s">
         <v>465</v>
-      </c>
-      <c r="AG474" t="s">
-        <v>471</v>
-      </c>
-      <c r="AH474" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="475" spans="1:34">
@@ -35124,16 +35133,16 @@
         <v>271</v>
       </c>
       <c r="W475" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AA475">
         <v>0</v>
       </c>
       <c r="AB475" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG475" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="476" spans="1:34">
@@ -35195,19 +35204,19 @@
         <v>271</v>
       </c>
       <c r="W476" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AA476">
         <v>0</v>
       </c>
       <c r="AB476" t="s">
+        <v>466</v>
+      </c>
+      <c r="AG476" t="s">
+        <v>472</v>
+      </c>
+      <c r="AH476" t="s">
         <v>465</v>
-      </c>
-      <c r="AG476" t="s">
-        <v>471</v>
-      </c>
-      <c r="AH476" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="477" spans="1:34">
@@ -35275,10 +35284,10 @@
         <v>238</v>
       </c>
       <c r="AG477" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH477" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="478" spans="1:34">
@@ -35340,19 +35349,19 @@
         <v>258</v>
       </c>
       <c r="W478" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AA478">
         <v>0</v>
       </c>
       <c r="AB478" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG478" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH478" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="479" spans="1:34">
@@ -35420,13 +35429,13 @@
         <v>0</v>
       </c>
       <c r="AB479" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG479" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH479" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="480" spans="1:34">
@@ -35491,7 +35500,7 @@
         <v>271</v>
       </c>
       <c r="W480" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AA480">
         <v>0</v>
@@ -35500,10 +35509,10 @@
         <v>243</v>
       </c>
       <c r="AG480" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH480" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="481" spans="1:34">
@@ -35568,19 +35577,19 @@
         <v>271</v>
       </c>
       <c r="W481" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AA481">
         <v>0</v>
       </c>
       <c r="AB481" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG481" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH481" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="482" spans="1:34">
@@ -35642,19 +35651,19 @@
         <v>261</v>
       </c>
       <c r="W482" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AA482">
         <v>0</v>
       </c>
       <c r="AB482" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG482" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH482" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="483" spans="1:34">
@@ -35713,19 +35722,19 @@
         <v>263</v>
       </c>
       <c r="W483" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AA483">
         <v>0</v>
       </c>
       <c r="AB483" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG483" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH483" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="484" spans="1:34">
@@ -35790,19 +35799,19 @@
         <v>271</v>
       </c>
       <c r="W484" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AA484">
         <v>0</v>
       </c>
       <c r="AB484" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG484" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH484" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="485" spans="1:34">
@@ -35864,19 +35873,19 @@
         <v>260</v>
       </c>
       <c r="W485" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AA485">
         <v>0</v>
       </c>
       <c r="AB485" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG485" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH485" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="486" spans="1:34">
@@ -35938,19 +35947,19 @@
         <v>264</v>
       </c>
       <c r="W486" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AA486">
         <v>0</v>
       </c>
       <c r="AB486" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG486" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH486" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="487" spans="1:34">
@@ -36012,19 +36021,19 @@
         <v>271</v>
       </c>
       <c r="W487" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AA487">
         <v>0</v>
       </c>
       <c r="AB487" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG487" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH487" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="488" spans="1:34">
@@ -36092,10 +36101,10 @@
         <v>243</v>
       </c>
       <c r="AG488" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH488" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="489" spans="1:34">
@@ -36154,19 +36163,19 @@
         <v>261</v>
       </c>
       <c r="W489" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AA489">
         <v>0</v>
       </c>
       <c r="AB489" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG489" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH489" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="490" spans="1:34">
@@ -36228,19 +36237,19 @@
         <v>271</v>
       </c>
       <c r="W490" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AA490">
         <v>0</v>
       </c>
       <c r="AB490" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG490" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH490" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="491" spans="1:34">
@@ -36302,13 +36311,13 @@
         <v>0</v>
       </c>
       <c r="AB491" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG491" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH491" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="492" spans="1:34">
@@ -36370,19 +36379,19 @@
         <v>263</v>
       </c>
       <c r="W492" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AA492">
         <v>0</v>
       </c>
       <c r="AB492" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG492" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH492" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="493" spans="1:34">
@@ -36441,19 +36450,19 @@
         <v>260</v>
       </c>
       <c r="W493" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AA493">
         <v>0</v>
       </c>
       <c r="AB493" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG493" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH493" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="494" spans="1:34">
@@ -36512,19 +36521,19 @@
         <v>264</v>
       </c>
       <c r="W494" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AA494">
         <v>0</v>
       </c>
       <c r="AB494" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG494" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH494" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="495" spans="1:34">
@@ -36586,7 +36595,7 @@
         <v>260</v>
       </c>
       <c r="W495" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AA495">
         <v>0</v>
@@ -36595,10 +36604,10 @@
         <v>243</v>
       </c>
       <c r="AG495" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH495" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="496" spans="1:34">
@@ -36663,7 +36672,7 @@
         <v>271</v>
       </c>
       <c r="W496" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AA496">
         <v>0</v>
@@ -36672,7 +36681,7 @@
         <v>244</v>
       </c>
       <c r="AG496" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="497" spans="1:33">
@@ -36734,7 +36743,7 @@
         <v>261</v>
       </c>
       <c r="W497" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AA497">
         <v>0</v>
@@ -36743,7 +36752,7 @@
         <v>244</v>
       </c>
       <c r="AG497" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="498" spans="1:33">
@@ -36808,7 +36817,7 @@
         <v>271</v>
       </c>
       <c r="W498" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AA498">
         <v>0</v>
@@ -36817,7 +36826,7 @@
         <v>244</v>
       </c>
       <c r="AG498" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="499" spans="1:33">
@@ -36879,7 +36888,7 @@
         <v>257</v>
       </c>
       <c r="W499" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AA499">
         <v>0</v>
@@ -36888,7 +36897,7 @@
         <v>244</v>
       </c>
       <c r="AG499" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="500" spans="1:33">
@@ -36947,7 +36956,7 @@
         <v>260</v>
       </c>
       <c r="W500" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AA500">
         <v>0</v>
@@ -36956,7 +36965,7 @@
         <v>244</v>
       </c>
       <c r="AG500" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="501" spans="1:33">
@@ -37018,10 +37027,10 @@
         <v>0</v>
       </c>
       <c r="AB501" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG501" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="502" spans="1:33">
@@ -37080,7 +37089,7 @@
         <v>264</v>
       </c>
       <c r="W502" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AA502">
         <v>0</v>
@@ -37089,7 +37098,7 @@
         <v>244</v>
       </c>
       <c r="AG502" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="503" spans="1:33">
@@ -37154,7 +37163,7 @@
         <v>271</v>
       </c>
       <c r="W503" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AA503">
         <v>0</v>
@@ -37163,7 +37172,7 @@
         <v>244</v>
       </c>
       <c r="AG503" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="504" spans="1:33">
@@ -37225,7 +37234,7 @@
         <v>263</v>
       </c>
       <c r="W504" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AA504">
         <v>0</v>
@@ -37234,7 +37243,7 @@
         <v>244</v>
       </c>
       <c r="AG504" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="505" spans="1:33">
@@ -37296,7 +37305,7 @@
         <v>271</v>
       </c>
       <c r="W505" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AA505">
         <v>0</v>
@@ -37305,7 +37314,7 @@
         <v>244</v>
       </c>
       <c r="AG505" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="506" spans="1:33">
@@ -37367,7 +37376,7 @@
         <v>257</v>
       </c>
       <c r="W506" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AA506">
         <v>0</v>
@@ -37376,7 +37385,7 @@
         <v>244</v>
       </c>
       <c r="AG506" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="507" spans="1:33">
@@ -37435,16 +37444,16 @@
         <v>260</v>
       </c>
       <c r="W507" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AA507">
         <v>0</v>
       </c>
       <c r="AB507" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG507" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="508" spans="1:33">
@@ -37506,10 +37515,10 @@
         <v>0</v>
       </c>
       <c r="AB508" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG508" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="509" spans="1:33">
@@ -37568,16 +37577,16 @@
         <v>264</v>
       </c>
       <c r="W509" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AA509">
         <v>0</v>
       </c>
       <c r="AB509" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG509" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="510" spans="1:33">
@@ -37636,16 +37645,16 @@
         <v>263</v>
       </c>
       <c r="W510" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AA510">
         <v>0</v>
       </c>
       <c r="AB510" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG510" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="511" spans="1:33">
@@ -37710,10 +37719,10 @@
         <v>0</v>
       </c>
       <c r="AB511" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG511" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="512" spans="1:33">
@@ -37772,16 +37781,16 @@
         <v>258</v>
       </c>
       <c r="W512" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AA512">
         <v>0</v>
       </c>
       <c r="AB512" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG512" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="513" spans="1:33">
@@ -37840,16 +37849,16 @@
         <v>260</v>
       </c>
       <c r="W513" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AA513">
         <v>0</v>
       </c>
       <c r="AB513" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG513" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="514" spans="1:33">
@@ -37911,16 +37920,16 @@
         <v>271</v>
       </c>
       <c r="W514" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AA514">
         <v>0</v>
       </c>
       <c r="AB514" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG514" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="515" spans="1:33">
@@ -37982,16 +37991,16 @@
         <v>271</v>
       </c>
       <c r="W515" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AA515">
         <v>0</v>
       </c>
       <c r="AB515" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG515" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="516" spans="1:33">
@@ -38053,16 +38062,16 @@
         <v>261</v>
       </c>
       <c r="W516" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AA516">
         <v>0</v>
       </c>
       <c r="AB516" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG516" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="517" spans="1:33">
@@ -38124,10 +38133,10 @@
         <v>0</v>
       </c>
       <c r="AB517" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG517" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="518" spans="1:33">
@@ -38186,16 +38195,16 @@
         <v>258</v>
       </c>
       <c r="W518" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AA518">
         <v>0</v>
       </c>
       <c r="AB518" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG518" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="519" spans="1:33">
@@ -38257,10 +38266,10 @@
         <v>0</v>
       </c>
       <c r="AB519" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG519" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="520" spans="1:33">
@@ -38322,10 +38331,10 @@
         <v>0</v>
       </c>
       <c r="AB520" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG520" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="521" spans="1:33">
@@ -38387,16 +38396,16 @@
         <v>260</v>
       </c>
       <c r="W521" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AA521">
         <v>0</v>
       </c>
       <c r="AB521" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG521" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="522" spans="1:33">
@@ -38458,16 +38467,16 @@
         <v>264</v>
       </c>
       <c r="W522" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AA522">
         <v>0</v>
       </c>
       <c r="AB522" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG522" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="523" spans="1:33">
@@ -38532,16 +38541,16 @@
         <v>271</v>
       </c>
       <c r="W523" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AA523">
         <v>0</v>
       </c>
       <c r="AB523" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG523" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="524" spans="1:33">
@@ -38606,16 +38615,16 @@
         <v>271</v>
       </c>
       <c r="W524" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AA524">
         <v>0</v>
       </c>
       <c r="AB524" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG524" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="525" spans="1:33">
@@ -38680,16 +38689,16 @@
         <v>271</v>
       </c>
       <c r="W525" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AA525">
         <v>0</v>
       </c>
       <c r="AB525" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG525" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="526" spans="1:33">
@@ -38754,16 +38763,16 @@
         <v>271</v>
       </c>
       <c r="W526" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AA526">
         <v>0</v>
       </c>
       <c r="AB526" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG526" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="527" spans="1:33">
@@ -38825,16 +38834,16 @@
         <v>263</v>
       </c>
       <c r="W527" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AA527">
         <v>0</v>
       </c>
       <c r="AB527" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG527" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="528" spans="1:33">
@@ -38899,16 +38908,16 @@
         <v>271</v>
       </c>
       <c r="W528" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AA528">
         <v>0</v>
       </c>
       <c r="AB528" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG528" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="529" spans="1:33">
@@ -38970,16 +38979,16 @@
         <v>261</v>
       </c>
       <c r="W529" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AA529">
         <v>0</v>
       </c>
       <c r="AB529" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG529" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="530" spans="1:33">
@@ -39044,16 +39053,16 @@
         <v>271</v>
       </c>
       <c r="W530" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AA530">
         <v>0</v>
       </c>
       <c r="AB530" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG530" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="531" spans="1:33">
@@ -39115,16 +39124,16 @@
         <v>257</v>
       </c>
       <c r="W531" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AA531">
         <v>0</v>
       </c>
       <c r="AB531" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG531" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="532" spans="1:33">
@@ -39186,16 +39195,16 @@
         <v>258</v>
       </c>
       <c r="W532" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AA532">
         <v>0</v>
       </c>
       <c r="AB532" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG532" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="533" spans="1:33">
@@ -39257,16 +39266,16 @@
         <v>259</v>
       </c>
       <c r="W533" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AA533">
         <v>0</v>
       </c>
       <c r="AB533" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG533" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="534" spans="1:33">
@@ -39328,16 +39337,16 @@
         <v>259</v>
       </c>
       <c r="W534" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AA534">
         <v>0</v>
       </c>
       <c r="AB534" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG534" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="535" spans="1:33">
@@ -39399,7 +39408,7 @@
         <v>260</v>
       </c>
       <c r="W535" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AA535">
         <v>0</v>
@@ -39408,7 +39417,7 @@
         <v>244</v>
       </c>
       <c r="AG535" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="536" spans="1:33">
@@ -39470,16 +39479,16 @@
         <v>264</v>
       </c>
       <c r="W536" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AA536">
         <v>0</v>
       </c>
       <c r="AB536" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG536" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="537" spans="1:33">
@@ -39544,16 +39553,16 @@
         <v>271</v>
       </c>
       <c r="W537" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AA537">
         <v>0</v>
       </c>
       <c r="AB537" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG537" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="538" spans="1:33">
@@ -39618,16 +39627,16 @@
         <v>271</v>
       </c>
       <c r="W538" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AA538">
         <v>0</v>
       </c>
       <c r="AB538" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG538" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="539" spans="1:33">
@@ -39692,16 +39701,16 @@
         <v>271</v>
       </c>
       <c r="W539" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AA539">
         <v>0</v>
       </c>
       <c r="AB539" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG539" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="540" spans="1:33">
@@ -39766,16 +39775,16 @@
         <v>271</v>
       </c>
       <c r="W540" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AA540">
         <v>0</v>
       </c>
       <c r="AB540" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG540" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="541" spans="1:33">
@@ -39837,16 +39846,16 @@
         <v>263</v>
       </c>
       <c r="W541" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AA541">
         <v>0</v>
       </c>
       <c r="AB541" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG541" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="542" spans="1:33">
@@ -39911,16 +39920,16 @@
         <v>271</v>
       </c>
       <c r="W542" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AA542">
         <v>0</v>
       </c>
       <c r="AB542" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG542" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="543" spans="1:33">
@@ -39982,16 +39991,16 @@
         <v>261</v>
       </c>
       <c r="W543" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AA543">
         <v>0</v>
       </c>
       <c r="AB543" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG543" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="544" spans="1:33">
@@ -40053,16 +40062,16 @@
         <v>257</v>
       </c>
       <c r="W544" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AA544">
         <v>0</v>
       </c>
       <c r="AB544" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG544" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="545" spans="1:33">
@@ -40124,16 +40133,16 @@
         <v>258</v>
       </c>
       <c r="W545" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AA545">
         <v>0</v>
       </c>
       <c r="AB545" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG545" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="546" spans="1:33">
@@ -40195,16 +40204,16 @@
         <v>260</v>
       </c>
       <c r="W546" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AA546">
         <v>0</v>
       </c>
       <c r="AB546" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG546" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="547" spans="1:33">
@@ -40266,16 +40275,16 @@
         <v>264</v>
       </c>
       <c r="W547" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AA547">
         <v>0</v>
       </c>
       <c r="AB547" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG547" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="548" spans="1:33">
@@ -40340,16 +40349,16 @@
         <v>271</v>
       </c>
       <c r="W548" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AA548">
         <v>0</v>
       </c>
       <c r="AB548" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG548" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="549" spans="1:33">
@@ -40414,16 +40423,16 @@
         <v>271</v>
       </c>
       <c r="W549" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AA549">
         <v>0</v>
       </c>
       <c r="AB549" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG549" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="550" spans="1:33">
@@ -40488,16 +40497,16 @@
         <v>271</v>
       </c>
       <c r="W550" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AA550">
         <v>0</v>
       </c>
       <c r="AB550" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG550" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="551" spans="1:33">
@@ -40562,16 +40571,16 @@
         <v>271</v>
       </c>
       <c r="W551" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AA551">
         <v>0</v>
       </c>
       <c r="AB551" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG551" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="552" spans="1:33">
@@ -40633,16 +40642,16 @@
         <v>263</v>
       </c>
       <c r="W552" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AA552">
         <v>0</v>
       </c>
       <c r="AB552" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG552" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="553" spans="1:33">
@@ -40707,16 +40716,16 @@
         <v>271</v>
       </c>
       <c r="W553" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AA553">
         <v>0</v>
       </c>
       <c r="AB553" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG553" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="554" spans="1:33">
@@ -40778,16 +40787,16 @@
         <v>261</v>
       </c>
       <c r="W554" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AA554">
         <v>0</v>
       </c>
       <c r="AB554" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG554" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="555" spans="1:33">
@@ -40852,16 +40861,16 @@
         <v>271</v>
       </c>
       <c r="W555" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AA555">
         <v>0</v>
       </c>
       <c r="AB555" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG555" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="556" spans="1:33">
@@ -40923,16 +40932,16 @@
         <v>257</v>
       </c>
       <c r="W556" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AA556">
         <v>0</v>
       </c>
       <c r="AB556" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG556" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="557" spans="1:33">
@@ -40994,16 +41003,16 @@
         <v>258</v>
       </c>
       <c r="W557" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AA557">
         <v>0</v>
       </c>
       <c r="AB557" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG557" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="558" spans="1:33">
@@ -41065,16 +41074,16 @@
         <v>259</v>
       </c>
       <c r="W558" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AA558">
         <v>0</v>
       </c>
       <c r="AB558" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG558" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="559" spans="1:33">
@@ -41136,16 +41145,16 @@
         <v>259</v>
       </c>
       <c r="W559" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AA559">
         <v>0</v>
       </c>
       <c r="AB559" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG559" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="560" spans="1:33">
@@ -41207,7 +41216,7 @@
         <v>260</v>
       </c>
       <c r="W560" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AA560">
         <v>0</v>
@@ -41216,7 +41225,7 @@
         <v>244</v>
       </c>
       <c r="AG560" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="561" spans="1:33">
@@ -41278,16 +41287,16 @@
         <v>264</v>
       </c>
       <c r="W561" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AA561">
         <v>0</v>
       </c>
       <c r="AB561" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG561" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="562" spans="1:33">
@@ -41352,16 +41361,16 @@
         <v>271</v>
       </c>
       <c r="W562" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AA562">
         <v>0</v>
       </c>
       <c r="AB562" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG562" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="563" spans="1:33">
@@ -41426,16 +41435,16 @@
         <v>271</v>
       </c>
       <c r="W563" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AA563">
         <v>0</v>
       </c>
       <c r="AB563" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG563" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="564" spans="1:33">
@@ -41500,16 +41509,16 @@
         <v>271</v>
       </c>
       <c r="W564" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AA564">
         <v>0</v>
       </c>
       <c r="AB564" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG564" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="565" spans="1:33">
@@ -41574,16 +41583,16 @@
         <v>271</v>
       </c>
       <c r="W565" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AA565">
         <v>0</v>
       </c>
       <c r="AB565" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG565" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="566" spans="1:33">
@@ -41645,16 +41654,16 @@
         <v>263</v>
       </c>
       <c r="W566" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AA566">
         <v>0</v>
       </c>
       <c r="AB566" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG566" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="567" spans="1:33">
@@ -41719,16 +41728,16 @@
         <v>271</v>
       </c>
       <c r="W567" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AA567">
         <v>0</v>
       </c>
       <c r="AB567" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG567" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="568" spans="1:33">
@@ -41790,16 +41799,16 @@
         <v>261</v>
       </c>
       <c r="W568" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AA568">
         <v>0</v>
       </c>
       <c r="AB568" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG568" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="569" spans="1:33">
@@ -41861,16 +41870,16 @@
         <v>257</v>
       </c>
       <c r="W569" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AA569">
         <v>0</v>
       </c>
       <c r="AB569" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG569" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="570" spans="1:33">
@@ -41932,16 +41941,16 @@
         <v>258</v>
       </c>
       <c r="W570" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AA570">
         <v>0</v>
       </c>
       <c r="AB570" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG570" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="571" spans="1:33">
@@ -42000,16 +42009,16 @@
         <v>264</v>
       </c>
       <c r="W571" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AA571">
         <v>0</v>
       </c>
       <c r="AB571" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG571" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="572" spans="1:33">
@@ -42071,16 +42080,16 @@
         <v>271</v>
       </c>
       <c r="W572" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AA572">
         <v>0</v>
       </c>
       <c r="AB572" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG572" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="573" spans="1:33">
@@ -42139,16 +42148,16 @@
         <v>260</v>
       </c>
       <c r="W573" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AA573">
         <v>0</v>
       </c>
       <c r="AB573" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG573" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="574" spans="1:33">
@@ -42207,16 +42216,16 @@
         <v>264</v>
       </c>
       <c r="W574" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AA574">
         <v>0</v>
       </c>
       <c r="AB574" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG574" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="575" spans="1:33">
@@ -42275,16 +42284,16 @@
         <v>267</v>
       </c>
       <c r="W575" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AE575" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AF575" t="s">
         <v>203</v>
       </c>
       <c r="AG575" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="576" spans="1:33">
@@ -42343,16 +42352,16 @@
         <v>267</v>
       </c>
       <c r="W576" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AE576" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AF576" t="s">
         <v>203</v>
       </c>
       <c r="AG576" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="577" spans="1:34">
@@ -42411,16 +42420,16 @@
         <v>268</v>
       </c>
       <c r="W577" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AE577" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AF577" t="s">
         <v>203</v>
       </c>
       <c r="AG577" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="578" spans="1:34">
@@ -42479,10 +42488,10 @@
         <v>257</v>
       </c>
       <c r="W578" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG578" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="579" spans="1:34">
@@ -42541,13 +42550,13 @@
         <v>269</v>
       </c>
       <c r="W579" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG579" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH579" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="580" spans="1:34">
@@ -42609,10 +42618,10 @@
         <v>355</v>
       </c>
       <c r="AG580" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH580" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="581" spans="1:34">
@@ -42674,10 +42683,10 @@
         <v>356</v>
       </c>
       <c r="AG581" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH581" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="582" spans="1:34">
@@ -42739,10 +42748,10 @@
         <v>356</v>
       </c>
       <c r="AG582" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH582" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="583" spans="1:34">
@@ -42804,10 +42813,10 @@
         <v>357</v>
       </c>
       <c r="AG583" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH583" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="584" spans="1:34">
@@ -42866,13 +42875,13 @@
         <v>270</v>
       </c>
       <c r="W584" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG584" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH584" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="585" spans="1:34">
@@ -42931,13 +42940,13 @@
         <v>269</v>
       </c>
       <c r="W585" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG585" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH585" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="586" spans="1:34">
@@ -42996,13 +43005,13 @@
         <v>269</v>
       </c>
       <c r="W586" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG586" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH586" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="587" spans="1:34">
@@ -43061,13 +43070,13 @@
         <v>270</v>
       </c>
       <c r="W587" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG587" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH587" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="588" spans="1:34">
@@ -43126,13 +43135,13 @@
         <v>270</v>
       </c>
       <c r="W588" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AG588" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH588" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="589" spans="1:34">
@@ -43191,10 +43200,10 @@
         <v>257</v>
       </c>
       <c r="W589" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG589" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="590" spans="1:34">
@@ -43253,10 +43262,10 @@
         <v>257</v>
       </c>
       <c r="W590" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG590" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="591" spans="1:34">
@@ -43315,10 +43324,10 @@
         <v>257</v>
       </c>
       <c r="W591" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG591" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="592" spans="1:34">
@@ -43377,10 +43386,10 @@
         <v>257</v>
       </c>
       <c r="W592" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG592" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="593" spans="1:34">
@@ -43439,10 +43448,10 @@
         <v>257</v>
       </c>
       <c r="W593" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG593" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="594" spans="1:34">
@@ -43501,10 +43510,10 @@
         <v>257</v>
       </c>
       <c r="W594" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG594" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="595" spans="1:34">
@@ -43563,10 +43572,10 @@
         <v>257</v>
       </c>
       <c r="W595" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG595" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="596" spans="1:34">
@@ -43625,10 +43634,10 @@
         <v>257</v>
       </c>
       <c r="W596" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG596" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="597" spans="1:34">
@@ -43687,10 +43696,10 @@
         <v>257</v>
       </c>
       <c r="W597" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG597" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="598" spans="1:34">
@@ -43749,10 +43758,10 @@
         <v>257</v>
       </c>
       <c r="W598" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG598" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="599" spans="1:34">
@@ -43811,10 +43820,10 @@
         <v>257</v>
       </c>
       <c r="W599" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG599" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="600" spans="1:34">
@@ -43873,10 +43882,10 @@
         <v>257</v>
       </c>
       <c r="W600" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG600" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="601" spans="1:34">
@@ -43935,10 +43944,10 @@
         <v>257</v>
       </c>
       <c r="W601" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG601" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="602" spans="1:34">
@@ -43997,10 +44006,10 @@
         <v>257</v>
       </c>
       <c r="W602" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG602" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="603" spans="1:34">
@@ -44059,10 +44068,10 @@
         <v>257</v>
       </c>
       <c r="W603" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG603" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="604" spans="1:34">
@@ -44124,10 +44133,10 @@
         <v>367</v>
       </c>
       <c r="AG604" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH604" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="605" spans="1:34">
@@ -44186,10 +44195,10 @@
         <v>269</v>
       </c>
       <c r="W605" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG605" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
   </sheetData>

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8980" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8981" uniqueCount="480">
   <si>
     <t>CodCliente</t>
   </si>
@@ -1142,7 +1142,7 @@
     <t>Comentário Colaborador + Previsão de Conclusão. Previsto para: 28/09/2026 - Data Comentário: 18/09/2026 15:27</t>
   </si>
   <si>
-    <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1807] sendo a ultima baixa feita [1807]-22/09/2026 10:05:26.. - Data Comentário: 22/09/2026 10:00</t>
+    <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1807] sendo a ultima baixa feita [1807]-22/09/2026 10:05:26.. - Data Comentário: 22/09/2026 12:56</t>
   </si>
   <si>
     <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1882] sendo a ultima baixa feita [1882]-18/09/2026 18:05:29.. - Data Comentário: 21/09/2026 09:20</t>
@@ -26634,6 +26634,9 @@
       <c r="L355" s="1">
         <v>46290</v>
       </c>
+      <c r="M355" t="s">
+        <v>210</v>
+      </c>
       <c r="N355" t="s">
         <v>218</v>
       </c>

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8981" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8980" uniqueCount="480">
   <si>
     <t>CodCliente</t>
   </si>
@@ -448,6 +448,9 @@
     <t>Fed - PIS/COFINS Não Cumul/Mon - 5856</t>
   </si>
   <si>
+    <t>Movimento - Sistema de Análise</t>
+  </si>
+  <si>
     <t>Digitalização de NF Ativo</t>
   </si>
   <si>
@@ -515,9 +518,6 @@
   </si>
   <si>
     <t>Fed - DAS</t>
-  </si>
-  <si>
-    <t>Movimento - Sistema de Análise</t>
   </si>
   <si>
     <t>Receitas Financeiras ( Aplicação Financeira )</t>
@@ -1134,6 +1134,9 @@
   </si>
   <si>
     <t>Comentário Colaborador + Previsão de Conclusão. Previsto para: 22/09/2026 - Data Comentário: 18/09/2026 15:24</t>
+  </si>
+  <si>
+    <t>Reaberto via API integração MGC x Sistema de Analise Fiscal em 22/09/2026 14:36:22. - Data Comentário: 22/09/2026 14:35</t>
   </si>
   <si>
     <t>Comentário Colaborador + Previsão de Conclusão. Previsto para: 24/09/2026 - Data Comentário: 18/09/2026 15:24</t>
@@ -1285,9 +1288,6 @@
   </si>
   <si>
     <t>Tarefa baixada via Rotina SisAnalise x MGC - ExecutarPisCofinsZeradosOuComCredito. - Data Comentário: 18/09/2026 18:03</t>
-  </si>
-  <si>
-    <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 21/09/2026 14:18:48. - Data Comentário: 21/09/2026 14:13</t>
   </si>
   <si>
     <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 17/09/2026 17:55:53. - Data Comentário: 17/09/2026 17:50</t>
@@ -26188,10 +26188,10 @@
     </row>
     <row r="349" spans="1:34">
       <c r="A349">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B349" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C349" t="s">
         <v>58</v>
@@ -26206,40 +26206,37 @@
         <v>64</v>
       </c>
       <c r="G349">
-        <v>6759</v>
+        <v>7026</v>
       </c>
       <c r="H349">
-        <v>1788</v>
+        <v>0</v>
       </c>
       <c r="I349" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J349" t="s">
         <v>144</v>
       </c>
       <c r="L349" s="1">
-        <v>46289</v>
-      </c>
-      <c r="M349" t="s">
-        <v>212</v>
+        <v>46288</v>
       </c>
       <c r="N349" t="s">
         <v>218</v>
       </c>
       <c r="O349">
-        <v>16976177</v>
+        <v>18094899</v>
       </c>
       <c r="P349" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="Q349" t="s">
         <v>253</v>
       </c>
       <c r="S349">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T349" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="V349" t="s">
         <v>270</v>
@@ -26254,21 +26251,21 @@
         <v>470</v>
       </c>
       <c r="AH349" t="s">
-        <v>479</v>
+        <v>463</v>
       </c>
     </row>
     <row r="350" spans="1:34">
       <c r="A350">
-        <v>6705</v>
+        <v>6486</v>
       </c>
       <c r="B350" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C350" t="s">
         <v>58</v>
       </c>
       <c r="D350" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E350" t="s">
         <v>62</v>
@@ -26286,7 +26283,7 @@
         <v>71</v>
       </c>
       <c r="J350" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L350" s="1">
         <v>46289</v>
@@ -26298,7 +26295,7 @@
         <v>218</v>
       </c>
       <c r="O350">
-        <v>17949019</v>
+        <v>16976177</v>
       </c>
       <c r="P350" t="s">
         <v>242</v>
@@ -26310,10 +26307,13 @@
         <v>-2</v>
       </c>
       <c r="T350" t="s">
-        <v>260</v>
+        <v>261</v>
+      </c>
+      <c r="V350" t="s">
+        <v>270</v>
       </c>
       <c r="W350" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AA350">
         <v>0</v>
@@ -26345,28 +26345,28 @@
         <v>64</v>
       </c>
       <c r="G351">
-        <v>1803</v>
+        <v>6759</v>
       </c>
       <c r="H351">
-        <v>0</v>
+        <v>1788</v>
       </c>
       <c r="I351" t="s">
         <v>71</v>
       </c>
       <c r="J351" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="L351" s="1">
-        <v>46293</v>
+        <v>46289</v>
       </c>
       <c r="M351" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="N351" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="O351">
-        <v>17948937</v>
+        <v>17949019</v>
       </c>
       <c r="P351" t="s">
         <v>242</v>
@@ -26375,7 +26375,7 @@
         <v>253</v>
       </c>
       <c r="S351">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="T351" t="s">
         <v>260</v>
@@ -26387,7 +26387,7 @@
         <v>0</v>
       </c>
       <c r="AG351" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AH351" t="s">
         <v>479</v>
@@ -26395,16 +26395,16 @@
     </row>
     <row r="352" spans="1:34">
       <c r="A352">
-        <v>6703</v>
+        <v>6705</v>
       </c>
       <c r="B352" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C352" t="s">
         <v>58</v>
       </c>
       <c r="D352" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E352" t="s">
         <v>62</v>
@@ -26413,7 +26413,7 @@
         <v>64</v>
       </c>
       <c r="G352">
-        <v>1807</v>
+        <v>1803</v>
       </c>
       <c r="H352">
         <v>0</v>
@@ -26422,19 +26422,19 @@
         <v>71</v>
       </c>
       <c r="J352" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="L352" s="1">
-        <v>46287</v>
+        <v>46293</v>
       </c>
       <c r="M352" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N352" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="O352">
-        <v>17948806</v>
+        <v>17948937</v>
       </c>
       <c r="P352" t="s">
         <v>242</v>
@@ -26443,13 +26443,13 @@
         <v>253</v>
       </c>
       <c r="S352">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="T352" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="W352" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AA352">
         <v>0</v>
@@ -26463,16 +26463,16 @@
     </row>
     <row r="353" spans="1:34">
       <c r="A353">
-        <v>5417</v>
+        <v>6703</v>
       </c>
       <c r="B353" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C353" t="s">
         <v>58</v>
       </c>
       <c r="D353" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E353" t="s">
         <v>62</v>
@@ -26481,7 +26481,7 @@
         <v>64</v>
       </c>
       <c r="G353">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="H353">
         <v>0</v>
@@ -26490,7 +26490,7 @@
         <v>71</v>
       </c>
       <c r="J353" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="L353" s="1">
         <v>46287</v>
@@ -26502,7 +26502,7 @@
         <v>218</v>
       </c>
       <c r="O353">
-        <v>17398965</v>
+        <v>17948806</v>
       </c>
       <c r="P353" t="s">
         <v>242</v>
@@ -26514,7 +26514,7 @@
         <v>0</v>
       </c>
       <c r="T353" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="W353" t="s">
         <v>363</v>
@@ -26531,10 +26531,10 @@
     </row>
     <row r="354" spans="1:34">
       <c r="A354">
-        <v>6704</v>
+        <v>5417</v>
       </c>
       <c r="B354" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C354" t="s">
         <v>58</v>
@@ -26570,7 +26570,7 @@
         <v>218</v>
       </c>
       <c r="O354">
-        <v>18085209</v>
+        <v>17398965</v>
       </c>
       <c r="P354" t="s">
         <v>242</v>
@@ -26582,10 +26582,7 @@
         <v>0</v>
       </c>
       <c r="T354" t="s">
-        <v>260</v>
-      </c>
-      <c r="V354" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="W354" t="s">
         <v>363</v>
@@ -26602,16 +26599,16 @@
     </row>
     <row r="355" spans="1:34">
       <c r="A355">
-        <v>6404</v>
+        <v>6704</v>
       </c>
       <c r="B355" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C355" t="s">
         <v>58</v>
       </c>
       <c r="D355" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E355" t="s">
         <v>62</v>
@@ -26620,43 +26617,46 @@
         <v>64</v>
       </c>
       <c r="G355">
-        <v>953</v>
+        <v>1808</v>
       </c>
       <c r="H355">
         <v>0</v>
       </c>
       <c r="I355" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J355" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="L355" s="1">
-        <v>46290</v>
+        <v>46287</v>
       </c>
       <c r="M355" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="N355" t="s">
         <v>218</v>
       </c>
       <c r="O355">
-        <v>16962107</v>
+        <v>18085209</v>
       </c>
       <c r="P355" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q355" t="s">
         <v>253</v>
       </c>
       <c r="S355">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="T355" t="s">
-        <v>263</v>
+        <v>260</v>
+      </c>
+      <c r="V355" t="s">
+        <v>270</v>
       </c>
       <c r="W355" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="AA355">
         <v>0</v>
@@ -26664,22 +26664,25 @@
       <c r="AG355" t="s">
         <v>471</v>
       </c>
+      <c r="AH355" t="s">
+        <v>479</v>
+      </c>
     </row>
     <row r="356" spans="1:34">
       <c r="A356">
-        <v>6627</v>
+        <v>6404</v>
       </c>
       <c r="B356" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C356" t="s">
         <v>58</v>
       </c>
       <c r="D356" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E356" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F356" t="s">
         <v>64</v>
@@ -26694,7 +26697,7 @@
         <v>72</v>
       </c>
       <c r="J356" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L356" s="1">
         <v>46290</v>
@@ -26706,7 +26709,7 @@
         <v>218</v>
       </c>
       <c r="O356">
-        <v>17042317</v>
+        <v>16962107</v>
       </c>
       <c r="P356" t="s">
         <v>243</v>
@@ -26718,10 +26721,7 @@
         <v>-3</v>
       </c>
       <c r="T356" t="s">
-        <v>255</v>
-      </c>
-      <c r="V356" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="W356" t="s">
         <v>367</v>
@@ -26735,22 +26735,22 @@
     </row>
     <row r="357" spans="1:34">
       <c r="A357">
-        <v>6962</v>
+        <v>6627</v>
       </c>
       <c r="B357" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C357" t="s">
         <v>58</v>
       </c>
       <c r="D357" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E357" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F357" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G357">
         <v>953</v>
@@ -26762,7 +26762,7 @@
         <v>72</v>
       </c>
       <c r="J357" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L357" s="1">
         <v>46290</v>
@@ -26774,7 +26774,7 @@
         <v>218</v>
       </c>
       <c r="O357">
-        <v>18188731</v>
+        <v>17042317</v>
       </c>
       <c r="P357" t="s">
         <v>243</v>
@@ -26786,7 +26786,10 @@
         <v>-3</v>
       </c>
       <c r="T357" t="s">
-        <v>258</v>
+        <v>255</v>
+      </c>
+      <c r="V357" t="s">
+        <v>270</v>
       </c>
       <c r="W357" t="s">
         <v>368</v>
@@ -26800,10 +26803,10 @@
     </row>
     <row r="358" spans="1:34">
       <c r="A358">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B358" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C358" t="s">
         <v>58</v>
@@ -26827,7 +26830,7 @@
         <v>72</v>
       </c>
       <c r="J358" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L358" s="1">
         <v>46290</v>
@@ -26839,7 +26842,7 @@
         <v>218</v>
       </c>
       <c r="O358">
-        <v>18188637</v>
+        <v>18188731</v>
       </c>
       <c r="P358" t="s">
         <v>243</v>
@@ -26865,25 +26868,25 @@
     </row>
     <row r="359" spans="1:34">
       <c r="A359">
-        <v>5417</v>
+        <v>6963</v>
       </c>
       <c r="B359" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C359" t="s">
         <v>58</v>
       </c>
       <c r="D359" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E359" t="s">
         <v>62</v>
       </c>
       <c r="F359" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G359">
-        <v>943</v>
+        <v>953</v>
       </c>
       <c r="H359">
         <v>0</v>
@@ -26895,16 +26898,16 @@
         <v>147</v>
       </c>
       <c r="L359" s="1">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="M359" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N359" t="s">
         <v>218</v>
       </c>
       <c r="O359">
-        <v>17398859</v>
+        <v>18188637</v>
       </c>
       <c r="P359" t="s">
         <v>243</v>
@@ -26913,27 +26916,27 @@
         <v>253</v>
       </c>
       <c r="S359">
-        <v>-8</v>
+        <v>-3</v>
       </c>
       <c r="T359" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="W359" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="AA359">
         <v>0</v>
       </c>
       <c r="AG359" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="360" spans="1:34">
       <c r="A360">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B360" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C360" t="s">
         <v>58</v>
@@ -26957,7 +26960,7 @@
         <v>72</v>
       </c>
       <c r="J360" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L360" s="1">
         <v>46295</v>
@@ -26969,7 +26972,7 @@
         <v>218</v>
       </c>
       <c r="O360">
-        <v>16975890</v>
+        <v>17398859</v>
       </c>
       <c r="P360" t="s">
         <v>243</v>
@@ -26981,13 +26984,10 @@
         <v>-8</v>
       </c>
       <c r="T360" t="s">
-        <v>261</v>
-      </c>
-      <c r="V360" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="W360" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="AA360">
         <v>0</v>
@@ -26998,16 +26998,16 @@
     </row>
     <row r="361" spans="1:34">
       <c r="A361">
-        <v>6703</v>
+        <v>6486</v>
       </c>
       <c r="B361" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C361" t="s">
         <v>58</v>
       </c>
       <c r="D361" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E361" t="s">
         <v>62</v>
@@ -27025,7 +27025,7 @@
         <v>72</v>
       </c>
       <c r="J361" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L361" s="1">
         <v>46295</v>
@@ -27037,7 +27037,7 @@
         <v>218</v>
       </c>
       <c r="O361">
-        <v>17941122</v>
+        <v>16975890</v>
       </c>
       <c r="P361" t="s">
         <v>243</v>
@@ -27049,10 +27049,13 @@
         <v>-8</v>
       </c>
       <c r="T361" t="s">
-        <v>262</v>
+        <v>261</v>
+      </c>
+      <c r="V361" t="s">
+        <v>270</v>
       </c>
       <c r="W361" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AA361">
         <v>0</v>
@@ -27063,16 +27066,16 @@
     </row>
     <row r="362" spans="1:34">
       <c r="A362">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B362" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C362" t="s">
         <v>58</v>
       </c>
       <c r="D362" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E362" t="s">
         <v>62</v>
@@ -27090,7 +27093,7 @@
         <v>72</v>
       </c>
       <c r="J362" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L362" s="1">
         <v>46295</v>
@@ -27102,7 +27105,7 @@
         <v>218</v>
       </c>
       <c r="O362">
-        <v>17952314</v>
+        <v>17941122</v>
       </c>
       <c r="P362" t="s">
         <v>243</v>
@@ -27114,13 +27117,10 @@
         <v>-8</v>
       </c>
       <c r="T362" t="s">
-        <v>260</v>
-      </c>
-      <c r="V362" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="W362" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AA362">
         <v>0</v>
@@ -27131,16 +27131,16 @@
     </row>
     <row r="363" spans="1:34">
       <c r="A363">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B363" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C363" t="s">
         <v>58</v>
       </c>
       <c r="D363" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E363" t="s">
         <v>62</v>
@@ -27158,7 +27158,7 @@
         <v>72</v>
       </c>
       <c r="J363" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L363" s="1">
         <v>46295</v>
@@ -27170,7 +27170,7 @@
         <v>218</v>
       </c>
       <c r="O363">
-        <v>17952513</v>
+        <v>17952314</v>
       </c>
       <c r="P363" t="s">
         <v>243</v>
@@ -27184,8 +27184,11 @@
       <c r="T363" t="s">
         <v>260</v>
       </c>
+      <c r="V363" t="s">
+        <v>270</v>
+      </c>
       <c r="W363" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AA363">
         <v>0</v>
@@ -27196,22 +27199,22 @@
     </row>
     <row r="364" spans="1:34">
       <c r="A364">
-        <v>6949</v>
+        <v>6705</v>
       </c>
       <c r="B364" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C364" t="s">
         <v>58</v>
       </c>
       <c r="D364" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E364" t="s">
         <v>62</v>
       </c>
       <c r="F364" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G364">
         <v>943</v>
@@ -27223,7 +27226,7 @@
         <v>72</v>
       </c>
       <c r="J364" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L364" s="1">
         <v>46295</v>
@@ -27235,7 +27238,7 @@
         <v>218</v>
       </c>
       <c r="O364">
-        <v>18178126</v>
+        <v>17952513</v>
       </c>
       <c r="P364" t="s">
         <v>243</v>
@@ -27247,10 +27250,10 @@
         <v>-8</v>
       </c>
       <c r="T364" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="W364" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AA364">
         <v>0</v>
@@ -27261,16 +27264,16 @@
     </row>
     <row r="365" spans="1:34">
       <c r="A365">
-        <v>6962</v>
+        <v>6949</v>
       </c>
       <c r="B365" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C365" t="s">
         <v>58</v>
       </c>
       <c r="D365" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E365" t="s">
         <v>62</v>
@@ -27288,7 +27291,7 @@
         <v>72</v>
       </c>
       <c r="J365" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L365" s="1">
         <v>46295</v>
@@ -27300,7 +27303,7 @@
         <v>218</v>
       </c>
       <c r="O365">
-        <v>18188710</v>
+        <v>18178126</v>
       </c>
       <c r="P365" t="s">
         <v>243</v>
@@ -27312,10 +27315,10 @@
         <v>-8</v>
       </c>
       <c r="T365" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="W365" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AA365">
         <v>0</v>
@@ -27326,10 +27329,10 @@
     </row>
     <row r="366" spans="1:34">
       <c r="A366">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B366" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C366" t="s">
         <v>58</v>
@@ -27353,7 +27356,7 @@
         <v>72</v>
       </c>
       <c r="J366" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L366" s="1">
         <v>46295</v>
@@ -27365,7 +27368,7 @@
         <v>218</v>
       </c>
       <c r="O366">
-        <v>18188616</v>
+        <v>18188710</v>
       </c>
       <c r="P366" t="s">
         <v>243</v>
@@ -27380,7 +27383,7 @@
         <v>258</v>
       </c>
       <c r="W366" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AA366">
         <v>0</v>
@@ -27391,58 +27394,58 @@
     </row>
     <row r="367" spans="1:34">
       <c r="A367">
-        <v>5417</v>
+        <v>6963</v>
       </c>
       <c r="B367" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C367" t="s">
         <v>58</v>
       </c>
       <c r="D367" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E367" t="s">
         <v>62</v>
       </c>
       <c r="F367" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G367">
-        <v>7877</v>
+        <v>943</v>
       </c>
       <c r="H367">
         <v>0</v>
       </c>
       <c r="I367" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J367" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="L367" s="1">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="M367" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N367" t="s">
         <v>218</v>
       </c>
       <c r="O367">
-        <v>17399330</v>
+        <v>18188616</v>
       </c>
       <c r="P367" t="s">
-        <v>62</v>
+        <v>243</v>
       </c>
       <c r="Q367" t="s">
         <v>253</v>
       </c>
       <c r="S367">
-        <v>-3</v>
+        <v>-8</v>
       </c>
       <c r="T367" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="W367" t="s">
         <v>371</v>
@@ -27456,10 +27459,10 @@
     </row>
     <row r="368" spans="1:34">
       <c r="A368">
-        <v>6949</v>
+        <v>5417</v>
       </c>
       <c r="B368" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C368" t="s">
         <v>58</v>
@@ -27471,43 +27474,43 @@
         <v>62</v>
       </c>
       <c r="F368" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G368">
-        <v>11056</v>
+        <v>7877</v>
       </c>
       <c r="H368">
         <v>0</v>
       </c>
       <c r="I368" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J368" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="L368" s="1">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="M368" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N368" t="s">
         <v>218</v>
       </c>
       <c r="O368">
-        <v>18279142</v>
+        <v>17399330</v>
       </c>
       <c r="P368" t="s">
-        <v>247</v>
+        <v>62</v>
       </c>
       <c r="Q368" t="s">
         <v>253</v>
       </c>
       <c r="S368">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="T368" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W368" t="s">
         <v>372</v>
@@ -27521,81 +27524,75 @@
     </row>
     <row r="369" spans="1:34">
       <c r="A369">
-        <v>6628</v>
+        <v>6949</v>
       </c>
       <c r="B369" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C369" t="s">
         <v>58</v>
       </c>
       <c r="D369" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E369" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F369" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G369">
-        <v>1650</v>
+        <v>11056</v>
       </c>
       <c r="H369">
         <v>0</v>
       </c>
       <c r="I369" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="J369" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="L369" s="1">
         <v>46293</v>
       </c>
+      <c r="M369" t="s">
+        <v>209</v>
+      </c>
       <c r="N369" t="s">
         <v>218</v>
       </c>
       <c r="O369">
-        <v>16959974</v>
+        <v>18279142</v>
       </c>
       <c r="P369" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="Q369" t="s">
-        <v>251</v>
-      </c>
-      <c r="R369" s="1">
-        <v>46265.00248284722</v>
+        <v>253</v>
       </c>
       <c r="S369">
         <v>-6</v>
       </c>
       <c r="T369" t="s">
-        <v>255</v>
-      </c>
-      <c r="V369" t="s">
-        <v>270</v>
+        <v>257</v>
+      </c>
+      <c r="W369" t="s">
+        <v>373</v>
       </c>
       <c r="AA369">
         <v>0</v>
-      </c>
-      <c r="AB369" t="s">
-        <v>464</v>
       </c>
       <c r="AG369" t="s">
         <v>470</v>
       </c>
-      <c r="AH369" t="s">
-        <v>474</v>
-      </c>
     </row>
     <row r="370" spans="1:34">
       <c r="A370">
-        <v>6945</v>
+        <v>6628</v>
       </c>
       <c r="B370" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C370" t="s">
         <v>58</v>
@@ -27604,10 +27601,10 @@
         <v>60</v>
       </c>
       <c r="E370" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F370" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G370">
         <v>1650</v>
@@ -27619,7 +27616,7 @@
         <v>67</v>
       </c>
       <c r="J370" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L370" s="1">
         <v>46293</v>
@@ -27628,22 +27625,25 @@
         <v>218</v>
       </c>
       <c r="O370">
-        <v>18163667</v>
+        <v>16959974</v>
       </c>
       <c r="P370" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q370" t="s">
         <v>251</v>
       </c>
       <c r="R370" s="1">
-        <v>46265.00255472222</v>
+        <v>46265.00248284722</v>
       </c>
       <c r="S370">
         <v>-6</v>
       </c>
       <c r="T370" t="s">
-        <v>256</v>
+        <v>255</v>
+      </c>
+      <c r="V370" t="s">
+        <v>270</v>
       </c>
       <c r="AA370">
         <v>0</v>
@@ -27660,25 +27660,25 @@
     </row>
     <row r="371" spans="1:34">
       <c r="A371">
-        <v>6548</v>
+        <v>6945</v>
       </c>
       <c r="B371" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C371" t="s">
         <v>58</v>
       </c>
       <c r="D371" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E371" t="s">
         <v>62</v>
       </c>
       <c r="F371" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G371">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="H371">
         <v>0</v>
@@ -27690,34 +27690,28 @@
         <v>149</v>
       </c>
       <c r="L371" s="1">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="N371" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="O371">
-        <v>17967989</v>
+        <v>18163667</v>
       </c>
       <c r="P371" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q371" t="s">
         <v>251</v>
       </c>
       <c r="R371" s="1">
-        <v>46234.66180127315</v>
+        <v>46265.00255472222</v>
       </c>
       <c r="S371">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="T371" t="s">
-        <v>254</v>
-      </c>
-      <c r="V371" t="s">
-        <v>270</v>
-      </c>
-      <c r="W371" t="s">
-        <v>373</v>
+        <v>256</v>
       </c>
       <c r="AA371">
         <v>0</v>
@@ -27726,18 +27720,18 @@
         <v>464</v>
       </c>
       <c r="AG371" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AH371" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="372" spans="1:34">
       <c r="A372">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B372" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C372" t="s">
         <v>58</v>
@@ -27746,7 +27740,7 @@
         <v>59</v>
       </c>
       <c r="E372" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F372" t="s">
         <v>64</v>
@@ -27761,7 +27755,7 @@
         <v>67</v>
       </c>
       <c r="J372" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L372" s="1">
         <v>46290</v>
@@ -27770,22 +27764,22 @@
         <v>221</v>
       </c>
       <c r="O372">
-        <v>17042389</v>
+        <v>17967989</v>
       </c>
       <c r="P372" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Q372" t="s">
         <v>251</v>
       </c>
       <c r="R372" s="1">
-        <v>46245.76585582176</v>
+        <v>46234.66180127315</v>
       </c>
       <c r="S372">
         <v>-3</v>
       </c>
       <c r="T372" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="V372" t="s">
         <v>270</v>
@@ -27803,15 +27797,15 @@
         <v>471</v>
       </c>
       <c r="AH372" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="373" spans="1:34">
       <c r="A373">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B373" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C373" t="s">
         <v>58</v>
@@ -27820,16 +27814,16 @@
         <v>59</v>
       </c>
       <c r="E373" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F373" t="s">
         <v>64</v>
       </c>
       <c r="G373">
-        <v>1697</v>
+        <v>1652</v>
       </c>
       <c r="H373">
-        <v>1650</v>
+        <v>0</v>
       </c>
       <c r="I373" t="s">
         <v>67</v>
@@ -27838,51 +27832,54 @@
         <v>150</v>
       </c>
       <c r="L373" s="1">
-        <v>46286</v>
+        <v>46290</v>
       </c>
       <c r="N373" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="O373">
-        <v>17968001</v>
+        <v>17042389</v>
       </c>
       <c r="P373" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q373" t="s">
         <v>251</v>
       </c>
       <c r="R373" s="1">
-        <v>46282.62254486111</v>
+        <v>46245.76585582176</v>
       </c>
       <c r="S373">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="T373" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="V373" t="s">
         <v>270</v>
       </c>
+      <c r="W373" t="s">
+        <v>375</v>
+      </c>
       <c r="AA373">
         <v>0</v>
       </c>
       <c r="AB373" t="s">
-        <v>223</v>
+        <v>464</v>
       </c>
       <c r="AG373" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AH373" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="374" spans="1:34">
       <c r="A374">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B374" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C374" t="s">
         <v>58</v>
@@ -27891,7 +27888,7 @@
         <v>59</v>
       </c>
       <c r="E374" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F374" t="s">
         <v>64</v>
@@ -27906,60 +27903,54 @@
         <v>67</v>
       </c>
       <c r="J374" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L374" s="1">
         <v>46286</v>
       </c>
-      <c r="M374" t="s">
-        <v>213</v>
-      </c>
       <c r="N374" t="s">
         <v>218</v>
       </c>
       <c r="O374">
-        <v>17042403</v>
+        <v>17968001</v>
       </c>
       <c r="P374" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Q374" t="s">
         <v>251</v>
       </c>
       <c r="R374" s="1">
-        <v>46286.64173940972</v>
+        <v>46282.62254486111</v>
       </c>
       <c r="S374">
         <v>1</v>
       </c>
       <c r="T374" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="V374" t="s">
         <v>270</v>
       </c>
-      <c r="W374" t="s">
-        <v>375</v>
-      </c>
       <c r="AA374">
         <v>0</v>
       </c>
       <c r="AB374" t="s">
-        <v>466</v>
+        <v>223</v>
       </c>
       <c r="AG374" t="s">
         <v>470</v>
       </c>
       <c r="AH374" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="375" spans="1:34">
       <c r="A375">
-        <v>6949</v>
+        <v>6627</v>
       </c>
       <c r="B375" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C375" t="s">
         <v>58</v>
@@ -27968,10 +27959,10 @@
         <v>59</v>
       </c>
       <c r="E375" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F375" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G375">
         <v>1697</v>
@@ -27983,51 +27974,60 @@
         <v>67</v>
       </c>
       <c r="J375" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L375" s="1">
         <v>46286</v>
       </c>
+      <c r="M375" t="s">
+        <v>213</v>
+      </c>
       <c r="N375" t="s">
         <v>218</v>
       </c>
       <c r="O375">
-        <v>18178280</v>
+        <v>17042403</v>
       </c>
       <c r="P375" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q375" t="s">
         <v>251</v>
       </c>
       <c r="R375" s="1">
-        <v>46283.44840582176</v>
+        <v>46286.64173940972</v>
       </c>
       <c r="S375">
         <v>1</v>
       </c>
       <c r="T375" t="s">
-        <v>257</v>
+        <v>255</v>
+      </c>
+      <c r="V375" t="s">
+        <v>270</v>
+      </c>
+      <c r="W375" t="s">
+        <v>376</v>
       </c>
       <c r="AA375">
         <v>0</v>
       </c>
       <c r="AB375" t="s">
-        <v>223</v>
+        <v>466</v>
       </c>
       <c r="AG375" t="s">
         <v>470</v>
       </c>
       <c r="AH375" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="376" spans="1:34">
       <c r="A376">
-        <v>6704</v>
+        <v>6949</v>
       </c>
       <c r="B376" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C376" t="s">
         <v>58</v>
@@ -28039,66 +28039,63 @@
         <v>62</v>
       </c>
       <c r="F376" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G376">
-        <v>7868</v>
+        <v>1697</v>
       </c>
       <c r="H376">
-        <v>0</v>
+        <v>1650</v>
       </c>
       <c r="I376" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J376" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="L376" s="1">
-        <v>46293</v>
+        <v>46286</v>
       </c>
       <c r="N376" t="s">
         <v>218</v>
       </c>
       <c r="O376">
-        <v>17955421</v>
+        <v>18178280</v>
       </c>
       <c r="P376" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="Q376" t="s">
         <v>251</v>
       </c>
       <c r="R376" s="1">
-        <v>46267.47365627315</v>
+        <v>46283.44840582176</v>
       </c>
       <c r="S376">
-        <v>-6</v>
+        <v>1</v>
       </c>
       <c r="T376" t="s">
-        <v>260</v>
-      </c>
-      <c r="V376" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="AA376">
         <v>0</v>
       </c>
       <c r="AB376" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="AG376" t="s">
         <v>470</v>
       </c>
       <c r="AH376" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="377" spans="1:34">
       <c r="A377">
-        <v>5417</v>
+        <v>6704</v>
       </c>
       <c r="B377" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C377" t="s">
         <v>58</v>
@@ -28113,7 +28110,7 @@
         <v>64</v>
       </c>
       <c r="G377">
-        <v>6890</v>
+        <v>7868</v>
       </c>
       <c r="H377">
         <v>0</v>
@@ -28122,49 +28119,46 @@
         <v>68</v>
       </c>
       <c r="J377" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L377" s="1">
-        <v>46290</v>
-      </c>
-      <c r="M377" t="s">
-        <v>210</v>
+        <v>46293</v>
       </c>
       <c r="N377" t="s">
         <v>218</v>
       </c>
       <c r="O377">
-        <v>17399260</v>
+        <v>17955421</v>
       </c>
       <c r="P377" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q377" t="s">
         <v>251</v>
       </c>
       <c r="R377" s="1">
-        <v>46287.48052434028</v>
+        <v>46267.47365627315</v>
       </c>
       <c r="S377">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="T377" t="s">
-        <v>259</v>
-      </c>
-      <c r="W377" t="s">
-        <v>358</v>
+        <v>260</v>
+      </c>
+      <c r="V377" t="s">
+        <v>270</v>
       </c>
       <c r="AA377">
         <v>0</v>
       </c>
       <c r="AB377" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG377" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="AH377" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="378" spans="1:34">
@@ -28187,7 +28181,7 @@
         <v>64</v>
       </c>
       <c r="G378">
-        <v>11276</v>
+        <v>6890</v>
       </c>
       <c r="H378">
         <v>0</v>
@@ -28196,16 +28190,19 @@
         <v>68</v>
       </c>
       <c r="J378" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="L378" s="1">
-        <v>46283</v>
+        <v>46290</v>
+      </c>
+      <c r="M378" t="s">
+        <v>210</v>
       </c>
       <c r="N378" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="O378">
-        <v>17399423</v>
+        <v>17399260</v>
       </c>
       <c r="P378" t="s">
         <v>227</v>
@@ -28214,22 +28211,25 @@
         <v>251</v>
       </c>
       <c r="R378" s="1">
-        <v>46266.47620831019</v>
+        <v>46287.48052434028</v>
       </c>
       <c r="S378">
-        <v>4</v>
+        <v>-3</v>
       </c>
       <c r="T378" t="s">
         <v>259</v>
       </c>
+      <c r="W378" t="s">
+        <v>358</v>
+      </c>
       <c r="AA378">
         <v>0</v>
       </c>
       <c r="AB378" t="s">
-        <v>467</v>
+        <v>227</v>
       </c>
       <c r="AG378" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AH378" t="s">
         <v>475</v>
@@ -28237,10 +28237,10 @@
     </row>
     <row r="379" spans="1:34">
       <c r="A379">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B379" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C379" t="s">
         <v>58</v>
@@ -28264,7 +28264,7 @@
         <v>68</v>
       </c>
       <c r="J379" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L379" s="1">
         <v>46283</v>
@@ -28273,31 +28273,28 @@
         <v>220</v>
       </c>
       <c r="O379">
-        <v>18152557</v>
+        <v>17399423</v>
       </c>
       <c r="P379" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="Q379" t="s">
         <v>251</v>
       </c>
       <c r="R379" s="1">
-        <v>46267.57586420139</v>
+        <v>46266.47620831019</v>
       </c>
       <c r="S379">
         <v>4</v>
       </c>
       <c r="T379" t="s">
-        <v>261</v>
-      </c>
-      <c r="V379" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="AA379">
         <v>0</v>
       </c>
       <c r="AB379" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AG379" t="s">
         <v>470</v>
@@ -28308,10 +28305,10 @@
     </row>
     <row r="380" spans="1:34">
       <c r="A380">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B380" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C380" t="s">
         <v>58</v>
@@ -28326,7 +28323,7 @@
         <v>64</v>
       </c>
       <c r="G380">
-        <v>1583</v>
+        <v>11276</v>
       </c>
       <c r="H380">
         <v>0</v>
@@ -28335,40 +28332,43 @@
         <v>68</v>
       </c>
       <c r="J380" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="L380" s="1">
-        <v>46290</v>
+        <v>46283</v>
       </c>
       <c r="N380" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O380">
-        <v>17398917</v>
+        <v>18152557</v>
       </c>
       <c r="P380" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="Q380" t="s">
         <v>251</v>
       </c>
       <c r="R380" s="1">
-        <v>46233.72355880787</v>
+        <v>46267.57586420139</v>
       </c>
       <c r="S380">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="T380" t="s">
-        <v>259</v>
+        <v>261</v>
+      </c>
+      <c r="V380" t="s">
+        <v>270</v>
       </c>
       <c r="AA380">
         <v>0</v>
       </c>
       <c r="AB380" t="s">
-        <v>227</v>
+        <v>468</v>
       </c>
       <c r="AG380" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AH380" t="s">
         <v>475</v>
@@ -28376,10 +28376,10 @@
     </row>
     <row r="381" spans="1:34">
       <c r="A381">
-        <v>5617</v>
+        <v>5417</v>
       </c>
       <c r="B381" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C381" t="s">
         <v>58</v>
@@ -28403,7 +28403,7 @@
         <v>68</v>
       </c>
       <c r="J381" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L381" s="1">
         <v>46290</v>
@@ -28412,36 +28412,42 @@
         <v>221</v>
       </c>
       <c r="O381">
-        <v>17407553</v>
+        <v>17398917</v>
+      </c>
+      <c r="P381" t="s">
+        <v>227</v>
       </c>
       <c r="Q381" t="s">
         <v>251</v>
       </c>
       <c r="R381" s="1">
-        <v>46261.36669849537</v>
+        <v>46233.72355880787</v>
       </c>
       <c r="S381">
         <v>-3</v>
       </c>
       <c r="T381" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="AA381">
         <v>0</v>
       </c>
       <c r="AB381" t="s">
-        <v>461</v>
+        <v>227</v>
       </c>
       <c r="AG381" t="s">
         <v>471</v>
       </c>
+      <c r="AH381" t="s">
+        <v>475</v>
+      </c>
     </row>
     <row r="382" spans="1:34">
       <c r="A382">
-        <v>6224</v>
+        <v>5617</v>
       </c>
       <c r="B382" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C382" t="s">
         <v>58</v>
@@ -28453,7 +28459,7 @@
         <v>62</v>
       </c>
       <c r="F382" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G382">
         <v>1583</v>
@@ -28465,7 +28471,7 @@
         <v>68</v>
       </c>
       <c r="J382" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L382" s="1">
         <v>46290</v>
@@ -28474,13 +28480,13 @@
         <v>221</v>
       </c>
       <c r="O382">
-        <v>17688645</v>
+        <v>17407553</v>
       </c>
       <c r="Q382" t="s">
         <v>251</v>
       </c>
       <c r="R382" s="1">
-        <v>46266.44156952546</v>
+        <v>46261.36669849537</v>
       </c>
       <c r="S382">
         <v>-3</v>
@@ -28488,14 +28494,11 @@
       <c r="T382" t="s">
         <v>264</v>
       </c>
-      <c r="V382" t="s">
-        <v>270</v>
-      </c>
       <c r="AA382">
         <v>0</v>
       </c>
       <c r="AB382" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AG382" t="s">
         <v>471</v>
@@ -28503,10 +28506,10 @@
     </row>
     <row r="383" spans="1:34">
       <c r="A383">
-        <v>6278</v>
+        <v>6224</v>
       </c>
       <c r="B383" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C383" t="s">
         <v>58</v>
@@ -28518,7 +28521,7 @@
         <v>62</v>
       </c>
       <c r="F383" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G383">
         <v>1583</v>
@@ -28530,7 +28533,7 @@
         <v>68</v>
       </c>
       <c r="J383" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L383" s="1">
         <v>46290</v>
@@ -28539,31 +28542,28 @@
         <v>221</v>
       </c>
       <c r="O383">
-        <v>18166312</v>
+        <v>17688645</v>
       </c>
       <c r="Q383" t="s">
         <v>251</v>
       </c>
       <c r="R383" s="1">
-        <v>46233.50562820602</v>
+        <v>46266.44156952546</v>
       </c>
       <c r="S383">
         <v>-3</v>
       </c>
       <c r="T383" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="V383" t="s">
         <v>270</v>
       </c>
-      <c r="W383" t="s">
-        <v>376</v>
-      </c>
       <c r="AA383">
         <v>0</v>
       </c>
       <c r="AB383" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="AG383" t="s">
         <v>471</v>
@@ -28571,10 +28571,10 @@
     </row>
     <row r="384" spans="1:34">
       <c r="A384">
-        <v>6486</v>
+        <v>6278</v>
       </c>
       <c r="B384" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C384" t="s">
         <v>58</v>
@@ -28598,7 +28598,7 @@
         <v>68</v>
       </c>
       <c r="J384" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L384" s="1">
         <v>46290</v>
@@ -28607,45 +28607,42 @@
         <v>221</v>
       </c>
       <c r="O384">
-        <v>18114208</v>
-      </c>
-      <c r="P384" t="s">
-        <v>245</v>
+        <v>18166312</v>
       </c>
       <c r="Q384" t="s">
         <v>251</v>
       </c>
       <c r="R384" s="1">
-        <v>46233.80164280093</v>
+        <v>46233.50562820602</v>
       </c>
       <c r="S384">
         <v>-3</v>
       </c>
       <c r="T384" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="V384" t="s">
         <v>270</v>
       </c>
+      <c r="W384" t="s">
+        <v>377</v>
+      </c>
       <c r="AA384">
         <v>0</v>
       </c>
       <c r="AB384" t="s">
-        <v>245</v>
+        <v>464</v>
       </c>
       <c r="AG384" t="s">
         <v>471</v>
       </c>
-      <c r="AH384" t="s">
-        <v>475</v>
-      </c>
     </row>
     <row r="385" spans="1:34">
       <c r="A385">
-        <v>6704</v>
+        <v>6486</v>
       </c>
       <c r="B385" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C385" t="s">
         <v>58</v>
@@ -28669,7 +28666,7 @@
         <v>68</v>
       </c>
       <c r="J385" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L385" s="1">
         <v>46290</v>
@@ -28678,22 +28675,22 @@
         <v>221</v>
       </c>
       <c r="O385">
-        <v>17955373</v>
+        <v>18114208</v>
       </c>
       <c r="P385" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="Q385" t="s">
         <v>251</v>
       </c>
       <c r="R385" s="1">
-        <v>46232.72913953703</v>
+        <v>46233.80164280093</v>
       </c>
       <c r="S385">
         <v>-3</v>
       </c>
       <c r="T385" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="V385" t="s">
         <v>270</v>
@@ -28702,21 +28699,21 @@
         <v>0</v>
       </c>
       <c r="AB385" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="AG385" t="s">
         <v>471</v>
       </c>
       <c r="AH385" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="386" spans="1:34">
       <c r="A386">
-        <v>5417</v>
+        <v>6704</v>
       </c>
       <c r="B386" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C386" t="s">
         <v>58</v>
@@ -28731,7 +28728,7 @@
         <v>64</v>
       </c>
       <c r="G386">
-        <v>11514</v>
+        <v>1583</v>
       </c>
       <c r="H386">
         <v>0</v>
@@ -28740,49 +28737,46 @@
         <v>68</v>
       </c>
       <c r="J386" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="L386" s="1">
         <v>46290</v>
       </c>
-      <c r="M386" t="s">
-        <v>210</v>
-      </c>
       <c r="N386" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="O386">
-        <v>17399465</v>
+        <v>17955373</v>
       </c>
       <c r="P386" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q386" t="s">
         <v>251</v>
       </c>
       <c r="R386" s="1">
-        <v>46287.48083141204</v>
+        <v>46232.72913953703</v>
       </c>
       <c r="S386">
         <v>-3</v>
       </c>
       <c r="T386" t="s">
-        <v>259</v>
-      </c>
-      <c r="W386" t="s">
-        <v>358</v>
+        <v>260</v>
+      </c>
+      <c r="V386" t="s">
+        <v>270</v>
       </c>
       <c r="AA386">
         <v>0</v>
       </c>
       <c r="AB386" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG386" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AH386" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="387" spans="1:34">
@@ -28805,7 +28799,7 @@
         <v>64</v>
       </c>
       <c r="G387">
-        <v>7874</v>
+        <v>11514</v>
       </c>
       <c r="H387">
         <v>0</v>
@@ -28814,16 +28808,19 @@
         <v>68</v>
       </c>
       <c r="J387" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="L387" s="1">
-        <v>46295</v>
+        <v>46290</v>
+      </c>
+      <c r="M387" t="s">
+        <v>210</v>
       </c>
       <c r="N387" t="s">
         <v>218</v>
       </c>
       <c r="O387">
-        <v>17399320</v>
+        <v>17399465</v>
       </c>
       <c r="P387" t="s">
         <v>227</v>
@@ -28832,25 +28829,25 @@
         <v>251</v>
       </c>
       <c r="R387" s="1">
-        <v>46283.6781059838</v>
+        <v>46287.48083141204</v>
       </c>
       <c r="S387">
-        <v>-8</v>
+        <v>-3</v>
       </c>
       <c r="T387" t="s">
         <v>259</v>
       </c>
       <c r="W387" t="s">
-        <v>377</v>
+        <v>358</v>
       </c>
       <c r="AA387">
         <v>0</v>
       </c>
       <c r="AB387" t="s">
-        <v>464</v>
+        <v>227</v>
       </c>
       <c r="AG387" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AH387" t="s">
         <v>475</v>
@@ -28876,25 +28873,25 @@
         <v>64</v>
       </c>
       <c r="G388">
-        <v>1628</v>
+        <v>7874</v>
       </c>
       <c r="H388">
-        <v>1581</v>
+        <v>0</v>
       </c>
       <c r="I388" t="s">
         <v>68</v>
       </c>
       <c r="J388" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="L388" s="1">
-        <v>46286</v>
+        <v>46295</v>
       </c>
       <c r="N388" t="s">
         <v>218</v>
       </c>
       <c r="O388">
-        <v>17398925</v>
+        <v>17399320</v>
       </c>
       <c r="P388" t="s">
         <v>227</v>
@@ -28903,19 +28900,22 @@
         <v>251</v>
       </c>
       <c r="R388" s="1">
-        <v>46280.37528408565</v>
+        <v>46283.6781059838</v>
       </c>
       <c r="S388">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="T388" t="s">
         <v>259</v>
       </c>
+      <c r="W388" t="s">
+        <v>378</v>
+      </c>
       <c r="AA388">
         <v>0</v>
       </c>
       <c r="AB388" t="s">
-        <v>227</v>
+        <v>464</v>
       </c>
       <c r="AG388" t="s">
         <v>470</v>
@@ -28926,16 +28926,16 @@
     </row>
     <row r="389" spans="1:34">
       <c r="A389">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B389" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C389" t="s">
         <v>58</v>
       </c>
       <c r="D389" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E389" t="s">
         <v>62</v>
@@ -28953,7 +28953,7 @@
         <v>68</v>
       </c>
       <c r="J389" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L389" s="1">
         <v>46286</v>
@@ -28962,42 +28962,42 @@
         <v>218</v>
       </c>
       <c r="O389">
-        <v>16962141</v>
+        <v>17398925</v>
       </c>
       <c r="P389" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="Q389" t="s">
         <v>251</v>
       </c>
       <c r="R389" s="1">
-        <v>46266.37634084491</v>
+        <v>46280.37528408565</v>
       </c>
       <c r="S389">
         <v>1</v>
       </c>
       <c r="T389" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="AA389">
         <v>0</v>
       </c>
       <c r="AB389" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="AG389" t="s">
         <v>470</v>
       </c>
       <c r="AH389" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="390" spans="1:34">
       <c r="A390">
-        <v>6703</v>
+        <v>6404</v>
       </c>
       <c r="B390" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C390" t="s">
         <v>58</v>
@@ -29021,7 +29021,7 @@
         <v>68</v>
       </c>
       <c r="J390" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L390" s="1">
         <v>46286</v>
@@ -29030,48 +29030,48 @@
         <v>218</v>
       </c>
       <c r="O390">
-        <v>17955176</v>
+        <v>16962141</v>
       </c>
       <c r="P390" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q390" t="s">
         <v>251</v>
       </c>
       <c r="R390" s="1">
-        <v>46282.42251184028</v>
+        <v>46266.37634084491</v>
       </c>
       <c r="S390">
         <v>1</v>
       </c>
       <c r="T390" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AA390">
         <v>0</v>
       </c>
       <c r="AB390" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG390" t="s">
         <v>470</v>
       </c>
       <c r="AH390" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="391" spans="1:34">
       <c r="A391">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B391" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C391" t="s">
         <v>58</v>
       </c>
       <c r="D391" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E391" t="s">
         <v>62</v>
@@ -29089,7 +29089,7 @@
         <v>68</v>
       </c>
       <c r="J391" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L391" s="1">
         <v>46286</v>
@@ -29098,51 +29098,48 @@
         <v>218</v>
       </c>
       <c r="O391">
-        <v>17955384</v>
+        <v>17955176</v>
       </c>
       <c r="P391" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="Q391" t="s">
         <v>251</v>
       </c>
       <c r="R391" s="1">
-        <v>46267.47452163194</v>
+        <v>46282.42251184028</v>
       </c>
       <c r="S391">
         <v>1</v>
       </c>
       <c r="T391" t="s">
-        <v>260</v>
-      </c>
-      <c r="V391" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="AA391">
         <v>0</v>
       </c>
       <c r="AB391" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="AG391" t="s">
         <v>470</v>
       </c>
       <c r="AH391" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="392" spans="1:34">
       <c r="A392">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B392" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C392" t="s">
         <v>58</v>
       </c>
       <c r="D392" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E392" t="s">
         <v>62</v>
@@ -29160,7 +29157,7 @@
         <v>68</v>
       </c>
       <c r="J392" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L392" s="1">
         <v>46286</v>
@@ -29169,7 +29166,7 @@
         <v>218</v>
       </c>
       <c r="O392">
-        <v>17955238</v>
+        <v>17955384</v>
       </c>
       <c r="P392" t="s">
         <v>228</v>
@@ -29178,7 +29175,7 @@
         <v>251</v>
       </c>
       <c r="R392" s="1">
-        <v>46267.4745221412</v>
+        <v>46267.47452163194</v>
       </c>
       <c r="S392">
         <v>1</v>
@@ -29186,6 +29183,9 @@
       <c r="T392" t="s">
         <v>260</v>
       </c>
+      <c r="V392" t="s">
+        <v>270</v>
+      </c>
       <c r="AA392">
         <v>0</v>
       </c>
@@ -29201,10 +29201,10 @@
     </row>
     <row r="393" spans="1:34">
       <c r="A393">
-        <v>6779</v>
+        <v>6705</v>
       </c>
       <c r="B393" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C393" t="s">
         <v>58</v>
@@ -29228,7 +29228,7 @@
         <v>68</v>
       </c>
       <c r="J393" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L393" s="1">
         <v>46286</v>
@@ -29237,7 +29237,7 @@
         <v>218</v>
       </c>
       <c r="O393">
-        <v>18056729</v>
+        <v>17955238</v>
       </c>
       <c r="P393" t="s">
         <v>228</v>
@@ -29246,7 +29246,7 @@
         <v>251</v>
       </c>
       <c r="R393" s="1">
-        <v>46267.47452299768</v>
+        <v>46267.4745221412</v>
       </c>
       <c r="S393">
         <v>1</v>
@@ -29254,9 +29254,6 @@
       <c r="T393" t="s">
         <v>260</v>
       </c>
-      <c r="V393" t="s">
-        <v>270</v>
-      </c>
       <c r="AA393">
         <v>0</v>
       </c>
@@ -29272,93 +29269,87 @@
     </row>
     <row r="394" spans="1:34">
       <c r="A394">
-        <v>6627</v>
+        <v>6779</v>
       </c>
       <c r="B394" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C394" t="s">
         <v>58</v>
       </c>
       <c r="D394" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E394" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F394" t="s">
         <v>64</v>
       </c>
       <c r="G394">
-        <v>5885</v>
+        <v>1628</v>
       </c>
       <c r="H394">
-        <v>5784</v>
+        <v>1581</v>
       </c>
       <c r="I394" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J394" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L394" s="1">
-        <v>46283</v>
-      </c>
-      <c r="M394" t="s">
-        <v>214</v>
+        <v>46286</v>
       </c>
       <c r="N394" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O394">
-        <v>18068566</v>
+        <v>18056729</v>
       </c>
       <c r="P394" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Q394" t="s">
         <v>251</v>
       </c>
       <c r="R394" s="1">
-        <v>46281.63558861111</v>
+        <v>46267.47452299768</v>
       </c>
       <c r="S394">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T394" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="V394" t="s">
         <v>270</v>
       </c>
-      <c r="W394" t="s">
-        <v>378</v>
-      </c>
       <c r="AA394">
         <v>0</v>
       </c>
       <c r="AB394" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AG394" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AH394" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="395" spans="1:34">
       <c r="A395">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B395" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C395" t="s">
         <v>58</v>
       </c>
       <c r="D395" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E395" t="s">
         <v>63</v>
@@ -29376,7 +29367,7 @@
         <v>69</v>
       </c>
       <c r="J395" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L395" s="1">
         <v>46283</v>
@@ -29388,7 +29379,7 @@
         <v>219</v>
       </c>
       <c r="O395">
-        <v>18052485</v>
+        <v>18068566</v>
       </c>
       <c r="P395" t="s">
         <v>229</v>
@@ -29397,7 +29388,7 @@
         <v>251</v>
       </c>
       <c r="R395" s="1">
-        <v>46281.6358927662</v>
+        <v>46281.63558861111</v>
       </c>
       <c r="S395">
         <v>4</v>
@@ -29409,7 +29400,7 @@
         <v>270</v>
       </c>
       <c r="W395" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AA395">
         <v>0</v>
@@ -29426,10 +29417,10 @@
     </row>
     <row r="396" spans="1:34">
       <c r="A396">
-        <v>6945</v>
+        <v>6628</v>
       </c>
       <c r="B396" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C396" t="s">
         <v>58</v>
@@ -29438,10 +29429,10 @@
         <v>60</v>
       </c>
       <c r="E396" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F396" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G396">
         <v>5885</v>
@@ -29453,34 +29444,37 @@
         <v>69</v>
       </c>
       <c r="J396" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L396" s="1">
         <v>46283</v>
       </c>
       <c r="M396" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="N396" t="s">
         <v>219</v>
       </c>
       <c r="O396">
-        <v>18206577</v>
+        <v>18052485</v>
       </c>
       <c r="P396" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Q396" t="s">
         <v>251</v>
       </c>
       <c r="R396" s="1">
-        <v>46281.47564895833</v>
+        <v>46281.6358927662</v>
       </c>
       <c r="S396">
         <v>4</v>
       </c>
       <c r="T396" t="s">
-        <v>256</v>
+        <v>255</v>
+      </c>
+      <c r="V396" t="s">
+        <v>270</v>
       </c>
       <c r="W396" t="s">
         <v>379</v>
@@ -29489,7 +29483,7 @@
         <v>0</v>
       </c>
       <c r="AB396" t="s">
-        <v>249</v>
+        <v>229</v>
       </c>
       <c r="AG396" t="s">
         <v>471</v>
@@ -29500,28 +29494,28 @@
     </row>
     <row r="397" spans="1:34">
       <c r="A397">
-        <v>6703</v>
+        <v>6945</v>
       </c>
       <c r="B397" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C397" t="s">
         <v>58</v>
       </c>
       <c r="D397" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E397" t="s">
         <v>62</v>
       </c>
       <c r="F397" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G397">
-        <v>6395</v>
+        <v>5885</v>
       </c>
       <c r="H397">
-        <v>5792</v>
+        <v>5784</v>
       </c>
       <c r="I397" t="s">
         <v>69</v>
@@ -29532,35 +29526,41 @@
       <c r="L397" s="1">
         <v>46283</v>
       </c>
+      <c r="M397" t="s">
+        <v>215</v>
+      </c>
       <c r="N397" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O397">
-        <v>18105120</v>
+        <v>18206577</v>
       </c>
       <c r="P397" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="Q397" t="s">
         <v>251</v>
       </c>
       <c r="R397" s="1">
-        <v>46268.58940019676</v>
+        <v>46281.47564895833</v>
       </c>
       <c r="S397">
         <v>4</v>
       </c>
       <c r="T397" t="s">
-        <v>262</v>
+        <v>256</v>
+      </c>
+      <c r="W397" t="s">
+        <v>380</v>
       </c>
       <c r="AA397">
         <v>0</v>
       </c>
       <c r="AB397" t="s">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="AG397" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AH397" t="s">
         <v>477</v>
@@ -29568,16 +29568,16 @@
     </row>
     <row r="398" spans="1:34">
       <c r="A398">
-        <v>6779</v>
+        <v>6703</v>
       </c>
       <c r="B398" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C398" t="s">
         <v>58</v>
       </c>
       <c r="D398" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E398" t="s">
         <v>62</v>
@@ -29586,7 +29586,7 @@
         <v>64</v>
       </c>
       <c r="G398">
-        <v>5882</v>
+        <v>6395</v>
       </c>
       <c r="H398">
         <v>5792</v>
@@ -29600,61 +29600,52 @@
       <c r="L398" s="1">
         <v>46283</v>
       </c>
-      <c r="M398" t="s">
-        <v>215</v>
-      </c>
       <c r="N398" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O398">
-        <v>18195621</v>
+        <v>18105120</v>
       </c>
       <c r="P398" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="Q398" t="s">
         <v>251</v>
       </c>
       <c r="R398" s="1">
-        <v>46279.66710767361</v>
+        <v>46268.58940019676</v>
       </c>
       <c r="S398">
         <v>4</v>
       </c>
       <c r="T398" t="s">
-        <v>260</v>
-      </c>
-      <c r="V398" t="s">
-        <v>270</v>
-      </c>
-      <c r="W398" t="s">
-        <v>380</v>
+        <v>262</v>
       </c>
       <c r="AA398">
         <v>0</v>
       </c>
       <c r="AB398" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AG398" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AH398" t="s">
-        <v>462</v>
+        <v>477</v>
       </c>
     </row>
     <row r="399" spans="1:34">
       <c r="A399">
-        <v>5417</v>
+        <v>6779</v>
       </c>
       <c r="B399" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C399" t="s">
         <v>58</v>
       </c>
       <c r="D399" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E399" t="s">
         <v>62</v>
@@ -29663,7 +29654,7 @@
         <v>64</v>
       </c>
       <c r="G399">
-        <v>5883</v>
+        <v>5882</v>
       </c>
       <c r="H399">
         <v>5792</v>
@@ -29672,48 +29663,60 @@
         <v>69</v>
       </c>
       <c r="J399" t="s">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="L399" s="1">
-        <v>46286</v>
+        <v>46283</v>
+      </c>
+      <c r="M399" t="s">
+        <v>215</v>
       </c>
       <c r="N399" t="s">
         <v>219</v>
       </c>
       <c r="O399">
-        <v>17399067</v>
+        <v>18195621</v>
       </c>
       <c r="P399" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q399" t="s">
         <v>251</v>
       </c>
       <c r="R399" s="1">
-        <v>46282.47420876157</v>
+        <v>46279.66710767361</v>
       </c>
       <c r="S399">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T399" t="s">
-        <v>259</v>
+        <v>260</v>
+      </c>
+      <c r="V399" t="s">
+        <v>270</v>
+      </c>
+      <c r="W399" t="s">
+        <v>381</v>
       </c>
       <c r="AA399">
         <v>0</v>
       </c>
       <c r="AB399" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="AG399" t="s">
-        <v>470</v>
+        <v>471</v>
+      </c>
+      <c r="AH399" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="400" spans="1:34">
       <c r="A400">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B400" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C400" t="s">
         <v>58</v>
@@ -29742,55 +29745,43 @@
       <c r="L400" s="1">
         <v>46286</v>
       </c>
-      <c r="M400" t="s">
-        <v>216</v>
-      </c>
       <c r="N400" t="s">
         <v>219</v>
       </c>
       <c r="O400">
-        <v>16976067</v>
+        <v>17399067</v>
       </c>
       <c r="P400" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q400" t="s">
         <v>251</v>
       </c>
       <c r="R400" s="1">
-        <v>46281.68877074074</v>
+        <v>46282.47420876157</v>
       </c>
       <c r="S400">
         <v>1</v>
       </c>
       <c r="T400" t="s">
-        <v>261</v>
-      </c>
-      <c r="V400" t="s">
-        <v>270</v>
-      </c>
-      <c r="W400" t="s">
-        <v>381</v>
+        <v>259</v>
       </c>
       <c r="AA400">
         <v>0</v>
       </c>
       <c r="AB400" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="AG400" t="s">
         <v>470</v>
       </c>
-      <c r="AH400" t="s">
-        <v>477</v>
-      </c>
     </row>
     <row r="401" spans="1:34">
       <c r="A401">
-        <v>6548</v>
+        <v>6486</v>
       </c>
       <c r="B401" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C401" t="s">
         <v>58</v>
@@ -29820,28 +29811,28 @@
         <v>46286</v>
       </c>
       <c r="M401" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="N401" t="s">
         <v>219</v>
       </c>
       <c r="O401">
-        <v>17222629</v>
+        <v>16976067</v>
       </c>
       <c r="P401" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="Q401" t="s">
         <v>251</v>
       </c>
       <c r="R401" s="1">
-        <v>46280.57958537037</v>
+        <v>46281.68877074074</v>
       </c>
       <c r="S401">
         <v>1</v>
       </c>
       <c r="T401" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="V401" t="s">
         <v>270</v>
@@ -29853,7 +29844,7 @@
         <v>0</v>
       </c>
       <c r="AB401" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="AG401" t="s">
         <v>470</v>
@@ -29864,10 +29855,10 @@
     </row>
     <row r="402" spans="1:34">
       <c r="A402">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B402" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C402" t="s">
         <v>58</v>
@@ -29876,7 +29867,7 @@
         <v>59</v>
       </c>
       <c r="E402" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F402" t="s">
         <v>64</v>
@@ -29897,40 +29888,40 @@
         <v>46286</v>
       </c>
       <c r="M402" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="N402" t="s">
         <v>219</v>
       </c>
       <c r="O402">
-        <v>18068544</v>
+        <v>17222629</v>
       </c>
       <c r="P402" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q402" t="s">
         <v>251</v>
       </c>
       <c r="R402" s="1">
-        <v>46281.63570936343</v>
+        <v>46280.57958537037</v>
       </c>
       <c r="S402">
         <v>1</v>
       </c>
       <c r="T402" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="V402" t="s">
         <v>270</v>
       </c>
       <c r="W402" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AA402">
         <v>0</v>
       </c>
       <c r="AB402" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AG402" t="s">
         <v>470</v>
@@ -29941,16 +29932,16 @@
     </row>
     <row r="403" spans="1:34">
       <c r="A403">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B403" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C403" t="s">
         <v>58</v>
       </c>
       <c r="D403" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E403" t="s">
         <v>63</v>
@@ -29980,7 +29971,7 @@
         <v>219</v>
       </c>
       <c r="O403">
-        <v>18052463</v>
+        <v>18068544</v>
       </c>
       <c r="P403" t="s">
         <v>229</v>
@@ -29989,7 +29980,7 @@
         <v>251</v>
       </c>
       <c r="R403" s="1">
-        <v>46281.63595871528</v>
+        <v>46281.63570936343</v>
       </c>
       <c r="S403">
         <v>1</v>
@@ -30001,7 +29992,7 @@
         <v>270</v>
       </c>
       <c r="W403" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AA403">
         <v>0</v>
@@ -30018,19 +30009,19 @@
     </row>
     <row r="404" spans="1:34">
       <c r="A404">
-        <v>6703</v>
+        <v>6628</v>
       </c>
       <c r="B404" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C404" t="s">
         <v>58</v>
       </c>
       <c r="D404" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E404" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F404" t="s">
         <v>64</v>
@@ -30050,32 +30041,41 @@
       <c r="L404" s="1">
         <v>46286</v>
       </c>
+      <c r="M404" t="s">
+        <v>216</v>
+      </c>
       <c r="N404" t="s">
         <v>219</v>
       </c>
       <c r="O404">
-        <v>18077112</v>
+        <v>18052463</v>
       </c>
       <c r="P404" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="Q404" t="s">
         <v>251</v>
       </c>
       <c r="R404" s="1">
-        <v>46279.62681744213</v>
+        <v>46281.63595871528</v>
       </c>
       <c r="S404">
         <v>1</v>
       </c>
       <c r="T404" t="s">
-        <v>262</v>
+        <v>255</v>
+      </c>
+      <c r="V404" t="s">
+        <v>270</v>
+      </c>
+      <c r="W404" t="s">
+        <v>382</v>
       </c>
       <c r="AA404">
         <v>0</v>
       </c>
       <c r="AB404" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="AG404" t="s">
         <v>470</v>
@@ -30086,16 +30086,16 @@
     </row>
     <row r="405" spans="1:34">
       <c r="A405">
-        <v>6779</v>
+        <v>6703</v>
       </c>
       <c r="B405" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C405" t="s">
         <v>58</v>
       </c>
       <c r="D405" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E405" t="s">
         <v>62</v>
@@ -30122,45 +30122,42 @@
         <v>219</v>
       </c>
       <c r="O405">
-        <v>18090189</v>
+        <v>18077112</v>
       </c>
       <c r="P405" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="Q405" t="s">
         <v>251</v>
       </c>
       <c r="R405" s="1">
-        <v>46279.66707821759</v>
+        <v>46279.62681744213</v>
       </c>
       <c r="S405">
         <v>1</v>
       </c>
       <c r="T405" t="s">
-        <v>260</v>
-      </c>
-      <c r="V405" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="AA405">
         <v>0</v>
       </c>
       <c r="AB405" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AG405" t="s">
         <v>470</v>
       </c>
       <c r="AH405" t="s">
-        <v>462</v>
+        <v>477</v>
       </c>
     </row>
     <row r="406" spans="1:34">
       <c r="A406">
-        <v>6945</v>
+        <v>6779</v>
       </c>
       <c r="B406" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C406" t="s">
         <v>58</v>
@@ -30172,7 +30169,7 @@
         <v>62</v>
       </c>
       <c r="F406" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G406">
         <v>5883</v>
@@ -30189,67 +30186,64 @@
       <c r="L406" s="1">
         <v>46286</v>
       </c>
-      <c r="M406" t="s">
-        <v>207</v>
-      </c>
       <c r="N406" t="s">
         <v>219</v>
       </c>
       <c r="O406">
-        <v>18179111</v>
+        <v>18090189</v>
       </c>
       <c r="P406" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="Q406" t="s">
         <v>251</v>
       </c>
       <c r="R406" s="1">
-        <v>46286.7220354051</v>
+        <v>46279.66707821759</v>
       </c>
       <c r="S406">
         <v>1</v>
       </c>
       <c r="T406" t="s">
-        <v>256</v>
-      </c>
-      <c r="W406" t="s">
-        <v>383</v>
+        <v>260</v>
+      </c>
+      <c r="V406" t="s">
+        <v>270</v>
       </c>
       <c r="AA406">
         <v>0</v>
       </c>
       <c r="AB406" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="AG406" t="s">
         <v>470</v>
       </c>
       <c r="AH406" t="s">
-        <v>477</v>
+        <v>462</v>
       </c>
     </row>
     <row r="407" spans="1:34">
       <c r="A407">
-        <v>5417</v>
+        <v>6945</v>
       </c>
       <c r="B407" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C407" t="s">
         <v>58</v>
       </c>
       <c r="D407" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E407" t="s">
         <v>62</v>
       </c>
       <c r="F407" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G407">
-        <v>5884</v>
+        <v>5883</v>
       </c>
       <c r="H407">
         <v>5792</v>
@@ -30258,48 +30252,57 @@
         <v>69</v>
       </c>
       <c r="J407" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L407" s="1">
         <v>46286</v>
       </c>
+      <c r="M407" t="s">
+        <v>207</v>
+      </c>
       <c r="N407" t="s">
         <v>219</v>
       </c>
       <c r="O407">
-        <v>17399077</v>
+        <v>18179111</v>
       </c>
       <c r="P407" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q407" t="s">
         <v>251</v>
       </c>
       <c r="R407" s="1">
-        <v>46282.47437324074</v>
+        <v>46286.7220354051</v>
       </c>
       <c r="S407">
         <v>1</v>
       </c>
       <c r="T407" t="s">
-        <v>259</v>
+        <v>256</v>
+      </c>
+      <c r="W407" t="s">
+        <v>384</v>
       </c>
       <c r="AA407">
         <v>0</v>
       </c>
       <c r="AB407" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AG407" t="s">
         <v>470</v>
       </c>
+      <c r="AH407" t="s">
+        <v>477</v>
+      </c>
     </row>
     <row r="408" spans="1:34">
       <c r="A408">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B408" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C408" t="s">
         <v>58</v>
@@ -30328,55 +30331,43 @@
       <c r="L408" s="1">
         <v>46286</v>
       </c>
-      <c r="M408" t="s">
-        <v>216</v>
-      </c>
       <c r="N408" t="s">
         <v>219</v>
       </c>
       <c r="O408">
-        <v>16976077</v>
+        <v>17399077</v>
       </c>
       <c r="P408" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q408" t="s">
         <v>251</v>
       </c>
       <c r="R408" s="1">
-        <v>46281.68880230324</v>
+        <v>46282.47437324074</v>
       </c>
       <c r="S408">
         <v>1</v>
       </c>
       <c r="T408" t="s">
-        <v>261</v>
-      </c>
-      <c r="V408" t="s">
-        <v>270</v>
-      </c>
-      <c r="W408" t="s">
-        <v>381</v>
+        <v>259</v>
       </c>
       <c r="AA408">
         <v>0</v>
       </c>
       <c r="AB408" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="AG408" t="s">
         <v>470</v>
       </c>
-      <c r="AH408" t="s">
-        <v>477</v>
-      </c>
     </row>
     <row r="409" spans="1:34">
       <c r="A409">
-        <v>6548</v>
+        <v>6486</v>
       </c>
       <c r="B409" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C409" t="s">
         <v>58</v>
@@ -30406,40 +30397,40 @@
         <v>46286</v>
       </c>
       <c r="M409" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="N409" t="s">
         <v>219</v>
       </c>
       <c r="O409">
-        <v>17222647</v>
+        <v>16976077</v>
       </c>
       <c r="P409" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="Q409" t="s">
         <v>251</v>
       </c>
       <c r="R409" s="1">
-        <v>46280.57972293982</v>
+        <v>46281.68880230324</v>
       </c>
       <c r="S409">
         <v>1</v>
       </c>
       <c r="T409" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="V409" t="s">
         <v>270</v>
       </c>
       <c r="W409" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="AA409">
         <v>0</v>
       </c>
       <c r="AB409" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="AG409" t="s">
         <v>470</v>
@@ -30450,10 +30441,10 @@
     </row>
     <row r="410" spans="1:34">
       <c r="A410">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B410" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C410" t="s">
         <v>58</v>
@@ -30462,7 +30453,7 @@
         <v>59</v>
       </c>
       <c r="E410" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F410" t="s">
         <v>64</v>
@@ -30483,40 +30474,40 @@
         <v>46286</v>
       </c>
       <c r="M410" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="N410" t="s">
         <v>219</v>
       </c>
       <c r="O410">
-        <v>18068555</v>
+        <v>17222647</v>
       </c>
       <c r="P410" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q410" t="s">
         <v>251</v>
       </c>
       <c r="R410" s="1">
-        <v>46281.63575075231</v>
+        <v>46280.57972293982</v>
       </c>
       <c r="S410">
         <v>1</v>
       </c>
       <c r="T410" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="V410" t="s">
         <v>270</v>
       </c>
       <c r="W410" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="AA410">
         <v>0</v>
       </c>
       <c r="AB410" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AG410" t="s">
         <v>470</v>
@@ -30527,16 +30518,16 @@
     </row>
     <row r="411" spans="1:34">
       <c r="A411">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B411" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C411" t="s">
         <v>58</v>
       </c>
       <c r="D411" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E411" t="s">
         <v>63</v>
@@ -30566,7 +30557,7 @@
         <v>219</v>
       </c>
       <c r="O411">
-        <v>18052474</v>
+        <v>18068555</v>
       </c>
       <c r="P411" t="s">
         <v>229</v>
@@ -30575,7 +30566,7 @@
         <v>251</v>
       </c>
       <c r="R411" s="1">
-        <v>46281.63599785879</v>
+        <v>46281.63575075231</v>
       </c>
       <c r="S411">
         <v>1</v>
@@ -30587,7 +30578,7 @@
         <v>270</v>
       </c>
       <c r="W411" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AA411">
         <v>0</v>
@@ -30604,19 +30595,19 @@
     </row>
     <row r="412" spans="1:34">
       <c r="A412">
-        <v>6703</v>
+        <v>6628</v>
       </c>
       <c r="B412" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C412" t="s">
         <v>58</v>
       </c>
       <c r="D412" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E412" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F412" t="s">
         <v>64</v>
@@ -30636,32 +30627,41 @@
       <c r="L412" s="1">
         <v>46286</v>
       </c>
+      <c r="M412" t="s">
+        <v>216</v>
+      </c>
       <c r="N412" t="s">
         <v>219</v>
       </c>
       <c r="O412">
-        <v>18077122</v>
+        <v>18052474</v>
       </c>
       <c r="P412" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="Q412" t="s">
         <v>251</v>
       </c>
       <c r="R412" s="1">
-        <v>46279.6268503125</v>
+        <v>46281.63599785879</v>
       </c>
       <c r="S412">
         <v>1</v>
       </c>
       <c r="T412" t="s">
-        <v>262</v>
+        <v>255</v>
+      </c>
+      <c r="V412" t="s">
+        <v>270</v>
+      </c>
+      <c r="W412" t="s">
+        <v>382</v>
       </c>
       <c r="AA412">
         <v>0</v>
       </c>
       <c r="AB412" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="AG412" t="s">
         <v>470</v>
@@ -30672,16 +30672,16 @@
     </row>
     <row r="413" spans="1:34">
       <c r="A413">
-        <v>6779</v>
+        <v>6703</v>
       </c>
       <c r="B413" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C413" t="s">
         <v>58</v>
       </c>
       <c r="D413" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E413" t="s">
         <v>62</v>
@@ -30708,45 +30708,42 @@
         <v>219</v>
       </c>
       <c r="O413">
-        <v>18090199</v>
+        <v>18077122</v>
       </c>
       <c r="P413" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="Q413" t="s">
         <v>251</v>
       </c>
       <c r="R413" s="1">
-        <v>46279.66698128472</v>
+        <v>46279.6268503125</v>
       </c>
       <c r="S413">
         <v>1</v>
       </c>
       <c r="T413" t="s">
-        <v>260</v>
-      </c>
-      <c r="V413" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="AA413">
         <v>0</v>
       </c>
       <c r="AB413" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AG413" t="s">
         <v>470</v>
       </c>
       <c r="AH413" t="s">
-        <v>462</v>
+        <v>477</v>
       </c>
     </row>
     <row r="414" spans="1:34">
       <c r="A414">
-        <v>6945</v>
+        <v>6779</v>
       </c>
       <c r="B414" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C414" t="s">
         <v>58</v>
@@ -30758,7 +30755,7 @@
         <v>62</v>
       </c>
       <c r="F414" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G414">
         <v>5884</v>
@@ -30775,126 +30772,129 @@
       <c r="L414" s="1">
         <v>46286</v>
       </c>
-      <c r="M414" t="s">
-        <v>207</v>
-      </c>
       <c r="N414" t="s">
         <v>219</v>
       </c>
       <c r="O414">
-        <v>18179118</v>
+        <v>18090199</v>
       </c>
       <c r="P414" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="Q414" t="s">
         <v>251</v>
       </c>
       <c r="R414" s="1">
-        <v>46286.7221544213</v>
+        <v>46279.66698128472</v>
       </c>
       <c r="S414">
         <v>1</v>
       </c>
       <c r="T414" t="s">
-        <v>256</v>
-      </c>
-      <c r="W414" t="s">
-        <v>355</v>
+        <v>260</v>
+      </c>
+      <c r="V414" t="s">
+        <v>270</v>
       </c>
       <c r="AA414">
         <v>0</v>
       </c>
       <c r="AB414" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="AG414" t="s">
         <v>470</v>
       </c>
       <c r="AH414" t="s">
-        <v>477</v>
+        <v>462</v>
       </c>
     </row>
     <row r="415" spans="1:34">
       <c r="A415">
-        <v>5417</v>
+        <v>6945</v>
       </c>
       <c r="B415" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C415" t="s">
         <v>58</v>
       </c>
       <c r="D415" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E415" t="s">
         <v>62</v>
       </c>
       <c r="F415" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G415">
-        <v>7012</v>
+        <v>5884</v>
       </c>
       <c r="H415">
-        <v>0</v>
+        <v>5792</v>
       </c>
       <c r="I415" t="s">
         <v>69</v>
       </c>
       <c r="J415" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="L415" s="1">
-        <v>46281</v>
+        <v>46286</v>
+      </c>
+      <c r="M415" t="s">
+        <v>207</v>
       </c>
       <c r="N415" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O415">
-        <v>18257773</v>
+        <v>18179118</v>
       </c>
       <c r="P415" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q415" t="s">
         <v>251</v>
       </c>
       <c r="R415" s="1">
-        <v>46279.66929922454</v>
+        <v>46286.7221544213</v>
       </c>
       <c r="S415">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T415" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="W415" t="s">
-        <v>385</v>
+        <v>355</v>
       </c>
       <c r="AA415">
         <v>0</v>
       </c>
       <c r="AB415" t="s">
-        <v>459</v>
+        <v>230</v>
       </c>
       <c r="AG415" t="s">
         <v>470</v>
       </c>
+      <c r="AH415" t="s">
+        <v>477</v>
+      </c>
     </row>
     <row r="416" spans="1:34">
       <c r="A416">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B416" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C416" t="s">
         <v>58</v>
       </c>
       <c r="D416" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E416" t="s">
         <v>62</v>
@@ -30912,7 +30912,7 @@
         <v>69</v>
       </c>
       <c r="J416" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L416" s="1">
         <v>46281</v>
@@ -30921,22 +30921,22 @@
         <v>218</v>
       </c>
       <c r="O416">
-        <v>18258536</v>
+        <v>18257773</v>
       </c>
       <c r="P416" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="Q416" t="s">
         <v>251</v>
       </c>
       <c r="R416" s="1">
-        <v>46280.61353684028</v>
+        <v>46279.66929922454</v>
       </c>
       <c r="S416">
         <v>6</v>
       </c>
       <c r="T416" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="W416" t="s">
         <v>386</v>
@@ -30950,22 +30950,19 @@
       <c r="AG416" t="s">
         <v>470</v>
       </c>
-      <c r="AH416" t="s">
-        <v>462</v>
-      </c>
     </row>
     <row r="417" spans="1:34">
       <c r="A417">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B417" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C417" t="s">
         <v>58</v>
       </c>
       <c r="D417" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E417" t="s">
         <v>62</v>
@@ -30983,7 +30980,7 @@
         <v>69</v>
       </c>
       <c r="J417" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L417" s="1">
         <v>46281</v>
@@ -30992,25 +30989,22 @@
         <v>218</v>
       </c>
       <c r="O417">
-        <v>18254964</v>
+        <v>18258536</v>
       </c>
       <c r="P417" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="Q417" t="s">
         <v>251</v>
       </c>
       <c r="R417" s="1">
-        <v>46280.61353920139</v>
+        <v>46280.61353684028</v>
       </c>
       <c r="S417">
         <v>6</v>
       </c>
       <c r="T417" t="s">
-        <v>261</v>
-      </c>
-      <c r="V417" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="W417" t="s">
         <v>387</v>
@@ -31025,15 +31019,15 @@
         <v>470</v>
       </c>
       <c r="AH417" t="s">
-        <v>477</v>
+        <v>462</v>
       </c>
     </row>
     <row r="418" spans="1:34">
       <c r="A418">
-        <v>6548</v>
+        <v>6486</v>
       </c>
       <c r="B418" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C418" t="s">
         <v>58</v>
@@ -31057,7 +31051,7 @@
         <v>69</v>
       </c>
       <c r="J418" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L418" s="1">
         <v>46281</v>
@@ -31066,22 +31060,22 @@
         <v>218</v>
       </c>
       <c r="O418">
-        <v>18255116</v>
+        <v>18254964</v>
       </c>
       <c r="P418" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="Q418" t="s">
         <v>251</v>
       </c>
       <c r="R418" s="1">
-        <v>46279.63250563657</v>
+        <v>46280.61353920139</v>
       </c>
       <c r="S418">
         <v>6</v>
       </c>
       <c r="T418" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="V418" t="s">
         <v>270</v>
@@ -31104,10 +31098,10 @@
     </row>
     <row r="419" spans="1:34">
       <c r="A419">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B419" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C419" t="s">
         <v>58</v>
@@ -31116,7 +31110,7 @@
         <v>59</v>
       </c>
       <c r="E419" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F419" t="s">
         <v>64</v>
@@ -31131,7 +31125,7 @@
         <v>69</v>
       </c>
       <c r="J419" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L419" s="1">
         <v>46281</v>
@@ -31140,28 +31134,28 @@
         <v>218</v>
       </c>
       <c r="O419">
-        <v>18257668</v>
+        <v>18255116</v>
       </c>
       <c r="P419" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q419" t="s">
         <v>251</v>
       </c>
       <c r="R419" s="1">
-        <v>46280.61354019676</v>
+        <v>46279.63250563657</v>
       </c>
       <c r="S419">
         <v>6</v>
       </c>
       <c r="T419" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="V419" t="s">
         <v>270</v>
       </c>
       <c r="W419" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AA419">
         <v>0</v>
@@ -31178,16 +31172,16 @@
     </row>
     <row r="420" spans="1:34">
       <c r="A420">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B420" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C420" t="s">
         <v>58</v>
       </c>
       <c r="D420" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E420" t="s">
         <v>63</v>
@@ -31205,7 +31199,7 @@
         <v>69</v>
       </c>
       <c r="J420" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L420" s="1">
         <v>46281</v>
@@ -31214,7 +31208,7 @@
         <v>218</v>
       </c>
       <c r="O420">
-        <v>18256366</v>
+        <v>18257668</v>
       </c>
       <c r="P420" t="s">
         <v>229</v>
@@ -31223,7 +31217,7 @@
         <v>251</v>
       </c>
       <c r="R420" s="1">
-        <v>46280.6135403125</v>
+        <v>46280.61354019676</v>
       </c>
       <c r="S420">
         <v>6</v>
@@ -31235,7 +31229,7 @@
         <v>270</v>
       </c>
       <c r="W420" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AA420">
         <v>0</v>
@@ -31252,19 +31246,19 @@
     </row>
     <row r="421" spans="1:34">
       <c r="A421">
-        <v>6703</v>
+        <v>6628</v>
       </c>
       <c r="B421" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C421" t="s">
         <v>58</v>
       </c>
       <c r="D421" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E421" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F421" t="s">
         <v>64</v>
@@ -31279,43 +31273,43 @@
         <v>69</v>
       </c>
       <c r="J421" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L421" s="1">
         <v>46281</v>
       </c>
-      <c r="M421" t="s">
-        <v>214</v>
-      </c>
       <c r="N421" t="s">
         <v>218</v>
       </c>
       <c r="O421">
-        <v>18256433</v>
+        <v>18256366</v>
       </c>
       <c r="P421" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="Q421" t="s">
         <v>251</v>
       </c>
       <c r="R421" s="1">
-        <v>46281.71218414352</v>
+        <v>46280.6135403125</v>
       </c>
       <c r="S421">
         <v>6</v>
       </c>
       <c r="T421" t="s">
-        <v>262</v>
+        <v>255</v>
+      </c>
+      <c r="V421" t="s">
+        <v>270</v>
       </c>
       <c r="W421" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AA421">
         <v>0</v>
       </c>
       <c r="AB421" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="AG421" t="s">
         <v>470</v>
@@ -31326,16 +31320,16 @@
     </row>
     <row r="422" spans="1:34">
       <c r="A422">
-        <v>6779</v>
+        <v>6703</v>
       </c>
       <c r="B422" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C422" t="s">
         <v>58</v>
       </c>
       <c r="D422" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E422" t="s">
         <v>62</v>
@@ -31353,34 +31347,34 @@
         <v>69</v>
       </c>
       <c r="J422" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L422" s="1">
         <v>46281</v>
       </c>
+      <c r="M422" t="s">
+        <v>214</v>
+      </c>
       <c r="N422" t="s">
         <v>218</v>
       </c>
       <c r="O422">
-        <v>18255012</v>
+        <v>18256433</v>
       </c>
       <c r="P422" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="Q422" t="s">
         <v>251</v>
       </c>
       <c r="R422" s="1">
-        <v>46281.41576883102</v>
+        <v>46281.71218414352</v>
       </c>
       <c r="S422">
         <v>6</v>
       </c>
       <c r="T422" t="s">
-        <v>260</v>
-      </c>
-      <c r="V422" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="W422" t="s">
         <v>390</v>
@@ -31389,21 +31383,21 @@
         <v>0</v>
       </c>
       <c r="AB422" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="AG422" t="s">
         <v>470</v>
       </c>
       <c r="AH422" t="s">
-        <v>462</v>
+        <v>477</v>
       </c>
     </row>
     <row r="423" spans="1:34">
       <c r="A423">
-        <v>6945</v>
+        <v>6779</v>
       </c>
       <c r="B423" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C423" t="s">
         <v>58</v>
@@ -31415,7 +31409,7 @@
         <v>62</v>
       </c>
       <c r="F423" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G423">
         <v>7012</v>
@@ -31427,7 +31421,7 @@
         <v>69</v>
       </c>
       <c r="J423" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L423" s="1">
         <v>46281</v>
@@ -31436,22 +31430,25 @@
         <v>218</v>
       </c>
       <c r="O423">
-        <v>18254903</v>
+        <v>18255012</v>
       </c>
       <c r="P423" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="Q423" t="s">
         <v>251</v>
       </c>
       <c r="R423" s="1">
-        <v>46280.43132989584</v>
+        <v>46281.41576883102</v>
       </c>
       <c r="S423">
         <v>6</v>
       </c>
       <c r="T423" t="s">
-        <v>256</v>
+        <v>260</v>
+      </c>
+      <c r="V423" t="s">
+        <v>270</v>
       </c>
       <c r="W423" t="s">
         <v>391</v>
@@ -31466,21 +31463,21 @@
         <v>470</v>
       </c>
       <c r="AH423" t="s">
-        <v>477</v>
+        <v>462</v>
       </c>
     </row>
     <row r="424" spans="1:34">
       <c r="A424">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B424" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C424" t="s">
         <v>58</v>
       </c>
       <c r="D424" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E424" t="s">
         <v>62</v>
@@ -31498,7 +31495,7 @@
         <v>69</v>
       </c>
       <c r="J424" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L424" s="1">
         <v>46281</v>
@@ -31507,22 +31504,22 @@
         <v>218</v>
       </c>
       <c r="O424">
-        <v>18258489</v>
+        <v>18254903</v>
       </c>
       <c r="P424" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q424" t="s">
         <v>251</v>
       </c>
       <c r="R424" s="1">
-        <v>46280.61367623843</v>
+        <v>46280.43132989584</v>
       </c>
       <c r="S424">
         <v>6</v>
       </c>
       <c r="T424" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="W424" t="s">
         <v>392</v>
@@ -31537,15 +31534,15 @@
         <v>470</v>
       </c>
       <c r="AH424" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="425" spans="1:34">
       <c r="A425">
-        <v>5417</v>
+        <v>6949</v>
       </c>
       <c r="B425" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C425" t="s">
         <v>58</v>
@@ -31557,46 +31554,43 @@
         <v>62</v>
       </c>
       <c r="F425" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G425">
-        <v>5836</v>
+        <v>7012</v>
       </c>
       <c r="H425">
-        <v>5784</v>
+        <v>0</v>
       </c>
       <c r="I425" t="s">
         <v>69</v>
       </c>
       <c r="J425" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="L425" s="1">
-        <v>46286</v>
-      </c>
-      <c r="M425" t="s">
-        <v>213</v>
+        <v>46281</v>
       </c>
       <c r="N425" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O425">
-        <v>17399027</v>
+        <v>18258489</v>
       </c>
       <c r="P425" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q425" t="s">
         <v>251</v>
       </c>
       <c r="R425" s="1">
-        <v>46286.71510853009</v>
+        <v>46280.61367623843</v>
       </c>
       <c r="S425">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T425" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="W425" t="s">
         <v>393</v>
@@ -31605,18 +31599,21 @@
         <v>0</v>
       </c>
       <c r="AB425" t="s">
-        <v>232</v>
+        <v>459</v>
       </c>
       <c r="AG425" t="s">
         <v>470</v>
       </c>
+      <c r="AH425" t="s">
+        <v>478</v>
+      </c>
     </row>
     <row r="426" spans="1:34">
       <c r="A426">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B426" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C426" t="s">
         <v>58</v>
@@ -31646,31 +31643,28 @@
         <v>46286</v>
       </c>
       <c r="M426" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="N426" t="s">
         <v>219</v>
       </c>
       <c r="O426">
-        <v>16976037</v>
+        <v>17399027</v>
       </c>
       <c r="P426" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q426" t="s">
         <v>251</v>
       </c>
       <c r="R426" s="1">
-        <v>46283.59424842593</v>
+        <v>46286.71510853009</v>
       </c>
       <c r="S426">
         <v>1</v>
       </c>
       <c r="T426" t="s">
-        <v>261</v>
-      </c>
-      <c r="V426" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="W426" t="s">
         <v>394</v>
@@ -31679,21 +31673,18 @@
         <v>0</v>
       </c>
       <c r="AB426" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="AG426" t="s">
         <v>470</v>
       </c>
-      <c r="AH426" t="s">
-        <v>477</v>
-      </c>
     </row>
     <row r="427" spans="1:34">
       <c r="A427">
-        <v>6548</v>
+        <v>6486</v>
       </c>
       <c r="B427" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C427" t="s">
         <v>58</v>
@@ -31729,22 +31720,22 @@
         <v>219</v>
       </c>
       <c r="O427">
-        <v>17222579</v>
+        <v>16976037</v>
       </c>
       <c r="P427" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="Q427" t="s">
         <v>251</v>
       </c>
       <c r="R427" s="1">
-        <v>46283.68435655093</v>
+        <v>46283.59424842593</v>
       </c>
       <c r="S427">
         <v>1</v>
       </c>
       <c r="T427" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="V427" t="s">
         <v>270</v>
@@ -31756,7 +31747,7 @@
         <v>0</v>
       </c>
       <c r="AB427" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="AG427" t="s">
         <v>470</v>
@@ -31767,10 +31758,10 @@
     </row>
     <row r="428" spans="1:34">
       <c r="A428">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B428" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C428" t="s">
         <v>58</v>
@@ -31779,7 +31770,7 @@
         <v>59</v>
       </c>
       <c r="E428" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F428" t="s">
         <v>64</v>
@@ -31806,34 +31797,34 @@
         <v>219</v>
       </c>
       <c r="O428">
-        <v>18068500</v>
+        <v>17222579</v>
       </c>
       <c r="P428" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q428" t="s">
         <v>251</v>
       </c>
       <c r="R428" s="1">
-        <v>46283.5942487037</v>
+        <v>46283.68435655093</v>
       </c>
       <c r="S428">
         <v>1</v>
       </c>
       <c r="T428" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="V428" t="s">
         <v>270</v>
       </c>
       <c r="W428" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AA428">
         <v>0</v>
       </c>
       <c r="AB428" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AG428" t="s">
         <v>470</v>
@@ -31844,16 +31835,16 @@
     </row>
     <row r="429" spans="1:34">
       <c r="A429">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B429" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C429" t="s">
         <v>58</v>
       </c>
       <c r="D429" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E429" t="s">
         <v>63</v>
@@ -31883,7 +31874,7 @@
         <v>219</v>
       </c>
       <c r="O429">
-        <v>18052419</v>
+        <v>18068500</v>
       </c>
       <c r="P429" t="s">
         <v>229</v>
@@ -31892,7 +31883,7 @@
         <v>251</v>
       </c>
       <c r="R429" s="1">
-        <v>46283.59424924768</v>
+        <v>46283.5942487037</v>
       </c>
       <c r="S429">
         <v>1</v>
@@ -31904,7 +31895,7 @@
         <v>270</v>
       </c>
       <c r="W429" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AA429">
         <v>0</v>
@@ -31921,19 +31912,19 @@
     </row>
     <row r="430" spans="1:34">
       <c r="A430">
-        <v>6703</v>
+        <v>6628</v>
       </c>
       <c r="B430" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C430" t="s">
         <v>58</v>
       </c>
       <c r="D430" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E430" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F430" t="s">
         <v>64</v>
@@ -31960,31 +31951,34 @@
         <v>219</v>
       </c>
       <c r="O430">
-        <v>18077082</v>
+        <v>18052419</v>
       </c>
       <c r="P430" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="Q430" t="s">
         <v>251</v>
       </c>
       <c r="R430" s="1">
-        <v>46283.68161918982</v>
+        <v>46283.59424924768</v>
       </c>
       <c r="S430">
         <v>1</v>
       </c>
       <c r="T430" t="s">
-        <v>262</v>
+        <v>255</v>
+      </c>
+      <c r="V430" t="s">
+        <v>270</v>
       </c>
       <c r="W430" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AA430">
         <v>0</v>
       </c>
       <c r="AB430" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="AG430" t="s">
         <v>470</v>
@@ -31995,16 +31989,16 @@
     </row>
     <row r="431" spans="1:34">
       <c r="A431">
-        <v>6779</v>
+        <v>6703</v>
       </c>
       <c r="B431" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C431" t="s">
         <v>58</v>
       </c>
       <c r="D431" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E431" t="s">
         <v>62</v>
@@ -32028,31 +32022,28 @@
         <v>46286</v>
       </c>
       <c r="M431" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N431" t="s">
         <v>219</v>
       </c>
       <c r="O431">
-        <v>18090149</v>
+        <v>18077082</v>
       </c>
       <c r="P431" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="Q431" t="s">
         <v>251</v>
       </c>
       <c r="R431" s="1">
-        <v>46286.6489187037</v>
+        <v>46283.68161918982</v>
       </c>
       <c r="S431">
         <v>1</v>
       </c>
       <c r="T431" t="s">
-        <v>260</v>
-      </c>
-      <c r="V431" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="W431" t="s">
         <v>397</v>
@@ -32061,27 +32052,27 @@
         <v>0</v>
       </c>
       <c r="AB431" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AG431" t="s">
         <v>470</v>
       </c>
       <c r="AH431" t="s">
-        <v>462</v>
+        <v>477</v>
       </c>
     </row>
     <row r="432" spans="1:34">
       <c r="A432">
-        <v>6404</v>
+        <v>6779</v>
       </c>
       <c r="B432" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C432" t="s">
         <v>58</v>
       </c>
       <c r="D432" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E432" t="s">
         <v>62</v>
@@ -32090,43 +32081,46 @@
         <v>64</v>
       </c>
       <c r="G432">
-        <v>5903</v>
+        <v>5836</v>
       </c>
       <c r="H432">
-        <v>5830</v>
+        <v>5784</v>
       </c>
       <c r="I432" t="s">
         <v>69</v>
       </c>
       <c r="J432" t="s">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="L432" s="1">
         <v>46286</v>
       </c>
       <c r="M432" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="N432" t="s">
         <v>219</v>
       </c>
       <c r="O432">
-        <v>16962221</v>
+        <v>18090149</v>
       </c>
       <c r="P432" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q432" t="s">
         <v>251</v>
       </c>
       <c r="R432" s="1">
-        <v>46282.42048836806</v>
+        <v>46286.6489187037</v>
       </c>
       <c r="S432">
         <v>1</v>
       </c>
       <c r="T432" t="s">
-        <v>263</v>
+        <v>260</v>
+      </c>
+      <c r="V432" t="s">
+        <v>270</v>
       </c>
       <c r="W432" t="s">
         <v>398</v>
@@ -32135,7 +32129,7 @@
         <v>0</v>
       </c>
       <c r="AB432" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG432" t="s">
         <v>470</v>
@@ -32164,10 +32158,10 @@
         <v>64</v>
       </c>
       <c r="G433">
+        <v>5903</v>
+      </c>
+      <c r="H433">
         <v>5830</v>
-      </c>
-      <c r="H433">
-        <v>5784</v>
       </c>
       <c r="I433" t="s">
         <v>69</v>
@@ -32178,11 +32172,14 @@
       <c r="L433" s="1">
         <v>46286</v>
       </c>
+      <c r="M433" t="s">
+        <v>215</v>
+      </c>
       <c r="N433" t="s">
         <v>219</v>
       </c>
       <c r="O433">
-        <v>16962211</v>
+        <v>16962221</v>
       </c>
       <c r="P433" t="s">
         <v>235</v>
@@ -32191,7 +32188,7 @@
         <v>251</v>
       </c>
       <c r="R433" s="1">
-        <v>46282.42138976852</v>
+        <v>46282.42048836806</v>
       </c>
       <c r="S433">
         <v>1</v>
@@ -32199,6 +32196,9 @@
       <c r="T433" t="s">
         <v>263</v>
       </c>
+      <c r="W433" t="s">
+        <v>399</v>
+      </c>
       <c r="AA433">
         <v>0</v>
       </c>
@@ -32214,16 +32214,16 @@
     </row>
     <row r="434" spans="1:34">
       <c r="A434">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B434" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C434" t="s">
         <v>58</v>
       </c>
       <c r="D434" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E434" t="s">
         <v>62</v>
@@ -32232,10 +32232,10 @@
         <v>64</v>
       </c>
       <c r="G434">
-        <v>5786</v>
+        <v>5830</v>
       </c>
       <c r="H434">
-        <v>0</v>
+        <v>5784</v>
       </c>
       <c r="I434" t="s">
         <v>69</v>
@@ -32244,51 +32244,54 @@
         <v>158</v>
       </c>
       <c r="L434" s="1">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="N434" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O434">
-        <v>17398997</v>
+        <v>16962211</v>
       </c>
       <c r="P434" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q434" t="s">
         <v>251</v>
       </c>
       <c r="R434" s="1">
-        <v>46279.66936339121</v>
+        <v>46282.42138976852</v>
       </c>
       <c r="S434">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T434" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="AA434">
         <v>0</v>
       </c>
       <c r="AB434" t="s">
-        <v>459</v>
+        <v>235</v>
       </c>
       <c r="AG434" t="s">
-        <v>471</v>
+        <v>470</v>
+      </c>
+      <c r="AH434" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="435" spans="1:34">
       <c r="A435">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B435" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C435" t="s">
         <v>58</v>
       </c>
       <c r="D435" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E435" t="s">
         <v>62</v>
@@ -32306,7 +32309,7 @@
         <v>69</v>
       </c>
       <c r="J435" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L435" s="1">
         <v>46283</v>
@@ -32315,48 +32318,45 @@
         <v>218</v>
       </c>
       <c r="O435">
-        <v>16962199</v>
+        <v>17398997</v>
       </c>
       <c r="P435" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="Q435" t="s">
         <v>251</v>
       </c>
       <c r="R435" s="1">
-        <v>46264.0028866088</v>
+        <v>46279.66936339121</v>
       </c>
       <c r="S435">
         <v>4</v>
       </c>
       <c r="T435" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="AA435">
         <v>0</v>
       </c>
       <c r="AB435" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="AG435" t="s">
         <v>471</v>
       </c>
-      <c r="AH435" t="s">
-        <v>462</v>
-      </c>
     </row>
     <row r="436" spans="1:34">
       <c r="A436">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B436" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C436" t="s">
         <v>58</v>
       </c>
       <c r="D436" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E436" t="s">
         <v>62</v>
@@ -32374,7 +32374,7 @@
         <v>69</v>
       </c>
       <c r="J436" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L436" s="1">
         <v>46283</v>
@@ -32383,45 +32383,42 @@
         <v>218</v>
       </c>
       <c r="O436">
-        <v>16976005</v>
+        <v>16962199</v>
       </c>
       <c r="P436" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="Q436" t="s">
         <v>251</v>
       </c>
       <c r="R436" s="1">
-        <v>46279.62931917824</v>
+        <v>46264.0028866088</v>
       </c>
       <c r="S436">
         <v>4</v>
       </c>
       <c r="T436" t="s">
-        <v>261</v>
-      </c>
-      <c r="V436" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="AA436">
         <v>0</v>
       </c>
       <c r="AB436" t="s">
-        <v>229</v>
+        <v>464</v>
       </c>
       <c r="AG436" t="s">
         <v>471</v>
       </c>
       <c r="AH436" t="s">
-        <v>477</v>
+        <v>462</v>
       </c>
     </row>
     <row r="437" spans="1:34">
       <c r="A437">
-        <v>6548</v>
+        <v>6486</v>
       </c>
       <c r="B437" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C437" t="s">
         <v>58</v>
@@ -32445,7 +32442,7 @@
         <v>69</v>
       </c>
       <c r="J437" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L437" s="1">
         <v>46283</v>
@@ -32454,22 +32451,22 @@
         <v>218</v>
       </c>
       <c r="O437">
-        <v>17222531</v>
+        <v>16976005</v>
       </c>
       <c r="P437" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="Q437" t="s">
         <v>251</v>
       </c>
       <c r="R437" s="1">
-        <v>46279.40189447917</v>
+        <v>46279.62931917824</v>
       </c>
       <c r="S437">
         <v>4</v>
       </c>
       <c r="T437" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="V437" t="s">
         <v>270</v>
@@ -32478,7 +32475,7 @@
         <v>0</v>
       </c>
       <c r="AB437" t="s">
-        <v>459</v>
+        <v>229</v>
       </c>
       <c r="AG437" t="s">
         <v>471</v>
@@ -32489,10 +32486,10 @@
     </row>
     <row r="438" spans="1:34">
       <c r="A438">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B438" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C438" t="s">
         <v>58</v>
@@ -32501,7 +32498,7 @@
         <v>59</v>
       </c>
       <c r="E438" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F438" t="s">
         <v>64</v>
@@ -32516,7 +32513,7 @@
         <v>69</v>
       </c>
       <c r="J438" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L438" s="1">
         <v>46283</v>
@@ -32525,22 +32522,22 @@
         <v>218</v>
       </c>
       <c r="O438">
-        <v>18068463</v>
+        <v>17222531</v>
       </c>
       <c r="P438" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q438" t="s">
         <v>251</v>
       </c>
       <c r="R438" s="1">
-        <v>46279.62936614583</v>
+        <v>46279.40189447917</v>
       </c>
       <c r="S438">
         <v>4</v>
       </c>
       <c r="T438" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="V438" t="s">
         <v>270</v>
@@ -32549,7 +32546,7 @@
         <v>0</v>
       </c>
       <c r="AB438" t="s">
-        <v>229</v>
+        <v>459</v>
       </c>
       <c r="AG438" t="s">
         <v>471</v>
@@ -32560,16 +32557,16 @@
     </row>
     <row r="439" spans="1:34">
       <c r="A439">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B439" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C439" t="s">
         <v>58</v>
       </c>
       <c r="D439" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E439" t="s">
         <v>63</v>
@@ -32587,7 +32584,7 @@
         <v>69</v>
       </c>
       <c r="J439" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L439" s="1">
         <v>46283</v>
@@ -32596,7 +32593,7 @@
         <v>218</v>
       </c>
       <c r="O439">
-        <v>18052384</v>
+        <v>18068463</v>
       </c>
       <c r="P439" t="s">
         <v>229</v>
@@ -32605,7 +32602,7 @@
         <v>251</v>
       </c>
       <c r="R439" s="1">
-        <v>46279.62936509259</v>
+        <v>46279.62936614583</v>
       </c>
       <c r="S439">
         <v>4</v>
@@ -32631,10 +32628,10 @@
     </row>
     <row r="440" spans="1:34">
       <c r="A440">
-        <v>6779</v>
+        <v>6628</v>
       </c>
       <c r="B440" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C440" t="s">
         <v>58</v>
@@ -32643,7 +32640,7 @@
         <v>60</v>
       </c>
       <c r="E440" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F440" t="s">
         <v>64</v>
@@ -32658,7 +32655,7 @@
         <v>69</v>
       </c>
       <c r="J440" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L440" s="1">
         <v>46283</v>
@@ -32667,22 +32664,22 @@
         <v>218</v>
       </c>
       <c r="O440">
-        <v>18090113</v>
+        <v>18052384</v>
       </c>
       <c r="P440" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="Q440" t="s">
         <v>251</v>
       </c>
       <c r="R440" s="1">
-        <v>46276.63187607639</v>
+        <v>46279.62936509259</v>
       </c>
       <c r="S440">
         <v>4</v>
       </c>
       <c r="T440" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="V440" t="s">
         <v>270</v>
@@ -32691,21 +32688,21 @@
         <v>0</v>
       </c>
       <c r="AB440" t="s">
-        <v>459</v>
+        <v>229</v>
       </c>
       <c r="AG440" t="s">
         <v>471</v>
       </c>
       <c r="AH440" t="s">
-        <v>462</v>
+        <v>477</v>
       </c>
     </row>
     <row r="441" spans="1:34">
       <c r="A441">
-        <v>6945</v>
+        <v>6779</v>
       </c>
       <c r="B441" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C441" t="s">
         <v>58</v>
@@ -32717,7 +32714,7 @@
         <v>62</v>
       </c>
       <c r="F441" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G441">
         <v>5786</v>
@@ -32729,7 +32726,7 @@
         <v>69</v>
       </c>
       <c r="J441" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L441" s="1">
         <v>46283</v>
@@ -32738,22 +32735,25 @@
         <v>218</v>
       </c>
       <c r="O441">
-        <v>18179053</v>
+        <v>18090113</v>
       </c>
       <c r="P441" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="Q441" t="s">
         <v>251</v>
       </c>
       <c r="R441" s="1">
-        <v>46279.62658503472</v>
+        <v>46276.63187607639</v>
       </c>
       <c r="S441">
         <v>4</v>
       </c>
       <c r="T441" t="s">
-        <v>256</v>
+        <v>260</v>
+      </c>
+      <c r="V441" t="s">
+        <v>270</v>
       </c>
       <c r="AA441">
         <v>0</v>
@@ -32765,21 +32765,21 @@
         <v>471</v>
       </c>
       <c r="AH441" t="s">
-        <v>477</v>
+        <v>462</v>
       </c>
     </row>
     <row r="442" spans="1:34">
       <c r="A442">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B442" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C442" t="s">
         <v>58</v>
       </c>
       <c r="D442" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E442" t="s">
         <v>62</v>
@@ -32797,7 +32797,7 @@
         <v>69</v>
       </c>
       <c r="J442" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L442" s="1">
         <v>46283</v>
@@ -32806,22 +32806,22 @@
         <v>218</v>
       </c>
       <c r="O442">
-        <v>18190370</v>
+        <v>18179053</v>
       </c>
       <c r="P442" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q442" t="s">
         <v>251</v>
       </c>
       <c r="R442" s="1">
-        <v>46279.63255474537</v>
+        <v>46279.62658503472</v>
       </c>
       <c r="S442">
         <v>4</v>
       </c>
       <c r="T442" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AA442">
         <v>0</v>
@@ -32833,15 +32833,15 @@
         <v>471</v>
       </c>
       <c r="AH442" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="443" spans="1:34">
       <c r="A443">
-        <v>6486</v>
+        <v>6949</v>
       </c>
       <c r="B443" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C443" t="s">
         <v>58</v>
@@ -32853,10 +32853,10 @@
         <v>62</v>
       </c>
       <c r="F443" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G443">
-        <v>5787</v>
+        <v>5786</v>
       </c>
       <c r="H443">
         <v>0</v>
@@ -32868,51 +32868,54 @@
         <v>159</v>
       </c>
       <c r="L443" s="1">
-        <v>46286</v>
+        <v>46283</v>
       </c>
       <c r="N443" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="O443">
-        <v>16976010</v>
+        <v>18190370</v>
+      </c>
+      <c r="P443" t="s">
+        <v>231</v>
       </c>
       <c r="Q443" t="s">
         <v>251</v>
       </c>
       <c r="R443" s="1">
-        <v>46256.00536641204</v>
+        <v>46279.63255474537</v>
       </c>
       <c r="S443">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T443" t="s">
-        <v>261</v>
-      </c>
-      <c r="V443" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="AA443">
         <v>0</v>
       </c>
       <c r="AB443" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="AG443" t="s">
-        <v>470</v>
+        <v>471</v>
+      </c>
+      <c r="AH443" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="444" spans="1:34">
       <c r="A444">
-        <v>6779</v>
+        <v>6486</v>
       </c>
       <c r="B444" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C444" t="s">
         <v>58</v>
       </c>
       <c r="D444" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E444" t="s">
         <v>62</v>
@@ -32930,7 +32933,7 @@
         <v>69</v>
       </c>
       <c r="J444" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L444" s="1">
         <v>46286</v>
@@ -32939,19 +32942,19 @@
         <v>222</v>
       </c>
       <c r="O444">
-        <v>18090118</v>
+        <v>16976010</v>
       </c>
       <c r="Q444" t="s">
         <v>251</v>
       </c>
       <c r="R444" s="1">
-        <v>46256.00539434027</v>
+        <v>46256.00536641204</v>
       </c>
       <c r="S444">
         <v>1</v>
       </c>
       <c r="T444" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="V444" t="s">
         <v>270</v>
@@ -32968,10 +32971,10 @@
     </row>
     <row r="445" spans="1:34">
       <c r="A445">
-        <v>6945</v>
+        <v>6779</v>
       </c>
       <c r="B445" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C445" t="s">
         <v>58</v>
@@ -32983,7 +32986,7 @@
         <v>62</v>
       </c>
       <c r="F445" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G445">
         <v>5787</v>
@@ -32995,7 +32998,7 @@
         <v>69</v>
       </c>
       <c r="J445" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L445" s="1">
         <v>46286</v>
@@ -33004,19 +33007,22 @@
         <v>222</v>
       </c>
       <c r="O445">
-        <v>18179058</v>
+        <v>18090118</v>
       </c>
       <c r="Q445" t="s">
         <v>251</v>
       </c>
       <c r="R445" s="1">
-        <v>46256.00540109954</v>
+        <v>46256.00539434027</v>
       </c>
       <c r="S445">
         <v>1</v>
       </c>
       <c r="T445" t="s">
-        <v>256</v>
+        <v>260</v>
+      </c>
+      <c r="V445" t="s">
+        <v>270</v>
       </c>
       <c r="AA445">
         <v>0</v>
@@ -33030,10 +33036,10 @@
     </row>
     <row r="446" spans="1:34">
       <c r="A446">
-        <v>6628</v>
+        <v>6945</v>
       </c>
       <c r="B446" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C446" t="s">
         <v>58</v>
@@ -33042,13 +33048,13 @@
         <v>60</v>
       </c>
       <c r="E446" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F446" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G446">
-        <v>11810</v>
+        <v>5787</v>
       </c>
       <c r="H446">
         <v>0</v>
@@ -33062,38 +33068,29 @@
       <c r="L446" s="1">
         <v>46286</v>
       </c>
-      <c r="M446" t="s">
-        <v>213</v>
-      </c>
       <c r="N446" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="O446">
-        <v>18278512</v>
+        <v>18179058</v>
       </c>
       <c r="Q446" t="s">
         <v>251</v>
       </c>
       <c r="R446" s="1">
-        <v>46286.6987844213</v>
+        <v>46256.00540109954</v>
       </c>
       <c r="S446">
         <v>1</v>
       </c>
       <c r="T446" t="s">
-        <v>255</v>
-      </c>
-      <c r="V446" t="s">
-        <v>270</v>
-      </c>
-      <c r="W446" t="s">
-        <v>399</v>
+        <v>256</v>
       </c>
       <c r="AA446">
         <v>0</v>
       </c>
       <c r="AB446" t="s">
-        <v>229</v>
+        <v>464</v>
       </c>
       <c r="AG446" t="s">
         <v>470</v>
@@ -33101,10 +33098,10 @@
     </row>
     <row r="447" spans="1:34">
       <c r="A447">
-        <v>6779</v>
+        <v>6628</v>
       </c>
       <c r="B447" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C447" t="s">
         <v>58</v>
@@ -33113,16 +33110,16 @@
         <v>60</v>
       </c>
       <c r="E447" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F447" t="s">
         <v>64</v>
       </c>
       <c r="G447">
-        <v>5837</v>
+        <v>11810</v>
       </c>
       <c r="H447">
-        <v>5784</v>
+        <v>0</v>
       </c>
       <c r="I447" t="s">
         <v>69</v>
@@ -33131,63 +33128,57 @@
         <v>161</v>
       </c>
       <c r="L447" s="1">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="M447" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="N447" t="s">
         <v>219</v>
       </c>
       <c r="O447">
-        <v>18195614</v>
-      </c>
-      <c r="P447" t="s">
-        <v>236</v>
+        <v>18278512</v>
       </c>
       <c r="Q447" t="s">
         <v>251</v>
       </c>
       <c r="R447" s="1">
-        <v>46279.66713805556</v>
+        <v>46286.6987844213</v>
       </c>
       <c r="S447">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T447" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="V447" t="s">
         <v>270</v>
       </c>
       <c r="W447" t="s">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="AA447">
         <v>0</v>
       </c>
       <c r="AB447" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="AG447" t="s">
-        <v>471</v>
-      </c>
-      <c r="AH447" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
     </row>
     <row r="448" spans="1:34">
       <c r="A448">
-        <v>5417</v>
+        <v>6779</v>
       </c>
       <c r="B448" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C448" t="s">
         <v>58</v>
       </c>
       <c r="D448" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E448" t="s">
         <v>62</v>
@@ -33196,63 +33187,69 @@
         <v>64</v>
       </c>
       <c r="G448">
-        <v>6348</v>
+        <v>5837</v>
       </c>
       <c r="H448">
-        <v>0</v>
+        <v>5784</v>
       </c>
       <c r="I448" t="s">
         <v>69</v>
       </c>
       <c r="J448" t="s">
-        <v>91</v>
+        <v>162</v>
       </c>
       <c r="L448" s="1">
-        <v>46288</v>
+        <v>46283</v>
       </c>
       <c r="M448" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="N448" t="s">
         <v>219</v>
       </c>
       <c r="O448">
-        <v>18274307</v>
+        <v>18195614</v>
       </c>
       <c r="P448" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q448" t="s">
         <v>251</v>
       </c>
       <c r="R448" s="1">
-        <v>46287.45807677083</v>
+        <v>46279.66713805556</v>
       </c>
       <c r="S448">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T448" t="s">
-        <v>259</v>
+        <v>260</v>
+      </c>
+      <c r="V448" t="s">
+        <v>270</v>
       </c>
       <c r="W448" t="s">
-        <v>400</v>
+        <v>381</v>
       </c>
       <c r="AA448">
         <v>0</v>
       </c>
       <c r="AB448" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="AG448" t="s">
         <v>471</v>
       </c>
+      <c r="AH448" t="s">
+        <v>462</v>
+      </c>
     </row>
     <row r="449" spans="1:34">
       <c r="A449">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B449" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C449" t="s">
         <v>58</v>
@@ -33279,31 +33276,31 @@
         <v>91</v>
       </c>
       <c r="L449" s="1">
-        <v>46282</v>
+        <v>46288</v>
       </c>
       <c r="M449" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="N449" t="s">
         <v>219</v>
       </c>
       <c r="O449">
-        <v>18271101</v>
+        <v>18274307</v>
+      </c>
+      <c r="P449" t="s">
+        <v>232</v>
       </c>
       <c r="Q449" t="s">
         <v>251</v>
       </c>
       <c r="R449" s="1">
-        <v>46281.63317659722</v>
+        <v>46287.45807677083</v>
       </c>
       <c r="S449">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="T449" t="s">
-        <v>261</v>
-      </c>
-      <c r="V449" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="W449" t="s">
         <v>401</v>
@@ -33312,7 +33309,7 @@
         <v>0</v>
       </c>
       <c r="AB449" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="AG449" t="s">
         <v>471</v>
@@ -33320,10 +33317,10 @@
     </row>
     <row r="450" spans="1:34">
       <c r="A450">
-        <v>6949</v>
+        <v>6486</v>
       </c>
       <c r="B450" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C450" t="s">
         <v>58</v>
@@ -33335,7 +33332,7 @@
         <v>62</v>
       </c>
       <c r="F450" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G450">
         <v>6348</v>
@@ -33350,31 +33347,31 @@
         <v>91</v>
       </c>
       <c r="L450" s="1">
-        <v>46288</v>
+        <v>46282</v>
       </c>
       <c r="M450" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="N450" t="s">
         <v>219</v>
       </c>
       <c r="O450">
-        <v>18275979</v>
-      </c>
-      <c r="P450" t="s">
-        <v>231</v>
+        <v>18271101</v>
       </c>
       <c r="Q450" t="s">
         <v>251</v>
       </c>
       <c r="R450" s="1">
-        <v>46286.74096042824</v>
+        <v>46281.63317659722</v>
       </c>
       <c r="S450">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T450" t="s">
-        <v>257</v>
+        <v>261</v>
+      </c>
+      <c r="V450" t="s">
+        <v>270</v>
       </c>
       <c r="W450" t="s">
         <v>402</v>
@@ -33383,21 +33380,18 @@
         <v>0</v>
       </c>
       <c r="AB450" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AG450" t="s">
         <v>471</v>
       </c>
-      <c r="AH450" t="s">
-        <v>478</v>
-      </c>
     </row>
     <row r="451" spans="1:34">
       <c r="A451">
-        <v>6548</v>
+        <v>6949</v>
       </c>
       <c r="B451" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C451" t="s">
         <v>58</v>
@@ -33409,66 +33403,69 @@
         <v>62</v>
       </c>
       <c r="F451" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G451">
-        <v>11550</v>
+        <v>6348</v>
       </c>
       <c r="H451">
-        <v>1862</v>
+        <v>0</v>
       </c>
       <c r="I451" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J451" t="s">
-        <v>162</v>
+        <v>91</v>
       </c>
       <c r="L451" s="1">
-        <v>46286</v>
+        <v>46288</v>
+      </c>
+      <c r="M451" t="s">
+        <v>208</v>
       </c>
       <c r="N451" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O451">
-        <v>17988603</v>
+        <v>18275979</v>
       </c>
       <c r="P451" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="Q451" t="s">
         <v>251</v>
       </c>
       <c r="R451" s="1">
-        <v>46267.72055925926</v>
+        <v>46286.74096042824</v>
       </c>
       <c r="S451">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="T451" t="s">
-        <v>254</v>
-      </c>
-      <c r="V451" t="s">
-        <v>270</v>
+        <v>257</v>
+      </c>
+      <c r="W451" t="s">
+        <v>403</v>
       </c>
       <c r="AA451">
         <v>0</v>
       </c>
       <c r="AB451" t="s">
-        <v>463</v>
+        <v>231</v>
       </c>
       <c r="AG451" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AH451" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
     </row>
     <row r="452" spans="1:34">
       <c r="A452">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B452" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C452" t="s">
         <v>58</v>
@@ -33477,7 +33474,7 @@
         <v>59</v>
       </c>
       <c r="E452" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F452" t="s">
         <v>64</v>
@@ -33492,7 +33489,7 @@
         <v>70</v>
       </c>
       <c r="J452" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L452" s="1">
         <v>46286</v>
@@ -33501,22 +33498,22 @@
         <v>218</v>
       </c>
       <c r="O452">
-        <v>18048493</v>
+        <v>17988603</v>
       </c>
       <c r="P452" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Q452" t="s">
         <v>251</v>
       </c>
       <c r="R452" s="1">
-        <v>46267.79441380787</v>
+        <v>46267.72055925926</v>
       </c>
       <c r="S452">
         <v>1</v>
       </c>
       <c r="T452" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="V452" t="s">
         <v>270</v>
@@ -33530,13 +33527,16 @@
       <c r="AG452" t="s">
         <v>470</v>
       </c>
+      <c r="AH452" t="s">
+        <v>463</v>
+      </c>
     </row>
     <row r="453" spans="1:34">
       <c r="A453">
-        <v>6949</v>
+        <v>6627</v>
       </c>
       <c r="B453" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C453" t="s">
         <v>58</v>
@@ -33545,10 +33545,10 @@
         <v>59</v>
       </c>
       <c r="E453" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F453" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G453">
         <v>11550</v>
@@ -33560,7 +33560,7 @@
         <v>70</v>
       </c>
       <c r="J453" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L453" s="1">
         <v>46286</v>
@@ -33569,42 +33569,42 @@
         <v>218</v>
       </c>
       <c r="O453">
-        <v>18214931</v>
+        <v>18048493</v>
       </c>
       <c r="P453" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="Q453" t="s">
         <v>251</v>
       </c>
       <c r="R453" s="1">
-        <v>46267.79441215278</v>
+        <v>46267.79441380787</v>
       </c>
       <c r="S453">
         <v>1</v>
       </c>
       <c r="T453" t="s">
-        <v>257</v>
+        <v>255</v>
+      </c>
+      <c r="V453" t="s">
+        <v>270</v>
       </c>
       <c r="AA453">
         <v>0</v>
       </c>
       <c r="AB453" t="s">
-        <v>240</v>
+        <v>463</v>
       </c>
       <c r="AG453" t="s">
         <v>470</v>
       </c>
-      <c r="AH453" t="s">
-        <v>463</v>
-      </c>
     </row>
     <row r="454" spans="1:34">
       <c r="A454">
-        <v>6548</v>
+        <v>6949</v>
       </c>
       <c r="B454" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C454" t="s">
         <v>58</v>
@@ -33616,10 +33616,10 @@
         <v>62</v>
       </c>
       <c r="F454" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G454">
-        <v>1913</v>
+        <v>11550</v>
       </c>
       <c r="H454">
         <v>1862</v>
@@ -33637,31 +33637,28 @@
         <v>218</v>
       </c>
       <c r="O454">
-        <v>17988579</v>
+        <v>18214931</v>
       </c>
       <c r="P454" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q454" t="s">
         <v>251</v>
       </c>
       <c r="R454" s="1">
-        <v>46283.3939177662</v>
+        <v>46267.79441215278</v>
       </c>
       <c r="S454">
         <v>1</v>
       </c>
       <c r="T454" t="s">
-        <v>254</v>
-      </c>
-      <c r="V454" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="AA454">
         <v>0</v>
       </c>
       <c r="AB454" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="AG454" t="s">
         <v>470</v>
@@ -33672,10 +33669,10 @@
     </row>
     <row r="455" spans="1:34">
       <c r="A455">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B455" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C455" t="s">
         <v>58</v>
@@ -33684,7 +33681,7 @@
         <v>59</v>
       </c>
       <c r="E455" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F455" t="s">
         <v>64</v>
@@ -33699,57 +33696,54 @@
         <v>70</v>
       </c>
       <c r="J455" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L455" s="1">
         <v>46286</v>
       </c>
-      <c r="M455" t="s">
-        <v>213</v>
-      </c>
       <c r="N455" t="s">
         <v>218</v>
       </c>
       <c r="O455">
-        <v>18048433</v>
+        <v>17988579</v>
       </c>
       <c r="P455" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Q455" t="s">
         <v>251</v>
       </c>
       <c r="R455" s="1">
-        <v>46286.64017539352</v>
+        <v>46283.3939177662</v>
       </c>
       <c r="S455">
         <v>1</v>
       </c>
       <c r="T455" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="V455" t="s">
         <v>270</v>
       </c>
-      <c r="W455" t="s">
-        <v>375</v>
-      </c>
       <c r="AA455">
         <v>0</v>
       </c>
       <c r="AB455" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AG455" t="s">
         <v>470</v>
       </c>
+      <c r="AH455" t="s">
+        <v>463</v>
+      </c>
     </row>
     <row r="456" spans="1:34">
       <c r="A456">
-        <v>6949</v>
+        <v>6627</v>
       </c>
       <c r="B456" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C456" t="s">
         <v>58</v>
@@ -33758,10 +33752,10 @@
         <v>59</v>
       </c>
       <c r="E456" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F456" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G456">
         <v>1913</v>
@@ -33773,7 +33767,7 @@
         <v>70</v>
       </c>
       <c r="J456" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L456" s="1">
         <v>46286</v>
@@ -33785,51 +33779,51 @@
         <v>218</v>
       </c>
       <c r="O456">
-        <v>18214877</v>
+        <v>18048433</v>
       </c>
       <c r="P456" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="Q456" t="s">
         <v>251</v>
       </c>
       <c r="R456" s="1">
-        <v>46286.7204416551</v>
+        <v>46286.64017539352</v>
       </c>
       <c r="S456">
         <v>1</v>
       </c>
       <c r="T456" t="s">
-        <v>257</v>
+        <v>255</v>
+      </c>
+      <c r="V456" t="s">
+        <v>270</v>
       </c>
       <c r="W456" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AA456">
         <v>0</v>
       </c>
       <c r="AB456" t="s">
-        <v>463</v>
+        <v>238</v>
       </c>
       <c r="AG456" t="s">
         <v>470</v>
       </c>
-      <c r="AH456" t="s">
-        <v>463</v>
-      </c>
     </row>
     <row r="457" spans="1:34">
       <c r="A457">
-        <v>6962</v>
+        <v>6949</v>
       </c>
       <c r="B457" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C457" t="s">
         <v>58</v>
       </c>
       <c r="D457" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E457" t="s">
         <v>62</v>
@@ -33838,55 +33832,55 @@
         <v>65</v>
       </c>
       <c r="G457">
-        <v>11873</v>
+        <v>1913</v>
       </c>
       <c r="H457">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="I457" t="s">
         <v>70</v>
       </c>
       <c r="J457" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="L457" s="1">
-        <v>46281</v>
+        <v>46286</v>
       </c>
       <c r="M457" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="N457" t="s">
         <v>218</v>
       </c>
       <c r="O457">
-        <v>18223029</v>
+        <v>18214877</v>
       </c>
       <c r="P457" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q457" t="s">
         <v>251</v>
       </c>
       <c r="R457" s="1">
-        <v>46280.62789608796</v>
+        <v>46286.7204416551</v>
       </c>
       <c r="S457">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T457" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="W457" t="s">
-        <v>403</v>
+        <v>376</v>
       </c>
       <c r="AA457">
         <v>0</v>
       </c>
       <c r="AB457" t="s">
-        <v>241</v>
+        <v>463</v>
       </c>
       <c r="AG457" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AH457" t="s">
         <v>463</v>
@@ -33894,10 +33888,10 @@
     </row>
     <row r="458" spans="1:34">
       <c r="A458">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B458" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C458" t="s">
         <v>58</v>
@@ -33921,7 +33915,7 @@
         <v>70</v>
       </c>
       <c r="J458" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L458" s="1">
         <v>46281</v>
@@ -33933,7 +33927,7 @@
         <v>218</v>
       </c>
       <c r="O458">
-        <v>18222688</v>
+        <v>18223029</v>
       </c>
       <c r="P458" t="s">
         <v>241</v>
@@ -33942,7 +33936,7 @@
         <v>251</v>
       </c>
       <c r="R458" s="1">
-        <v>46280.63189497685</v>
+        <v>46280.62789608796</v>
       </c>
       <c r="S458">
         <v>6</v>
@@ -33951,7 +33945,7 @@
         <v>258</v>
       </c>
       <c r="W458" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AA458">
         <v>0</v>
@@ -33968,25 +33962,25 @@
     </row>
     <row r="459" spans="1:34">
       <c r="A459">
-        <v>6548</v>
+        <v>6963</v>
       </c>
       <c r="B459" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C459" t="s">
         <v>58</v>
       </c>
       <c r="D459" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E459" t="s">
         <v>62</v>
       </c>
       <c r="F459" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G459">
-        <v>1876</v>
+        <v>11873</v>
       </c>
       <c r="H459">
         <v>0</v>
@@ -33995,34 +33989,34 @@
         <v>70</v>
       </c>
       <c r="J459" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="L459" s="1">
-        <v>46283</v>
+        <v>46281</v>
+      </c>
+      <c r="M459" t="s">
+        <v>214</v>
       </c>
       <c r="N459" t="s">
         <v>218</v>
       </c>
       <c r="O459">
-        <v>17988555</v>
+        <v>18222688</v>
       </c>
       <c r="P459" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q459" t="s">
         <v>251</v>
       </c>
       <c r="R459" s="1">
-        <v>46283.66538607639</v>
+        <v>46280.63189497685</v>
       </c>
       <c r="S459">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T459" t="s">
-        <v>254</v>
-      </c>
-      <c r="V459" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="W459" t="s">
         <v>404</v>
@@ -34031,7 +34025,7 @@
         <v>0</v>
       </c>
       <c r="AB459" t="s">
-        <v>464</v>
+        <v>241</v>
       </c>
       <c r="AG459" t="s">
         <v>471</v>
@@ -34042,10 +34036,10 @@
     </row>
     <row r="460" spans="1:34">
       <c r="A460">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B460" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C460" t="s">
         <v>58</v>
@@ -34054,13 +34048,13 @@
         <v>59</v>
       </c>
       <c r="E460" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F460" t="s">
         <v>64</v>
       </c>
       <c r="G460">
-        <v>11411</v>
+        <v>1876</v>
       </c>
       <c r="H460">
         <v>0</v>
@@ -34078,22 +34072,22 @@
         <v>218</v>
       </c>
       <c r="O460">
-        <v>18048483</v>
+        <v>17988555</v>
       </c>
       <c r="P460" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Q460" t="s">
         <v>251</v>
       </c>
       <c r="R460" s="1">
-        <v>46286.43482986111</v>
+        <v>46283.66538607639</v>
       </c>
       <c r="S460">
         <v>4</v>
       </c>
       <c r="T460" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="V460" t="s">
         <v>270</v>
@@ -34105,18 +34099,21 @@
         <v>0</v>
       </c>
       <c r="AB460" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="AG460" t="s">
         <v>471</v>
       </c>
+      <c r="AH460" t="s">
+        <v>463</v>
+      </c>
     </row>
     <row r="461" spans="1:34">
       <c r="A461">
-        <v>6949</v>
+        <v>6627</v>
       </c>
       <c r="B461" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C461" t="s">
         <v>58</v>
@@ -34125,10 +34122,10 @@
         <v>59</v>
       </c>
       <c r="E461" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F461" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G461">
         <v>11411</v>
@@ -34140,7 +34137,7 @@
         <v>70</v>
       </c>
       <c r="J461" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L461" s="1">
         <v>46283</v>
@@ -34149,22 +34146,25 @@
         <v>218</v>
       </c>
       <c r="O461">
-        <v>18214925</v>
+        <v>18048483</v>
       </c>
       <c r="P461" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="Q461" t="s">
         <v>251</v>
       </c>
       <c r="R461" s="1">
-        <v>46286.74368133102</v>
+        <v>46286.43482986111</v>
       </c>
       <c r="S461">
         <v>4</v>
       </c>
       <c r="T461" t="s">
-        <v>257</v>
+        <v>255</v>
+      </c>
+      <c r="V461" t="s">
+        <v>270</v>
       </c>
       <c r="W461" t="s">
         <v>406</v>
@@ -34178,31 +34178,28 @@
       <c r="AG461" t="s">
         <v>471</v>
       </c>
-      <c r="AH461" t="s">
-        <v>463</v>
-      </c>
     </row>
     <row r="462" spans="1:34">
       <c r="A462">
-        <v>6628</v>
+        <v>6949</v>
       </c>
       <c r="B462" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C462" t="s">
         <v>58</v>
       </c>
       <c r="D462" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E462" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F462" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G462">
-        <v>1862</v>
+        <v>11411</v>
       </c>
       <c r="H462">
         <v>0</v>
@@ -34211,43 +34208,43 @@
         <v>70</v>
       </c>
       <c r="J462" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="L462" s="1">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="N462" t="s">
         <v>218</v>
       </c>
       <c r="O462">
-        <v>18047772</v>
+        <v>18214925</v>
       </c>
       <c r="P462" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q462" t="s">
         <v>251</v>
       </c>
       <c r="R462" s="1">
-        <v>46265.00319547454</v>
+        <v>46286.74368133102</v>
       </c>
       <c r="S462">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T462" t="s">
-        <v>255</v>
-      </c>
-      <c r="V462" t="s">
-        <v>270</v>
+        <v>257</v>
+      </c>
+      <c r="W462" t="s">
+        <v>407</v>
       </c>
       <c r="AA462">
         <v>0</v>
       </c>
       <c r="AB462" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="AG462" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AH462" t="s">
         <v>463</v>
@@ -34255,10 +34252,10 @@
     </row>
     <row r="463" spans="1:34">
       <c r="A463">
-        <v>6945</v>
+        <v>6628</v>
       </c>
       <c r="B463" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C463" t="s">
         <v>58</v>
@@ -34267,10 +34264,10 @@
         <v>60</v>
       </c>
       <c r="E463" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F463" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G463">
         <v>1862</v>
@@ -34282,7 +34279,7 @@
         <v>70</v>
       </c>
       <c r="J463" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L463" s="1">
         <v>46281</v>
@@ -34291,39 +34288,45 @@
         <v>218</v>
       </c>
       <c r="O463">
-        <v>18220176</v>
+        <v>18047772</v>
       </c>
       <c r="P463" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q463" t="s">
         <v>251</v>
       </c>
       <c r="R463" s="1">
-        <v>46276.37795540509</v>
+        <v>46265.00319547454</v>
       </c>
       <c r="S463">
         <v>6</v>
       </c>
       <c r="T463" t="s">
-        <v>256</v>
+        <v>255</v>
+      </c>
+      <c r="V463" t="s">
+        <v>270</v>
       </c>
       <c r="AA463">
         <v>0</v>
       </c>
       <c r="AB463" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AG463" t="s">
         <v>470</v>
       </c>
+      <c r="AH463" t="s">
+        <v>463</v>
+      </c>
     </row>
     <row r="464" spans="1:34">
       <c r="A464">
-        <v>6628</v>
+        <v>6945</v>
       </c>
       <c r="B464" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C464" t="s">
         <v>58</v>
@@ -34332,13 +34335,13 @@
         <v>60</v>
       </c>
       <c r="E464" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F464" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G464">
-        <v>1879</v>
+        <v>1862</v>
       </c>
       <c r="H464">
         <v>0</v>
@@ -34347,57 +34350,48 @@
         <v>70</v>
       </c>
       <c r="J464" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="L464" s="1">
-        <v>46283</v>
+        <v>46281</v>
       </c>
       <c r="N464" t="s">
         <v>218</v>
       </c>
       <c r="O464">
-        <v>17988684</v>
+        <v>18220176</v>
       </c>
       <c r="P464" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q464" t="s">
         <v>251</v>
       </c>
       <c r="R464" s="1">
-        <v>46283.41459880787</v>
+        <v>46276.37795540509</v>
       </c>
       <c r="S464">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T464" t="s">
-        <v>255</v>
-      </c>
-      <c r="V464" t="s">
-        <v>270</v>
-      </c>
-      <c r="W464" t="s">
-        <v>407</v>
+        <v>256</v>
       </c>
       <c r="AA464">
         <v>0</v>
       </c>
       <c r="AB464" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="AG464" t="s">
-        <v>471</v>
-      </c>
-      <c r="AH464" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
     </row>
     <row r="465" spans="1:34">
       <c r="A465">
-        <v>6945</v>
+        <v>6628</v>
       </c>
       <c r="B465" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C465" t="s">
         <v>58</v>
@@ -34406,10 +34400,10 @@
         <v>60</v>
       </c>
       <c r="E465" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F465" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G465">
         <v>1879</v>
@@ -34421,7 +34415,7 @@
         <v>70</v>
       </c>
       <c r="J465" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L465" s="1">
         <v>46283</v>
@@ -34430,22 +34424,25 @@
         <v>218</v>
       </c>
       <c r="O465">
-        <v>18220194</v>
+        <v>17988684</v>
       </c>
       <c r="P465" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q465" t="s">
         <v>251</v>
       </c>
       <c r="R465" s="1">
-        <v>46283.73838344908</v>
+        <v>46283.41459880787</v>
       </c>
       <c r="S465">
         <v>4</v>
       </c>
       <c r="T465" t="s">
-        <v>256</v>
+        <v>255</v>
+      </c>
+      <c r="V465" t="s">
+        <v>270</v>
       </c>
       <c r="W465" t="s">
         <v>408</v>
@@ -34459,19 +34456,22 @@
       <c r="AG465" t="s">
         <v>471</v>
       </c>
+      <c r="AH465" t="s">
+        <v>463</v>
+      </c>
     </row>
     <row r="466" spans="1:34">
       <c r="A466">
-        <v>6962</v>
+        <v>6945</v>
       </c>
       <c r="B466" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C466" t="s">
         <v>58</v>
       </c>
       <c r="D466" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E466" t="s">
         <v>62</v>
@@ -34480,7 +34480,7 @@
         <v>65</v>
       </c>
       <c r="G466">
-        <v>1881</v>
+        <v>1879</v>
       </c>
       <c r="H466">
         <v>0</v>
@@ -34489,31 +34489,31 @@
         <v>70</v>
       </c>
       <c r="J466" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="L466" s="1">
-        <v>46287</v>
+        <v>46283</v>
       </c>
       <c r="N466" t="s">
         <v>218</v>
       </c>
       <c r="O466">
-        <v>18260044</v>
+        <v>18220194</v>
       </c>
       <c r="P466" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="Q466" t="s">
         <v>251</v>
       </c>
       <c r="R466" s="1">
-        <v>46286.76327152778</v>
+        <v>46283.73838344908</v>
       </c>
       <c r="S466">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T466" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="W466" t="s">
         <v>409</v>
@@ -34527,16 +34527,13 @@
       <c r="AG466" t="s">
         <v>471</v>
       </c>
-      <c r="AH466" t="s">
-        <v>463</v>
-      </c>
     </row>
     <row r="467" spans="1:34">
       <c r="A467">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B467" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C467" t="s">
         <v>58</v>
@@ -34560,7 +34557,7 @@
         <v>70</v>
       </c>
       <c r="J467" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L467" s="1">
         <v>46287</v>
@@ -34569,7 +34566,7 @@
         <v>218</v>
       </c>
       <c r="O467">
-        <v>18260177</v>
+        <v>18260044</v>
       </c>
       <c r="P467" t="s">
         <v>241</v>
@@ -34578,7 +34575,7 @@
         <v>251</v>
       </c>
       <c r="R467" s="1">
-        <v>46286.76330447917</v>
+        <v>46286.76327152778</v>
       </c>
       <c r="S467">
         <v>0</v>
@@ -34587,7 +34584,7 @@
         <v>258</v>
       </c>
       <c r="W467" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AA467">
         <v>0</v>
@@ -34604,25 +34601,25 @@
     </row>
     <row r="468" spans="1:34">
       <c r="A468">
-        <v>6548</v>
+        <v>6963</v>
       </c>
       <c r="B468" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C468" t="s">
         <v>58</v>
       </c>
       <c r="D468" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E468" t="s">
         <v>62</v>
       </c>
       <c r="F468" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G468">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="H468">
         <v>0</v>
@@ -34631,37 +34628,31 @@
         <v>70</v>
       </c>
       <c r="J468" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="L468" s="1">
         <v>46287</v>
       </c>
-      <c r="M468" t="s">
-        <v>207</v>
-      </c>
       <c r="N468" t="s">
         <v>218</v>
       </c>
       <c r="O468">
-        <v>17988567</v>
+        <v>18260177</v>
       </c>
       <c r="P468" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q468" t="s">
         <v>251</v>
       </c>
       <c r="R468" s="1">
-        <v>46287.42040790509</v>
+        <v>46286.76330447917</v>
       </c>
       <c r="S468">
         <v>0</v>
       </c>
       <c r="T468" t="s">
-        <v>254</v>
-      </c>
-      <c r="V468" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="W468" t="s">
         <v>410</v>
@@ -34681,10 +34672,10 @@
     </row>
     <row r="469" spans="1:34">
       <c r="A469">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B469" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C469" t="s">
         <v>58</v>
@@ -34693,7 +34684,7 @@
         <v>59</v>
       </c>
       <c r="E469" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F469" t="s">
         <v>64</v>
@@ -34713,26 +34704,29 @@
       <c r="L469" s="1">
         <v>46287</v>
       </c>
+      <c r="M469" t="s">
+        <v>207</v>
+      </c>
       <c r="N469" t="s">
         <v>218</v>
       </c>
       <c r="O469">
-        <v>17968390</v>
+        <v>17988567</v>
       </c>
       <c r="P469" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Q469" t="s">
         <v>251</v>
       </c>
       <c r="R469" s="1">
-        <v>46283.75381304398</v>
+        <v>46287.42040790509</v>
       </c>
       <c r="S469">
         <v>0</v>
       </c>
       <c r="T469" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="V469" t="s">
         <v>270</v>
@@ -34744,18 +34738,21 @@
         <v>0</v>
       </c>
       <c r="AB469" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="AG469" t="s">
         <v>471</v>
       </c>
+      <c r="AH469" t="s">
+        <v>463</v>
+      </c>
     </row>
     <row r="470" spans="1:34">
       <c r="A470">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B470" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C470" t="s">
         <v>58</v>
@@ -34764,13 +34761,13 @@
         <v>59</v>
       </c>
       <c r="E470" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F470" t="s">
         <v>64</v>
       </c>
       <c r="G470">
-        <v>7026</v>
+        <v>1882</v>
       </c>
       <c r="H470">
         <v>0</v>
@@ -34779,31 +34776,31 @@
         <v>70</v>
       </c>
       <c r="J470" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
       <c r="L470" s="1">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="N470" t="s">
         <v>218</v>
       </c>
       <c r="O470">
-        <v>18094899</v>
+        <v>17968390</v>
       </c>
       <c r="P470" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q470" t="s">
         <v>251</v>
       </c>
       <c r="R470" s="1">
-        <v>46286.59476721065</v>
+        <v>46283.75381304398</v>
       </c>
       <c r="S470">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T470" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="V470" t="s">
         <v>270</v>
@@ -34818,10 +34815,7 @@
         <v>464</v>
       </c>
       <c r="AG470" t="s">
-        <v>470</v>
-      </c>
-      <c r="AH470" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
     </row>
     <row r="471" spans="1:34">
@@ -34853,7 +34847,7 @@
         <v>70</v>
       </c>
       <c r="J471" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="L471" s="1">
         <v>46288</v>
@@ -34924,7 +34918,7 @@
         <v>70</v>
       </c>
       <c r="J472" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="L472" s="1">
         <v>46288</v>
@@ -35099,7 +35093,7 @@
         <v>257</v>
       </c>
       <c r="W474" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AA474">
         <v>0</v>
@@ -35143,7 +35137,7 @@
         <v>71</v>
       </c>
       <c r="J475" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L475" s="1">
         <v>46289</v>
@@ -35173,7 +35167,7 @@
         <v>259</v>
       </c>
       <c r="W475" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AA475">
         <v>0</v>
@@ -35442,7 +35436,7 @@
         <v>71</v>
       </c>
       <c r="J479" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L479" s="1">
         <v>46281</v>
@@ -35519,7 +35513,7 @@
         <v>71</v>
       </c>
       <c r="J480" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L480" s="1">
         <v>46281</v>
@@ -35593,7 +35587,7 @@
         <v>71</v>
       </c>
       <c r="J481" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L481" s="1">
         <v>46283</v>
@@ -35664,7 +35658,7 @@
         <v>71</v>
       </c>
       <c r="J482" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L482" s="1">
         <v>46283</v>
@@ -35741,7 +35735,7 @@
         <v>71</v>
       </c>
       <c r="J483" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L483" s="1">
         <v>46283</v>
@@ -35815,7 +35809,7 @@
         <v>71</v>
       </c>
       <c r="J484" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L484" s="1">
         <v>46283</v>
@@ -35889,7 +35883,7 @@
         <v>71</v>
       </c>
       <c r="J485" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L485" s="1">
         <v>46283</v>
@@ -36034,7 +36028,7 @@
         <v>71</v>
       </c>
       <c r="J487" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L487" s="1">
         <v>46283</v>
@@ -36105,7 +36099,7 @@
         <v>71</v>
       </c>
       <c r="J488" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L488" s="1">
         <v>46283</v>
@@ -36321,7 +36315,7 @@
         <v>71</v>
       </c>
       <c r="J491" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L491" s="1">
         <v>46287</v>
@@ -36395,7 +36389,7 @@
         <v>71</v>
       </c>
       <c r="J492" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="L492" s="1">
         <v>46288</v>
@@ -36466,7 +36460,7 @@
         <v>71</v>
       </c>
       <c r="J493" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="L493" s="1">
         <v>46288</v>
@@ -37389,7 +37383,7 @@
         <v>72</v>
       </c>
       <c r="J506" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L506" s="1">
         <v>46290</v>
@@ -37457,7 +37451,7 @@
         <v>72</v>
       </c>
       <c r="J507" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L507" s="1">
         <v>46290</v>
@@ -37522,7 +37516,7 @@
         <v>72</v>
       </c>
       <c r="J508" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L508" s="1">
         <v>46290</v>
@@ -37590,7 +37584,7 @@
         <v>72</v>
       </c>
       <c r="J509" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L509" s="1">
         <v>46290</v>
@@ -37658,7 +37652,7 @@
         <v>72</v>
       </c>
       <c r="J510" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L510" s="1">
         <v>46290</v>
@@ -42025,7 +42019,7 @@
         <v>73</v>
       </c>
       <c r="J571" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="L571" s="1">
         <v>46289</v>
@@ -42093,7 +42087,7 @@
         <v>73</v>
       </c>
       <c r="J572" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="L572" s="1">
         <v>46289</v>
@@ -42596,7 +42590,7 @@
         <v>268</v>
       </c>
       <c r="W579" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG579" t="s">
         <v>470</v>
@@ -42764,7 +42758,7 @@
         <v>69</v>
       </c>
       <c r="J582" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L582" s="1">
         <v>46286</v>
@@ -42829,7 +42823,7 @@
         <v>69</v>
       </c>
       <c r="J583" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L583" s="1">
         <v>46286</v>

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8980" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8977" uniqueCount="480">
   <si>
     <t>CodCliente</t>
   </si>
@@ -1136,7 +1136,7 @@
     <t>Comentário Colaborador + Previsão de Conclusão. Previsto para: 22/09/2026 - Data Comentário: 18/09/2026 15:24</t>
   </si>
   <si>
-    <t>Reaberto via API integração MGC x Sistema de Analise Fiscal em 22/09/2026 14:36:22. - Data Comentário: 22/09/2026 14:35</t>
+    <t>Reaberto via API integração MGC x Sistema de Analise Fiscal em 22/09/2026 15:19:22. - Data Comentário: 22/09/2026 15:16</t>
   </si>
   <si>
     <t>Comentário Colaborador + Previsão de Conclusão. Previsto para: 24/09/2026 - Data Comentário: 18/09/2026 15:24</t>
@@ -33287,9 +33287,6 @@
       <c r="O449">
         <v>18274307</v>
       </c>
-      <c r="P449" t="s">
-        <v>232</v>
-      </c>
       <c r="Q449" t="s">
         <v>251</v>
       </c>
@@ -42169,9 +42166,6 @@
       <c r="O573">
         <v>18275526</v>
       </c>
-      <c r="P573" t="s">
-        <v>247</v>
-      </c>
       <c r="Q573" t="s">
         <v>251</v>
       </c>
@@ -42240,9 +42234,6 @@
       <c r="O574">
         <v>18274091</v>
       </c>
-      <c r="P574" t="s">
-        <v>247</v>
-      </c>
       <c r="Q574" t="s">
         <v>251</v>
       </c>
@@ -42578,7 +42569,7 @@
         <v>18216396</v>
       </c>
       <c r="P579" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="Q579" t="s">
         <v>252</v>
@@ -42643,7 +42634,7 @@
         <v>18216401</v>
       </c>
       <c r="P580" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="Q580" t="s">
         <v>252</v>
@@ -42708,7 +42699,7 @@
         <v>18216376</v>
       </c>
       <c r="P581" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="Q581" t="s">
         <v>252</v>

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8738" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8739" uniqueCount="467">
   <si>
     <t>CodCliente</t>
   </si>
@@ -418,6 +418,12 @@
     <t>Envio Planilha de Fechamento</t>
   </si>
   <si>
+    <t>Fed - PIS/COFINS Não Cumul/Mon - 5856</t>
+  </si>
+  <si>
+    <t>Fed - PIS/COFINS Cumulativo - 2172</t>
+  </si>
+  <si>
     <t xml:space="preserve">Envio do Razão Conta - Valores à Classificar </t>
   </si>
   <si>
@@ -445,13 +451,7 @@
     <t>Est - ICMS SN - Diferencial Alíquota</t>
   </si>
   <si>
-    <t>Fed - PIS/COFINS Não Cumul/Mon - 5856</t>
-  </si>
-  <si>
     <t>Digitalização de NF Ativo</t>
-  </si>
-  <si>
-    <t>Fed - PIS/COFINS Cumulativo - 2172</t>
   </si>
   <si>
     <t>Confirm Rec - PIS/COFINS</t>
@@ -1069,6 +1069,16 @@
 Em processamento, previsão de conclusão em 23/09/2026 - Data Comentário: 21/09/2026 09:48</t>
   </si>
   <si>
+    <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 23/09/2026 
+Em atendimento - Data Comentário: 22/09/2026 17:12</t>
+  </si>
+  <si>
+    <t>Atraso da Operação, processo em elaboração conforme data prevista   Previsão para conclusão dia 23/09/2026 - Data Comentário: 22/09/2026 17:40</t>
+  </si>
+  <si>
+    <t>Atraso da Operação, processo em elaboração conforme data prevista  Previsão para conclusão dia 23/09/2026 - Data Comentário: 22/09/2026 17:39</t>
+  </si>
+  <si>
     <t>Comentário Colaborador + Previsão de Conclusão. Previsto para: 28/09/2026 - Data Comentário: 18/09/2026 15:26</t>
   </si>
   <si>
@@ -1088,23 +1098,13 @@
 aguardando cliente enviar - Data Comentário: 18/09/2026 15:32</t>
   </si>
   <si>
-    <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 23/09/2026 
-Em atendimento - Data Comentário: 22/09/2026 17:12</t>
-  </si>
-  <si>
     <t>Comentário Colaborador + Previsão de Conclusão. Previsto para: 24/09/2026 - Data Comentário: 18/09/2026 15:24</t>
   </si>
   <si>
     <t>Comentário Colaborador + Previsão de Conclusão. Previsto para: 28/09/2026 - Data Comentário: 18/09/2026 15:27</t>
   </si>
   <si>
-    <t>Atraso da Operação, processo em elaboração conforme data prevista   Previsão para conclusão dia 23/09/2026 - Data Comentário: 22/09/2026 17:40</t>
-  </si>
-  <si>
-    <t>Atraso da Operação, processo em elaboração conforme data prevista  Previsão para conclusão dia 23/09/2026 - Data Comentário: 22/09/2026 17:39</t>
-  </si>
-  <si>
-    <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1808] sendo a ultima baixa feita [1808]-22/09/2026 18:08:36.. - Data Comentário: 22/09/2026 18:03</t>
+    <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1808] sendo a ultima baixa feita [1808]-22/09/2026 18:08:36.. - Data Comentário: 22/09/2026 18:31</t>
   </si>
   <si>
     <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1807] sendo a ultima baixa feita [1807]-22/09/2026 10:05:26.. - Data Comentário: 22/09/2026 12:56</t>
@@ -1392,8 +1392,8 @@
     <t>Atraso da Operação, processo em elaboração conforme data prevista   Previsão para conclusão dia 23/09/2026 - Data Comentário: 22/09/2026 17:33</t>
   </si>
   <si>
-    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 25/09/2026 
-Aguardando assinatura do contrato, link enviado ao cliente! - Data Comentário: 16/09/2026 14:41</t>
+    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 30/09/2026 
+Aguardando assinatura do contrato, link enviado ao cliente! - Data Comentário: 23/09/2026 08:19</t>
   </si>
   <si>
     <t>Juan Rodrigues</t>
@@ -1949,7 +1949,7 @@
         <v>46267.75233784723</v>
       </c>
       <c r="S2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T2" t="s">
         <v>239</v>
@@ -2020,7 +2020,7 @@
         <v>46267.75233927083</v>
       </c>
       <c r="S3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T3" t="s">
         <v>240</v>
@@ -2091,7 +2091,7 @@
         <v>46267.7523394676</v>
       </c>
       <c r="S4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T4" t="s">
         <v>240</v>
@@ -2162,7 +2162,7 @@
         <v>46267.75234278935</v>
       </c>
       <c r="S5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T5" t="s">
         <v>241</v>
@@ -2230,7 +2230,7 @@
         <v>46267.75234309028</v>
       </c>
       <c r="S6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T6" t="s">
         <v>242</v>
@@ -2298,7 +2298,7 @@
         <v>46267.75234383102</v>
       </c>
       <c r="S7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T7" t="s">
         <v>243</v>
@@ -2366,7 +2366,7 @@
         <v>46267.75234424769</v>
       </c>
       <c r="S8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T8" t="s">
         <v>243</v>
@@ -2434,7 +2434,7 @@
         <v>46267.75231010417</v>
       </c>
       <c r="S9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T9" t="s">
         <v>244</v>
@@ -2502,7 +2502,7 @@
         <v>46267.75234059028</v>
       </c>
       <c r="S10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T10" t="s">
         <v>245</v>
@@ -2573,7 +2573,7 @@
         <v>46267.7523409375</v>
       </c>
       <c r="S11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T11" t="s">
         <v>245</v>
@@ -2641,7 +2641,7 @@
         <v>46267.75234170139</v>
       </c>
       <c r="S12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T12" t="s">
         <v>245</v>
@@ -2715,7 +2715,7 @@
         <v>46268.37896984954</v>
       </c>
       <c r="S13">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T13" t="s">
         <v>240</v>
@@ -2789,7 +2789,7 @@
         <v>46269.71652982639</v>
       </c>
       <c r="S14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T14" t="s">
         <v>241</v>
@@ -2860,7 +2860,7 @@
         <v>46269.71069613426</v>
       </c>
       <c r="S15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T15" t="s">
         <v>242</v>
@@ -2934,7 +2934,7 @@
         <v>46267.55838734953</v>
       </c>
       <c r="S16">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T16" t="s">
         <v>244</v>
@@ -3002,7 +3002,7 @@
         <v>46258.63662372685</v>
       </c>
       <c r="S17">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T17" t="s">
         <v>246</v>
@@ -3076,7 +3076,7 @@
         <v>46259.74277608797</v>
       </c>
       <c r="S18">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T18" t="s">
         <v>239</v>
@@ -3153,7 +3153,7 @@
         <v>46258.44838504629</v>
       </c>
       <c r="S19">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T19" t="s">
         <v>247</v>
@@ -3224,7 +3224,7 @@
         <v>46265.43840615741</v>
       </c>
       <c r="S20">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T20" t="s">
         <v>242</v>
@@ -3295,7 +3295,7 @@
         <v>46274.60593387731</v>
       </c>
       <c r="S21">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T21" t="s">
         <v>244</v>
@@ -3366,7 +3366,7 @@
         <v>46273.59003707176</v>
       </c>
       <c r="S22">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T22" t="s">
         <v>248</v>
@@ -3440,7 +3440,7 @@
         <v>46274.47210818287</v>
       </c>
       <c r="S23">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T23" t="s">
         <v>246</v>
@@ -3517,7 +3517,7 @@
         <v>46268.74069754629</v>
       </c>
       <c r="S24">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T24" t="s">
         <v>239</v>
@@ -3594,7 +3594,7 @@
         <v>46276.48975401621</v>
       </c>
       <c r="S25">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T25" t="s">
         <v>240</v>
@@ -3671,7 +3671,7 @@
         <v>46279.38429019676</v>
       </c>
       <c r="S26">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T26" t="s">
         <v>240</v>
@@ -3748,7 +3748,7 @@
         <v>46273.45940115741</v>
       </c>
       <c r="S27">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T27" t="s">
         <v>247</v>
@@ -3822,7 +3822,7 @@
         <v>46274.48792050926</v>
       </c>
       <c r="S28">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T28" t="s">
         <v>245</v>
@@ -3899,7 +3899,7 @@
         <v>46274.588374375</v>
       </c>
       <c r="S29">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T29" t="s">
         <v>241</v>
@@ -3970,7 +3970,7 @@
         <v>46274.34198912037</v>
       </c>
       <c r="S30">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T30" t="s">
         <v>242</v>
@@ -4041,7 +4041,7 @@
         <v>46267.66088636574</v>
       </c>
       <c r="S31">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T31" t="s">
         <v>244</v>
@@ -4112,7 +4112,7 @@
         <v>46268.45922827546</v>
       </c>
       <c r="S32">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T32" t="s">
         <v>246</v>
@@ -4189,7 +4189,7 @@
         <v>46269.59248078704</v>
       </c>
       <c r="S33">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T33" t="s">
         <v>240</v>
@@ -4266,7 +4266,7 @@
         <v>46269.59224453704</v>
       </c>
       <c r="S34">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T34" t="s">
         <v>240</v>
@@ -4343,7 +4343,7 @@
         <v>46268.5891771875</v>
       </c>
       <c r="S35">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T35" t="s">
         <v>247</v>
@@ -4417,7 +4417,7 @@
         <v>46267.64795916666</v>
       </c>
       <c r="S36">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T36" t="s">
         <v>245</v>
@@ -4494,7 +4494,7 @@
         <v>46267.4478849537</v>
       </c>
       <c r="S37">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T37" t="s">
         <v>241</v>
@@ -4568,7 +4568,7 @@
         <v>46269.59056300926</v>
       </c>
       <c r="S38">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T38" t="s">
         <v>242</v>
@@ -4639,7 +4639,7 @@
         <v>46273.67026252315</v>
       </c>
       <c r="S39">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T39" t="s">
         <v>244</v>
@@ -4704,7 +4704,7 @@
         <v>46269.677524375</v>
       </c>
       <c r="S40">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T40" t="s">
         <v>246</v>
@@ -4775,7 +4775,7 @@
         <v>46269.677525</v>
       </c>
       <c r="S41">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T41" t="s">
         <v>240</v>
@@ -4846,7 +4846,7 @@
         <v>46269.677525625</v>
       </c>
       <c r="S42">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T42" t="s">
         <v>240</v>
@@ -4917,7 +4917,7 @@
         <v>46268.58906282407</v>
       </c>
       <c r="S43">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T43" t="s">
         <v>247</v>
@@ -4985,7 +4985,7 @@
         <v>46267.64761306713</v>
       </c>
       <c r="S44">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T44" t="s">
         <v>245</v>
@@ -5059,7 +5059,7 @@
         <v>46273.64957155092</v>
       </c>
       <c r="S45">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T45" t="s">
         <v>241</v>
@@ -5130,7 +5130,7 @@
         <v>46273.39871140046</v>
       </c>
       <c r="S46">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T46" t="s">
         <v>242</v>
@@ -5198,7 +5198,7 @@
         <v>46279.6693627662</v>
       </c>
       <c r="S47">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T47" t="s">
         <v>244</v>
@@ -5269,7 +5269,7 @@
         <v>46279.5886965625</v>
       </c>
       <c r="S48">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T48" t="s">
         <v>246</v>
@@ -5343,7 +5343,7 @@
         <v>46279.40189383102</v>
       </c>
       <c r="S49">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T49" t="s">
         <v>239</v>
@@ -5420,7 +5420,7 @@
         <v>46279.58878520833</v>
       </c>
       <c r="S50">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T50" t="s">
         <v>240</v>
@@ -5497,7 +5497,7 @@
         <v>46279.58873577546</v>
       </c>
       <c r="S51">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T51" t="s">
         <v>240</v>
@@ -5571,7 +5571,7 @@
         <v>46279.63255</v>
       </c>
       <c r="S52">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T52" t="s">
         <v>247</v>
@@ -5642,7 +5642,7 @@
         <v>46276.63187557871</v>
       </c>
       <c r="S53">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T53" t="s">
         <v>245</v>
@@ -5716,7 +5716,7 @@
         <v>46279.6265846875</v>
       </c>
       <c r="S54">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T54" t="s">
         <v>241</v>
@@ -5787,7 +5787,7 @@
         <v>46279.63255401621</v>
       </c>
       <c r="S55">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T55" t="s">
         <v>242</v>
@@ -5858,7 +5858,7 @@
         <v>46265.67124341435</v>
       </c>
       <c r="S56">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T56" t="s">
         <v>244</v>
@@ -5923,7 +5923,7 @@
         <v>46258.64004601852</v>
       </c>
       <c r="S57">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T57" t="s">
         <v>246</v>
@@ -5997,7 +5997,7 @@
         <v>46259.74136743056</v>
       </c>
       <c r="S58">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T58" t="s">
         <v>239</v>
@@ -6074,7 +6074,7 @@
         <v>46258.44623673611</v>
       </c>
       <c r="S59">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T59" t="s">
         <v>247</v>
@@ -6145,7 +6145,7 @@
         <v>46265.4571174537</v>
       </c>
       <c r="S60">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T60" t="s">
         <v>242</v>
@@ -6213,7 +6213,7 @@
         <v>46252.727308125</v>
       </c>
       <c r="S61">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T61" t="s">
         <v>244</v>
@@ -6278,7 +6278,7 @@
         <v>46251.67425219907</v>
       </c>
       <c r="S62">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T62" t="s">
         <v>246</v>
@@ -6349,7 +6349,7 @@
         <v>46251.37122638889</v>
       </c>
       <c r="S63">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T63" t="s">
         <v>239</v>
@@ -6420,7 +6420,7 @@
         <v>46251.67103197917</v>
       </c>
       <c r="S64">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T64" t="s">
         <v>240</v>
@@ -6491,7 +6491,7 @@
         <v>46251.67273518519</v>
       </c>
       <c r="S65">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T65" t="s">
         <v>240</v>
@@ -6562,7 +6562,7 @@
         <v>46246.63098449074</v>
       </c>
       <c r="S66">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T66" t="s">
         <v>245</v>
@@ -6633,7 +6633,7 @@
         <v>46241.44111328704</v>
       </c>
       <c r="S67">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T67" t="s">
         <v>241</v>
@@ -6701,7 +6701,7 @@
         <v>46252.68172707176</v>
       </c>
       <c r="S68">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T68" t="s">
         <v>242</v>
@@ -6772,7 +6772,7 @@
         <v>46267.35832805555</v>
       </c>
       <c r="S69">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T69" t="s">
         <v>246</v>
@@ -6849,7 +6849,7 @@
         <v>46268.71229238426</v>
       </c>
       <c r="S70">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T70" t="s">
         <v>240</v>
@@ -6926,7 +6926,7 @@
         <v>46268.71229297454</v>
       </c>
       <c r="S71">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T71" t="s">
         <v>240</v>
@@ -7003,7 +7003,7 @@
         <v>46267.74532275463</v>
       </c>
       <c r="S72">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T72" t="s">
         <v>247</v>
@@ -7074,7 +7074,7 @@
         <v>46261.36356</v>
       </c>
       <c r="S73">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T73" t="s">
         <v>239</v>
@@ -7148,7 +7148,7 @@
         <v>46269.60160202546</v>
       </c>
       <c r="S74">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T74" t="s">
         <v>244</v>
@@ -7219,7 +7219,7 @@
         <v>46273.64508760416</v>
       </c>
       <c r="S75">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T75" t="s">
         <v>248</v>
@@ -7293,7 +7293,7 @@
         <v>46268.45926839121</v>
       </c>
       <c r="S76">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T76" t="s">
         <v>246</v>
@@ -7370,7 +7370,7 @@
         <v>46269.59250902777</v>
       </c>
       <c r="S77">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T77" t="s">
         <v>240</v>
@@ -7447,7 +7447,7 @@
         <v>46269.5922865625</v>
       </c>
       <c r="S78">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T78" t="s">
         <v>240</v>
@@ -7524,7 +7524,7 @@
         <v>46268.58922707176</v>
       </c>
       <c r="S79">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T79" t="s">
         <v>247</v>
@@ -7598,7 +7598,7 @@
         <v>46267.64800344907</v>
       </c>
       <c r="S80">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T80" t="s">
         <v>245</v>
@@ -7675,7 +7675,7 @@
         <v>46267.44799793982</v>
       </c>
       <c r="S81">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T81" t="s">
         <v>241</v>
@@ -7749,7 +7749,7 @@
         <v>46269.59070487269</v>
       </c>
       <c r="S82">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T82" t="s">
         <v>242</v>
@@ -7823,7 +7823,7 @@
         <v>46269.49635894676</v>
       </c>
       <c r="S83">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T83" t="s">
         <v>246</v>
@@ -7897,7 +7897,7 @@
         <v>46269.63659284722</v>
       </c>
       <c r="S84">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T84" t="s">
         <v>244</v>
@@ -7962,7 +7962,7 @@
         <v>46273.64532122685</v>
       </c>
       <c r="S85">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T85" t="s">
         <v>248</v>
@@ -8030,7 +8030,7 @@
         <v>46268.45929986111</v>
       </c>
       <c r="S86">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T86" t="s">
         <v>246</v>
@@ -8101,7 +8101,7 @@
         <v>46269.5925421875</v>
       </c>
       <c r="S87">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T87" t="s">
         <v>240</v>
@@ -8172,7 +8172,7 @@
         <v>46269.59231454861</v>
       </c>
       <c r="S88">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T88" t="s">
         <v>240</v>
@@ -8243,7 +8243,7 @@
         <v>46268.58932953704</v>
       </c>
       <c r="S89">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T89" t="s">
         <v>247</v>
@@ -8311,7 +8311,7 @@
         <v>46267.648038125</v>
       </c>
       <c r="S90">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T90" t="s">
         <v>245</v>
@@ -8382,7 +8382,7 @@
         <v>46267.44824061343</v>
       </c>
       <c r="S91">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T91" t="s">
         <v>241</v>
@@ -8450,7 +8450,7 @@
         <v>46269.59082328704</v>
       </c>
       <c r="S92">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T92" t="s">
         <v>242</v>
@@ -8518,7 +8518,7 @@
         <v>46275.39631951389</v>
       </c>
       <c r="S93">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T93" t="s">
         <v>240</v>
@@ -8589,7 +8589,7 @@
         <v>46275.39631994213</v>
       </c>
       <c r="S94">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T94" t="s">
         <v>240</v>
@@ -8660,7 +8660,7 @@
         <v>46273.63629708334</v>
       </c>
       <c r="S95">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T95" t="s">
         <v>242</v>
@@ -8728,7 +8728,7 @@
         <v>46273.64318633102</v>
       </c>
       <c r="S96">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T96" t="s">
         <v>242</v>
@@ -8796,7 +8796,7 @@
         <v>46273.64880981482</v>
       </c>
       <c r="S97">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T97" t="s">
         <v>242</v>
@@ -8864,7 +8864,7 @@
         <v>46267.7205502662</v>
       </c>
       <c r="S98">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T98" t="s">
         <v>239</v>
@@ -8935,7 +8935,7 @@
         <v>46267.79439748843</v>
       </c>
       <c r="S99">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T99" t="s">
         <v>240</v>
@@ -9003,7 +9003,7 @@
         <v>46267.79440011574</v>
       </c>
       <c r="S100">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T100" t="s">
         <v>241</v>
@@ -9068,7 +9068,7 @@
         <v>46267.79439818287</v>
       </c>
       <c r="S101">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T101" t="s">
         <v>242</v>
@@ -9133,7 +9133,7 @@
         <v>46267.7202693287</v>
       </c>
       <c r="S102">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T102" t="s">
         <v>239</v>
@@ -9204,7 +9204,7 @@
         <v>46267.79409846065</v>
       </c>
       <c r="S103">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T103" t="s">
         <v>240</v>
@@ -9272,7 +9272,7 @@
         <v>46267.79409725694</v>
       </c>
       <c r="S104">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T104" t="s">
         <v>240</v>
@@ -9340,7 +9340,7 @@
         <v>46267.79410239583</v>
       </c>
       <c r="S105">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T105" t="s">
         <v>241</v>
@@ -9402,7 +9402,7 @@
         <v>46267.79409934028</v>
       </c>
       <c r="S106">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T106" t="s">
         <v>242</v>
@@ -9467,7 +9467,7 @@
         <v>46267.72033356482</v>
       </c>
       <c r="S107">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T107" t="s">
         <v>239</v>
@@ -9538,7 +9538,7 @@
         <v>46267.79418105324</v>
       </c>
       <c r="S108">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T108" t="s">
         <v>240</v>
@@ -9606,7 +9606,7 @@
         <v>46267.79418005787</v>
       </c>
       <c r="S109">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T109" t="s">
         <v>240</v>
@@ -9674,7 +9674,7 @@
         <v>46267.79418379629</v>
       </c>
       <c r="S110">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T110" t="s">
         <v>241</v>
@@ -9736,7 +9736,7 @@
         <v>46267.79418283565</v>
       </c>
       <c r="S111">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T111" t="s">
         <v>242</v>
@@ -9801,7 +9801,7 @@
         <v>46267.71937662037</v>
       </c>
       <c r="S112">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T112" t="s">
         <v>239</v>
@@ -9872,7 +9872,7 @@
         <v>46267.79259834491</v>
       </c>
       <c r="S113">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T113" t="s">
         <v>240</v>
@@ -9940,7 +9940,7 @@
         <v>46267.79260170139</v>
       </c>
       <c r="S114">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T114" t="s">
         <v>242</v>
@@ -10011,7 +10011,7 @@
         <v>46268.37621265047</v>
       </c>
       <c r="S115">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T115" t="s">
         <v>243</v>
@@ -10082,7 +10082,7 @@
         <v>46267.79440636574</v>
       </c>
       <c r="S116">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T116" t="s">
         <v>241</v>
@@ -10147,7 +10147,7 @@
         <v>46267.72037954861</v>
       </c>
       <c r="S117">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T117" t="s">
         <v>239</v>
@@ -10218,7 +10218,7 @@
         <v>46267.79424664352</v>
       </c>
       <c r="S118">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T118" t="s">
         <v>240</v>
@@ -10286,7 +10286,7 @@
         <v>46267.79424586806</v>
       </c>
       <c r="S119">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T119" t="s">
         <v>240</v>
@@ -10354,7 +10354,7 @@
         <v>46267.79424864583</v>
       </c>
       <c r="S120">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T120" t="s">
         <v>241</v>
@@ -10416,7 +10416,7 @@
         <v>46267.79424725694</v>
       </c>
       <c r="S121">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T121" t="s">
         <v>242</v>
@@ -10481,7 +10481,7 @@
         <v>46267.79425081018</v>
       </c>
       <c r="S122">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T122" t="s">
         <v>243</v>
@@ -10549,7 +10549,7 @@
         <v>46267.71942916667</v>
       </c>
       <c r="S123">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T123" t="s">
         <v>239</v>
@@ -10620,7 +10620,7 @@
         <v>46267.79268530093</v>
       </c>
       <c r="S124">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T124" t="s">
         <v>241</v>
@@ -10685,7 +10685,7 @@
         <v>46267.79268769676</v>
       </c>
       <c r="S125">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T125" t="s">
         <v>242</v>
@@ -10753,7 +10753,7 @@
         <v>46267.79249748842</v>
       </c>
       <c r="S126">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T126" t="s">
         <v>241</v>
@@ -10818,7 +10818,7 @@
         <v>46267.79249788194</v>
       </c>
       <c r="S127">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T127" t="s">
         <v>242</v>
@@ -10886,7 +10886,7 @@
         <v>46267.71927280092</v>
       </c>
       <c r="S128">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T128" t="s">
         <v>239</v>
@@ -10957,7 +10957,7 @@
         <v>46267.79251079861</v>
       </c>
       <c r="S129">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T129" t="s">
         <v>241</v>
@@ -11022,7 +11022,7 @@
         <v>46267.79251038194</v>
       </c>
       <c r="S130">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T130" t="s">
         <v>242</v>
@@ -11090,7 +11090,7 @@
         <v>46267.72044811342</v>
       </c>
       <c r="S131">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T131" t="s">
         <v>239</v>
@@ -11161,7 +11161,7 @@
         <v>46267.79429737268</v>
       </c>
       <c r="S132">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T132" t="s">
         <v>240</v>
@@ -11229,7 +11229,7 @@
         <v>46267.79429603009</v>
       </c>
       <c r="S133">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T133" t="s">
         <v>240</v>
@@ -11297,7 +11297,7 @@
         <v>46267.79429876158</v>
       </c>
       <c r="S134">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T134" t="s">
         <v>241</v>
@@ -11359,7 +11359,7 @@
         <v>46267.79429826389</v>
       </c>
       <c r="S135">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T135" t="s">
         <v>242</v>
@@ -11424,7 +11424,7 @@
         <v>46267.72050385417</v>
       </c>
       <c r="S136">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T136" t="s">
         <v>239</v>
@@ -11495,7 +11495,7 @@
         <v>46267.79434996528</v>
       </c>
       <c r="S137">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T137" t="s">
         <v>240</v>
@@ -11563,7 +11563,7 @@
         <v>46267.79434864583</v>
       </c>
       <c r="S138">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T138" t="s">
         <v>240</v>
@@ -11631,7 +11631,7 @@
         <v>46267.79435208334</v>
       </c>
       <c r="S139">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T139" t="s">
         <v>241</v>
@@ -11693,7 +11693,7 @@
         <v>46267.79435100695</v>
       </c>
       <c r="S140">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T140" t="s">
         <v>242</v>
@@ -11761,7 +11761,7 @@
         <v>46280.72961366898</v>
       </c>
       <c r="S141">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T141" t="s">
         <v>240</v>
@@ -11838,7 +11838,7 @@
         <v>46276.66923222222</v>
       </c>
       <c r="S142">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T142" t="s">
         <v>239</v>
@@ -11912,7 +11912,7 @@
         <v>46276.40669469907</v>
       </c>
       <c r="S143">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T143" t="s">
         <v>240</v>
@@ -11983,7 +11983,7 @@
         <v>46276.64773491898</v>
       </c>
       <c r="S144">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T144" t="s">
         <v>240</v>
@@ -12060,7 +12060,7 @@
         <v>46276.39101108797</v>
       </c>
       <c r="S145">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T145" t="s">
         <v>241</v>
@@ -12131,7 +12131,7 @@
         <v>46280.40395534722</v>
       </c>
       <c r="S146">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T146" t="s">
         <v>242</v>
@@ -12202,7 +12202,7 @@
         <v>46279.74982357639</v>
       </c>
       <c r="S147">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T147" t="s">
         <v>243</v>
@@ -12276,7 +12276,7 @@
         <v>46276.66651596065</v>
       </c>
       <c r="S148">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T148" t="s">
         <v>243</v>
@@ -12347,7 +12347,7 @@
         <v>46274.36843923611</v>
       </c>
       <c r="S149">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T149" t="s">
         <v>240</v>
@@ -12421,7 +12421,7 @@
         <v>46273.6788224074</v>
       </c>
       <c r="S150">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T150" t="s">
         <v>242</v>
@@ -12492,7 +12492,7 @@
         <v>46274.66470667824</v>
       </c>
       <c r="S151">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T151" t="s">
         <v>243</v>
@@ -12563,7 +12563,7 @@
         <v>46274.74452168981</v>
       </c>
       <c r="S152">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T152" t="s">
         <v>243</v>
@@ -12637,7 +12637,7 @@
         <v>46274.64801501157</v>
       </c>
       <c r="S153">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T153" t="s">
         <v>239</v>
@@ -12711,7 +12711,7 @@
         <v>46274.36695243056</v>
       </c>
       <c r="S154">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T154" t="s">
         <v>240</v>
@@ -12782,7 +12782,7 @@
         <v>46276.4084265625</v>
       </c>
       <c r="S155">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T155" t="s">
         <v>241</v>
@@ -12853,7 +12853,7 @@
         <v>46273.67943539352</v>
       </c>
       <c r="S156">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T156" t="s">
         <v>242</v>
@@ -12924,7 +12924,7 @@
         <v>46274.7274781713</v>
       </c>
       <c r="S157">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T157" t="s">
         <v>243</v>
@@ -12992,7 +12992,7 @@
         <v>46274.74558746528</v>
       </c>
       <c r="S158">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T158" t="s">
         <v>243</v>
@@ -13060,7 +13060,7 @@
         <v>46275.79245582176</v>
       </c>
       <c r="S159">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T159" t="s">
         <v>242</v>
@@ -13131,7 +13131,7 @@
         <v>46280.63707425926</v>
       </c>
       <c r="S160">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T160" t="s">
         <v>240</v>
@@ -13205,7 +13205,7 @@
         <v>46280.38311703704</v>
       </c>
       <c r="S161">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T161" t="s">
         <v>241</v>
@@ -13276,7 +13276,7 @@
         <v>46280.37743127315</v>
       </c>
       <c r="S162">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T162" t="s">
         <v>242</v>
@@ -13347,7 +13347,7 @@
         <v>46266.37636392361</v>
       </c>
       <c r="S163">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T163" t="s">
         <v>244</v>
@@ -13415,7 +13415,7 @@
         <v>46266.37598834491</v>
       </c>
       <c r="S164">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T164" t="s">
         <v>244</v>
@@ -13486,7 +13486,7 @@
         <v>46268.45899988426</v>
       </c>
       <c r="S165">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T165" t="s">
         <v>246</v>
@@ -13560,7 +13560,7 @@
         <v>46266.45957881944</v>
       </c>
       <c r="S166">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T166" t="s">
         <v>245</v>
@@ -13631,7 +13631,7 @@
         <v>46266.37645462963</v>
       </c>
       <c r="S167">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T167" t="s">
         <v>244</v>
@@ -13699,7 +13699,7 @@
         <v>46266.37649475694</v>
       </c>
       <c r="S168">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T168" t="s">
         <v>244</v>
@@ -13767,7 +13767,7 @@
         <v>46266.37591180555</v>
       </c>
       <c r="S169">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T169" t="s">
         <v>244</v>
@@ -13838,7 +13838,7 @@
         <v>46268.45896508102</v>
       </c>
       <c r="S170">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T170" t="s">
         <v>246</v>
@@ -13912,7 +13912,7 @@
         <v>46266.45946195602</v>
       </c>
       <c r="S171">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T171" t="s">
         <v>245</v>
@@ -13983,7 +13983,7 @@
         <v>46266.37538684028</v>
       </c>
       <c r="S172">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T172" t="s">
         <v>244</v>
@@ -14051,7 +14051,7 @@
         <v>46266.37538506944</v>
       </c>
       <c r="S173">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T173" t="s">
         <v>248</v>
@@ -14122,7 +14122,7 @@
         <v>46268.45881820602</v>
       </c>
       <c r="S174">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T174" t="s">
         <v>246</v>
@@ -14196,7 +14196,7 @@
         <v>46266.45895332176</v>
       </c>
       <c r="S175">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T175" t="s">
         <v>247</v>
@@ -14264,7 +14264,7 @@
         <v>46266.45874105324</v>
       </c>
       <c r="S176">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T176" t="s">
         <v>245</v>
@@ -14335,7 +14335,7 @@
         <v>46266.45873584491</v>
       </c>
       <c r="S177">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T177" t="s">
         <v>245</v>
@@ -14406,7 +14406,7 @@
         <v>46280.45035295139</v>
       </c>
       <c r="S178">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T178" t="s">
         <v>246</v>
@@ -14480,7 +14480,7 @@
         <v>46273.6799675</v>
       </c>
       <c r="S179">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T179" t="s">
         <v>245</v>
@@ -14551,7 +14551,7 @@
         <v>46273.55254606481</v>
       </c>
       <c r="S180">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T180" t="s">
         <v>244</v>
@@ -14619,7 +14619,7 @@
         <v>46273.55252126158</v>
       </c>
       <c r="S181">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T181" t="s">
         <v>248</v>
@@ -14687,7 +14687,7 @@
         <v>46273.55254163194</v>
       </c>
       <c r="S182">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T182" t="s">
         <v>246</v>
@@ -14758,7 +14758,7 @@
         <v>46273.5525440162</v>
       </c>
       <c r="S183">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T183" t="s">
         <v>247</v>
@@ -14826,7 +14826,7 @@
         <v>46273.84422141204</v>
       </c>
       <c r="S184">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T184" t="s">
         <v>245</v>
@@ -14897,7 +14897,7 @@
         <v>46273.55254652778</v>
       </c>
       <c r="S185">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T185" t="s">
         <v>245</v>
@@ -14968,7 +14968,7 @@
         <v>46280.73313407407</v>
       </c>
       <c r="S186">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T186" t="s">
         <v>245</v>
@@ -15039,7 +15039,7 @@
         <v>46276.49596842592</v>
       </c>
       <c r="S187">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T187" t="s">
         <v>244</v>
@@ -15107,7 +15107,7 @@
         <v>46276.53874935185</v>
       </c>
       <c r="S188">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T188" t="s">
         <v>248</v>
@@ -15175,7 +15175,7 @@
         <v>46276.49597027778</v>
       </c>
       <c r="S189">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T189" t="s">
         <v>246</v>
@@ -15246,7 +15246,7 @@
         <v>46276.62604146991</v>
       </c>
       <c r="S190">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T190" t="s">
         <v>247</v>
@@ -15314,7 +15314,7 @@
         <v>46276.68231165509</v>
       </c>
       <c r="S191">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T191" t="s">
         <v>245</v>
@@ -15388,7 +15388,7 @@
         <v>46276.7163278588</v>
       </c>
       <c r="S192">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T192" t="s">
         <v>245</v>
@@ -15459,7 +15459,7 @@
         <v>46276.6823121412</v>
       </c>
       <c r="S193">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T193" t="s">
         <v>245</v>
@@ -15533,7 +15533,7 @@
         <v>46280.69323744213</v>
       </c>
       <c r="S194">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T194" t="s">
         <v>244</v>
@@ -15604,7 +15604,7 @@
         <v>46274.70622837963</v>
       </c>
       <c r="S195">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T195" t="s">
         <v>248</v>
@@ -15672,7 +15672,7 @@
         <v>46275.71996309028</v>
       </c>
       <c r="S196">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T196" t="s">
         <v>247</v>
@@ -15740,7 +15740,7 @@
         <v>46275.54278886574</v>
       </c>
       <c r="S197">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T197" t="s">
         <v>245</v>
@@ -15811,7 +15811,7 @@
         <v>46275.7000328588</v>
       </c>
       <c r="S198">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T198" t="s">
         <v>248</v>
@@ -15879,7 +15879,7 @@
         <v>46275.72031699074</v>
       </c>
       <c r="S199">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T199" t="s">
         <v>246</v>
@@ -15950,7 +15950,7 @@
         <v>46275.54095912037</v>
       </c>
       <c r="S200">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T200" t="s">
         <v>247</v>
@@ -16018,7 +16018,7 @@
         <v>46275.72225363426</v>
       </c>
       <c r="S201">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T201" t="s">
         <v>245</v>
@@ -16089,7 +16089,7 @@
         <v>46275.7222629051</v>
       </c>
       <c r="S202">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T202" t="s">
         <v>245</v>
@@ -16157,7 +16157,7 @@
         <v>46275.7222709838</v>
       </c>
       <c r="S203">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T203" t="s">
         <v>245</v>
@@ -16231,7 +16231,7 @@
         <v>46274.74838096065</v>
       </c>
       <c r="S204">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T204" t="s">
         <v>247</v>
@@ -16305,7 +16305,7 @@
         <v>46268.45898549769</v>
       </c>
       <c r="S205">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T205" t="s">
         <v>246</v>
@@ -16379,7 +16379,7 @@
         <v>46268.45915543981</v>
       </c>
       <c r="S206">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T206" t="s">
         <v>246</v>
@@ -16450,7 +16450,7 @@
         <v>46273.56305208334</v>
       </c>
       <c r="S207">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T207" t="s">
         <v>245</v>
@@ -16521,7 +16521,7 @@
         <v>46280.56274502315</v>
       </c>
       <c r="S208">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T208" t="s">
         <v>245</v>
@@ -16592,7 +16592,7 @@
         <v>46274.42878043981</v>
       </c>
       <c r="S209">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T209" t="s">
         <v>244</v>
@@ -16663,7 +16663,7 @@
         <v>46275.40196778935</v>
       </c>
       <c r="S210">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T210" t="s">
         <v>246</v>
@@ -16737,7 +16737,7 @@
         <v>46267.44505795139</v>
       </c>
       <c r="S211">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T211" t="s">
         <v>245</v>
@@ -16808,7 +16808,7 @@
         <v>46276.52399603009</v>
       </c>
       <c r="S212">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T212" t="s">
         <v>247</v>
@@ -16879,7 +16879,7 @@
         <v>46276.5240703125</v>
       </c>
       <c r="S213">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T213" t="s">
         <v>245</v>
@@ -16950,7 +16950,7 @@
         <v>46275.4100730787</v>
       </c>
       <c r="S214">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T214" t="s">
         <v>242</v>
@@ -17018,7 +17018,7 @@
         <v>46275.40964188657</v>
       </c>
       <c r="S215">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T215" t="s">
         <v>243</v>
@@ -17086,7 +17086,7 @@
         <v>46275.40964245371</v>
       </c>
       <c r="S216">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T216" t="s">
         <v>243</v>
@@ -17154,7 +17154,7 @@
         <v>46275.45011145833</v>
       </c>
       <c r="S217">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T217" t="s">
         <v>239</v>
@@ -17225,7 +17225,7 @@
         <v>46275.44901016204</v>
       </c>
       <c r="S218">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T218" t="s">
         <v>240</v>
@@ -17296,7 +17296,7 @@
         <v>46276.71732053241</v>
       </c>
       <c r="S219">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T219" t="s">
         <v>247</v>
@@ -17367,7 +17367,7 @@
         <v>46276.71697232639</v>
       </c>
       <c r="S220">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T220" t="s">
         <v>245</v>
@@ -17441,7 +17441,7 @@
         <v>46276.7175884838</v>
       </c>
       <c r="S221">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T221" t="s">
         <v>245</v>
@@ -17512,7 +17512,7 @@
         <v>46276.7175895949</v>
       </c>
       <c r="S222">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T222" t="s">
         <v>245</v>
@@ -17586,7 +17586,7 @@
         <v>46276.71759461806</v>
       </c>
       <c r="S223">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T223" t="s">
         <v>241</v>
@@ -17654,7 +17654,7 @@
         <v>46275.44975668981</v>
       </c>
       <c r="S224">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T224" t="s">
         <v>242</v>
@@ -17722,7 +17722,7 @@
         <v>46275.44933692129</v>
       </c>
       <c r="S225">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T225" t="s">
         <v>243</v>
@@ -17790,7 +17790,7 @@
         <v>46275.44933814815</v>
       </c>
       <c r="S226">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T226" t="s">
         <v>243</v>
@@ -17861,7 +17861,7 @@
         <v>46268.62318445602</v>
       </c>
       <c r="S227">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T227" t="s">
         <v>244</v>
@@ -17932,7 +17932,7 @@
         <v>46268.62319864584</v>
       </c>
       <c r="S228">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T228" t="s">
         <v>248</v>
@@ -18003,7 +18003,7 @@
         <v>46268.62320026621</v>
       </c>
       <c r="S229">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T229" t="s">
         <v>246</v>
@@ -18077,7 +18077,7 @@
         <v>46268.62320177083</v>
       </c>
       <c r="S230">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T230" t="s">
         <v>239</v>
@@ -18151,7 +18151,7 @@
         <v>46268.62320378472</v>
       </c>
       <c r="S231">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T231" t="s">
         <v>240</v>
@@ -18225,7 +18225,7 @@
         <v>46268.62320393518</v>
       </c>
       <c r="S232">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T232" t="s">
         <v>240</v>
@@ -18299,7 +18299,7 @@
         <v>46268.62320697917</v>
       </c>
       <c r="S233">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T233" t="s">
         <v>247</v>
@@ -18370,7 +18370,7 @@
         <v>46268.62320717592</v>
       </c>
       <c r="S234">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T234" t="s">
         <v>245</v>
@@ -18444,7 +18444,7 @@
         <v>46268.62320732639</v>
       </c>
       <c r="S235">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T235" t="s">
         <v>245</v>
@@ -18515,7 +18515,7 @@
         <v>46268.62320810185</v>
       </c>
       <c r="S236">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T236" t="s">
         <v>245</v>
@@ -18589,7 +18589,7 @@
         <v>46268.6232125</v>
       </c>
       <c r="S237">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T237" t="s">
         <v>241</v>
@@ -18660,7 +18660,7 @@
         <v>46268.62321412037</v>
       </c>
       <c r="S238">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T238" t="s">
         <v>242</v>
@@ -18731,7 +18731,7 @@
         <v>46268.6232128125</v>
       </c>
       <c r="S239">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T239" t="s">
         <v>243</v>
@@ -18802,7 +18802,7 @@
         <v>46268.62321296296</v>
       </c>
       <c r="S240">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T240" t="s">
         <v>243</v>
@@ -18870,7 +18870,7 @@
         <v>46269.41908927084</v>
       </c>
       <c r="S241">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T241" t="s">
         <v>244</v>
@@ -18935,7 +18935,7 @@
         <v>46269.41910457176</v>
       </c>
       <c r="S242">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T242" t="s">
         <v>248</v>
@@ -19000,7 +19000,7 @@
         <v>46269.37885223379</v>
       </c>
       <c r="S243">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T243" t="s">
         <v>246</v>
@@ -19068,7 +19068,7 @@
         <v>46269.3782503125</v>
       </c>
       <c r="S244">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T244" t="s">
         <v>239</v>
@@ -19136,7 +19136,7 @@
         <v>46269.41913152778</v>
       </c>
       <c r="S245">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T245" t="s">
         <v>240</v>
@@ -19204,7 +19204,7 @@
         <v>46269.41913775463</v>
       </c>
       <c r="S246">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T246" t="s">
         <v>240</v>
@@ -19272,7 +19272,7 @@
         <v>46274.41771849537</v>
       </c>
       <c r="S247">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T247" t="s">
         <v>247</v>
@@ -19337,7 +19337,7 @@
         <v>46274.41775447917</v>
       </c>
       <c r="S248">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T248" t="s">
         <v>245</v>
@@ -19405,7 +19405,7 @@
         <v>46274.41777533565</v>
       </c>
       <c r="S249">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T249" t="s">
         <v>245</v>
@@ -19470,7 +19470,7 @@
         <v>46274.41799166667</v>
       </c>
       <c r="S250">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T250" t="s">
         <v>241</v>
@@ -19535,7 +19535,7 @@
         <v>46274.41800114583</v>
       </c>
       <c r="S251">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T251" t="s">
         <v>242</v>
@@ -19600,7 +19600,7 @@
         <v>46248.68263490741</v>
       </c>
       <c r="S252">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T252" t="s">
         <v>244</v>
@@ -19665,7 +19665,7 @@
         <v>46248.68265498843</v>
       </c>
       <c r="S253">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T253" t="s">
         <v>248</v>
@@ -19730,7 +19730,7 @@
         <v>46248.682663125</v>
       </c>
       <c r="S254">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T254" t="s">
         <v>246</v>
@@ -19798,7 +19798,7 @@
         <v>46248.68266583333</v>
       </c>
       <c r="S255">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T255" t="s">
         <v>240</v>
@@ -19866,7 +19866,7 @@
         <v>46248.68266673611</v>
       </c>
       <c r="S256">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T256" t="s">
         <v>245</v>
@@ -19934,7 +19934,7 @@
         <v>46248.68266710648</v>
       </c>
       <c r="S257">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T257" t="s">
         <v>245</v>
@@ -19999,7 +19999,7 @@
         <v>46248.68267306713</v>
       </c>
       <c r="S258">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T258" t="s">
         <v>241</v>
@@ -20064,7 +20064,7 @@
         <v>46268.7596207176</v>
       </c>
       <c r="S259">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T259" t="s">
         <v>244</v>
@@ -20129,7 +20129,7 @@
         <v>46268.75963109954</v>
       </c>
       <c r="S260">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T260" t="s">
         <v>248</v>
@@ -20194,7 +20194,7 @@
         <v>46268.75963225694</v>
       </c>
       <c r="S261">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T261" t="s">
         <v>246</v>
@@ -20262,7 +20262,7 @@
         <v>46268.75963348379</v>
       </c>
       <c r="S262">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T262" t="s">
         <v>239</v>
@@ -20330,7 +20330,7 @@
         <v>46268.75963414352</v>
       </c>
       <c r="S263">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T263" t="s">
         <v>240</v>
@@ -20398,7 +20398,7 @@
         <v>46268.62326365741</v>
       </c>
       <c r="S264">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T264" t="s">
         <v>240</v>
@@ -20466,7 +20466,7 @@
         <v>46268.75963472222</v>
       </c>
       <c r="S265">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T265" t="s">
         <v>247</v>
@@ -20531,7 +20531,7 @@
         <v>46268.75963475694</v>
       </c>
       <c r="S266">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T266" t="s">
         <v>245</v>
@@ -20599,7 +20599,7 @@
         <v>46268.75963506944</v>
       </c>
       <c r="S267">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T267" t="s">
         <v>245</v>
@@ -20664,7 +20664,7 @@
         <v>46268.7596360301</v>
       </c>
       <c r="S268">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T268" t="s">
         <v>245</v>
@@ -20732,7 +20732,7 @@
         <v>46268.62327121528</v>
       </c>
       <c r="S269">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T269" t="s">
         <v>241</v>
@@ -20797,7 +20797,7 @@
         <v>46268.75963931713</v>
       </c>
       <c r="S270">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T270" t="s">
         <v>242</v>
@@ -20862,7 +20862,7 @@
         <v>46268.75963822917</v>
       </c>
       <c r="S271">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T271" t="s">
         <v>243</v>
@@ -20927,7 +20927,7 @@
         <v>46268.75963857639</v>
       </c>
       <c r="S272">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T272" t="s">
         <v>243</v>
@@ -20992,7 +20992,7 @@
         <v>46269.41908901621</v>
       </c>
       <c r="S273">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T273" t="s">
         <v>244</v>
@@ -21057,7 +21057,7 @@
         <v>46269.41910425926</v>
       </c>
       <c r="S274">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T274" t="s">
         <v>248</v>
@@ -21122,7 +21122,7 @@
         <v>46269.37890997685</v>
       </c>
       <c r="S275">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T275" t="s">
         <v>246</v>
@@ -21190,7 +21190,7 @@
         <v>46269.37833320602</v>
       </c>
       <c r="S276">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T276" t="s">
         <v>239</v>
@@ -21258,7 +21258,7 @@
         <v>46269.41913112268</v>
       </c>
       <c r="S277">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T277" t="s">
         <v>240</v>
@@ -21326,7 +21326,7 @@
         <v>46269.41913740741</v>
       </c>
       <c r="S278">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T278" t="s">
         <v>240</v>
@@ -21394,7 +21394,7 @@
         <v>46274.41772148148</v>
       </c>
       <c r="S279">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T279" t="s">
         <v>247</v>
@@ -21459,7 +21459,7 @@
         <v>46274.41773631945</v>
       </c>
       <c r="S280">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T280" t="s">
         <v>245</v>
@@ -21527,7 +21527,7 @@
         <v>46274.41777481481</v>
       </c>
       <c r="S281">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T281" t="s">
         <v>245</v>
@@ -21592,7 +21592,7 @@
         <v>46274.41799332176</v>
       </c>
       <c r="S282">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T282" t="s">
         <v>241</v>
@@ -21657,7 +21657,7 @@
         <v>46274.41800085648</v>
       </c>
       <c r="S283">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T283" t="s">
         <v>242</v>
@@ -21722,7 +21722,7 @@
         <v>46275.31737530093</v>
       </c>
       <c r="S284">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T284" t="s">
         <v>244</v>
@@ -21787,7 +21787,7 @@
         <v>46275.31747032407</v>
       </c>
       <c r="S285">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T285" t="s">
         <v>248</v>
@@ -21852,7 +21852,7 @@
         <v>46275.31747981482</v>
       </c>
       <c r="S286">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T286" t="s">
         <v>246</v>
@@ -21920,7 +21920,7 @@
         <v>46275.31748724537</v>
       </c>
       <c r="S287">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T287" t="s">
         <v>239</v>
@@ -21988,7 +21988,7 @@
         <v>46275.31749535879</v>
       </c>
       <c r="S288">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T288" t="s">
         <v>240</v>
@@ -22056,7 +22056,7 @@
         <v>46275.31750491898</v>
       </c>
       <c r="S289">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T289" t="s">
         <v>247</v>
@@ -22121,7 +22121,7 @@
         <v>46275.31750555555</v>
       </c>
       <c r="S290">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T290" t="s">
         <v>245</v>
@@ -22189,7 +22189,7 @@
         <v>46275.31750599537</v>
       </c>
       <c r="S291">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T291" t="s">
         <v>245</v>
@@ -22254,7 +22254,7 @@
         <v>46276.41675075232</v>
       </c>
       <c r="S292">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T292" t="s">
         <v>240</v>
@@ -22325,7 +22325,7 @@
         <v>46269.46753030093</v>
       </c>
       <c r="S293">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T293" t="s">
         <v>241</v>
@@ -22393,7 +22393,7 @@
         <v>237</v>
       </c>
       <c r="S294">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T294" t="s">
         <v>242</v>
@@ -22461,7 +22461,7 @@
         <v>237</v>
       </c>
       <c r="S295">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T295" t="s">
         <v>242</v>
@@ -22529,7 +22529,7 @@
         <v>237</v>
       </c>
       <c r="S296">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T296" t="s">
         <v>241</v>
@@ -22549,10 +22549,10 @@
     </row>
     <row r="297" spans="1:34">
       <c r="A297">
-        <v>6627</v>
+        <v>6949</v>
       </c>
       <c r="B297" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C297" t="s">
         <v>58</v>
@@ -22561,49 +22561,46 @@
         <v>59</v>
       </c>
       <c r="E297" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F297" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G297">
-        <v>7869</v>
+        <v>1882</v>
       </c>
       <c r="H297">
         <v>0</v>
       </c>
       <c r="I297" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="J297" t="s">
         <v>134</v>
       </c>
       <c r="L297" s="1">
-        <v>46293</v>
+        <v>46287</v>
       </c>
       <c r="M297" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N297" t="s">
         <v>203</v>
       </c>
       <c r="O297">
-        <v>17042546</v>
+        <v>18214871</v>
       </c>
       <c r="P297" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="Q297" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="S297">
-        <v>-6</v>
+        <v>1</v>
       </c>
       <c r="T297" t="s">
-        <v>240</v>
-      </c>
-      <c r="V297" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="W297" t="s">
         <v>342</v>
@@ -22612,89 +22609,86 @@
         <v>0</v>
       </c>
       <c r="AG297" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AH297" t="s">
-        <v>461</v>
+        <v>450</v>
       </c>
     </row>
     <row r="298" spans="1:34">
       <c r="A298">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B298" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C298" t="s">
         <v>58</v>
       </c>
       <c r="D298" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E298" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F298" t="s">
         <v>64</v>
       </c>
       <c r="G298">
-        <v>7869</v>
+        <v>1807</v>
       </c>
       <c r="H298">
         <v>0</v>
       </c>
       <c r="I298" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="J298" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L298" s="1">
-        <v>46293</v>
+        <v>46287</v>
       </c>
       <c r="M298" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N298" t="s">
         <v>203</v>
       </c>
       <c r="O298">
-        <v>16960048</v>
+        <v>17948806</v>
       </c>
       <c r="P298" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="Q298" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="S298">
-        <v>-6</v>
+        <v>1</v>
       </c>
       <c r="T298" t="s">
-        <v>240</v>
-      </c>
-      <c r="V298" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="W298" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AA298">
         <v>0</v>
       </c>
       <c r="AG298" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AH298" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="299" spans="1:34">
       <c r="A299">
-        <v>6949</v>
+        <v>6704</v>
       </c>
       <c r="B299" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C299" t="s">
         <v>58</v>
@@ -22706,63 +22700,66 @@
         <v>62</v>
       </c>
       <c r="F299" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G299">
-        <v>7869</v>
+        <v>1808</v>
       </c>
       <c r="H299">
         <v>0</v>
       </c>
       <c r="I299" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="J299" t="s">
         <v>134</v>
       </c>
       <c r="L299" s="1">
-        <v>46293</v>
+        <v>46287</v>
       </c>
       <c r="M299" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N299" t="s">
         <v>203</v>
       </c>
       <c r="O299">
-        <v>18178300</v>
+        <v>18085209</v>
       </c>
       <c r="P299" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="Q299" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="S299">
-        <v>-6</v>
+        <v>1</v>
       </c>
       <c r="T299" t="s">
-        <v>242</v>
+        <v>245</v>
+      </c>
+      <c r="V299" t="s">
+        <v>255</v>
       </c>
       <c r="W299" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AA299">
         <v>0</v>
       </c>
       <c r="AG299" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AH299" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
     </row>
     <row r="300" spans="1:34">
       <c r="A300">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B300" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C300" t="s">
         <v>58</v>
@@ -22771,13 +22768,13 @@
         <v>59</v>
       </c>
       <c r="E300" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F300" t="s">
         <v>64</v>
       </c>
       <c r="G300">
-        <v>6892</v>
+        <v>7869</v>
       </c>
       <c r="H300">
         <v>0</v>
@@ -22786,60 +22783,60 @@
         <v>67</v>
       </c>
       <c r="J300" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L300" s="1">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="M300" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N300" t="s">
         <v>203</v>
       </c>
       <c r="O300">
-        <v>17968017</v>
+        <v>17042546</v>
       </c>
       <c r="P300" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q300" t="s">
         <v>238</v>
       </c>
       <c r="S300">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="T300" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="V300" t="s">
         <v>255</v>
       </c>
       <c r="W300" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AA300">
         <v>0</v>
       </c>
       <c r="AG300" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AH300" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="301" spans="1:34">
       <c r="A301">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B301" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C301" t="s">
         <v>58</v>
       </c>
       <c r="D301" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E301" t="s">
         <v>63</v>
@@ -22848,7 +22845,7 @@
         <v>64</v>
       </c>
       <c r="G301">
-        <v>6892</v>
+        <v>7869</v>
       </c>
       <c r="H301">
         <v>0</v>
@@ -22857,19 +22854,19 @@
         <v>67</v>
       </c>
       <c r="J301" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L301" s="1">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="M301" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N301" t="s">
         <v>203</v>
       </c>
       <c r="O301">
-        <v>17042486</v>
+        <v>16960048</v>
       </c>
       <c r="P301" t="s">
         <v>209</v>
@@ -22878,7 +22875,7 @@
         <v>238</v>
       </c>
       <c r="S301">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="T301" t="s">
         <v>240</v>
@@ -22887,13 +22884,13 @@
         <v>255</v>
       </c>
       <c r="W301" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AA301">
         <v>0</v>
       </c>
       <c r="AG301" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AH301" t="s">
         <v>461</v>
@@ -22901,25 +22898,25 @@
     </row>
     <row r="302" spans="1:34">
       <c r="A302">
-        <v>6628</v>
+        <v>6949</v>
       </c>
       <c r="B302" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C302" t="s">
         <v>58</v>
       </c>
       <c r="D302" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E302" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F302" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G302">
-        <v>6892</v>
+        <v>7869</v>
       </c>
       <c r="H302">
         <v>0</v>
@@ -22928,66 +22925,63 @@
         <v>67</v>
       </c>
       <c r="J302" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L302" s="1">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="M302" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N302" t="s">
         <v>203</v>
       </c>
       <c r="O302">
-        <v>16960024</v>
+        <v>18178300</v>
       </c>
       <c r="P302" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Q302" t="s">
         <v>238</v>
       </c>
       <c r="S302">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="T302" t="s">
-        <v>240</v>
-      </c>
-      <c r="V302" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="W302" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AA302">
         <v>0</v>
       </c>
       <c r="AG302" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AH302" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="303" spans="1:34">
       <c r="A303">
-        <v>6945</v>
+        <v>6548</v>
       </c>
       <c r="B303" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C303" t="s">
         <v>58</v>
       </c>
       <c r="D303" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E303" t="s">
         <v>62</v>
       </c>
       <c r="F303" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G303">
         <v>6892</v>
@@ -22999,34 +22993,37 @@
         <v>67</v>
       </c>
       <c r="J303" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L303" s="1">
         <v>46290</v>
       </c>
       <c r="M303" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N303" t="s">
         <v>203</v>
       </c>
       <c r="O303">
-        <v>18163676</v>
+        <v>17968017</v>
       </c>
       <c r="P303" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Q303" t="s">
         <v>238</v>
       </c>
       <c r="S303">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T303" t="s">
-        <v>241</v>
+        <v>239</v>
+      </c>
+      <c r="V303" t="s">
+        <v>255</v>
       </c>
       <c r="W303" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AA303">
         <v>0</v>
@@ -23035,15 +23032,15 @@
         <v>459</v>
       </c>
       <c r="AH303" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="304" spans="1:34">
       <c r="A304">
-        <v>6949</v>
+        <v>6627</v>
       </c>
       <c r="B304" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C304" t="s">
         <v>58</v>
@@ -23052,10 +23049,10 @@
         <v>59</v>
       </c>
       <c r="E304" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F304" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G304">
         <v>6892</v>
@@ -23067,7 +23064,7 @@
         <v>67</v>
       </c>
       <c r="J304" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L304" s="1">
         <v>46290</v>
@@ -23079,22 +23076,25 @@
         <v>203</v>
       </c>
       <c r="O304">
-        <v>18178288</v>
+        <v>17042486</v>
       </c>
       <c r="P304" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q304" t="s">
         <v>238</v>
       </c>
       <c r="S304">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T304" t="s">
-        <v>242</v>
+        <v>240</v>
+      </c>
+      <c r="V304" t="s">
+        <v>255</v>
       </c>
       <c r="W304" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AA304">
         <v>0</v>
@@ -23103,27 +23103,27 @@
         <v>459</v>
       </c>
       <c r="AH304" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="305" spans="1:34">
       <c r="A305">
-        <v>6962</v>
+        <v>6628</v>
       </c>
       <c r="B305" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C305" t="s">
         <v>58</v>
       </c>
       <c r="D305" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E305" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F305" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G305">
         <v>6892</v>
@@ -23135,7 +23135,7 @@
         <v>67</v>
       </c>
       <c r="J305" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L305" s="1">
         <v>46290</v>
@@ -23147,22 +23147,25 @@
         <v>203</v>
       </c>
       <c r="O305">
-        <v>18187955</v>
+        <v>16960024</v>
       </c>
       <c r="P305" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="Q305" t="s">
         <v>238</v>
       </c>
       <c r="S305">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T305" t="s">
-        <v>243</v>
+        <v>240</v>
+      </c>
+      <c r="V305" t="s">
+        <v>255</v>
       </c>
       <c r="W305" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AA305">
         <v>0</v>
@@ -23176,16 +23179,16 @@
     </row>
     <row r="306" spans="1:34">
       <c r="A306">
-        <v>6963</v>
+        <v>6945</v>
       </c>
       <c r="B306" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C306" t="s">
         <v>58</v>
       </c>
       <c r="D306" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E306" t="s">
         <v>62</v>
@@ -23203,34 +23206,34 @@
         <v>67</v>
       </c>
       <c r="J306" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L306" s="1">
         <v>46290</v>
       </c>
       <c r="M306" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N306" t="s">
         <v>203</v>
       </c>
       <c r="O306">
-        <v>18187893</v>
+        <v>18163676</v>
       </c>
       <c r="P306" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q306" t="s">
         <v>238</v>
       </c>
       <c r="S306">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T306" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="W306" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="AA306">
         <v>0</v>
@@ -23244,10 +23247,10 @@
     </row>
     <row r="307" spans="1:34">
       <c r="A307">
-        <v>6548</v>
+        <v>6949</v>
       </c>
       <c r="B307" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C307" t="s">
         <v>58</v>
@@ -23259,10 +23262,10 @@
         <v>62</v>
       </c>
       <c r="F307" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G307">
-        <v>11516</v>
+        <v>6892</v>
       </c>
       <c r="H307">
         <v>0</v>
@@ -23271,7 +23274,7 @@
         <v>67</v>
       </c>
       <c r="J307" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L307" s="1">
         <v>46290</v>
@@ -23283,7 +23286,7 @@
         <v>203</v>
       </c>
       <c r="O307">
-        <v>17968053</v>
+        <v>18178288</v>
       </c>
       <c r="P307" t="s">
         <v>208</v>
@@ -23292,16 +23295,13 @@
         <v>238</v>
       </c>
       <c r="S307">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T307" t="s">
-        <v>239</v>
-      </c>
-      <c r="V307" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="W307" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AA307">
         <v>0</v>
@@ -23315,25 +23315,25 @@
     </row>
     <row r="308" spans="1:34">
       <c r="A308">
-        <v>6627</v>
+        <v>6962</v>
       </c>
       <c r="B308" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C308" t="s">
         <v>58</v>
       </c>
       <c r="D308" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E308" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F308" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G308">
-        <v>11516</v>
+        <v>6892</v>
       </c>
       <c r="H308">
         <v>0</v>
@@ -23342,7 +23342,7 @@
         <v>67</v>
       </c>
       <c r="J308" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L308" s="1">
         <v>46290</v>
@@ -23354,25 +23354,22 @@
         <v>203</v>
       </c>
       <c r="O308">
-        <v>17042662</v>
+        <v>18187955</v>
       </c>
       <c r="P308" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q308" t="s">
         <v>238</v>
       </c>
       <c r="S308">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T308" t="s">
-        <v>240</v>
-      </c>
-      <c r="V308" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="W308" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AA308">
         <v>0</v>
@@ -23386,16 +23383,16 @@
     </row>
     <row r="309" spans="1:34">
       <c r="A309">
-        <v>6949</v>
+        <v>6963</v>
       </c>
       <c r="B309" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C309" t="s">
         <v>58</v>
       </c>
       <c r="D309" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E309" t="s">
         <v>62</v>
@@ -23404,7 +23401,7 @@
         <v>65</v>
       </c>
       <c r="G309">
-        <v>11516</v>
+        <v>6892</v>
       </c>
       <c r="H309">
         <v>0</v>
@@ -23413,7 +23410,7 @@
         <v>67</v>
       </c>
       <c r="J309" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L309" s="1">
         <v>46290</v>
@@ -23425,22 +23422,22 @@
         <v>203</v>
       </c>
       <c r="O309">
-        <v>18178314</v>
+        <v>18187893</v>
       </c>
       <c r="P309" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q309" t="s">
         <v>238</v>
       </c>
       <c r="S309">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T309" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="W309" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AA309">
         <v>0</v>
@@ -23449,27 +23446,27 @@
         <v>459</v>
       </c>
       <c r="AH309" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="310" spans="1:34">
       <c r="A310">
-        <v>6962</v>
+        <v>6548</v>
       </c>
       <c r="B310" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C310" t="s">
         <v>58</v>
       </c>
       <c r="D310" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E310" t="s">
         <v>62</v>
       </c>
       <c r="F310" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G310">
         <v>11516</v>
@@ -23481,7 +23478,7 @@
         <v>67</v>
       </c>
       <c r="J310" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L310" s="1">
         <v>46290</v>
@@ -23493,22 +23490,25 @@
         <v>203</v>
       </c>
       <c r="O310">
-        <v>18187985</v>
+        <v>17968053</v>
       </c>
       <c r="P310" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="Q310" t="s">
         <v>238</v>
       </c>
       <c r="S310">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T310" t="s">
-        <v>243</v>
+        <v>239</v>
+      </c>
+      <c r="V310" t="s">
+        <v>255</v>
       </c>
       <c r="W310" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AA310">
         <v>0</v>
@@ -23517,27 +23517,27 @@
         <v>459</v>
       </c>
       <c r="AH310" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="311" spans="1:34">
       <c r="A311">
-        <v>6963</v>
+        <v>6627</v>
       </c>
       <c r="B311" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C311" t="s">
         <v>58</v>
       </c>
       <c r="D311" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E311" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F311" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G311">
         <v>11516</v>
@@ -23549,7 +23549,7 @@
         <v>67</v>
       </c>
       <c r="J311" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L311" s="1">
         <v>46290</v>
@@ -23561,22 +23561,25 @@
         <v>203</v>
       </c>
       <c r="O311">
-        <v>18241255</v>
+        <v>17042662</v>
       </c>
       <c r="P311" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="Q311" t="s">
         <v>238</v>
       </c>
       <c r="S311">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T311" t="s">
-        <v>243</v>
+        <v>240</v>
+      </c>
+      <c r="V311" t="s">
+        <v>255</v>
       </c>
       <c r="W311" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AA311">
         <v>0</v>
@@ -23590,16 +23593,16 @@
     </row>
     <row r="312" spans="1:34">
       <c r="A312">
-        <v>6962</v>
+        <v>6949</v>
       </c>
       <c r="B312" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C312" t="s">
         <v>58</v>
       </c>
       <c r="D312" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E312" t="s">
         <v>62</v>
@@ -23608,7 +23611,7 @@
         <v>65</v>
       </c>
       <c r="G312">
-        <v>10992</v>
+        <v>11516</v>
       </c>
       <c r="H312">
         <v>0</v>
@@ -23617,51 +23620,51 @@
         <v>67</v>
       </c>
       <c r="J312" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L312" s="1">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="M312" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N312" t="s">
         <v>203</v>
       </c>
       <c r="O312">
-        <v>18249084</v>
+        <v>18178314</v>
       </c>
       <c r="P312" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="Q312" t="s">
         <v>238</v>
       </c>
       <c r="S312">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="T312" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="W312" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AA312">
         <v>0</v>
       </c>
       <c r="AG312" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AH312" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="313" spans="1:34">
       <c r="A313">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B313" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C313" t="s">
         <v>58</v>
@@ -23676,7 +23679,7 @@
         <v>65</v>
       </c>
       <c r="G313">
-        <v>10992</v>
+        <v>11516</v>
       </c>
       <c r="H313">
         <v>0</v>
@@ -23685,19 +23688,19 @@
         <v>67</v>
       </c>
       <c r="J313" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L313" s="1">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="M313" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N313" t="s">
         <v>203</v>
       </c>
       <c r="O313">
-        <v>18249092</v>
+        <v>18187985</v>
       </c>
       <c r="P313" t="s">
         <v>211</v>
@@ -23706,19 +23709,19 @@
         <v>238</v>
       </c>
       <c r="S313">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="T313" t="s">
         <v>243</v>
       </c>
       <c r="W313" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AA313">
         <v>0</v>
       </c>
       <c r="AG313" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AH313" t="s">
         <v>461</v>
@@ -23726,25 +23729,25 @@
     </row>
     <row r="314" spans="1:34">
       <c r="A314">
-        <v>6548</v>
+        <v>6963</v>
       </c>
       <c r="B314" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C314" t="s">
         <v>58</v>
       </c>
       <c r="D314" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E314" t="s">
         <v>62</v>
       </c>
       <c r="F314" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G314">
-        <v>7875</v>
+        <v>11516</v>
       </c>
       <c r="H314">
         <v>0</v>
@@ -23756,66 +23759,63 @@
         <v>138</v>
       </c>
       <c r="L314" s="1">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="M314" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N314" t="s">
         <v>203</v>
       </c>
       <c r="O314">
-        <v>18096234</v>
+        <v>18241255</v>
       </c>
       <c r="P314" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q314" t="s">
         <v>238</v>
       </c>
       <c r="S314">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="T314" t="s">
-        <v>239</v>
-      </c>
-      <c r="V314" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="W314" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AA314">
         <v>0</v>
       </c>
       <c r="AG314" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AH314" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="315" spans="1:34">
       <c r="A315">
-        <v>6627</v>
+        <v>6962</v>
       </c>
       <c r="B315" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C315" t="s">
         <v>58</v>
       </c>
       <c r="D315" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E315" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F315" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G315">
-        <v>7875</v>
+        <v>10992</v>
       </c>
       <c r="H315">
         <v>0</v>
@@ -23824,7 +23824,7 @@
         <v>67</v>
       </c>
       <c r="J315" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L315" s="1">
         <v>46295</v>
@@ -23836,25 +23836,22 @@
         <v>203</v>
       </c>
       <c r="O315">
-        <v>18096487</v>
+        <v>18249084</v>
       </c>
       <c r="P315" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q315" t="s">
         <v>238</v>
       </c>
       <c r="S315">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="T315" t="s">
-        <v>240</v>
-      </c>
-      <c r="V315" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="W315" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="AA315">
         <v>0</v>
@@ -23868,16 +23865,16 @@
     </row>
     <row r="316" spans="1:34">
       <c r="A316">
-        <v>6949</v>
+        <v>6963</v>
       </c>
       <c r="B316" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C316" t="s">
         <v>58</v>
       </c>
       <c r="D316" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E316" t="s">
         <v>62</v>
@@ -23886,7 +23883,7 @@
         <v>65</v>
       </c>
       <c r="G316">
-        <v>7875</v>
+        <v>10992</v>
       </c>
       <c r="H316">
         <v>0</v>
@@ -23895,7 +23892,7 @@
         <v>67</v>
       </c>
       <c r="J316" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L316" s="1">
         <v>46295</v>
@@ -23907,22 +23904,22 @@
         <v>203</v>
       </c>
       <c r="O316">
-        <v>18254144</v>
+        <v>18249092</v>
       </c>
       <c r="P316" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q316" t="s">
         <v>238</v>
       </c>
       <c r="S316">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="T316" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="W316" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="AA316">
         <v>0</v>
@@ -23931,27 +23928,27 @@
         <v>457</v>
       </c>
       <c r="AH316" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="317" spans="1:34">
       <c r="A317">
-        <v>6962</v>
+        <v>6548</v>
       </c>
       <c r="B317" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C317" t="s">
         <v>58</v>
       </c>
       <c r="D317" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E317" t="s">
         <v>62</v>
       </c>
       <c r="F317" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G317">
         <v>7875</v>
@@ -23963,7 +23960,7 @@
         <v>67</v>
       </c>
       <c r="J317" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L317" s="1">
         <v>46295</v>
@@ -23975,22 +23972,25 @@
         <v>203</v>
       </c>
       <c r="O317">
-        <v>18200037</v>
+        <v>18096234</v>
       </c>
       <c r="P317" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="Q317" t="s">
         <v>238</v>
       </c>
       <c r="S317">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="T317" t="s">
-        <v>243</v>
+        <v>239</v>
+      </c>
+      <c r="V317" t="s">
+        <v>255</v>
       </c>
       <c r="W317" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="AA317">
         <v>0</v>
@@ -23999,27 +23999,27 @@
         <v>457</v>
       </c>
       <c r="AH317" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="318" spans="1:34">
       <c r="A318">
-        <v>6963</v>
+        <v>6627</v>
       </c>
       <c r="B318" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C318" t="s">
         <v>58</v>
       </c>
       <c r="D318" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E318" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F318" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G318">
         <v>7875</v>
@@ -24031,7 +24031,7 @@
         <v>67</v>
       </c>
       <c r="J318" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L318" s="1">
         <v>46295</v>
@@ -24043,22 +24043,25 @@
         <v>203</v>
       </c>
       <c r="O318">
-        <v>18200056</v>
+        <v>18096487</v>
       </c>
       <c r="P318" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="Q318" t="s">
         <v>238</v>
       </c>
       <c r="S318">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="T318" t="s">
-        <v>243</v>
+        <v>240</v>
+      </c>
+      <c r="V318" t="s">
+        <v>255</v>
       </c>
       <c r="W318" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="AA318">
         <v>0</v>
@@ -24072,25 +24075,25 @@
     </row>
     <row r="319" spans="1:34">
       <c r="A319">
-        <v>6628</v>
+        <v>6949</v>
       </c>
       <c r="B319" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C319" t="s">
         <v>58</v>
       </c>
       <c r="D319" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E319" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F319" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G319">
-        <v>9764</v>
+        <v>7875</v>
       </c>
       <c r="H319">
         <v>0</v>
@@ -24099,7 +24102,7 @@
         <v>67</v>
       </c>
       <c r="J319" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L319" s="1">
         <v>46295</v>
@@ -24111,25 +24114,22 @@
         <v>203</v>
       </c>
       <c r="O319">
-        <v>18096422</v>
+        <v>18254144</v>
       </c>
       <c r="P319" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Q319" t="s">
         <v>238</v>
       </c>
       <c r="S319">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="T319" t="s">
-        <v>240</v>
-      </c>
-      <c r="V319" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="W319" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="AA319">
         <v>0</v>
@@ -24138,21 +24138,21 @@
         <v>457</v>
       </c>
       <c r="AH319" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="320" spans="1:34">
       <c r="A320">
-        <v>6945</v>
+        <v>6962</v>
       </c>
       <c r="B320" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C320" t="s">
         <v>58</v>
       </c>
       <c r="D320" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E320" t="s">
         <v>62</v>
@@ -24161,7 +24161,7 @@
         <v>65</v>
       </c>
       <c r="G320">
-        <v>9764</v>
+        <v>7875</v>
       </c>
       <c r="H320">
         <v>0</v>
@@ -24170,7 +24170,7 @@
         <v>67</v>
       </c>
       <c r="J320" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L320" s="1">
         <v>46295</v>
@@ -24182,22 +24182,22 @@
         <v>203</v>
       </c>
       <c r="O320">
-        <v>18200045</v>
+        <v>18200037</v>
       </c>
       <c r="P320" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q320" t="s">
         <v>238</v>
       </c>
       <c r="S320">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="T320" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="W320" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AA320">
         <v>0</v>
@@ -24211,61 +24211,61 @@
     </row>
     <row r="321" spans="1:34">
       <c r="A321">
-        <v>5417</v>
+        <v>6963</v>
       </c>
       <c r="B321" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C321" t="s">
         <v>58</v>
       </c>
       <c r="D321" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E321" t="s">
         <v>62</v>
       </c>
       <c r="F321" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G321">
-        <v>7868</v>
+        <v>7875</v>
       </c>
       <c r="H321">
         <v>0</v>
       </c>
       <c r="I321" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J321" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="L321" s="1">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="M321" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N321" t="s">
         <v>203</v>
       </c>
       <c r="O321">
-        <v>17399310</v>
+        <v>18200056</v>
       </c>
       <c r="P321" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q321" t="s">
         <v>238</v>
       </c>
       <c r="S321">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="T321" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="W321" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="AA321">
         <v>0</v>
@@ -24274,69 +24274,69 @@
         <v>457</v>
       </c>
       <c r="AH321" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="322" spans="1:34">
       <c r="A322">
-        <v>6486</v>
+        <v>6628</v>
       </c>
       <c r="B322" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C322" t="s">
         <v>58</v>
       </c>
       <c r="D322" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E322" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F322" t="s">
         <v>64</v>
       </c>
       <c r="G322">
-        <v>7868</v>
+        <v>9764</v>
       </c>
       <c r="H322">
         <v>0</v>
       </c>
       <c r="I322" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J322" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="L322" s="1">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="M322" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N322" t="s">
         <v>203</v>
       </c>
       <c r="O322">
-        <v>18114218</v>
+        <v>18096422</v>
       </c>
       <c r="P322" t="s">
-        <v>230</v>
+        <v>209</v>
       </c>
       <c r="Q322" t="s">
         <v>238</v>
       </c>
       <c r="S322">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="T322" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="V322" t="s">
         <v>255</v>
       </c>
       <c r="W322" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="AA322">
         <v>0</v>
@@ -24345,83 +24345,83 @@
         <v>457</v>
       </c>
       <c r="AH322" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="323" spans="1:34">
       <c r="A323">
-        <v>6404</v>
+        <v>6945</v>
       </c>
       <c r="B323" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C323" t="s">
         <v>58</v>
       </c>
       <c r="D323" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E323" t="s">
         <v>62</v>
       </c>
       <c r="F323" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G323">
-        <v>6890</v>
+        <v>9764</v>
       </c>
       <c r="H323">
         <v>0</v>
       </c>
       <c r="I323" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J323" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="L323" s="1">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="M323" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N323" t="s">
         <v>203</v>
       </c>
       <c r="O323">
-        <v>16962328</v>
+        <v>18200045</v>
       </c>
       <c r="P323" t="s">
-        <v>231</v>
+        <v>210</v>
       </c>
       <c r="Q323" t="s">
         <v>238</v>
       </c>
       <c r="S323">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="T323" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="W323" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="AA323">
         <v>0</v>
       </c>
       <c r="AG323" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AH323" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="324" spans="1:34">
       <c r="A324">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B324" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C324" t="s">
         <v>58</v>
@@ -24436,7 +24436,7 @@
         <v>64</v>
       </c>
       <c r="G324">
-        <v>6890</v>
+        <v>7868</v>
       </c>
       <c r="H324">
         <v>0</v>
@@ -24445,43 +24445,40 @@
         <v>68</v>
       </c>
       <c r="J324" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L324" s="1">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="M324" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N324" t="s">
         <v>203</v>
       </c>
       <c r="O324">
-        <v>18152538</v>
+        <v>17399310</v>
       </c>
       <c r="P324" t="s">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="Q324" t="s">
         <v>238</v>
       </c>
       <c r="S324">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="T324" t="s">
-        <v>246</v>
-      </c>
-      <c r="V324" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="W324" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AA324">
         <v>0</v>
       </c>
       <c r="AG324" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AH324" t="s">
         <v>462</v>
@@ -24489,16 +24486,16 @@
     </row>
     <row r="325" spans="1:34">
       <c r="A325">
-        <v>6703</v>
+        <v>6486</v>
       </c>
       <c r="B325" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C325" t="s">
         <v>58</v>
       </c>
       <c r="D325" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E325" t="s">
         <v>62</v>
@@ -24507,7 +24504,7 @@
         <v>64</v>
       </c>
       <c r="G325">
-        <v>6890</v>
+        <v>7868</v>
       </c>
       <c r="H325">
         <v>0</v>
@@ -24516,19 +24513,19 @@
         <v>68</v>
       </c>
       <c r="J325" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L325" s="1">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="M325" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N325" t="s">
         <v>203</v>
       </c>
       <c r="O325">
-        <v>17955186</v>
+        <v>18114218</v>
       </c>
       <c r="P325" t="s">
         <v>230</v>
@@ -24537,19 +24534,22 @@
         <v>238</v>
       </c>
       <c r="S325">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="T325" t="s">
-        <v>247</v>
+        <v>246</v>
+      </c>
+      <c r="V325" t="s">
+        <v>255</v>
       </c>
       <c r="W325" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AA325">
         <v>0</v>
       </c>
       <c r="AG325" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AH325" t="s">
         <v>462</v>
@@ -24557,16 +24557,16 @@
     </row>
     <row r="326" spans="1:34">
       <c r="A326">
-        <v>6704</v>
+        <v>6404</v>
       </c>
       <c r="B326" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C326" t="s">
         <v>58</v>
       </c>
       <c r="D326" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E326" t="s">
         <v>62</v>
@@ -24584,7 +24584,7 @@
         <v>68</v>
       </c>
       <c r="J326" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L326" s="1">
         <v>46290</v>
@@ -24596,25 +24596,22 @@
         <v>203</v>
       </c>
       <c r="O326">
-        <v>17955399</v>
+        <v>16962328</v>
       </c>
       <c r="P326" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="Q326" t="s">
         <v>238</v>
       </c>
       <c r="S326">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T326" t="s">
-        <v>245</v>
-      </c>
-      <c r="V326" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="W326" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AA326">
         <v>0</v>
@@ -24628,16 +24625,16 @@
     </row>
     <row r="327" spans="1:34">
       <c r="A327">
-        <v>6705</v>
+        <v>6486</v>
       </c>
       <c r="B327" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C327" t="s">
         <v>58</v>
       </c>
       <c r="D327" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E327" t="s">
         <v>62</v>
@@ -24655,7 +24652,7 @@
         <v>68</v>
       </c>
       <c r="J327" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L327" s="1">
         <v>46290</v>
@@ -24667,22 +24664,25 @@
         <v>203</v>
       </c>
       <c r="O327">
-        <v>17955249</v>
+        <v>18152538</v>
       </c>
       <c r="P327" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="Q327" t="s">
         <v>238</v>
       </c>
       <c r="S327">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T327" t="s">
-        <v>245</v>
+        <v>246</v>
+      </c>
+      <c r="V327" t="s">
+        <v>255</v>
       </c>
       <c r="W327" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AA327">
         <v>0</v>
@@ -24691,21 +24691,21 @@
         <v>459</v>
       </c>
       <c r="AH327" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="328" spans="1:34">
       <c r="A328">
-        <v>6779</v>
+        <v>6703</v>
       </c>
       <c r="B328" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C328" t="s">
         <v>58</v>
       </c>
       <c r="D328" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E328" t="s">
         <v>62</v>
@@ -24723,7 +24723,7 @@
         <v>68</v>
       </c>
       <c r="J328" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L328" s="1">
         <v>46290</v>
@@ -24735,25 +24735,22 @@
         <v>203</v>
       </c>
       <c r="O328">
-        <v>18056769</v>
+        <v>17955186</v>
       </c>
       <c r="P328" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="Q328" t="s">
         <v>238</v>
       </c>
       <c r="S328">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T328" t="s">
-        <v>245</v>
-      </c>
-      <c r="V328" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="W328" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AA328">
         <v>0</v>
@@ -24762,21 +24759,21 @@
         <v>459</v>
       </c>
       <c r="AH328" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="329" spans="1:34">
       <c r="A329">
-        <v>6404</v>
+        <v>6704</v>
       </c>
       <c r="B329" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C329" t="s">
         <v>58</v>
       </c>
       <c r="D329" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E329" t="s">
         <v>62</v>
@@ -24785,7 +24782,7 @@
         <v>64</v>
       </c>
       <c r="G329">
-        <v>11514</v>
+        <v>6890</v>
       </c>
       <c r="H329">
         <v>0</v>
@@ -24794,7 +24791,7 @@
         <v>68</v>
       </c>
       <c r="J329" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L329" s="1">
         <v>46290</v>
@@ -24806,22 +24803,25 @@
         <v>203</v>
       </c>
       <c r="O329">
-        <v>16962474</v>
+        <v>17955399</v>
       </c>
       <c r="P329" t="s">
-        <v>231</v>
+        <v>213</v>
       </c>
       <c r="Q329" t="s">
         <v>238</v>
       </c>
       <c r="S329">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T329" t="s">
-        <v>248</v>
+        <v>245</v>
+      </c>
+      <c r="V329" t="s">
+        <v>255</v>
       </c>
       <c r="W329" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AA329">
         <v>0</v>
@@ -24835,16 +24835,16 @@
     </row>
     <row r="330" spans="1:34">
       <c r="A330">
-        <v>6486</v>
+        <v>6705</v>
       </c>
       <c r="B330" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C330" t="s">
         <v>58</v>
       </c>
       <c r="D330" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E330" t="s">
         <v>62</v>
@@ -24853,7 +24853,7 @@
         <v>64</v>
       </c>
       <c r="G330">
-        <v>11514</v>
+        <v>6890</v>
       </c>
       <c r="H330">
         <v>0</v>
@@ -24862,7 +24862,7 @@
         <v>68</v>
       </c>
       <c r="J330" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L330" s="1">
         <v>46290</v>
@@ -24874,25 +24874,22 @@
         <v>203</v>
       </c>
       <c r="O330">
-        <v>18114227</v>
+        <v>17955249</v>
       </c>
       <c r="P330" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="Q330" t="s">
         <v>238</v>
       </c>
       <c r="S330">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T330" t="s">
-        <v>246</v>
-      </c>
-      <c r="V330" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="W330" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AA330">
         <v>0</v>
@@ -24901,21 +24898,21 @@
         <v>459</v>
       </c>
       <c r="AH330" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="331" spans="1:34">
       <c r="A331">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B331" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C331" t="s">
         <v>58</v>
       </c>
       <c r="D331" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E331" t="s">
         <v>62</v>
@@ -24924,7 +24921,7 @@
         <v>64</v>
       </c>
       <c r="G331">
-        <v>11514</v>
+        <v>6890</v>
       </c>
       <c r="H331">
         <v>0</v>
@@ -24933,7 +24930,7 @@
         <v>68</v>
       </c>
       <c r="J331" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L331" s="1">
         <v>46290</v>
@@ -24945,22 +24942,25 @@
         <v>203</v>
       </c>
       <c r="O331">
-        <v>17955212</v>
+        <v>18056769</v>
       </c>
       <c r="P331" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="Q331" t="s">
         <v>238</v>
       </c>
       <c r="S331">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T331" t="s">
-        <v>247</v>
+        <v>245</v>
+      </c>
+      <c r="V331" t="s">
+        <v>255</v>
       </c>
       <c r="W331" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AA331">
         <v>0</v>
@@ -24969,21 +24969,21 @@
         <v>459</v>
       </c>
       <c r="AH331" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="332" spans="1:34">
       <c r="A332">
-        <v>6704</v>
+        <v>6404</v>
       </c>
       <c r="B332" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C332" t="s">
         <v>58</v>
       </c>
       <c r="D332" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E332" t="s">
         <v>62</v>
@@ -25001,7 +25001,7 @@
         <v>68</v>
       </c>
       <c r="J332" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L332" s="1">
         <v>46290</v>
@@ -25013,25 +25013,22 @@
         <v>203</v>
       </c>
       <c r="O332">
-        <v>17955445</v>
+        <v>16962474</v>
       </c>
       <c r="P332" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="Q332" t="s">
         <v>238</v>
       </c>
       <c r="S332">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T332" t="s">
-        <v>245</v>
-      </c>
-      <c r="V332" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="W332" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AA332">
         <v>0</v>
@@ -25045,16 +25042,16 @@
     </row>
     <row r="333" spans="1:34">
       <c r="A333">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B333" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C333" t="s">
         <v>58</v>
       </c>
       <c r="D333" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E333" t="s">
         <v>62</v>
@@ -25063,7 +25060,7 @@
         <v>64</v>
       </c>
       <c r="G333">
-        <v>10988</v>
+        <v>11514</v>
       </c>
       <c r="H333">
         <v>0</v>
@@ -25072,43 +25069,46 @@
         <v>68</v>
       </c>
       <c r="J333" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L333" s="1">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="M333" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N333" t="s">
         <v>203</v>
       </c>
       <c r="O333">
-        <v>16962444</v>
+        <v>18114227</v>
       </c>
       <c r="P333" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q333" t="s">
         <v>238</v>
       </c>
       <c r="S333">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="T333" t="s">
-        <v>248</v>
+        <v>246</v>
+      </c>
+      <c r="V333" t="s">
+        <v>255</v>
       </c>
       <c r="W333" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AA333">
         <v>0</v>
       </c>
       <c r="AG333" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AH333" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="334" spans="1:34">
@@ -25131,7 +25131,7 @@
         <v>64</v>
       </c>
       <c r="G334">
-        <v>10988</v>
+        <v>11514</v>
       </c>
       <c r="H334">
         <v>0</v>
@@ -25140,19 +25140,19 @@
         <v>68</v>
       </c>
       <c r="J334" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L334" s="1">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="M334" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N334" t="s">
         <v>203</v>
       </c>
       <c r="O334">
-        <v>18112918</v>
+        <v>17955212</v>
       </c>
       <c r="P334" t="s">
         <v>230</v>
@@ -25161,19 +25161,19 @@
         <v>238</v>
       </c>
       <c r="S334">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="T334" t="s">
         <v>247</v>
       </c>
       <c r="W334" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AA334">
         <v>0</v>
       </c>
       <c r="AG334" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AH334" t="s">
         <v>462</v>
@@ -25181,10 +25181,10 @@
     </row>
     <row r="335" spans="1:34">
       <c r="A335">
-        <v>6486</v>
+        <v>6704</v>
       </c>
       <c r="B335" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C335" t="s">
         <v>58</v>
@@ -25199,7 +25199,7 @@
         <v>64</v>
       </c>
       <c r="G335">
-        <v>7874</v>
+        <v>11514</v>
       </c>
       <c r="H335">
         <v>0</v>
@@ -25211,57 +25211,57 @@
         <v>138</v>
       </c>
       <c r="L335" s="1">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="M335" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N335" t="s">
         <v>203</v>
       </c>
       <c r="O335">
-        <v>18130463</v>
+        <v>17955445</v>
       </c>
       <c r="P335" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="Q335" t="s">
         <v>238</v>
       </c>
       <c r="S335">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="T335" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="V335" t="s">
         <v>255</v>
       </c>
       <c r="W335" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AA335">
         <v>0</v>
       </c>
       <c r="AG335" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AH335" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="336" spans="1:34">
       <c r="A336">
-        <v>6704</v>
+        <v>6404</v>
       </c>
       <c r="B336" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C336" t="s">
         <v>58</v>
       </c>
       <c r="D336" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E336" t="s">
         <v>62</v>
@@ -25270,7 +25270,7 @@
         <v>64</v>
       </c>
       <c r="G336">
-        <v>7874</v>
+        <v>10988</v>
       </c>
       <c r="H336">
         <v>0</v>
@@ -25279,7 +25279,7 @@
         <v>68</v>
       </c>
       <c r="J336" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L336" s="1">
         <v>46295</v>
@@ -25291,25 +25291,22 @@
         <v>203</v>
       </c>
       <c r="O336">
-        <v>18096767</v>
+        <v>16962444</v>
       </c>
       <c r="P336" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="Q336" t="s">
         <v>238</v>
       </c>
       <c r="S336">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="T336" t="s">
-        <v>245</v>
-      </c>
-      <c r="V336" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="W336" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="AA336">
         <v>0</v>
@@ -25323,16 +25320,16 @@
     </row>
     <row r="337" spans="1:34">
       <c r="A337">
-        <v>6705</v>
+        <v>6703</v>
       </c>
       <c r="B337" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C337" t="s">
         <v>58</v>
       </c>
       <c r="D337" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E337" t="s">
         <v>62</v>
@@ -25341,7 +25338,7 @@
         <v>64</v>
       </c>
       <c r="G337">
-        <v>9762</v>
+        <v>10988</v>
       </c>
       <c r="H337">
         <v>0</v>
@@ -25362,22 +25359,22 @@
         <v>203</v>
       </c>
       <c r="O337">
-        <v>18096939</v>
+        <v>18112918</v>
       </c>
       <c r="P337" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="Q337" t="s">
         <v>238</v>
       </c>
       <c r="S337">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="T337" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="W337" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="AA337">
         <v>0</v>
@@ -25386,21 +25383,21 @@
         <v>457</v>
       </c>
       <c r="AH337" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="338" spans="1:34">
       <c r="A338">
-        <v>6779</v>
+        <v>6486</v>
       </c>
       <c r="B338" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C338" t="s">
         <v>58</v>
       </c>
       <c r="D338" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E338" t="s">
         <v>62</v>
@@ -25409,7 +25406,7 @@
         <v>64</v>
       </c>
       <c r="G338">
-        <v>9762</v>
+        <v>7874</v>
       </c>
       <c r="H338">
         <v>0</v>
@@ -25418,7 +25415,7 @@
         <v>68</v>
       </c>
       <c r="J338" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L338" s="1">
         <v>46295</v>
@@ -25430,25 +25427,25 @@
         <v>203</v>
       </c>
       <c r="O338">
-        <v>18130484</v>
+        <v>18130463</v>
       </c>
       <c r="P338" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="Q338" t="s">
         <v>238</v>
       </c>
       <c r="S338">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="T338" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="V338" t="s">
         <v>255</v>
       </c>
       <c r="W338" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="AA338">
         <v>0</v>
@@ -25457,15 +25454,15 @@
         <v>457</v>
       </c>
       <c r="AH338" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="339" spans="1:34">
       <c r="A339">
-        <v>6548</v>
+        <v>6704</v>
       </c>
       <c r="B339" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C339" t="s">
         <v>58</v>
@@ -25480,16 +25477,16 @@
         <v>64</v>
       </c>
       <c r="G339">
-        <v>5859</v>
+        <v>7874</v>
       </c>
       <c r="H339">
-        <v>5786</v>
+        <v>0</v>
       </c>
       <c r="I339" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J339" t="s">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="L339" s="1">
         <v>46295</v>
@@ -25498,51 +25495,51 @@
         <v>195</v>
       </c>
       <c r="N339" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O339">
-        <v>17222602</v>
+        <v>18096767</v>
       </c>
       <c r="P339" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="Q339" t="s">
         <v>238</v>
       </c>
       <c r="S339">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="T339" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="V339" t="s">
         <v>255</v>
       </c>
       <c r="W339" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="AA339">
         <v>0</v>
       </c>
       <c r="AG339" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AH339" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="340" spans="1:34">
       <c r="A340">
-        <v>6548</v>
+        <v>6705</v>
       </c>
       <c r="B340" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="C340" t="s">
         <v>58</v>
       </c>
       <c r="D340" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E340" t="s">
         <v>62</v>
@@ -25551,16 +25548,16 @@
         <v>64</v>
       </c>
       <c r="G340">
-        <v>5905</v>
+        <v>9762</v>
       </c>
       <c r="H340">
-        <v>5784</v>
+        <v>0</v>
       </c>
       <c r="I340" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J340" t="s">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="L340" s="1">
         <v>46295</v>
@@ -25569,51 +25566,48 @@
         <v>195</v>
       </c>
       <c r="N340" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O340">
-        <v>17222671</v>
+        <v>18096939</v>
       </c>
       <c r="P340" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="Q340" t="s">
         <v>238</v>
       </c>
       <c r="S340">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="T340" t="s">
-        <v>239</v>
-      </c>
-      <c r="V340" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="W340" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="AA340">
         <v>0</v>
       </c>
       <c r="AG340" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AH340" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="341" spans="1:34">
       <c r="A341">
-        <v>6548</v>
+        <v>6779</v>
       </c>
       <c r="B341" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="C341" t="s">
         <v>58</v>
       </c>
       <c r="D341" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E341" t="s">
         <v>62</v>
@@ -25622,16 +25616,16 @@
         <v>64</v>
       </c>
       <c r="G341">
-        <v>5853</v>
+        <v>9762</v>
       </c>
       <c r="H341">
-        <v>5784</v>
+        <v>0</v>
       </c>
       <c r="I341" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J341" t="s">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="L341" s="1">
         <v>46295</v>
@@ -25640,28 +25634,28 @@
         <v>195</v>
       </c>
       <c r="N341" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O341">
-        <v>17222589</v>
+        <v>18130484</v>
       </c>
       <c r="P341" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="Q341" t="s">
         <v>238</v>
       </c>
       <c r="S341">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="T341" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="V341" t="s">
         <v>255</v>
       </c>
       <c r="W341" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="AA341">
         <v>0</v>
@@ -25670,15 +25664,15 @@
         <v>457</v>
       </c>
       <c r="AH341" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="342" spans="1:34">
       <c r="A342">
-        <v>5417</v>
+        <v>6548</v>
       </c>
       <c r="B342" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C342" t="s">
         <v>58</v>
@@ -25693,63 +25687,69 @@
         <v>64</v>
       </c>
       <c r="G342">
-        <v>5847</v>
+        <v>5859</v>
       </c>
       <c r="H342">
-        <v>5784</v>
+        <v>5786</v>
       </c>
       <c r="I342" t="s">
         <v>69</v>
       </c>
       <c r="J342" t="s">
-        <v>140</v>
+        <v>77</v>
       </c>
       <c r="L342" s="1">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="M342" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N342" t="s">
         <v>204</v>
       </c>
       <c r="O342">
-        <v>18158417</v>
+        <v>17222602</v>
       </c>
       <c r="P342" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q342" t="s">
         <v>238</v>
       </c>
       <c r="S342">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="T342" t="s">
-        <v>244</v>
+        <v>239</v>
+      </c>
+      <c r="V342" t="s">
+        <v>255</v>
       </c>
       <c r="W342" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AA342">
         <v>0</v>
       </c>
       <c r="AG342" t="s">
-        <v>457</v>
+        <v>458</v>
+      </c>
+      <c r="AH342" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="343" spans="1:34">
       <c r="A343">
-        <v>6779</v>
+        <v>6548</v>
       </c>
       <c r="B343" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C343" t="s">
         <v>58</v>
       </c>
       <c r="D343" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E343" t="s">
         <v>62</v>
@@ -25758,7 +25758,7 @@
         <v>64</v>
       </c>
       <c r="G343">
-        <v>5847</v>
+        <v>5905</v>
       </c>
       <c r="H343">
         <v>5784</v>
@@ -25767,46 +25767,46 @@
         <v>69</v>
       </c>
       <c r="J343" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="L343" s="1">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="M343" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N343" t="s">
         <v>204</v>
       </c>
       <c r="O343">
-        <v>18158764</v>
+        <v>17222671</v>
       </c>
       <c r="P343" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="Q343" t="s">
         <v>238</v>
       </c>
       <c r="S343">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="T343" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="V343" t="s">
         <v>255</v>
       </c>
       <c r="W343" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="AA343">
         <v>0</v>
       </c>
       <c r="AG343" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AH343" t="s">
-        <v>449</v>
+        <v>464</v>
       </c>
     </row>
     <row r="344" spans="1:34">
@@ -25829,7 +25829,7 @@
         <v>64</v>
       </c>
       <c r="G344">
-        <v>5906</v>
+        <v>5853</v>
       </c>
       <c r="H344">
         <v>5784</v>
@@ -25838,7 +25838,7 @@
         <v>69</v>
       </c>
       <c r="J344" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L344" s="1">
         <v>46295</v>
@@ -25850,7 +25850,7 @@
         <v>204</v>
       </c>
       <c r="O344">
-        <v>17222688</v>
+        <v>17222589</v>
       </c>
       <c r="P344" t="s">
         <v>218</v>
@@ -25859,7 +25859,7 @@
         <v>238</v>
       </c>
       <c r="S344">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="T344" t="s">
         <v>239</v>
@@ -25868,13 +25868,13 @@
         <v>255</v>
       </c>
       <c r="W344" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="AA344">
         <v>0</v>
       </c>
       <c r="AG344" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AH344" t="s">
         <v>464</v>
@@ -25882,10 +25882,10 @@
     </row>
     <row r="345" spans="1:34">
       <c r="A345">
-        <v>6548</v>
+        <v>5417</v>
       </c>
       <c r="B345" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C345" t="s">
         <v>58</v>
@@ -25900,7 +25900,7 @@
         <v>64</v>
       </c>
       <c r="G345">
-        <v>5907</v>
+        <v>5847</v>
       </c>
       <c r="H345">
         <v>5784</v>
@@ -25909,37 +25909,34 @@
         <v>69</v>
       </c>
       <c r="J345" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="L345" s="1">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="M345" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="N345" t="s">
         <v>204</v>
       </c>
       <c r="O345">
-        <v>17222699</v>
+        <v>18158417</v>
       </c>
       <c r="P345" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q345" t="s">
         <v>238</v>
       </c>
       <c r="S345">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="T345" t="s">
-        <v>239</v>
-      </c>
-      <c r="V345" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="W345" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="AA345">
         <v>0</v>
@@ -25947,16 +25944,13 @@
       <c r="AG345" t="s">
         <v>457</v>
       </c>
-      <c r="AH345" t="s">
-        <v>464</v>
-      </c>
     </row>
     <row r="346" spans="1:34">
       <c r="A346">
-        <v>6945</v>
+        <v>6779</v>
       </c>
       <c r="B346" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C346" t="s">
         <v>58</v>
@@ -25968,125 +25962,137 @@
         <v>62</v>
       </c>
       <c r="F346" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G346">
-        <v>5764</v>
+        <v>5847</v>
       </c>
       <c r="H346">
-        <v>0</v>
+        <v>5784</v>
       </c>
       <c r="I346" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J346" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L346" s="1">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="M346" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N346" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O346">
-        <v>18220203</v>
+        <v>18158764</v>
       </c>
       <c r="P346" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="Q346" t="s">
         <v>238</v>
       </c>
       <c r="S346">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="T346" t="s">
-        <v>241</v>
+        <v>245</v>
+      </c>
+      <c r="V346" t="s">
+        <v>255</v>
       </c>
       <c r="W346" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AA346">
         <v>0</v>
       </c>
       <c r="AG346" t="s">
-        <v>459</v>
+        <v>457</v>
+      </c>
+      <c r="AH346" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="347" spans="1:34">
       <c r="A347">
-        <v>6945</v>
+        <v>6548</v>
       </c>
       <c r="B347" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C347" t="s">
         <v>58</v>
       </c>
       <c r="D347" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E347" t="s">
         <v>62</v>
       </c>
       <c r="F347" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G347">
-        <v>1877</v>
+        <v>5906</v>
       </c>
       <c r="H347">
-        <v>0</v>
+        <v>5784</v>
       </c>
       <c r="I347" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J347" t="s">
-        <v>142</v>
+        <v>88</v>
       </c>
       <c r="L347" s="1">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="M347" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N347" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O347">
-        <v>18220188</v>
+        <v>17222688</v>
       </c>
       <c r="P347" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="Q347" t="s">
         <v>238</v>
       </c>
       <c r="S347">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="T347" t="s">
-        <v>241</v>
+        <v>239</v>
+      </c>
+      <c r="V347" t="s">
+        <v>255</v>
       </c>
       <c r="W347" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="AA347">
         <v>0</v>
       </c>
       <c r="AG347" t="s">
-        <v>458</v>
+        <v>459</v>
+      </c>
+      <c r="AH347" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="348" spans="1:34">
       <c r="A348">
-        <v>6949</v>
+        <v>6548</v>
       </c>
       <c r="B348" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C348" t="s">
         <v>58</v>
@@ -26098,43 +26104,46 @@
         <v>62</v>
       </c>
       <c r="F348" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G348">
-        <v>1882</v>
+        <v>5907</v>
       </c>
       <c r="H348">
-        <v>0</v>
+        <v>5784</v>
       </c>
       <c r="I348" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J348" t="s">
-        <v>143</v>
+        <v>90</v>
       </c>
       <c r="L348" s="1">
-        <v>46287</v>
+        <v>46295</v>
       </c>
       <c r="M348" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="N348" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O348">
-        <v>18214871</v>
+        <v>17222699</v>
       </c>
       <c r="P348" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="Q348" t="s">
         <v>238</v>
       </c>
       <c r="S348">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="T348" t="s">
-        <v>242</v>
+        <v>239</v>
+      </c>
+      <c r="V348" t="s">
+        <v>255</v>
       </c>
       <c r="W348" t="s">
         <v>348</v>
@@ -26143,57 +26152,57 @@
         <v>0</v>
       </c>
       <c r="AG348" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AH348" t="s">
-        <v>450</v>
+        <v>464</v>
       </c>
     </row>
     <row r="349" spans="1:34">
       <c r="A349">
-        <v>6486</v>
+        <v>6945</v>
       </c>
       <c r="B349" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C349" t="s">
         <v>58</v>
       </c>
       <c r="D349" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E349" t="s">
         <v>62</v>
       </c>
       <c r="F349" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G349">
-        <v>6759</v>
+        <v>5764</v>
       </c>
       <c r="H349">
-        <v>1788</v>
+        <v>0</v>
       </c>
       <c r="I349" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J349" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L349" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="M349" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="N349" t="s">
         <v>203</v>
       </c>
       <c r="O349">
-        <v>16976177</v>
+        <v>18220203</v>
       </c>
       <c r="P349" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="Q349" t="s">
         <v>238</v>
@@ -26202,30 +26211,24 @@
         <v>-2</v>
       </c>
       <c r="T349" t="s">
-        <v>246</v>
-      </c>
-      <c r="V349" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="W349" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="AA349">
         <v>0</v>
       </c>
       <c r="AG349" t="s">
-        <v>457</v>
-      </c>
-      <c r="AH349" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="350" spans="1:34">
       <c r="A350">
-        <v>6705</v>
+        <v>6945</v>
       </c>
       <c r="B350" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C350" t="s">
         <v>58</v>
@@ -26237,69 +26240,66 @@
         <v>62</v>
       </c>
       <c r="F350" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G350">
-        <v>6759</v>
+        <v>1877</v>
       </c>
       <c r="H350">
-        <v>1788</v>
+        <v>0</v>
       </c>
       <c r="I350" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J350" t="s">
         <v>144</v>
       </c>
       <c r="L350" s="1">
-        <v>46289</v>
+        <v>46293</v>
       </c>
       <c r="M350" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="N350" t="s">
         <v>203</v>
       </c>
       <c r="O350">
-        <v>17949019</v>
+        <v>18220188</v>
       </c>
       <c r="P350" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="Q350" t="s">
         <v>238</v>
       </c>
       <c r="S350">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="T350" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="W350" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="AA350">
         <v>0</v>
       </c>
       <c r="AG350" t="s">
-        <v>457</v>
-      </c>
-      <c r="AH350" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
     </row>
     <row r="351" spans="1:34">
       <c r="A351">
-        <v>6705</v>
+        <v>6486</v>
       </c>
       <c r="B351" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C351" t="s">
         <v>58</v>
       </c>
       <c r="D351" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E351" t="s">
         <v>62</v>
@@ -26308,28 +26308,28 @@
         <v>64</v>
       </c>
       <c r="G351">
-        <v>1803</v>
+        <v>6759</v>
       </c>
       <c r="H351">
-        <v>0</v>
+        <v>1788</v>
       </c>
       <c r="I351" t="s">
         <v>71</v>
       </c>
       <c r="J351" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="L351" s="1">
-        <v>46293</v>
+        <v>46289</v>
       </c>
       <c r="M351" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="N351" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="O351">
-        <v>17948937</v>
+        <v>16976177</v>
       </c>
       <c r="P351" t="s">
         <v>227</v>
@@ -26338,19 +26338,22 @@
         <v>238</v>
       </c>
       <c r="S351">
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="T351" t="s">
-        <v>245</v>
+        <v>246</v>
+      </c>
+      <c r="V351" t="s">
+        <v>255</v>
       </c>
       <c r="W351" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AA351">
         <v>0</v>
       </c>
       <c r="AG351" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AH351" t="s">
         <v>466</v>
@@ -26358,16 +26361,16 @@
     </row>
     <row r="352" spans="1:34">
       <c r="A352">
-        <v>6703</v>
+        <v>6705</v>
       </c>
       <c r="B352" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C352" t="s">
         <v>58</v>
       </c>
       <c r="D352" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E352" t="s">
         <v>62</v>
@@ -26376,10 +26379,10 @@
         <v>64</v>
       </c>
       <c r="G352">
-        <v>1807</v>
+        <v>6759</v>
       </c>
       <c r="H352">
-        <v>0</v>
+        <v>1788</v>
       </c>
       <c r="I352" t="s">
         <v>71</v>
@@ -26388,16 +26391,16 @@
         <v>145</v>
       </c>
       <c r="L352" s="1">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="M352" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="N352" t="s">
         <v>203</v>
       </c>
       <c r="O352">
-        <v>17948806</v>
+        <v>17949019</v>
       </c>
       <c r="P352" t="s">
         <v>227</v>
@@ -26406,10 +26409,10 @@
         <v>238</v>
       </c>
       <c r="S352">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T352" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="W352" t="s">
         <v>351</v>
@@ -26418,7 +26421,7 @@
         <v>0</v>
       </c>
       <c r="AG352" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AH352" t="s">
         <v>466</v>
@@ -26426,16 +26429,16 @@
     </row>
     <row r="353" spans="1:34">
       <c r="A353">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B353" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C353" t="s">
         <v>58</v>
       </c>
       <c r="D353" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E353" t="s">
         <v>62</v>
@@ -26444,7 +26447,7 @@
         <v>64</v>
       </c>
       <c r="G353">
-        <v>1808</v>
+        <v>1803</v>
       </c>
       <c r="H353">
         <v>0</v>
@@ -26453,19 +26456,19 @@
         <v>71</v>
       </c>
       <c r="J353" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L353" s="1">
-        <v>46287</v>
+        <v>46293</v>
       </c>
       <c r="M353" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N353" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="O353">
-        <v>18085209</v>
+        <v>17948937</v>
       </c>
       <c r="P353" t="s">
         <v>227</v>
@@ -26474,13 +26477,10 @@
         <v>238</v>
       </c>
       <c r="S353">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="T353" t="s">
         <v>245</v>
-      </c>
-      <c r="V353" t="s">
-        <v>255</v>
       </c>
       <c r="W353" t="s">
         <v>352</v>
@@ -26529,6 +26529,9 @@
       <c r="L354" s="1">
         <v>46290</v>
       </c>
+      <c r="M354" t="s">
+        <v>194</v>
+      </c>
       <c r="N354" t="s">
         <v>203</v>
       </c>
@@ -26542,7 +26545,7 @@
         <v>238</v>
       </c>
       <c r="S354">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T354" t="s">
         <v>244</v>
@@ -26607,7 +26610,7 @@
         <v>238</v>
       </c>
       <c r="S355">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T355" t="s">
         <v>248</v>
@@ -26672,7 +26675,7 @@
         <v>238</v>
       </c>
       <c r="S356">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T356" t="s">
         <v>240</v>
@@ -26740,7 +26743,7 @@
         <v>238</v>
       </c>
       <c r="S357">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T357" t="s">
         <v>243</v>
@@ -26805,7 +26808,7 @@
         <v>238</v>
       </c>
       <c r="S358">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T358" t="s">
         <v>243</v>
@@ -26870,13 +26873,13 @@
         <v>238</v>
       </c>
       <c r="S359">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="T359" t="s">
         <v>244</v>
       </c>
       <c r="W359" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="AA359">
         <v>0</v>
@@ -26935,7 +26938,7 @@
         <v>238</v>
       </c>
       <c r="S360">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="T360" t="s">
         <v>246</v>
@@ -27003,7 +27006,7 @@
         <v>238</v>
       </c>
       <c r="S361">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="T361" t="s">
         <v>247</v>
@@ -27068,7 +27071,7 @@
         <v>238</v>
       </c>
       <c r="S362">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="T362" t="s">
         <v>245</v>
@@ -27136,7 +27139,7 @@
         <v>238</v>
       </c>
       <c r="S363">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="T363" t="s">
         <v>245</v>
@@ -27201,7 +27204,7 @@
         <v>238</v>
       </c>
       <c r="S364">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="T364" t="s">
         <v>242</v>
@@ -27266,7 +27269,7 @@
         <v>238</v>
       </c>
       <c r="S365">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="T365" t="s">
         <v>243</v>
@@ -27331,7 +27334,7 @@
         <v>238</v>
       </c>
       <c r="S366">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="T366" t="s">
         <v>243</v>
@@ -27375,7 +27378,7 @@
         <v>73</v>
       </c>
       <c r="J367" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L367" s="1">
         <v>46290</v>
@@ -27396,7 +27399,7 @@
         <v>238</v>
       </c>
       <c r="S367">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T367" t="s">
         <v>244</v>
@@ -27461,7 +27464,7 @@
         <v>238</v>
       </c>
       <c r="S368">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="T368" t="s">
         <v>242</v>
@@ -27526,7 +27529,7 @@
         <v>46265.00248284722</v>
       </c>
       <c r="S369">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="T369" t="s">
         <v>240</v>
@@ -27597,7 +27600,7 @@
         <v>46265.00255472222</v>
       </c>
       <c r="S370">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="T370" t="s">
         <v>241</v>
@@ -27665,7 +27668,7 @@
         <v>46234.66180127315</v>
       </c>
       <c r="S371">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T371" t="s">
         <v>239</v>
@@ -27739,7 +27742,7 @@
         <v>46245.76585582176</v>
       </c>
       <c r="S372">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T372" t="s">
         <v>240</v>
@@ -27813,7 +27816,7 @@
         <v>46282.62254486111</v>
       </c>
       <c r="S373">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T373" t="s">
         <v>239</v>
@@ -27887,7 +27890,7 @@
         <v>46286.64173940972</v>
       </c>
       <c r="S374">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T374" t="s">
         <v>240</v>
@@ -27961,7 +27964,7 @@
         <v>46283.44840582176</v>
       </c>
       <c r="S375">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T375" t="s">
         <v>242</v>
@@ -28008,7 +28011,7 @@
         <v>68</v>
       </c>
       <c r="J376" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L376" s="1">
         <v>46293</v>
@@ -28029,7 +28032,7 @@
         <v>46267.47365627315</v>
       </c>
       <c r="S376">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="T376" t="s">
         <v>245</v>
@@ -28079,7 +28082,7 @@
         <v>68</v>
       </c>
       <c r="J377" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L377" s="1">
         <v>46290</v>
@@ -28103,13 +28106,13 @@
         <v>46287.48052434028</v>
       </c>
       <c r="S377">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T377" t="s">
         <v>244</v>
       </c>
       <c r="W377" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AA377">
         <v>0</v>
@@ -28174,7 +28177,7 @@
         <v>46266.47620831019</v>
       </c>
       <c r="S378">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T378" t="s">
         <v>244</v>
@@ -28242,7 +28245,7 @@
         <v>46267.57586420139</v>
       </c>
       <c r="S379">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T379" t="s">
         <v>246</v>
@@ -28313,7 +28316,7 @@
         <v>46233.72355880787</v>
       </c>
       <c r="S380">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T380" t="s">
         <v>244</v>
@@ -28378,7 +28381,7 @@
         <v>46261.36669849537</v>
       </c>
       <c r="S381">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T381" t="s">
         <v>249</v>
@@ -28440,7 +28443,7 @@
         <v>46266.44156952546</v>
       </c>
       <c r="S382">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T382" t="s">
         <v>249</v>
@@ -28505,7 +28508,7 @@
         <v>46233.50562820602</v>
       </c>
       <c r="S383">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T383" t="s">
         <v>250</v>
@@ -28576,7 +28579,7 @@
         <v>46233.80164280093</v>
       </c>
       <c r="S384">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T384" t="s">
         <v>246</v>
@@ -28647,7 +28650,7 @@
         <v>46232.72913953703</v>
       </c>
       <c r="S385">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T385" t="s">
         <v>245</v>
@@ -28697,7 +28700,7 @@
         <v>68</v>
       </c>
       <c r="J386" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L386" s="1">
         <v>46290</v>
@@ -28721,13 +28724,13 @@
         <v>46287.48083141204</v>
       </c>
       <c r="S386">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T386" t="s">
         <v>244</v>
       </c>
       <c r="W386" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AA386">
         <v>0</v>
@@ -28771,7 +28774,7 @@
         <v>68</v>
       </c>
       <c r="J387" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L387" s="1">
         <v>46295</v>
@@ -28792,7 +28795,7 @@
         <v>46283.6781059838</v>
       </c>
       <c r="S387">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="T387" t="s">
         <v>244</v>
@@ -28863,7 +28866,7 @@
         <v>46280.37528408565</v>
       </c>
       <c r="S388">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T388" t="s">
         <v>244</v>
@@ -28931,7 +28934,7 @@
         <v>46266.37634084491</v>
       </c>
       <c r="S389">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T389" t="s">
         <v>248</v>
@@ -28999,7 +29002,7 @@
         <v>46282.42251184028</v>
       </c>
       <c r="S390">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T390" t="s">
         <v>247</v>
@@ -29067,7 +29070,7 @@
         <v>46267.47452163194</v>
       </c>
       <c r="S391">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T391" t="s">
         <v>245</v>
@@ -29138,7 +29141,7 @@
         <v>46267.4745221412</v>
       </c>
       <c r="S392">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T392" t="s">
         <v>245</v>
@@ -29206,7 +29209,7 @@
         <v>46267.47452299768</v>
       </c>
       <c r="S393">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T393" t="s">
         <v>245</v>
@@ -29280,7 +29283,7 @@
         <v>46281.63558861111</v>
       </c>
       <c r="S394">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T394" t="s">
         <v>240</v>
@@ -29357,7 +29360,7 @@
         <v>46281.6358927662</v>
       </c>
       <c r="S395">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T395" t="s">
         <v>240</v>
@@ -29434,7 +29437,7 @@
         <v>46281.47564895833</v>
       </c>
       <c r="S396">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T396" t="s">
         <v>241</v>
@@ -29505,7 +29508,7 @@
         <v>46268.58940019676</v>
       </c>
       <c r="S397">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T397" t="s">
         <v>247</v>
@@ -29576,7 +29579,7 @@
         <v>46279.66710767361</v>
       </c>
       <c r="S398">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T398" t="s">
         <v>245</v>
@@ -29650,7 +29653,7 @@
         <v>46282.47420876157</v>
       </c>
       <c r="S399">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T399" t="s">
         <v>244</v>
@@ -29718,7 +29721,7 @@
         <v>46281.68877074074</v>
       </c>
       <c r="S400">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T400" t="s">
         <v>246</v>
@@ -29795,7 +29798,7 @@
         <v>46280.57958537037</v>
       </c>
       <c r="S401">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T401" t="s">
         <v>239</v>
@@ -29872,7 +29875,7 @@
         <v>46281.63570936343</v>
       </c>
       <c r="S402">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T402" t="s">
         <v>240</v>
@@ -29949,7 +29952,7 @@
         <v>46281.63595871528</v>
       </c>
       <c r="S403">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T403" t="s">
         <v>240</v>
@@ -30023,7 +30026,7 @@
         <v>46279.62681744213</v>
       </c>
       <c r="S404">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T404" t="s">
         <v>247</v>
@@ -30091,7 +30094,7 @@
         <v>46279.66707821759</v>
       </c>
       <c r="S405">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T405" t="s">
         <v>245</v>
@@ -30165,7 +30168,7 @@
         <v>46286.7220354051</v>
       </c>
       <c r="S406">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T406" t="s">
         <v>241</v>
@@ -30236,7 +30239,7 @@
         <v>46282.47437324074</v>
       </c>
       <c r="S407">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T407" t="s">
         <v>244</v>
@@ -30304,7 +30307,7 @@
         <v>46281.68880230324</v>
       </c>
       <c r="S408">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T408" t="s">
         <v>246</v>
@@ -30381,7 +30384,7 @@
         <v>46280.57972293982</v>
       </c>
       <c r="S409">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T409" t="s">
         <v>239</v>
@@ -30458,7 +30461,7 @@
         <v>46281.63575075231</v>
       </c>
       <c r="S410">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T410" t="s">
         <v>240</v>
@@ -30535,7 +30538,7 @@
         <v>46281.63599785879</v>
       </c>
       <c r="S411">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T411" t="s">
         <v>240</v>
@@ -30609,7 +30612,7 @@
         <v>46279.6268503125</v>
       </c>
       <c r="S412">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T412" t="s">
         <v>247</v>
@@ -30677,7 +30680,7 @@
         <v>46279.66698128472</v>
       </c>
       <c r="S413">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T413" t="s">
         <v>245</v>
@@ -30751,7 +30754,7 @@
         <v>46286.7221544213</v>
       </c>
       <c r="S414">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T414" t="s">
         <v>241</v>
@@ -30822,7 +30825,7 @@
         <v>46279.66929922454</v>
       </c>
       <c r="S415">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T415" t="s">
         <v>244</v>
@@ -30890,7 +30893,7 @@
         <v>46280.61353684028</v>
       </c>
       <c r="S416">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T416" t="s">
         <v>248</v>
@@ -30961,7 +30964,7 @@
         <v>46280.61353920139</v>
       </c>
       <c r="S417">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T417" t="s">
         <v>246</v>
@@ -31035,7 +31038,7 @@
         <v>46279.63250563657</v>
       </c>
       <c r="S418">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T418" t="s">
         <v>239</v>
@@ -31109,7 +31112,7 @@
         <v>46280.61354019676</v>
       </c>
       <c r="S419">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T419" t="s">
         <v>240</v>
@@ -31183,7 +31186,7 @@
         <v>46280.6135403125</v>
       </c>
       <c r="S420">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T420" t="s">
         <v>240</v>
@@ -31260,7 +31263,7 @@
         <v>46281.71218414352</v>
       </c>
       <c r="S421">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T421" t="s">
         <v>247</v>
@@ -31331,7 +31334,7 @@
         <v>46281.41576883102</v>
       </c>
       <c r="S422">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T422" t="s">
         <v>245</v>
@@ -31405,7 +31408,7 @@
         <v>46280.43132989584</v>
       </c>
       <c r="S423">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T423" t="s">
         <v>241</v>
@@ -31476,7 +31479,7 @@
         <v>46280.61367623843</v>
       </c>
       <c r="S424">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T424" t="s">
         <v>242</v>
@@ -31550,7 +31553,7 @@
         <v>46286.71510853009</v>
       </c>
       <c r="S425">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T425" t="s">
         <v>244</v>
@@ -31621,7 +31624,7 @@
         <v>46283.59424842593</v>
       </c>
       <c r="S426">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T426" t="s">
         <v>246</v>
@@ -31698,7 +31701,7 @@
         <v>46283.68435655093</v>
       </c>
       <c r="S427">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T427" t="s">
         <v>239</v>
@@ -31775,7 +31778,7 @@
         <v>46283.5942487037</v>
       </c>
       <c r="S428">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T428" t="s">
         <v>240</v>
@@ -31852,7 +31855,7 @@
         <v>46283.59424924768</v>
       </c>
       <c r="S429">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T429" t="s">
         <v>240</v>
@@ -31929,7 +31932,7 @@
         <v>46283.68161918982</v>
       </c>
       <c r="S430">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T430" t="s">
         <v>247</v>
@@ -32003,7 +32006,7 @@
         <v>46286.6489187037</v>
       </c>
       <c r="S431">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T431" t="s">
         <v>245</v>
@@ -32080,7 +32083,7 @@
         <v>46282.42048836806</v>
       </c>
       <c r="S432">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T432" t="s">
         <v>248</v>
@@ -32151,7 +32154,7 @@
         <v>46282.42138976852</v>
       </c>
       <c r="S433">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T433" t="s">
         <v>248</v>
@@ -32219,7 +32222,7 @@
         <v>46279.66936339121</v>
       </c>
       <c r="S434">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T434" t="s">
         <v>244</v>
@@ -32284,7 +32287,7 @@
         <v>46264.0028866088</v>
       </c>
       <c r="S435">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T435" t="s">
         <v>248</v>
@@ -32352,7 +32355,7 @@
         <v>46279.62931917824</v>
       </c>
       <c r="S436">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T436" t="s">
         <v>246</v>
@@ -32423,7 +32426,7 @@
         <v>46279.40189447917</v>
       </c>
       <c r="S437">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T437" t="s">
         <v>239</v>
@@ -32494,7 +32497,7 @@
         <v>46279.62936614583</v>
       </c>
       <c r="S438">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T438" t="s">
         <v>240</v>
@@ -32565,7 +32568,7 @@
         <v>46279.62936509259</v>
       </c>
       <c r="S439">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T439" t="s">
         <v>240</v>
@@ -32636,7 +32639,7 @@
         <v>46276.63187607639</v>
       </c>
       <c r="S440">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T440" t="s">
         <v>245</v>
@@ -32707,7 +32710,7 @@
         <v>46279.62658503472</v>
       </c>
       <c r="S441">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T441" t="s">
         <v>241</v>
@@ -32775,7 +32778,7 @@
         <v>46279.63255474537</v>
       </c>
       <c r="S442">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T442" t="s">
         <v>242</v>
@@ -32840,7 +32843,7 @@
         <v>46256.00536641204</v>
       </c>
       <c r="S443">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T443" t="s">
         <v>246</v>
@@ -32905,7 +32908,7 @@
         <v>46256.00539434027</v>
       </c>
       <c r="S444">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T444" t="s">
         <v>245</v>
@@ -32970,7 +32973,7 @@
         <v>46256.00540109954</v>
       </c>
       <c r="S445">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T445" t="s">
         <v>241</v>
@@ -33035,7 +33038,7 @@
         <v>46286.6987844213</v>
       </c>
       <c r="S446">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T446" t="s">
         <v>240</v>
@@ -33109,7 +33112,7 @@
         <v>46279.66713805556</v>
       </c>
       <c r="S447">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T447" t="s">
         <v>245</v>
@@ -33183,7 +33186,7 @@
         <v>46287.45807677083</v>
       </c>
       <c r="S448">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T448" t="s">
         <v>244</v>
@@ -33251,7 +33254,7 @@
         <v>46281.63317659722</v>
       </c>
       <c r="S449">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T449" t="s">
         <v>246</v>
@@ -33325,7 +33328,7 @@
         <v>46286.74096042824</v>
       </c>
       <c r="S450">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T450" t="s">
         <v>242</v>
@@ -33396,7 +33399,7 @@
         <v>46267.72055925926</v>
       </c>
       <c r="S451">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T451" t="s">
         <v>239</v>
@@ -33467,7 +33470,7 @@
         <v>46267.79441380787</v>
       </c>
       <c r="S452">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T452" t="s">
         <v>240</v>
@@ -33535,7 +33538,7 @@
         <v>46267.79441215278</v>
       </c>
       <c r="S453">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T453" t="s">
         <v>242</v>
@@ -33603,7 +33606,7 @@
         <v>46283.3939177662</v>
       </c>
       <c r="S454">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T454" t="s">
         <v>239</v>
@@ -33677,7 +33680,7 @@
         <v>46286.64017539352</v>
       </c>
       <c r="S455">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T455" t="s">
         <v>240</v>
@@ -33751,7 +33754,7 @@
         <v>46286.7204416551</v>
       </c>
       <c r="S456">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T456" t="s">
         <v>242</v>
@@ -33825,7 +33828,7 @@
         <v>46280.62789608796</v>
       </c>
       <c r="S457">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T457" t="s">
         <v>243</v>
@@ -33899,7 +33902,7 @@
         <v>46280.63189497685</v>
       </c>
       <c r="S458">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T458" t="s">
         <v>243</v>
@@ -33970,7 +33973,7 @@
         <v>46283.66538607639</v>
       </c>
       <c r="S459">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T459" t="s">
         <v>239</v>
@@ -34044,7 +34047,7 @@
         <v>46286.43482986111</v>
       </c>
       <c r="S460">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T460" t="s">
         <v>240</v>
@@ -34115,7 +34118,7 @@
         <v>46286.74368133102</v>
       </c>
       <c r="S461">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T461" t="s">
         <v>242</v>
@@ -34186,7 +34189,7 @@
         <v>46265.00319547454</v>
       </c>
       <c r="S462">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T462" t="s">
         <v>240</v>
@@ -34257,7 +34260,7 @@
         <v>46276.37795540509</v>
       </c>
       <c r="S463">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T463" t="s">
         <v>241</v>
@@ -34322,7 +34325,7 @@
         <v>46283.41459880787</v>
       </c>
       <c r="S464">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T464" t="s">
         <v>240</v>
@@ -34396,7 +34399,7 @@
         <v>46283.73838344908</v>
       </c>
       <c r="S465">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T465" t="s">
         <v>241</v>
@@ -34443,7 +34446,7 @@
         <v>70</v>
       </c>
       <c r="J466" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="L466" s="1">
         <v>46287</v>
@@ -34464,7 +34467,7 @@
         <v>46286.76327152778</v>
       </c>
       <c r="S466">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T466" t="s">
         <v>243</v>
@@ -34514,7 +34517,7 @@
         <v>70</v>
       </c>
       <c r="J467" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="L467" s="1">
         <v>46287</v>
@@ -34535,7 +34538,7 @@
         <v>46286.76330447917</v>
       </c>
       <c r="S467">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T467" t="s">
         <v>243</v>
@@ -34585,7 +34588,7 @@
         <v>70</v>
       </c>
       <c r="J468" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="L468" s="1">
         <v>46287</v>
@@ -34609,7 +34612,7 @@
         <v>46287.42040790509</v>
       </c>
       <c r="S468">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T468" t="s">
         <v>239</v>
@@ -34662,7 +34665,7 @@
         <v>70</v>
       </c>
       <c r="J469" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="L469" s="1">
         <v>46287</v>
@@ -34683,7 +34686,7 @@
         <v>46283.75381304398</v>
       </c>
       <c r="S469">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T469" t="s">
         <v>240</v>
@@ -34757,7 +34760,7 @@
         <v>46287.67534456019</v>
       </c>
       <c r="S470">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T470" t="s">
         <v>239</v>
@@ -34831,7 +34834,7 @@
         <v>46282.74485532408</v>
       </c>
       <c r="S471">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T471" t="s">
         <v>240</v>
@@ -34902,7 +34905,7 @@
         <v>46280.66345891204</v>
       </c>
       <c r="S472">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T472" t="s">
         <v>240</v>
@@ -34976,7 +34979,7 @@
         <v>46283.39413969908</v>
       </c>
       <c r="S473">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T473" t="s">
         <v>239</v>
@@ -35050,7 +35053,7 @@
         <v>46286.72051887732</v>
       </c>
       <c r="S474">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T474" t="s">
         <v>242</v>
@@ -35100,7 +35103,7 @@
         <v>71</v>
       </c>
       <c r="J475" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L475" s="1">
         <v>46289</v>
@@ -35124,13 +35127,13 @@
         <v>46283.54620269676</v>
       </c>
       <c r="S475">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T475" t="s">
         <v>244</v>
       </c>
       <c r="W475" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AA475">
         <v>0</v>
@@ -35198,7 +35201,7 @@
         <v>46287.46001957176</v>
       </c>
       <c r="S476">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T476" t="s">
         <v>244</v>
@@ -35272,7 +35275,7 @@
         <v>46287.46001266204</v>
       </c>
       <c r="S477">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T477" t="s">
         <v>248</v>
@@ -35346,7 +35349,7 @@
         <v>46286.72594498843</v>
       </c>
       <c r="S478">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T478" t="s">
         <v>246</v>
@@ -35423,7 +35426,7 @@
         <v>46282.70138376157</v>
       </c>
       <c r="S479">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T479" t="s">
         <v>245</v>
@@ -35500,7 +35503,7 @@
         <v>46282.7013840625</v>
       </c>
       <c r="S480">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T480" t="s">
         <v>245</v>
@@ -35571,7 +35574,7 @@
         <v>46283.75077045139</v>
       </c>
       <c r="S481">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T481" t="s">
         <v>247</v>
@@ -35645,7 +35648,7 @@
         <v>46286.36164050926</v>
       </c>
       <c r="S482">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T482" t="s">
         <v>245</v>
@@ -35722,7 +35725,7 @@
         <v>46286.36164494213</v>
       </c>
       <c r="S483">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T483" t="s">
         <v>244</v>
@@ -35796,7 +35799,7 @@
         <v>46286.36164826389</v>
       </c>
       <c r="S484">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T484" t="s">
         <v>248</v>
@@ -35867,7 +35870,7 @@
         <v>46280.59788275463</v>
       </c>
       <c r="S485">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T485" t="s">
         <v>246</v>
@@ -35941,7 +35944,7 @@
         <v>46266.45957931713</v>
       </c>
       <c r="S486">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T486" t="s">
         <v>245</v>
@@ -36012,7 +36015,7 @@
         <v>46283.35452896991</v>
       </c>
       <c r="S487">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T487" t="s">
         <v>245</v>
@@ -36083,7 +36086,7 @@
         <v>46283.35453171296</v>
       </c>
       <c r="S488">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T488" t="s">
         <v>245</v>
@@ -36157,7 +36160,7 @@
         <v>46240.6829959838</v>
       </c>
       <c r="S489">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T489" t="s">
         <v>248</v>
@@ -36228,7 +36231,7 @@
         <v>46287.36782538195</v>
       </c>
       <c r="S490">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T490" t="s">
         <v>247</v>
@@ -36278,7 +36281,7 @@
         <v>71</v>
       </c>
       <c r="J491" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="L491" s="1">
         <v>46287</v>
@@ -36302,7 +36305,7 @@
         <v>46287.42044105324</v>
       </c>
       <c r="S491">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T491" t="s">
         <v>248</v>
@@ -36352,7 +36355,7 @@
         <v>71</v>
       </c>
       <c r="J492" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="L492" s="1">
         <v>46287</v>
@@ -36376,7 +36379,7 @@
         <v>46287.75597989583</v>
       </c>
       <c r="S492">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T492" t="s">
         <v>244</v>
@@ -36447,7 +36450,7 @@
         <v>46283.38367943287</v>
       </c>
       <c r="S493">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T493" t="s">
         <v>244</v>
@@ -36518,7 +36521,7 @@
         <v>46282.54038741898</v>
       </c>
       <c r="S494">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T494" t="s">
         <v>248</v>
@@ -36592,7 +36595,7 @@
         <v>46280.74859975695</v>
       </c>
       <c r="S495">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T495" t="s">
         <v>244</v>
@@ -36666,7 +36669,7 @@
         <v>46283.64213659722</v>
       </c>
       <c r="S496">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T496" t="s">
         <v>240</v>
@@ -36740,7 +36743,7 @@
         <v>46283.65291121528</v>
       </c>
       <c r="S497">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T497" t="s">
         <v>245</v>
@@ -36811,7 +36814,7 @@
         <v>46283.65291194445</v>
       </c>
       <c r="S498">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T498" t="s">
         <v>245</v>
@@ -36885,7 +36888,7 @@
         <v>46286.39955256944</v>
       </c>
       <c r="S499">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T499" t="s">
         <v>241</v>
@@ -36953,7 +36956,7 @@
         <v>46286.42397924769</v>
       </c>
       <c r="S500">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T500" t="s">
         <v>244</v>
@@ -37018,7 +37021,7 @@
         <v>46023.15052320602</v>
       </c>
       <c r="S501">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T501" t="s">
         <v>250</v>
@@ -37086,7 +37089,7 @@
         <v>46286.42389136574</v>
       </c>
       <c r="S502">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T502" t="s">
         <v>248</v>
@@ -37157,7 +37160,7 @@
         <v>46283.67999300926</v>
       </c>
       <c r="S503">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T503" t="s">
         <v>240</v>
@@ -37231,7 +37234,7 @@
         <v>46286.42398471065</v>
       </c>
       <c r="S504">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T504" t="s">
         <v>247</v>
@@ -37299,7 +37302,7 @@
         <v>46286.42398568287</v>
       </c>
       <c r="S505">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T505" t="s">
         <v>245</v>
@@ -37373,7 +37376,7 @@
         <v>46283.67625043981</v>
       </c>
       <c r="S506">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T506" t="s">
         <v>241</v>
@@ -37438,7 +37441,7 @@
         <v>46023.15053086806</v>
       </c>
       <c r="S507">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T507" t="s">
         <v>250</v>
@@ -37506,7 +37509,7 @@
         <v>46266.25364633102</v>
       </c>
       <c r="S508">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T508" t="s">
         <v>247</v>
@@ -37574,7 +37577,7 @@
         <v>46057.39080065972</v>
       </c>
       <c r="S509">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T509" t="s">
         <v>245</v>
@@ -37642,7 +37645,7 @@
         <v>46266.25369826389</v>
       </c>
       <c r="S510">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T510" t="s">
         <v>242</v>
@@ -37710,7 +37713,7 @@
         <v>46266.25305112269</v>
       </c>
       <c r="S511">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T511" t="s">
         <v>244</v>
@@ -37778,7 +37781,7 @@
         <v>46266.25275173611</v>
       </c>
       <c r="S512">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T512" t="s">
         <v>240</v>
@@ -37849,7 +37852,7 @@
         <v>46266.25364869213</v>
       </c>
       <c r="S513">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T513" t="s">
         <v>245</v>
@@ -37923,7 +37926,7 @@
         <v>46283.38329579861</v>
       </c>
       <c r="S514">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T514" t="s">
         <v>245</v>
@@ -37991,7 +37994,7 @@
         <v>46168.72822087963</v>
       </c>
       <c r="S515">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T515" t="s">
         <v>241</v>
@@ -38056,7 +38059,7 @@
         <v>46266.25369988426</v>
       </c>
       <c r="S516">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T516" t="s">
         <v>242</v>
@@ -38124,7 +38127,7 @@
         <v>46192.56687822917</v>
       </c>
       <c r="S517">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T517" t="s">
         <v>243</v>
@@ -38189,7 +38192,7 @@
         <v>46192.56342662037</v>
       </c>
       <c r="S518">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T518" t="s">
         <v>243</v>
@@ -38257,7 +38260,7 @@
         <v>46282.36440621527</v>
       </c>
       <c r="S519">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T519" t="s">
         <v>244</v>
@@ -38328,7 +38331,7 @@
         <v>46282.36462596065</v>
       </c>
       <c r="S520">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T520" t="s">
         <v>248</v>
@@ -38399,7 +38402,7 @@
         <v>46282.36464421296</v>
       </c>
       <c r="S521">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T521" t="s">
         <v>246</v>
@@ -38473,7 +38476,7 @@
         <v>46282.36467337963</v>
       </c>
       <c r="S522">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T522" t="s">
         <v>239</v>
@@ -38547,7 +38550,7 @@
         <v>46282.36469679398</v>
       </c>
       <c r="S523">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T523" t="s">
         <v>240</v>
@@ -38621,7 +38624,7 @@
         <v>46282.36469869213</v>
       </c>
       <c r="S524">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T524" t="s">
         <v>240</v>
@@ -38695,7 +38698,7 @@
         <v>46282.36473159722</v>
       </c>
       <c r="S525">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T525" t="s">
         <v>247</v>
@@ -38766,7 +38769,7 @@
         <v>46282.36473394676</v>
       </c>
       <c r="S526">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T526" t="s">
         <v>245</v>
@@ -38840,7 +38843,7 @@
         <v>46282.36473579861</v>
       </c>
       <c r="S527">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T527" t="s">
         <v>245</v>
@@ -38911,7 +38914,7 @@
         <v>46282.36475297454</v>
       </c>
       <c r="S528">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T528" t="s">
         <v>245</v>
@@ -38985,7 +38988,7 @@
         <v>46282.36486408565</v>
       </c>
       <c r="S529">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T529" t="s">
         <v>241</v>
@@ -39056,7 +39059,7 @@
         <v>46282.36487561343</v>
       </c>
       <c r="S530">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T530" t="s">
         <v>242</v>
@@ -39127,7 +39130,7 @@
         <v>46282.36486778935</v>
       </c>
       <c r="S531">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T531" t="s">
         <v>243</v>
@@ -39198,7 +39201,7 @@
         <v>46282.36486851852</v>
       </c>
       <c r="S532">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T532" t="s">
         <v>243</v>
@@ -39269,7 +39272,7 @@
         <v>46286.45925082176</v>
       </c>
       <c r="S533">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T533" t="s">
         <v>244</v>
@@ -39340,7 +39343,7 @@
         <v>46282.79619427084</v>
       </c>
       <c r="S534">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T534" t="s">
         <v>248</v>
@@ -39411,7 +39414,7 @@
         <v>46282.79620872685</v>
       </c>
       <c r="S535">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T535" t="s">
         <v>246</v>
@@ -39485,7 +39488,7 @@
         <v>46282.79623825232</v>
       </c>
       <c r="S536">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T536" t="s">
         <v>239</v>
@@ -39559,7 +39562,7 @@
         <v>46282.7962541551</v>
       </c>
       <c r="S537">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T537" t="s">
         <v>240</v>
@@ -39633,7 +39636,7 @@
         <v>46282.7962703125</v>
       </c>
       <c r="S538">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T538" t="s">
         <v>240</v>
@@ -39707,7 +39710,7 @@
         <v>46282.79628381944</v>
       </c>
       <c r="S539">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T539" t="s">
         <v>247</v>
@@ -39778,7 +39781,7 @@
         <v>46282.79630119213</v>
       </c>
       <c r="S540">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T540" t="s">
         <v>245</v>
@@ -39852,7 +39855,7 @@
         <v>46282.79631224537</v>
       </c>
       <c r="S541">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T541" t="s">
         <v>245</v>
@@ -39923,7 +39926,7 @@
         <v>46282.79637734954</v>
       </c>
       <c r="S542">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T542" t="s">
         <v>241</v>
@@ -39994,7 +39997,7 @@
         <v>46282.79638922454</v>
       </c>
       <c r="S543">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T543" t="s">
         <v>242</v>
@@ -40065,7 +40068,7 @@
         <v>46282.3651903588</v>
       </c>
       <c r="S544">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T544" t="s">
         <v>244</v>
@@ -40136,7 +40139,7 @@
         <v>46282.36525856482</v>
       </c>
       <c r="S545">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T545" t="s">
         <v>248</v>
@@ -40207,7 +40210,7 @@
         <v>46282.36526855324</v>
       </c>
       <c r="S546">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T546" t="s">
         <v>246</v>
@@ -40281,7 +40284,7 @@
         <v>46282.36527959491</v>
       </c>
       <c r="S547">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T547" t="s">
         <v>239</v>
@@ -40355,7 +40358,7 @@
         <v>46282.36528526621</v>
       </c>
       <c r="S548">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T548" t="s">
         <v>240</v>
@@ -40429,7 +40432,7 @@
         <v>46282.36528619213</v>
       </c>
       <c r="S549">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T549" t="s">
         <v>240</v>
@@ -40503,7 +40506,7 @@
         <v>46282.36529351852</v>
       </c>
       <c r="S550">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T550" t="s">
         <v>247</v>
@@ -40574,7 +40577,7 @@
         <v>46282.36529424768</v>
       </c>
       <c r="S551">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T551" t="s">
         <v>245</v>
@@ -40648,7 +40651,7 @@
         <v>46282.36529490741</v>
       </c>
       <c r="S552">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T552" t="s">
         <v>245</v>
@@ -40719,7 +40722,7 @@
         <v>46282.36529869213</v>
       </c>
       <c r="S553">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T553" t="s">
         <v>245</v>
@@ -40793,7 +40796,7 @@
         <v>46282.36531149306</v>
       </c>
       <c r="S554">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T554" t="s">
         <v>241</v>
@@ -40864,7 +40867,7 @@
         <v>46282.36531554398</v>
       </c>
       <c r="S555">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T555" t="s">
         <v>242</v>
@@ -40935,7 +40938,7 @@
         <v>46282.36531253472</v>
       </c>
       <c r="S556">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T556" t="s">
         <v>243</v>
@@ -41006,7 +41009,7 @@
         <v>46282.36531288194</v>
       </c>
       <c r="S557">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T557" t="s">
         <v>243</v>
@@ -41077,7 +41080,7 @@
         <v>46286.45925106481</v>
       </c>
       <c r="S558">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T558" t="s">
         <v>244</v>
@@ -41148,7 +41151,7 @@
         <v>46282.79619331018</v>
       </c>
       <c r="S559">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T559" t="s">
         <v>248</v>
@@ -41219,7 +41222,7 @@
         <v>46282.79620888889</v>
       </c>
       <c r="S560">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T560" t="s">
         <v>246</v>
@@ -41293,7 +41296,7 @@
         <v>46282.79623803241</v>
       </c>
       <c r="S561">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T561" t="s">
         <v>239</v>
@@ -41367,7 +41370,7 @@
         <v>46282.79625384259</v>
       </c>
       <c r="S562">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T562" t="s">
         <v>240</v>
@@ -41441,7 +41444,7 @@
         <v>46282.79626969907</v>
       </c>
       <c r="S563">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T563" t="s">
         <v>240</v>
@@ -41515,7 +41518,7 @@
         <v>46282.79628394676</v>
       </c>
       <c r="S564">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T564" t="s">
         <v>247</v>
@@ -41586,7 +41589,7 @@
         <v>46282.79630097222</v>
       </c>
       <c r="S565">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T565" t="s">
         <v>245</v>
@@ -41660,7 +41663,7 @@
         <v>46282.79631204861</v>
       </c>
       <c r="S566">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T566" t="s">
         <v>245</v>
@@ -41731,7 +41734,7 @@
         <v>46282.79637748843</v>
       </c>
       <c r="S567">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T567" t="s">
         <v>241</v>
@@ -41802,7 +41805,7 @@
         <v>46282.79638901621</v>
       </c>
       <c r="S568">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T568" t="s">
         <v>242</v>
@@ -41849,7 +41852,7 @@
         <v>73</v>
       </c>
       <c r="J569" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L569" s="1">
         <v>46290</v>
@@ -41870,7 +41873,7 @@
         <v>46235.0433193287</v>
       </c>
       <c r="S569">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T569" t="s">
         <v>248</v>
@@ -41917,7 +41920,7 @@
         <v>73</v>
       </c>
       <c r="J570" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="L570" s="1">
         <v>46290</v>
@@ -41938,7 +41941,7 @@
         <v>46235.04371431713</v>
       </c>
       <c r="S570">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T570" t="s">
         <v>246</v>
@@ -42009,7 +42012,7 @@
         <v>46283.39832862269</v>
       </c>
       <c r="S571">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T571" t="s">
         <v>244</v>
@@ -42077,7 +42080,7 @@
         <v>46282.64018086805</v>
       </c>
       <c r="S572">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T572" t="s">
         <v>248</v>
@@ -42145,7 +42148,7 @@
         <v>46287.492834375</v>
       </c>
       <c r="S573">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T573" t="s">
         <v>244</v>
@@ -42213,7 +42216,7 @@
         <v>46287.49337789352</v>
       </c>
       <c r="S574">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T574" t="s">
         <v>243</v>
@@ -42281,7 +42284,7 @@
         <v>237</v>
       </c>
       <c r="S575">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T575" t="s">
         <v>251</v>
@@ -42349,7 +42352,7 @@
         <v>237</v>
       </c>
       <c r="S576">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T576" t="s">
         <v>251</v>
@@ -42417,7 +42420,7 @@
         <v>237</v>
       </c>
       <c r="S577">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T577" t="s">
         <v>252</v>
@@ -42485,7 +42488,7 @@
         <v>237</v>
       </c>
       <c r="S578">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T578" t="s">
         <v>241</v>
@@ -42547,7 +42550,7 @@
         <v>237</v>
       </c>
       <c r="S579">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T579" t="s">
         <v>253</v>
@@ -42612,7 +42615,7 @@
         <v>237</v>
       </c>
       <c r="S580">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T580" t="s">
         <v>253</v>
@@ -42677,7 +42680,7 @@
         <v>237</v>
       </c>
       <c r="S581">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T581" t="s">
         <v>253</v>
@@ -42712,19 +42715,19 @@
         <v>65</v>
       </c>
       <c r="G582">
-        <v>7884</v>
+        <v>1808</v>
       </c>
       <c r="H582">
-        <v>9114</v>
+        <v>0</v>
       </c>
       <c r="I582" t="s">
         <v>71</v>
       </c>
       <c r="J582" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="L582" s="1">
-        <v>46280</v>
+        <v>46287</v>
       </c>
       <c r="M582" t="s">
         <v>192</v>
@@ -42733,7 +42736,7 @@
         <v>203</v>
       </c>
       <c r="O582">
-        <v>18273949</v>
+        <v>18201041</v>
       </c>
       <c r="P582" t="s">
         <v>227</v>
@@ -42742,16 +42745,16 @@
         <v>237</v>
       </c>
       <c r="S582">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="T582" t="s">
         <v>254</v>
       </c>
       <c r="W582" t="s">
-        <v>444</v>
+        <v>344</v>
       </c>
       <c r="AG582" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AH582" t="s">
         <v>466</v>
@@ -42759,16 +42762,16 @@
     </row>
     <row r="583" spans="1:34">
       <c r="A583">
-        <v>7095</v>
+        <v>6981</v>
       </c>
       <c r="B583" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C583" t="s">
         <v>58</v>
       </c>
       <c r="D583" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E583" t="s">
         <v>62</v>
@@ -42777,60 +42780,63 @@
         <v>65</v>
       </c>
       <c r="G583">
-        <v>10880</v>
+        <v>7884</v>
       </c>
       <c r="H583">
-        <v>0</v>
+        <v>9114</v>
       </c>
       <c r="I583" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="J583" t="s">
-        <v>180</v>
+        <v>117</v>
       </c>
       <c r="L583" s="1">
-        <v>46286</v>
+        <v>46280</v>
       </c>
       <c r="M583" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N583" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O583">
-        <v>18272578</v>
+        <v>18273949</v>
       </c>
       <c r="P583" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="Q583" t="s">
         <v>237</v>
       </c>
       <c r="S583">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T583" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="W583" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG583" t="s">
         <v>457</v>
       </c>
+      <c r="AH583" t="s">
+        <v>466</v>
+      </c>
     </row>
     <row r="584" spans="1:34">
       <c r="A584">
-        <v>6981</v>
+        <v>7095</v>
       </c>
       <c r="B584" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C584" t="s">
         <v>58</v>
       </c>
       <c r="D584" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E584" t="s">
         <v>62</v>
@@ -42839,49 +42845,46 @@
         <v>65</v>
       </c>
       <c r="G584">
-        <v>1808</v>
+        <v>10880</v>
       </c>
       <c r="H584">
         <v>0</v>
       </c>
       <c r="I584" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="J584" t="s">
-        <v>143</v>
+        <v>180</v>
       </c>
       <c r="L584" s="1">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="M584" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="N584" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O584">
-        <v>18201041</v>
+        <v>18272578</v>
       </c>
       <c r="P584" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="Q584" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="S584">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T584" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="W584" t="s">
-        <v>352</v>
+        <v>445</v>
       </c>
       <c r="AG584" t="s">
-        <v>458</v>
-      </c>
-      <c r="AH584" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
     </row>
   </sheetData>

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8739" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8740" uniqueCount="467">
   <si>
     <t>CodCliente</t>
   </si>
@@ -415,73 +415,73 @@
     <t>Controle de Férias</t>
   </si>
   <si>
+    <t>Fed - PIS/COFINS Não Cumul/Mon - 5856</t>
+  </si>
+  <si>
+    <t>Fed - PIS/COFINS Cumulativo - 2172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Envio do Razão Conta - Valores à Classificar </t>
+  </si>
+  <si>
+    <t>Fed - DCTFWEB</t>
+  </si>
+  <si>
+    <t>Módulo de Inclusão Tributária (MIT)</t>
+  </si>
+  <si>
+    <t>Movimento - Analise de Balanço Lucro Presumido</t>
+  </si>
+  <si>
+    <t>Movimento - Analise de Balanço Lucro Real</t>
+  </si>
+  <si>
+    <t>Movimento - Analise de Balanço Simples Nacional</t>
+  </si>
+  <si>
+    <t>Rebto planilha/Resumo de Folha (28)</t>
+  </si>
+  <si>
+    <t>Est - DeSTDA</t>
+  </si>
+  <si>
+    <t>Est - ICMS SN - Diferencial Alíquota</t>
+  </si>
+  <si>
+    <t>Digitalização de NF Ativo</t>
+  </si>
+  <si>
+    <t>Confirm Rec - PIS/COFINS</t>
+  </si>
+  <si>
+    <t>Inclusão de Ata de Reunião</t>
+  </si>
+  <si>
+    <t>Fechamento Mensal</t>
+  </si>
+  <si>
+    <t>Fed - IRPJ/CSLL - 3ª Quota corrigida</t>
+  </si>
+  <si>
+    <t>Outras Receitas</t>
+  </si>
+  <si>
+    <t>Fed - DIRBI</t>
+  </si>
+  <si>
+    <t>Adiantamento Salarial (20)</t>
+  </si>
+  <si>
+    <t>Cartão de Ponto</t>
+  </si>
+  <si>
+    <t>Controle Afastamento</t>
+  </si>
+  <si>
+    <t>Envio de Impostos - DCTF Web</t>
+  </si>
+  <si>
     <t>Envio Planilha de Fechamento</t>
-  </si>
-  <si>
-    <t>Fed - PIS/COFINS Não Cumul/Mon - 5856</t>
-  </si>
-  <si>
-    <t>Fed - PIS/COFINS Cumulativo - 2172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Envio do Razão Conta - Valores à Classificar </t>
-  </si>
-  <si>
-    <t>Fed - DCTFWEB</t>
-  </si>
-  <si>
-    <t>Módulo de Inclusão Tributária (MIT)</t>
-  </si>
-  <si>
-    <t>Movimento - Analise de Balanço Lucro Presumido</t>
-  </si>
-  <si>
-    <t>Movimento - Analise de Balanço Lucro Real</t>
-  </si>
-  <si>
-    <t>Movimento - Analise de Balanço Simples Nacional</t>
-  </si>
-  <si>
-    <t>Rebto planilha/Resumo de Folha (28)</t>
-  </si>
-  <si>
-    <t>Est - DeSTDA</t>
-  </si>
-  <si>
-    <t>Est - ICMS SN - Diferencial Alíquota</t>
-  </si>
-  <si>
-    <t>Digitalização de NF Ativo</t>
-  </si>
-  <si>
-    <t>Confirm Rec - PIS/COFINS</t>
-  </si>
-  <si>
-    <t>Inclusão de Ata de Reunião</t>
-  </si>
-  <si>
-    <t>Fechamento Mensal</t>
-  </si>
-  <si>
-    <t>Fed - IRPJ/CSLL - 3ª Quota corrigida</t>
-  </si>
-  <si>
-    <t>Outras Receitas</t>
-  </si>
-  <si>
-    <t>Fed - DIRBI</t>
-  </si>
-  <si>
-    <t>Adiantamento Salarial (20)</t>
-  </si>
-  <si>
-    <t>Cartão de Ponto</t>
-  </si>
-  <si>
-    <t>Controle Afastamento</t>
-  </si>
-  <si>
-    <t>Envio de Impostos - DCTF Web</t>
   </si>
   <si>
     <t>Folha Pró-Lab/Autônomo</t>
@@ -1065,150 +1065,150 @@
 Em processamento, empresa passou a ser de responsabilidade da Roberta Souza - Data Comentário: 22/09/2026 16:17</t>
   </si>
   <si>
+    <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 23/09/2026 
+Em atendimento - Data Comentário: 22/09/2026 17:12</t>
+  </si>
+  <si>
+    <t>Atraso da Operação, processo em elaboração conforme data prevista   Previsão para conclusão dia 23/09/2026 - Data Comentário: 22/09/2026 17:40</t>
+  </si>
+  <si>
+    <t>Atraso da Operação, processo em elaboração conforme data prevista  Previsão para conclusão dia 23/09/2026 - Data Comentário: 22/09/2026 17:39</t>
+  </si>
+  <si>
+    <t>Comentário Colaborador + Previsão de Conclusão. Previsto para: 28/09/2026 - Data Comentário: 18/09/2026 15:26</t>
+  </si>
+  <si>
+    <t>Comentário Colaborador + Previsão de Conclusão. Previsto para: 25/09/2026 - Data Comentário: 18/09/2026 15:25</t>
+  </si>
+  <si>
+    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 30/09/2026 - Data Comentário: 15/09/2026 15:01</t>
+  </si>
+  <si>
+    <t>Comentário Colaborador + Previsão de Conclusão. Previsto para: 30/09/2026 - Data Comentário: 18/09/2026 15:27</t>
+  </si>
+  <si>
+    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 30/09/2026 - Data Comentário: 15/09/2026 15:03</t>
+  </si>
+  <si>
+    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 28/09/2026 
+aguardando cliente enviar - Data Comentário: 18/09/2026 15:32</t>
+  </si>
+  <si>
+    <t>Comentário Colaborador + Previsão de Conclusão. Previsto para: 24/09/2026 - Data Comentário: 18/09/2026 15:24</t>
+  </si>
+  <si>
+    <t>Comentário Colaborador + Previsão de Conclusão. Previsto para: 28/09/2026 - Data Comentário: 18/09/2026 15:27</t>
+  </si>
+  <si>
+    <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1808] sendo a ultima baixa feita [1808]-22/09/2026 18:08:36.. - Data Comentário: 22/09/2026 18:31</t>
+  </si>
+  <si>
+    <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1807] sendo a ultima baixa feita [1807]-22/09/2026 10:05:26.. - Data Comentário: 22/09/2026 12:56</t>
+  </si>
+  <si>
+    <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1882] sendo a ultima baixa feita [1882]-18/09/2026 18:05:29.. - Data Comentário: 21/09/2026 09:20</t>
+  </si>
+  <si>
+    <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1881] sendo a ultima baixa feita [1881]-21/09/2026 18:19:06.. - Data Comentário: 22/09/2026 09:15</t>
+  </si>
+  <si>
+    <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1881] sendo a ultima baixa feita [1881]-21/09/2026 18:19:09.. - Data Comentário: 22/09/2026 09:15</t>
+  </si>
+  <si>
+    <t>Comentário Colaborador + Previsão de Conclusão. Previsto para: 30/09/2026 - Data Comentário: 18/09/2026 15:28</t>
+  </si>
+  <si>
+    <t>Reaberto via API integração MGC x Analise Balanço em 18/09/2026 16:16:28. - Data Comentário: 21/09/2026 09:20</t>
+  </si>
+  <si>
+    <t>AGUARDANDO CONFIRMAÇÃO - Data Comentário: 21/09/2026 17:08</t>
+  </si>
+  <si>
+    <t>Tarefa baixada automaticamente, cliente baixado com prejuizo na 1 Quota. - Data Comentário: 31/07/2026 15:52</t>
+  </si>
+  <si>
+    <t>Tarefa baixada automaticamente, cliente baixado com prejuizo na 1 Quota. - Data Comentário: 11/08/2026 18:21</t>
+  </si>
+  <si>
+    <t>Comentário Colaborador + Previsão de Conclusão. Previsto para: 21/09/2026 - Data Comentário: 18/09/2026 15:23</t>
+  </si>
+  <si>
+    <t>Tarefa baixada automaticamente, cliente baixado com prejuizo na 1 Quota. - Data Comentário: 30/07/2026 12:07</t>
+  </si>
+  <si>
+    <t>Baixado via API integração MGC x Analise Balanço em 18/09/2026 16:20:21. - Data Comentário: 18/09/2026 16:15</t>
+  </si>
+  <si>
+    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 16/09/2026 - Data Comentário: 15/09/2026 09:23</t>
+  </si>
+  <si>
+    <t>1. Folha em Processamento  Previsão para conclusão dia 18/09/2026 - Data Comentário: 15/09/2026 09:24</t>
+  </si>
+  <si>
+    <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 18/09/2026 
+Em processamento. - Data Comentário: 14/09/2026 09:07</t>
+  </si>
+  <si>
+    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 17/09/2026 - Data Comentário: 15/09/2026 15:18</t>
+  </si>
+  <si>
+    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 15/09/2026 - Data Comentário: 10/09/2026 08:21</t>
+  </si>
+  <si>
+    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 22/09/2026 
+Em processamento, previsão de conclusão em 22/09/2026 - Data Comentário: 21/09/2026 09:45</t>
+  </si>
+  <si>
+    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 15/09/2026 - Data Comentário: 10/09/2026 08:22</t>
+  </si>
+  <si>
+    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 22/09/2026 
+Em processamento, previsão de conclusão em 22/09/2026 - Data Comentário: 21/09/2026 09:46</t>
+  </si>
+  <si>
+    <t>Imposto enviado via SCI Report - Data Comentário: 14/09/2026 15:49</t>
+  </si>
+  <si>
+    <t>Imposto enviado via SCI Report - Data Comentário: 15/09/2026 13:38</t>
+  </si>
+  <si>
+    <t>Imposto enviado via SCI Report - Data Comentário: 15/09/2026 11:45</t>
+  </si>
+  <si>
+    <t>Imposto enviado via SCI Report - Data Comentário: 14/09/2026 13:54</t>
+  </si>
+  <si>
+    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 16/09/2026 - Data Comentário: 16/09/2026 16:48</t>
+  </si>
+  <si>
+    <t>Imposto enviado via SCI Report - Data Comentário: 16/09/2026 08:55</t>
+  </si>
+  <si>
+    <t>Imposto enviado via SCI Report - Data Comentário: 15/09/2026 10:07</t>
+  </si>
+  <si>
+    <t>Imposto enviado via SCI Report - Data Comentário: 15/09/2026 11:25</t>
+  </si>
+  <si>
+    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 21/09/2026 
+em processo de emissão e liberação - Data Comentário: 18/09/2026 10:59</t>
+  </si>
+  <si>
+    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 18/09/2026 - Data Comentário: 15/09/2026 15:19</t>
+  </si>
+  <si>
+    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 18/09/2026 - Data Comentário: 10/09/2026 08:23</t>
+  </si>
+  <si>
+    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 18/09/2026 - Data Comentário: 14/09/2026 10:55</t>
+  </si>
+  <si>
+    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 21/09/2026 
+Em processamento. - Data Comentário: 15/09/2026 14:34</t>
+  </si>
+  <si>
     <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 23/09/2026 
 Em processamento, previsão de conclusão em 23/09/2026 - Data Comentário: 21/09/2026 09:48</t>
-  </si>
-  <si>
-    <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 23/09/2026 
-Em atendimento - Data Comentário: 22/09/2026 17:12</t>
-  </si>
-  <si>
-    <t>Atraso da Operação, processo em elaboração conforme data prevista   Previsão para conclusão dia 23/09/2026 - Data Comentário: 22/09/2026 17:40</t>
-  </si>
-  <si>
-    <t>Atraso da Operação, processo em elaboração conforme data prevista  Previsão para conclusão dia 23/09/2026 - Data Comentário: 22/09/2026 17:39</t>
-  </si>
-  <si>
-    <t>Comentário Colaborador + Previsão de Conclusão. Previsto para: 28/09/2026 - Data Comentário: 18/09/2026 15:26</t>
-  </si>
-  <si>
-    <t>Comentário Colaborador + Previsão de Conclusão. Previsto para: 25/09/2026 - Data Comentário: 18/09/2026 15:25</t>
-  </si>
-  <si>
-    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 30/09/2026 - Data Comentário: 15/09/2026 15:01</t>
-  </si>
-  <si>
-    <t>Comentário Colaborador + Previsão de Conclusão. Previsto para: 30/09/2026 - Data Comentário: 18/09/2026 15:27</t>
-  </si>
-  <si>
-    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 30/09/2026 - Data Comentário: 15/09/2026 15:03</t>
-  </si>
-  <si>
-    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 28/09/2026 
-aguardando cliente enviar - Data Comentário: 18/09/2026 15:32</t>
-  </si>
-  <si>
-    <t>Comentário Colaborador + Previsão de Conclusão. Previsto para: 24/09/2026 - Data Comentário: 18/09/2026 15:24</t>
-  </si>
-  <si>
-    <t>Comentário Colaborador + Previsão de Conclusão. Previsto para: 28/09/2026 - Data Comentário: 18/09/2026 15:27</t>
-  </si>
-  <si>
-    <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1808] sendo a ultima baixa feita [1808]-22/09/2026 18:08:36.. - Data Comentário: 22/09/2026 18:31</t>
-  </si>
-  <si>
-    <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1807] sendo a ultima baixa feita [1807]-22/09/2026 10:05:26.. - Data Comentário: 22/09/2026 12:56</t>
-  </si>
-  <si>
-    <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1882] sendo a ultima baixa feita [1882]-18/09/2026 18:05:29.. - Data Comentário: 21/09/2026 09:20</t>
-  </si>
-  <si>
-    <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1881] sendo a ultima baixa feita [1881]-21/09/2026 18:19:06.. - Data Comentário: 22/09/2026 09:15</t>
-  </si>
-  <si>
-    <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1881] sendo a ultima baixa feita [1881]-21/09/2026 18:19:09.. - Data Comentário: 22/09/2026 09:15</t>
-  </si>
-  <si>
-    <t>Comentário Colaborador + Previsão de Conclusão. Previsto para: 30/09/2026 - Data Comentário: 18/09/2026 15:28</t>
-  </si>
-  <si>
-    <t>Reaberto via API integração MGC x Analise Balanço em 18/09/2026 16:16:28. - Data Comentário: 21/09/2026 09:20</t>
-  </si>
-  <si>
-    <t>AGUARDANDO CONFIRMAÇÃO - Data Comentário: 21/09/2026 17:08</t>
-  </si>
-  <si>
-    <t>Tarefa baixada automaticamente, cliente baixado com prejuizo na 1 Quota. - Data Comentário: 31/07/2026 15:52</t>
-  </si>
-  <si>
-    <t>Tarefa baixada automaticamente, cliente baixado com prejuizo na 1 Quota. - Data Comentário: 11/08/2026 18:21</t>
-  </si>
-  <si>
-    <t>Comentário Colaborador + Previsão de Conclusão. Previsto para: 21/09/2026 - Data Comentário: 18/09/2026 15:23</t>
-  </si>
-  <si>
-    <t>Tarefa baixada automaticamente, cliente baixado com prejuizo na 1 Quota. - Data Comentário: 30/07/2026 12:07</t>
-  </si>
-  <si>
-    <t>Baixado via API integração MGC x Analise Balanço em 18/09/2026 16:20:21. - Data Comentário: 18/09/2026 16:15</t>
-  </si>
-  <si>
-    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 16/09/2026 - Data Comentário: 15/09/2026 09:23</t>
-  </si>
-  <si>
-    <t>1. Folha em Processamento  Previsão para conclusão dia 18/09/2026 - Data Comentário: 15/09/2026 09:24</t>
-  </si>
-  <si>
-    <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 18/09/2026 
-Em processamento. - Data Comentário: 14/09/2026 09:07</t>
-  </si>
-  <si>
-    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 17/09/2026 - Data Comentário: 15/09/2026 15:18</t>
-  </si>
-  <si>
-    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 15/09/2026 - Data Comentário: 10/09/2026 08:21</t>
-  </si>
-  <si>
-    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 22/09/2026 
-Em processamento, previsão de conclusão em 22/09/2026 - Data Comentário: 21/09/2026 09:45</t>
-  </si>
-  <si>
-    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 15/09/2026 - Data Comentário: 10/09/2026 08:22</t>
-  </si>
-  <si>
-    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 22/09/2026 
-Em processamento, previsão de conclusão em 22/09/2026 - Data Comentário: 21/09/2026 09:46</t>
-  </si>
-  <si>
-    <t>Imposto enviado via SCI Report - Data Comentário: 14/09/2026 15:49</t>
-  </si>
-  <si>
-    <t>Imposto enviado via SCI Report - Data Comentário: 15/09/2026 13:38</t>
-  </si>
-  <si>
-    <t>Imposto enviado via SCI Report - Data Comentário: 15/09/2026 11:45</t>
-  </si>
-  <si>
-    <t>Imposto enviado via SCI Report - Data Comentário: 14/09/2026 13:54</t>
-  </si>
-  <si>
-    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 16/09/2026 - Data Comentário: 16/09/2026 16:48</t>
-  </si>
-  <si>
-    <t>Imposto enviado via SCI Report - Data Comentário: 16/09/2026 08:55</t>
-  </si>
-  <si>
-    <t>Imposto enviado via SCI Report - Data Comentário: 15/09/2026 10:07</t>
-  </si>
-  <si>
-    <t>Imposto enviado via SCI Report - Data Comentário: 15/09/2026 11:25</t>
-  </si>
-  <si>
-    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 21/09/2026 
-em processo de emissão e liberação - Data Comentário: 18/09/2026 10:59</t>
-  </si>
-  <si>
-    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 18/09/2026 - Data Comentário: 15/09/2026 15:19</t>
-  </si>
-  <si>
-    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 18/09/2026 - Data Comentário: 10/09/2026 08:23</t>
-  </si>
-  <si>
-    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 18/09/2026 - Data Comentário: 14/09/2026 10:55</t>
-  </si>
-  <si>
-    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 21/09/2026 
-Em processamento. - Data Comentário: 15/09/2026 14:34</t>
   </si>
   <si>
     <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 18/09/2026 
@@ -22481,16 +22481,16 @@
     </row>
     <row r="296" spans="1:34">
       <c r="A296">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B296" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C296" t="s">
         <v>58</v>
       </c>
       <c r="D296" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E296" t="s">
         <v>62</v>
@@ -22499,40 +22499,40 @@
         <v>65</v>
       </c>
       <c r="G296">
-        <v>5836</v>
+        <v>1882</v>
       </c>
       <c r="H296">
-        <v>5784</v>
+        <v>0</v>
       </c>
       <c r="I296" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J296" t="s">
         <v>133</v>
       </c>
       <c r="L296" s="1">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="M296" t="s">
         <v>192</v>
       </c>
       <c r="N296" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O296">
-        <v>18179083</v>
+        <v>18214871</v>
       </c>
       <c r="P296" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="Q296" t="s">
         <v>237</v>
       </c>
       <c r="S296">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T296" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="W296" t="s">
         <v>341</v>
@@ -22541,39 +22541,39 @@
         <v>0</v>
       </c>
       <c r="AG296" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AH296" t="s">
-        <v>464</v>
+        <v>450</v>
       </c>
     </row>
     <row r="297" spans="1:34">
       <c r="A297">
-        <v>6949</v>
+        <v>6703</v>
       </c>
       <c r="B297" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C297" t="s">
         <v>58</v>
       </c>
       <c r="D297" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E297" t="s">
         <v>62</v>
       </c>
       <c r="F297" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G297">
-        <v>1882</v>
+        <v>1807</v>
       </c>
       <c r="H297">
         <v>0</v>
       </c>
       <c r="I297" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J297" t="s">
         <v>134</v>
@@ -22588,10 +22588,10 @@
         <v>203</v>
       </c>
       <c r="O297">
-        <v>18214871</v>
+        <v>17948806</v>
       </c>
       <c r="P297" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q297" t="s">
         <v>237</v>
@@ -22600,7 +22600,7 @@
         <v>1</v>
       </c>
       <c r="T297" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="W297" t="s">
         <v>342</v>
@@ -22612,21 +22612,21 @@
         <v>458</v>
       </c>
       <c r="AH297" t="s">
-        <v>450</v>
+        <v>466</v>
       </c>
     </row>
     <row r="298" spans="1:34">
       <c r="A298">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B298" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C298" t="s">
         <v>58</v>
       </c>
       <c r="D298" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E298" t="s">
         <v>62</v>
@@ -22635,7 +22635,7 @@
         <v>64</v>
       </c>
       <c r="G298">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="H298">
         <v>0</v>
@@ -22644,7 +22644,7 @@
         <v>71</v>
       </c>
       <c r="J298" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L298" s="1">
         <v>46287</v>
@@ -22656,7 +22656,7 @@
         <v>203</v>
       </c>
       <c r="O298">
-        <v>17948806</v>
+        <v>18085209</v>
       </c>
       <c r="P298" t="s">
         <v>227</v>
@@ -22668,7 +22668,10 @@
         <v>1</v>
       </c>
       <c r="T298" t="s">
-        <v>247</v>
+        <v>245</v>
+      </c>
+      <c r="V298" t="s">
+        <v>255</v>
       </c>
       <c r="W298" t="s">
         <v>343</v>
@@ -22685,10 +22688,10 @@
     </row>
     <row r="299" spans="1:34">
       <c r="A299">
-        <v>6704</v>
+        <v>6627</v>
       </c>
       <c r="B299" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C299" t="s">
         <v>58</v>
@@ -22697,46 +22700,46 @@
         <v>59</v>
       </c>
       <c r="E299" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F299" t="s">
         <v>64</v>
       </c>
       <c r="G299">
-        <v>1808</v>
+        <v>7869</v>
       </c>
       <c r="H299">
         <v>0</v>
       </c>
       <c r="I299" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="J299" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L299" s="1">
-        <v>46287</v>
+        <v>46293</v>
       </c>
       <c r="M299" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N299" t="s">
         <v>203</v>
       </c>
       <c r="O299">
-        <v>18085209</v>
+        <v>17042546</v>
       </c>
       <c r="P299" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="Q299" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="S299">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="T299" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="V299" t="s">
         <v>255</v>
@@ -22748,24 +22751,24 @@
         <v>0</v>
       </c>
       <c r="AG299" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AH299" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
     </row>
     <row r="300" spans="1:34">
       <c r="A300">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B300" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C300" t="s">
         <v>58</v>
       </c>
       <c r="D300" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E300" t="s">
         <v>63</v>
@@ -22783,7 +22786,7 @@
         <v>67</v>
       </c>
       <c r="J300" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L300" s="1">
         <v>46293</v>
@@ -22795,7 +22798,7 @@
         <v>203</v>
       </c>
       <c r="O300">
-        <v>17042546</v>
+        <v>16960048</v>
       </c>
       <c r="P300" t="s">
         <v>209</v>
@@ -22813,7 +22816,7 @@
         <v>255</v>
       </c>
       <c r="W300" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AA300">
         <v>0</v>
@@ -22827,22 +22830,22 @@
     </row>
     <row r="301" spans="1:34">
       <c r="A301">
-        <v>6628</v>
+        <v>6949</v>
       </c>
       <c r="B301" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C301" t="s">
         <v>58</v>
       </c>
       <c r="D301" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E301" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F301" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G301">
         <v>7869</v>
@@ -22854,7 +22857,7 @@
         <v>67</v>
       </c>
       <c r="J301" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L301" s="1">
         <v>46293</v>
@@ -22866,10 +22869,10 @@
         <v>203</v>
       </c>
       <c r="O301">
-        <v>16960048</v>
+        <v>18178300</v>
       </c>
       <c r="P301" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Q301" t="s">
         <v>238</v>
@@ -22878,13 +22881,10 @@
         <v>-5</v>
       </c>
       <c r="T301" t="s">
-        <v>240</v>
-      </c>
-      <c r="V301" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="W301" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AA301">
         <v>0</v>
@@ -22893,15 +22893,15 @@
         <v>457</v>
       </c>
       <c r="AH301" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="302" spans="1:34">
       <c r="A302">
-        <v>6949</v>
+        <v>6548</v>
       </c>
       <c r="B302" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C302" t="s">
         <v>58</v>
@@ -22913,10 +22913,10 @@
         <v>62</v>
       </c>
       <c r="F302" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G302">
-        <v>7869</v>
+        <v>6892</v>
       </c>
       <c r="H302">
         <v>0</v>
@@ -22928,16 +22928,16 @@
         <v>136</v>
       </c>
       <c r="L302" s="1">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="M302" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N302" t="s">
         <v>203</v>
       </c>
       <c r="O302">
-        <v>18178300</v>
+        <v>17968017</v>
       </c>
       <c r="P302" t="s">
         <v>208</v>
@@ -22946,10 +22946,13 @@
         <v>238</v>
       </c>
       <c r="S302">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="T302" t="s">
-        <v>242</v>
+        <v>239</v>
+      </c>
+      <c r="V302" t="s">
+        <v>255</v>
       </c>
       <c r="W302" t="s">
         <v>345</v>
@@ -22958,7 +22961,7 @@
         <v>0</v>
       </c>
       <c r="AG302" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AH302" t="s">
         <v>460</v>
@@ -22966,10 +22969,10 @@
     </row>
     <row r="303" spans="1:34">
       <c r="A303">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B303" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C303" t="s">
         <v>58</v>
@@ -22978,7 +22981,7 @@
         <v>59</v>
       </c>
       <c r="E303" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F303" t="s">
         <v>64</v>
@@ -22993,7 +22996,7 @@
         <v>67</v>
       </c>
       <c r="J303" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L303" s="1">
         <v>46290</v>
@@ -23005,10 +23008,10 @@
         <v>203</v>
       </c>
       <c r="O303">
-        <v>17968017</v>
+        <v>17042486</v>
       </c>
       <c r="P303" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q303" t="s">
         <v>238</v>
@@ -23017,13 +23020,13 @@
         <v>-2</v>
       </c>
       <c r="T303" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="V303" t="s">
         <v>255</v>
       </c>
       <c r="W303" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AA303">
         <v>0</v>
@@ -23032,21 +23035,21 @@
         <v>459</v>
       </c>
       <c r="AH303" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="304" spans="1:34">
       <c r="A304">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B304" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C304" t="s">
         <v>58</v>
       </c>
       <c r="D304" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E304" t="s">
         <v>63</v>
@@ -23064,7 +23067,7 @@
         <v>67</v>
       </c>
       <c r="J304" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L304" s="1">
         <v>46290</v>
@@ -23076,7 +23079,7 @@
         <v>203</v>
       </c>
       <c r="O304">
-        <v>17042486</v>
+        <v>16960024</v>
       </c>
       <c r="P304" t="s">
         <v>209</v>
@@ -23094,7 +23097,7 @@
         <v>255</v>
       </c>
       <c r="W304" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AA304">
         <v>0</v>
@@ -23108,10 +23111,10 @@
     </row>
     <row r="305" spans="1:34">
       <c r="A305">
-        <v>6628</v>
+        <v>6945</v>
       </c>
       <c r="B305" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C305" t="s">
         <v>58</v>
@@ -23120,10 +23123,10 @@
         <v>60</v>
       </c>
       <c r="E305" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F305" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G305">
         <v>6892</v>
@@ -23135,22 +23138,22 @@
         <v>67</v>
       </c>
       <c r="J305" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L305" s="1">
         <v>46290</v>
       </c>
       <c r="M305" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N305" t="s">
         <v>203</v>
       </c>
       <c r="O305">
-        <v>16960024</v>
+        <v>18163676</v>
       </c>
       <c r="P305" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q305" t="s">
         <v>238</v>
@@ -23159,10 +23162,7 @@
         <v>-2</v>
       </c>
       <c r="T305" t="s">
-        <v>240</v>
-      </c>
-      <c r="V305" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="W305" t="s">
         <v>346</v>
@@ -23179,16 +23179,16 @@
     </row>
     <row r="306" spans="1:34">
       <c r="A306">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B306" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C306" t="s">
         <v>58</v>
       </c>
       <c r="D306" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E306" t="s">
         <v>62</v>
@@ -23206,22 +23206,22 @@
         <v>67</v>
       </c>
       <c r="J306" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L306" s="1">
         <v>46290</v>
       </c>
       <c r="M306" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N306" t="s">
         <v>203</v>
       </c>
       <c r="O306">
-        <v>18163676</v>
+        <v>18178288</v>
       </c>
       <c r="P306" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Q306" t="s">
         <v>238</v>
@@ -23230,10 +23230,10 @@
         <v>-2</v>
       </c>
       <c r="T306" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="W306" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AA306">
         <v>0</v>
@@ -23242,21 +23242,21 @@
         <v>459</v>
       </c>
       <c r="AH306" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="307" spans="1:34">
       <c r="A307">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B307" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C307" t="s">
         <v>58</v>
       </c>
       <c r="D307" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E307" t="s">
         <v>62</v>
@@ -23274,7 +23274,7 @@
         <v>67</v>
       </c>
       <c r="J307" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L307" s="1">
         <v>46290</v>
@@ -23286,10 +23286,10 @@
         <v>203</v>
       </c>
       <c r="O307">
-        <v>18178288</v>
+        <v>18187955</v>
       </c>
       <c r="P307" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q307" t="s">
         <v>238</v>
@@ -23298,10 +23298,10 @@
         <v>-2</v>
       </c>
       <c r="T307" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="W307" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AA307">
         <v>0</v>
@@ -23310,15 +23310,15 @@
         <v>459</v>
       </c>
       <c r="AH307" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="308" spans="1:34">
       <c r="A308">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B308" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C308" t="s">
         <v>58</v>
@@ -23342,7 +23342,7 @@
         <v>67</v>
       </c>
       <c r="J308" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L308" s="1">
         <v>46290</v>
@@ -23354,7 +23354,7 @@
         <v>203</v>
       </c>
       <c r="O308">
-        <v>18187955</v>
+        <v>18187893</v>
       </c>
       <c r="P308" t="s">
         <v>211</v>
@@ -23369,7 +23369,7 @@
         <v>243</v>
       </c>
       <c r="W308" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AA308">
         <v>0</v>
@@ -23383,25 +23383,25 @@
     </row>
     <row r="309" spans="1:34">
       <c r="A309">
-        <v>6963</v>
+        <v>6548</v>
       </c>
       <c r="B309" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C309" t="s">
         <v>58</v>
       </c>
       <c r="D309" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E309" t="s">
         <v>62</v>
       </c>
       <c r="F309" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G309">
-        <v>6892</v>
+        <v>11516</v>
       </c>
       <c r="H309">
         <v>0</v>
@@ -23422,10 +23422,10 @@
         <v>203</v>
       </c>
       <c r="O309">
-        <v>18187893</v>
+        <v>17968053</v>
       </c>
       <c r="P309" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="Q309" t="s">
         <v>238</v>
@@ -23434,10 +23434,13 @@
         <v>-2</v>
       </c>
       <c r="T309" t="s">
-        <v>243</v>
+        <v>239</v>
+      </c>
+      <c r="V309" t="s">
+        <v>255</v>
       </c>
       <c r="W309" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AA309">
         <v>0</v>
@@ -23446,15 +23449,15 @@
         <v>459</v>
       </c>
       <c r="AH309" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="310" spans="1:34">
       <c r="A310">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B310" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C310" t="s">
         <v>58</v>
@@ -23463,7 +23466,7 @@
         <v>59</v>
       </c>
       <c r="E310" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F310" t="s">
         <v>64</v>
@@ -23478,7 +23481,7 @@
         <v>67</v>
       </c>
       <c r="J310" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L310" s="1">
         <v>46290</v>
@@ -23490,10 +23493,10 @@
         <v>203</v>
       </c>
       <c r="O310">
-        <v>17968053</v>
+        <v>17042662</v>
       </c>
       <c r="P310" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q310" t="s">
         <v>238</v>
@@ -23502,13 +23505,13 @@
         <v>-2</v>
       </c>
       <c r="T310" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="V310" t="s">
         <v>255</v>
       </c>
       <c r="W310" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AA310">
         <v>0</v>
@@ -23517,15 +23520,15 @@
         <v>459</v>
       </c>
       <c r="AH310" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="311" spans="1:34">
       <c r="A311">
-        <v>6627</v>
+        <v>6949</v>
       </c>
       <c r="B311" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C311" t="s">
         <v>58</v>
@@ -23534,10 +23537,10 @@
         <v>59</v>
       </c>
       <c r="E311" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F311" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G311">
         <v>11516</v>
@@ -23549,7 +23552,7 @@
         <v>67</v>
       </c>
       <c r="J311" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L311" s="1">
         <v>46290</v>
@@ -23561,10 +23564,10 @@
         <v>203</v>
       </c>
       <c r="O311">
-        <v>17042662</v>
+        <v>18178314</v>
       </c>
       <c r="P311" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Q311" t="s">
         <v>238</v>
@@ -23573,13 +23576,10 @@
         <v>-2</v>
       </c>
       <c r="T311" t="s">
-        <v>240</v>
-      </c>
-      <c r="V311" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="W311" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AA311">
         <v>0</v>
@@ -23588,21 +23588,21 @@
         <v>459</v>
       </c>
       <c r="AH311" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="312" spans="1:34">
       <c r="A312">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B312" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C312" t="s">
         <v>58</v>
       </c>
       <c r="D312" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E312" t="s">
         <v>62</v>
@@ -23620,7 +23620,7 @@
         <v>67</v>
       </c>
       <c r="J312" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L312" s="1">
         <v>46290</v>
@@ -23632,10 +23632,10 @@
         <v>203</v>
       </c>
       <c r="O312">
-        <v>18178314</v>
+        <v>18187985</v>
       </c>
       <c r="P312" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q312" t="s">
         <v>238</v>
@@ -23644,10 +23644,10 @@
         <v>-2</v>
       </c>
       <c r="T312" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="W312" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AA312">
         <v>0</v>
@@ -23656,15 +23656,15 @@
         <v>459</v>
       </c>
       <c r="AH312" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="313" spans="1:34">
       <c r="A313">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B313" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C313" t="s">
         <v>58</v>
@@ -23688,7 +23688,7 @@
         <v>67</v>
       </c>
       <c r="J313" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L313" s="1">
         <v>46290</v>
@@ -23700,7 +23700,7 @@
         <v>203</v>
       </c>
       <c r="O313">
-        <v>18187985</v>
+        <v>18241255</v>
       </c>
       <c r="P313" t="s">
         <v>211</v>
@@ -23715,7 +23715,7 @@
         <v>243</v>
       </c>
       <c r="W313" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AA313">
         <v>0</v>
@@ -23729,10 +23729,10 @@
     </row>
     <row r="314" spans="1:34">
       <c r="A314">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B314" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C314" t="s">
         <v>58</v>
@@ -23747,7 +23747,7 @@
         <v>65</v>
       </c>
       <c r="G314">
-        <v>11516</v>
+        <v>10992</v>
       </c>
       <c r="H314">
         <v>0</v>
@@ -23759,16 +23759,16 @@
         <v>138</v>
       </c>
       <c r="L314" s="1">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="M314" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N314" t="s">
         <v>203</v>
       </c>
       <c r="O314">
-        <v>18241255</v>
+        <v>18249084</v>
       </c>
       <c r="P314" t="s">
         <v>211</v>
@@ -23777,19 +23777,19 @@
         <v>238</v>
       </c>
       <c r="S314">
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="T314" t="s">
         <v>243</v>
       </c>
       <c r="W314" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AA314">
         <v>0</v>
       </c>
       <c r="AG314" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AH314" t="s">
         <v>461</v>
@@ -23797,10 +23797,10 @@
     </row>
     <row r="315" spans="1:34">
       <c r="A315">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B315" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C315" t="s">
         <v>58</v>
@@ -23824,7 +23824,7 @@
         <v>67</v>
       </c>
       <c r="J315" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L315" s="1">
         <v>46295</v>
@@ -23836,7 +23836,7 @@
         <v>203</v>
       </c>
       <c r="O315">
-        <v>18249084</v>
+        <v>18249092</v>
       </c>
       <c r="P315" t="s">
         <v>211</v>
@@ -23851,7 +23851,7 @@
         <v>243</v>
       </c>
       <c r="W315" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AA315">
         <v>0</v>
@@ -23865,25 +23865,25 @@
     </row>
     <row r="316" spans="1:34">
       <c r="A316">
-        <v>6963</v>
+        <v>6548</v>
       </c>
       <c r="B316" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C316" t="s">
         <v>58</v>
       </c>
       <c r="D316" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E316" t="s">
         <v>62</v>
       </c>
       <c r="F316" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G316">
-        <v>10992</v>
+        <v>7875</v>
       </c>
       <c r="H316">
         <v>0</v>
@@ -23904,10 +23904,10 @@
         <v>203</v>
       </c>
       <c r="O316">
-        <v>18249092</v>
+        <v>18096234</v>
       </c>
       <c r="P316" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="Q316" t="s">
         <v>238</v>
@@ -23916,10 +23916,13 @@
         <v>-7</v>
       </c>
       <c r="T316" t="s">
-        <v>243</v>
+        <v>239</v>
+      </c>
+      <c r="V316" t="s">
+        <v>255</v>
       </c>
       <c r="W316" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AA316">
         <v>0</v>
@@ -23928,15 +23931,15 @@
         <v>457</v>
       </c>
       <c r="AH316" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="317" spans="1:34">
       <c r="A317">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B317" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C317" t="s">
         <v>58</v>
@@ -23945,7 +23948,7 @@
         <v>59</v>
       </c>
       <c r="E317" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F317" t="s">
         <v>64</v>
@@ -23960,7 +23963,7 @@
         <v>67</v>
       </c>
       <c r="J317" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L317" s="1">
         <v>46295</v>
@@ -23972,10 +23975,10 @@
         <v>203</v>
       </c>
       <c r="O317">
-        <v>18096234</v>
+        <v>18096487</v>
       </c>
       <c r="P317" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q317" t="s">
         <v>238</v>
@@ -23984,13 +23987,13 @@
         <v>-7</v>
       </c>
       <c r="T317" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="V317" t="s">
         <v>255</v>
       </c>
       <c r="W317" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AA317">
         <v>0</v>
@@ -23999,15 +24002,15 @@
         <v>457</v>
       </c>
       <c r="AH317" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="318" spans="1:34">
       <c r="A318">
-        <v>6627</v>
+        <v>6949</v>
       </c>
       <c r="B318" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C318" t="s">
         <v>58</v>
@@ -24016,10 +24019,10 @@
         <v>59</v>
       </c>
       <c r="E318" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F318" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G318">
         <v>7875</v>
@@ -24031,7 +24034,7 @@
         <v>67</v>
       </c>
       <c r="J318" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L318" s="1">
         <v>46295</v>
@@ -24043,10 +24046,10 @@
         <v>203</v>
       </c>
       <c r="O318">
-        <v>18096487</v>
+        <v>18254144</v>
       </c>
       <c r="P318" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Q318" t="s">
         <v>238</v>
@@ -24055,13 +24058,10 @@
         <v>-7</v>
       </c>
       <c r="T318" t="s">
-        <v>240</v>
-      </c>
-      <c r="V318" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="W318" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AA318">
         <v>0</v>
@@ -24070,21 +24070,21 @@
         <v>457</v>
       </c>
       <c r="AH318" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="319" spans="1:34">
       <c r="A319">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B319" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C319" t="s">
         <v>58</v>
       </c>
       <c r="D319" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E319" t="s">
         <v>62</v>
@@ -24102,7 +24102,7 @@
         <v>67</v>
       </c>
       <c r="J319" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L319" s="1">
         <v>46295</v>
@@ -24114,10 +24114,10 @@
         <v>203</v>
       </c>
       <c r="O319">
-        <v>18254144</v>
+        <v>18200037</v>
       </c>
       <c r="P319" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q319" t="s">
         <v>238</v>
@@ -24126,10 +24126,10 @@
         <v>-7</v>
       </c>
       <c r="T319" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="W319" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AA319">
         <v>0</v>
@@ -24138,15 +24138,15 @@
         <v>457</v>
       </c>
       <c r="AH319" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="320" spans="1:34">
       <c r="A320">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B320" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C320" t="s">
         <v>58</v>
@@ -24170,7 +24170,7 @@
         <v>67</v>
       </c>
       <c r="J320" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L320" s="1">
         <v>46295</v>
@@ -24182,7 +24182,7 @@
         <v>203</v>
       </c>
       <c r="O320">
-        <v>18200037</v>
+        <v>18200056</v>
       </c>
       <c r="P320" t="s">
         <v>211</v>
@@ -24197,7 +24197,7 @@
         <v>243</v>
       </c>
       <c r="W320" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AA320">
         <v>0</v>
@@ -24211,25 +24211,25 @@
     </row>
     <row r="321" spans="1:34">
       <c r="A321">
-        <v>6963</v>
+        <v>6628</v>
       </c>
       <c r="B321" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C321" t="s">
         <v>58</v>
       </c>
       <c r="D321" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E321" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F321" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G321">
-        <v>7875</v>
+        <v>9764</v>
       </c>
       <c r="H321">
         <v>0</v>
@@ -24250,10 +24250,10 @@
         <v>203</v>
       </c>
       <c r="O321">
-        <v>18200056</v>
+        <v>18096422</v>
       </c>
       <c r="P321" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="Q321" t="s">
         <v>238</v>
@@ -24262,10 +24262,13 @@
         <v>-7</v>
       </c>
       <c r="T321" t="s">
-        <v>243</v>
+        <v>240</v>
+      </c>
+      <c r="V321" t="s">
+        <v>255</v>
       </c>
       <c r="W321" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AA321">
         <v>0</v>
@@ -24279,10 +24282,10 @@
     </row>
     <row r="322" spans="1:34">
       <c r="A322">
-        <v>6628</v>
+        <v>6945</v>
       </c>
       <c r="B322" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C322" t="s">
         <v>58</v>
@@ -24291,10 +24294,10 @@
         <v>60</v>
       </c>
       <c r="E322" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F322" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G322">
         <v>9764</v>
@@ -24306,7 +24309,7 @@
         <v>67</v>
       </c>
       <c r="J322" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L322" s="1">
         <v>46295</v>
@@ -24318,10 +24321,10 @@
         <v>203</v>
       </c>
       <c r="O322">
-        <v>18096422</v>
+        <v>18200045</v>
       </c>
       <c r="P322" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q322" t="s">
         <v>238</v>
@@ -24330,10 +24333,7 @@
         <v>-7</v>
       </c>
       <c r="T322" t="s">
-        <v>240</v>
-      </c>
-      <c r="V322" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="W322" t="s">
         <v>348</v>
@@ -24350,61 +24350,61 @@
     </row>
     <row r="323" spans="1:34">
       <c r="A323">
-        <v>6945</v>
+        <v>5417</v>
       </c>
       <c r="B323" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C323" t="s">
         <v>58</v>
       </c>
       <c r="D323" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E323" t="s">
         <v>62</v>
       </c>
       <c r="F323" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G323">
-        <v>9764</v>
+        <v>7868</v>
       </c>
       <c r="H323">
         <v>0</v>
       </c>
       <c r="I323" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J323" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="L323" s="1">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="M323" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="N323" t="s">
         <v>203</v>
       </c>
       <c r="O323">
-        <v>18200045</v>
+        <v>17399310</v>
       </c>
       <c r="P323" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q323" t="s">
         <v>238</v>
       </c>
       <c r="S323">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="T323" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="W323" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="AA323">
         <v>0</v>
@@ -24413,15 +24413,15 @@
         <v>457</v>
       </c>
       <c r="AH323" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="324" spans="1:34">
       <c r="A324">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B324" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C324" t="s">
         <v>58</v>
@@ -24445,7 +24445,7 @@
         <v>68</v>
       </c>
       <c r="J324" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L324" s="1">
         <v>46293</v>
@@ -24457,10 +24457,10 @@
         <v>203</v>
       </c>
       <c r="O324">
-        <v>17399310</v>
+        <v>18114218</v>
       </c>
       <c r="P324" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="Q324" t="s">
         <v>238</v>
@@ -24469,10 +24469,13 @@
         <v>-5</v>
       </c>
       <c r="T324" t="s">
-        <v>244</v>
+        <v>246</v>
+      </c>
+      <c r="V324" t="s">
+        <v>255</v>
       </c>
       <c r="W324" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AA324">
         <v>0</v>
@@ -24486,16 +24489,16 @@
     </row>
     <row r="325" spans="1:34">
       <c r="A325">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B325" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C325" t="s">
         <v>58</v>
       </c>
       <c r="D325" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E325" t="s">
         <v>62</v>
@@ -24504,7 +24507,7 @@
         <v>64</v>
       </c>
       <c r="G325">
-        <v>7868</v>
+        <v>6890</v>
       </c>
       <c r="H325">
         <v>0</v>
@@ -24516,31 +24519,28 @@
         <v>136</v>
       </c>
       <c r="L325" s="1">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="M325" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N325" t="s">
         <v>203</v>
       </c>
       <c r="O325">
-        <v>18114218</v>
+        <v>16962328</v>
       </c>
       <c r="P325" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q325" t="s">
         <v>238</v>
       </c>
       <c r="S325">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="T325" t="s">
-        <v>246</v>
-      </c>
-      <c r="V325" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="W325" t="s">
         <v>345</v>
@@ -24549,24 +24549,24 @@
         <v>0</v>
       </c>
       <c r="AG325" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AH325" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="326" spans="1:34">
       <c r="A326">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B326" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C326" t="s">
         <v>58</v>
       </c>
       <c r="D326" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E326" t="s">
         <v>62</v>
@@ -24584,7 +24584,7 @@
         <v>68</v>
       </c>
       <c r="J326" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L326" s="1">
         <v>46290</v>
@@ -24596,10 +24596,10 @@
         <v>203</v>
       </c>
       <c r="O326">
-        <v>16962328</v>
+        <v>18152538</v>
       </c>
       <c r="P326" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q326" t="s">
         <v>238</v>
@@ -24608,10 +24608,13 @@
         <v>-2</v>
       </c>
       <c r="T326" t="s">
-        <v>248</v>
+        <v>246</v>
+      </c>
+      <c r="V326" t="s">
+        <v>255</v>
       </c>
       <c r="W326" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AA326">
         <v>0</v>
@@ -24620,21 +24623,21 @@
         <v>459</v>
       </c>
       <c r="AH326" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="327" spans="1:34">
       <c r="A327">
-        <v>6486</v>
+        <v>6703</v>
       </c>
       <c r="B327" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C327" t="s">
         <v>58</v>
       </c>
       <c r="D327" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E327" t="s">
         <v>62</v>
@@ -24652,7 +24655,7 @@
         <v>68</v>
       </c>
       <c r="J327" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L327" s="1">
         <v>46290</v>
@@ -24664,7 +24667,7 @@
         <v>203</v>
       </c>
       <c r="O327">
-        <v>18152538</v>
+        <v>17955186</v>
       </c>
       <c r="P327" t="s">
         <v>230</v>
@@ -24676,13 +24679,10 @@
         <v>-2</v>
       </c>
       <c r="T327" t="s">
-        <v>246</v>
-      </c>
-      <c r="V327" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="W327" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AA327">
         <v>0</v>
@@ -24696,16 +24696,16 @@
     </row>
     <row r="328" spans="1:34">
       <c r="A328">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B328" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C328" t="s">
         <v>58</v>
       </c>
       <c r="D328" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E328" t="s">
         <v>62</v>
@@ -24723,7 +24723,7 @@
         <v>68</v>
       </c>
       <c r="J328" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L328" s="1">
         <v>46290</v>
@@ -24735,10 +24735,10 @@
         <v>203</v>
       </c>
       <c r="O328">
-        <v>17955186</v>
+        <v>17955399</v>
       </c>
       <c r="P328" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="Q328" t="s">
         <v>238</v>
@@ -24747,10 +24747,13 @@
         <v>-2</v>
       </c>
       <c r="T328" t="s">
-        <v>247</v>
+        <v>245</v>
+      </c>
+      <c r="V328" t="s">
+        <v>255</v>
       </c>
       <c r="W328" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AA328">
         <v>0</v>
@@ -24759,21 +24762,21 @@
         <v>459</v>
       </c>
       <c r="AH328" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="329" spans="1:34">
       <c r="A329">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B329" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C329" t="s">
         <v>58</v>
       </c>
       <c r="D329" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E329" t="s">
         <v>62</v>
@@ -24791,7 +24794,7 @@
         <v>68</v>
       </c>
       <c r="J329" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L329" s="1">
         <v>46290</v>
@@ -24803,7 +24806,7 @@
         <v>203</v>
       </c>
       <c r="O329">
-        <v>17955399</v>
+        <v>17955249</v>
       </c>
       <c r="P329" t="s">
         <v>213</v>
@@ -24817,11 +24820,8 @@
       <c r="T329" t="s">
         <v>245</v>
       </c>
-      <c r="V329" t="s">
-        <v>255</v>
-      </c>
       <c r="W329" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AA329">
         <v>0</v>
@@ -24835,10 +24835,10 @@
     </row>
     <row r="330" spans="1:34">
       <c r="A330">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B330" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C330" t="s">
         <v>58</v>
@@ -24862,7 +24862,7 @@
         <v>68</v>
       </c>
       <c r="J330" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L330" s="1">
         <v>46290</v>
@@ -24874,7 +24874,7 @@
         <v>203</v>
       </c>
       <c r="O330">
-        <v>17955249</v>
+        <v>18056769</v>
       </c>
       <c r="P330" t="s">
         <v>213</v>
@@ -24888,8 +24888,11 @@
       <c r="T330" t="s">
         <v>245</v>
       </c>
+      <c r="V330" t="s">
+        <v>255</v>
+      </c>
       <c r="W330" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AA330">
         <v>0</v>
@@ -24903,16 +24906,16 @@
     </row>
     <row r="331" spans="1:34">
       <c r="A331">
-        <v>6779</v>
+        <v>6404</v>
       </c>
       <c r="B331" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C331" t="s">
         <v>58</v>
       </c>
       <c r="D331" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E331" t="s">
         <v>62</v>
@@ -24921,7 +24924,7 @@
         <v>64</v>
       </c>
       <c r="G331">
-        <v>6890</v>
+        <v>11514</v>
       </c>
       <c r="H331">
         <v>0</v>
@@ -24942,10 +24945,10 @@
         <v>203</v>
       </c>
       <c r="O331">
-        <v>18056769</v>
+        <v>16962474</v>
       </c>
       <c r="P331" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="Q331" t="s">
         <v>238</v>
@@ -24954,13 +24957,10 @@
         <v>-2</v>
       </c>
       <c r="T331" t="s">
-        <v>245</v>
-      </c>
-      <c r="V331" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="W331" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AA331">
         <v>0</v>
@@ -24974,16 +24974,16 @@
     </row>
     <row r="332" spans="1:34">
       <c r="A332">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B332" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C332" t="s">
         <v>58</v>
       </c>
       <c r="D332" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E332" t="s">
         <v>62</v>
@@ -25001,7 +25001,7 @@
         <v>68</v>
       </c>
       <c r="J332" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L332" s="1">
         <v>46290</v>
@@ -25013,10 +25013,10 @@
         <v>203</v>
       </c>
       <c r="O332">
-        <v>16962474</v>
+        <v>18114227</v>
       </c>
       <c r="P332" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q332" t="s">
         <v>238</v>
@@ -25025,10 +25025,13 @@
         <v>-2</v>
       </c>
       <c r="T332" t="s">
-        <v>248</v>
+        <v>246</v>
+      </c>
+      <c r="V332" t="s">
+        <v>255</v>
       </c>
       <c r="W332" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AA332">
         <v>0</v>
@@ -25037,21 +25040,21 @@
         <v>459</v>
       </c>
       <c r="AH332" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="333" spans="1:34">
       <c r="A333">
-        <v>6486</v>
+        <v>6703</v>
       </c>
       <c r="B333" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C333" t="s">
         <v>58</v>
       </c>
       <c r="D333" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E333" t="s">
         <v>62</v>
@@ -25069,7 +25072,7 @@
         <v>68</v>
       </c>
       <c r="J333" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L333" s="1">
         <v>46290</v>
@@ -25081,7 +25084,7 @@
         <v>203</v>
       </c>
       <c r="O333">
-        <v>18114227</v>
+        <v>17955212</v>
       </c>
       <c r="P333" t="s">
         <v>230</v>
@@ -25093,13 +25096,10 @@
         <v>-2</v>
       </c>
       <c r="T333" t="s">
-        <v>246</v>
-      </c>
-      <c r="V333" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="W333" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AA333">
         <v>0</v>
@@ -25113,16 +25113,16 @@
     </row>
     <row r="334" spans="1:34">
       <c r="A334">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B334" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C334" t="s">
         <v>58</v>
       </c>
       <c r="D334" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E334" t="s">
         <v>62</v>
@@ -25140,7 +25140,7 @@
         <v>68</v>
       </c>
       <c r="J334" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L334" s="1">
         <v>46290</v>
@@ -25152,10 +25152,10 @@
         <v>203</v>
       </c>
       <c r="O334">
-        <v>17955212</v>
+        <v>17955445</v>
       </c>
       <c r="P334" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="Q334" t="s">
         <v>238</v>
@@ -25164,10 +25164,13 @@
         <v>-2</v>
       </c>
       <c r="T334" t="s">
-        <v>247</v>
+        <v>245</v>
+      </c>
+      <c r="V334" t="s">
+        <v>255</v>
       </c>
       <c r="W334" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AA334">
         <v>0</v>
@@ -25176,21 +25179,21 @@
         <v>459</v>
       </c>
       <c r="AH334" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="335" spans="1:34">
       <c r="A335">
-        <v>6704</v>
+        <v>6404</v>
       </c>
       <c r="B335" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C335" t="s">
         <v>58</v>
       </c>
       <c r="D335" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E335" t="s">
         <v>62</v>
@@ -25199,7 +25202,7 @@
         <v>64</v>
       </c>
       <c r="G335">
-        <v>11514</v>
+        <v>10988</v>
       </c>
       <c r="H335">
         <v>0</v>
@@ -25211,40 +25214,37 @@
         <v>138</v>
       </c>
       <c r="L335" s="1">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="M335" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N335" t="s">
         <v>203</v>
       </c>
       <c r="O335">
-        <v>17955445</v>
+        <v>16962444</v>
       </c>
       <c r="P335" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="Q335" t="s">
         <v>238</v>
       </c>
       <c r="S335">
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="T335" t="s">
-        <v>245</v>
-      </c>
-      <c r="V335" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="W335" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AA335">
         <v>0</v>
       </c>
       <c r="AG335" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AH335" t="s">
         <v>463</v>
@@ -25252,10 +25252,10 @@
     </row>
     <row r="336" spans="1:34">
       <c r="A336">
-        <v>6404</v>
+        <v>6703</v>
       </c>
       <c r="B336" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C336" t="s">
         <v>58</v>
@@ -25279,7 +25279,7 @@
         <v>68</v>
       </c>
       <c r="J336" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L336" s="1">
         <v>46295</v>
@@ -25291,10 +25291,10 @@
         <v>203</v>
       </c>
       <c r="O336">
-        <v>16962444</v>
+        <v>18112918</v>
       </c>
       <c r="P336" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q336" t="s">
         <v>238</v>
@@ -25303,10 +25303,10 @@
         <v>-7</v>
       </c>
       <c r="T336" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="W336" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AA336">
         <v>0</v>
@@ -25315,21 +25315,21 @@
         <v>457</v>
       </c>
       <c r="AH336" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="337" spans="1:34">
       <c r="A337">
-        <v>6703</v>
+        <v>6486</v>
       </c>
       <c r="B337" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C337" t="s">
         <v>58</v>
       </c>
       <c r="D337" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E337" t="s">
         <v>62</v>
@@ -25338,7 +25338,7 @@
         <v>64</v>
       </c>
       <c r="G337">
-        <v>10988</v>
+        <v>7874</v>
       </c>
       <c r="H337">
         <v>0</v>
@@ -25359,7 +25359,7 @@
         <v>203</v>
       </c>
       <c r="O337">
-        <v>18112918</v>
+        <v>18130463</v>
       </c>
       <c r="P337" t="s">
         <v>230</v>
@@ -25371,10 +25371,13 @@
         <v>-7</v>
       </c>
       <c r="T337" t="s">
-        <v>247</v>
+        <v>246</v>
+      </c>
+      <c r="V337" t="s">
+        <v>255</v>
       </c>
       <c r="W337" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AA337">
         <v>0</v>
@@ -25388,10 +25391,10 @@
     </row>
     <row r="338" spans="1:34">
       <c r="A338">
-        <v>6486</v>
+        <v>6704</v>
       </c>
       <c r="B338" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C338" t="s">
         <v>58</v>
@@ -25415,7 +25418,7 @@
         <v>68</v>
       </c>
       <c r="J338" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L338" s="1">
         <v>46295</v>
@@ -25427,10 +25430,10 @@
         <v>203</v>
       </c>
       <c r="O338">
-        <v>18130463</v>
+        <v>18096767</v>
       </c>
       <c r="P338" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="Q338" t="s">
         <v>238</v>
@@ -25439,13 +25442,13 @@
         <v>-7</v>
       </c>
       <c r="T338" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="V338" t="s">
         <v>255</v>
       </c>
       <c r="W338" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AA338">
         <v>0</v>
@@ -25454,21 +25457,21 @@
         <v>457</v>
       </c>
       <c r="AH338" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="339" spans="1:34">
       <c r="A339">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B339" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C339" t="s">
         <v>58</v>
       </c>
       <c r="D339" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E339" t="s">
         <v>62</v>
@@ -25477,7 +25480,7 @@
         <v>64</v>
       </c>
       <c r="G339">
-        <v>7874</v>
+        <v>9762</v>
       </c>
       <c r="H339">
         <v>0</v>
@@ -25498,7 +25501,7 @@
         <v>203</v>
       </c>
       <c r="O339">
-        <v>18096767</v>
+        <v>18096939</v>
       </c>
       <c r="P339" t="s">
         <v>213</v>
@@ -25512,11 +25515,8 @@
       <c r="T339" t="s">
         <v>245</v>
       </c>
-      <c r="V339" t="s">
-        <v>255</v>
-      </c>
       <c r="W339" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AA339">
         <v>0</v>
@@ -25530,10 +25530,10 @@
     </row>
     <row r="340" spans="1:34">
       <c r="A340">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B340" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C340" t="s">
         <v>58</v>
@@ -25557,7 +25557,7 @@
         <v>68</v>
       </c>
       <c r="J340" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L340" s="1">
         <v>46295</v>
@@ -25569,7 +25569,7 @@
         <v>203</v>
       </c>
       <c r="O340">
-        <v>18096939</v>
+        <v>18130484</v>
       </c>
       <c r="P340" t="s">
         <v>213</v>
@@ -25583,8 +25583,11 @@
       <c r="T340" t="s">
         <v>245</v>
       </c>
+      <c r="V340" t="s">
+        <v>255</v>
+      </c>
       <c r="W340" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AA340">
         <v>0</v>
@@ -25598,16 +25601,16 @@
     </row>
     <row r="341" spans="1:34">
       <c r="A341">
-        <v>6779</v>
+        <v>6548</v>
       </c>
       <c r="B341" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C341" t="s">
         <v>58</v>
       </c>
       <c r="D341" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E341" t="s">
         <v>62</v>
@@ -25616,16 +25619,16 @@
         <v>64</v>
       </c>
       <c r="G341">
-        <v>9762</v>
+        <v>5859</v>
       </c>
       <c r="H341">
-        <v>0</v>
+        <v>5786</v>
       </c>
       <c r="I341" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J341" t="s">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="L341" s="1">
         <v>46295</v>
@@ -25634,13 +25637,13 @@
         <v>195</v>
       </c>
       <c r="N341" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O341">
-        <v>18130484</v>
+        <v>17222602</v>
       </c>
       <c r="P341" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="Q341" t="s">
         <v>238</v>
@@ -25649,22 +25652,22 @@
         <v>-7</v>
       </c>
       <c r="T341" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="V341" t="s">
         <v>255</v>
       </c>
       <c r="W341" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AA341">
         <v>0</v>
       </c>
       <c r="AG341" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AH341" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="342" spans="1:34">
@@ -25687,16 +25690,16 @@
         <v>64</v>
       </c>
       <c r="G342">
-        <v>5859</v>
+        <v>5905</v>
       </c>
       <c r="H342">
-        <v>5786</v>
+        <v>5784</v>
       </c>
       <c r="I342" t="s">
         <v>69</v>
       </c>
       <c r="J342" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="L342" s="1">
         <v>46295</v>
@@ -25708,7 +25711,7 @@
         <v>204</v>
       </c>
       <c r="O342">
-        <v>17222602</v>
+        <v>17222671</v>
       </c>
       <c r="P342" t="s">
         <v>218</v>
@@ -25726,13 +25729,13 @@
         <v>255</v>
       </c>
       <c r="W342" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AA342">
         <v>0</v>
       </c>
       <c r="AG342" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AH342" t="s">
         <v>464</v>
@@ -25758,7 +25761,7 @@
         <v>64</v>
       </c>
       <c r="G343">
-        <v>5905</v>
+        <v>5853</v>
       </c>
       <c r="H343">
         <v>5784</v>
@@ -25767,7 +25770,7 @@
         <v>69</v>
       </c>
       <c r="J343" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L343" s="1">
         <v>46295</v>
@@ -25779,7 +25782,7 @@
         <v>204</v>
       </c>
       <c r="O343">
-        <v>17222671</v>
+        <v>17222589</v>
       </c>
       <c r="P343" t="s">
         <v>218</v>
@@ -25797,13 +25800,13 @@
         <v>255</v>
       </c>
       <c r="W343" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AA343">
         <v>0</v>
       </c>
       <c r="AG343" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AH343" t="s">
         <v>464</v>
@@ -25811,10 +25814,10 @@
     </row>
     <row r="344" spans="1:34">
       <c r="A344">
-        <v>6548</v>
+        <v>5417</v>
       </c>
       <c r="B344" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C344" t="s">
         <v>58</v>
@@ -25829,7 +25832,7 @@
         <v>64</v>
       </c>
       <c r="G344">
-        <v>5853</v>
+        <v>5847</v>
       </c>
       <c r="H344">
         <v>5784</v>
@@ -25838,37 +25841,34 @@
         <v>69</v>
       </c>
       <c r="J344" t="s">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="L344" s="1">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="M344" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="N344" t="s">
         <v>204</v>
       </c>
       <c r="O344">
-        <v>17222589</v>
+        <v>18158417</v>
       </c>
       <c r="P344" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q344" t="s">
         <v>238</v>
       </c>
       <c r="S344">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="T344" t="s">
-        <v>239</v>
-      </c>
-      <c r="V344" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="W344" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AA344">
         <v>0</v>
@@ -25876,22 +25876,19 @@
       <c r="AG344" t="s">
         <v>457</v>
       </c>
-      <c r="AH344" t="s">
-        <v>464</v>
-      </c>
     </row>
     <row r="345" spans="1:34">
       <c r="A345">
-        <v>5417</v>
+        <v>6779</v>
       </c>
       <c r="B345" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C345" t="s">
         <v>58</v>
       </c>
       <c r="D345" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E345" t="s">
         <v>62</v>
@@ -25909,7 +25906,7 @@
         <v>69</v>
       </c>
       <c r="J345" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L345" s="1">
         <v>46293</v>
@@ -25921,10 +25918,10 @@
         <v>204</v>
       </c>
       <c r="O345">
-        <v>18158417</v>
+        <v>18158764</v>
       </c>
       <c r="P345" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="Q345" t="s">
         <v>238</v>
@@ -25933,10 +25930,13 @@
         <v>-5</v>
       </c>
       <c r="T345" t="s">
-        <v>244</v>
+        <v>245</v>
+      </c>
+      <c r="V345" t="s">
+        <v>255</v>
       </c>
       <c r="W345" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="AA345">
         <v>0</v>
@@ -25944,19 +25944,22 @@
       <c r="AG345" t="s">
         <v>457</v>
       </c>
+      <c r="AH345" t="s">
+        <v>449</v>
+      </c>
     </row>
     <row r="346" spans="1:34">
       <c r="A346">
-        <v>6779</v>
+        <v>6548</v>
       </c>
       <c r="B346" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C346" t="s">
         <v>58</v>
       </c>
       <c r="D346" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E346" t="s">
         <v>62</v>
@@ -25965,7 +25968,7 @@
         <v>64</v>
       </c>
       <c r="G346">
-        <v>5847</v>
+        <v>5906</v>
       </c>
       <c r="H346">
         <v>5784</v>
@@ -25974,46 +25977,46 @@
         <v>69</v>
       </c>
       <c r="J346" t="s">
-        <v>142</v>
+        <v>88</v>
       </c>
       <c r="L346" s="1">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="M346" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N346" t="s">
         <v>204</v>
       </c>
       <c r="O346">
-        <v>18158764</v>
+        <v>17222688</v>
       </c>
       <c r="P346" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="Q346" t="s">
         <v>238</v>
       </c>
       <c r="S346">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="T346" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="V346" t="s">
         <v>255</v>
       </c>
       <c r="W346" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AA346">
         <v>0</v>
       </c>
       <c r="AG346" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AH346" t="s">
-        <v>449</v>
+        <v>464</v>
       </c>
     </row>
     <row r="347" spans="1:34">
@@ -26036,7 +26039,7 @@
         <v>64</v>
       </c>
       <c r="G347">
-        <v>5906</v>
+        <v>5907</v>
       </c>
       <c r="H347">
         <v>5784</v>
@@ -26045,7 +26048,7 @@
         <v>69</v>
       </c>
       <c r="J347" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L347" s="1">
         <v>46295</v>
@@ -26057,7 +26060,7 @@
         <v>204</v>
       </c>
       <c r="O347">
-        <v>17222688</v>
+        <v>17222699</v>
       </c>
       <c r="P347" t="s">
         <v>218</v>
@@ -26075,13 +26078,13 @@
         <v>255</v>
       </c>
       <c r="W347" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AA347">
         <v>0</v>
       </c>
       <c r="AG347" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AH347" t="s">
         <v>464</v>
@@ -26089,73 +26092,67 @@
     </row>
     <row r="348" spans="1:34">
       <c r="A348">
-        <v>6548</v>
+        <v>6945</v>
       </c>
       <c r="B348" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C348" t="s">
         <v>58</v>
       </c>
       <c r="D348" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E348" t="s">
         <v>62</v>
       </c>
       <c r="F348" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G348">
-        <v>5907</v>
+        <v>5764</v>
       </c>
       <c r="H348">
-        <v>5784</v>
+        <v>0</v>
       </c>
       <c r="I348" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J348" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="L348" s="1">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="M348" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N348" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O348">
-        <v>17222699</v>
+        <v>18220203</v>
       </c>
       <c r="P348" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="Q348" t="s">
         <v>238</v>
       </c>
       <c r="S348">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="T348" t="s">
-        <v>239</v>
-      </c>
-      <c r="V348" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="W348" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="AA348">
         <v>0</v>
       </c>
       <c r="AG348" t="s">
-        <v>457</v>
-      </c>
-      <c r="AH348" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
     </row>
     <row r="349" spans="1:34">
@@ -26178,7 +26175,7 @@
         <v>65</v>
       </c>
       <c r="G349">
-        <v>5764</v>
+        <v>1877</v>
       </c>
       <c r="H349">
         <v>0</v>
@@ -26190,16 +26187,16 @@
         <v>143</v>
       </c>
       <c r="L349" s="1">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="M349" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N349" t="s">
         <v>203</v>
       </c>
       <c r="O349">
-        <v>18220203</v>
+        <v>18220188</v>
       </c>
       <c r="P349" t="s">
         <v>223</v>
@@ -26208,98 +26205,104 @@
         <v>238</v>
       </c>
       <c r="S349">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="T349" t="s">
         <v>241</v>
       </c>
       <c r="W349" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AA349">
         <v>0</v>
       </c>
       <c r="AG349" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="350" spans="1:34">
       <c r="A350">
-        <v>6945</v>
+        <v>6486</v>
       </c>
       <c r="B350" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C350" t="s">
         <v>58</v>
       </c>
       <c r="D350" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E350" t="s">
         <v>62</v>
       </c>
       <c r="F350" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G350">
-        <v>1877</v>
+        <v>6759</v>
       </c>
       <c r="H350">
-        <v>0</v>
+        <v>1788</v>
       </c>
       <c r="I350" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J350" t="s">
         <v>144</v>
       </c>
       <c r="L350" s="1">
-        <v>46293</v>
+        <v>46289</v>
       </c>
       <c r="M350" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="N350" t="s">
         <v>203</v>
       </c>
       <c r="O350">
-        <v>18220188</v>
+        <v>16976177</v>
       </c>
       <c r="P350" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q350" t="s">
         <v>238</v>
       </c>
       <c r="S350">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="T350" t="s">
-        <v>241</v>
+        <v>246</v>
+      </c>
+      <c r="V350" t="s">
+        <v>255</v>
       </c>
       <c r="W350" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="AA350">
         <v>0</v>
       </c>
       <c r="AG350" t="s">
-        <v>458</v>
+        <v>457</v>
+      </c>
+      <c r="AH350" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="351" spans="1:34">
       <c r="A351">
-        <v>6486</v>
+        <v>6705</v>
       </c>
       <c r="B351" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C351" t="s">
         <v>58</v>
       </c>
       <c r="D351" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E351" t="s">
         <v>62</v>
@@ -26317,7 +26320,7 @@
         <v>71</v>
       </c>
       <c r="J351" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L351" s="1">
         <v>46289</v>
@@ -26329,7 +26332,7 @@
         <v>203</v>
       </c>
       <c r="O351">
-        <v>16976177</v>
+        <v>17949019</v>
       </c>
       <c r="P351" t="s">
         <v>227</v>
@@ -26341,13 +26344,10 @@
         <v>-1</v>
       </c>
       <c r="T351" t="s">
-        <v>246</v>
-      </c>
-      <c r="V351" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="W351" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AA351">
         <v>0</v>
@@ -26379,28 +26379,28 @@
         <v>64</v>
       </c>
       <c r="G352">
-        <v>6759</v>
+        <v>1803</v>
       </c>
       <c r="H352">
-        <v>1788</v>
+        <v>0</v>
       </c>
       <c r="I352" t="s">
         <v>71</v>
       </c>
       <c r="J352" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L352" s="1">
-        <v>46289</v>
+        <v>46293</v>
       </c>
       <c r="M352" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="N352" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="O352">
-        <v>17949019</v>
+        <v>17948937</v>
       </c>
       <c r="P352" t="s">
         <v>227</v>
@@ -26409,7 +26409,7 @@
         <v>238</v>
       </c>
       <c r="S352">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="T352" t="s">
         <v>245</v>
@@ -26421,7 +26421,7 @@
         <v>0</v>
       </c>
       <c r="AG352" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AH352" t="s">
         <v>466</v>
@@ -26429,16 +26429,16 @@
     </row>
     <row r="353" spans="1:34">
       <c r="A353">
-        <v>6705</v>
+        <v>5417</v>
       </c>
       <c r="B353" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C353" t="s">
         <v>58</v>
       </c>
       <c r="D353" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E353" t="s">
         <v>62</v>
@@ -26447,40 +26447,40 @@
         <v>64</v>
       </c>
       <c r="G353">
-        <v>1803</v>
+        <v>953</v>
       </c>
       <c r="H353">
         <v>0</v>
       </c>
       <c r="I353" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J353" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L353" s="1">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="M353" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N353" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="O353">
-        <v>17948937</v>
+        <v>17398883</v>
       </c>
       <c r="P353" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q353" t="s">
         <v>238</v>
       </c>
       <c r="S353">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="T353" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="W353" t="s">
         <v>352</v>
@@ -26491,22 +26491,19 @@
       <c r="AG353" t="s">
         <v>458</v>
       </c>
-      <c r="AH353" t="s">
-        <v>466</v>
-      </c>
     </row>
     <row r="354" spans="1:34">
       <c r="A354">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B354" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C354" t="s">
         <v>58</v>
       </c>
       <c r="D354" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E354" t="s">
         <v>62</v>
@@ -26524,7 +26521,7 @@
         <v>72</v>
       </c>
       <c r="J354" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L354" s="1">
         <v>46290</v>
@@ -26536,7 +26533,7 @@
         <v>203</v>
       </c>
       <c r="O354">
-        <v>17398883</v>
+        <v>16962107</v>
       </c>
       <c r="P354" t="s">
         <v>228</v>
@@ -26548,7 +26545,7 @@
         <v>-2</v>
       </c>
       <c r="T354" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="W354" t="s">
         <v>353</v>
@@ -26562,19 +26559,19 @@
     </row>
     <row r="355" spans="1:34">
       <c r="A355">
-        <v>6404</v>
+        <v>6627</v>
       </c>
       <c r="B355" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C355" t="s">
         <v>58</v>
       </c>
       <c r="D355" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E355" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F355" t="s">
         <v>64</v>
@@ -26589,7 +26586,7 @@
         <v>72</v>
       </c>
       <c r="J355" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L355" s="1">
         <v>46290</v>
@@ -26601,7 +26598,7 @@
         <v>203</v>
       </c>
       <c r="O355">
-        <v>16962107</v>
+        <v>17042317</v>
       </c>
       <c r="P355" t="s">
         <v>228</v>
@@ -26613,7 +26610,10 @@
         <v>-2</v>
       </c>
       <c r="T355" t="s">
-        <v>248</v>
+        <v>240</v>
+      </c>
+      <c r="V355" t="s">
+        <v>255</v>
       </c>
       <c r="W355" t="s">
         <v>354</v>
@@ -26627,22 +26627,22 @@
     </row>
     <row r="356" spans="1:34">
       <c r="A356">
-        <v>6627</v>
+        <v>6962</v>
       </c>
       <c r="B356" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C356" t="s">
         <v>58</v>
       </c>
       <c r="D356" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E356" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F356" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G356">
         <v>953</v>
@@ -26654,7 +26654,7 @@
         <v>72</v>
       </c>
       <c r="J356" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L356" s="1">
         <v>46290</v>
@@ -26666,7 +26666,7 @@
         <v>203</v>
       </c>
       <c r="O356">
-        <v>17042317</v>
+        <v>18188731</v>
       </c>
       <c r="P356" t="s">
         <v>228</v>
@@ -26678,10 +26678,7 @@
         <v>-2</v>
       </c>
       <c r="T356" t="s">
-        <v>240</v>
-      </c>
-      <c r="V356" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="W356" t="s">
         <v>355</v>
@@ -26695,10 +26692,10 @@
     </row>
     <row r="357" spans="1:34">
       <c r="A357">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B357" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C357" t="s">
         <v>58</v>
@@ -26722,7 +26719,7 @@
         <v>72</v>
       </c>
       <c r="J357" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L357" s="1">
         <v>46290</v>
@@ -26734,7 +26731,7 @@
         <v>203</v>
       </c>
       <c r="O357">
-        <v>18188731</v>
+        <v>18188637</v>
       </c>
       <c r="P357" t="s">
         <v>228</v>
@@ -26760,25 +26757,25 @@
     </row>
     <row r="358" spans="1:34">
       <c r="A358">
-        <v>6963</v>
+        <v>5417</v>
       </c>
       <c r="B358" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C358" t="s">
         <v>58</v>
       </c>
       <c r="D358" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E358" t="s">
         <v>62</v>
       </c>
       <c r="F358" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G358">
-        <v>953</v>
+        <v>943</v>
       </c>
       <c r="H358">
         <v>0</v>
@@ -26790,16 +26787,16 @@
         <v>146</v>
       </c>
       <c r="L358" s="1">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="M358" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N358" t="s">
         <v>203</v>
       </c>
       <c r="O358">
-        <v>18188637</v>
+        <v>17398859</v>
       </c>
       <c r="P358" t="s">
         <v>228</v>
@@ -26808,27 +26805,27 @@
         <v>238</v>
       </c>
       <c r="S358">
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="T358" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="W358" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="AA358">
         <v>0</v>
       </c>
       <c r="AG358" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="359" spans="1:34">
       <c r="A359">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B359" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C359" t="s">
         <v>58</v>
@@ -26852,7 +26849,7 @@
         <v>72</v>
       </c>
       <c r="J359" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="L359" s="1">
         <v>46295</v>
@@ -26864,7 +26861,7 @@
         <v>203</v>
       </c>
       <c r="O359">
-        <v>17398859</v>
+        <v>16975890</v>
       </c>
       <c r="P359" t="s">
         <v>228</v>
@@ -26876,10 +26873,13 @@
         <v>-7</v>
       </c>
       <c r="T359" t="s">
-        <v>244</v>
+        <v>246</v>
+      </c>
+      <c r="V359" t="s">
+        <v>255</v>
       </c>
       <c r="W359" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="AA359">
         <v>0</v>
@@ -26890,16 +26890,16 @@
     </row>
     <row r="360" spans="1:34">
       <c r="A360">
-        <v>6486</v>
+        <v>6703</v>
       </c>
       <c r="B360" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C360" t="s">
         <v>58</v>
       </c>
       <c r="D360" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E360" t="s">
         <v>62</v>
@@ -26917,7 +26917,7 @@
         <v>72</v>
       </c>
       <c r="J360" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="L360" s="1">
         <v>46295</v>
@@ -26929,7 +26929,7 @@
         <v>203</v>
       </c>
       <c r="O360">
-        <v>16975890</v>
+        <v>17941122</v>
       </c>
       <c r="P360" t="s">
         <v>228</v>
@@ -26941,13 +26941,10 @@
         <v>-7</v>
       </c>
       <c r="T360" t="s">
-        <v>246</v>
-      </c>
-      <c r="V360" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="W360" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AA360">
         <v>0</v>
@@ -26958,16 +26955,16 @@
     </row>
     <row r="361" spans="1:34">
       <c r="A361">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B361" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C361" t="s">
         <v>58</v>
       </c>
       <c r="D361" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E361" t="s">
         <v>62</v>
@@ -26985,7 +26982,7 @@
         <v>72</v>
       </c>
       <c r="J361" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="L361" s="1">
         <v>46295</v>
@@ -26997,7 +26994,7 @@
         <v>203</v>
       </c>
       <c r="O361">
-        <v>17941122</v>
+        <v>17952314</v>
       </c>
       <c r="P361" t="s">
         <v>228</v>
@@ -27009,10 +27006,13 @@
         <v>-7</v>
       </c>
       <c r="T361" t="s">
-        <v>247</v>
+        <v>245</v>
+      </c>
+      <c r="V361" t="s">
+        <v>255</v>
       </c>
       <c r="W361" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AA361">
         <v>0</v>
@@ -27023,16 +27023,16 @@
     </row>
     <row r="362" spans="1:34">
       <c r="A362">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B362" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C362" t="s">
         <v>58</v>
       </c>
       <c r="D362" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E362" t="s">
         <v>62</v>
@@ -27050,7 +27050,7 @@
         <v>72</v>
       </c>
       <c r="J362" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="L362" s="1">
         <v>46295</v>
@@ -27062,7 +27062,7 @@
         <v>203</v>
       </c>
       <c r="O362">
-        <v>17952314</v>
+        <v>17952513</v>
       </c>
       <c r="P362" t="s">
         <v>228</v>
@@ -27076,11 +27076,8 @@
       <c r="T362" t="s">
         <v>245</v>
       </c>
-      <c r="V362" t="s">
-        <v>255</v>
-      </c>
       <c r="W362" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AA362">
         <v>0</v>
@@ -27091,22 +27088,22 @@
     </row>
     <row r="363" spans="1:34">
       <c r="A363">
-        <v>6705</v>
+        <v>6949</v>
       </c>
       <c r="B363" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C363" t="s">
         <v>58</v>
       </c>
       <c r="D363" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E363" t="s">
         <v>62</v>
       </c>
       <c r="F363" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G363">
         <v>943</v>
@@ -27118,7 +27115,7 @@
         <v>72</v>
       </c>
       <c r="J363" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="L363" s="1">
         <v>46295</v>
@@ -27130,7 +27127,7 @@
         <v>203</v>
       </c>
       <c r="O363">
-        <v>17952513</v>
+        <v>18178126</v>
       </c>
       <c r="P363" t="s">
         <v>228</v>
@@ -27142,10 +27139,10 @@
         <v>-7</v>
       </c>
       <c r="T363" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="W363" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AA363">
         <v>0</v>
@@ -27156,16 +27153,16 @@
     </row>
     <row r="364" spans="1:34">
       <c r="A364">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B364" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C364" t="s">
         <v>58</v>
       </c>
       <c r="D364" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E364" t="s">
         <v>62</v>
@@ -27183,7 +27180,7 @@
         <v>72</v>
       </c>
       <c r="J364" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="L364" s="1">
         <v>46295</v>
@@ -27195,7 +27192,7 @@
         <v>203</v>
       </c>
       <c r="O364">
-        <v>18178126</v>
+        <v>18188710</v>
       </c>
       <c r="P364" t="s">
         <v>228</v>
@@ -27207,10 +27204,10 @@
         <v>-7</v>
       </c>
       <c r="T364" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="W364" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AA364">
         <v>0</v>
@@ -27221,10 +27218,10 @@
     </row>
     <row r="365" spans="1:34">
       <c r="A365">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B365" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C365" t="s">
         <v>58</v>
@@ -27248,7 +27245,7 @@
         <v>72</v>
       </c>
       <c r="J365" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="L365" s="1">
         <v>46295</v>
@@ -27260,7 +27257,7 @@
         <v>203</v>
       </c>
       <c r="O365">
-        <v>18188710</v>
+        <v>18188616</v>
       </c>
       <c r="P365" t="s">
         <v>228</v>
@@ -27275,7 +27272,7 @@
         <v>243</v>
       </c>
       <c r="W365" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AA365">
         <v>0</v>
@@ -27286,58 +27283,58 @@
     </row>
     <row r="366" spans="1:34">
       <c r="A366">
-        <v>6963</v>
+        <v>5417</v>
       </c>
       <c r="B366" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C366" t="s">
         <v>58</v>
       </c>
       <c r="D366" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E366" t="s">
         <v>62</v>
       </c>
       <c r="F366" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G366">
-        <v>943</v>
+        <v>7877</v>
       </c>
       <c r="H366">
         <v>0</v>
       </c>
       <c r="I366" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J366" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="L366" s="1">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="M366" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N366" t="s">
         <v>203</v>
       </c>
       <c r="O366">
-        <v>18188616</v>
+        <v>17399330</v>
       </c>
       <c r="P366" t="s">
-        <v>228</v>
+        <v>62</v>
       </c>
       <c r="Q366" t="s">
         <v>238</v>
       </c>
       <c r="S366">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="T366" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="W366" t="s">
         <v>358</v>
@@ -27351,10 +27348,10 @@
     </row>
     <row r="367" spans="1:34">
       <c r="A367">
-        <v>5417</v>
+        <v>6949</v>
       </c>
       <c r="B367" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C367" t="s">
         <v>58</v>
@@ -27366,43 +27363,43 @@
         <v>62</v>
       </c>
       <c r="F367" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G367">
-        <v>7877</v>
+        <v>11056</v>
       </c>
       <c r="H367">
         <v>0</v>
       </c>
       <c r="I367" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J367" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="L367" s="1">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="M367" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N367" t="s">
         <v>203</v>
       </c>
       <c r="O367">
-        <v>17399330</v>
+        <v>18279142</v>
       </c>
       <c r="P367" t="s">
-        <v>62</v>
+        <v>232</v>
       </c>
       <c r="Q367" t="s">
         <v>238</v>
       </c>
       <c r="S367">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="T367" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="W367" t="s">
         <v>359</v>
@@ -27416,75 +27413,81 @@
     </row>
     <row r="368" spans="1:34">
       <c r="A368">
-        <v>6949</v>
+        <v>6628</v>
       </c>
       <c r="B368" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C368" t="s">
         <v>58</v>
       </c>
       <c r="D368" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E368" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F368" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G368">
-        <v>11056</v>
+        <v>1650</v>
       </c>
       <c r="H368">
         <v>0</v>
       </c>
       <c r="I368" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="J368" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="L368" s="1">
         <v>46293</v>
       </c>
-      <c r="M368" t="s">
-        <v>193</v>
-      </c>
       <c r="N368" t="s">
         <v>203</v>
       </c>
       <c r="O368">
-        <v>18279142</v>
+        <v>16959974</v>
       </c>
       <c r="P368" t="s">
-        <v>232</v>
+        <v>209</v>
       </c>
       <c r="Q368" t="s">
-        <v>238</v>
+        <v>236</v>
+      </c>
+      <c r="R368" s="1">
+        <v>46265.00248284722</v>
       </c>
       <c r="S368">
         <v>-5</v>
       </c>
       <c r="T368" t="s">
-        <v>242</v>
-      </c>
-      <c r="W368" t="s">
-        <v>360</v>
+        <v>240</v>
+      </c>
+      <c r="V368" t="s">
+        <v>255</v>
       </c>
       <c r="AA368">
         <v>0</v>
+      </c>
+      <c r="AB368" t="s">
+        <v>451</v>
       </c>
       <c r="AG368" t="s">
         <v>457</v>
       </c>
+      <c r="AH368" t="s">
+        <v>461</v>
+      </c>
     </row>
     <row r="369" spans="1:34">
       <c r="A369">
-        <v>6628</v>
+        <v>6945</v>
       </c>
       <c r="B369" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C369" t="s">
         <v>58</v>
@@ -27493,10 +27496,10 @@
         <v>60</v>
       </c>
       <c r="E369" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F369" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G369">
         <v>1650</v>
@@ -27508,7 +27511,7 @@
         <v>67</v>
       </c>
       <c r="J369" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L369" s="1">
         <v>46293</v>
@@ -27517,25 +27520,22 @@
         <v>203</v>
       </c>
       <c r="O369">
-        <v>16959974</v>
+        <v>18163667</v>
       </c>
       <c r="P369" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q369" t="s">
         <v>236</v>
       </c>
       <c r="R369" s="1">
-        <v>46265.00248284722</v>
+        <v>46265.00255472222</v>
       </c>
       <c r="S369">
         <v>-5</v>
       </c>
       <c r="T369" t="s">
-        <v>240</v>
-      </c>
-      <c r="V369" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="AA369">
         <v>0</v>
@@ -27552,25 +27552,25 @@
     </row>
     <row r="370" spans="1:34">
       <c r="A370">
-        <v>6945</v>
+        <v>6548</v>
       </c>
       <c r="B370" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C370" t="s">
         <v>58</v>
       </c>
       <c r="D370" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E370" t="s">
         <v>62</v>
       </c>
       <c r="F370" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G370">
-        <v>1650</v>
+        <v>1652</v>
       </c>
       <c r="H370">
         <v>0</v>
@@ -27582,28 +27582,34 @@
         <v>148</v>
       </c>
       <c r="L370" s="1">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="N370" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="O370">
-        <v>18163667</v>
+        <v>17967989</v>
       </c>
       <c r="P370" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Q370" t="s">
         <v>236</v>
       </c>
       <c r="R370" s="1">
-        <v>46265.00255472222</v>
+        <v>46234.66180127315</v>
       </c>
       <c r="S370">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="T370" t="s">
-        <v>241</v>
+        <v>239</v>
+      </c>
+      <c r="V370" t="s">
+        <v>255</v>
+      </c>
+      <c r="W370" t="s">
+        <v>360</v>
       </c>
       <c r="AA370">
         <v>0</v>
@@ -27612,18 +27618,18 @@
         <v>451</v>
       </c>
       <c r="AG370" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AH370" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="371" spans="1:34">
       <c r="A371">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B371" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C371" t="s">
         <v>58</v>
@@ -27632,7 +27638,7 @@
         <v>59</v>
       </c>
       <c r="E371" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F371" t="s">
         <v>64</v>
@@ -27647,7 +27653,7 @@
         <v>67</v>
       </c>
       <c r="J371" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="L371" s="1">
         <v>46290</v>
@@ -27656,22 +27662,22 @@
         <v>206</v>
       </c>
       <c r="O371">
-        <v>17967989</v>
+        <v>17042389</v>
       </c>
       <c r="P371" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q371" t="s">
         <v>236</v>
       </c>
       <c r="R371" s="1">
-        <v>46234.66180127315</v>
+        <v>46245.76585582176</v>
       </c>
       <c r="S371">
         <v>-2</v>
       </c>
       <c r="T371" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="V371" t="s">
         <v>255</v>
@@ -27689,15 +27695,15 @@
         <v>458</v>
       </c>
       <c r="AH371" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="372" spans="1:34">
       <c r="A372">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B372" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C372" t="s">
         <v>58</v>
@@ -27706,16 +27712,16 @@
         <v>59</v>
       </c>
       <c r="E372" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F372" t="s">
         <v>64</v>
       </c>
       <c r="G372">
-        <v>1652</v>
+        <v>1697</v>
       </c>
       <c r="H372">
-        <v>0</v>
+        <v>1650</v>
       </c>
       <c r="I372" t="s">
         <v>67</v>
@@ -27724,54 +27730,51 @@
         <v>149</v>
       </c>
       <c r="L372" s="1">
-        <v>46290</v>
+        <v>46286</v>
       </c>
       <c r="N372" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="O372">
-        <v>17042389</v>
+        <v>17968001</v>
       </c>
       <c r="P372" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Q372" t="s">
         <v>236</v>
       </c>
       <c r="R372" s="1">
-        <v>46245.76585582176</v>
+        <v>46282.62254486111</v>
       </c>
       <c r="S372">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="T372" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="V372" t="s">
         <v>255</v>
       </c>
-      <c r="W372" t="s">
-        <v>362</v>
-      </c>
       <c r="AA372">
         <v>0</v>
       </c>
       <c r="AB372" t="s">
-        <v>451</v>
+        <v>208</v>
       </c>
       <c r="AG372" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AH372" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="373" spans="1:34">
       <c r="A373">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B373" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C373" t="s">
         <v>58</v>
@@ -27780,7 +27783,7 @@
         <v>59</v>
       </c>
       <c r="E373" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F373" t="s">
         <v>64</v>
@@ -27795,54 +27798,60 @@
         <v>67</v>
       </c>
       <c r="J373" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L373" s="1">
         <v>46286</v>
       </c>
+      <c r="M373" t="s">
+        <v>197</v>
+      </c>
       <c r="N373" t="s">
         <v>203</v>
       </c>
       <c r="O373">
-        <v>17968001</v>
+        <v>17042403</v>
       </c>
       <c r="P373" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q373" t="s">
         <v>236</v>
       </c>
       <c r="R373" s="1">
-        <v>46282.62254486111</v>
+        <v>46286.64173940972</v>
       </c>
       <c r="S373">
         <v>2</v>
       </c>
       <c r="T373" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="V373" t="s">
         <v>255</v>
       </c>
+      <c r="W373" t="s">
+        <v>362</v>
+      </c>
       <c r="AA373">
         <v>0</v>
       </c>
       <c r="AB373" t="s">
-        <v>208</v>
+        <v>453</v>
       </c>
       <c r="AG373" t="s">
         <v>457</v>
       </c>
       <c r="AH373" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="374" spans="1:34">
       <c r="A374">
-        <v>6627</v>
+        <v>6949</v>
       </c>
       <c r="B374" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C374" t="s">
         <v>58</v>
@@ -27851,10 +27860,10 @@
         <v>59</v>
       </c>
       <c r="E374" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F374" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G374">
         <v>1697</v>
@@ -27866,60 +27875,51 @@
         <v>67</v>
       </c>
       <c r="J374" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L374" s="1">
         <v>46286</v>
       </c>
-      <c r="M374" t="s">
-        <v>197</v>
-      </c>
       <c r="N374" t="s">
         <v>203</v>
       </c>
       <c r="O374">
-        <v>17042403</v>
+        <v>18178280</v>
       </c>
       <c r="P374" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Q374" t="s">
         <v>236</v>
       </c>
       <c r="R374" s="1">
-        <v>46286.64173940972</v>
+        <v>46283.44840582176</v>
       </c>
       <c r="S374">
         <v>2</v>
       </c>
       <c r="T374" t="s">
-        <v>240</v>
-      </c>
-      <c r="V374" t="s">
-        <v>255</v>
-      </c>
-      <c r="W374" t="s">
-        <v>363</v>
+        <v>242</v>
       </c>
       <c r="AA374">
         <v>0</v>
       </c>
       <c r="AB374" t="s">
-        <v>453</v>
+        <v>208</v>
       </c>
       <c r="AG374" t="s">
         <v>457</v>
       </c>
       <c r="AH374" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="375" spans="1:34">
       <c r="A375">
-        <v>6949</v>
+        <v>6704</v>
       </c>
       <c r="B375" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C375" t="s">
         <v>58</v>
@@ -27931,63 +27931,66 @@
         <v>62</v>
       </c>
       <c r="F375" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G375">
-        <v>1697</v>
+        <v>7868</v>
       </c>
       <c r="H375">
-        <v>1650</v>
+        <v>0</v>
       </c>
       <c r="I375" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J375" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="L375" s="1">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="N375" t="s">
         <v>203</v>
       </c>
       <c r="O375">
-        <v>18178280</v>
+        <v>17955421</v>
       </c>
       <c r="P375" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="Q375" t="s">
         <v>236</v>
       </c>
       <c r="R375" s="1">
-        <v>46283.44840582176</v>
+        <v>46267.47365627315</v>
       </c>
       <c r="S375">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="T375" t="s">
-        <v>242</v>
+        <v>245</v>
+      </c>
+      <c r="V375" t="s">
+        <v>255</v>
       </c>
       <c r="AA375">
         <v>0</v>
       </c>
       <c r="AB375" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="AG375" t="s">
         <v>457</v>
       </c>
       <c r="AH375" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="376" spans="1:34">
       <c r="A376">
-        <v>6704</v>
+        <v>5417</v>
       </c>
       <c r="B376" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C376" t="s">
         <v>58</v>
@@ -28002,7 +28005,7 @@
         <v>64</v>
       </c>
       <c r="G376">
-        <v>7868</v>
+        <v>6890</v>
       </c>
       <c r="H376">
         <v>0</v>
@@ -28014,43 +28017,46 @@
         <v>136</v>
       </c>
       <c r="L376" s="1">
-        <v>46293</v>
+        <v>46290</v>
+      </c>
+      <c r="M376" t="s">
+        <v>194</v>
       </c>
       <c r="N376" t="s">
         <v>203</v>
       </c>
       <c r="O376">
-        <v>17955421</v>
+        <v>17399260</v>
       </c>
       <c r="P376" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q376" t="s">
         <v>236</v>
       </c>
       <c r="R376" s="1">
-        <v>46267.47365627315</v>
+        <v>46287.48052434028</v>
       </c>
       <c r="S376">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="T376" t="s">
-        <v>245</v>
-      </c>
-      <c r="V376" t="s">
-        <v>255</v>
+        <v>244</v>
+      </c>
+      <c r="W376" t="s">
+        <v>345</v>
       </c>
       <c r="AA376">
         <v>0</v>
       </c>
       <c r="AB376" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AG376" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AH376" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="377" spans="1:34">
@@ -28073,7 +28079,7 @@
         <v>64</v>
       </c>
       <c r="G377">
-        <v>6890</v>
+        <v>11276</v>
       </c>
       <c r="H377">
         <v>0</v>
@@ -28082,19 +28088,16 @@
         <v>68</v>
       </c>
       <c r="J377" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="L377" s="1">
-        <v>46290</v>
-      </c>
-      <c r="M377" t="s">
-        <v>194</v>
+        <v>46283</v>
       </c>
       <c r="N377" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="O377">
-        <v>17399260</v>
+        <v>17399423</v>
       </c>
       <c r="P377" t="s">
         <v>212</v>
@@ -28103,25 +28106,22 @@
         <v>236</v>
       </c>
       <c r="R377" s="1">
-        <v>46287.48052434028</v>
+        <v>46266.47620831019</v>
       </c>
       <c r="S377">
-        <v>-2</v>
+        <v>5</v>
       </c>
       <c r="T377" t="s">
         <v>244</v>
       </c>
-      <c r="W377" t="s">
-        <v>346</v>
-      </c>
       <c r="AA377">
         <v>0</v>
       </c>
       <c r="AB377" t="s">
-        <v>212</v>
+        <v>454</v>
       </c>
       <c r="AG377" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AH377" t="s">
         <v>462</v>
@@ -28129,10 +28129,10 @@
     </row>
     <row r="378" spans="1:34">
       <c r="A378">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B378" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C378" t="s">
         <v>58</v>
@@ -28156,7 +28156,7 @@
         <v>68</v>
       </c>
       <c r="J378" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L378" s="1">
         <v>46283</v>
@@ -28165,28 +28165,31 @@
         <v>205</v>
       </c>
       <c r="O378">
-        <v>17399423</v>
+        <v>18152557</v>
       </c>
       <c r="P378" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="Q378" t="s">
         <v>236</v>
       </c>
       <c r="R378" s="1">
-        <v>46266.47620831019</v>
+        <v>46267.57586420139</v>
       </c>
       <c r="S378">
         <v>5</v>
       </c>
       <c r="T378" t="s">
-        <v>244</v>
+        <v>246</v>
+      </c>
+      <c r="V378" t="s">
+        <v>255</v>
       </c>
       <c r="AA378">
         <v>0</v>
       </c>
       <c r="AB378" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG378" t="s">
         <v>457</v>
@@ -28197,10 +28200,10 @@
     </row>
     <row r="379" spans="1:34">
       <c r="A379">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B379" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C379" t="s">
         <v>58</v>
@@ -28215,7 +28218,7 @@
         <v>64</v>
       </c>
       <c r="G379">
-        <v>11276</v>
+        <v>1583</v>
       </c>
       <c r="H379">
         <v>0</v>
@@ -28224,43 +28227,40 @@
         <v>68</v>
       </c>
       <c r="J379" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L379" s="1">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="N379" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O379">
-        <v>18152557</v>
+        <v>17398917</v>
       </c>
       <c r="P379" t="s">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="Q379" t="s">
         <v>236</v>
       </c>
       <c r="R379" s="1">
-        <v>46267.57586420139</v>
+        <v>46233.72355880787</v>
       </c>
       <c r="S379">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="T379" t="s">
-        <v>246</v>
-      </c>
-      <c r="V379" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="AA379">
         <v>0</v>
       </c>
       <c r="AB379" t="s">
-        <v>455</v>
+        <v>212</v>
       </c>
       <c r="AG379" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AH379" t="s">
         <v>462</v>
@@ -28268,10 +28268,10 @@
     </row>
     <row r="380" spans="1:34">
       <c r="A380">
-        <v>5417</v>
+        <v>5617</v>
       </c>
       <c r="B380" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C380" t="s">
         <v>58</v>
@@ -28295,7 +28295,7 @@
         <v>68</v>
       </c>
       <c r="J380" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="L380" s="1">
         <v>46290</v>
@@ -28304,42 +28304,36 @@
         <v>206</v>
       </c>
       <c r="O380">
-        <v>17398917</v>
-      </c>
-      <c r="P380" t="s">
-        <v>212</v>
+        <v>17407553</v>
       </c>
       <c r="Q380" t="s">
         <v>236</v>
       </c>
       <c r="R380" s="1">
-        <v>46233.72355880787</v>
+        <v>46261.36669849537</v>
       </c>
       <c r="S380">
         <v>-2</v>
       </c>
       <c r="T380" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="AA380">
         <v>0</v>
       </c>
       <c r="AB380" t="s">
-        <v>212</v>
+        <v>448</v>
       </c>
       <c r="AG380" t="s">
         <v>458</v>
       </c>
-      <c r="AH380" t="s">
-        <v>462</v>
-      </c>
     </row>
     <row r="381" spans="1:34">
       <c r="A381">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B381" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C381" t="s">
         <v>58</v>
@@ -28351,7 +28345,7 @@
         <v>62</v>
       </c>
       <c r="F381" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G381">
         <v>1583</v>
@@ -28363,7 +28357,7 @@
         <v>68</v>
       </c>
       <c r="J381" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="L381" s="1">
         <v>46290</v>
@@ -28372,13 +28366,13 @@
         <v>206</v>
       </c>
       <c r="O381">
-        <v>17407553</v>
+        <v>17688645</v>
       </c>
       <c r="Q381" t="s">
         <v>236</v>
       </c>
       <c r="R381" s="1">
-        <v>46261.36669849537</v>
+        <v>46266.44156952546</v>
       </c>
       <c r="S381">
         <v>-2</v>
@@ -28386,11 +28380,14 @@
       <c r="T381" t="s">
         <v>249</v>
       </c>
+      <c r="V381" t="s">
+        <v>255</v>
+      </c>
       <c r="AA381">
         <v>0</v>
       </c>
       <c r="AB381" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="AG381" t="s">
         <v>458</v>
@@ -28398,10 +28395,10 @@
     </row>
     <row r="382" spans="1:34">
       <c r="A382">
-        <v>6224</v>
+        <v>6278</v>
       </c>
       <c r="B382" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C382" t="s">
         <v>58</v>
@@ -28413,7 +28410,7 @@
         <v>62</v>
       </c>
       <c r="F382" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G382">
         <v>1583</v>
@@ -28425,7 +28422,7 @@
         <v>68</v>
       </c>
       <c r="J382" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="L382" s="1">
         <v>46290</v>
@@ -28434,28 +28431,31 @@
         <v>206</v>
       </c>
       <c r="O382">
-        <v>17688645</v>
+        <v>18166312</v>
       </c>
       <c r="Q382" t="s">
         <v>236</v>
       </c>
       <c r="R382" s="1">
-        <v>46266.44156952546</v>
+        <v>46233.50562820602</v>
       </c>
       <c r="S382">
         <v>-2</v>
       </c>
       <c r="T382" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="V382" t="s">
         <v>255</v>
       </c>
+      <c r="W382" t="s">
+        <v>363</v>
+      </c>
       <c r="AA382">
         <v>0</v>
       </c>
       <c r="AB382" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="AG382" t="s">
         <v>458</v>
@@ -28463,10 +28463,10 @@
     </row>
     <row r="383" spans="1:34">
       <c r="A383">
-        <v>6278</v>
+        <v>6486</v>
       </c>
       <c r="B383" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C383" t="s">
         <v>58</v>
@@ -28490,7 +28490,7 @@
         <v>68</v>
       </c>
       <c r="J383" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="L383" s="1">
         <v>46290</v>
@@ -28499,42 +28499,45 @@
         <v>206</v>
       </c>
       <c r="O383">
-        <v>18166312</v>
+        <v>18114208</v>
+      </c>
+      <c r="P383" t="s">
+        <v>230</v>
       </c>
       <c r="Q383" t="s">
         <v>236</v>
       </c>
       <c r="R383" s="1">
-        <v>46233.50562820602</v>
+        <v>46233.80164280093</v>
       </c>
       <c r="S383">
         <v>-2</v>
       </c>
       <c r="T383" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="V383" t="s">
         <v>255</v>
       </c>
-      <c r="W383" t="s">
-        <v>364</v>
-      </c>
       <c r="AA383">
         <v>0</v>
       </c>
       <c r="AB383" t="s">
-        <v>451</v>
+        <v>230</v>
       </c>
       <c r="AG383" t="s">
         <v>458</v>
       </c>
+      <c r="AH383" t="s">
+        <v>462</v>
+      </c>
     </row>
     <row r="384" spans="1:34">
       <c r="A384">
-        <v>6486</v>
+        <v>6704</v>
       </c>
       <c r="B384" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C384" t="s">
         <v>58</v>
@@ -28558,7 +28561,7 @@
         <v>68</v>
       </c>
       <c r="J384" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="L384" s="1">
         <v>46290</v>
@@ -28567,22 +28570,22 @@
         <v>206</v>
       </c>
       <c r="O384">
-        <v>18114208</v>
+        <v>17955373</v>
       </c>
       <c r="P384" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="Q384" t="s">
         <v>236</v>
       </c>
       <c r="R384" s="1">
-        <v>46233.80164280093</v>
+        <v>46232.72913953703</v>
       </c>
       <c r="S384">
         <v>-2</v>
       </c>
       <c r="T384" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="V384" t="s">
         <v>255</v>
@@ -28591,21 +28594,21 @@
         <v>0</v>
       </c>
       <c r="AB384" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="AG384" t="s">
         <v>458</v>
       </c>
       <c r="AH384" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="385" spans="1:34">
       <c r="A385">
-        <v>6704</v>
+        <v>5417</v>
       </c>
       <c r="B385" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C385" t="s">
         <v>58</v>
@@ -28620,7 +28623,7 @@
         <v>64</v>
       </c>
       <c r="G385">
-        <v>1583</v>
+        <v>11514</v>
       </c>
       <c r="H385">
         <v>0</v>
@@ -28629,46 +28632,49 @@
         <v>68</v>
       </c>
       <c r="J385" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="L385" s="1">
         <v>46290</v>
       </c>
+      <c r="M385" t="s">
+        <v>194</v>
+      </c>
       <c r="N385" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="O385">
-        <v>17955373</v>
+        <v>17399465</v>
       </c>
       <c r="P385" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q385" t="s">
         <v>236</v>
       </c>
       <c r="R385" s="1">
-        <v>46232.72913953703</v>
+        <v>46287.48083141204</v>
       </c>
       <c r="S385">
         <v>-2</v>
       </c>
       <c r="T385" t="s">
-        <v>245</v>
-      </c>
-      <c r="V385" t="s">
-        <v>255</v>
+        <v>244</v>
+      </c>
+      <c r="W385" t="s">
+        <v>345</v>
       </c>
       <c r="AA385">
         <v>0</v>
       </c>
       <c r="AB385" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AG385" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AH385" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="386" spans="1:34">
@@ -28691,7 +28697,7 @@
         <v>64</v>
       </c>
       <c r="G386">
-        <v>11514</v>
+        <v>7874</v>
       </c>
       <c r="H386">
         <v>0</v>
@@ -28700,19 +28706,16 @@
         <v>68</v>
       </c>
       <c r="J386" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L386" s="1">
-        <v>46290</v>
-      </c>
-      <c r="M386" t="s">
-        <v>194</v>
+        <v>46295</v>
       </c>
       <c r="N386" t="s">
         <v>203</v>
       </c>
       <c r="O386">
-        <v>17399465</v>
+        <v>17399320</v>
       </c>
       <c r="P386" t="s">
         <v>212</v>
@@ -28721,25 +28724,25 @@
         <v>236</v>
       </c>
       <c r="R386" s="1">
-        <v>46287.48083141204</v>
+        <v>46283.6781059838</v>
       </c>
       <c r="S386">
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="T386" t="s">
         <v>244</v>
       </c>
       <c r="W386" t="s">
-        <v>346</v>
+        <v>364</v>
       </c>
       <c r="AA386">
         <v>0</v>
       </c>
       <c r="AB386" t="s">
-        <v>212</v>
+        <v>451</v>
       </c>
       <c r="AG386" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AH386" t="s">
         <v>462</v>
@@ -28765,25 +28768,25 @@
         <v>64</v>
       </c>
       <c r="G387">
-        <v>7874</v>
+        <v>1628</v>
       </c>
       <c r="H387">
-        <v>0</v>
+        <v>1581</v>
       </c>
       <c r="I387" t="s">
         <v>68</v>
       </c>
       <c r="J387" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="L387" s="1">
-        <v>46295</v>
+        <v>46286</v>
       </c>
       <c r="N387" t="s">
         <v>203</v>
       </c>
       <c r="O387">
-        <v>17399320</v>
+        <v>17398925</v>
       </c>
       <c r="P387" t="s">
         <v>212</v>
@@ -28792,22 +28795,19 @@
         <v>236</v>
       </c>
       <c r="R387" s="1">
-        <v>46283.6781059838</v>
+        <v>46280.37528408565</v>
       </c>
       <c r="S387">
-        <v>-7</v>
+        <v>2</v>
       </c>
       <c r="T387" t="s">
         <v>244</v>
       </c>
-      <c r="W387" t="s">
-        <v>365</v>
-      </c>
       <c r="AA387">
         <v>0</v>
       </c>
       <c r="AB387" t="s">
-        <v>451</v>
+        <v>212</v>
       </c>
       <c r="AG387" t="s">
         <v>457</v>
@@ -28818,16 +28818,16 @@
     </row>
     <row r="388" spans="1:34">
       <c r="A388">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B388" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C388" t="s">
         <v>58</v>
       </c>
       <c r="D388" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E388" t="s">
         <v>62</v>
@@ -28845,7 +28845,7 @@
         <v>68</v>
       </c>
       <c r="J388" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L388" s="1">
         <v>46286</v>
@@ -28854,42 +28854,42 @@
         <v>203</v>
       </c>
       <c r="O388">
-        <v>17398925</v>
+        <v>16962141</v>
       </c>
       <c r="P388" t="s">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="Q388" t="s">
         <v>236</v>
       </c>
       <c r="R388" s="1">
-        <v>46280.37528408565</v>
+        <v>46266.37634084491</v>
       </c>
       <c r="S388">
         <v>2</v>
       </c>
       <c r="T388" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="AA388">
         <v>0</v>
       </c>
       <c r="AB388" t="s">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="AG388" t="s">
         <v>457</v>
       </c>
       <c r="AH388" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="389" spans="1:34">
       <c r="A389">
-        <v>6404</v>
+        <v>6703</v>
       </c>
       <c r="B389" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C389" t="s">
         <v>58</v>
@@ -28913,7 +28913,7 @@
         <v>68</v>
       </c>
       <c r="J389" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L389" s="1">
         <v>46286</v>
@@ -28922,48 +28922,48 @@
         <v>203</v>
       </c>
       <c r="O389">
-        <v>16962141</v>
+        <v>17955176</v>
       </c>
       <c r="P389" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q389" t="s">
         <v>236</v>
       </c>
       <c r="R389" s="1">
-        <v>46266.37634084491</v>
+        <v>46282.42251184028</v>
       </c>
       <c r="S389">
         <v>2</v>
       </c>
       <c r="T389" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AA389">
         <v>0</v>
       </c>
       <c r="AB389" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG389" t="s">
         <v>457</v>
       </c>
       <c r="AH389" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="390" spans="1:34">
       <c r="A390">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B390" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C390" t="s">
         <v>58</v>
       </c>
       <c r="D390" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E390" t="s">
         <v>62</v>
@@ -28981,7 +28981,7 @@
         <v>68</v>
       </c>
       <c r="J390" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L390" s="1">
         <v>46286</v>
@@ -28990,48 +28990,51 @@
         <v>203</v>
       </c>
       <c r="O390">
-        <v>17955176</v>
+        <v>17955384</v>
       </c>
       <c r="P390" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="Q390" t="s">
         <v>236</v>
       </c>
       <c r="R390" s="1">
-        <v>46282.42251184028</v>
+        <v>46267.47452163194</v>
       </c>
       <c r="S390">
         <v>2</v>
       </c>
       <c r="T390" t="s">
-        <v>247</v>
+        <v>245</v>
+      </c>
+      <c r="V390" t="s">
+        <v>255</v>
       </c>
       <c r="AA390">
         <v>0</v>
       </c>
       <c r="AB390" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="AG390" t="s">
         <v>457</v>
       </c>
       <c r="AH390" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="391" spans="1:34">
       <c r="A391">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B391" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C391" t="s">
         <v>58</v>
       </c>
       <c r="D391" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E391" t="s">
         <v>62</v>
@@ -29049,7 +29052,7 @@
         <v>68</v>
       </c>
       <c r="J391" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L391" s="1">
         <v>46286</v>
@@ -29058,7 +29061,7 @@
         <v>203</v>
       </c>
       <c r="O391">
-        <v>17955384</v>
+        <v>17955238</v>
       </c>
       <c r="P391" t="s">
         <v>213</v>
@@ -29067,7 +29070,7 @@
         <v>236</v>
       </c>
       <c r="R391" s="1">
-        <v>46267.47452163194</v>
+        <v>46267.4745221412</v>
       </c>
       <c r="S391">
         <v>2</v>
@@ -29075,9 +29078,6 @@
       <c r="T391" t="s">
         <v>245</v>
       </c>
-      <c r="V391" t="s">
-        <v>255</v>
-      </c>
       <c r="AA391">
         <v>0</v>
       </c>
@@ -29093,10 +29093,10 @@
     </row>
     <row r="392" spans="1:34">
       <c r="A392">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B392" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C392" t="s">
         <v>58</v>
@@ -29120,7 +29120,7 @@
         <v>68</v>
       </c>
       <c r="J392" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L392" s="1">
         <v>46286</v>
@@ -29129,7 +29129,7 @@
         <v>203</v>
       </c>
       <c r="O392">
-        <v>17955238</v>
+        <v>18056729</v>
       </c>
       <c r="P392" t="s">
         <v>213</v>
@@ -29138,7 +29138,7 @@
         <v>236</v>
       </c>
       <c r="R392" s="1">
-        <v>46267.4745221412</v>
+        <v>46267.47452299768</v>
       </c>
       <c r="S392">
         <v>2</v>
@@ -29146,6 +29146,9 @@
       <c r="T392" t="s">
         <v>245</v>
       </c>
+      <c r="V392" t="s">
+        <v>255</v>
+      </c>
       <c r="AA392">
         <v>0</v>
       </c>
@@ -29161,87 +29164,93 @@
     </row>
     <row r="393" spans="1:34">
       <c r="A393">
-        <v>6779</v>
+        <v>6627</v>
       </c>
       <c r="B393" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="C393" t="s">
         <v>58</v>
       </c>
       <c r="D393" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E393" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F393" t="s">
         <v>64</v>
       </c>
       <c r="G393">
-        <v>1628</v>
+        <v>5885</v>
       </c>
       <c r="H393">
-        <v>1581</v>
+        <v>5784</v>
       </c>
       <c r="I393" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J393" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L393" s="1">
-        <v>46286</v>
+        <v>46283</v>
+      </c>
+      <c r="M393" t="s">
+        <v>198</v>
       </c>
       <c r="N393" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O393">
-        <v>18056729</v>
+        <v>18068566</v>
       </c>
       <c r="P393" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q393" t="s">
         <v>236</v>
       </c>
       <c r="R393" s="1">
-        <v>46267.47452299768</v>
+        <v>46281.63558861111</v>
       </c>
       <c r="S393">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T393" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="V393" t="s">
         <v>255</v>
       </c>
+      <c r="W393" t="s">
+        <v>365</v>
+      </c>
       <c r="AA393">
         <v>0</v>
       </c>
       <c r="AB393" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG393" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AH393" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="394" spans="1:34">
       <c r="A394">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B394" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C394" t="s">
         <v>58</v>
       </c>
       <c r="D394" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E394" t="s">
         <v>63</v>
@@ -29259,7 +29268,7 @@
         <v>69</v>
       </c>
       <c r="J394" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L394" s="1">
         <v>46283</v>
@@ -29271,7 +29280,7 @@
         <v>204</v>
       </c>
       <c r="O394">
-        <v>18068566</v>
+        <v>18052485</v>
       </c>
       <c r="P394" t="s">
         <v>214</v>
@@ -29280,7 +29289,7 @@
         <v>236</v>
       </c>
       <c r="R394" s="1">
-        <v>46281.63558861111</v>
+        <v>46281.6358927662</v>
       </c>
       <c r="S394">
         <v>5</v>
@@ -29292,7 +29301,7 @@
         <v>255</v>
       </c>
       <c r="W394" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AA394">
         <v>0</v>
@@ -29309,10 +29318,10 @@
     </row>
     <row r="395" spans="1:34">
       <c r="A395">
-        <v>6628</v>
+        <v>6945</v>
       </c>
       <c r="B395" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C395" t="s">
         <v>58</v>
@@ -29321,10 +29330,10 @@
         <v>60</v>
       </c>
       <c r="E395" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F395" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G395">
         <v>5885</v>
@@ -29336,37 +29345,34 @@
         <v>69</v>
       </c>
       <c r="J395" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L395" s="1">
         <v>46283</v>
       </c>
       <c r="M395" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N395" t="s">
         <v>204</v>
       </c>
       <c r="O395">
-        <v>18052485</v>
+        <v>18206577</v>
       </c>
       <c r="P395" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q395" t="s">
         <v>236</v>
       </c>
       <c r="R395" s="1">
-        <v>46281.6358927662</v>
+        <v>46281.47564895833</v>
       </c>
       <c r="S395">
         <v>5</v>
       </c>
       <c r="T395" t="s">
-        <v>240</v>
-      </c>
-      <c r="V395" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="W395" t="s">
         <v>366</v>
@@ -29375,7 +29381,7 @@
         <v>0</v>
       </c>
       <c r="AB395" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="AG395" t="s">
         <v>458</v>
@@ -29386,28 +29392,28 @@
     </row>
     <row r="396" spans="1:34">
       <c r="A396">
-        <v>6945</v>
+        <v>6703</v>
       </c>
       <c r="B396" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C396" t="s">
         <v>58</v>
       </c>
       <c r="D396" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E396" t="s">
         <v>62</v>
       </c>
       <c r="F396" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G396">
-        <v>5885</v>
+        <v>6395</v>
       </c>
       <c r="H396">
-        <v>5784</v>
+        <v>5792</v>
       </c>
       <c r="I396" t="s">
         <v>69</v>
@@ -29418,41 +29424,35 @@
       <c r="L396" s="1">
         <v>46283</v>
       </c>
-      <c r="M396" t="s">
-        <v>199</v>
-      </c>
       <c r="N396" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O396">
-        <v>18206577</v>
+        <v>18105120</v>
       </c>
       <c r="P396" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="Q396" t="s">
         <v>236</v>
       </c>
       <c r="R396" s="1">
-        <v>46281.47564895833</v>
+        <v>46268.58940019676</v>
       </c>
       <c r="S396">
         <v>5</v>
       </c>
       <c r="T396" t="s">
-        <v>241</v>
-      </c>
-      <c r="W396" t="s">
-        <v>367</v>
+        <v>247</v>
       </c>
       <c r="AA396">
         <v>0</v>
       </c>
       <c r="AB396" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="AG396" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AH396" t="s">
         <v>464</v>
@@ -29460,16 +29460,16 @@
     </row>
     <row r="397" spans="1:34">
       <c r="A397">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B397" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C397" t="s">
         <v>58</v>
       </c>
       <c r="D397" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E397" t="s">
         <v>62</v>
@@ -29478,7 +29478,7 @@
         <v>64</v>
       </c>
       <c r="G397">
-        <v>6395</v>
+        <v>5882</v>
       </c>
       <c r="H397">
         <v>5792</v>
@@ -29492,52 +29492,61 @@
       <c r="L397" s="1">
         <v>46283</v>
       </c>
+      <c r="M397" t="s">
+        <v>199</v>
+      </c>
       <c r="N397" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O397">
-        <v>18105120</v>
+        <v>18195621</v>
       </c>
       <c r="P397" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q397" t="s">
         <v>236</v>
       </c>
       <c r="R397" s="1">
-        <v>46268.58940019676</v>
+        <v>46279.66710767361</v>
       </c>
       <c r="S397">
         <v>5</v>
       </c>
       <c r="T397" t="s">
-        <v>247</v>
+        <v>245</v>
+      </c>
+      <c r="V397" t="s">
+        <v>255</v>
+      </c>
+      <c r="W397" t="s">
+        <v>367</v>
       </c>
       <c r="AA397">
         <v>0</v>
       </c>
       <c r="AB397" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AG397" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AH397" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
     </row>
     <row r="398" spans="1:34">
       <c r="A398">
-        <v>6779</v>
+        <v>5417</v>
       </c>
       <c r="B398" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C398" t="s">
         <v>58</v>
       </c>
       <c r="D398" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E398" t="s">
         <v>62</v>
@@ -29546,7 +29555,7 @@
         <v>64</v>
       </c>
       <c r="G398">
-        <v>5882</v>
+        <v>5883</v>
       </c>
       <c r="H398">
         <v>5792</v>
@@ -29555,60 +29564,48 @@
         <v>69</v>
       </c>
       <c r="J398" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="L398" s="1">
-        <v>46283</v>
-      </c>
-      <c r="M398" t="s">
-        <v>199</v>
+        <v>46286</v>
       </c>
       <c r="N398" t="s">
         <v>204</v>
       </c>
       <c r="O398">
-        <v>18195621</v>
+        <v>17399067</v>
       </c>
       <c r="P398" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="Q398" t="s">
         <v>236</v>
       </c>
       <c r="R398" s="1">
-        <v>46279.66710767361</v>
+        <v>46282.47420876157</v>
       </c>
       <c r="S398">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T398" t="s">
-        <v>245</v>
-      </c>
-      <c r="V398" t="s">
-        <v>255</v>
-      </c>
-      <c r="W398" t="s">
-        <v>368</v>
+        <v>244</v>
       </c>
       <c r="AA398">
         <v>0</v>
       </c>
       <c r="AB398" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="AG398" t="s">
-        <v>458</v>
-      </c>
-      <c r="AH398" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
     </row>
     <row r="399" spans="1:34">
       <c r="A399">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B399" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C399" t="s">
         <v>58</v>
@@ -29637,43 +29634,55 @@
       <c r="L399" s="1">
         <v>46286</v>
       </c>
+      <c r="M399" t="s">
+        <v>200</v>
+      </c>
       <c r="N399" t="s">
         <v>204</v>
       </c>
       <c r="O399">
-        <v>17399067</v>
+        <v>16976067</v>
       </c>
       <c r="P399" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="Q399" t="s">
         <v>236</v>
       </c>
       <c r="R399" s="1">
-        <v>46282.47420876157</v>
+        <v>46281.68877074074</v>
       </c>
       <c r="S399">
         <v>2</v>
       </c>
       <c r="T399" t="s">
-        <v>244</v>
+        <v>246</v>
+      </c>
+      <c r="V399" t="s">
+        <v>255</v>
+      </c>
+      <c r="W399" t="s">
+        <v>368</v>
       </c>
       <c r="AA399">
         <v>0</v>
       </c>
       <c r="AB399" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="AG399" t="s">
         <v>457</v>
       </c>
+      <c r="AH399" t="s">
+        <v>464</v>
+      </c>
     </row>
     <row r="400" spans="1:34">
       <c r="A400">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B400" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C400" t="s">
         <v>58</v>
@@ -29703,28 +29712,28 @@
         <v>46286</v>
       </c>
       <c r="M400" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="N400" t="s">
         <v>204</v>
       </c>
       <c r="O400">
-        <v>16976067</v>
+        <v>17222629</v>
       </c>
       <c r="P400" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Q400" t="s">
         <v>236</v>
       </c>
       <c r="R400" s="1">
-        <v>46281.68877074074</v>
+        <v>46280.57958537037</v>
       </c>
       <c r="S400">
         <v>2</v>
       </c>
       <c r="T400" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="V400" t="s">
         <v>255</v>
@@ -29736,7 +29745,7 @@
         <v>0</v>
       </c>
       <c r="AB400" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="AG400" t="s">
         <v>457</v>
@@ -29747,10 +29756,10 @@
     </row>
     <row r="401" spans="1:34">
       <c r="A401">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B401" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C401" t="s">
         <v>58</v>
@@ -29759,7 +29768,7 @@
         <v>59</v>
       </c>
       <c r="E401" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F401" t="s">
         <v>64</v>
@@ -29780,40 +29789,40 @@
         <v>46286</v>
       </c>
       <c r="M401" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="N401" t="s">
         <v>204</v>
       </c>
       <c r="O401">
-        <v>17222629</v>
+        <v>18068544</v>
       </c>
       <c r="P401" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="Q401" t="s">
         <v>236</v>
       </c>
       <c r="R401" s="1">
-        <v>46280.57958537037</v>
+        <v>46281.63570936343</v>
       </c>
       <c r="S401">
         <v>2</v>
       </c>
       <c r="T401" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="V401" t="s">
         <v>255</v>
       </c>
       <c r="W401" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="AA401">
         <v>0</v>
       </c>
       <c r="AB401" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AG401" t="s">
         <v>457</v>
@@ -29824,16 +29833,16 @@
     </row>
     <row r="402" spans="1:34">
       <c r="A402">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B402" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C402" t="s">
         <v>58</v>
       </c>
       <c r="D402" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E402" t="s">
         <v>63</v>
@@ -29863,7 +29872,7 @@
         <v>204</v>
       </c>
       <c r="O402">
-        <v>18068544</v>
+        <v>18052463</v>
       </c>
       <c r="P402" t="s">
         <v>214</v>
@@ -29872,7 +29881,7 @@
         <v>236</v>
       </c>
       <c r="R402" s="1">
-        <v>46281.63570936343</v>
+        <v>46281.63595871528</v>
       </c>
       <c r="S402">
         <v>2</v>
@@ -29884,7 +29893,7 @@
         <v>255</v>
       </c>
       <c r="W402" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AA402">
         <v>0</v>
@@ -29901,19 +29910,19 @@
     </row>
     <row r="403" spans="1:34">
       <c r="A403">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B403" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C403" t="s">
         <v>58</v>
       </c>
       <c r="D403" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E403" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F403" t="s">
         <v>64</v>
@@ -29933,41 +29942,32 @@
       <c r="L403" s="1">
         <v>46286</v>
       </c>
-      <c r="M403" t="s">
-        <v>200</v>
-      </c>
       <c r="N403" t="s">
         <v>204</v>
       </c>
       <c r="O403">
-        <v>18052463</v>
+        <v>18077112</v>
       </c>
       <c r="P403" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="Q403" t="s">
         <v>236</v>
       </c>
       <c r="R403" s="1">
-        <v>46281.63595871528</v>
+        <v>46279.62681744213</v>
       </c>
       <c r="S403">
         <v>2</v>
       </c>
       <c r="T403" t="s">
-        <v>240</v>
-      </c>
-      <c r="V403" t="s">
-        <v>255</v>
-      </c>
-      <c r="W403" t="s">
-        <v>369</v>
+        <v>247</v>
       </c>
       <c r="AA403">
         <v>0</v>
       </c>
       <c r="AB403" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="AG403" t="s">
         <v>457</v>
@@ -29978,16 +29978,16 @@
     </row>
     <row r="404" spans="1:34">
       <c r="A404">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B404" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C404" t="s">
         <v>58</v>
       </c>
       <c r="D404" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E404" t="s">
         <v>62</v>
@@ -30014,42 +30014,45 @@
         <v>204</v>
       </c>
       <c r="O404">
-        <v>18077112</v>
+        <v>18090189</v>
       </c>
       <c r="P404" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q404" t="s">
         <v>236</v>
       </c>
       <c r="R404" s="1">
-        <v>46279.62681744213</v>
+        <v>46279.66707821759</v>
       </c>
       <c r="S404">
         <v>2</v>
       </c>
       <c r="T404" t="s">
-        <v>247</v>
+        <v>245</v>
+      </c>
+      <c r="V404" t="s">
+        <v>255</v>
       </c>
       <c r="AA404">
         <v>0</v>
       </c>
       <c r="AB404" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AG404" t="s">
         <v>457</v>
       </c>
       <c r="AH404" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
     </row>
     <row r="405" spans="1:34">
       <c r="A405">
-        <v>6779</v>
+        <v>6945</v>
       </c>
       <c r="B405" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C405" t="s">
         <v>58</v>
@@ -30061,7 +30064,7 @@
         <v>62</v>
       </c>
       <c r="F405" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G405">
         <v>5883</v>
@@ -30078,64 +30081,67 @@
       <c r="L405" s="1">
         <v>46286</v>
       </c>
+      <c r="M405" t="s">
+        <v>201</v>
+      </c>
       <c r="N405" t="s">
         <v>204</v>
       </c>
       <c r="O405">
-        <v>18090189</v>
+        <v>18179111</v>
       </c>
       <c r="P405" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="Q405" t="s">
         <v>236</v>
       </c>
       <c r="R405" s="1">
-        <v>46279.66707821759</v>
+        <v>46286.7220354051</v>
       </c>
       <c r="S405">
         <v>2</v>
       </c>
       <c r="T405" t="s">
-        <v>245</v>
-      </c>
-      <c r="V405" t="s">
-        <v>255</v>
+        <v>241</v>
+      </c>
+      <c r="W405" t="s">
+        <v>370</v>
       </c>
       <c r="AA405">
         <v>0</v>
       </c>
       <c r="AB405" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="AG405" t="s">
         <v>457</v>
       </c>
       <c r="AH405" t="s">
-        <v>449</v>
+        <v>464</v>
       </c>
     </row>
     <row r="406" spans="1:34">
       <c r="A406">
-        <v>6945</v>
+        <v>5417</v>
       </c>
       <c r="B406" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C406" t="s">
         <v>58</v>
       </c>
       <c r="D406" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E406" t="s">
         <v>62</v>
       </c>
       <c r="F406" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G406">
-        <v>5883</v>
+        <v>5884</v>
       </c>
       <c r="H406">
         <v>5792</v>
@@ -30144,57 +30150,48 @@
         <v>69</v>
       </c>
       <c r="J406" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L406" s="1">
         <v>46286</v>
       </c>
-      <c r="M406" t="s">
-        <v>201</v>
-      </c>
       <c r="N406" t="s">
         <v>204</v>
       </c>
       <c r="O406">
-        <v>18179111</v>
+        <v>17399077</v>
       </c>
       <c r="P406" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q406" t="s">
         <v>236</v>
       </c>
       <c r="R406" s="1">
-        <v>46286.7220354051</v>
+        <v>46282.47437324074</v>
       </c>
       <c r="S406">
         <v>2</v>
       </c>
       <c r="T406" t="s">
-        <v>241</v>
-      </c>
-      <c r="W406" t="s">
-        <v>371</v>
+        <v>244</v>
       </c>
       <c r="AA406">
         <v>0</v>
       </c>
       <c r="AB406" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG406" t="s">
         <v>457</v>
       </c>
-      <c r="AH406" t="s">
-        <v>464</v>
-      </c>
     </row>
     <row r="407" spans="1:34">
       <c r="A407">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B407" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C407" t="s">
         <v>58</v>
@@ -30223,43 +30220,55 @@
       <c r="L407" s="1">
         <v>46286</v>
       </c>
+      <c r="M407" t="s">
+        <v>200</v>
+      </c>
       <c r="N407" t="s">
         <v>204</v>
       </c>
       <c r="O407">
-        <v>17399077</v>
+        <v>16976077</v>
       </c>
       <c r="P407" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="Q407" t="s">
         <v>236</v>
       </c>
       <c r="R407" s="1">
-        <v>46282.47437324074</v>
+        <v>46281.68880230324</v>
       </c>
       <c r="S407">
         <v>2</v>
       </c>
       <c r="T407" t="s">
-        <v>244</v>
+        <v>246</v>
+      </c>
+      <c r="V407" t="s">
+        <v>255</v>
+      </c>
+      <c r="W407" t="s">
+        <v>368</v>
       </c>
       <c r="AA407">
         <v>0</v>
       </c>
       <c r="AB407" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="AG407" t="s">
         <v>457</v>
       </c>
+      <c r="AH407" t="s">
+        <v>464</v>
+      </c>
     </row>
     <row r="408" spans="1:34">
       <c r="A408">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B408" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C408" t="s">
         <v>58</v>
@@ -30289,40 +30298,40 @@
         <v>46286</v>
       </c>
       <c r="M408" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="N408" t="s">
         <v>204</v>
       </c>
       <c r="O408">
-        <v>16976077</v>
+        <v>17222647</v>
       </c>
       <c r="P408" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Q408" t="s">
         <v>236</v>
       </c>
       <c r="R408" s="1">
-        <v>46281.68880230324</v>
+        <v>46280.57972293982</v>
       </c>
       <c r="S408">
         <v>2</v>
       </c>
       <c r="T408" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="V408" t="s">
         <v>255</v>
       </c>
       <c r="W408" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AA408">
         <v>0</v>
       </c>
       <c r="AB408" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="AG408" t="s">
         <v>457</v>
@@ -30333,10 +30342,10 @@
     </row>
     <row r="409" spans="1:34">
       <c r="A409">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B409" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C409" t="s">
         <v>58</v>
@@ -30345,7 +30354,7 @@
         <v>59</v>
       </c>
       <c r="E409" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F409" t="s">
         <v>64</v>
@@ -30366,40 +30375,40 @@
         <v>46286</v>
       </c>
       <c r="M409" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="N409" t="s">
         <v>204</v>
       </c>
       <c r="O409">
-        <v>17222647</v>
+        <v>18068555</v>
       </c>
       <c r="P409" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="Q409" t="s">
         <v>236</v>
       </c>
       <c r="R409" s="1">
-        <v>46280.57972293982</v>
+        <v>46281.63575075231</v>
       </c>
       <c r="S409">
         <v>2</v>
       </c>
       <c r="T409" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="V409" t="s">
         <v>255</v>
       </c>
       <c r="W409" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="AA409">
         <v>0</v>
       </c>
       <c r="AB409" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AG409" t="s">
         <v>457</v>
@@ -30410,16 +30419,16 @@
     </row>
     <row r="410" spans="1:34">
       <c r="A410">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B410" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C410" t="s">
         <v>58</v>
       </c>
       <c r="D410" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E410" t="s">
         <v>63</v>
@@ -30449,7 +30458,7 @@
         <v>204</v>
       </c>
       <c r="O410">
-        <v>18068555</v>
+        <v>18052474</v>
       </c>
       <c r="P410" t="s">
         <v>214</v>
@@ -30458,7 +30467,7 @@
         <v>236</v>
       </c>
       <c r="R410" s="1">
-        <v>46281.63575075231</v>
+        <v>46281.63599785879</v>
       </c>
       <c r="S410">
         <v>2</v>
@@ -30470,7 +30479,7 @@
         <v>255</v>
       </c>
       <c r="W410" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AA410">
         <v>0</v>
@@ -30487,19 +30496,19 @@
     </row>
     <row r="411" spans="1:34">
       <c r="A411">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B411" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C411" t="s">
         <v>58</v>
       </c>
       <c r="D411" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E411" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F411" t="s">
         <v>64</v>
@@ -30519,41 +30528,32 @@
       <c r="L411" s="1">
         <v>46286</v>
       </c>
-      <c r="M411" t="s">
-        <v>200</v>
-      </c>
       <c r="N411" t="s">
         <v>204</v>
       </c>
       <c r="O411">
-        <v>18052474</v>
+        <v>18077122</v>
       </c>
       <c r="P411" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="Q411" t="s">
         <v>236</v>
       </c>
       <c r="R411" s="1">
-        <v>46281.63599785879</v>
+        <v>46279.6268503125</v>
       </c>
       <c r="S411">
         <v>2</v>
       </c>
       <c r="T411" t="s">
-        <v>240</v>
-      </c>
-      <c r="V411" t="s">
-        <v>255</v>
-      </c>
-      <c r="W411" t="s">
-        <v>369</v>
+        <v>247</v>
       </c>
       <c r="AA411">
         <v>0</v>
       </c>
       <c r="AB411" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="AG411" t="s">
         <v>457</v>
@@ -30564,16 +30564,16 @@
     </row>
     <row r="412" spans="1:34">
       <c r="A412">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B412" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C412" t="s">
         <v>58</v>
       </c>
       <c r="D412" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E412" t="s">
         <v>62</v>
@@ -30600,42 +30600,45 @@
         <v>204</v>
       </c>
       <c r="O412">
-        <v>18077122</v>
+        <v>18090199</v>
       </c>
       <c r="P412" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q412" t="s">
         <v>236</v>
       </c>
       <c r="R412" s="1">
-        <v>46279.6268503125</v>
+        <v>46279.66698128472</v>
       </c>
       <c r="S412">
         <v>2</v>
       </c>
       <c r="T412" t="s">
-        <v>247</v>
+        <v>245</v>
+      </c>
+      <c r="V412" t="s">
+        <v>255</v>
       </c>
       <c r="AA412">
         <v>0</v>
       </c>
       <c r="AB412" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AG412" t="s">
         <v>457</v>
       </c>
       <c r="AH412" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
     </row>
     <row r="413" spans="1:34">
       <c r="A413">
-        <v>6779</v>
+        <v>6945</v>
       </c>
       <c r="B413" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C413" t="s">
         <v>58</v>
@@ -30647,7 +30650,7 @@
         <v>62</v>
       </c>
       <c r="F413" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G413">
         <v>5884</v>
@@ -30664,100 +30667,100 @@
       <c r="L413" s="1">
         <v>46286</v>
       </c>
+      <c r="M413" t="s">
+        <v>201</v>
+      </c>
       <c r="N413" t="s">
         <v>204</v>
       </c>
       <c r="O413">
-        <v>18090199</v>
+        <v>18179118</v>
       </c>
       <c r="P413" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="Q413" t="s">
         <v>236</v>
       </c>
       <c r="R413" s="1">
-        <v>46279.66698128472</v>
+        <v>46286.7221544213</v>
       </c>
       <c r="S413">
         <v>2</v>
       </c>
       <c r="T413" t="s">
-        <v>245</v>
-      </c>
-      <c r="V413" t="s">
-        <v>255</v>
+        <v>241</v>
+      </c>
+      <c r="W413" t="s">
+        <v>372</v>
       </c>
       <c r="AA413">
         <v>0</v>
       </c>
       <c r="AB413" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="AG413" t="s">
         <v>457</v>
       </c>
       <c r="AH413" t="s">
-        <v>449</v>
+        <v>464</v>
       </c>
     </row>
     <row r="414" spans="1:34">
       <c r="A414">
-        <v>6945</v>
+        <v>5417</v>
       </c>
       <c r="B414" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C414" t="s">
         <v>58</v>
       </c>
       <c r="D414" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E414" t="s">
         <v>62</v>
       </c>
       <c r="F414" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G414">
-        <v>5884</v>
+        <v>7012</v>
       </c>
       <c r="H414">
-        <v>5792</v>
+        <v>0</v>
       </c>
       <c r="I414" t="s">
         <v>69</v>
       </c>
       <c r="J414" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="L414" s="1">
-        <v>46286</v>
-      </c>
-      <c r="M414" t="s">
-        <v>201</v>
+        <v>46281</v>
       </c>
       <c r="N414" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O414">
-        <v>18179118</v>
+        <v>18257773</v>
       </c>
       <c r="P414" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q414" t="s">
         <v>236</v>
       </c>
       <c r="R414" s="1">
-        <v>46286.7221544213</v>
+        <v>46279.66929922454</v>
       </c>
       <c r="S414">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T414" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="W414" t="s">
         <v>373</v>
@@ -30766,27 +30769,24 @@
         <v>0</v>
       </c>
       <c r="AB414" t="s">
-        <v>215</v>
+        <v>446</v>
       </c>
       <c r="AG414" t="s">
         <v>457</v>
       </c>
-      <c r="AH414" t="s">
-        <v>464</v>
-      </c>
     </row>
     <row r="415" spans="1:34">
       <c r="A415">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B415" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C415" t="s">
         <v>58</v>
       </c>
       <c r="D415" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E415" t="s">
         <v>62</v>
@@ -30804,7 +30804,7 @@
         <v>69</v>
       </c>
       <c r="J415" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L415" s="1">
         <v>46281</v>
@@ -30813,22 +30813,22 @@
         <v>203</v>
       </c>
       <c r="O415">
-        <v>18257773</v>
+        <v>18258536</v>
       </c>
       <c r="P415" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q415" t="s">
         <v>236</v>
       </c>
       <c r="R415" s="1">
-        <v>46279.66929922454</v>
+        <v>46280.61353684028</v>
       </c>
       <c r="S415">
         <v>7</v>
       </c>
       <c r="T415" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="W415" t="s">
         <v>374</v>
@@ -30842,19 +30842,22 @@
       <c r="AG415" t="s">
         <v>457</v>
       </c>
+      <c r="AH415" t="s">
+        <v>449</v>
+      </c>
     </row>
     <row r="416" spans="1:34">
       <c r="A416">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B416" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C416" t="s">
         <v>58</v>
       </c>
       <c r="D416" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E416" t="s">
         <v>62</v>
@@ -30872,7 +30875,7 @@
         <v>69</v>
       </c>
       <c r="J416" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L416" s="1">
         <v>46281</v>
@@ -30881,22 +30884,25 @@
         <v>203</v>
       </c>
       <c r="O416">
-        <v>18258536</v>
+        <v>18254964</v>
       </c>
       <c r="P416" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="Q416" t="s">
         <v>236</v>
       </c>
       <c r="R416" s="1">
-        <v>46280.61353684028</v>
+        <v>46280.61353920139</v>
       </c>
       <c r="S416">
         <v>7</v>
       </c>
       <c r="T416" t="s">
-        <v>248</v>
+        <v>246</v>
+      </c>
+      <c r="V416" t="s">
+        <v>255</v>
       </c>
       <c r="W416" t="s">
         <v>375</v>
@@ -30911,15 +30917,15 @@
         <v>457</v>
       </c>
       <c r="AH416" t="s">
-        <v>449</v>
+        <v>464</v>
       </c>
     </row>
     <row r="417" spans="1:34">
       <c r="A417">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B417" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C417" t="s">
         <v>58</v>
@@ -30943,7 +30949,7 @@
         <v>69</v>
       </c>
       <c r="J417" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L417" s="1">
         <v>46281</v>
@@ -30952,22 +30958,22 @@
         <v>203</v>
       </c>
       <c r="O417">
-        <v>18254964</v>
+        <v>18255116</v>
       </c>
       <c r="P417" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Q417" t="s">
         <v>236</v>
       </c>
       <c r="R417" s="1">
-        <v>46280.61353920139</v>
+        <v>46279.63250563657</v>
       </c>
       <c r="S417">
         <v>7</v>
       </c>
       <c r="T417" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="V417" t="s">
         <v>255</v>
@@ -30990,10 +30996,10 @@
     </row>
     <row r="418" spans="1:34">
       <c r="A418">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B418" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C418" t="s">
         <v>58</v>
@@ -31002,7 +31008,7 @@
         <v>59</v>
       </c>
       <c r="E418" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F418" t="s">
         <v>64</v>
@@ -31017,7 +31023,7 @@
         <v>69</v>
       </c>
       <c r="J418" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L418" s="1">
         <v>46281</v>
@@ -31026,28 +31032,28 @@
         <v>203</v>
       </c>
       <c r="O418">
-        <v>18255116</v>
+        <v>18257668</v>
       </c>
       <c r="P418" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="Q418" t="s">
         <v>236</v>
       </c>
       <c r="R418" s="1">
-        <v>46279.63250563657</v>
+        <v>46280.61354019676</v>
       </c>
       <c r="S418">
         <v>7</v>
       </c>
       <c r="T418" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="V418" t="s">
         <v>255</v>
       </c>
       <c r="W418" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="AA418">
         <v>0</v>
@@ -31064,16 +31070,16 @@
     </row>
     <row r="419" spans="1:34">
       <c r="A419">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B419" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C419" t="s">
         <v>58</v>
       </c>
       <c r="D419" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E419" t="s">
         <v>63</v>
@@ -31091,7 +31097,7 @@
         <v>69</v>
       </c>
       <c r="J419" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L419" s="1">
         <v>46281</v>
@@ -31100,7 +31106,7 @@
         <v>203</v>
       </c>
       <c r="O419">
-        <v>18257668</v>
+        <v>18256366</v>
       </c>
       <c r="P419" t="s">
         <v>214</v>
@@ -31109,7 +31115,7 @@
         <v>236</v>
       </c>
       <c r="R419" s="1">
-        <v>46280.61354019676</v>
+        <v>46280.6135403125</v>
       </c>
       <c r="S419">
         <v>7</v>
@@ -31121,7 +31127,7 @@
         <v>255</v>
       </c>
       <c r="W419" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AA419">
         <v>0</v>
@@ -31138,19 +31144,19 @@
     </row>
     <row r="420" spans="1:34">
       <c r="A420">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B420" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C420" t="s">
         <v>58</v>
       </c>
       <c r="D420" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E420" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F420" t="s">
         <v>64</v>
@@ -31165,43 +31171,43 @@
         <v>69</v>
       </c>
       <c r="J420" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L420" s="1">
         <v>46281</v>
       </c>
+      <c r="M420" t="s">
+        <v>198</v>
+      </c>
       <c r="N420" t="s">
         <v>203</v>
       </c>
       <c r="O420">
-        <v>18256366</v>
+        <v>18256433</v>
       </c>
       <c r="P420" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="Q420" t="s">
         <v>236</v>
       </c>
       <c r="R420" s="1">
-        <v>46280.6135403125</v>
+        <v>46281.71218414352</v>
       </c>
       <c r="S420">
         <v>7</v>
       </c>
       <c r="T420" t="s">
-        <v>240</v>
-      </c>
-      <c r="V420" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="W420" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AA420">
         <v>0</v>
       </c>
       <c r="AB420" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="AG420" t="s">
         <v>457</v>
@@ -31212,16 +31218,16 @@
     </row>
     <row r="421" spans="1:34">
       <c r="A421">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B421" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C421" t="s">
         <v>58</v>
       </c>
       <c r="D421" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E421" t="s">
         <v>62</v>
@@ -31239,34 +31245,34 @@
         <v>69</v>
       </c>
       <c r="J421" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L421" s="1">
         <v>46281</v>
       </c>
-      <c r="M421" t="s">
-        <v>198</v>
-      </c>
       <c r="N421" t="s">
         <v>203</v>
       </c>
       <c r="O421">
-        <v>18256433</v>
+        <v>18255012</v>
       </c>
       <c r="P421" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q421" t="s">
         <v>236</v>
       </c>
       <c r="R421" s="1">
-        <v>46281.71218414352</v>
+        <v>46281.41576883102</v>
       </c>
       <c r="S421">
         <v>7</v>
       </c>
       <c r="T421" t="s">
-        <v>247</v>
+        <v>245</v>
+      </c>
+      <c r="V421" t="s">
+        <v>255</v>
       </c>
       <c r="W421" t="s">
         <v>378</v>
@@ -31275,21 +31281,21 @@
         <v>0</v>
       </c>
       <c r="AB421" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="AG421" t="s">
         <v>457</v>
       </c>
       <c r="AH421" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
     </row>
     <row r="422" spans="1:34">
       <c r="A422">
-        <v>6779</v>
+        <v>6945</v>
       </c>
       <c r="B422" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C422" t="s">
         <v>58</v>
@@ -31301,7 +31307,7 @@
         <v>62</v>
       </c>
       <c r="F422" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G422">
         <v>7012</v>
@@ -31313,7 +31319,7 @@
         <v>69</v>
       </c>
       <c r="J422" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L422" s="1">
         <v>46281</v>
@@ -31322,25 +31328,22 @@
         <v>203</v>
       </c>
       <c r="O422">
-        <v>18255012</v>
+        <v>18254903</v>
       </c>
       <c r="P422" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="Q422" t="s">
         <v>236</v>
       </c>
       <c r="R422" s="1">
-        <v>46281.41576883102</v>
+        <v>46280.43132989584</v>
       </c>
       <c r="S422">
         <v>7</v>
       </c>
       <c r="T422" t="s">
-        <v>245</v>
-      </c>
-      <c r="V422" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="W422" t="s">
         <v>379</v>
@@ -31355,21 +31358,21 @@
         <v>457</v>
       </c>
       <c r="AH422" t="s">
-        <v>449</v>
+        <v>464</v>
       </c>
     </row>
     <row r="423" spans="1:34">
       <c r="A423">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B423" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C423" t="s">
         <v>58</v>
       </c>
       <c r="D423" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E423" t="s">
         <v>62</v>
@@ -31387,7 +31390,7 @@
         <v>69</v>
       </c>
       <c r="J423" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L423" s="1">
         <v>46281</v>
@@ -31396,22 +31399,22 @@
         <v>203</v>
       </c>
       <c r="O423">
-        <v>18254903</v>
+        <v>18258489</v>
       </c>
       <c r="P423" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q423" t="s">
         <v>236</v>
       </c>
       <c r="R423" s="1">
-        <v>46280.43132989584</v>
+        <v>46280.61367623843</v>
       </c>
       <c r="S423">
         <v>7</v>
       </c>
       <c r="T423" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="W423" t="s">
         <v>380</v>
@@ -31426,15 +31429,15 @@
         <v>457</v>
       </c>
       <c r="AH423" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="424" spans="1:34">
       <c r="A424">
-        <v>6949</v>
+        <v>5417</v>
       </c>
       <c r="B424" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C424" t="s">
         <v>58</v>
@@ -31446,13 +31449,13 @@
         <v>62</v>
       </c>
       <c r="F424" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G424">
-        <v>7012</v>
+        <v>5836</v>
       </c>
       <c r="H424">
-        <v>0</v>
+        <v>5784</v>
       </c>
       <c r="I424" t="s">
         <v>69</v>
@@ -31461,28 +31464,31 @@
         <v>155</v>
       </c>
       <c r="L424" s="1">
-        <v>46281</v>
+        <v>46286</v>
+      </c>
+      <c r="M424" t="s">
+        <v>197</v>
       </c>
       <c r="N424" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O424">
-        <v>18258489</v>
+        <v>17399027</v>
       </c>
       <c r="P424" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q424" t="s">
         <v>236</v>
       </c>
       <c r="R424" s="1">
-        <v>46280.61367623843</v>
+        <v>46286.71510853009</v>
       </c>
       <c r="S424">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="T424" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="W424" t="s">
         <v>381</v>
@@ -31491,21 +31497,18 @@
         <v>0</v>
       </c>
       <c r="AB424" t="s">
-        <v>446</v>
+        <v>217</v>
       </c>
       <c r="AG424" t="s">
         <v>457</v>
       </c>
-      <c r="AH424" t="s">
-        <v>465</v>
-      </c>
     </row>
     <row r="425" spans="1:34">
       <c r="A425">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B425" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C425" t="s">
         <v>58</v>
@@ -31529,34 +31532,37 @@
         <v>69</v>
       </c>
       <c r="J425" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="L425" s="1">
         <v>46286</v>
       </c>
       <c r="M425" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="N425" t="s">
         <v>204</v>
       </c>
       <c r="O425">
-        <v>17399027</v>
+        <v>16976037</v>
       </c>
       <c r="P425" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="Q425" t="s">
         <v>236</v>
       </c>
       <c r="R425" s="1">
-        <v>46286.71510853009</v>
+        <v>46283.59424842593</v>
       </c>
       <c r="S425">
         <v>2</v>
       </c>
       <c r="T425" t="s">
-        <v>244</v>
+        <v>246</v>
+      </c>
+      <c r="V425" t="s">
+        <v>255</v>
       </c>
       <c r="W425" t="s">
         <v>382</v>
@@ -31565,18 +31571,21 @@
         <v>0</v>
       </c>
       <c r="AB425" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="AG425" t="s">
         <v>457</v>
       </c>
+      <c r="AH425" t="s">
+        <v>464</v>
+      </c>
     </row>
     <row r="426" spans="1:34">
       <c r="A426">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B426" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C426" t="s">
         <v>58</v>
@@ -31600,7 +31609,7 @@
         <v>69</v>
       </c>
       <c r="J426" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="L426" s="1">
         <v>46286</v>
@@ -31612,22 +31621,22 @@
         <v>204</v>
       </c>
       <c r="O426">
-        <v>16976037</v>
+        <v>17222579</v>
       </c>
       <c r="P426" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Q426" t="s">
         <v>236</v>
       </c>
       <c r="R426" s="1">
-        <v>46283.59424842593</v>
+        <v>46283.68435655093</v>
       </c>
       <c r="S426">
         <v>2</v>
       </c>
       <c r="T426" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="V426" t="s">
         <v>255</v>
@@ -31639,7 +31648,7 @@
         <v>0</v>
       </c>
       <c r="AB426" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="AG426" t="s">
         <v>457</v>
@@ -31650,10 +31659,10 @@
     </row>
     <row r="427" spans="1:34">
       <c r="A427">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B427" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C427" t="s">
         <v>58</v>
@@ -31662,7 +31671,7 @@
         <v>59</v>
       </c>
       <c r="E427" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F427" t="s">
         <v>64</v>
@@ -31677,7 +31686,7 @@
         <v>69</v>
       </c>
       <c r="J427" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="L427" s="1">
         <v>46286</v>
@@ -31689,34 +31698,34 @@
         <v>204</v>
       </c>
       <c r="O427">
-        <v>17222579</v>
+        <v>18068500</v>
       </c>
       <c r="P427" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="Q427" t="s">
         <v>236</v>
       </c>
       <c r="R427" s="1">
-        <v>46283.68435655093</v>
+        <v>46283.5942487037</v>
       </c>
       <c r="S427">
         <v>2</v>
       </c>
       <c r="T427" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="V427" t="s">
         <v>255</v>
       </c>
       <c r="W427" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="AA427">
         <v>0</v>
       </c>
       <c r="AB427" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AG427" t="s">
         <v>457</v>
@@ -31727,16 +31736,16 @@
     </row>
     <row r="428" spans="1:34">
       <c r="A428">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B428" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C428" t="s">
         <v>58</v>
       </c>
       <c r="D428" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E428" t="s">
         <v>63</v>
@@ -31754,7 +31763,7 @@
         <v>69</v>
       </c>
       <c r="J428" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="L428" s="1">
         <v>46286</v>
@@ -31766,7 +31775,7 @@
         <v>204</v>
       </c>
       <c r="O428">
-        <v>18068500</v>
+        <v>18052419</v>
       </c>
       <c r="P428" t="s">
         <v>214</v>
@@ -31775,7 +31784,7 @@
         <v>236</v>
       </c>
       <c r="R428" s="1">
-        <v>46283.5942487037</v>
+        <v>46283.59424924768</v>
       </c>
       <c r="S428">
         <v>2</v>
@@ -31787,7 +31796,7 @@
         <v>255</v>
       </c>
       <c r="W428" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AA428">
         <v>0</v>
@@ -31804,19 +31813,19 @@
     </row>
     <row r="429" spans="1:34">
       <c r="A429">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B429" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C429" t="s">
         <v>58</v>
       </c>
       <c r="D429" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E429" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F429" t="s">
         <v>64</v>
@@ -31831,7 +31840,7 @@
         <v>69</v>
       </c>
       <c r="J429" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="L429" s="1">
         <v>46286</v>
@@ -31843,34 +31852,31 @@
         <v>204</v>
       </c>
       <c r="O429">
-        <v>18052419</v>
+        <v>18077082</v>
       </c>
       <c r="P429" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="Q429" t="s">
         <v>236</v>
       </c>
       <c r="R429" s="1">
-        <v>46283.59424924768</v>
+        <v>46283.68161918982</v>
       </c>
       <c r="S429">
         <v>2</v>
       </c>
       <c r="T429" t="s">
-        <v>240</v>
-      </c>
-      <c r="V429" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="W429" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AA429">
         <v>0</v>
       </c>
       <c r="AB429" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="AG429" t="s">
         <v>457</v>
@@ -31881,16 +31887,16 @@
     </row>
     <row r="430" spans="1:34">
       <c r="A430">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B430" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C430" t="s">
         <v>58</v>
       </c>
       <c r="D430" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E430" t="s">
         <v>62</v>
@@ -31908,34 +31914,37 @@
         <v>69</v>
       </c>
       <c r="J430" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="L430" s="1">
         <v>46286</v>
       </c>
       <c r="M430" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="N430" t="s">
         <v>204</v>
       </c>
       <c r="O430">
-        <v>18077082</v>
+        <v>18090149</v>
       </c>
       <c r="P430" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q430" t="s">
         <v>236</v>
       </c>
       <c r="R430" s="1">
-        <v>46283.68161918982</v>
+        <v>46286.6489187037</v>
       </c>
       <c r="S430">
         <v>2</v>
       </c>
       <c r="T430" t="s">
-        <v>247</v>
+        <v>245</v>
+      </c>
+      <c r="V430" t="s">
+        <v>255</v>
       </c>
       <c r="W430" t="s">
         <v>385</v>
@@ -31944,21 +31953,21 @@
         <v>0</v>
       </c>
       <c r="AB430" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AG430" t="s">
         <v>457</v>
       </c>
       <c r="AH430" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
     </row>
     <row r="431" spans="1:34">
       <c r="A431">
-        <v>6779</v>
+        <v>6945</v>
       </c>
       <c r="B431" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C431" t="s">
         <v>58</v>
@@ -31970,7 +31979,7 @@
         <v>62</v>
       </c>
       <c r="F431" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G431">
         <v>5836</v>
@@ -31982,37 +31991,34 @@
         <v>69</v>
       </c>
       <c r="J431" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="L431" s="1">
         <v>46286</v>
       </c>
       <c r="M431" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="N431" t="s">
         <v>204</v>
       </c>
       <c r="O431">
-        <v>18090149</v>
+        <v>18179083</v>
       </c>
       <c r="P431" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="Q431" t="s">
         <v>236</v>
       </c>
       <c r="R431" s="1">
-        <v>46286.6489187037</v>
+        <v>46288.38004474537</v>
       </c>
       <c r="S431">
         <v>2</v>
       </c>
       <c r="T431" t="s">
-        <v>245</v>
-      </c>
-      <c r="V431" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="W431" t="s">
         <v>386</v>
@@ -32021,13 +32027,13 @@
         <v>0</v>
       </c>
       <c r="AB431" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="AG431" t="s">
         <v>457</v>
       </c>
       <c r="AH431" t="s">
-        <v>449</v>
+        <v>464</v>
       </c>
     </row>
     <row r="432" spans="1:34">
@@ -33121,7 +33127,7 @@
         <v>255</v>
       </c>
       <c r="W447" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AA447">
         <v>0</v>
@@ -33689,7 +33695,7 @@
         <v>255</v>
       </c>
       <c r="W455" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AA455">
         <v>0</v>
@@ -33760,7 +33766,7 @@
         <v>242</v>
       </c>
       <c r="W456" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AA456">
         <v>0</v>
@@ -33804,7 +33810,7 @@
         <v>70</v>
       </c>
       <c r="J457" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L457" s="1">
         <v>46281</v>
@@ -33878,7 +33884,7 @@
         <v>70</v>
       </c>
       <c r="J458" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L458" s="1">
         <v>46281</v>
@@ -34168,7 +34174,7 @@
         <v>70</v>
       </c>
       <c r="J462" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L462" s="1">
         <v>46281</v>
@@ -34239,7 +34245,7 @@
         <v>70</v>
       </c>
       <c r="J463" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L463" s="1">
         <v>46281</v>
@@ -34446,7 +34452,7 @@
         <v>70</v>
       </c>
       <c r="J466" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L466" s="1">
         <v>46287</v>
@@ -34517,7 +34523,7 @@
         <v>70</v>
       </c>
       <c r="J467" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L467" s="1">
         <v>46287</v>
@@ -34588,7 +34594,7 @@
         <v>70</v>
       </c>
       <c r="J468" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L468" s="1">
         <v>46287</v>
@@ -34665,7 +34671,7 @@
         <v>70</v>
       </c>
       <c r="J469" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L469" s="1">
         <v>46287</v>
@@ -35059,7 +35065,7 @@
         <v>242</v>
       </c>
       <c r="W474" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AA474">
         <v>0</v>
@@ -35103,7 +35109,7 @@
         <v>71</v>
       </c>
       <c r="J475" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L475" s="1">
         <v>46289</v>
@@ -35133,7 +35139,7 @@
         <v>244</v>
       </c>
       <c r="W475" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AA475">
         <v>0</v>
@@ -35402,7 +35408,7 @@
         <v>71</v>
       </c>
       <c r="J479" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L479" s="1">
         <v>46281</v>
@@ -35479,7 +35485,7 @@
         <v>71</v>
       </c>
       <c r="J480" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L480" s="1">
         <v>46281</v>
@@ -36281,7 +36287,7 @@
         <v>71</v>
       </c>
       <c r="J491" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L491" s="1">
         <v>46287</v>
@@ -36355,7 +36361,7 @@
         <v>71</v>
       </c>
       <c r="J492" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L492" s="1">
         <v>46287</v>
@@ -37423,7 +37429,7 @@
         <v>72</v>
       </c>
       <c r="J507" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L507" s="1">
         <v>46290</v>
@@ -37488,7 +37494,7 @@
         <v>72</v>
       </c>
       <c r="J508" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L508" s="1">
         <v>46290</v>
@@ -37556,7 +37562,7 @@
         <v>72</v>
       </c>
       <c r="J509" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L509" s="1">
         <v>46290</v>
@@ -37624,7 +37630,7 @@
         <v>72</v>
       </c>
       <c r="J510" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L510" s="1">
         <v>46290</v>
@@ -41852,7 +41858,7 @@
         <v>73</v>
       </c>
       <c r="J569" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L569" s="1">
         <v>46290</v>
@@ -41920,7 +41926,7 @@
         <v>73</v>
       </c>
       <c r="J570" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L570" s="1">
         <v>46290</v>
@@ -42529,7 +42535,7 @@
         <v>69</v>
       </c>
       <c r="J579" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="L579" s="1">
         <v>46286</v>
@@ -42556,7 +42562,7 @@
         <v>253</v>
       </c>
       <c r="W579" t="s">
-        <v>341</v>
+        <v>386</v>
       </c>
       <c r="AG579" t="s">
         <v>457</v>
@@ -42724,7 +42730,7 @@
         <v>71</v>
       </c>
       <c r="J582" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L582" s="1">
         <v>46287</v>
@@ -42751,7 +42757,7 @@
         <v>254</v>
       </c>
       <c r="W582" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AG582" t="s">
         <v>458</v>

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8740" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8782" uniqueCount="466">
   <si>
     <t>CodCliente</t>
   </si>
@@ -1444,9 +1444,6 @@
     <t>Isabella Nascimento</t>
   </si>
   <si>
-    <t>Karina Santos</t>
-  </si>
-  <si>
     <t>Fernanda Araujo</t>
   </si>
   <si>
@@ -1456,7 +1453,7 @@
     <t>Leandro Matos</t>
   </si>
   <si>
-    <t>Ricardo Fischer</t>
+    <t>Larice Souza</t>
   </si>
 </sst>
 </file>
@@ -2449,7 +2446,7 @@
         <v>457</v>
       </c>
       <c r="AH9" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
     </row>
     <row r="10" spans="1:34">
@@ -2520,7 +2517,7 @@
         <v>457</v>
       </c>
       <c r="AH10" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="11" spans="1:34">
@@ -2588,7 +2585,7 @@
         <v>457</v>
       </c>
       <c r="AH11" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="12" spans="1:34">
@@ -2659,7 +2656,7 @@
         <v>457</v>
       </c>
       <c r="AH12" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="13" spans="1:34">
@@ -2736,7 +2733,7 @@
         <v>458</v>
       </c>
       <c r="AH13" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="14" spans="1:34">
@@ -2804,7 +2801,7 @@
         <v>458</v>
       </c>
       <c r="AH14" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="15" spans="1:34">
@@ -2878,7 +2875,7 @@
         <v>458</v>
       </c>
       <c r="AH15" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="16" spans="1:34">
@@ -2951,6 +2948,9 @@
       <c r="AG16" t="s">
         <v>459</v>
       </c>
+      <c r="AH16" t="s">
+        <v>449</v>
+      </c>
     </row>
     <row r="17" spans="1:34">
       <c r="A17">
@@ -3020,7 +3020,7 @@
         <v>459</v>
       </c>
       <c r="AH17" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="18" spans="1:34">
@@ -3097,7 +3097,7 @@
         <v>459</v>
       </c>
       <c r="AH18" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="19" spans="1:34">
@@ -3171,7 +3171,7 @@
         <v>459</v>
       </c>
       <c r="AH19" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="20" spans="1:34">
@@ -3239,7 +3239,7 @@
         <v>459</v>
       </c>
       <c r="AH20" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="21" spans="1:34">
@@ -3312,6 +3312,9 @@
       <c r="AG21" t="s">
         <v>457</v>
       </c>
+      <c r="AH21" t="s">
+        <v>449</v>
+      </c>
     </row>
     <row r="22" spans="1:34">
       <c r="A22">
@@ -3461,7 +3464,7 @@
         <v>457</v>
       </c>
       <c r="AH23" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="24" spans="1:34">
@@ -3538,7 +3541,7 @@
         <v>457</v>
       </c>
       <c r="AH24" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="25" spans="1:34">
@@ -3615,7 +3618,7 @@
         <v>457</v>
       </c>
       <c r="AH25" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="26" spans="1:34">
@@ -3692,7 +3695,7 @@
         <v>457</v>
       </c>
       <c r="AH26" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="27" spans="1:34">
@@ -3766,7 +3769,7 @@
         <v>457</v>
       </c>
       <c r="AH27" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="28" spans="1:34">
@@ -3917,7 +3920,7 @@
         <v>457</v>
       </c>
       <c r="AH29" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="30" spans="1:34">
@@ -3985,7 +3988,7 @@
         <v>457</v>
       </c>
       <c r="AH30" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="31" spans="1:34">
@@ -4058,6 +4061,9 @@
       <c r="AG31" t="s">
         <v>459</v>
       </c>
+      <c r="AH31" t="s">
+        <v>449</v>
+      </c>
     </row>
     <row r="32" spans="1:34">
       <c r="A32">
@@ -4133,7 +4139,7 @@
         <v>459</v>
       </c>
       <c r="AH32" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="33" spans="1:34">
@@ -4210,7 +4216,7 @@
         <v>459</v>
       </c>
       <c r="AH33" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="34" spans="1:34">
@@ -4287,7 +4293,7 @@
         <v>459</v>
       </c>
       <c r="AH34" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="35" spans="1:34">
@@ -4361,7 +4367,7 @@
         <v>459</v>
       </c>
       <c r="AH35" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="36" spans="1:34">
@@ -4512,7 +4518,7 @@
         <v>459</v>
       </c>
       <c r="AH37" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="38" spans="1:34">
@@ -4586,7 +4592,7 @@
         <v>459</v>
       </c>
       <c r="AH38" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="39" spans="1:34">
@@ -4653,6 +4659,9 @@
       <c r="AG39" t="s">
         <v>457</v>
       </c>
+      <c r="AH39" t="s">
+        <v>449</v>
+      </c>
     </row>
     <row r="40" spans="1:34">
       <c r="A40">
@@ -4722,7 +4731,7 @@
         <v>457</v>
       </c>
       <c r="AH40" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="41" spans="1:34">
@@ -4793,7 +4802,7 @@
         <v>457</v>
       </c>
       <c r="AH41" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="42" spans="1:34">
@@ -4864,7 +4873,7 @@
         <v>457</v>
       </c>
       <c r="AH42" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="43" spans="1:34">
@@ -4932,7 +4941,7 @@
         <v>457</v>
       </c>
       <c r="AH43" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="44" spans="1:34">
@@ -5077,7 +5086,7 @@
         <v>457</v>
       </c>
       <c r="AH45" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="46" spans="1:34">
@@ -5145,7 +5154,7 @@
         <v>457</v>
       </c>
       <c r="AH46" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="47" spans="1:34">
@@ -5215,6 +5224,9 @@
       <c r="AG47" t="s">
         <v>458</v>
       </c>
+      <c r="AH47" t="s">
+        <v>449</v>
+      </c>
     </row>
     <row r="48" spans="1:34">
       <c r="A48">
@@ -5290,7 +5302,7 @@
         <v>458</v>
       </c>
       <c r="AH48" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="49" spans="1:34">
@@ -5364,7 +5376,7 @@
         <v>458</v>
       </c>
       <c r="AH49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="50" spans="1:34">
@@ -5441,7 +5453,7 @@
         <v>458</v>
       </c>
       <c r="AH50" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="51" spans="1:34">
@@ -5518,7 +5530,7 @@
         <v>458</v>
       </c>
       <c r="AH51" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="52" spans="1:34">
@@ -5589,7 +5601,7 @@
         <v>458</v>
       </c>
       <c r="AH52" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="53" spans="1:34">
@@ -5734,7 +5746,7 @@
         <v>458</v>
       </c>
       <c r="AH54" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="55" spans="1:34">
@@ -5805,7 +5817,7 @@
         <v>458</v>
       </c>
       <c r="AH55" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="56" spans="1:34">
@@ -5872,6 +5884,9 @@
       <c r="AG56" t="s">
         <v>459</v>
       </c>
+      <c r="AH56" t="s">
+        <v>449</v>
+      </c>
     </row>
     <row r="57" spans="1:34">
       <c r="A57">
@@ -5941,7 +5956,7 @@
         <v>459</v>
       </c>
       <c r="AH57" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="58" spans="1:34">
@@ -6018,7 +6033,7 @@
         <v>459</v>
       </c>
       <c r="AH58" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="59" spans="1:34">
@@ -6092,7 +6107,7 @@
         <v>459</v>
       </c>
       <c r="AH59" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="60" spans="1:34">
@@ -6160,7 +6175,7 @@
         <v>459</v>
       </c>
       <c r="AH60" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="61" spans="1:34">
@@ -6227,6 +6242,9 @@
       <c r="AG61" t="s">
         <v>457</v>
       </c>
+      <c r="AH61" t="s">
+        <v>449</v>
+      </c>
     </row>
     <row r="62" spans="1:34">
       <c r="A62">
@@ -6296,7 +6314,7 @@
         <v>457</v>
       </c>
       <c r="AH62" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="63" spans="1:34">
@@ -6367,7 +6385,7 @@
         <v>457</v>
       </c>
       <c r="AH63" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="64" spans="1:34">
@@ -6438,7 +6456,7 @@
         <v>457</v>
       </c>
       <c r="AH64" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="65" spans="1:34">
@@ -6509,7 +6527,7 @@
         <v>457</v>
       </c>
       <c r="AH65" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="66" spans="1:34">
@@ -6648,7 +6666,7 @@
         <v>457</v>
       </c>
       <c r="AH67" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="68" spans="1:34">
@@ -6716,7 +6734,7 @@
         <v>457</v>
       </c>
       <c r="AH68" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="69" spans="1:34">
@@ -6793,7 +6811,7 @@
         <v>457</v>
       </c>
       <c r="AH69" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="70" spans="1:34">
@@ -6870,7 +6888,7 @@
         <v>457</v>
       </c>
       <c r="AH70" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="71" spans="1:34">
@@ -6947,7 +6965,7 @@
         <v>457</v>
       </c>
       <c r="AH71" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="72" spans="1:34">
@@ -7021,7 +7039,7 @@
         <v>457</v>
       </c>
       <c r="AH72" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="73" spans="1:34">
@@ -7092,7 +7110,7 @@
         <v>457</v>
       </c>
       <c r="AH73" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="74" spans="1:34">
@@ -7165,6 +7183,9 @@
       <c r="AG74" t="s">
         <v>459</v>
       </c>
+      <c r="AH74" t="s">
+        <v>449</v>
+      </c>
     </row>
     <row r="75" spans="1:34">
       <c r="A75">
@@ -7314,7 +7335,7 @@
         <v>459</v>
       </c>
       <c r="AH76" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="77" spans="1:34">
@@ -7391,7 +7412,7 @@
         <v>459</v>
       </c>
       <c r="AH77" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="78" spans="1:34">
@@ -7468,7 +7489,7 @@
         <v>459</v>
       </c>
       <c r="AH78" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="79" spans="1:34">
@@ -7542,7 +7563,7 @@
         <v>459</v>
       </c>
       <c r="AH79" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="80" spans="1:34">
@@ -7693,7 +7714,7 @@
         <v>459</v>
       </c>
       <c r="AH81" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="82" spans="1:34">
@@ -7767,7 +7788,7 @@
         <v>459</v>
       </c>
       <c r="AH82" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="83" spans="1:34">
@@ -7844,7 +7865,7 @@
         <v>457</v>
       </c>
       <c r="AH83" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="84" spans="1:34">
@@ -7911,6 +7932,9 @@
       <c r="AG84" t="s">
         <v>457</v>
       </c>
+      <c r="AH84" t="s">
+        <v>449</v>
+      </c>
     </row>
     <row r="85" spans="1:34">
       <c r="A85">
@@ -8048,7 +8072,7 @@
         <v>457</v>
       </c>
       <c r="AH86" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="87" spans="1:34">
@@ -8119,7 +8143,7 @@
         <v>457</v>
       </c>
       <c r="AH87" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="88" spans="1:34">
@@ -8190,7 +8214,7 @@
         <v>457</v>
       </c>
       <c r="AH88" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="89" spans="1:34">
@@ -8258,7 +8282,7 @@
         <v>457</v>
       </c>
       <c r="AH89" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="90" spans="1:34">
@@ -8397,7 +8421,7 @@
         <v>457</v>
       </c>
       <c r="AH91" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="92" spans="1:34">
@@ -8465,7 +8489,7 @@
         <v>457</v>
       </c>
       <c r="AH92" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="93" spans="1:34">
@@ -8952,6 +8976,9 @@
       <c r="AG99" t="s">
         <v>457</v>
       </c>
+      <c r="AH99" t="s">
+        <v>450</v>
+      </c>
     </row>
     <row r="100" spans="1:34">
       <c r="A100">
@@ -9221,6 +9248,9 @@
       <c r="AG103" t="s">
         <v>457</v>
       </c>
+      <c r="AH103" t="s">
+        <v>450</v>
+      </c>
     </row>
     <row r="104" spans="1:34">
       <c r="A104">
@@ -9555,6 +9585,9 @@
       <c r="AG108" t="s">
         <v>457</v>
       </c>
+      <c r="AH108" t="s">
+        <v>450</v>
+      </c>
     </row>
     <row r="109" spans="1:34">
       <c r="A109">
@@ -9889,6 +9922,9 @@
       <c r="AG113" t="s">
         <v>457</v>
       </c>
+      <c r="AH113" t="s">
+        <v>450</v>
+      </c>
     </row>
     <row r="114" spans="1:34">
       <c r="A114">
@@ -10096,6 +10132,9 @@
       <c r="AG116" t="s">
         <v>457</v>
       </c>
+      <c r="AH116" t="s">
+        <v>450</v>
+      </c>
     </row>
     <row r="117" spans="1:34">
       <c r="A117">
@@ -10235,6 +10274,9 @@
       <c r="AG118" t="s">
         <v>457</v>
       </c>
+      <c r="AH118" t="s">
+        <v>450</v>
+      </c>
     </row>
     <row r="119" spans="1:34">
       <c r="A119">
@@ -10634,6 +10676,9 @@
       <c r="AG124" t="s">
         <v>457</v>
       </c>
+      <c r="AH124" t="s">
+        <v>450</v>
+      </c>
     </row>
     <row r="125" spans="1:34">
       <c r="A125">
@@ -10767,6 +10812,9 @@
       <c r="AG126" t="s">
         <v>457</v>
       </c>
+      <c r="AH126" t="s">
+        <v>450</v>
+      </c>
     </row>
     <row r="127" spans="1:34">
       <c r="A127">
@@ -10971,6 +11019,9 @@
       <c r="AG129" t="s">
         <v>457</v>
       </c>
+      <c r="AH129" t="s">
+        <v>450</v>
+      </c>
     </row>
     <row r="130" spans="1:34">
       <c r="A130">
@@ -11178,6 +11229,9 @@
       <c r="AG132" t="s">
         <v>457</v>
       </c>
+      <c r="AH132" t="s">
+        <v>450</v>
+      </c>
     </row>
     <row r="133" spans="1:34">
       <c r="A133">
@@ -11512,6 +11566,9 @@
       <c r="AG137" t="s">
         <v>457</v>
       </c>
+      <c r="AH137" t="s">
+        <v>450</v>
+      </c>
     </row>
     <row r="138" spans="1:34">
       <c r="A138">
@@ -11929,6 +11986,9 @@
       <c r="AG143" t="s">
         <v>459</v>
       </c>
+      <c r="AH143" t="s">
+        <v>450</v>
+      </c>
     </row>
     <row r="144" spans="1:34">
       <c r="A144">
@@ -12077,6 +12137,9 @@
       <c r="AG145" t="s">
         <v>459</v>
       </c>
+      <c r="AH145" t="s">
+        <v>450</v>
+      </c>
     </row>
     <row r="146" spans="1:34">
       <c r="A146">
@@ -12367,6 +12430,9 @@
       <c r="AG149" t="s">
         <v>458</v>
       </c>
+      <c r="AH149" t="s">
+        <v>450</v>
+      </c>
     </row>
     <row r="150" spans="1:34">
       <c r="A150">
@@ -12728,6 +12794,9 @@
       <c r="AG154" t="s">
         <v>458</v>
       </c>
+      <c r="AH154" t="s">
+        <v>450</v>
+      </c>
     </row>
     <row r="155" spans="1:34">
       <c r="A155">
@@ -12799,6 +12868,9 @@
       <c r="AG155" t="s">
         <v>458</v>
       </c>
+      <c r="AH155" t="s">
+        <v>450</v>
+      </c>
     </row>
     <row r="156" spans="1:34">
       <c r="A156">
@@ -13151,6 +13223,9 @@
       <c r="AG160" t="s">
         <v>457</v>
       </c>
+      <c r="AH160" t="s">
+        <v>450</v>
+      </c>
     </row>
     <row r="161" spans="1:34">
       <c r="A161">
@@ -13222,6 +13297,9 @@
       <c r="AG161" t="s">
         <v>457</v>
       </c>
+      <c r="AH161" t="s">
+        <v>450</v>
+      </c>
     </row>
     <row r="162" spans="1:34">
       <c r="A162">
@@ -13362,7 +13440,7 @@
         <v>457</v>
       </c>
       <c r="AH163" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="164" spans="1:34">
@@ -13430,7 +13508,7 @@
         <v>457</v>
       </c>
       <c r="AH164" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="165" spans="1:34">
@@ -13507,7 +13585,7 @@
         <v>457</v>
       </c>
       <c r="AH165" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="166" spans="1:34">
@@ -13578,7 +13656,7 @@
         <v>457</v>
       </c>
       <c r="AH166" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="167" spans="1:34">
@@ -13646,7 +13724,7 @@
         <v>457</v>
       </c>
       <c r="AH167" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="168" spans="1:34">
@@ -13714,7 +13792,7 @@
         <v>457</v>
       </c>
       <c r="AH168" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="169" spans="1:34">
@@ -13782,7 +13860,7 @@
         <v>457</v>
       </c>
       <c r="AH169" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="170" spans="1:34">
@@ -13859,7 +13937,7 @@
         <v>457</v>
       </c>
       <c r="AH170" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="171" spans="1:34">
@@ -13930,7 +14008,7 @@
         <v>457</v>
       </c>
       <c r="AH171" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="172" spans="1:34">
@@ -13998,7 +14076,7 @@
         <v>457</v>
       </c>
       <c r="AH172" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="173" spans="1:34">
@@ -14066,7 +14144,7 @@
         <v>457</v>
       </c>
       <c r="AH173" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="174" spans="1:34">
@@ -14143,7 +14221,7 @@
         <v>457</v>
       </c>
       <c r="AH174" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="175" spans="1:34">
@@ -14211,7 +14289,7 @@
         <v>457</v>
       </c>
       <c r="AH175" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="176" spans="1:34">
@@ -14282,7 +14360,7 @@
         <v>457</v>
       </c>
       <c r="AH176" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="177" spans="1:34">
@@ -14350,7 +14428,7 @@
         <v>457</v>
       </c>
       <c r="AH177" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="178" spans="1:34">
@@ -14427,7 +14505,7 @@
         <v>457</v>
       </c>
       <c r="AH178" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="179" spans="1:34">
@@ -14498,7 +14576,7 @@
         <v>457</v>
       </c>
       <c r="AH179" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="180" spans="1:34">
@@ -14566,7 +14644,7 @@
         <v>457</v>
       </c>
       <c r="AH180" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="181" spans="1:34">
@@ -14634,7 +14712,7 @@
         <v>457</v>
       </c>
       <c r="AH181" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="182" spans="1:34">
@@ -14705,7 +14783,7 @@
         <v>457</v>
       </c>
       <c r="AH182" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="183" spans="1:34">
@@ -14773,7 +14851,7 @@
         <v>457</v>
       </c>
       <c r="AH183" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="184" spans="1:34">
@@ -14844,7 +14922,7 @@
         <v>457</v>
       </c>
       <c r="AH184" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="185" spans="1:34">
@@ -14912,7 +14990,7 @@
         <v>457</v>
       </c>
       <c r="AH185" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="186" spans="1:34">
@@ -14986,7 +15064,7 @@
         <v>459</v>
       </c>
       <c r="AH186" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="187" spans="1:34">
@@ -15054,7 +15132,7 @@
         <v>459</v>
       </c>
       <c r="AH187" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="188" spans="1:34">
@@ -15122,7 +15200,7 @@
         <v>459</v>
       </c>
       <c r="AH188" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="189" spans="1:34">
@@ -15193,7 +15271,7 @@
         <v>459</v>
       </c>
       <c r="AH189" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="190" spans="1:34">
@@ -15261,7 +15339,7 @@
         <v>459</v>
       </c>
       <c r="AH190" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="191" spans="1:34">
@@ -15332,7 +15410,7 @@
         <v>459</v>
       </c>
       <c r="AH191" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="192" spans="1:34">
@@ -15406,7 +15484,7 @@
         <v>459</v>
       </c>
       <c r="AH192" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="193" spans="1:34">
@@ -15477,7 +15555,7 @@
         <v>459</v>
       </c>
       <c r="AH193" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="194" spans="1:34">
@@ -15551,7 +15629,7 @@
         <v>457</v>
       </c>
       <c r="AH194" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="195" spans="1:34">
@@ -15619,7 +15697,7 @@
         <v>458</v>
       </c>
       <c r="AH195" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="196" spans="1:34">
@@ -15687,7 +15765,7 @@
         <v>458</v>
       </c>
       <c r="AH196" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="197" spans="1:34">
@@ -15758,7 +15836,7 @@
         <v>458</v>
       </c>
       <c r="AH197" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="198" spans="1:34">
@@ -15826,7 +15904,7 @@
         <v>458</v>
       </c>
       <c r="AH198" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="199" spans="1:34">
@@ -15897,7 +15975,7 @@
         <v>458</v>
       </c>
       <c r="AH199" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:34">
@@ -15965,7 +16043,7 @@
         <v>458</v>
       </c>
       <c r="AH200" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:34">
@@ -16036,7 +16114,7 @@
         <v>458</v>
       </c>
       <c r="AH201" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="202" spans="1:34">
@@ -16104,7 +16182,7 @@
         <v>458</v>
       </c>
       <c r="AH202" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="203" spans="1:34">
@@ -16175,7 +16253,7 @@
         <v>458</v>
       </c>
       <c r="AH203" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="204" spans="1:34">
@@ -16249,7 +16327,7 @@
         <v>457</v>
       </c>
       <c r="AH204" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="205" spans="1:34">
@@ -16326,7 +16404,7 @@
         <v>457</v>
       </c>
       <c r="AH205" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="206" spans="1:34">
@@ -16397,7 +16475,7 @@
         <v>457</v>
       </c>
       <c r="AH206" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="207" spans="1:34">
@@ -16465,7 +16543,7 @@
         <v>457</v>
       </c>
       <c r="AH207" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="208" spans="1:34">
@@ -16539,7 +16617,7 @@
         <v>457</v>
       </c>
       <c r="AH208" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="209" spans="1:34">
@@ -16610,7 +16688,7 @@
         <v>457</v>
       </c>
       <c r="AH209" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="210" spans="1:34">
@@ -16684,7 +16762,7 @@
         <v>457</v>
       </c>
       <c r="AH210" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="211" spans="1:34">
@@ -16752,7 +16830,7 @@
         <v>457</v>
       </c>
       <c r="AH211" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="212" spans="1:34">
@@ -22408,7 +22486,7 @@
         <v>457</v>
       </c>
       <c r="AH294" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="295" spans="1:34">
@@ -22476,7 +22554,7 @@
         <v>457</v>
       </c>
       <c r="AH295" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="296" spans="1:34">
@@ -22612,7 +22690,7 @@
         <v>458</v>
       </c>
       <c r="AH297" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="298" spans="1:34">
@@ -22683,7 +22761,7 @@
         <v>458</v>
       </c>
       <c r="AH298" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="299" spans="1:34">
@@ -24413,7 +24491,7 @@
         <v>457</v>
       </c>
       <c r="AH323" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
     </row>
     <row r="324" spans="1:34">
@@ -24484,7 +24562,7 @@
         <v>457</v>
       </c>
       <c r="AH324" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
     </row>
     <row r="325" spans="1:34">
@@ -24552,7 +24630,7 @@
         <v>459</v>
       </c>
       <c r="AH325" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="326" spans="1:34">
@@ -24623,7 +24701,7 @@
         <v>459</v>
       </c>
       <c r="AH326" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
     </row>
     <row r="327" spans="1:34">
@@ -24691,7 +24769,7 @@
         <v>459</v>
       </c>
       <c r="AH327" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
     </row>
     <row r="328" spans="1:34">
@@ -24762,7 +24840,7 @@
         <v>459</v>
       </c>
       <c r="AH328" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="329" spans="1:34">
@@ -24830,7 +24908,7 @@
         <v>459</v>
       </c>
       <c r="AH329" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="330" spans="1:34">
@@ -24901,7 +24979,7 @@
         <v>459</v>
       </c>
       <c r="AH330" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="331" spans="1:34">
@@ -24969,7 +25047,7 @@
         <v>459</v>
       </c>
       <c r="AH331" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="332" spans="1:34">
@@ -25040,7 +25118,7 @@
         <v>459</v>
       </c>
       <c r="AH332" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
     </row>
     <row r="333" spans="1:34">
@@ -25108,7 +25186,7 @@
         <v>459</v>
       </c>
       <c r="AH333" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
     </row>
     <row r="334" spans="1:34">
@@ -25179,7 +25257,7 @@
         <v>459</v>
       </c>
       <c r="AH334" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="335" spans="1:34">
@@ -25247,7 +25325,7 @@
         <v>457</v>
       </c>
       <c r="AH335" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="336" spans="1:34">
@@ -25315,7 +25393,7 @@
         <v>457</v>
       </c>
       <c r="AH336" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
     </row>
     <row r="337" spans="1:34">
@@ -25386,7 +25464,7 @@
         <v>457</v>
       </c>
       <c r="AH337" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
     </row>
     <row r="338" spans="1:34">
@@ -25457,7 +25535,7 @@
         <v>457</v>
       </c>
       <c r="AH338" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="339" spans="1:34">
@@ -25525,7 +25603,7 @@
         <v>457</v>
       </c>
       <c r="AH339" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="340" spans="1:34">
@@ -25596,7 +25674,7 @@
         <v>457</v>
       </c>
       <c r="AH340" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="341" spans="1:34">
@@ -25667,7 +25745,7 @@
         <v>458</v>
       </c>
       <c r="AH341" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="342" spans="1:34">
@@ -25738,7 +25816,7 @@
         <v>459</v>
       </c>
       <c r="AH342" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="343" spans="1:34">
@@ -25809,7 +25887,7 @@
         <v>457</v>
       </c>
       <c r="AH343" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="344" spans="1:34">
@@ -25876,6 +25954,9 @@
       <c r="AG344" t="s">
         <v>457</v>
       </c>
+      <c r="AH344" t="s">
+        <v>449</v>
+      </c>
     </row>
     <row r="345" spans="1:34">
       <c r="A345">
@@ -26016,7 +26097,7 @@
         <v>459</v>
       </c>
       <c r="AH346" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="347" spans="1:34">
@@ -26087,7 +26168,7 @@
         <v>457</v>
       </c>
       <c r="AH347" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="348" spans="1:34">
@@ -26154,6 +26235,9 @@
       <c r="AG348" t="s">
         <v>459</v>
       </c>
+      <c r="AH348" t="s">
+        <v>450</v>
+      </c>
     </row>
     <row r="349" spans="1:34">
       <c r="A349">
@@ -26219,6 +26303,9 @@
       <c r="AG349" t="s">
         <v>458</v>
       </c>
+      <c r="AH349" t="s">
+        <v>450</v>
+      </c>
     </row>
     <row r="350" spans="1:34">
       <c r="A350">
@@ -26288,7 +26375,7 @@
         <v>457</v>
       </c>
       <c r="AH350" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="351" spans="1:34">
@@ -26356,7 +26443,7 @@
         <v>457</v>
       </c>
       <c r="AH351" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="352" spans="1:34">
@@ -26424,7 +26511,7 @@
         <v>458</v>
       </c>
       <c r="AH352" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="353" spans="1:34">
@@ -27982,7 +28069,7 @@
         <v>457</v>
       </c>
       <c r="AH375" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="376" spans="1:34">
@@ -28056,7 +28143,7 @@
         <v>459</v>
       </c>
       <c r="AH376" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
     </row>
     <row r="377" spans="1:34">
@@ -28124,7 +28211,7 @@
         <v>457</v>
       </c>
       <c r="AH377" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
     </row>
     <row r="378" spans="1:34">
@@ -28195,7 +28282,7 @@
         <v>457</v>
       </c>
       <c r="AH378" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
     </row>
     <row r="379" spans="1:34">
@@ -28263,7 +28350,7 @@
         <v>458</v>
       </c>
       <c r="AH379" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
     </row>
     <row r="380" spans="1:34">
@@ -28529,7 +28616,7 @@
         <v>458</v>
       </c>
       <c r="AH383" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
     </row>
     <row r="384" spans="1:34">
@@ -28600,7 +28687,7 @@
         <v>458</v>
       </c>
       <c r="AH384" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="385" spans="1:34">
@@ -28674,7 +28761,7 @@
         <v>459</v>
       </c>
       <c r="AH385" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
     </row>
     <row r="386" spans="1:34">
@@ -28745,7 +28832,7 @@
         <v>457</v>
       </c>
       <c r="AH386" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
     </row>
     <row r="387" spans="1:34">
@@ -28813,7 +28900,7 @@
         <v>457</v>
       </c>
       <c r="AH387" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
     </row>
     <row r="388" spans="1:34">
@@ -28881,7 +28968,7 @@
         <v>457</v>
       </c>
       <c r="AH388" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="389" spans="1:34">
@@ -28949,7 +29036,7 @@
         <v>457</v>
       </c>
       <c r="AH389" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
     </row>
     <row r="390" spans="1:34">
@@ -29020,7 +29107,7 @@
         <v>457</v>
       </c>
       <c r="AH390" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="391" spans="1:34">
@@ -29088,7 +29175,7 @@
         <v>457</v>
       </c>
       <c r="AH391" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="392" spans="1:34">
@@ -29159,7 +29246,7 @@
         <v>457</v>
       </c>
       <c r="AH392" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="393" spans="1:34">
@@ -29236,7 +29323,7 @@
         <v>458</v>
       </c>
       <c r="AH393" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="394" spans="1:34">
@@ -29313,7 +29400,7 @@
         <v>458</v>
       </c>
       <c r="AH394" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="395" spans="1:34">
@@ -29387,7 +29474,7 @@
         <v>458</v>
       </c>
       <c r="AH395" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="396" spans="1:34">
@@ -29455,7 +29542,7 @@
         <v>457</v>
       </c>
       <c r="AH396" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="397" spans="1:34">
@@ -29599,6 +29686,9 @@
       <c r="AG398" t="s">
         <v>457</v>
       </c>
+      <c r="AH398" t="s">
+        <v>449</v>
+      </c>
     </row>
     <row r="399" spans="1:34">
       <c r="A399">
@@ -29674,7 +29764,7 @@
         <v>457</v>
       </c>
       <c r="AH399" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="400" spans="1:34">
@@ -29751,7 +29841,7 @@
         <v>457</v>
       </c>
       <c r="AH400" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="401" spans="1:34">
@@ -29828,7 +29918,7 @@
         <v>457</v>
       </c>
       <c r="AH401" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="402" spans="1:34">
@@ -29905,7 +29995,7 @@
         <v>457</v>
       </c>
       <c r="AH402" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="403" spans="1:34">
@@ -29973,7 +30063,7 @@
         <v>457</v>
       </c>
       <c r="AH403" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="404" spans="1:34">
@@ -30118,7 +30208,7 @@
         <v>457</v>
       </c>
       <c r="AH405" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="406" spans="1:34">
@@ -30185,6 +30275,9 @@
       <c r="AG406" t="s">
         <v>457</v>
       </c>
+      <c r="AH406" t="s">
+        <v>449</v>
+      </c>
     </row>
     <row r="407" spans="1:34">
       <c r="A407">
@@ -30260,7 +30353,7 @@
         <v>457</v>
       </c>
       <c r="AH407" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="408" spans="1:34">
@@ -30337,7 +30430,7 @@
         <v>457</v>
       </c>
       <c r="AH408" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="409" spans="1:34">
@@ -30414,7 +30507,7 @@
         <v>457</v>
       </c>
       <c r="AH409" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="410" spans="1:34">
@@ -30491,7 +30584,7 @@
         <v>457</v>
       </c>
       <c r="AH410" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="411" spans="1:34">
@@ -30559,7 +30652,7 @@
         <v>457</v>
       </c>
       <c r="AH411" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="412" spans="1:34">
@@ -30704,7 +30797,7 @@
         <v>457</v>
       </c>
       <c r="AH413" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="414" spans="1:34">
@@ -30774,6 +30867,9 @@
       <c r="AG414" t="s">
         <v>457</v>
       </c>
+      <c r="AH414" t="s">
+        <v>449</v>
+      </c>
     </row>
     <row r="415" spans="1:34">
       <c r="A415">
@@ -30917,7 +31013,7 @@
         <v>457</v>
       </c>
       <c r="AH416" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="417" spans="1:34">
@@ -30991,7 +31087,7 @@
         <v>457</v>
       </c>
       <c r="AH417" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="418" spans="1:34">
@@ -31065,7 +31161,7 @@
         <v>457</v>
       </c>
       <c r="AH418" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="419" spans="1:34">
@@ -31139,7 +31235,7 @@
         <v>457</v>
       </c>
       <c r="AH419" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="420" spans="1:34">
@@ -31213,7 +31309,7 @@
         <v>457</v>
       </c>
       <c r="AH420" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="421" spans="1:34">
@@ -31358,7 +31454,7 @@
         <v>457</v>
       </c>
       <c r="AH422" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="423" spans="1:34">
@@ -31429,7 +31525,7 @@
         <v>457</v>
       </c>
       <c r="AH423" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="424" spans="1:34">
@@ -31502,6 +31598,9 @@
       <c r="AG424" t="s">
         <v>457</v>
       </c>
+      <c r="AH424" t="s">
+        <v>449</v>
+      </c>
     </row>
     <row r="425" spans="1:34">
       <c r="A425">
@@ -31577,7 +31676,7 @@
         <v>457</v>
       </c>
       <c r="AH425" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="426" spans="1:34">
@@ -31654,7 +31753,7 @@
         <v>457</v>
       </c>
       <c r="AH426" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="427" spans="1:34">
@@ -31731,7 +31830,7 @@
         <v>457</v>
       </c>
       <c r="AH427" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="428" spans="1:34">
@@ -31808,7 +31907,7 @@
         <v>457</v>
       </c>
       <c r="AH428" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="429" spans="1:34">
@@ -31882,7 +31981,7 @@
         <v>457</v>
       </c>
       <c r="AH429" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="430" spans="1:34">
@@ -32033,7 +32132,7 @@
         <v>457</v>
       </c>
       <c r="AH431" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="432" spans="1:34">
@@ -32242,6 +32341,9 @@
       <c r="AG434" t="s">
         <v>458</v>
       </c>
+      <c r="AH434" t="s">
+        <v>449</v>
+      </c>
     </row>
     <row r="435" spans="1:34">
       <c r="A435">
@@ -32379,7 +32481,7 @@
         <v>458</v>
       </c>
       <c r="AH436" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="437" spans="1:34">
@@ -32450,7 +32552,7 @@
         <v>458</v>
       </c>
       <c r="AH437" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="438" spans="1:34">
@@ -32521,7 +32623,7 @@
         <v>458</v>
       </c>
       <c r="AH438" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="439" spans="1:34">
@@ -32592,7 +32694,7 @@
         <v>458</v>
       </c>
       <c r="AH439" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="440" spans="1:34">
@@ -32731,7 +32833,7 @@
         <v>458</v>
       </c>
       <c r="AH441" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="442" spans="1:34">
@@ -32799,7 +32901,7 @@
         <v>458</v>
       </c>
       <c r="AH442" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="443" spans="1:34">
@@ -33352,7 +33454,7 @@
         <v>458</v>
       </c>
       <c r="AH450" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="451" spans="1:34">
@@ -33493,6 +33595,9 @@
       <c r="AG452" t="s">
         <v>457</v>
       </c>
+      <c r="AH452" t="s">
+        <v>450</v>
+      </c>
     </row>
     <row r="453" spans="1:34">
       <c r="A453">
@@ -33706,6 +33811,9 @@
       <c r="AG455" t="s">
         <v>457</v>
       </c>
+      <c r="AH455" t="s">
+        <v>450</v>
+      </c>
     </row>
     <row r="456" spans="1:34">
       <c r="A456">
@@ -34073,6 +34181,9 @@
       <c r="AG460" t="s">
         <v>458</v>
       </c>
+      <c r="AH460" t="s">
+        <v>450</v>
+      </c>
     </row>
     <row r="461" spans="1:34">
       <c r="A461">
@@ -34280,6 +34391,9 @@
       <c r="AG463" t="s">
         <v>457</v>
       </c>
+      <c r="AH463" t="s">
+        <v>450</v>
+      </c>
     </row>
     <row r="464" spans="1:34">
       <c r="A464">
@@ -34422,6 +34536,9 @@
       <c r="AG465" t="s">
         <v>458</v>
       </c>
+      <c r="AH465" t="s">
+        <v>450</v>
+      </c>
     </row>
     <row r="466" spans="1:34">
       <c r="A466">
@@ -34712,6 +34829,9 @@
       <c r="AG469" t="s">
         <v>458</v>
       </c>
+      <c r="AH469" t="s">
+        <v>450</v>
+      </c>
     </row>
     <row r="470" spans="1:34">
       <c r="A470">
@@ -34860,6 +34980,9 @@
       <c r="AG471" t="s">
         <v>457</v>
       </c>
+      <c r="AH471" t="s">
+        <v>450</v>
+      </c>
     </row>
     <row r="472" spans="1:34">
       <c r="A472">
@@ -35151,7 +35274,7 @@
         <v>457</v>
       </c>
       <c r="AH475" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="476" spans="1:34">
@@ -35225,7 +35348,7 @@
         <v>457</v>
       </c>
       <c r="AH476" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="477" spans="1:34">
@@ -35299,7 +35422,7 @@
         <v>457</v>
       </c>
       <c r="AH477" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="478" spans="1:34">
@@ -35376,7 +35499,7 @@
         <v>457</v>
       </c>
       <c r="AH478" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="479" spans="1:34">
@@ -35453,7 +35576,7 @@
         <v>458</v>
       </c>
       <c r="AH479" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="480" spans="1:34">
@@ -35527,7 +35650,7 @@
         <v>458</v>
       </c>
       <c r="AH480" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="481" spans="1:34">
@@ -35598,7 +35721,7 @@
         <v>458</v>
       </c>
       <c r="AH481" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="482" spans="1:34">
@@ -35675,7 +35798,7 @@
         <v>458</v>
       </c>
       <c r="AH482" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="483" spans="1:34">
@@ -35749,7 +35872,7 @@
         <v>458</v>
       </c>
       <c r="AH483" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="484" spans="1:34">
@@ -35823,7 +35946,7 @@
         <v>458</v>
       </c>
       <c r="AH484" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="485" spans="1:34">
@@ -35897,7 +36020,7 @@
         <v>458</v>
       </c>
       <c r="AH485" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="486" spans="1:34">
@@ -35968,7 +36091,7 @@
         <v>457</v>
       </c>
       <c r="AH486" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="487" spans="1:34">
@@ -36039,7 +36162,7 @@
         <v>458</v>
       </c>
       <c r="AH487" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="488" spans="1:34">
@@ -36113,7 +36236,7 @@
         <v>458</v>
       </c>
       <c r="AH488" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="489" spans="1:34">
@@ -36181,7 +36304,7 @@
         <v>458</v>
       </c>
       <c r="AH489" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="490" spans="1:34">
@@ -36255,7 +36378,7 @@
         <v>458</v>
       </c>
       <c r="AH490" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="491" spans="1:34">
@@ -36329,7 +36452,7 @@
         <v>458</v>
       </c>
       <c r="AH491" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="492" spans="1:34">
@@ -36403,7 +36526,7 @@
         <v>458</v>
       </c>
       <c r="AH492" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="493" spans="1:34">
@@ -36474,7 +36597,7 @@
         <v>457</v>
       </c>
       <c r="AH493" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="494" spans="1:34">
@@ -36545,7 +36668,7 @@
         <v>457</v>
       </c>
       <c r="AH494" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="495" spans="1:34">
@@ -36619,7 +36742,7 @@
         <v>458</v>
       </c>
       <c r="AH495" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="496" spans="1:34">
@@ -42568,7 +42691,7 @@
         <v>457</v>
       </c>
       <c r="AH579" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="580" spans="1:34">
@@ -42633,7 +42756,7 @@
         <v>457</v>
       </c>
       <c r="AH580" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="581" spans="1:34">
@@ -42698,7 +42821,7 @@
         <v>457</v>
       </c>
       <c r="AH581" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="582" spans="1:34">
@@ -42763,7 +42886,7 @@
         <v>458</v>
       </c>
       <c r="AH582" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="583" spans="1:34">
@@ -42828,7 +42951,7 @@
         <v>457</v>
       </c>
       <c r="AH583" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="584" spans="1:34">

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -1066,7 +1066,7 @@
 Em atendimento - Data Comentário: 22/09/2026 17:12</t>
   </si>
   <si>
-    <t>Atraso da Operação, processo em elaboração conforme data prevista   Previsão para conclusão dia 23/09/2026 - Data Comentário: 22/09/2026 17:40</t>
+    <t>Imposto enviado via SCI Report   Previsão para conclusão dia 23/09/2026 - Data Comentário: 23/09/2026 11:19</t>
   </si>
   <si>
     <t>Atraso da Operação, processo em elaboração conforme data prevista  Previsão para conclusão dia 23/09/2026 - Data Comentário: 22/09/2026 17:39</t>

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8742" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8743" uniqueCount="472">
   <si>
     <t>CodCliente</t>
   </si>
@@ -430,91 +430,91 @@
     <t>Est - ICMS SN - Diferencial Alíquota</t>
   </si>
   <si>
+    <t>Confirm Rec - PIS/COFINS</t>
+  </si>
+  <si>
+    <t>Inclusão de Ata de Reunião</t>
+  </si>
+  <si>
+    <t>Fechamento Mensal</t>
+  </si>
+  <si>
+    <t>Fed - IRPJ/CSLL - 3ª Quota corrigida</t>
+  </si>
+  <si>
+    <t>Outras Receitas</t>
+  </si>
+  <si>
+    <t>Fed - DIRBI</t>
+  </si>
+  <si>
+    <t>Adiantamento Salarial (20)</t>
+  </si>
+  <si>
+    <t>Cartão de Ponto</t>
+  </si>
+  <si>
+    <t>Controle Afastamento</t>
+  </si>
+  <si>
+    <t>Controle Contr. Experiência</t>
+  </si>
+  <si>
+    <t>Controle de Férias</t>
+  </si>
+  <si>
+    <t>Envio de Impostos - DCTF Web</t>
+  </si>
+  <si>
+    <t>Envio Planilha de Fechamento</t>
+  </si>
+  <si>
+    <t>Folha Pró-Lab/Autônomo</t>
+  </si>
+  <si>
+    <t>Folha Pró-Lab/Autônomo - Impressão PDF</t>
+  </si>
+  <si>
+    <t>Impostos Folha Mensal</t>
+  </si>
+  <si>
+    <t>Lançamentos de atestados</t>
+  </si>
+  <si>
+    <t>PAT</t>
+  </si>
+  <si>
+    <t>Prévias rescisões individuais</t>
+  </si>
+  <si>
+    <t>Relação de Aniversariantes</t>
+  </si>
+  <si>
+    <t>Bloco K</t>
+  </si>
+  <si>
+    <t>Depreciação</t>
+  </si>
+  <si>
+    <t>Est - ICMS RPA - CÓD. 046-2</t>
+  </si>
+  <si>
+    <t>Est - ICMS RPA - CÓD. 046-2 (GO)</t>
+  </si>
+  <si>
+    <t>Fed - DAS</t>
+  </si>
+  <si>
+    <t>Fed - PIS/COFINS Cumulativo - 2172</t>
+  </si>
+  <si>
+    <t>Movimento - Sistema de Análise</t>
+  </si>
+  <si>
+    <t>Receitas Financeiras ( Aplicação Financeira )</t>
+  </si>
+  <si>
     <t>Digitalização de NF Ativo</t>
-  </si>
-  <si>
-    <t>Confirm Rec - PIS/COFINS</t>
-  </si>
-  <si>
-    <t>Inclusão de Ata de Reunião</t>
-  </si>
-  <si>
-    <t>Fechamento Mensal</t>
-  </si>
-  <si>
-    <t>Fed - IRPJ/CSLL - 3ª Quota corrigida</t>
-  </si>
-  <si>
-    <t>Outras Receitas</t>
-  </si>
-  <si>
-    <t>Fed - DIRBI</t>
-  </si>
-  <si>
-    <t>Adiantamento Salarial (20)</t>
-  </si>
-  <si>
-    <t>Cartão de Ponto</t>
-  </si>
-  <si>
-    <t>Controle Afastamento</t>
-  </si>
-  <si>
-    <t>Controle Contr. Experiência</t>
-  </si>
-  <si>
-    <t>Controle de Férias</t>
-  </si>
-  <si>
-    <t>Envio de Impostos - DCTF Web</t>
-  </si>
-  <si>
-    <t>Envio Planilha de Fechamento</t>
-  </si>
-  <si>
-    <t>Folha Pró-Lab/Autônomo</t>
-  </si>
-  <si>
-    <t>Folha Pró-Lab/Autônomo - Impressão PDF</t>
-  </si>
-  <si>
-    <t>Impostos Folha Mensal</t>
-  </si>
-  <si>
-    <t>Lançamentos de atestados</t>
-  </si>
-  <si>
-    <t>PAT</t>
-  </si>
-  <si>
-    <t>Prévias rescisões individuais</t>
-  </si>
-  <si>
-    <t>Relação de Aniversariantes</t>
-  </si>
-  <si>
-    <t>Bloco K</t>
-  </si>
-  <si>
-    <t>Depreciação</t>
-  </si>
-  <si>
-    <t>Est - ICMS RPA - CÓD. 046-2</t>
-  </si>
-  <si>
-    <t>Est - ICMS RPA - CÓD. 046-2 (GO)</t>
-  </si>
-  <si>
-    <t>Fed - DAS</t>
-  </si>
-  <si>
-    <t>Fed - PIS/COFINS Cumulativo - 2172</t>
-  </si>
-  <si>
-    <t>Movimento - Sistema de Análise</t>
-  </si>
-  <si>
-    <t>Receitas Financeiras ( Aplicação Financeira )</t>
   </si>
   <si>
     <t>Encerramento de Competência – ISS Prefeitura</t>
@@ -1078,9 +1078,6 @@
   <si>
     <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 28/09/2026 
 aguardando cliente enviar - Data Comentário: 18/09/2026 15:32</t>
-  </si>
-  <si>
-    <t>Comentário Colaborador + Previsão de Conclusão. Previsto para: 24/09/2026 - Data Comentário: 18/09/2026 15:24</t>
   </si>
   <si>
     <t>Comentário Colaborador + Previsão de Conclusão. Previsto para: 28/09/2026 - Data Comentário: 18/09/2026 15:27</t>
@@ -1263,6 +1260,9 @@
   </si>
   <si>
     <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 15/09/2026 15:55:44. - Data Comentário: 15/09/2026 15:50</t>
+  </si>
+  <si>
+    <t>Comentário Colaborador + Previsão de Conclusão. Previsto para: 24/09/2026 - Data Comentário: 18/09/2026 15:24</t>
   </si>
   <si>
     <t>Tarefa baixada via Rotina SisAnalise x MGC - ExecutarNFsAtivos. - Data Comentário: 23/09/2026 14:01</t>
@@ -25860,28 +25860,28 @@
         <v>61</v>
       </c>
       <c r="G343">
-        <v>6759</v>
+        <v>1803</v>
       </c>
       <c r="H343">
-        <v>1788</v>
+        <v>0</v>
       </c>
       <c r="I343" t="s">
         <v>68</v>
       </c>
       <c r="J343" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L343" s="1">
-        <v>46289</v>
+        <v>46293</v>
       </c>
       <c r="M343" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="N343" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="O343">
-        <v>17949019</v>
+        <v>17948937</v>
       </c>
       <c r="P343" t="s">
         <v>226</v>
@@ -25890,7 +25890,7 @@
         <v>237</v>
       </c>
       <c r="S343">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="T343" t="s">
         <v>244</v>
@@ -25902,7 +25902,7 @@
         <v>0</v>
       </c>
       <c r="AG343" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AH343" t="s">
         <v>470</v>
@@ -25910,16 +25910,16 @@
     </row>
     <row r="344" spans="1:34">
       <c r="A344">
-        <v>6705</v>
+        <v>5417</v>
       </c>
       <c r="B344" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C344" t="s">
         <v>55</v>
       </c>
       <c r="D344" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E344" t="s">
         <v>59</v>
@@ -25928,40 +25928,40 @@
         <v>61</v>
       </c>
       <c r="G344">
-        <v>1803</v>
+        <v>953</v>
       </c>
       <c r="H344">
         <v>0</v>
       </c>
       <c r="I344" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J344" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L344" s="1">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="M344" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="N344" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="O344">
-        <v>17948937</v>
+        <v>17398883</v>
       </c>
       <c r="P344" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q344" t="s">
         <v>237</v>
       </c>
       <c r="S344">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="T344" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="W344" t="s">
         <v>347</v>
@@ -25972,22 +25972,19 @@
       <c r="AG344" t="s">
         <v>464</v>
       </c>
-      <c r="AH344" t="s">
-        <v>470</v>
-      </c>
     </row>
     <row r="345" spans="1:34">
       <c r="A345">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B345" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C345" t="s">
         <v>55</v>
       </c>
       <c r="D345" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E345" t="s">
         <v>59</v>
@@ -26005,7 +26002,7 @@
         <v>69</v>
       </c>
       <c r="J345" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L345" s="1">
         <v>46290</v>
@@ -26017,7 +26014,7 @@
         <v>202</v>
       </c>
       <c r="O345">
-        <v>17398883</v>
+        <v>16962107</v>
       </c>
       <c r="P345" t="s">
         <v>227</v>
@@ -26029,7 +26026,7 @@
         <v>-1</v>
       </c>
       <c r="T345" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="W345" t="s">
         <v>348</v>
@@ -26043,19 +26040,19 @@
     </row>
     <row r="346" spans="1:34">
       <c r="A346">
-        <v>6404</v>
+        <v>6627</v>
       </c>
       <c r="B346" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C346" t="s">
         <v>55</v>
       </c>
       <c r="D346" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E346" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F346" t="s">
         <v>61</v>
@@ -26070,7 +26067,7 @@
         <v>69</v>
       </c>
       <c r="J346" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L346" s="1">
         <v>46290</v>
@@ -26082,7 +26079,7 @@
         <v>202</v>
       </c>
       <c r="O346">
-        <v>16962107</v>
+        <v>17042317</v>
       </c>
       <c r="P346" t="s">
         <v>227</v>
@@ -26094,7 +26091,10 @@
         <v>-1</v>
       </c>
       <c r="T346" t="s">
-        <v>247</v>
+        <v>239</v>
+      </c>
+      <c r="V346" t="s">
+        <v>253</v>
       </c>
       <c r="W346" t="s">
         <v>349</v>
@@ -26108,19 +26108,19 @@
     </row>
     <row r="347" spans="1:34">
       <c r="A347">
-        <v>6627</v>
+        <v>6703</v>
       </c>
       <c r="B347" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C347" t="s">
         <v>55</v>
       </c>
       <c r="D347" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E347" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F347" t="s">
         <v>61</v>
@@ -26135,7 +26135,7 @@
         <v>69</v>
       </c>
       <c r="J347" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L347" s="1">
         <v>46290</v>
@@ -26147,7 +26147,7 @@
         <v>202</v>
       </c>
       <c r="O347">
-        <v>17042317</v>
+        <v>17941166</v>
       </c>
       <c r="P347" t="s">
         <v>227</v>
@@ -26159,10 +26159,7 @@
         <v>-1</v>
       </c>
       <c r="T347" t="s">
-        <v>239</v>
-      </c>
-      <c r="V347" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="W347" t="s">
         <v>350</v>
@@ -26176,16 +26173,16 @@
     </row>
     <row r="348" spans="1:34">
       <c r="A348">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B348" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C348" t="s">
         <v>55</v>
       </c>
       <c r="D348" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E348" t="s">
         <v>59</v>
@@ -26203,19 +26200,16 @@
         <v>69</v>
       </c>
       <c r="J348" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L348" s="1">
         <v>46290</v>
       </c>
-      <c r="M348" t="s">
-        <v>191</v>
-      </c>
       <c r="N348" t="s">
         <v>202</v>
       </c>
       <c r="O348">
-        <v>17941166</v>
+        <v>17952362</v>
       </c>
       <c r="P348" t="s">
         <v>227</v>
@@ -26227,7 +26221,10 @@
         <v>-1</v>
       </c>
       <c r="T348" t="s">
-        <v>246</v>
+        <v>244</v>
+      </c>
+      <c r="V348" t="s">
+        <v>253</v>
       </c>
       <c r="W348" t="s">
         <v>351</v>
@@ -26241,22 +26238,22 @@
     </row>
     <row r="349" spans="1:34">
       <c r="A349">
-        <v>6704</v>
+        <v>6962</v>
       </c>
       <c r="B349" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C349" t="s">
         <v>55</v>
       </c>
       <c r="D349" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E349" t="s">
         <v>59</v>
       </c>
       <c r="F349" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G349">
         <v>953</v>
@@ -26268,16 +26265,19 @@
         <v>69</v>
       </c>
       <c r="J349" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L349" s="1">
         <v>46290</v>
       </c>
+      <c r="M349" t="s">
+        <v>191</v>
+      </c>
       <c r="N349" t="s">
         <v>202</v>
       </c>
       <c r="O349">
-        <v>17952362</v>
+        <v>18188731</v>
       </c>
       <c r="P349" t="s">
         <v>227</v>
@@ -26289,10 +26289,7 @@
         <v>-1</v>
       </c>
       <c r="T349" t="s">
-        <v>244</v>
-      </c>
-      <c r="V349" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="W349" t="s">
         <v>352</v>
@@ -26306,10 +26303,10 @@
     </row>
     <row r="350" spans="1:34">
       <c r="A350">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B350" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C350" t="s">
         <v>55</v>
@@ -26333,7 +26330,7 @@
         <v>69</v>
       </c>
       <c r="J350" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L350" s="1">
         <v>46290</v>
@@ -26345,7 +26342,7 @@
         <v>202</v>
       </c>
       <c r="O350">
-        <v>18188731</v>
+        <v>18188637</v>
       </c>
       <c r="P350" t="s">
         <v>227</v>
@@ -26371,25 +26368,25 @@
     </row>
     <row r="351" spans="1:34">
       <c r="A351">
-        <v>6963</v>
+        <v>5417</v>
       </c>
       <c r="B351" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C351" t="s">
         <v>55</v>
       </c>
       <c r="D351" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E351" t="s">
         <v>59</v>
       </c>
       <c r="F351" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G351">
-        <v>953</v>
+        <v>943</v>
       </c>
       <c r="H351">
         <v>0</v>
@@ -26401,16 +26398,16 @@
         <v>139</v>
       </c>
       <c r="L351" s="1">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="M351" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N351" t="s">
         <v>202</v>
       </c>
       <c r="O351">
-        <v>18188637</v>
+        <v>17398859</v>
       </c>
       <c r="P351" t="s">
         <v>227</v>
@@ -26419,27 +26416,27 @@
         <v>237</v>
       </c>
       <c r="S351">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="T351" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="W351" t="s">
-        <v>354</v>
+        <v>340</v>
       </c>
       <c r="AA351">
         <v>0</v>
       </c>
       <c r="AG351" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="352" spans="1:34">
       <c r="A352">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B352" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C352" t="s">
         <v>55</v>
@@ -26463,7 +26460,7 @@
         <v>69</v>
       </c>
       <c r="J352" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L352" s="1">
         <v>46295</v>
@@ -26475,7 +26472,7 @@
         <v>202</v>
       </c>
       <c r="O352">
-        <v>17398859</v>
+        <v>16975890</v>
       </c>
       <c r="P352" t="s">
         <v>227</v>
@@ -26487,10 +26484,13 @@
         <v>-6</v>
       </c>
       <c r="T352" t="s">
-        <v>243</v>
+        <v>245</v>
+      </c>
+      <c r="V352" t="s">
+        <v>253</v>
       </c>
       <c r="W352" t="s">
-        <v>340</v>
+        <v>354</v>
       </c>
       <c r="AA352">
         <v>0</v>
@@ -26501,16 +26501,16 @@
     </row>
     <row r="353" spans="1:34">
       <c r="A353">
-        <v>6486</v>
+        <v>6703</v>
       </c>
       <c r="B353" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C353" t="s">
         <v>55</v>
       </c>
       <c r="D353" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E353" t="s">
         <v>59</v>
@@ -26528,7 +26528,7 @@
         <v>69</v>
       </c>
       <c r="J353" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L353" s="1">
         <v>46295</v>
@@ -26540,7 +26540,7 @@
         <v>202</v>
       </c>
       <c r="O353">
-        <v>16975890</v>
+        <v>17941122</v>
       </c>
       <c r="P353" t="s">
         <v>227</v>
@@ -26552,13 +26552,10 @@
         <v>-6</v>
       </c>
       <c r="T353" t="s">
-        <v>245</v>
-      </c>
-      <c r="V353" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="W353" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AA353">
         <v>0</v>
@@ -26569,16 +26566,16 @@
     </row>
     <row r="354" spans="1:34">
       <c r="A354">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B354" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C354" t="s">
         <v>55</v>
       </c>
       <c r="D354" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E354" t="s">
         <v>59</v>
@@ -26596,7 +26593,7 @@
         <v>69</v>
       </c>
       <c r="J354" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L354" s="1">
         <v>46295</v>
@@ -26608,7 +26605,7 @@
         <v>202</v>
       </c>
       <c r="O354">
-        <v>17941122</v>
+        <v>17952314</v>
       </c>
       <c r="P354" t="s">
         <v>227</v>
@@ -26620,10 +26617,13 @@
         <v>-6</v>
       </c>
       <c r="T354" t="s">
-        <v>246</v>
+        <v>244</v>
+      </c>
+      <c r="V354" t="s">
+        <v>253</v>
       </c>
       <c r="W354" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AA354">
         <v>0</v>
@@ -26634,16 +26634,16 @@
     </row>
     <row r="355" spans="1:34">
       <c r="A355">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B355" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C355" t="s">
         <v>55</v>
       </c>
       <c r="D355" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E355" t="s">
         <v>59</v>
@@ -26661,7 +26661,7 @@
         <v>69</v>
       </c>
       <c r="J355" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L355" s="1">
         <v>46295</v>
@@ -26673,7 +26673,7 @@
         <v>202</v>
       </c>
       <c r="O355">
-        <v>17952314</v>
+        <v>17952513</v>
       </c>
       <c r="P355" t="s">
         <v>227</v>
@@ -26687,11 +26687,8 @@
       <c r="T355" t="s">
         <v>244</v>
       </c>
-      <c r="V355" t="s">
-        <v>253</v>
-      </c>
       <c r="W355" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AA355">
         <v>0</v>
@@ -26702,22 +26699,22 @@
     </row>
     <row r="356" spans="1:34">
       <c r="A356">
-        <v>6705</v>
+        <v>6949</v>
       </c>
       <c r="B356" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C356" t="s">
         <v>55</v>
       </c>
       <c r="D356" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E356" t="s">
         <v>59</v>
       </c>
       <c r="F356" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G356">
         <v>943</v>
@@ -26729,7 +26726,7 @@
         <v>69</v>
       </c>
       <c r="J356" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L356" s="1">
         <v>46295</v>
@@ -26741,7 +26738,7 @@
         <v>202</v>
       </c>
       <c r="O356">
-        <v>17952513</v>
+        <v>18178126</v>
       </c>
       <c r="P356" t="s">
         <v>227</v>
@@ -26753,10 +26750,10 @@
         <v>-6</v>
       </c>
       <c r="T356" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="W356" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AA356">
         <v>0</v>
@@ -26767,16 +26764,16 @@
     </row>
     <row r="357" spans="1:34">
       <c r="A357">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B357" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C357" t="s">
         <v>55</v>
       </c>
       <c r="D357" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E357" t="s">
         <v>59</v>
@@ -26794,7 +26791,7 @@
         <v>69</v>
       </c>
       <c r="J357" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L357" s="1">
         <v>46295</v>
@@ -26806,7 +26803,7 @@
         <v>202</v>
       </c>
       <c r="O357">
-        <v>18178126</v>
+        <v>18188710</v>
       </c>
       <c r="P357" t="s">
         <v>227</v>
@@ -26818,10 +26815,10 @@
         <v>-6</v>
       </c>
       <c r="T357" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="W357" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AA357">
         <v>0</v>
@@ -26832,10 +26829,10 @@
     </row>
     <row r="358" spans="1:34">
       <c r="A358">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B358" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C358" t="s">
         <v>55</v>
@@ -26859,7 +26856,7 @@
         <v>69</v>
       </c>
       <c r="J358" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L358" s="1">
         <v>46295</v>
@@ -26871,7 +26868,7 @@
         <v>202</v>
       </c>
       <c r="O358">
-        <v>18188710</v>
+        <v>18188616</v>
       </c>
       <c r="P358" t="s">
         <v>227</v>
@@ -26886,7 +26883,7 @@
         <v>242</v>
       </c>
       <c r="W358" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AA358">
         <v>0</v>
@@ -26897,16 +26894,16 @@
     </row>
     <row r="359" spans="1:34">
       <c r="A359">
-        <v>6963</v>
+        <v>6949</v>
       </c>
       <c r="B359" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C359" t="s">
         <v>55</v>
       </c>
       <c r="D359" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E359" t="s">
         <v>59</v>
@@ -26915,40 +26912,40 @@
         <v>62</v>
       </c>
       <c r="G359">
-        <v>943</v>
+        <v>11056</v>
       </c>
       <c r="H359">
         <v>0</v>
       </c>
       <c r="I359" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J359" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="L359" s="1">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="M359" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N359" t="s">
         <v>202</v>
       </c>
       <c r="O359">
-        <v>18188616</v>
+        <v>18279142</v>
       </c>
       <c r="P359" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q359" t="s">
         <v>237</v>
       </c>
       <c r="S359">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="T359" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="W359" t="s">
         <v>355</v>
@@ -26962,10 +26959,10 @@
     </row>
     <row r="360" spans="1:34">
       <c r="A360">
-        <v>6949</v>
+        <v>6627</v>
       </c>
       <c r="B360" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C360" t="s">
         <v>55</v>
@@ -26974,22 +26971,22 @@
         <v>56</v>
       </c>
       <c r="E360" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F360" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G360">
-        <v>11056</v>
+        <v>7869</v>
       </c>
       <c r="H360">
         <v>0</v>
       </c>
       <c r="I360" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="J360" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="L360" s="1">
         <v>46293</v>
@@ -27001,42 +26998,54 @@
         <v>202</v>
       </c>
       <c r="O360">
-        <v>18279142</v>
+        <v>17042546</v>
       </c>
       <c r="P360" t="s">
-        <v>231</v>
+        <v>208</v>
       </c>
       <c r="Q360" t="s">
-        <v>237</v>
+        <v>235</v>
+      </c>
+      <c r="R360" s="1">
+        <v>46288.76065641204</v>
       </c>
       <c r="S360">
         <v>-4</v>
       </c>
       <c r="T360" t="s">
-        <v>241</v>
+        <v>239</v>
+      </c>
+      <c r="V360" t="s">
+        <v>253</v>
       </c>
       <c r="W360" t="s">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="AA360">
         <v>0</v>
+      </c>
+      <c r="AB360" t="s">
+        <v>458</v>
       </c>
       <c r="AG360" t="s">
         <v>463</v>
       </c>
+      <c r="AH360" t="s">
+        <v>466</v>
+      </c>
     </row>
     <row r="361" spans="1:34">
       <c r="A361">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B361" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C361" t="s">
         <v>55</v>
       </c>
       <c r="D361" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E361" t="s">
         <v>60</v>
@@ -27066,7 +27075,7 @@
         <v>202</v>
       </c>
       <c r="O361">
-        <v>17042546</v>
+        <v>16960048</v>
       </c>
       <c r="P361" t="s">
         <v>208</v>
@@ -27075,7 +27084,7 @@
         <v>235</v>
       </c>
       <c r="R361" s="1">
-        <v>46288.76065641204</v>
+        <v>46288.7606568287</v>
       </c>
       <c r="S361">
         <v>-4</v>
@@ -27104,22 +27113,22 @@
     </row>
     <row r="362" spans="1:34">
       <c r="A362">
-        <v>6628</v>
+        <v>6949</v>
       </c>
       <c r="B362" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C362" t="s">
         <v>55</v>
       </c>
       <c r="D362" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E362" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F362" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G362">
         <v>7869</v>
@@ -27143,25 +27152,22 @@
         <v>202</v>
       </c>
       <c r="O362">
-        <v>16960048</v>
+        <v>18178300</v>
       </c>
       <c r="P362" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Q362" t="s">
         <v>235</v>
       </c>
       <c r="R362" s="1">
-        <v>46288.7606568287</v>
+        <v>46288.76066791666</v>
       </c>
       <c r="S362">
         <v>-4</v>
       </c>
       <c r="T362" t="s">
-        <v>239</v>
-      </c>
-      <c r="V362" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="W362" t="s">
         <v>341</v>
@@ -27176,30 +27182,30 @@
         <v>463</v>
       </c>
       <c r="AH362" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
     </row>
     <row r="363" spans="1:34">
       <c r="A363">
-        <v>6949</v>
+        <v>6628</v>
       </c>
       <c r="B363" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C363" t="s">
         <v>55</v>
       </c>
       <c r="D363" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E363" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F363" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G363">
-        <v>7869</v>
+        <v>1650</v>
       </c>
       <c r="H363">
         <v>0</v>
@@ -27208,57 +27214,54 @@
         <v>64</v>
       </c>
       <c r="J363" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="L363" s="1">
         <v>46293</v>
       </c>
-      <c r="M363" t="s">
-        <v>193</v>
-      </c>
       <c r="N363" t="s">
         <v>202</v>
       </c>
       <c r="O363">
-        <v>18178300</v>
+        <v>16959974</v>
       </c>
       <c r="P363" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q363" t="s">
         <v>235</v>
       </c>
       <c r="R363" s="1">
-        <v>46288.76066791666</v>
+        <v>46265.00248284722</v>
       </c>
       <c r="S363">
         <v>-4</v>
       </c>
       <c r="T363" t="s">
-        <v>241</v>
-      </c>
-      <c r="W363" t="s">
-        <v>341</v>
+        <v>239</v>
+      </c>
+      <c r="V363" t="s">
+        <v>253</v>
       </c>
       <c r="AA363">
         <v>0</v>
       </c>
       <c r="AB363" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AG363" t="s">
         <v>463</v>
       </c>
       <c r="AH363" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
     </row>
     <row r="364" spans="1:34">
       <c r="A364">
-        <v>6628</v>
+        <v>6945</v>
       </c>
       <c r="B364" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C364" t="s">
         <v>55</v>
@@ -27267,10 +27270,10 @@
         <v>57</v>
       </c>
       <c r="E364" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F364" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G364">
         <v>1650</v>
@@ -27282,7 +27285,7 @@
         <v>64</v>
       </c>
       <c r="J364" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L364" s="1">
         <v>46293</v>
@@ -27291,25 +27294,22 @@
         <v>202</v>
       </c>
       <c r="O364">
-        <v>16959974</v>
+        <v>18163667</v>
       </c>
       <c r="P364" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q364" t="s">
         <v>235</v>
       </c>
       <c r="R364" s="1">
-        <v>46265.00248284722</v>
+        <v>46265.00255472222</v>
       </c>
       <c r="S364">
         <v>-4</v>
       </c>
       <c r="T364" t="s">
-        <v>239</v>
-      </c>
-      <c r="V364" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="AA364">
         <v>0</v>
@@ -27326,25 +27326,25 @@
     </row>
     <row r="365" spans="1:34">
       <c r="A365">
-        <v>6945</v>
+        <v>6548</v>
       </c>
       <c r="B365" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C365" t="s">
         <v>55</v>
       </c>
       <c r="D365" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E365" t="s">
         <v>59</v>
       </c>
       <c r="F365" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G365">
-        <v>1650</v>
+        <v>1652</v>
       </c>
       <c r="H365">
         <v>0</v>
@@ -27356,28 +27356,34 @@
         <v>141</v>
       </c>
       <c r="L365" s="1">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="N365" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="O365">
-        <v>18163667</v>
+        <v>17967989</v>
       </c>
       <c r="P365" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="Q365" t="s">
         <v>235</v>
       </c>
       <c r="R365" s="1">
-        <v>46265.00255472222</v>
+        <v>46234.66180127315</v>
       </c>
       <c r="S365">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="T365" t="s">
-        <v>240</v>
+        <v>238</v>
+      </c>
+      <c r="V365" t="s">
+        <v>253</v>
+      </c>
+      <c r="W365" t="s">
+        <v>356</v>
       </c>
       <c r="AA365">
         <v>0</v>
@@ -27386,18 +27392,18 @@
         <v>456</v>
       </c>
       <c r="AG365" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AH365" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
     </row>
     <row r="366" spans="1:34">
       <c r="A366">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B366" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C366" t="s">
         <v>55</v>
@@ -27406,7 +27412,7 @@
         <v>56</v>
       </c>
       <c r="E366" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F366" t="s">
         <v>61</v>
@@ -27421,7 +27427,7 @@
         <v>64</v>
       </c>
       <c r="J366" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L366" s="1">
         <v>46290</v>
@@ -27430,22 +27436,22 @@
         <v>205</v>
       </c>
       <c r="O366">
-        <v>17967989</v>
+        <v>17042389</v>
       </c>
       <c r="P366" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q366" t="s">
         <v>235</v>
       </c>
       <c r="R366" s="1">
-        <v>46234.66180127315</v>
+        <v>46245.76585582176</v>
       </c>
       <c r="S366">
         <v>-1</v>
       </c>
       <c r="T366" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="V366" t="s">
         <v>253</v>
@@ -27463,30 +27469,30 @@
         <v>464</v>
       </c>
       <c r="AH366" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
     </row>
     <row r="367" spans="1:34">
       <c r="A367">
-        <v>6627</v>
+        <v>6945</v>
       </c>
       <c r="B367" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C367" t="s">
         <v>55</v>
       </c>
       <c r="D367" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E367" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F367" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G367">
-        <v>1652</v>
+        <v>9764</v>
       </c>
       <c r="H367">
         <v>0</v>
@@ -27495,34 +27501,31 @@
         <v>64</v>
       </c>
       <c r="J367" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="L367" s="1">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="N367" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="O367">
-        <v>17042389</v>
+        <v>18200045</v>
       </c>
       <c r="P367" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q367" t="s">
         <v>235</v>
       </c>
       <c r="R367" s="1">
-        <v>46245.76585582176</v>
+        <v>46288.43167056713</v>
       </c>
       <c r="S367">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="T367" t="s">
-        <v>239</v>
-      </c>
-      <c r="V367" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="W367" t="s">
         <v>358</v>
@@ -27534,7 +27537,7 @@
         <v>456</v>
       </c>
       <c r="AG367" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AH367" t="s">
         <v>466</v>
@@ -27542,81 +27545,81 @@
     </row>
     <row r="368" spans="1:34">
       <c r="A368">
-        <v>6945</v>
+        <v>6548</v>
       </c>
       <c r="B368" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C368" t="s">
         <v>55</v>
       </c>
       <c r="D368" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E368" t="s">
         <v>59</v>
       </c>
       <c r="F368" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G368">
-        <v>9764</v>
+        <v>1697</v>
       </c>
       <c r="H368">
-        <v>0</v>
+        <v>1650</v>
       </c>
       <c r="I368" t="s">
         <v>64</v>
       </c>
       <c r="J368" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="L368" s="1">
-        <v>46295</v>
+        <v>46286</v>
       </c>
       <c r="N368" t="s">
         <v>202</v>
       </c>
       <c r="O368">
-        <v>18200045</v>
+        <v>17968001</v>
       </c>
       <c r="P368" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="Q368" t="s">
         <v>235</v>
       </c>
       <c r="R368" s="1">
-        <v>46288.43167056713</v>
+        <v>46282.62254486111</v>
       </c>
       <c r="S368">
-        <v>-6</v>
+        <v>3</v>
       </c>
       <c r="T368" t="s">
-        <v>240</v>
-      </c>
-      <c r="W368" t="s">
-        <v>359</v>
+        <v>238</v>
+      </c>
+      <c r="V368" t="s">
+        <v>253</v>
       </c>
       <c r="AA368">
         <v>0</v>
       </c>
       <c r="AB368" t="s">
-        <v>456</v>
+        <v>207</v>
       </c>
       <c r="AG368" t="s">
         <v>463</v>
       </c>
       <c r="AH368" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
     </row>
     <row r="369" spans="1:34">
       <c r="A369">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B369" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C369" t="s">
         <v>55</v>
@@ -27625,7 +27628,7 @@
         <v>56</v>
       </c>
       <c r="E369" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F369" t="s">
         <v>61</v>
@@ -27640,54 +27643,60 @@
         <v>64</v>
       </c>
       <c r="J369" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L369" s="1">
         <v>46286</v>
       </c>
+      <c r="M369" t="s">
+        <v>195</v>
+      </c>
       <c r="N369" t="s">
         <v>202</v>
       </c>
       <c r="O369">
-        <v>17968001</v>
+        <v>17042403</v>
       </c>
       <c r="P369" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q369" t="s">
         <v>235</v>
       </c>
       <c r="R369" s="1">
-        <v>46282.62254486111</v>
+        <v>46286.64173940972</v>
       </c>
       <c r="S369">
         <v>3</v>
       </c>
       <c r="T369" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="V369" t="s">
         <v>253</v>
       </c>
+      <c r="W369" t="s">
+        <v>359</v>
+      </c>
       <c r="AA369">
         <v>0</v>
       </c>
       <c r="AB369" t="s">
-        <v>207</v>
+        <v>459</v>
       </c>
       <c r="AG369" t="s">
         <v>463</v>
       </c>
       <c r="AH369" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
     </row>
     <row r="370" spans="1:34">
       <c r="A370">
-        <v>6627</v>
+        <v>6949</v>
       </c>
       <c r="B370" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C370" t="s">
         <v>55</v>
@@ -27696,10 +27705,10 @@
         <v>56</v>
       </c>
       <c r="E370" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F370" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G370">
         <v>1697</v>
@@ -27711,60 +27720,51 @@
         <v>64</v>
       </c>
       <c r="J370" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L370" s="1">
         <v>46286</v>
       </c>
-      <c r="M370" t="s">
-        <v>195</v>
-      </c>
       <c r="N370" t="s">
         <v>202</v>
       </c>
       <c r="O370">
-        <v>17042403</v>
+        <v>18178280</v>
       </c>
       <c r="P370" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Q370" t="s">
         <v>235</v>
       </c>
       <c r="R370" s="1">
-        <v>46286.64173940972</v>
+        <v>46283.44840582176</v>
       </c>
       <c r="S370">
         <v>3</v>
       </c>
       <c r="T370" t="s">
-        <v>239</v>
-      </c>
-      <c r="V370" t="s">
-        <v>253</v>
-      </c>
-      <c r="W370" t="s">
-        <v>360</v>
+        <v>241</v>
       </c>
       <c r="AA370">
         <v>0</v>
       </c>
       <c r="AB370" t="s">
-        <v>459</v>
+        <v>207</v>
       </c>
       <c r="AG370" t="s">
         <v>463</v>
       </c>
       <c r="AH370" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
     </row>
     <row r="371" spans="1:34">
       <c r="A371">
-        <v>6949</v>
+        <v>6704</v>
       </c>
       <c r="B371" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C371" t="s">
         <v>55</v>
@@ -27776,63 +27776,66 @@
         <v>59</v>
       </c>
       <c r="F371" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G371">
-        <v>1697</v>
+        <v>7868</v>
       </c>
       <c r="H371">
-        <v>1650</v>
+        <v>0</v>
       </c>
       <c r="I371" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J371" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="L371" s="1">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="N371" t="s">
         <v>202</v>
       </c>
       <c r="O371">
-        <v>18178280</v>
+        <v>17955421</v>
       </c>
       <c r="P371" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="Q371" t="s">
         <v>235</v>
       </c>
       <c r="R371" s="1">
-        <v>46283.44840582176</v>
+        <v>46267.47365627315</v>
       </c>
       <c r="S371">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="T371" t="s">
-        <v>241</v>
+        <v>244</v>
+      </c>
+      <c r="V371" t="s">
+        <v>253</v>
       </c>
       <c r="AA371">
         <v>0</v>
       </c>
       <c r="AB371" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="AG371" t="s">
         <v>463</v>
       </c>
       <c r="AH371" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="372" spans="1:34">
       <c r="A372">
-        <v>6704</v>
+        <v>5417</v>
       </c>
       <c r="B372" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C372" t="s">
         <v>55</v>
@@ -27847,7 +27850,7 @@
         <v>61</v>
       </c>
       <c r="G372">
-        <v>7868</v>
+        <v>6890</v>
       </c>
       <c r="H372">
         <v>0</v>
@@ -27856,46 +27859,49 @@
         <v>65</v>
       </c>
       <c r="J372" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="L372" s="1">
-        <v>46293</v>
+        <v>46290</v>
+      </c>
+      <c r="M372" t="s">
+        <v>191</v>
       </c>
       <c r="N372" t="s">
         <v>202</v>
       </c>
       <c r="O372">
-        <v>17955421</v>
+        <v>17399260</v>
       </c>
       <c r="P372" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q372" t="s">
         <v>235</v>
       </c>
       <c r="R372" s="1">
-        <v>46267.47365627315</v>
+        <v>46287.48052434028</v>
       </c>
       <c r="S372">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="T372" t="s">
-        <v>244</v>
-      </c>
-      <c r="V372" t="s">
-        <v>253</v>
+        <v>243</v>
+      </c>
+      <c r="W372" t="s">
+        <v>338</v>
       </c>
       <c r="AA372">
         <v>0</v>
       </c>
       <c r="AB372" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AG372" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AH372" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
     </row>
     <row r="373" spans="1:34">
@@ -27918,7 +27924,7 @@
         <v>61</v>
       </c>
       <c r="G373">
-        <v>6890</v>
+        <v>11276</v>
       </c>
       <c r="H373">
         <v>0</v>
@@ -27927,19 +27933,16 @@
         <v>65</v>
       </c>
       <c r="J373" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="L373" s="1">
-        <v>46290</v>
-      </c>
-      <c r="M373" t="s">
-        <v>191</v>
+        <v>46283</v>
       </c>
       <c r="N373" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="O373">
-        <v>17399260</v>
+        <v>17399423</v>
       </c>
       <c r="P373" t="s">
         <v>211</v>
@@ -27948,25 +27951,22 @@
         <v>235</v>
       </c>
       <c r="R373" s="1">
-        <v>46287.48052434028</v>
+        <v>46266.47620831019</v>
       </c>
       <c r="S373">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T373" t="s">
         <v>243</v>
       </c>
-      <c r="W373" t="s">
-        <v>338</v>
-      </c>
       <c r="AA373">
         <v>0</v>
       </c>
       <c r="AB373" t="s">
-        <v>211</v>
+        <v>460</v>
       </c>
       <c r="AG373" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="AH373" t="s">
         <v>461</v>
@@ -27974,10 +27974,10 @@
     </row>
     <row r="374" spans="1:34">
       <c r="A374">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B374" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C374" t="s">
         <v>55</v>
@@ -28001,7 +28001,7 @@
         <v>65</v>
       </c>
       <c r="J374" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L374" s="1">
         <v>46283</v>
@@ -28010,28 +28010,31 @@
         <v>204</v>
       </c>
       <c r="O374">
-        <v>17399423</v>
+        <v>18152557</v>
       </c>
       <c r="P374" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="Q374" t="s">
         <v>235</v>
       </c>
       <c r="R374" s="1">
-        <v>46266.47620831019</v>
+        <v>46267.57586420139</v>
       </c>
       <c r="S374">
         <v>6</v>
       </c>
       <c r="T374" t="s">
-        <v>243</v>
+        <v>245</v>
+      </c>
+      <c r="V374" t="s">
+        <v>253</v>
       </c>
       <c r="AA374">
         <v>0</v>
       </c>
       <c r="AB374" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG374" t="s">
         <v>463</v>
@@ -28042,10 +28045,10 @@
     </row>
     <row r="375" spans="1:34">
       <c r="A375">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B375" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C375" t="s">
         <v>55</v>
@@ -28060,7 +28063,7 @@
         <v>61</v>
       </c>
       <c r="G375">
-        <v>11276</v>
+        <v>1583</v>
       </c>
       <c r="H375">
         <v>0</v>
@@ -28069,43 +28072,40 @@
         <v>65</v>
       </c>
       <c r="J375" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L375" s="1">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="N375" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O375">
-        <v>18152557</v>
+        <v>17398917</v>
       </c>
       <c r="P375" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="Q375" t="s">
         <v>235</v>
       </c>
       <c r="R375" s="1">
-        <v>46267.57586420139</v>
+        <v>46233.72355880787</v>
       </c>
       <c r="S375">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="T375" t="s">
-        <v>245</v>
-      </c>
-      <c r="V375" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="AA375">
         <v>0</v>
       </c>
       <c r="AB375" t="s">
-        <v>461</v>
+        <v>211</v>
       </c>
       <c r="AG375" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AH375" t="s">
         <v>461</v>
@@ -28113,10 +28113,10 @@
     </row>
     <row r="376" spans="1:34">
       <c r="A376">
-        <v>5417</v>
+        <v>5617</v>
       </c>
       <c r="B376" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C376" t="s">
         <v>55</v>
@@ -28140,7 +28140,7 @@
         <v>65</v>
       </c>
       <c r="J376" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L376" s="1">
         <v>46290</v>
@@ -28149,42 +28149,36 @@
         <v>205</v>
       </c>
       <c r="O376">
-        <v>17398917</v>
-      </c>
-      <c r="P376" t="s">
-        <v>211</v>
+        <v>17407553</v>
       </c>
       <c r="Q376" t="s">
         <v>235</v>
       </c>
       <c r="R376" s="1">
-        <v>46233.72355880787</v>
+        <v>46261.36669849537</v>
       </c>
       <c r="S376">
         <v>-1</v>
       </c>
       <c r="T376" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="AA376">
         <v>0</v>
       </c>
       <c r="AB376" t="s">
-        <v>211</v>
+        <v>453</v>
       </c>
       <c r="AG376" t="s">
         <v>464</v>
       </c>
-      <c r="AH376" t="s">
-        <v>461</v>
-      </c>
     </row>
     <row r="377" spans="1:34">
       <c r="A377">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B377" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C377" t="s">
         <v>55</v>
@@ -28196,7 +28190,7 @@
         <v>59</v>
       </c>
       <c r="F377" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G377">
         <v>1583</v>
@@ -28208,7 +28202,7 @@
         <v>65</v>
       </c>
       <c r="J377" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L377" s="1">
         <v>46290</v>
@@ -28217,13 +28211,13 @@
         <v>205</v>
       </c>
       <c r="O377">
-        <v>17407553</v>
+        <v>17688645</v>
       </c>
       <c r="Q377" t="s">
         <v>235</v>
       </c>
       <c r="R377" s="1">
-        <v>46261.36669849537</v>
+        <v>46266.44156952546</v>
       </c>
       <c r="S377">
         <v>-1</v>
@@ -28231,11 +28225,14 @@
       <c r="T377" t="s">
         <v>248</v>
       </c>
+      <c r="V377" t="s">
+        <v>253</v>
+      </c>
       <c r="AA377">
         <v>0</v>
       </c>
       <c r="AB377" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="AG377" t="s">
         <v>464</v>
@@ -28243,10 +28240,10 @@
     </row>
     <row r="378" spans="1:34">
       <c r="A378">
-        <v>6224</v>
+        <v>6278</v>
       </c>
       <c r="B378" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C378" t="s">
         <v>55</v>
@@ -28258,7 +28255,7 @@
         <v>59</v>
       </c>
       <c r="F378" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G378">
         <v>1583</v>
@@ -28270,7 +28267,7 @@
         <v>65</v>
       </c>
       <c r="J378" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L378" s="1">
         <v>46290</v>
@@ -28279,28 +28276,31 @@
         <v>205</v>
       </c>
       <c r="O378">
-        <v>17688645</v>
+        <v>18166312</v>
       </c>
       <c r="Q378" t="s">
         <v>235</v>
       </c>
       <c r="R378" s="1">
-        <v>46266.44156952546</v>
+        <v>46233.50562820602</v>
       </c>
       <c r="S378">
         <v>-1</v>
       </c>
       <c r="T378" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="V378" t="s">
         <v>253</v>
       </c>
+      <c r="W378" t="s">
+        <v>360</v>
+      </c>
       <c r="AA378">
         <v>0</v>
       </c>
       <c r="AB378" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="AG378" t="s">
         <v>464</v>
@@ -28308,10 +28308,10 @@
     </row>
     <row r="379" spans="1:34">
       <c r="A379">
-        <v>6278</v>
+        <v>6486</v>
       </c>
       <c r="B379" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C379" t="s">
         <v>55</v>
@@ -28335,7 +28335,7 @@
         <v>65</v>
       </c>
       <c r="J379" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L379" s="1">
         <v>46290</v>
@@ -28344,42 +28344,45 @@
         <v>205</v>
       </c>
       <c r="O379">
-        <v>18166312</v>
+        <v>18114208</v>
+      </c>
+      <c r="P379" t="s">
+        <v>229</v>
       </c>
       <c r="Q379" t="s">
         <v>235</v>
       </c>
       <c r="R379" s="1">
-        <v>46233.50562820602</v>
+        <v>46233.80164280093</v>
       </c>
       <c r="S379">
         <v>-1</v>
       </c>
       <c r="T379" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="V379" t="s">
         <v>253</v>
       </c>
-      <c r="W379" t="s">
-        <v>361</v>
-      </c>
       <c r="AA379">
         <v>0</v>
       </c>
       <c r="AB379" t="s">
-        <v>456</v>
+        <v>229</v>
       </c>
       <c r="AG379" t="s">
         <v>464</v>
       </c>
+      <c r="AH379" t="s">
+        <v>461</v>
+      </c>
     </row>
     <row r="380" spans="1:34">
       <c r="A380">
-        <v>6486</v>
+        <v>6704</v>
       </c>
       <c r="B380" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C380" t="s">
         <v>55</v>
@@ -28403,7 +28406,7 @@
         <v>65</v>
       </c>
       <c r="J380" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L380" s="1">
         <v>46290</v>
@@ -28412,22 +28415,22 @@
         <v>205</v>
       </c>
       <c r="O380">
-        <v>18114208</v>
+        <v>17955373</v>
       </c>
       <c r="P380" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="Q380" t="s">
         <v>235</v>
       </c>
       <c r="R380" s="1">
-        <v>46233.80164280093</v>
+        <v>46232.72913953703</v>
       </c>
       <c r="S380">
         <v>-1</v>
       </c>
       <c r="T380" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="V380" t="s">
         <v>253</v>
@@ -28436,21 +28439,21 @@
         <v>0</v>
       </c>
       <c r="AB380" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="AG380" t="s">
         <v>464</v>
       </c>
       <c r="AH380" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
     </row>
     <row r="381" spans="1:34">
       <c r="A381">
-        <v>6704</v>
+        <v>5417</v>
       </c>
       <c r="B381" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C381" t="s">
         <v>55</v>
@@ -28465,7 +28468,7 @@
         <v>61</v>
       </c>
       <c r="G381">
-        <v>1583</v>
+        <v>11514</v>
       </c>
       <c r="H381">
         <v>0</v>
@@ -28474,46 +28477,49 